--- a/設備点検表.xlsx
+++ b/設備点検表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kosuk\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C203E09-9A76-4796-9632-130647BA660F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A366A603-2684-417E-AFEF-0C428427669C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-610" yWindow="930" windowWidth="15500" windowHeight="11280" xr2:uid="{6C56CF13-AF7F-4C1F-982C-EF388A11F51A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6C56CF13-AF7F-4C1F-982C-EF388A11F51A}"/>
   </bookViews>
   <sheets>
     <sheet name="日常～週" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="136">
   <si>
     <t>改版</t>
     <rPh sb="0" eb="2">
@@ -1176,10 +1176,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>８</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>稼働状況　［稼働：✔　非稼働：／ ］</t>
     <rPh sb="6" eb="8">
       <t>カドウ</t>
@@ -1310,13 +1306,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="176" formatCode="m"/>
     <numFmt numFmtId="177" formatCode="m/d;@"/>
     <numFmt numFmtId="178" formatCode="@&quot;年&quot;"/>
-    <numFmt numFmtId="179" formatCode="@&quot;月&quot;"/>
-    <numFmt numFmtId="180" formatCode="d"/>
-    <numFmt numFmtId="181" formatCode="@&quot; 年度&quot;"/>
+    <numFmt numFmtId="179" formatCode="d"/>
+    <numFmt numFmtId="180" formatCode="@&quot; 年度&quot;"/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -1514,7 +1509,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="76">
+  <borders count="78">
     <border>
       <left/>
       <right/>
@@ -2419,6 +2414,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2426,7 +2449,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="180">
+  <cellXfs count="194">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2592,23 +2615,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2691,26 +2699,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="13" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="26" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2727,46 +2726,46 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2793,19 +2792,19 @@
     <xf numFmtId="178" fontId="12" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="25" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
@@ -2832,41 +2831,59 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="71" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -2877,22 +2894,46 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="73" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="25" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="67" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="25" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="74" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="25" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="25" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="25" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="25" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="25" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="25" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="25" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="25" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="75" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2910,19 +2951,43 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="13" fillId="0" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="13" fillId="0" borderId="67" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="13" fillId="0" borderId="74" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="77" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2930,11 +2995,15 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準_設備点検表書式" xfId="1" xr:uid="{15F629F0-A893-4DD8-8A94-9D447F97F79C}"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="12">
     <dxf>
+      <font>
+        <strike val="0"/>
+        <color theme="1"/>
+      </font>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2956,6 +3025,89 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2970,9 +3122,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3010,7 +3162,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3116,7 +3268,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3258,7 +3410,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3280,45 +3432,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:254" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A1" s="153" t="s">
+      <c r="A1" s="108" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="153"/>
-      <c r="C1" s="90"/>
-      <c r="F1" s="154" t="s">
+      <c r="B1" s="108"/>
+      <c r="C1" s="85"/>
+      <c r="F1" s="109" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="154"/>
-      <c r="H1" s="154"/>
-      <c r="I1" s="154"/>
-      <c r="J1" s="154"/>
-      <c r="K1" s="154"/>
-      <c r="L1" s="154"/>
-      <c r="M1" s="154"/>
-      <c r="N1" s="154"/>
-      <c r="O1" s="154"/>
-      <c r="P1" s="154"/>
-      <c r="Q1" s="154"/>
-      <c r="R1" s="154"/>
-      <c r="S1" s="154"/>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="154"/>
-      <c r="W1" s="154"/>
-      <c r="X1" s="154"/>
-      <c r="Y1" s="154"/>
-      <c r="Z1" s="154"/>
-      <c r="AA1" s="154"/>
-      <c r="AB1" s="154"/>
-      <c r="AC1" s="154"/>
-      <c r="AD1" s="154"/>
-      <c r="AE1" s="154"/>
-      <c r="AF1" s="154"/>
-      <c r="AG1" s="154"/>
-      <c r="AH1" s="154"/>
-      <c r="AI1" s="154"/>
-      <c r="AJ1" s="154"/>
-      <c r="AK1" s="154"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
+      <c r="V1" s="109"/>
+      <c r="W1" s="109"/>
+      <c r="X1" s="109"/>
+      <c r="Y1" s="109"/>
+      <c r="Z1" s="109"/>
+      <c r="AA1" s="109"/>
+      <c r="AB1" s="109"/>
+      <c r="AC1" s="109"/>
+      <c r="AD1" s="109"/>
+      <c r="AE1" s="109"/>
+      <c r="AF1" s="109"/>
+      <c r="AG1" s="109"/>
+      <c r="AH1" s="109"/>
+      <c r="AI1" s="109"/>
+      <c r="AJ1" s="109"/>
+      <c r="AK1" s="109"/>
       <c r="AN1" s="3"/>
       <c r="AO1" s="3"/>
       <c r="AP1" s="3"/>
@@ -3789,52 +3941,52 @@
       <c r="IT2" s="3"/>
     </row>
     <row r="3" spans="1:254" s="2" customFormat="1" ht="20" customHeight="1" thickBot="1">
-      <c r="A3" s="155" t="s">
+      <c r="A3" s="110" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="157"/>
-      <c r="E3" s="99"/>
+      <c r="B3" s="111"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="94"/>
       <c r="G3" s="51"/>
       <c r="H3" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="151" t="s">
+      <c r="K3" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="151"/>
-      <c r="M3" s="151" t="s">
+      <c r="L3" s="113"/>
+      <c r="M3" s="113" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="151"/>
-      <c r="O3" s="151"/>
-      <c r="P3" s="151" t="s">
+      <c r="N3" s="113"/>
+      <c r="O3" s="113"/>
+      <c r="P3" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="Q3" s="151"/>
-      <c r="R3" s="151"/>
+      <c r="Q3" s="113"/>
+      <c r="R3" s="113"/>
       <c r="S3" s="3"/>
-      <c r="T3" s="158" t="s">
+      <c r="T3" s="114" t="s">
         <v>3</v>
       </c>
-      <c r="U3" s="159"/>
-      <c r="V3" s="159"/>
-      <c r="W3" s="159"/>
-      <c r="X3" s="159"/>
-      <c r="Y3" s="159"/>
-      <c r="Z3" s="159"/>
-      <c r="AA3" s="159"/>
-      <c r="AB3" s="159"/>
-      <c r="AC3" s="159"/>
-      <c r="AD3" s="159"/>
-      <c r="AE3" s="159"/>
-      <c r="AF3" s="159"/>
-      <c r="AG3" s="159"/>
-      <c r="AH3" s="159"/>
-      <c r="AI3" s="159"/>
-      <c r="AJ3" s="159"/>
-      <c r="AK3" s="160"/>
+      <c r="U3" s="115"/>
+      <c r="V3" s="115"/>
+      <c r="W3" s="115"/>
+      <c r="X3" s="115"/>
+      <c r="Y3" s="115"/>
+      <c r="Z3" s="115"/>
+      <c r="AA3" s="115"/>
+      <c r="AB3" s="115"/>
+      <c r="AC3" s="115"/>
+      <c r="AD3" s="115"/>
+      <c r="AE3" s="115"/>
+      <c r="AF3" s="115"/>
+      <c r="AG3" s="115"/>
+      <c r="AH3" s="115"/>
+      <c r="AI3" s="115"/>
+      <c r="AJ3" s="115"/>
+      <c r="AK3" s="116"/>
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
@@ -4063,47 +4215,47 @@
       <c r="H4" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="151" t="s">
+      <c r="K4" s="113" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="151"/>
-      <c r="M4" s="152">
+      <c r="L4" s="113"/>
+      <c r="M4" s="119">
         <v>46113</v>
       </c>
-      <c r="N4" s="152"/>
-      <c r="O4" s="152"/>
-      <c r="P4" s="151" t="s">
+      <c r="N4" s="119"/>
+      <c r="O4" s="119"/>
+      <c r="P4" s="113" t="s">
         <v>50</v>
       </c>
-      <c r="Q4" s="151"/>
-      <c r="R4" s="151"/>
+      <c r="Q4" s="113"/>
+      <c r="R4" s="113"/>
       <c r="S4" s="3"/>
-      <c r="T4" s="128" t="s">
+      <c r="T4" s="120" t="s">
         <v>5</v>
       </c>
-      <c r="U4" s="129"/>
-      <c r="V4" s="129"/>
-      <c r="W4" s="129"/>
-      <c r="X4" s="129"/>
-      <c r="Y4" s="130"/>
-      <c r="Z4" s="128" t="s">
+      <c r="U4" s="121"/>
+      <c r="V4" s="121"/>
+      <c r="W4" s="121"/>
+      <c r="X4" s="121"/>
+      <c r="Y4" s="122"/>
+      <c r="Z4" s="120" t="s">
         <v>6</v>
       </c>
-      <c r="AA4" s="129"/>
-      <c r="AB4" s="129"/>
-      <c r="AC4" s="130"/>
-      <c r="AD4" s="128" t="s">
+      <c r="AA4" s="121"/>
+      <c r="AB4" s="121"/>
+      <c r="AC4" s="122"/>
+      <c r="AD4" s="120" t="s">
         <v>7</v>
       </c>
-      <c r="AE4" s="129"/>
-      <c r="AF4" s="129"/>
-      <c r="AG4" s="130"/>
-      <c r="AH4" s="128" t="s">
+      <c r="AE4" s="121"/>
+      <c r="AF4" s="121"/>
+      <c r="AG4" s="122"/>
+      <c r="AH4" s="120" t="s">
         <v>8</v>
       </c>
-      <c r="AI4" s="129"/>
-      <c r="AJ4" s="129"/>
-      <c r="AK4" s="130"/>
+      <c r="AI4" s="121"/>
+      <c r="AJ4" s="121"/>
+      <c r="AK4" s="122"/>
       <c r="AN4" s="3"/>
       <c r="AO4" s="3"/>
       <c r="AP4" s="3"/>
@@ -4331,16 +4483,16 @@
         <v>23</v>
       </c>
       <c r="S5" s="3"/>
-      <c r="T5" s="131" t="s">
+      <c r="T5" s="123" t="s">
         <v>64</v>
       </c>
-      <c r="U5" s="132"/>
-      <c r="V5" s="132"/>
-      <c r="W5" s="136" t="s">
-        <v>124</v>
-      </c>
-      <c r="X5" s="137"/>
-      <c r="Y5" s="138"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="124"/>
+      <c r="W5" s="128">
+        <v>7</v>
+      </c>
+      <c r="X5" s="129"/>
+      <c r="Y5" s="130"/>
       <c r="Z5" s="11"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
@@ -4349,10 +4501,10 @@
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
       <c r="AG5" s="12"/>
-      <c r="AH5" s="141"/>
-      <c r="AI5" s="142"/>
-      <c r="AJ5" s="142"/>
-      <c r="AK5" s="143"/>
+      <c r="AH5" s="133"/>
+      <c r="AI5" s="134"/>
+      <c r="AJ5" s="134"/>
+      <c r="AK5" s="135"/>
       <c r="AN5" s="3"/>
       <c r="AO5" s="3"/>
       <c r="AP5" s="3"/>
@@ -4584,12 +4736,12 @@
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
-      <c r="T6" s="133"/>
-      <c r="U6" s="132"/>
-      <c r="V6" s="132"/>
-      <c r="W6" s="137"/>
-      <c r="X6" s="137"/>
-      <c r="Y6" s="138"/>
+      <c r="T6" s="125"/>
+      <c r="U6" s="124"/>
+      <c r="V6" s="124"/>
+      <c r="W6" s="129"/>
+      <c r="X6" s="129"/>
+      <c r="Y6" s="130"/>
       <c r="Z6" s="11"/>
       <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
@@ -4598,10 +4750,10 @@
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
       <c r="AG6" s="12"/>
-      <c r="AH6" s="141"/>
-      <c r="AI6" s="142"/>
-      <c r="AJ6" s="142"/>
-      <c r="AK6" s="143"/>
+      <c r="AH6" s="133"/>
+      <c r="AI6" s="134"/>
+      <c r="AJ6" s="134"/>
+      <c r="AK6" s="135"/>
       <c r="AN6" s="3"/>
       <c r="AO6" s="3"/>
       <c r="AP6" s="3"/>
@@ -4833,12 +4985,12 @@
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
-      <c r="T7" s="134"/>
-      <c r="U7" s="135"/>
-      <c r="V7" s="135"/>
-      <c r="W7" s="139"/>
-      <c r="X7" s="139"/>
-      <c r="Y7" s="140"/>
+      <c r="T7" s="126"/>
+      <c r="U7" s="127"/>
+      <c r="V7" s="127"/>
+      <c r="W7" s="131"/>
+      <c r="X7" s="131"/>
+      <c r="Y7" s="132"/>
       <c r="Z7" s="21"/>
       <c r="AA7" s="22"/>
       <c r="AB7" s="22"/>
@@ -4847,11 +4999,11 @@
       <c r="AE7" s="22"/>
       <c r="AF7" s="22"/>
       <c r="AG7" s="23"/>
-      <c r="AH7" s="144"/>
-      <c r="AI7" s="145"/>
-      <c r="AJ7" s="145"/>
-      <c r="AK7" s="146"/>
-      <c r="AL7" s="91"/>
+      <c r="AH7" s="136"/>
+      <c r="AI7" s="137"/>
+      <c r="AJ7" s="137"/>
+      <c r="AK7" s="138"/>
+      <c r="AL7" s="86"/>
       <c r="AN7" s="3"/>
       <c r="AO7" s="3"/>
       <c r="AP7" s="3"/>
@@ -5075,8 +5227,8 @@
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
-      <c r="G8" s="111" t="s">
-        <v>125</v>
+      <c r="G8" s="103" t="s">
+        <v>124</v>
       </c>
       <c r="H8" s="24"/>
       <c r="I8" s="24"/>
@@ -5143,23 +5295,23 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AH8" s="103" t="str">
+      <c r="AH8" s="98" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AI8" s="103" t="str">
+      <c r="AI8" s="98" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AJ8" s="103" t="str">
+      <c r="AJ8" s="98" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AK8" s="103" t="str">
+      <c r="AK8" s="98" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AL8" s="92"/>
+      <c r="AL8" s="87"/>
       <c r="AN8" s="3"/>
       <c r="AO8" s="3"/>
       <c r="AP8" s="3"/>
@@ -5389,131 +5541,131 @@
         <v>48</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="G9" s="102">
+        <v>125</v>
+      </c>
+      <c r="G9" s="97">
         <f>DATE($T$5,$W$5,1)</f>
-        <v>46235</v>
-      </c>
-      <c r="H9" s="102">
+        <v>46204</v>
+      </c>
+      <c r="H9" s="97">
         <f>DATE($T$5,$W$5,2)</f>
-        <v>46236</v>
-      </c>
-      <c r="I9" s="102">
+        <v>46205</v>
+      </c>
+      <c r="I9" s="97">
         <f>DATE($T$5,$W$5,3)</f>
-        <v>46237</v>
-      </c>
-      <c r="J9" s="102">
+        <v>46206</v>
+      </c>
+      <c r="J9" s="97">
         <f t="shared" ref="J9:AK9" si="1">I9+1</f>
-        <v>46238</v>
-      </c>
-      <c r="K9" s="102">
+        <v>46207</v>
+      </c>
+      <c r="K9" s="97">
         <f t="shared" si="1"/>
-        <v>46239</v>
-      </c>
-      <c r="L9" s="102">
+        <v>46208</v>
+      </c>
+      <c r="L9" s="97">
         <f t="shared" si="1"/>
-        <v>46240</v>
-      </c>
-      <c r="M9" s="102">
+        <v>46209</v>
+      </c>
+      <c r="M9" s="97">
         <f t="shared" si="1"/>
-        <v>46241</v>
-      </c>
-      <c r="N9" s="102">
+        <v>46210</v>
+      </c>
+      <c r="N9" s="97">
         <f t="shared" si="1"/>
-        <v>46242</v>
-      </c>
-      <c r="O9" s="102">
+        <v>46211</v>
+      </c>
+      <c r="O9" s="97">
         <f t="shared" si="1"/>
-        <v>46243</v>
-      </c>
-      <c r="P9" s="102">
+        <v>46212</v>
+      </c>
+      <c r="P9" s="97">
         <f t="shared" si="1"/>
-        <v>46244</v>
-      </c>
-      <c r="Q9" s="102">
+        <v>46213</v>
+      </c>
+      <c r="Q9" s="97">
         <f t="shared" si="1"/>
-        <v>46245</v>
-      </c>
-      <c r="R9" s="102">
+        <v>46214</v>
+      </c>
+      <c r="R9" s="97">
         <f t="shared" si="1"/>
-        <v>46246</v>
-      </c>
-      <c r="S9" s="102">
+        <v>46215</v>
+      </c>
+      <c r="S9" s="97">
         <f t="shared" si="1"/>
-        <v>46247</v>
-      </c>
-      <c r="T9" s="102">
+        <v>46216</v>
+      </c>
+      <c r="T9" s="97">
         <f t="shared" si="1"/>
-        <v>46248</v>
-      </c>
-      <c r="U9" s="102">
+        <v>46217</v>
+      </c>
+      <c r="U9" s="97">
         <f t="shared" si="1"/>
-        <v>46249</v>
-      </c>
-      <c r="V9" s="102">
+        <v>46218</v>
+      </c>
+      <c r="V9" s="97">
         <f t="shared" si="1"/>
-        <v>46250</v>
-      </c>
-      <c r="W9" s="102">
+        <v>46219</v>
+      </c>
+      <c r="W9" s="97">
         <f t="shared" si="1"/>
-        <v>46251</v>
-      </c>
-      <c r="X9" s="102">
+        <v>46220</v>
+      </c>
+      <c r="X9" s="97">
         <f t="shared" si="1"/>
-        <v>46252</v>
-      </c>
-      <c r="Y9" s="102">
+        <v>46221</v>
+      </c>
+      <c r="Y9" s="97">
         <f t="shared" si="1"/>
-        <v>46253</v>
-      </c>
-      <c r="Z9" s="102">
+        <v>46222</v>
+      </c>
+      <c r="Z9" s="97">
         <f t="shared" si="1"/>
-        <v>46254</v>
-      </c>
-      <c r="AA9" s="102">
+        <v>46223</v>
+      </c>
+      <c r="AA9" s="97">
         <f t="shared" si="1"/>
-        <v>46255</v>
-      </c>
-      <c r="AB9" s="102">
+        <v>46224</v>
+      </c>
+      <c r="AB9" s="97">
         <f t="shared" si="1"/>
-        <v>46256</v>
-      </c>
-      <c r="AC9" s="102">
+        <v>46225</v>
+      </c>
+      <c r="AC9" s="97">
         <f t="shared" si="1"/>
-        <v>46257</v>
-      </c>
-      <c r="AD9" s="102">
+        <v>46226</v>
+      </c>
+      <c r="AD9" s="97">
         <f t="shared" si="1"/>
-        <v>46258</v>
-      </c>
-      <c r="AE9" s="102">
+        <v>46227</v>
+      </c>
+      <c r="AE9" s="97">
         <f t="shared" si="1"/>
-        <v>46259</v>
-      </c>
-      <c r="AF9" s="102">
+        <v>46228</v>
+      </c>
+      <c r="AF9" s="97">
         <f t="shared" si="1"/>
-        <v>46260</v>
-      </c>
-      <c r="AG9" s="102">
+        <v>46229</v>
+      </c>
+      <c r="AG9" s="97">
         <f t="shared" si="1"/>
-        <v>46261</v>
-      </c>
-      <c r="AH9" s="102">
+        <v>46230</v>
+      </c>
+      <c r="AH9" s="97">
         <f t="shared" si="1"/>
-        <v>46262</v>
-      </c>
-      <c r="AI9" s="102">
+        <v>46231</v>
+      </c>
+      <c r="AI9" s="97">
         <f t="shared" si="1"/>
-        <v>46263</v>
-      </c>
-      <c r="AJ9" s="102">
+        <v>46232</v>
+      </c>
+      <c r="AJ9" s="97">
         <f t="shared" si="1"/>
-        <v>46264</v>
-      </c>
-      <c r="AK9" s="102">
+        <v>46233</v>
+      </c>
+      <c r="AK9" s="193">
         <f t="shared" si="1"/>
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="AN9" s="3"/>
       <c r="AO9" s="3"/>
@@ -5733,136 +5885,136 @@
     </row>
     <row r="10" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A10" s="29"/>
-      <c r="B10" s="147"/>
-      <c r="C10" s="148"/>
+      <c r="B10" s="139"/>
+      <c r="C10" s="140"/>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G10" s="32" t="str">
         <f>TEXT(G9,"aaa")</f>
-        <v>土</v>
+        <v>水</v>
       </c>
       <c r="H10" s="32" t="str">
         <f>TEXT(H9,"aaa")</f>
-        <v>日</v>
+        <v>木</v>
       </c>
       <c r="I10" s="32" t="str">
         <f t="shared" ref="I10:AK10" si="2">TEXT(I9,"aaa")</f>
-        <v>月</v>
+        <v>金</v>
       </c>
       <c r="J10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>火</v>
+        <v>土</v>
       </c>
       <c r="K10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>水</v>
+        <v>日</v>
       </c>
       <c r="L10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>木</v>
+        <v>月</v>
       </c>
       <c r="M10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>金</v>
+        <v>火</v>
       </c>
       <c r="N10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>土</v>
+        <v>水</v>
       </c>
       <c r="O10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>日</v>
+        <v>木</v>
       </c>
       <c r="P10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>月</v>
+        <v>金</v>
       </c>
       <c r="Q10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>火</v>
+        <v>土</v>
       </c>
       <c r="R10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>水</v>
+        <v>日</v>
       </c>
       <c r="S10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>木</v>
+        <v>月</v>
       </c>
       <c r="T10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>金</v>
+        <v>火</v>
       </c>
       <c r="U10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>土</v>
+        <v>水</v>
       </c>
       <c r="V10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>日</v>
+        <v>木</v>
       </c>
       <c r="W10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>月</v>
+        <v>金</v>
       </c>
       <c r="X10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>火</v>
+        <v>土</v>
       </c>
       <c r="Y10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>水</v>
+        <v>日</v>
       </c>
       <c r="Z10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>木</v>
+        <v>月</v>
       </c>
       <c r="AA10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>金</v>
+        <v>火</v>
       </c>
       <c r="AB10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>土</v>
+        <v>水</v>
       </c>
       <c r="AC10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>日</v>
+        <v>木</v>
       </c>
       <c r="AD10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>月</v>
+        <v>金</v>
       </c>
       <c r="AE10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>火</v>
+        <v>土</v>
       </c>
       <c r="AF10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>水</v>
+        <v>日</v>
       </c>
       <c r="AG10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>木</v>
+        <v>月</v>
       </c>
       <c r="AH10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>金</v>
+        <v>火</v>
       </c>
       <c r="AI10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>土</v>
+        <v>水</v>
       </c>
       <c r="AJ10" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>日</v>
+        <v>木</v>
       </c>
       <c r="AK10" s="33" t="str">
         <f t="shared" si="2"/>
-        <v>月</v>
+        <v>金</v>
       </c>
       <c r="AN10" s="3"/>
       <c r="AO10" s="3"/>
@@ -6082,46 +6234,46 @@
     </row>
     <row r="11" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A11" s="34"/>
-      <c r="B11" s="149" t="s">
+      <c r="B11" s="117" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="150"/>
+      <c r="C11" s="118"/>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
-      <c r="F11" s="110" t="s">
+      <c r="F11" s="102" t="s">
         <v>122</v>
       </c>
-      <c r="G11" s="68"/>
-      <c r="H11" s="68"/>
-      <c r="I11" s="68"/>
-      <c r="J11" s="68"/>
-      <c r="K11" s="68"/>
-      <c r="L11" s="68"/>
-      <c r="M11" s="68"/>
-      <c r="N11" s="68"/>
-      <c r="O11" s="68"/>
-      <c r="P11" s="68"/>
-      <c r="Q11" s="68"/>
-      <c r="R11" s="68"/>
-      <c r="S11" s="68"/>
-      <c r="T11" s="68"/>
-      <c r="U11" s="68"/>
-      <c r="V11" s="68"/>
-      <c r="W11" s="68"/>
-      <c r="X11" s="68"/>
-      <c r="Y11" s="68"/>
-      <c r="Z11" s="68"/>
-      <c r="AA11" s="68"/>
-      <c r="AB11" s="68"/>
-      <c r="AC11" s="68"/>
-      <c r="AD11" s="68"/>
-      <c r="AE11" s="68"/>
-      <c r="AF11" s="68"/>
-      <c r="AG11" s="68"/>
-      <c r="AH11" s="68"/>
-      <c r="AI11" s="68"/>
-      <c r="AJ11" s="68"/>
-      <c r="AK11" s="69"/>
+      <c r="G11" s="181"/>
+      <c r="H11" s="181"/>
+      <c r="I11" s="181"/>
+      <c r="J11" s="181"/>
+      <c r="K11" s="181"/>
+      <c r="L11" s="181"/>
+      <c r="M11" s="181"/>
+      <c r="N11" s="181"/>
+      <c r="O11" s="181"/>
+      <c r="P11" s="181"/>
+      <c r="Q11" s="181"/>
+      <c r="R11" s="181"/>
+      <c r="S11" s="181"/>
+      <c r="T11" s="181"/>
+      <c r="U11" s="181"/>
+      <c r="V11" s="181"/>
+      <c r="W11" s="181"/>
+      <c r="X11" s="181"/>
+      <c r="Y11" s="181"/>
+      <c r="Z11" s="181"/>
+      <c r="AA11" s="181"/>
+      <c r="AB11" s="181"/>
+      <c r="AC11" s="181"/>
+      <c r="AD11" s="181"/>
+      <c r="AE11" s="181"/>
+      <c r="AF11" s="181"/>
+      <c r="AG11" s="181"/>
+      <c r="AH11" s="181"/>
+      <c r="AI11" s="181"/>
+      <c r="AJ11" s="181"/>
+      <c r="AK11" s="182"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
@@ -6339,53 +6491,53 @@
       <c r="IT11" s="3"/>
     </row>
     <row r="12" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A12" s="106">
+      <c r="A12" s="99">
         <v>1</v>
       </c>
-      <c r="B12" s="112" t="s">
+      <c r="B12" s="104" t="s">
         <v>119</v>
       </c>
-      <c r="C12" s="113"/>
-      <c r="D12" s="97" t="s">
+      <c r="C12" s="105"/>
+      <c r="D12" s="92" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="97" t="s">
+      <c r="E12" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="116" t="s">
+      <c r="F12" s="158" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="70"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="70"/>
-      <c r="J12" s="70"/>
-      <c r="K12" s="70"/>
-      <c r="L12" s="70"/>
-      <c r="M12" s="70"/>
-      <c r="N12" s="70"/>
-      <c r="O12" s="70"/>
-      <c r="P12" s="70"/>
-      <c r="Q12" s="70"/>
-      <c r="R12" s="70"/>
-      <c r="S12" s="70"/>
-      <c r="T12" s="70"/>
-      <c r="U12" s="70"/>
-      <c r="V12" s="70"/>
-      <c r="W12" s="70"/>
-      <c r="X12" s="70"/>
-      <c r="Y12" s="70"/>
-      <c r="Z12" s="70"/>
-      <c r="AA12" s="70"/>
-      <c r="AB12" s="70"/>
-      <c r="AC12" s="70"/>
-      <c r="AD12" s="70"/>
-      <c r="AE12" s="70"/>
-      <c r="AF12" s="70"/>
-      <c r="AG12" s="70"/>
-      <c r="AH12" s="70"/>
-      <c r="AI12" s="70"/>
-      <c r="AJ12" s="70"/>
-      <c r="AK12" s="71"/>
+      <c r="G12" s="183"/>
+      <c r="H12" s="183"/>
+      <c r="I12" s="183"/>
+      <c r="J12" s="183"/>
+      <c r="K12" s="183"/>
+      <c r="L12" s="183"/>
+      <c r="M12" s="183"/>
+      <c r="N12" s="183"/>
+      <c r="O12" s="183"/>
+      <c r="P12" s="183"/>
+      <c r="Q12" s="183"/>
+      <c r="R12" s="183"/>
+      <c r="S12" s="183"/>
+      <c r="T12" s="183"/>
+      <c r="U12" s="183"/>
+      <c r="V12" s="183"/>
+      <c r="W12" s="183"/>
+      <c r="X12" s="183"/>
+      <c r="Y12" s="183"/>
+      <c r="Z12" s="183"/>
+      <c r="AA12" s="183"/>
+      <c r="AB12" s="183"/>
+      <c r="AC12" s="183"/>
+      <c r="AD12" s="183"/>
+      <c r="AE12" s="183"/>
+      <c r="AF12" s="183"/>
+      <c r="AG12" s="183"/>
+      <c r="AH12" s="183"/>
+      <c r="AI12" s="183"/>
+      <c r="AJ12" s="183"/>
+      <c r="AK12" s="184"/>
       <c r="AN12" s="3"/>
       <c r="AO12" s="3"/>
       <c r="AP12" s="3"/>
@@ -6603,49 +6755,49 @@
       <c r="IT12" s="3"/>
     </row>
     <row r="13" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A13" s="106">
+      <c r="A13" s="99">
         <v>2</v>
       </c>
-      <c r="B13" s="112" t="s">
+      <c r="B13" s="104" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="97" t="s">
+      <c r="C13" s="105"/>
+      <c r="D13" s="92" t="s">
         <v>99</v>
       </c>
-      <c r="E13" s="97"/>
-      <c r="F13" s="117"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
-      <c r="I13" s="70"/>
-      <c r="J13" s="70"/>
-      <c r="K13" s="70"/>
-      <c r="L13" s="70"/>
-      <c r="M13" s="70"/>
-      <c r="N13" s="70"/>
-      <c r="O13" s="70"/>
-      <c r="P13" s="70"/>
-      <c r="Q13" s="70"/>
-      <c r="R13" s="70"/>
-      <c r="S13" s="70"/>
-      <c r="T13" s="70"/>
-      <c r="U13" s="70"/>
-      <c r="V13" s="70"/>
-      <c r="W13" s="70"/>
-      <c r="X13" s="70"/>
-      <c r="Y13" s="70"/>
-      <c r="Z13" s="70"/>
-      <c r="AA13" s="70"/>
-      <c r="AB13" s="70"/>
-      <c r="AC13" s="70"/>
-      <c r="AD13" s="70"/>
-      <c r="AE13" s="70"/>
-      <c r="AF13" s="70"/>
-      <c r="AG13" s="70"/>
-      <c r="AH13" s="70"/>
-      <c r="AI13" s="70"/>
-      <c r="AJ13" s="70"/>
-      <c r="AK13" s="71"/>
+      <c r="E13" s="92"/>
+      <c r="F13" s="106"/>
+      <c r="G13" s="183"/>
+      <c r="H13" s="183"/>
+      <c r="I13" s="183"/>
+      <c r="J13" s="183"/>
+      <c r="K13" s="183"/>
+      <c r="L13" s="183"/>
+      <c r="M13" s="183"/>
+      <c r="N13" s="183"/>
+      <c r="O13" s="183"/>
+      <c r="P13" s="183"/>
+      <c r="Q13" s="183"/>
+      <c r="R13" s="183"/>
+      <c r="S13" s="183"/>
+      <c r="T13" s="183"/>
+      <c r="U13" s="183"/>
+      <c r="V13" s="183"/>
+      <c r="W13" s="183"/>
+      <c r="X13" s="183"/>
+      <c r="Y13" s="183"/>
+      <c r="Z13" s="183"/>
+      <c r="AA13" s="183"/>
+      <c r="AB13" s="183"/>
+      <c r="AC13" s="183"/>
+      <c r="AD13" s="183"/>
+      <c r="AE13" s="183"/>
+      <c r="AF13" s="183"/>
+      <c r="AG13" s="183"/>
+      <c r="AH13" s="183"/>
+      <c r="AI13" s="183"/>
+      <c r="AJ13" s="183"/>
+      <c r="AK13" s="184"/>
       <c r="AN13" s="3"/>
       <c r="AO13" s="3"/>
       <c r="AP13" s="3"/>
@@ -6863,51 +7015,51 @@
       <c r="IT13" s="3"/>
     </row>
     <row r="14" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A14" s="106">
+      <c r="A14" s="99">
         <v>3</v>
       </c>
-      <c r="B14" s="112" t="s">
-        <v>131</v>
-      </c>
-      <c r="C14" s="113"/>
-      <c r="D14" s="97" t="s">
+      <c r="B14" s="104" t="s">
+        <v>130</v>
+      </c>
+      <c r="C14" s="105"/>
+      <c r="D14" s="92" t="s">
         <v>99</v>
       </c>
-      <c r="E14" s="97" t="s">
+      <c r="E14" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="117"/>
-      <c r="G14" s="70"/>
-      <c r="H14" s="70"/>
-      <c r="I14" s="70"/>
-      <c r="J14" s="70"/>
-      <c r="K14" s="70"/>
-      <c r="L14" s="70"/>
-      <c r="M14" s="70"/>
-      <c r="N14" s="70"/>
-      <c r="O14" s="70"/>
-      <c r="P14" s="70"/>
-      <c r="Q14" s="70"/>
-      <c r="R14" s="70"/>
-      <c r="S14" s="70"/>
-      <c r="T14" s="70"/>
-      <c r="U14" s="70"/>
-      <c r="V14" s="70"/>
-      <c r="W14" s="70"/>
-      <c r="X14" s="70"/>
-      <c r="Y14" s="70"/>
-      <c r="Z14" s="70"/>
-      <c r="AA14" s="70"/>
-      <c r="AB14" s="70"/>
-      <c r="AC14" s="70"/>
-      <c r="AD14" s="70"/>
-      <c r="AE14" s="70"/>
-      <c r="AF14" s="70"/>
-      <c r="AG14" s="70"/>
-      <c r="AH14" s="70"/>
-      <c r="AI14" s="70"/>
-      <c r="AJ14" s="70"/>
-      <c r="AK14" s="71"/>
+      <c r="F14" s="106"/>
+      <c r="G14" s="183"/>
+      <c r="H14" s="183"/>
+      <c r="I14" s="183"/>
+      <c r="J14" s="183"/>
+      <c r="K14" s="183"/>
+      <c r="L14" s="183"/>
+      <c r="M14" s="183"/>
+      <c r="N14" s="183"/>
+      <c r="O14" s="183"/>
+      <c r="P14" s="183"/>
+      <c r="Q14" s="183"/>
+      <c r="R14" s="183"/>
+      <c r="S14" s="183"/>
+      <c r="T14" s="183"/>
+      <c r="U14" s="183"/>
+      <c r="V14" s="183"/>
+      <c r="W14" s="183"/>
+      <c r="X14" s="183"/>
+      <c r="Y14" s="183"/>
+      <c r="Z14" s="183"/>
+      <c r="AA14" s="183"/>
+      <c r="AB14" s="183"/>
+      <c r="AC14" s="183"/>
+      <c r="AD14" s="183"/>
+      <c r="AE14" s="183"/>
+      <c r="AF14" s="183"/>
+      <c r="AG14" s="183"/>
+      <c r="AH14" s="183"/>
+      <c r="AI14" s="183"/>
+      <c r="AJ14" s="183"/>
+      <c r="AK14" s="184"/>
       <c r="AN14" s="3"/>
       <c r="AO14" s="3"/>
       <c r="AP14" s="3"/>
@@ -7125,51 +7277,51 @@
       <c r="IT14" s="3"/>
     </row>
     <row r="15" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A15" s="106">
+      <c r="A15" s="99">
         <v>4</v>
       </c>
-      <c r="B15" s="112" t="s">
-        <v>132</v>
-      </c>
-      <c r="C15" s="113"/>
-      <c r="D15" s="97" t="s">
+      <c r="B15" s="104" t="s">
+        <v>131</v>
+      </c>
+      <c r="C15" s="105"/>
+      <c r="D15" s="92" t="s">
         <v>99</v>
       </c>
-      <c r="E15" s="97" t="s">
+      <c r="E15" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="117"/>
-      <c r="G15" s="70"/>
-      <c r="H15" s="70"/>
-      <c r="I15" s="70"/>
-      <c r="J15" s="70"/>
-      <c r="K15" s="70"/>
-      <c r="L15" s="70"/>
-      <c r="M15" s="70"/>
-      <c r="N15" s="70"/>
-      <c r="O15" s="70"/>
-      <c r="P15" s="70"/>
-      <c r="Q15" s="70"/>
-      <c r="R15" s="70"/>
-      <c r="S15" s="70"/>
-      <c r="T15" s="70"/>
-      <c r="U15" s="70"/>
-      <c r="V15" s="70"/>
-      <c r="W15" s="70"/>
-      <c r="X15" s="70"/>
-      <c r="Y15" s="70"/>
-      <c r="Z15" s="70"/>
-      <c r="AA15" s="70"/>
-      <c r="AB15" s="70"/>
-      <c r="AC15" s="70"/>
-      <c r="AD15" s="70"/>
-      <c r="AE15" s="70"/>
-      <c r="AF15" s="70"/>
-      <c r="AG15" s="70"/>
-      <c r="AH15" s="70"/>
-      <c r="AI15" s="70"/>
-      <c r="AJ15" s="70"/>
-      <c r="AK15" s="71"/>
+      <c r="F15" s="106"/>
+      <c r="G15" s="183"/>
+      <c r="H15" s="183"/>
+      <c r="I15" s="183"/>
+      <c r="J15" s="183"/>
+      <c r="K15" s="183"/>
+      <c r="L15" s="183"/>
+      <c r="M15" s="183"/>
+      <c r="N15" s="183"/>
+      <c r="O15" s="183"/>
+      <c r="P15" s="183"/>
+      <c r="Q15" s="183"/>
+      <c r="R15" s="183"/>
+      <c r="S15" s="183"/>
+      <c r="T15" s="183"/>
+      <c r="U15" s="183"/>
+      <c r="V15" s="183"/>
+      <c r="W15" s="183"/>
+      <c r="X15" s="183"/>
+      <c r="Y15" s="183"/>
+      <c r="Z15" s="183"/>
+      <c r="AA15" s="183"/>
+      <c r="AB15" s="183"/>
+      <c r="AC15" s="183"/>
+      <c r="AD15" s="183"/>
+      <c r="AE15" s="183"/>
+      <c r="AF15" s="183"/>
+      <c r="AG15" s="183"/>
+      <c r="AH15" s="183"/>
+      <c r="AI15" s="183"/>
+      <c r="AJ15" s="183"/>
+      <c r="AK15" s="184"/>
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
       <c r="AP15" s="3"/>
@@ -7387,51 +7539,51 @@
       <c r="IT15" s="3"/>
     </row>
     <row r="16" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A16" s="106">
+      <c r="A16" s="99">
         <v>5</v>
       </c>
-      <c r="B16" s="112" t="s">
+      <c r="B16" s="104" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="113"/>
-      <c r="D16" s="97" t="s">
-        <v>134</v>
-      </c>
-      <c r="E16" s="97" t="s">
+      <c r="C16" s="105"/>
+      <c r="D16" s="92" t="s">
+        <v>133</v>
+      </c>
+      <c r="E16" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="117"/>
-      <c r="G16" s="70"/>
-      <c r="H16" s="70"/>
-      <c r="I16" s="70"/>
-      <c r="J16" s="70"/>
-      <c r="K16" s="70"/>
-      <c r="L16" s="70"/>
-      <c r="M16" s="70"/>
-      <c r="N16" s="70"/>
-      <c r="O16" s="70"/>
-      <c r="P16" s="70"/>
-      <c r="Q16" s="70"/>
-      <c r="R16" s="70"/>
-      <c r="S16" s="70"/>
-      <c r="T16" s="70"/>
-      <c r="U16" s="70"/>
-      <c r="V16" s="70"/>
-      <c r="W16" s="70"/>
-      <c r="X16" s="70"/>
-      <c r="Y16" s="70"/>
-      <c r="Z16" s="70"/>
-      <c r="AA16" s="70"/>
-      <c r="AB16" s="70"/>
-      <c r="AC16" s="70"/>
-      <c r="AD16" s="70"/>
-      <c r="AE16" s="70"/>
-      <c r="AF16" s="70"/>
-      <c r="AG16" s="70"/>
-      <c r="AH16" s="70"/>
-      <c r="AI16" s="70"/>
-      <c r="AJ16" s="70"/>
-      <c r="AK16" s="71"/>
+      <c r="F16" s="106"/>
+      <c r="G16" s="183"/>
+      <c r="H16" s="183"/>
+      <c r="I16" s="183"/>
+      <c r="J16" s="183"/>
+      <c r="K16" s="183"/>
+      <c r="L16" s="183"/>
+      <c r="M16" s="183"/>
+      <c r="N16" s="183"/>
+      <c r="O16" s="183"/>
+      <c r="P16" s="183"/>
+      <c r="Q16" s="183"/>
+      <c r="R16" s="183"/>
+      <c r="S16" s="183"/>
+      <c r="T16" s="183"/>
+      <c r="U16" s="183"/>
+      <c r="V16" s="183"/>
+      <c r="W16" s="183"/>
+      <c r="X16" s="183"/>
+      <c r="Y16" s="183"/>
+      <c r="Z16" s="183"/>
+      <c r="AA16" s="183"/>
+      <c r="AB16" s="183"/>
+      <c r="AC16" s="183"/>
+      <c r="AD16" s="183"/>
+      <c r="AE16" s="183"/>
+      <c r="AF16" s="183"/>
+      <c r="AG16" s="183"/>
+      <c r="AH16" s="183"/>
+      <c r="AI16" s="183"/>
+      <c r="AJ16" s="183"/>
+      <c r="AK16" s="184"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
@@ -7649,51 +7801,51 @@
       <c r="IT16" s="3"/>
     </row>
     <row r="17" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A17" s="106">
+      <c r="A17" s="99">
         <v>6</v>
       </c>
-      <c r="B17" s="112" t="s">
-        <v>135</v>
-      </c>
-      <c r="C17" s="113"/>
-      <c r="D17" s="97" t="s">
+      <c r="B17" s="104" t="s">
+        <v>134</v>
+      </c>
+      <c r="C17" s="105"/>
+      <c r="D17" s="92" t="s">
         <v>99</v>
       </c>
-      <c r="E17" s="97" t="s">
+      <c r="E17" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="117"/>
-      <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
-      <c r="I17" s="70"/>
-      <c r="J17" s="70"/>
-      <c r="K17" s="70"/>
-      <c r="L17" s="70"/>
-      <c r="M17" s="70"/>
-      <c r="N17" s="70"/>
-      <c r="O17" s="70"/>
-      <c r="P17" s="70"/>
-      <c r="Q17" s="70"/>
-      <c r="R17" s="70"/>
-      <c r="S17" s="70"/>
-      <c r="T17" s="70"/>
-      <c r="U17" s="70"/>
-      <c r="V17" s="70"/>
-      <c r="W17" s="70"/>
-      <c r="X17" s="70"/>
-      <c r="Y17" s="70"/>
-      <c r="Z17" s="70"/>
-      <c r="AA17" s="70"/>
-      <c r="AB17" s="70"/>
-      <c r="AC17" s="70"/>
-      <c r="AD17" s="70"/>
-      <c r="AE17" s="70"/>
-      <c r="AF17" s="70"/>
-      <c r="AG17" s="70"/>
-      <c r="AH17" s="70"/>
-      <c r="AI17" s="70"/>
-      <c r="AJ17" s="70"/>
-      <c r="AK17" s="71"/>
+      <c r="F17" s="106"/>
+      <c r="G17" s="183"/>
+      <c r="H17" s="183"/>
+      <c r="I17" s="183"/>
+      <c r="J17" s="183"/>
+      <c r="K17" s="183"/>
+      <c r="L17" s="183"/>
+      <c r="M17" s="183"/>
+      <c r="N17" s="183"/>
+      <c r="O17" s="183"/>
+      <c r="P17" s="183"/>
+      <c r="Q17" s="183"/>
+      <c r="R17" s="183"/>
+      <c r="S17" s="183"/>
+      <c r="T17" s="183"/>
+      <c r="U17" s="183"/>
+      <c r="V17" s="183"/>
+      <c r="W17" s="183"/>
+      <c r="X17" s="183"/>
+      <c r="Y17" s="183"/>
+      <c r="Z17" s="183"/>
+      <c r="AA17" s="183"/>
+      <c r="AB17" s="183"/>
+      <c r="AC17" s="183"/>
+      <c r="AD17" s="183"/>
+      <c r="AE17" s="183"/>
+      <c r="AF17" s="183"/>
+      <c r="AG17" s="183"/>
+      <c r="AH17" s="183"/>
+      <c r="AI17" s="183"/>
+      <c r="AJ17" s="183"/>
+      <c r="AK17" s="184"/>
       <c r="AN17" s="3"/>
       <c r="AO17" s="3"/>
       <c r="AP17" s="3"/>
@@ -7911,51 +8063,51 @@
       <c r="IT17" s="3"/>
     </row>
     <row r="18" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A18" s="106">
+      <c r="A18" s="99">
         <v>7</v>
       </c>
-      <c r="B18" s="112" t="s">
+      <c r="B18" s="104" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="113"/>
-      <c r="D18" s="97" t="s">
+      <c r="C18" s="105"/>
+      <c r="D18" s="92" t="s">
         <v>99</v>
       </c>
-      <c r="E18" s="97" t="s">
+      <c r="E18" s="92" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="117"/>
-      <c r="G18" s="70"/>
-      <c r="H18" s="70"/>
-      <c r="I18" s="70"/>
-      <c r="J18" s="70"/>
-      <c r="K18" s="70"/>
-      <c r="L18" s="70"/>
-      <c r="M18" s="70"/>
-      <c r="N18" s="70"/>
-      <c r="O18" s="70"/>
-      <c r="P18" s="70"/>
-      <c r="Q18" s="70"/>
-      <c r="R18" s="70"/>
-      <c r="S18" s="70"/>
-      <c r="T18" s="70"/>
-      <c r="U18" s="70"/>
-      <c r="V18" s="70"/>
-      <c r="W18" s="70"/>
-      <c r="X18" s="70"/>
-      <c r="Y18" s="70"/>
-      <c r="Z18" s="70"/>
-      <c r="AA18" s="70"/>
-      <c r="AB18" s="70"/>
-      <c r="AC18" s="70"/>
-      <c r="AD18" s="70"/>
-      <c r="AE18" s="70"/>
-      <c r="AF18" s="70"/>
-      <c r="AG18" s="70"/>
-      <c r="AH18" s="70"/>
-      <c r="AI18" s="70"/>
-      <c r="AJ18" s="70"/>
-      <c r="AK18" s="71"/>
+      <c r="F18" s="106"/>
+      <c r="G18" s="183"/>
+      <c r="H18" s="183"/>
+      <c r="I18" s="183"/>
+      <c r="J18" s="183"/>
+      <c r="K18" s="183"/>
+      <c r="L18" s="183"/>
+      <c r="M18" s="183"/>
+      <c r="N18" s="183"/>
+      <c r="O18" s="183"/>
+      <c r="P18" s="183"/>
+      <c r="Q18" s="183"/>
+      <c r="R18" s="183"/>
+      <c r="S18" s="183"/>
+      <c r="T18" s="183"/>
+      <c r="U18" s="183"/>
+      <c r="V18" s="183"/>
+      <c r="W18" s="183"/>
+      <c r="X18" s="183"/>
+      <c r="Y18" s="183"/>
+      <c r="Z18" s="183"/>
+      <c r="AA18" s="183"/>
+      <c r="AB18" s="183"/>
+      <c r="AC18" s="183"/>
+      <c r="AD18" s="183"/>
+      <c r="AE18" s="183"/>
+      <c r="AF18" s="183"/>
+      <c r="AG18" s="183"/>
+      <c r="AH18" s="183"/>
+      <c r="AI18" s="183"/>
+      <c r="AJ18" s="183"/>
+      <c r="AK18" s="184"/>
       <c r="AN18" s="3"/>
       <c r="AO18" s="3"/>
       <c r="AP18" s="3"/>
@@ -8173,51 +8325,51 @@
       <c r="IT18" s="3"/>
     </row>
     <row r="19" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A19" s="106">
+      <c r="A19" s="99">
         <v>8</v>
       </c>
-      <c r="B19" s="112" t="s">
+      <c r="B19" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="113"/>
-      <c r="D19" s="97" t="s">
+      <c r="C19" s="105"/>
+      <c r="D19" s="92" t="s">
         <v>99</v>
       </c>
-      <c r="E19" s="97" t="s">
+      <c r="E19" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="F19" s="117"/>
-      <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
-      <c r="I19" s="70"/>
-      <c r="J19" s="70"/>
-      <c r="K19" s="70"/>
-      <c r="L19" s="70"/>
-      <c r="M19" s="70"/>
-      <c r="N19" s="70"/>
-      <c r="O19" s="70"/>
-      <c r="P19" s="70"/>
-      <c r="Q19" s="70"/>
-      <c r="R19" s="70"/>
-      <c r="S19" s="70"/>
-      <c r="T19" s="70"/>
-      <c r="U19" s="70"/>
-      <c r="V19" s="70"/>
-      <c r="W19" s="70"/>
-      <c r="X19" s="70"/>
-      <c r="Y19" s="70"/>
-      <c r="Z19" s="70"/>
-      <c r="AA19" s="70"/>
-      <c r="AB19" s="70"/>
-      <c r="AC19" s="70"/>
-      <c r="AD19" s="70"/>
-      <c r="AE19" s="70"/>
-      <c r="AF19" s="70"/>
-      <c r="AG19" s="70"/>
-      <c r="AH19" s="70"/>
-      <c r="AI19" s="70"/>
-      <c r="AJ19" s="70"/>
-      <c r="AK19" s="71"/>
+      <c r="F19" s="106"/>
+      <c r="G19" s="183"/>
+      <c r="H19" s="183"/>
+      <c r="I19" s="183"/>
+      <c r="J19" s="183"/>
+      <c r="K19" s="183"/>
+      <c r="L19" s="183"/>
+      <c r="M19" s="183"/>
+      <c r="N19" s="183"/>
+      <c r="O19" s="183"/>
+      <c r="P19" s="183"/>
+      <c r="Q19" s="183"/>
+      <c r="R19" s="183"/>
+      <c r="S19" s="183"/>
+      <c r="T19" s="183"/>
+      <c r="U19" s="183"/>
+      <c r="V19" s="183"/>
+      <c r="W19" s="183"/>
+      <c r="X19" s="183"/>
+      <c r="Y19" s="183"/>
+      <c r="Z19" s="183"/>
+      <c r="AA19" s="183"/>
+      <c r="AB19" s="183"/>
+      <c r="AC19" s="183"/>
+      <c r="AD19" s="183"/>
+      <c r="AE19" s="183"/>
+      <c r="AF19" s="183"/>
+      <c r="AG19" s="183"/>
+      <c r="AH19" s="183"/>
+      <c r="AI19" s="183"/>
+      <c r="AJ19" s="183"/>
+      <c r="AK19" s="184"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
@@ -8435,51 +8587,51 @@
       <c r="IT19" s="3"/>
     </row>
     <row r="20" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A20" s="106">
+      <c r="A20" s="99">
         <v>9</v>
       </c>
-      <c r="B20" s="112" t="s">
+      <c r="B20" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="113"/>
-      <c r="D20" s="97" t="s">
+      <c r="C20" s="105"/>
+      <c r="D20" s="92" t="s">
         <v>99</v>
       </c>
-      <c r="E20" s="97" t="s">
+      <c r="E20" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="F20" s="117"/>
-      <c r="G20" s="70"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="70"/>
-      <c r="J20" s="70"/>
-      <c r="K20" s="70"/>
-      <c r="L20" s="70"/>
-      <c r="M20" s="70"/>
-      <c r="N20" s="70"/>
-      <c r="O20" s="70"/>
-      <c r="P20" s="70"/>
-      <c r="Q20" s="70"/>
-      <c r="R20" s="70"/>
-      <c r="S20" s="70"/>
-      <c r="T20" s="70"/>
-      <c r="U20" s="70"/>
-      <c r="V20" s="70"/>
-      <c r="W20" s="70"/>
-      <c r="X20" s="70"/>
-      <c r="Y20" s="70"/>
-      <c r="Z20" s="70"/>
-      <c r="AA20" s="70"/>
-      <c r="AB20" s="70"/>
-      <c r="AC20" s="70"/>
-      <c r="AD20" s="70"/>
-      <c r="AE20" s="70"/>
-      <c r="AF20" s="70"/>
-      <c r="AG20" s="70"/>
-      <c r="AH20" s="70"/>
-      <c r="AI20" s="70"/>
-      <c r="AJ20" s="70"/>
-      <c r="AK20" s="71"/>
+      <c r="F20" s="106"/>
+      <c r="G20" s="183"/>
+      <c r="H20" s="183"/>
+      <c r="I20" s="183"/>
+      <c r="J20" s="183"/>
+      <c r="K20" s="183"/>
+      <c r="L20" s="183"/>
+      <c r="M20" s="183"/>
+      <c r="N20" s="183"/>
+      <c r="O20" s="183"/>
+      <c r="P20" s="183"/>
+      <c r="Q20" s="183"/>
+      <c r="R20" s="183"/>
+      <c r="S20" s="183"/>
+      <c r="T20" s="183"/>
+      <c r="U20" s="183"/>
+      <c r="V20" s="183"/>
+      <c r="W20" s="183"/>
+      <c r="X20" s="183"/>
+      <c r="Y20" s="183"/>
+      <c r="Z20" s="183"/>
+      <c r="AA20" s="183"/>
+      <c r="AB20" s="183"/>
+      <c r="AC20" s="183"/>
+      <c r="AD20" s="183"/>
+      <c r="AE20" s="183"/>
+      <c r="AF20" s="183"/>
+      <c r="AG20" s="183"/>
+      <c r="AH20" s="183"/>
+      <c r="AI20" s="183"/>
+      <c r="AJ20" s="183"/>
+      <c r="AK20" s="184"/>
       <c r="AN20" s="3"/>
       <c r="AO20" s="3"/>
       <c r="AP20" s="3"/>
@@ -8697,49 +8849,49 @@
       <c r="IT20" s="3"/>
     </row>
     <row r="21" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A21" s="106">
+      <c r="A21" s="99">
         <v>10</v>
       </c>
-      <c r="B21" s="112" t="s">
+      <c r="B21" s="104" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="113"/>
-      <c r="D21" s="97" t="s">
+      <c r="C21" s="105"/>
+      <c r="D21" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="E21" s="97"/>
-      <c r="F21" s="117"/>
-      <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
-      <c r="I21" s="70"/>
-      <c r="J21" s="70"/>
-      <c r="K21" s="70"/>
-      <c r="L21" s="70"/>
-      <c r="M21" s="70"/>
-      <c r="N21" s="70"/>
-      <c r="O21" s="70"/>
-      <c r="P21" s="70"/>
-      <c r="Q21" s="70"/>
-      <c r="R21" s="70"/>
-      <c r="S21" s="70"/>
-      <c r="T21" s="70"/>
-      <c r="U21" s="70"/>
-      <c r="V21" s="70"/>
-      <c r="W21" s="70"/>
-      <c r="X21" s="70"/>
-      <c r="Y21" s="70"/>
-      <c r="Z21" s="70"/>
-      <c r="AA21" s="70"/>
-      <c r="AB21" s="70"/>
-      <c r="AC21" s="70"/>
-      <c r="AD21" s="70"/>
-      <c r="AE21" s="70"/>
-      <c r="AF21" s="70"/>
-      <c r="AG21" s="70"/>
-      <c r="AH21" s="70"/>
-      <c r="AI21" s="70"/>
-      <c r="AJ21" s="70"/>
-      <c r="AK21" s="71"/>
+      <c r="E21" s="92"/>
+      <c r="F21" s="106"/>
+      <c r="G21" s="183"/>
+      <c r="H21" s="183"/>
+      <c r="I21" s="183"/>
+      <c r="J21" s="183"/>
+      <c r="K21" s="183"/>
+      <c r="L21" s="183"/>
+      <c r="M21" s="183"/>
+      <c r="N21" s="183"/>
+      <c r="O21" s="183"/>
+      <c r="P21" s="183"/>
+      <c r="Q21" s="183"/>
+      <c r="R21" s="183"/>
+      <c r="S21" s="183"/>
+      <c r="T21" s="183"/>
+      <c r="U21" s="183"/>
+      <c r="V21" s="183"/>
+      <c r="W21" s="183"/>
+      <c r="X21" s="183"/>
+      <c r="Y21" s="183"/>
+      <c r="Z21" s="183"/>
+      <c r="AA21" s="183"/>
+      <c r="AB21" s="183"/>
+      <c r="AC21" s="183"/>
+      <c r="AD21" s="183"/>
+      <c r="AE21" s="183"/>
+      <c r="AF21" s="183"/>
+      <c r="AG21" s="183"/>
+      <c r="AH21" s="183"/>
+      <c r="AI21" s="183"/>
+      <c r="AJ21" s="183"/>
+      <c r="AK21" s="184"/>
       <c r="AN21" s="3"/>
       <c r="AO21" s="3"/>
       <c r="AP21" s="3"/>
@@ -8957,51 +9109,51 @@
       <c r="IT21" s="3"/>
     </row>
     <row r="22" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A22" s="106">
+      <c r="A22" s="99">
         <v>11</v>
       </c>
-      <c r="B22" s="112" t="s">
+      <c r="B22" s="104" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="113"/>
-      <c r="D22" s="97" t="s">
+      <c r="C22" s="105"/>
+      <c r="D22" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="97"/>
-      <c r="F22" s="117" t="s">
-        <v>136</v>
-      </c>
-      <c r="G22" s="70"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
-      <c r="J22" s="70"/>
-      <c r="K22" s="70"/>
-      <c r="L22" s="70"/>
-      <c r="M22" s="70"/>
-      <c r="N22" s="70"/>
-      <c r="O22" s="70"/>
-      <c r="P22" s="70"/>
-      <c r="Q22" s="70"/>
-      <c r="R22" s="70"/>
-      <c r="S22" s="70"/>
-      <c r="T22" s="70"/>
-      <c r="U22" s="70"/>
-      <c r="V22" s="70"/>
-      <c r="W22" s="70"/>
-      <c r="X22" s="70"/>
-      <c r="Y22" s="70"/>
-      <c r="Z22" s="70"/>
-      <c r="AA22" s="70"/>
-      <c r="AB22" s="70"/>
-      <c r="AC22" s="70"/>
-      <c r="AD22" s="70"/>
-      <c r="AE22" s="70"/>
-      <c r="AF22" s="70"/>
-      <c r="AG22" s="70"/>
-      <c r="AH22" s="70"/>
-      <c r="AI22" s="70"/>
-      <c r="AJ22" s="70"/>
-      <c r="AK22" s="71"/>
+      <c r="E22" s="92"/>
+      <c r="F22" s="106" t="s">
+        <v>135</v>
+      </c>
+      <c r="G22" s="183"/>
+      <c r="H22" s="183"/>
+      <c r="I22" s="183"/>
+      <c r="J22" s="183"/>
+      <c r="K22" s="183"/>
+      <c r="L22" s="183"/>
+      <c r="M22" s="183"/>
+      <c r="N22" s="183"/>
+      <c r="O22" s="183"/>
+      <c r="P22" s="183"/>
+      <c r="Q22" s="183"/>
+      <c r="R22" s="183"/>
+      <c r="S22" s="183"/>
+      <c r="T22" s="183"/>
+      <c r="U22" s="183"/>
+      <c r="V22" s="183"/>
+      <c r="W22" s="183"/>
+      <c r="X22" s="183"/>
+      <c r="Y22" s="183"/>
+      <c r="Z22" s="183"/>
+      <c r="AA22" s="183"/>
+      <c r="AB22" s="183"/>
+      <c r="AC22" s="183"/>
+      <c r="AD22" s="183"/>
+      <c r="AE22" s="183"/>
+      <c r="AF22" s="183"/>
+      <c r="AG22" s="183"/>
+      <c r="AH22" s="183"/>
+      <c r="AI22" s="183"/>
+      <c r="AJ22" s="183"/>
+      <c r="AK22" s="184"/>
       <c r="AN22" s="3"/>
       <c r="AO22" s="3"/>
       <c r="AP22" s="3"/>
@@ -9219,51 +9371,51 @@
       <c r="IT22" s="3"/>
     </row>
     <row r="23" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A23" s="106">
+      <c r="A23" s="99">
         <v>13</v>
       </c>
-      <c r="B23" s="112" t="s">
-        <v>133</v>
-      </c>
-      <c r="C23" s="113"/>
-      <c r="D23" s="97" t="s">
+      <c r="B23" s="104" t="s">
+        <v>132</v>
+      </c>
+      <c r="C23" s="105"/>
+      <c r="D23" s="92" t="s">
         <v>99</v>
       </c>
-      <c r="E23" s="97" t="s">
+      <c r="E23" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="F23" s="127"/>
-      <c r="G23" s="68"/>
-      <c r="H23" s="68"/>
-      <c r="I23" s="68"/>
-      <c r="J23" s="68"/>
-      <c r="K23" s="68"/>
-      <c r="L23" s="68"/>
-      <c r="M23" s="68"/>
-      <c r="N23" s="68"/>
-      <c r="O23" s="68"/>
-      <c r="P23" s="68"/>
-      <c r="Q23" s="68"/>
-      <c r="R23" s="68"/>
-      <c r="S23" s="68"/>
-      <c r="T23" s="68"/>
-      <c r="U23" s="68"/>
-      <c r="V23" s="68"/>
-      <c r="W23" s="68"/>
-      <c r="X23" s="68"/>
-      <c r="Y23" s="68"/>
-      <c r="Z23" s="68"/>
-      <c r="AA23" s="68"/>
-      <c r="AB23" s="68"/>
-      <c r="AC23" s="68"/>
-      <c r="AD23" s="68"/>
-      <c r="AE23" s="68"/>
-      <c r="AF23" s="68"/>
-      <c r="AG23" s="68"/>
-      <c r="AH23" s="68"/>
-      <c r="AI23" s="68"/>
-      <c r="AJ23" s="68"/>
-      <c r="AK23" s="69"/>
+      <c r="F23" s="107"/>
+      <c r="G23" s="181"/>
+      <c r="H23" s="181"/>
+      <c r="I23" s="181"/>
+      <c r="J23" s="181"/>
+      <c r="K23" s="181"/>
+      <c r="L23" s="181"/>
+      <c r="M23" s="181"/>
+      <c r="N23" s="181"/>
+      <c r="O23" s="181"/>
+      <c r="P23" s="181"/>
+      <c r="Q23" s="181"/>
+      <c r="R23" s="181"/>
+      <c r="S23" s="181"/>
+      <c r="T23" s="181"/>
+      <c r="U23" s="181"/>
+      <c r="V23" s="181"/>
+      <c r="W23" s="181"/>
+      <c r="X23" s="181"/>
+      <c r="Y23" s="181"/>
+      <c r="Z23" s="181"/>
+      <c r="AA23" s="181"/>
+      <c r="AB23" s="181"/>
+      <c r="AC23" s="181"/>
+      <c r="AD23" s="181"/>
+      <c r="AE23" s="181"/>
+      <c r="AF23" s="181"/>
+      <c r="AG23" s="181"/>
+      <c r="AH23" s="181"/>
+      <c r="AI23" s="181"/>
+      <c r="AJ23" s="181"/>
+      <c r="AK23" s="182"/>
       <c r="AN23" s="3"/>
       <c r="AO23" s="3"/>
       <c r="AP23" s="3"/>
@@ -9481,53 +9633,53 @@
       <c r="IT23" s="3"/>
     </row>
     <row r="24" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A24" s="106">
+      <c r="A24" s="99">
         <v>12</v>
       </c>
-      <c r="B24" s="112" t="s">
+      <c r="B24" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="113"/>
-      <c r="D24" s="97" t="s">
+      <c r="C24" s="105"/>
+      <c r="D24" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="E24" s="97" t="s">
+      <c r="E24" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="F24" s="98" t="s">
+      <c r="F24" s="93" t="s">
         <v>39</v>
       </c>
-      <c r="G24" s="68"/>
-      <c r="H24" s="68"/>
-      <c r="I24" s="68"/>
-      <c r="J24" s="68"/>
-      <c r="K24" s="68"/>
-      <c r="L24" s="68"/>
-      <c r="M24" s="68"/>
-      <c r="N24" s="68"/>
-      <c r="O24" s="68"/>
-      <c r="P24" s="68"/>
-      <c r="Q24" s="68"/>
-      <c r="R24" s="68"/>
-      <c r="S24" s="68"/>
-      <c r="T24" s="68"/>
-      <c r="U24" s="68"/>
-      <c r="V24" s="68"/>
-      <c r="W24" s="68"/>
-      <c r="X24" s="68"/>
-      <c r="Y24" s="68"/>
-      <c r="Z24" s="68"/>
-      <c r="AA24" s="68"/>
-      <c r="AB24" s="68"/>
-      <c r="AC24" s="68"/>
-      <c r="AD24" s="68"/>
-      <c r="AE24" s="68"/>
-      <c r="AF24" s="68"/>
-      <c r="AG24" s="68"/>
-      <c r="AH24" s="68"/>
-      <c r="AI24" s="68"/>
-      <c r="AJ24" s="68"/>
-      <c r="AK24" s="69"/>
+      <c r="G24" s="181"/>
+      <c r="H24" s="181"/>
+      <c r="I24" s="181"/>
+      <c r="J24" s="181"/>
+      <c r="K24" s="181"/>
+      <c r="L24" s="181"/>
+      <c r="M24" s="181"/>
+      <c r="N24" s="181"/>
+      <c r="O24" s="181"/>
+      <c r="P24" s="181"/>
+      <c r="Q24" s="181"/>
+      <c r="R24" s="181"/>
+      <c r="S24" s="181"/>
+      <c r="T24" s="181"/>
+      <c r="U24" s="181"/>
+      <c r="V24" s="181"/>
+      <c r="W24" s="181"/>
+      <c r="X24" s="181"/>
+      <c r="Y24" s="181"/>
+      <c r="Z24" s="181"/>
+      <c r="AA24" s="181"/>
+      <c r="AB24" s="181"/>
+      <c r="AC24" s="181"/>
+      <c r="AD24" s="181"/>
+      <c r="AE24" s="181"/>
+      <c r="AF24" s="181"/>
+      <c r="AG24" s="181"/>
+      <c r="AH24" s="181"/>
+      <c r="AI24" s="181"/>
+      <c r="AJ24" s="181"/>
+      <c r="AK24" s="182"/>
       <c r="AN24" s="3"/>
       <c r="AO24" s="3"/>
       <c r="AP24" s="3"/>
@@ -9746,42 +9898,42 @@
     </row>
     <row r="25" spans="1:254" s="2" customFormat="1" ht="10" customHeight="1">
       <c r="A25" s="37"/>
-      <c r="B25" s="112"/>
-      <c r="C25" s="113"/>
-      <c r="D25" s="97"/>
-      <c r="E25" s="97"/>
+      <c r="B25" s="104"/>
+      <c r="C25" s="105"/>
+      <c r="D25" s="92"/>
+      <c r="E25" s="92"/>
       <c r="F25" s="36"/>
-      <c r="G25" s="68"/>
-      <c r="H25" s="68"/>
-      <c r="I25" s="68"/>
-      <c r="J25" s="68"/>
-      <c r="K25" s="68"/>
-      <c r="L25" s="68"/>
-      <c r="M25" s="68"/>
-      <c r="N25" s="68"/>
-      <c r="O25" s="68"/>
-      <c r="P25" s="68"/>
-      <c r="Q25" s="68"/>
-      <c r="R25" s="68"/>
-      <c r="S25" s="68"/>
-      <c r="T25" s="68"/>
-      <c r="U25" s="68"/>
-      <c r="V25" s="68"/>
-      <c r="W25" s="68"/>
-      <c r="X25" s="68"/>
-      <c r="Y25" s="68"/>
-      <c r="Z25" s="68"/>
-      <c r="AA25" s="68"/>
-      <c r="AB25" s="68"/>
-      <c r="AC25" s="68"/>
-      <c r="AD25" s="68"/>
-      <c r="AE25" s="68"/>
-      <c r="AF25" s="68"/>
-      <c r="AG25" s="68"/>
-      <c r="AH25" s="68"/>
-      <c r="AI25" s="68"/>
-      <c r="AJ25" s="68"/>
-      <c r="AK25" s="69"/>
+      <c r="G25" s="181"/>
+      <c r="H25" s="181"/>
+      <c r="I25" s="181"/>
+      <c r="J25" s="181"/>
+      <c r="K25" s="181"/>
+      <c r="L25" s="181"/>
+      <c r="M25" s="181"/>
+      <c r="N25" s="181"/>
+      <c r="O25" s="181"/>
+      <c r="P25" s="181"/>
+      <c r="Q25" s="181"/>
+      <c r="R25" s="181"/>
+      <c r="S25" s="181"/>
+      <c r="T25" s="181"/>
+      <c r="U25" s="181"/>
+      <c r="V25" s="181"/>
+      <c r="W25" s="181"/>
+      <c r="X25" s="181"/>
+      <c r="Y25" s="181"/>
+      <c r="Z25" s="181"/>
+      <c r="AA25" s="181"/>
+      <c r="AB25" s="181"/>
+      <c r="AC25" s="181"/>
+      <c r="AD25" s="181"/>
+      <c r="AE25" s="181"/>
+      <c r="AF25" s="181"/>
+      <c r="AG25" s="181"/>
+      <c r="AH25" s="181"/>
+      <c r="AI25" s="181"/>
+      <c r="AJ25" s="181"/>
+      <c r="AK25" s="182"/>
       <c r="AN25" s="3"/>
       <c r="AO25" s="3"/>
       <c r="AP25" s="3"/>
@@ -10000,44 +10152,44 @@
     </row>
     <row r="26" spans="1:254" s="2" customFormat="1" ht="28.25" customHeight="1">
       <c r="A26" s="38"/>
-      <c r="B26" s="125" t="s">
+      <c r="B26" s="143" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="126"/>
+      <c r="C26" s="144"/>
       <c r="D26" s="35"/>
       <c r="E26" s="35"/>
       <c r="F26" s="39"/>
-      <c r="G26" s="68"/>
-      <c r="H26" s="68"/>
-      <c r="I26" s="68"/>
-      <c r="J26" s="68"/>
-      <c r="K26" s="68"/>
-      <c r="L26" s="68"/>
-      <c r="M26" s="68"/>
-      <c r="N26" s="68"/>
-      <c r="O26" s="68"/>
-      <c r="P26" s="68"/>
-      <c r="Q26" s="68"/>
-      <c r="R26" s="68"/>
-      <c r="S26" s="68"/>
-      <c r="T26" s="68"/>
-      <c r="U26" s="68"/>
-      <c r="V26" s="68"/>
-      <c r="W26" s="68"/>
-      <c r="X26" s="68"/>
-      <c r="Y26" s="68"/>
-      <c r="Z26" s="68"/>
-      <c r="AA26" s="68"/>
-      <c r="AB26" s="68"/>
-      <c r="AC26" s="68"/>
-      <c r="AD26" s="68"/>
-      <c r="AE26" s="68"/>
-      <c r="AF26" s="68"/>
-      <c r="AG26" s="68"/>
-      <c r="AH26" s="68"/>
-      <c r="AI26" s="68"/>
-      <c r="AJ26" s="68"/>
-      <c r="AK26" s="69"/>
+      <c r="G26" s="181"/>
+      <c r="H26" s="181"/>
+      <c r="I26" s="181"/>
+      <c r="J26" s="181"/>
+      <c r="K26" s="181"/>
+      <c r="L26" s="181"/>
+      <c r="M26" s="181"/>
+      <c r="N26" s="181"/>
+      <c r="O26" s="181"/>
+      <c r="P26" s="181"/>
+      <c r="Q26" s="181"/>
+      <c r="R26" s="181"/>
+      <c r="S26" s="181"/>
+      <c r="T26" s="181"/>
+      <c r="U26" s="181"/>
+      <c r="V26" s="181"/>
+      <c r="W26" s="181"/>
+      <c r="X26" s="181"/>
+      <c r="Y26" s="181"/>
+      <c r="Z26" s="181"/>
+      <c r="AA26" s="181"/>
+      <c r="AB26" s="181"/>
+      <c r="AC26" s="181"/>
+      <c r="AD26" s="181"/>
+      <c r="AE26" s="181"/>
+      <c r="AF26" s="181"/>
+      <c r="AG26" s="181"/>
+      <c r="AH26" s="181"/>
+      <c r="AI26" s="181"/>
+      <c r="AJ26" s="181"/>
+      <c r="AK26" s="182"/>
       <c r="AN26" s="3"/>
       <c r="AO26" s="3"/>
       <c r="AP26" s="3"/>
@@ -10258,50 +10410,50 @@
       <c r="A27" s="37">
         <v>1</v>
       </c>
-      <c r="B27" s="114" t="s">
+      <c r="B27" s="141" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="115"/>
-      <c r="D27" s="97" t="s">
+      <c r="C27" s="142"/>
+      <c r="D27" s="92" t="s">
         <v>99</v>
       </c>
-      <c r="E27" s="97" t="s">
+      <c r="E27" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="116" t="s">
+      <c r="F27" s="158" t="s">
         <v>15</v>
       </c>
-      <c r="G27" s="70"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="70"/>
-      <c r="J27" s="70"/>
-      <c r="K27" s="70"/>
-      <c r="L27" s="70"/>
-      <c r="M27" s="70"/>
-      <c r="N27" s="70"/>
-      <c r="O27" s="70"/>
-      <c r="P27" s="70"/>
-      <c r="Q27" s="70"/>
-      <c r="R27" s="70"/>
-      <c r="S27" s="70"/>
-      <c r="T27" s="70"/>
-      <c r="U27" s="70"/>
-      <c r="V27" s="70"/>
-      <c r="W27" s="70"/>
-      <c r="X27" s="70"/>
-      <c r="Y27" s="70"/>
-      <c r="Z27" s="70"/>
-      <c r="AA27" s="70"/>
-      <c r="AB27" s="70"/>
-      <c r="AC27" s="70"/>
-      <c r="AD27" s="70"/>
-      <c r="AE27" s="70"/>
-      <c r="AF27" s="70"/>
-      <c r="AG27" s="70"/>
-      <c r="AH27" s="70"/>
-      <c r="AI27" s="70"/>
-      <c r="AJ27" s="70"/>
-      <c r="AK27" s="71"/>
+      <c r="G27" s="183"/>
+      <c r="H27" s="183"/>
+      <c r="I27" s="183"/>
+      <c r="J27" s="183"/>
+      <c r="K27" s="183"/>
+      <c r="L27" s="183"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="183"/>
+      <c r="O27" s="183"/>
+      <c r="P27" s="183"/>
+      <c r="Q27" s="183"/>
+      <c r="R27" s="183"/>
+      <c r="S27" s="183"/>
+      <c r="T27" s="183"/>
+      <c r="U27" s="183"/>
+      <c r="V27" s="183"/>
+      <c r="W27" s="183"/>
+      <c r="X27" s="183"/>
+      <c r="Y27" s="183"/>
+      <c r="Z27" s="183"/>
+      <c r="AA27" s="183"/>
+      <c r="AB27" s="183"/>
+      <c r="AC27" s="183"/>
+      <c r="AD27" s="183"/>
+      <c r="AE27" s="183"/>
+      <c r="AF27" s="183"/>
+      <c r="AG27" s="183"/>
+      <c r="AH27" s="183"/>
+      <c r="AI27" s="183"/>
+      <c r="AJ27" s="183"/>
+      <c r="AK27" s="184"/>
       <c r="AN27" s="3"/>
       <c r="AO27" s="3"/>
       <c r="AP27" s="3"/>
@@ -10522,46 +10674,46 @@
       <c r="A28" s="37">
         <v>2</v>
       </c>
-      <c r="B28" s="114" t="s">
+      <c r="B28" s="141" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="115"/>
+      <c r="C28" s="142"/>
       <c r="D28" s="35" t="s">
         <v>77</v>
       </c>
       <c r="E28" s="35"/>
-      <c r="F28" s="117"/>
-      <c r="G28" s="70"/>
-      <c r="H28" s="70"/>
-      <c r="I28" s="70"/>
-      <c r="J28" s="70"/>
-      <c r="K28" s="70"/>
-      <c r="L28" s="70"/>
-      <c r="M28" s="70"/>
-      <c r="N28" s="70"/>
-      <c r="O28" s="70"/>
-      <c r="P28" s="70"/>
-      <c r="Q28" s="70"/>
-      <c r="R28" s="70"/>
-      <c r="S28" s="70"/>
-      <c r="T28" s="70"/>
-      <c r="U28" s="70"/>
-      <c r="V28" s="70"/>
-      <c r="W28" s="70"/>
-      <c r="X28" s="70"/>
-      <c r="Y28" s="70"/>
-      <c r="Z28" s="70"/>
-      <c r="AA28" s="70"/>
-      <c r="AB28" s="70"/>
-      <c r="AC28" s="70"/>
-      <c r="AD28" s="70"/>
-      <c r="AE28" s="70"/>
-      <c r="AF28" s="70"/>
-      <c r="AG28" s="70"/>
-      <c r="AH28" s="70"/>
-      <c r="AI28" s="70"/>
-      <c r="AJ28" s="70"/>
-      <c r="AK28" s="71"/>
+      <c r="F28" s="106"/>
+      <c r="G28" s="183"/>
+      <c r="H28" s="183"/>
+      <c r="I28" s="183"/>
+      <c r="J28" s="183"/>
+      <c r="K28" s="183"/>
+      <c r="L28" s="183"/>
+      <c r="M28" s="183"/>
+      <c r="N28" s="183"/>
+      <c r="O28" s="183"/>
+      <c r="P28" s="183"/>
+      <c r="Q28" s="183"/>
+      <c r="R28" s="183"/>
+      <c r="S28" s="183"/>
+      <c r="T28" s="183"/>
+      <c r="U28" s="183"/>
+      <c r="V28" s="183"/>
+      <c r="W28" s="183"/>
+      <c r="X28" s="183"/>
+      <c r="Y28" s="183"/>
+      <c r="Z28" s="183"/>
+      <c r="AA28" s="183"/>
+      <c r="AB28" s="183"/>
+      <c r="AC28" s="183"/>
+      <c r="AD28" s="183"/>
+      <c r="AE28" s="183"/>
+      <c r="AF28" s="183"/>
+      <c r="AG28" s="183"/>
+      <c r="AH28" s="183"/>
+      <c r="AI28" s="183"/>
+      <c r="AJ28" s="183"/>
+      <c r="AK28" s="184"/>
       <c r="AN28" s="3"/>
       <c r="AO28" s="3"/>
       <c r="AP28" s="3"/>
@@ -10782,46 +10934,46 @@
       <c r="A29" s="37">
         <v>3</v>
       </c>
-      <c r="B29" s="112" t="s">
+      <c r="B29" s="104" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="113"/>
+      <c r="C29" s="105"/>
       <c r="D29" s="35" t="s">
         <v>77</v>
       </c>
       <c r="E29" s="35"/>
-      <c r="F29" s="117"/>
-      <c r="G29" s="70"/>
-      <c r="H29" s="70"/>
-      <c r="I29" s="70"/>
-      <c r="J29" s="70"/>
-      <c r="K29" s="70"/>
-      <c r="L29" s="70"/>
-      <c r="M29" s="70"/>
-      <c r="N29" s="70"/>
-      <c r="O29" s="70"/>
-      <c r="P29" s="70"/>
-      <c r="Q29" s="70"/>
-      <c r="R29" s="70"/>
-      <c r="S29" s="70"/>
-      <c r="T29" s="70"/>
-      <c r="U29" s="70"/>
-      <c r="V29" s="70"/>
-      <c r="W29" s="70"/>
-      <c r="X29" s="70"/>
-      <c r="Y29" s="70"/>
-      <c r="Z29" s="70"/>
-      <c r="AA29" s="70"/>
-      <c r="AB29" s="70"/>
-      <c r="AC29" s="70"/>
-      <c r="AD29" s="70"/>
-      <c r="AE29" s="70"/>
-      <c r="AF29" s="70"/>
-      <c r="AG29" s="70"/>
-      <c r="AH29" s="70"/>
-      <c r="AI29" s="70"/>
-      <c r="AJ29" s="70"/>
-      <c r="AK29" s="72"/>
+      <c r="F29" s="106"/>
+      <c r="G29" s="183"/>
+      <c r="H29" s="183"/>
+      <c r="I29" s="183"/>
+      <c r="J29" s="183"/>
+      <c r="K29" s="183"/>
+      <c r="L29" s="183"/>
+      <c r="M29" s="183"/>
+      <c r="N29" s="183"/>
+      <c r="O29" s="183"/>
+      <c r="P29" s="183"/>
+      <c r="Q29" s="183"/>
+      <c r="R29" s="183"/>
+      <c r="S29" s="183"/>
+      <c r="T29" s="183"/>
+      <c r="U29" s="183"/>
+      <c r="V29" s="183"/>
+      <c r="W29" s="183"/>
+      <c r="X29" s="183"/>
+      <c r="Y29" s="183"/>
+      <c r="Z29" s="183"/>
+      <c r="AA29" s="183"/>
+      <c r="AB29" s="183"/>
+      <c r="AC29" s="183"/>
+      <c r="AD29" s="183"/>
+      <c r="AE29" s="183"/>
+      <c r="AF29" s="183"/>
+      <c r="AG29" s="183"/>
+      <c r="AH29" s="183"/>
+      <c r="AI29" s="183"/>
+      <c r="AJ29" s="183"/>
+      <c r="AK29" s="185"/>
       <c r="AN29" s="3"/>
       <c r="AO29" s="3"/>
       <c r="AP29" s="3"/>
@@ -11042,48 +11194,48 @@
       <c r="A30" s="37">
         <v>4</v>
       </c>
-      <c r="B30" s="112" t="s">
+      <c r="B30" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="C30" s="113"/>
-      <c r="D30" s="101" t="s">
+      <c r="C30" s="105"/>
+      <c r="D30" s="96" t="s">
         <v>103</v>
       </c>
-      <c r="E30" s="97" t="s">
+      <c r="E30" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="F30" s="117"/>
-      <c r="G30" s="68"/>
-      <c r="H30" s="68"/>
-      <c r="I30" s="68"/>
-      <c r="J30" s="68"/>
-      <c r="K30" s="68"/>
-      <c r="L30" s="68"/>
-      <c r="M30" s="68"/>
-      <c r="N30" s="68"/>
-      <c r="O30" s="68"/>
-      <c r="P30" s="68"/>
-      <c r="Q30" s="68"/>
-      <c r="R30" s="68"/>
-      <c r="S30" s="68"/>
-      <c r="T30" s="68"/>
-      <c r="U30" s="68"/>
-      <c r="V30" s="68"/>
-      <c r="W30" s="68"/>
-      <c r="X30" s="68"/>
-      <c r="Y30" s="68"/>
-      <c r="Z30" s="68"/>
-      <c r="AA30" s="68"/>
-      <c r="AB30" s="68"/>
-      <c r="AC30" s="68"/>
-      <c r="AD30" s="68"/>
-      <c r="AE30" s="68"/>
-      <c r="AF30" s="68"/>
-      <c r="AG30" s="68"/>
-      <c r="AH30" s="68"/>
-      <c r="AI30" s="68"/>
-      <c r="AJ30" s="68"/>
-      <c r="AK30" s="69"/>
+      <c r="F30" s="106"/>
+      <c r="G30" s="181"/>
+      <c r="H30" s="181"/>
+      <c r="I30" s="181"/>
+      <c r="J30" s="181"/>
+      <c r="K30" s="181"/>
+      <c r="L30" s="181"/>
+      <c r="M30" s="181"/>
+      <c r="N30" s="181"/>
+      <c r="O30" s="181"/>
+      <c r="P30" s="181"/>
+      <c r="Q30" s="181"/>
+      <c r="R30" s="181"/>
+      <c r="S30" s="181"/>
+      <c r="T30" s="181"/>
+      <c r="U30" s="181"/>
+      <c r="V30" s="181"/>
+      <c r="W30" s="181"/>
+      <c r="X30" s="181"/>
+      <c r="Y30" s="181"/>
+      <c r="Z30" s="181"/>
+      <c r="AA30" s="181"/>
+      <c r="AB30" s="181"/>
+      <c r="AC30" s="181"/>
+      <c r="AD30" s="181"/>
+      <c r="AE30" s="181"/>
+      <c r="AF30" s="181"/>
+      <c r="AG30" s="181"/>
+      <c r="AH30" s="181"/>
+      <c r="AI30" s="181"/>
+      <c r="AJ30" s="181"/>
+      <c r="AK30" s="182"/>
       <c r="AN30" s="3"/>
       <c r="AO30" s="3"/>
       <c r="AP30" s="3"/>
@@ -11304,46 +11456,46 @@
       <c r="A31" s="37">
         <v>5</v>
       </c>
-      <c r="B31" s="114" t="s">
+      <c r="B31" s="141" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="115"/>
-      <c r="D31" s="97" t="s">
+      <c r="C31" s="142"/>
+      <c r="D31" s="92" t="s">
         <v>80</v>
       </c>
       <c r="E31" s="35"/>
-      <c r="F31" s="117"/>
-      <c r="G31" s="68"/>
-      <c r="H31" s="68"/>
-      <c r="I31" s="68"/>
-      <c r="J31" s="68"/>
-      <c r="K31" s="68"/>
-      <c r="L31" s="68"/>
-      <c r="M31" s="68"/>
-      <c r="N31" s="68"/>
-      <c r="O31" s="68"/>
-      <c r="P31" s="68"/>
-      <c r="Q31" s="68"/>
-      <c r="R31" s="68"/>
-      <c r="S31" s="68"/>
-      <c r="T31" s="68"/>
-      <c r="U31" s="68"/>
-      <c r="V31" s="68"/>
-      <c r="W31" s="68"/>
-      <c r="X31" s="68"/>
-      <c r="Y31" s="68"/>
-      <c r="Z31" s="68"/>
-      <c r="AA31" s="68"/>
-      <c r="AB31" s="68"/>
-      <c r="AC31" s="68"/>
-      <c r="AD31" s="68"/>
-      <c r="AE31" s="68"/>
-      <c r="AF31" s="68"/>
-      <c r="AG31" s="68"/>
-      <c r="AH31" s="68"/>
-      <c r="AI31" s="68"/>
-      <c r="AJ31" s="68"/>
-      <c r="AK31" s="69"/>
+      <c r="F31" s="106"/>
+      <c r="G31" s="181"/>
+      <c r="H31" s="181"/>
+      <c r="I31" s="181"/>
+      <c r="J31" s="181"/>
+      <c r="K31" s="181"/>
+      <c r="L31" s="181"/>
+      <c r="M31" s="181"/>
+      <c r="N31" s="181"/>
+      <c r="O31" s="181"/>
+      <c r="P31" s="181"/>
+      <c r="Q31" s="181"/>
+      <c r="R31" s="181"/>
+      <c r="S31" s="181"/>
+      <c r="T31" s="181"/>
+      <c r="U31" s="181"/>
+      <c r="V31" s="181"/>
+      <c r="W31" s="181"/>
+      <c r="X31" s="181"/>
+      <c r="Y31" s="181"/>
+      <c r="Z31" s="181"/>
+      <c r="AA31" s="181"/>
+      <c r="AB31" s="181"/>
+      <c r="AC31" s="181"/>
+      <c r="AD31" s="181"/>
+      <c r="AE31" s="181"/>
+      <c r="AF31" s="181"/>
+      <c r="AG31" s="181"/>
+      <c r="AH31" s="181"/>
+      <c r="AI31" s="181"/>
+      <c r="AJ31" s="181"/>
+      <c r="AK31" s="182"/>
       <c r="AN31" s="3"/>
       <c r="AO31" s="3"/>
       <c r="AP31" s="3"/>
@@ -11564,46 +11716,46 @@
       <c r="A32" s="37">
         <v>6</v>
       </c>
-      <c r="B32" s="112" t="s">
+      <c r="B32" s="104" t="s">
         <v>57</v>
       </c>
-      <c r="C32" s="113"/>
-      <c r="D32" s="97" t="s">
+      <c r="C32" s="105"/>
+      <c r="D32" s="92" t="s">
         <v>118</v>
       </c>
       <c r="E32" s="35"/>
-      <c r="F32" s="117"/>
-      <c r="G32" s="68"/>
-      <c r="H32" s="68"/>
-      <c r="I32" s="68"/>
-      <c r="J32" s="68"/>
-      <c r="K32" s="68"/>
-      <c r="L32" s="68"/>
-      <c r="M32" s="68"/>
-      <c r="N32" s="68"/>
-      <c r="O32" s="68"/>
-      <c r="P32" s="68"/>
-      <c r="Q32" s="68"/>
-      <c r="R32" s="68"/>
-      <c r="S32" s="68"/>
-      <c r="T32" s="68"/>
-      <c r="U32" s="68"/>
-      <c r="V32" s="68"/>
-      <c r="W32" s="68"/>
-      <c r="X32" s="68"/>
-      <c r="Y32" s="68"/>
-      <c r="Z32" s="68"/>
-      <c r="AA32" s="68"/>
-      <c r="AB32" s="68"/>
-      <c r="AC32" s="68"/>
-      <c r="AD32" s="68"/>
-      <c r="AE32" s="68"/>
-      <c r="AF32" s="68"/>
-      <c r="AG32" s="68"/>
-      <c r="AH32" s="68"/>
-      <c r="AI32" s="68"/>
-      <c r="AJ32" s="73"/>
-      <c r="AK32" s="74"/>
+      <c r="F32" s="106"/>
+      <c r="G32" s="181"/>
+      <c r="H32" s="181"/>
+      <c r="I32" s="181"/>
+      <c r="J32" s="181"/>
+      <c r="K32" s="181"/>
+      <c r="L32" s="181"/>
+      <c r="M32" s="181"/>
+      <c r="N32" s="181"/>
+      <c r="O32" s="181"/>
+      <c r="P32" s="181"/>
+      <c r="Q32" s="181"/>
+      <c r="R32" s="181"/>
+      <c r="S32" s="181"/>
+      <c r="T32" s="181"/>
+      <c r="U32" s="181"/>
+      <c r="V32" s="181"/>
+      <c r="W32" s="181"/>
+      <c r="X32" s="181"/>
+      <c r="Y32" s="181"/>
+      <c r="Z32" s="181"/>
+      <c r="AA32" s="181"/>
+      <c r="AB32" s="181"/>
+      <c r="AC32" s="181"/>
+      <c r="AD32" s="181"/>
+      <c r="AE32" s="181"/>
+      <c r="AF32" s="181"/>
+      <c r="AG32" s="181"/>
+      <c r="AH32" s="181"/>
+      <c r="AI32" s="181"/>
+      <c r="AJ32" s="186"/>
+      <c r="AK32" s="187"/>
       <c r="AN32" s="3"/>
       <c r="AO32" s="3"/>
       <c r="AP32" s="3"/>
@@ -11824,46 +11976,46 @@
       <c r="A33" s="37">
         <v>7</v>
       </c>
-      <c r="B33" s="112" t="s">
+      <c r="B33" s="104" t="s">
         <v>58</v>
       </c>
-      <c r="C33" s="113"/>
-      <c r="D33" s="97" t="s">
+      <c r="C33" s="105"/>
+      <c r="D33" s="92" t="s">
         <v>118</v>
       </c>
       <c r="E33" s="35"/>
-      <c r="F33" s="117"/>
-      <c r="G33" s="68"/>
-      <c r="H33" s="68"/>
-      <c r="I33" s="68"/>
-      <c r="J33" s="68"/>
-      <c r="K33" s="68"/>
-      <c r="L33" s="68"/>
-      <c r="M33" s="68"/>
-      <c r="N33" s="68"/>
-      <c r="O33" s="68"/>
-      <c r="P33" s="68"/>
-      <c r="Q33" s="68"/>
-      <c r="R33" s="68"/>
-      <c r="S33" s="68"/>
-      <c r="T33" s="68"/>
-      <c r="U33" s="68"/>
-      <c r="V33" s="68"/>
-      <c r="W33" s="68"/>
-      <c r="X33" s="68"/>
-      <c r="Y33" s="68"/>
-      <c r="Z33" s="68"/>
-      <c r="AA33" s="68"/>
-      <c r="AB33" s="68"/>
-      <c r="AC33" s="68"/>
-      <c r="AD33" s="68"/>
-      <c r="AE33" s="68"/>
-      <c r="AF33" s="68"/>
-      <c r="AG33" s="68"/>
-      <c r="AH33" s="68"/>
-      <c r="AI33" s="68"/>
-      <c r="AJ33" s="73"/>
-      <c r="AK33" s="74"/>
+      <c r="F33" s="106"/>
+      <c r="G33" s="181"/>
+      <c r="H33" s="181"/>
+      <c r="I33" s="181"/>
+      <c r="J33" s="181"/>
+      <c r="K33" s="181"/>
+      <c r="L33" s="181"/>
+      <c r="M33" s="181"/>
+      <c r="N33" s="181"/>
+      <c r="O33" s="181"/>
+      <c r="P33" s="181"/>
+      <c r="Q33" s="181"/>
+      <c r="R33" s="181"/>
+      <c r="S33" s="181"/>
+      <c r="T33" s="181"/>
+      <c r="U33" s="181"/>
+      <c r="V33" s="181"/>
+      <c r="W33" s="181"/>
+      <c r="X33" s="181"/>
+      <c r="Y33" s="181"/>
+      <c r="Z33" s="181"/>
+      <c r="AA33" s="181"/>
+      <c r="AB33" s="181"/>
+      <c r="AC33" s="181"/>
+      <c r="AD33" s="181"/>
+      <c r="AE33" s="181"/>
+      <c r="AF33" s="181"/>
+      <c r="AG33" s="181"/>
+      <c r="AH33" s="181"/>
+      <c r="AI33" s="181"/>
+      <c r="AJ33" s="186"/>
+      <c r="AK33" s="187"/>
       <c r="AN33" s="3"/>
       <c r="AO33" s="3"/>
       <c r="AP33" s="3"/>
@@ -12084,46 +12236,46 @@
       <c r="A34" s="37">
         <v>8</v>
       </c>
-      <c r="B34" s="114" t="s">
+      <c r="B34" s="141" t="s">
         <v>59</v>
       </c>
-      <c r="C34" s="115"/>
-      <c r="D34" s="97" t="s">
+      <c r="C34" s="142"/>
+      <c r="D34" s="92" t="s">
         <v>99</v>
       </c>
       <c r="E34" s="40"/>
-      <c r="F34" s="117"/>
-      <c r="G34" s="70"/>
-      <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
-      <c r="J34" s="70"/>
-      <c r="K34" s="70"/>
-      <c r="L34" s="70"/>
-      <c r="M34" s="70"/>
-      <c r="N34" s="70"/>
-      <c r="O34" s="70"/>
-      <c r="P34" s="70"/>
-      <c r="Q34" s="70"/>
-      <c r="R34" s="70"/>
-      <c r="S34" s="70"/>
-      <c r="T34" s="70"/>
-      <c r="U34" s="70"/>
-      <c r="V34" s="70"/>
-      <c r="W34" s="70"/>
-      <c r="X34" s="70"/>
-      <c r="Y34" s="70"/>
-      <c r="Z34" s="70"/>
-      <c r="AA34" s="70"/>
-      <c r="AB34" s="70"/>
-      <c r="AC34" s="70"/>
-      <c r="AD34" s="70"/>
-      <c r="AE34" s="70"/>
-      <c r="AF34" s="70"/>
-      <c r="AG34" s="70"/>
-      <c r="AH34" s="70"/>
-      <c r="AI34" s="70"/>
-      <c r="AJ34" s="75"/>
-      <c r="AK34" s="76"/>
+      <c r="F34" s="106"/>
+      <c r="G34" s="183"/>
+      <c r="H34" s="183"/>
+      <c r="I34" s="183"/>
+      <c r="J34" s="183"/>
+      <c r="K34" s="183"/>
+      <c r="L34" s="183"/>
+      <c r="M34" s="183"/>
+      <c r="N34" s="183"/>
+      <c r="O34" s="183"/>
+      <c r="P34" s="183"/>
+      <c r="Q34" s="183"/>
+      <c r="R34" s="183"/>
+      <c r="S34" s="183"/>
+      <c r="T34" s="183"/>
+      <c r="U34" s="183"/>
+      <c r="V34" s="183"/>
+      <c r="W34" s="183"/>
+      <c r="X34" s="183"/>
+      <c r="Y34" s="183"/>
+      <c r="Z34" s="183"/>
+      <c r="AA34" s="183"/>
+      <c r="AB34" s="183"/>
+      <c r="AC34" s="183"/>
+      <c r="AD34" s="183"/>
+      <c r="AE34" s="183"/>
+      <c r="AF34" s="183"/>
+      <c r="AG34" s="183"/>
+      <c r="AH34" s="183"/>
+      <c r="AI34" s="183"/>
+      <c r="AJ34" s="188"/>
+      <c r="AK34" s="189"/>
       <c r="AN34" s="3"/>
       <c r="AO34" s="3"/>
       <c r="AP34" s="3"/>
@@ -12344,46 +12496,46 @@
       <c r="A35" s="37">
         <v>9</v>
       </c>
-      <c r="B35" s="114" t="s">
+      <c r="B35" s="141" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="115"/>
-      <c r="D35" s="97" t="s">
+      <c r="C35" s="142"/>
+      <c r="D35" s="92" t="s">
         <v>49</v>
       </c>
       <c r="E35" s="40"/>
-      <c r="F35" s="127"/>
-      <c r="G35" s="70"/>
-      <c r="H35" s="70"/>
-      <c r="I35" s="70"/>
-      <c r="J35" s="70"/>
-      <c r="K35" s="70"/>
-      <c r="L35" s="70"/>
-      <c r="M35" s="70"/>
-      <c r="N35" s="70"/>
-      <c r="O35" s="70"/>
-      <c r="P35" s="70"/>
-      <c r="Q35" s="70"/>
-      <c r="R35" s="70"/>
-      <c r="S35" s="70"/>
-      <c r="T35" s="70"/>
-      <c r="U35" s="70"/>
-      <c r="V35" s="70"/>
-      <c r="W35" s="70"/>
-      <c r="X35" s="70"/>
-      <c r="Y35" s="70"/>
-      <c r="Z35" s="70"/>
-      <c r="AA35" s="70"/>
-      <c r="AB35" s="70"/>
-      <c r="AC35" s="70"/>
-      <c r="AD35" s="70"/>
-      <c r="AE35" s="70"/>
-      <c r="AF35" s="70"/>
-      <c r="AG35" s="70"/>
-      <c r="AH35" s="70"/>
-      <c r="AI35" s="70"/>
-      <c r="AJ35" s="75"/>
-      <c r="AK35" s="76"/>
+      <c r="F35" s="107"/>
+      <c r="G35" s="183"/>
+      <c r="H35" s="183"/>
+      <c r="I35" s="183"/>
+      <c r="J35" s="183"/>
+      <c r="K35" s="183"/>
+      <c r="L35" s="183"/>
+      <c r="M35" s="183"/>
+      <c r="N35" s="183"/>
+      <c r="O35" s="183"/>
+      <c r="P35" s="183"/>
+      <c r="Q35" s="183"/>
+      <c r="R35" s="183"/>
+      <c r="S35" s="183"/>
+      <c r="T35" s="183"/>
+      <c r="U35" s="183"/>
+      <c r="V35" s="183"/>
+      <c r="W35" s="183"/>
+      <c r="X35" s="183"/>
+      <c r="Y35" s="183"/>
+      <c r="Z35" s="183"/>
+      <c r="AA35" s="183"/>
+      <c r="AB35" s="183"/>
+      <c r="AC35" s="183"/>
+      <c r="AD35" s="183"/>
+      <c r="AE35" s="183"/>
+      <c r="AF35" s="183"/>
+      <c r="AG35" s="183"/>
+      <c r="AH35" s="183"/>
+      <c r="AI35" s="183"/>
+      <c r="AJ35" s="188"/>
+      <c r="AK35" s="189"/>
       <c r="AN35" s="3"/>
       <c r="AO35" s="3"/>
       <c r="AP35" s="3"/>
@@ -12602,44 +12754,44 @@
     </row>
     <row r="36" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A36" s="37"/>
-      <c r="B36" s="125" t="s">
-        <v>128</v>
-      </c>
-      <c r="C36" s="126"/>
-      <c r="D36" s="97"/>
+      <c r="B36" s="143" t="s">
+        <v>127</v>
+      </c>
+      <c r="C36" s="144"/>
+      <c r="D36" s="92"/>
       <c r="E36" s="40"/>
-      <c r="F36" s="98"/>
-      <c r="G36" s="70"/>
-      <c r="H36" s="70"/>
-      <c r="I36" s="70"/>
-      <c r="J36" s="70"/>
-      <c r="K36" s="70"/>
-      <c r="L36" s="70"/>
-      <c r="M36" s="70"/>
-      <c r="N36" s="70"/>
-      <c r="O36" s="70"/>
-      <c r="P36" s="70"/>
-      <c r="Q36" s="70"/>
-      <c r="R36" s="70"/>
-      <c r="S36" s="70"/>
-      <c r="T36" s="70"/>
-      <c r="U36" s="70"/>
-      <c r="V36" s="70"/>
-      <c r="W36" s="70"/>
-      <c r="X36" s="70"/>
-      <c r="Y36" s="70"/>
-      <c r="Z36" s="70"/>
-      <c r="AA36" s="70"/>
-      <c r="AB36" s="70"/>
-      <c r="AC36" s="70"/>
-      <c r="AD36" s="70"/>
-      <c r="AE36" s="70"/>
-      <c r="AF36" s="70"/>
-      <c r="AG36" s="70"/>
-      <c r="AH36" s="70"/>
-      <c r="AI36" s="70"/>
-      <c r="AJ36" s="75"/>
-      <c r="AK36" s="76"/>
+      <c r="F36" s="93"/>
+      <c r="G36" s="183"/>
+      <c r="H36" s="183"/>
+      <c r="I36" s="183"/>
+      <c r="J36" s="183"/>
+      <c r="K36" s="183"/>
+      <c r="L36" s="183"/>
+      <c r="M36" s="183"/>
+      <c r="N36" s="183"/>
+      <c r="O36" s="183"/>
+      <c r="P36" s="183"/>
+      <c r="Q36" s="183"/>
+      <c r="R36" s="183"/>
+      <c r="S36" s="183"/>
+      <c r="T36" s="183"/>
+      <c r="U36" s="183"/>
+      <c r="V36" s="183"/>
+      <c r="W36" s="183"/>
+      <c r="X36" s="183"/>
+      <c r="Y36" s="183"/>
+      <c r="Z36" s="183"/>
+      <c r="AA36" s="183"/>
+      <c r="AB36" s="183"/>
+      <c r="AC36" s="183"/>
+      <c r="AD36" s="183"/>
+      <c r="AE36" s="183"/>
+      <c r="AF36" s="183"/>
+      <c r="AG36" s="183"/>
+      <c r="AH36" s="183"/>
+      <c r="AI36" s="183"/>
+      <c r="AJ36" s="188"/>
+      <c r="AK36" s="189"/>
       <c r="AN36" s="3"/>
       <c r="AO36" s="3"/>
       <c r="AP36" s="3"/>
@@ -12858,44 +13010,44 @@
     </row>
     <row r="37" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A37" s="37"/>
-      <c r="B37" s="114" t="s">
-        <v>129</v>
-      </c>
-      <c r="C37" s="115"/>
-      <c r="D37" s="97"/>
+      <c r="B37" s="141" t="s">
+        <v>128</v>
+      </c>
+      <c r="C37" s="142"/>
+      <c r="D37" s="92"/>
       <c r="E37" s="40"/>
-      <c r="F37" s="98"/>
-      <c r="G37" s="70"/>
-      <c r="H37" s="70"/>
-      <c r="I37" s="70"/>
-      <c r="J37" s="70"/>
-      <c r="K37" s="70"/>
-      <c r="L37" s="70"/>
-      <c r="M37" s="70"/>
-      <c r="N37" s="70"/>
-      <c r="O37" s="70"/>
-      <c r="P37" s="70"/>
-      <c r="Q37" s="70"/>
-      <c r="R37" s="70"/>
-      <c r="S37" s="70"/>
-      <c r="T37" s="70"/>
-      <c r="U37" s="70"/>
-      <c r="V37" s="70"/>
-      <c r="W37" s="70"/>
-      <c r="X37" s="70"/>
-      <c r="Y37" s="70"/>
-      <c r="Z37" s="70"/>
-      <c r="AA37" s="70"/>
-      <c r="AB37" s="70"/>
-      <c r="AC37" s="70"/>
-      <c r="AD37" s="70"/>
-      <c r="AE37" s="70"/>
-      <c r="AF37" s="70"/>
-      <c r="AG37" s="70"/>
-      <c r="AH37" s="70"/>
-      <c r="AI37" s="70"/>
-      <c r="AJ37" s="75"/>
-      <c r="AK37" s="76"/>
+      <c r="F37" s="93"/>
+      <c r="G37" s="183"/>
+      <c r="H37" s="183"/>
+      <c r="I37" s="183"/>
+      <c r="J37" s="183"/>
+      <c r="K37" s="183"/>
+      <c r="L37" s="183"/>
+      <c r="M37" s="183"/>
+      <c r="N37" s="183"/>
+      <c r="O37" s="183"/>
+      <c r="P37" s="183"/>
+      <c r="Q37" s="183"/>
+      <c r="R37" s="183"/>
+      <c r="S37" s="183"/>
+      <c r="T37" s="183"/>
+      <c r="U37" s="183"/>
+      <c r="V37" s="183"/>
+      <c r="W37" s="183"/>
+      <c r="X37" s="183"/>
+      <c r="Y37" s="183"/>
+      <c r="Z37" s="183"/>
+      <c r="AA37" s="183"/>
+      <c r="AB37" s="183"/>
+      <c r="AC37" s="183"/>
+      <c r="AD37" s="183"/>
+      <c r="AE37" s="183"/>
+      <c r="AF37" s="183"/>
+      <c r="AG37" s="183"/>
+      <c r="AH37" s="183"/>
+      <c r="AI37" s="183"/>
+      <c r="AJ37" s="188"/>
+      <c r="AK37" s="189"/>
       <c r="AN37" s="3"/>
       <c r="AO37" s="3"/>
       <c r="AP37" s="3"/>
@@ -13114,44 +13266,44 @@
     </row>
     <row r="38" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A38" s="37"/>
-      <c r="B38" s="123" t="s">
-        <v>130</v>
-      </c>
-      <c r="C38" s="124"/>
-      <c r="D38" s="97"/>
+      <c r="B38" s="147" t="s">
+        <v>129</v>
+      </c>
+      <c r="C38" s="148"/>
+      <c r="D38" s="92"/>
       <c r="E38" s="40"/>
-      <c r="F38" s="98"/>
-      <c r="G38" s="70"/>
-      <c r="H38" s="70"/>
-      <c r="I38" s="70"/>
-      <c r="J38" s="70"/>
-      <c r="K38" s="70"/>
-      <c r="L38" s="70"/>
-      <c r="M38" s="70"/>
-      <c r="N38" s="70"/>
-      <c r="O38" s="70"/>
-      <c r="P38" s="70"/>
-      <c r="Q38" s="70"/>
-      <c r="R38" s="70"/>
-      <c r="S38" s="70"/>
-      <c r="T38" s="70"/>
-      <c r="U38" s="70"/>
-      <c r="V38" s="70"/>
-      <c r="W38" s="70"/>
-      <c r="X38" s="70"/>
-      <c r="Y38" s="70"/>
-      <c r="Z38" s="70"/>
-      <c r="AA38" s="70"/>
-      <c r="AB38" s="70"/>
-      <c r="AC38" s="70"/>
-      <c r="AD38" s="70"/>
-      <c r="AE38" s="70"/>
-      <c r="AF38" s="70"/>
-      <c r="AG38" s="70"/>
-      <c r="AH38" s="70"/>
-      <c r="AI38" s="70"/>
-      <c r="AJ38" s="75"/>
-      <c r="AK38" s="76"/>
+      <c r="F38" s="93"/>
+      <c r="G38" s="183"/>
+      <c r="H38" s="183"/>
+      <c r="I38" s="183"/>
+      <c r="J38" s="183"/>
+      <c r="K38" s="183"/>
+      <c r="L38" s="183"/>
+      <c r="M38" s="183"/>
+      <c r="N38" s="183"/>
+      <c r="O38" s="183"/>
+      <c r="P38" s="183"/>
+      <c r="Q38" s="183"/>
+      <c r="R38" s="183"/>
+      <c r="S38" s="183"/>
+      <c r="T38" s="183"/>
+      <c r="U38" s="183"/>
+      <c r="V38" s="183"/>
+      <c r="W38" s="183"/>
+      <c r="X38" s="183"/>
+      <c r="Y38" s="183"/>
+      <c r="Z38" s="183"/>
+      <c r="AA38" s="183"/>
+      <c r="AB38" s="183"/>
+      <c r="AC38" s="183"/>
+      <c r="AD38" s="183"/>
+      <c r="AE38" s="183"/>
+      <c r="AF38" s="183"/>
+      <c r="AG38" s="183"/>
+      <c r="AH38" s="183"/>
+      <c r="AI38" s="183"/>
+      <c r="AJ38" s="188"/>
+      <c r="AK38" s="189"/>
       <c r="AN38" s="3"/>
       <c r="AO38" s="3"/>
       <c r="AP38" s="3"/>
@@ -13370,42 +13522,42 @@
     </row>
     <row r="39" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A39" s="37"/>
-      <c r="B39" s="123"/>
-      <c r="C39" s="124"/>
-      <c r="D39" s="97"/>
+      <c r="B39" s="147"/>
+      <c r="C39" s="148"/>
+      <c r="D39" s="92"/>
       <c r="E39" s="40"/>
-      <c r="F39" s="98"/>
-      <c r="G39" s="70"/>
-      <c r="H39" s="70"/>
-      <c r="I39" s="70"/>
-      <c r="J39" s="70"/>
-      <c r="K39" s="70"/>
-      <c r="L39" s="70"/>
-      <c r="M39" s="70"/>
-      <c r="N39" s="70"/>
-      <c r="O39" s="70"/>
-      <c r="P39" s="70"/>
-      <c r="Q39" s="70"/>
-      <c r="R39" s="70"/>
-      <c r="S39" s="70"/>
-      <c r="T39" s="70"/>
-      <c r="U39" s="70"/>
-      <c r="V39" s="70"/>
-      <c r="W39" s="70"/>
-      <c r="X39" s="70"/>
-      <c r="Y39" s="70"/>
-      <c r="Z39" s="70"/>
-      <c r="AA39" s="70"/>
-      <c r="AB39" s="70"/>
-      <c r="AC39" s="70"/>
-      <c r="AD39" s="70"/>
-      <c r="AE39" s="70"/>
-      <c r="AF39" s="70"/>
-      <c r="AG39" s="70"/>
-      <c r="AH39" s="70"/>
-      <c r="AI39" s="70"/>
-      <c r="AJ39" s="75"/>
-      <c r="AK39" s="76"/>
+      <c r="F39" s="93"/>
+      <c r="G39" s="183"/>
+      <c r="H39" s="183"/>
+      <c r="I39" s="183"/>
+      <c r="J39" s="183"/>
+      <c r="K39" s="183"/>
+      <c r="L39" s="183"/>
+      <c r="M39" s="183"/>
+      <c r="N39" s="183"/>
+      <c r="O39" s="183"/>
+      <c r="P39" s="183"/>
+      <c r="Q39" s="183"/>
+      <c r="R39" s="183"/>
+      <c r="S39" s="183"/>
+      <c r="T39" s="183"/>
+      <c r="U39" s="183"/>
+      <c r="V39" s="183"/>
+      <c r="W39" s="183"/>
+      <c r="X39" s="183"/>
+      <c r="Y39" s="183"/>
+      <c r="Z39" s="183"/>
+      <c r="AA39" s="183"/>
+      <c r="AB39" s="183"/>
+      <c r="AC39" s="183"/>
+      <c r="AD39" s="183"/>
+      <c r="AE39" s="183"/>
+      <c r="AF39" s="183"/>
+      <c r="AG39" s="183"/>
+      <c r="AH39" s="183"/>
+      <c r="AI39" s="183"/>
+      <c r="AJ39" s="188"/>
+      <c r="AK39" s="189"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
@@ -13624,46 +13776,46 @@
     </row>
     <row r="40" spans="1:254" s="2" customFormat="1" ht="42" customHeight="1" thickBot="1">
       <c r="A40" s="41"/>
-      <c r="B40" s="121" t="s">
+      <c r="B40" s="145" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="122"/>
+      <c r="C40" s="146"/>
       <c r="D40" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="E40" s="100"/>
+      <c r="E40" s="95"/>
       <c r="F40" s="43"/>
-      <c r="G40" s="77"/>
-      <c r="H40" s="77"/>
-      <c r="I40" s="77"/>
-      <c r="J40" s="77"/>
-      <c r="K40" s="77"/>
-      <c r="L40" s="77"/>
-      <c r="M40" s="77"/>
-      <c r="N40" s="77"/>
-      <c r="O40" s="77"/>
-      <c r="P40" s="77"/>
-      <c r="Q40" s="77"/>
-      <c r="R40" s="77"/>
-      <c r="S40" s="77"/>
-      <c r="T40" s="77"/>
-      <c r="U40" s="77"/>
-      <c r="V40" s="77"/>
-      <c r="W40" s="77"/>
-      <c r="X40" s="77"/>
-      <c r="Y40" s="77"/>
-      <c r="Z40" s="77"/>
-      <c r="AA40" s="77"/>
-      <c r="AB40" s="77"/>
-      <c r="AC40" s="77"/>
-      <c r="AD40" s="77"/>
-      <c r="AE40" s="77"/>
-      <c r="AF40" s="77"/>
-      <c r="AG40" s="77"/>
-      <c r="AH40" s="77"/>
-      <c r="AI40" s="77"/>
-      <c r="AJ40" s="78"/>
-      <c r="AK40" s="79"/>
+      <c r="G40" s="190"/>
+      <c r="H40" s="190"/>
+      <c r="I40" s="190"/>
+      <c r="J40" s="190"/>
+      <c r="K40" s="190"/>
+      <c r="L40" s="190"/>
+      <c r="M40" s="190"/>
+      <c r="N40" s="190"/>
+      <c r="O40" s="190"/>
+      <c r="P40" s="190"/>
+      <c r="Q40" s="190"/>
+      <c r="R40" s="190"/>
+      <c r="S40" s="190"/>
+      <c r="T40" s="190"/>
+      <c r="U40" s="190"/>
+      <c r="V40" s="190"/>
+      <c r="W40" s="190"/>
+      <c r="X40" s="190"/>
+      <c r="Y40" s="190"/>
+      <c r="Z40" s="190"/>
+      <c r="AA40" s="190"/>
+      <c r="AB40" s="190"/>
+      <c r="AC40" s="190"/>
+      <c r="AD40" s="190"/>
+      <c r="AE40" s="190"/>
+      <c r="AF40" s="190"/>
+      <c r="AG40" s="190"/>
+      <c r="AH40" s="190"/>
+      <c r="AI40" s="190"/>
+      <c r="AJ40" s="191"/>
+      <c r="AK40" s="192"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
@@ -13890,79 +14042,79 @@
       <c r="E41" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="F41" s="80"/>
-      <c r="G41" s="119"/>
-      <c r="H41" s="119"/>
-      <c r="I41" s="119"/>
-      <c r="J41" s="119"/>
-      <c r="K41" s="81"/>
-      <c r="L41" s="80"/>
-      <c r="M41" s="119"/>
-      <c r="N41" s="119"/>
-      <c r="O41" s="119"/>
-      <c r="P41" s="119"/>
-      <c r="Q41" s="81"/>
-      <c r="R41" s="80"/>
-      <c r="S41" s="119"/>
-      <c r="T41" s="119"/>
-      <c r="U41" s="119"/>
-      <c r="V41" s="119"/>
-      <c r="W41" s="81"/>
-      <c r="X41" s="80"/>
-      <c r="Y41" s="119"/>
-      <c r="Z41" s="119"/>
-      <c r="AA41" s="119"/>
-      <c r="AB41" s="119"/>
-      <c r="AC41" s="81"/>
-      <c r="AD41" s="80"/>
-      <c r="AE41" s="119"/>
-      <c r="AF41" s="119"/>
-      <c r="AG41" s="119"/>
-      <c r="AH41" s="119"/>
-      <c r="AI41" s="104"/>
-      <c r="AJ41" s="55"/>
-      <c r="AK41" s="56"/>
+      <c r="F41" s="75"/>
+      <c r="G41" s="149"/>
+      <c r="H41" s="149"/>
+      <c r="I41" s="149"/>
+      <c r="J41" s="149"/>
+      <c r="K41" s="149"/>
+      <c r="L41" s="149"/>
+      <c r="M41" s="149"/>
+      <c r="N41" s="149"/>
+      <c r="O41" s="149"/>
+      <c r="P41" s="149"/>
+      <c r="Q41" s="149"/>
+      <c r="R41" s="149"/>
+      <c r="S41" s="149"/>
+      <c r="T41" s="149"/>
+      <c r="U41" s="149"/>
+      <c r="V41" s="149"/>
+      <c r="W41" s="149"/>
+      <c r="X41" s="149"/>
+      <c r="Y41" s="149"/>
+      <c r="Z41" s="149"/>
+      <c r="AA41" s="150"/>
+      <c r="AB41" s="150"/>
+      <c r="AC41" s="150"/>
+      <c r="AD41" s="150"/>
+      <c r="AE41" s="150"/>
+      <c r="AF41" s="150"/>
+      <c r="AG41" s="150"/>
+      <c r="AH41" s="150"/>
+      <c r="AI41" s="150"/>
+      <c r="AJ41" s="150"/>
+      <c r="AK41" s="151"/>
     </row>
     <row r="42" spans="1:254" ht="23" customHeight="1">
       <c r="A42" s="45"/>
       <c r="B42" s="46"/>
-      <c r="C42" s="93"/>
-      <c r="D42" s="95"/>
+      <c r="C42" s="88"/>
+      <c r="D42" s="90"/>
       <c r="E42" s="58" t="s">
         <v>97</v>
       </c>
-      <c r="F42" s="82"/>
-      <c r="G42" s="120"/>
-      <c r="H42" s="120"/>
-      <c r="I42" s="120"/>
-      <c r="J42" s="120"/>
-      <c r="K42" s="83"/>
-      <c r="L42" s="82"/>
-      <c r="M42" s="120"/>
-      <c r="N42" s="120"/>
-      <c r="O42" s="120"/>
-      <c r="P42" s="120"/>
-      <c r="Q42" s="83"/>
-      <c r="R42" s="82"/>
-      <c r="S42" s="120"/>
-      <c r="T42" s="120"/>
-      <c r="U42" s="120"/>
-      <c r="V42" s="120"/>
-      <c r="W42" s="83"/>
-      <c r="X42" s="82"/>
-      <c r="Y42" s="120"/>
-      <c r="Z42" s="120"/>
-      <c r="AA42" s="120"/>
-      <c r="AB42" s="120"/>
-      <c r="AC42" s="83"/>
-      <c r="AD42" s="82"/>
-      <c r="AE42" s="120"/>
-      <c r="AF42" s="120"/>
-      <c r="AG42" s="120"/>
-      <c r="AH42" s="120"/>
-      <c r="AI42" s="105"/>
-      <c r="AJ42" s="61"/>
-      <c r="AK42" s="84"/>
+      <c r="F42" s="77"/>
+      <c r="G42" s="152"/>
+      <c r="H42" s="152"/>
+      <c r="I42" s="152"/>
+      <c r="J42" s="152"/>
+      <c r="K42" s="152"/>
+      <c r="L42" s="152"/>
+      <c r="M42" s="152"/>
+      <c r="N42" s="152"/>
+      <c r="O42" s="152"/>
+      <c r="P42" s="152"/>
+      <c r="Q42" s="154"/>
+      <c r="R42" s="154"/>
+      <c r="S42" s="154"/>
+      <c r="T42" s="154"/>
+      <c r="U42" s="154"/>
+      <c r="V42" s="154"/>
+      <c r="W42" s="154"/>
+      <c r="X42" s="154"/>
+      <c r="Y42" s="154"/>
+      <c r="Z42" s="154"/>
+      <c r="AA42" s="152"/>
+      <c r="AB42" s="152"/>
+      <c r="AC42" s="152"/>
+      <c r="AD42" s="152"/>
+      <c r="AE42" s="152"/>
+      <c r="AF42" s="152"/>
+      <c r="AG42" s="152"/>
+      <c r="AH42" s="152"/>
+      <c r="AI42" s="152"/>
+      <c r="AJ42" s="152"/>
+      <c r="AK42" s="153"/>
     </row>
     <row r="43" spans="1:254" ht="23" customHeight="1" thickBot="1">
       <c r="A43" s="49"/>
@@ -13972,38 +14124,38 @@
       <c r="E43" s="60" t="s">
         <v>98</v>
       </c>
-      <c r="F43" s="87"/>
-      <c r="G43" s="118"/>
-      <c r="H43" s="118"/>
-      <c r="I43" s="118"/>
-      <c r="J43" s="118"/>
-      <c r="K43" s="88"/>
-      <c r="L43" s="87"/>
-      <c r="M43" s="118"/>
-      <c r="N43" s="118"/>
-      <c r="O43" s="118"/>
-      <c r="P43" s="118"/>
-      <c r="Q43" s="88"/>
-      <c r="R43" s="87"/>
-      <c r="S43" s="118"/>
-      <c r="T43" s="118"/>
-      <c r="U43" s="118"/>
-      <c r="V43" s="118"/>
-      <c r="W43" s="88"/>
-      <c r="X43" s="87"/>
-      <c r="Y43" s="118"/>
-      <c r="Z43" s="118"/>
-      <c r="AA43" s="118"/>
-      <c r="AB43" s="118"/>
-      <c r="AC43" s="88"/>
-      <c r="AD43" s="87"/>
-      <c r="AE43" s="118"/>
-      <c r="AF43" s="118"/>
-      <c r="AG43" s="118"/>
-      <c r="AH43" s="118"/>
-      <c r="AI43" s="108"/>
-      <c r="AJ43" s="63"/>
-      <c r="AK43" s="89"/>
+      <c r="F43" s="82"/>
+      <c r="G43" s="155"/>
+      <c r="H43" s="155"/>
+      <c r="I43" s="155"/>
+      <c r="J43" s="155"/>
+      <c r="K43" s="155"/>
+      <c r="L43" s="155"/>
+      <c r="M43" s="155"/>
+      <c r="N43" s="155"/>
+      <c r="O43" s="155"/>
+      <c r="P43" s="155"/>
+      <c r="Q43" s="157"/>
+      <c r="R43" s="157"/>
+      <c r="S43" s="157"/>
+      <c r="T43" s="157"/>
+      <c r="U43" s="157"/>
+      <c r="V43" s="157"/>
+      <c r="W43" s="157"/>
+      <c r="X43" s="157"/>
+      <c r="Y43" s="157"/>
+      <c r="Z43" s="157"/>
+      <c r="AA43" s="155"/>
+      <c r="AB43" s="155"/>
+      <c r="AC43" s="155"/>
+      <c r="AD43" s="155"/>
+      <c r="AE43" s="155"/>
+      <c r="AF43" s="155"/>
+      <c r="AG43" s="155"/>
+      <c r="AH43" s="155"/>
+      <c r="AI43" s="155"/>
+      <c r="AJ43" s="155"/>
+      <c r="AK43" s="156"/>
     </row>
     <row r="44" spans="1:254">
       <c r="A44" s="52"/>
@@ -14018,7 +14170,51 @@
       <c r="C45" s="52"/>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="60">
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="AA43:AK43"/>
+    <mergeCell ref="Q43:Z43"/>
+    <mergeCell ref="G43:P43"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="F12:F21"/>
+    <mergeCell ref="F27:F35"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="Q41:Z41"/>
+    <mergeCell ref="AA41:AK41"/>
+    <mergeCell ref="AA42:AK42"/>
+    <mergeCell ref="Q42:Z42"/>
+    <mergeCell ref="G42:P42"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="G41:P41"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="W5:Y7"/>
+    <mergeCell ref="AH5:AK7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="Z4:AC4"/>
+    <mergeCell ref="AD4:AG4"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="F22:F23"/>
     <mergeCell ref="A1:B1"/>
@@ -14035,66 +14231,21 @@
     <mergeCell ref="T4:Y4"/>
     <mergeCell ref="AH4:AK4"/>
     <mergeCell ref="T5:V7"/>
-    <mergeCell ref="W5:Y7"/>
-    <mergeCell ref="AH5:AK7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="Z4:AC4"/>
-    <mergeCell ref="AD4:AG4"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="G41:J41"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="M41:P41"/>
-    <mergeCell ref="S41:V41"/>
-    <mergeCell ref="Y41:AB41"/>
-    <mergeCell ref="AE41:AH41"/>
-    <mergeCell ref="G42:J42"/>
-    <mergeCell ref="M42:P42"/>
-    <mergeCell ref="S42:V42"/>
-    <mergeCell ref="Y42:AB42"/>
-    <mergeCell ref="AE42:AH42"/>
-    <mergeCell ref="G43:J43"/>
-    <mergeCell ref="M43:P43"/>
-    <mergeCell ref="S43:V43"/>
-    <mergeCell ref="Y43:AB43"/>
-    <mergeCell ref="AE43:AH43"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="F12:F21"/>
-    <mergeCell ref="F27:F35"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B24:C24"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="G9:AK10">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>TEXT(G9,"aaa")="土"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9:AK40">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>TEXT(G9,"aaa")="日"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11:AK40">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>G$11="－"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.23622047244094491" right="3.937007874015748E-2" top="0.55118110236220474" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -14118,40 +14269,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:254" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A1" s="153" t="s">
+      <c r="A1" s="108" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="153"/>
-      <c r="C1" s="90"/>
-      <c r="F1" s="154" t="s">
+      <c r="B1" s="108"/>
+      <c r="C1" s="85"/>
+      <c r="F1" s="109" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="154"/>
-      <c r="H1" s="154"/>
-      <c r="I1" s="154"/>
-      <c r="J1" s="154"/>
-      <c r="K1" s="154"/>
-      <c r="L1" s="154"/>
-      <c r="M1" s="154"/>
-      <c r="N1" s="154"/>
-      <c r="O1" s="154"/>
-      <c r="P1" s="154"/>
-      <c r="Q1" s="154"/>
-      <c r="R1" s="154"/>
-      <c r="S1" s="154"/>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="154"/>
-      <c r="W1" s="154"/>
-      <c r="X1" s="154"/>
-      <c r="Y1" s="154"/>
-      <c r="Z1" s="154"/>
-      <c r="AA1" s="154"/>
-      <c r="AB1" s="154"/>
-      <c r="AC1" s="154"/>
-      <c r="AD1" s="154"/>
-      <c r="AE1" s="154"/>
-      <c r="AF1" s="154"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
+      <c r="V1" s="109"/>
+      <c r="W1" s="109"/>
+      <c r="X1" s="109"/>
+      <c r="Y1" s="109"/>
+      <c r="Z1" s="109"/>
+      <c r="AA1" s="109"/>
+      <c r="AB1" s="109"/>
+      <c r="AC1" s="109"/>
+      <c r="AD1" s="109"/>
+      <c r="AE1" s="109"/>
+      <c r="AF1" s="109"/>
       <c r="AI1" s="3"/>
       <c r="AJ1" s="3"/>
       <c r="AK1" s="3"/>
@@ -14617,47 +14768,47 @@
       <c r="IO2" s="3"/>
     </row>
     <row r="3" spans="1:254" s="2" customFormat="1" ht="20" customHeight="1" thickBot="1">
-      <c r="A3" s="155" t="s">
+      <c r="A3" s="110" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="157"/>
-      <c r="E3" s="99"/>
+      <c r="B3" s="111"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="94"/>
       <c r="G3" s="51"/>
       <c r="H3" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="151" t="s">
+      <c r="K3" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="151"/>
-      <c r="M3" s="151" t="s">
+      <c r="L3" s="113"/>
+      <c r="M3" s="113" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="151"/>
-      <c r="O3" s="151"/>
-      <c r="P3" s="151" t="s">
+      <c r="N3" s="113"/>
+      <c r="O3" s="113"/>
+      <c r="P3" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="Q3" s="151"/>
-      <c r="R3" s="151"/>
+      <c r="Q3" s="113"/>
+      <c r="R3" s="113"/>
       <c r="S3" s="3"/>
-      <c r="T3" s="158" t="s">
+      <c r="T3" s="114" t="s">
         <v>3</v>
       </c>
-      <c r="U3" s="159"/>
-      <c r="V3" s="159"/>
-      <c r="W3" s="159"/>
-      <c r="X3" s="159"/>
-      <c r="Y3" s="159"/>
-      <c r="Z3" s="159"/>
-      <c r="AA3" s="159"/>
-      <c r="AB3" s="159"/>
-      <c r="AC3" s="159"/>
-      <c r="AD3" s="159"/>
-      <c r="AE3" s="159"/>
-      <c r="AF3" s="160"/>
+      <c r="U3" s="115"/>
+      <c r="V3" s="115"/>
+      <c r="W3" s="115"/>
+      <c r="X3" s="115"/>
+      <c r="Y3" s="115"/>
+      <c r="Z3" s="115"/>
+      <c r="AA3" s="115"/>
+      <c r="AB3" s="115"/>
+      <c r="AC3" s="115"/>
+      <c r="AD3" s="115"/>
+      <c r="AE3" s="115"/>
+      <c r="AF3" s="116"/>
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
       <c r="AK3" s="3"/>
@@ -14886,42 +15037,42 @@
       <c r="H4" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="151" t="s">
+      <c r="K4" s="113" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="151"/>
-      <c r="M4" s="152">
+      <c r="L4" s="113"/>
+      <c r="M4" s="119">
         <v>46113</v>
       </c>
-      <c r="N4" s="152"/>
-      <c r="O4" s="152"/>
-      <c r="P4" s="151" t="s">
+      <c r="N4" s="119"/>
+      <c r="O4" s="119"/>
+      <c r="P4" s="113" t="s">
         <v>50</v>
       </c>
-      <c r="Q4" s="151"/>
-      <c r="R4" s="151"/>
+      <c r="Q4" s="113"/>
+      <c r="R4" s="113"/>
       <c r="S4" s="3"/>
-      <c r="T4" s="128" t="s">
+      <c r="T4" s="120" t="s">
         <v>5</v>
       </c>
-      <c r="U4" s="129"/>
-      <c r="V4" s="129"/>
-      <c r="W4" s="130"/>
-      <c r="X4" s="128" t="s">
+      <c r="U4" s="121"/>
+      <c r="V4" s="121"/>
+      <c r="W4" s="122"/>
+      <c r="X4" s="120" t="s">
         <v>6</v>
       </c>
-      <c r="Y4" s="129"/>
-      <c r="Z4" s="130"/>
-      <c r="AA4" s="128" t="s">
+      <c r="Y4" s="121"/>
+      <c r="Z4" s="122"/>
+      <c r="AA4" s="120" t="s">
         <v>7</v>
       </c>
-      <c r="AB4" s="129"/>
-      <c r="AC4" s="130"/>
-      <c r="AD4" s="128" t="s">
+      <c r="AB4" s="121"/>
+      <c r="AC4" s="122"/>
+      <c r="AD4" s="120" t="s">
         <v>8</v>
       </c>
-      <c r="AE4" s="129"/>
-      <c r="AF4" s="130"/>
+      <c r="AE4" s="121"/>
+      <c r="AF4" s="122"/>
       <c r="AI4" s="3"/>
       <c r="AJ4" s="3"/>
       <c r="AK4" s="3"/>
@@ -15149,21 +15300,21 @@
         <v>23</v>
       </c>
       <c r="S5" s="3"/>
-      <c r="T5" s="164" t="s">
+      <c r="T5" s="170" t="s">
         <v>64</v>
       </c>
-      <c r="U5" s="165"/>
-      <c r="V5" s="165"/>
-      <c r="W5" s="166"/>
+      <c r="U5" s="171"/>
+      <c r="V5" s="171"/>
+      <c r="W5" s="172"/>
       <c r="X5" s="11"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="12"/>
       <c r="AA5" s="11"/>
       <c r="AB5" s="3"/>
       <c r="AC5" s="12"/>
-      <c r="AD5" s="141"/>
-      <c r="AE5" s="142"/>
-      <c r="AF5" s="143"/>
+      <c r="AD5" s="133"/>
+      <c r="AE5" s="134"/>
+      <c r="AF5" s="135"/>
       <c r="AI5" s="3"/>
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3"/>
@@ -15381,7 +15532,7 @@
       <c r="IO5" s="3"/>
     </row>
     <row r="6" spans="1:254" s="2" customFormat="1" ht="18.75" customHeight="1" thickTop="1">
-      <c r="A6" s="107" t="s">
+      <c r="A6" s="100" t="s">
         <v>121</v>
       </c>
       <c r="B6" s="14"/>
@@ -15395,19 +15546,19 @@
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
-      <c r="T6" s="164"/>
-      <c r="U6" s="165"/>
-      <c r="V6" s="165"/>
-      <c r="W6" s="166"/>
+      <c r="T6" s="170"/>
+      <c r="U6" s="171"/>
+      <c r="V6" s="171"/>
+      <c r="W6" s="172"/>
       <c r="X6" s="11"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="12"/>
       <c r="AA6" s="11"/>
       <c r="AB6" s="3"/>
       <c r="AC6" s="12"/>
-      <c r="AD6" s="141"/>
-      <c r="AE6" s="142"/>
-      <c r="AF6" s="143"/>
+      <c r="AD6" s="133"/>
+      <c r="AE6" s="134"/>
+      <c r="AF6" s="135"/>
       <c r="AI6" s="3"/>
       <c r="AJ6" s="3"/>
       <c r="AK6" s="3"/>
@@ -15639,20 +15790,20 @@
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
-      <c r="T7" s="167"/>
-      <c r="U7" s="168"/>
-      <c r="V7" s="168"/>
-      <c r="W7" s="169"/>
+      <c r="T7" s="173"/>
+      <c r="U7" s="174"/>
+      <c r="V7" s="174"/>
+      <c r="W7" s="175"/>
       <c r="X7" s="21"/>
       <c r="Y7" s="22"/>
       <c r="Z7" s="23"/>
       <c r="AA7" s="21"/>
       <c r="AB7" s="22"/>
       <c r="AC7" s="23"/>
-      <c r="AD7" s="144"/>
-      <c r="AE7" s="145"/>
-      <c r="AF7" s="146"/>
-      <c r="AG7" s="91"/>
+      <c r="AD7" s="136"/>
+      <c r="AE7" s="137"/>
+      <c r="AF7" s="138"/>
+      <c r="AG7" s="86"/>
       <c r="AI7" s="3"/>
       <c r="AJ7" s="3"/>
       <c r="AK7" s="3"/>
@@ -15899,10 +16050,10 @@
       <c r="AA8" s="24"/>
       <c r="AB8" s="24"/>
       <c r="AC8" s="24"/>
-      <c r="AD8" s="103"/>
-      <c r="AE8" s="103"/>
-      <c r="AF8" s="103"/>
-      <c r="AG8" s="92"/>
+      <c r="AD8" s="98"/>
+      <c r="AE8" s="98"/>
+      <c r="AF8" s="98"/>
+      <c r="AG8" s="87"/>
       <c r="AI8" s="3"/>
       <c r="AJ8" s="3"/>
       <c r="AK8" s="3"/>
@@ -16132,58 +16283,58 @@
         <v>48</v>
       </c>
       <c r="F9" s="28"/>
-      <c r="G9" s="102" t="s">
+      <c r="G9" s="97" t="s">
         <v>65</v>
       </c>
-      <c r="H9" s="102" t="s">
+      <c r="H9" s="97" t="s">
         <v>66</v>
       </c>
-      <c r="I9" s="102" t="s">
+      <c r="I9" s="97" t="s">
         <v>67</v>
       </c>
-      <c r="J9" s="102" t="s">
+      <c r="J9" s="97" t="s">
         <v>68</v>
       </c>
-      <c r="K9" s="102" t="s">
+      <c r="K9" s="97" t="s">
         <v>69</v>
       </c>
-      <c r="L9" s="102" t="s">
+      <c r="L9" s="97" t="s">
         <v>70</v>
       </c>
-      <c r="M9" s="102" t="s">
+      <c r="M9" s="97" t="s">
         <v>71</v>
       </c>
-      <c r="N9" s="102" t="s">
+      <c r="N9" s="97" t="s">
         <v>72</v>
       </c>
-      <c r="O9" s="102" t="s">
+      <c r="O9" s="97" t="s">
         <v>73</v>
       </c>
-      <c r="P9" s="102" t="s">
+      <c r="P9" s="97" t="s">
         <v>74</v>
       </c>
-      <c r="Q9" s="102" t="s">
+      <c r="Q9" s="97" t="s">
         <v>75</v>
       </c>
-      <c r="R9" s="102" t="s">
+      <c r="R9" s="97" t="s">
         <v>76</v>
       </c>
-      <c r="S9" s="177" t="s">
+      <c r="S9" s="163" t="s">
         <v>78</v>
       </c>
-      <c r="T9" s="178"/>
-      <c r="U9" s="178"/>
-      <c r="V9" s="178"/>
-      <c r="W9" s="178"/>
-      <c r="X9" s="178"/>
-      <c r="Y9" s="178"/>
-      <c r="Z9" s="178"/>
-      <c r="AA9" s="178"/>
-      <c r="AB9" s="178"/>
-      <c r="AC9" s="178"/>
-      <c r="AD9" s="178"/>
-      <c r="AE9" s="178"/>
-      <c r="AF9" s="179"/>
+      <c r="T9" s="164"/>
+      <c r="U9" s="164"/>
+      <c r="V9" s="164"/>
+      <c r="W9" s="164"/>
+      <c r="X9" s="164"/>
+      <c r="Y9" s="164"/>
+      <c r="Z9" s="164"/>
+      <c r="AA9" s="164"/>
+      <c r="AB9" s="164"/>
+      <c r="AC9" s="164"/>
+      <c r="AD9" s="164"/>
+      <c r="AE9" s="164"/>
+      <c r="AF9" s="165"/>
       <c r="AI9" s="3"/>
       <c r="AJ9" s="3"/>
       <c r="AK9" s="3"/>
@@ -16402,8 +16553,8 @@
     </row>
     <row r="10" spans="1:254" s="2" customFormat="1" ht="23" hidden="1" customHeight="1">
       <c r="A10" s="29"/>
-      <c r="B10" s="147"/>
-      <c r="C10" s="148"/>
+      <c r="B10" s="139"/>
+      <c r="C10" s="140"/>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="31"/>
@@ -16729,44 +16880,44 @@
     </row>
     <row r="11" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A11" s="37"/>
-      <c r="B11" s="125" t="s">
+      <c r="B11" s="143" t="s">
         <v>105</v>
       </c>
-      <c r="C11" s="126"/>
-      <c r="D11" s="97"/>
+      <c r="C11" s="144"/>
+      <c r="D11" s="92"/>
       <c r="E11" s="40"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="70"/>
-      <c r="K11" s="70"/>
-      <c r="L11" s="70"/>
-      <c r="M11" s="70"/>
-      <c r="N11" s="70"/>
-      <c r="O11" s="70"/>
-      <c r="P11" s="70"/>
-      <c r="Q11" s="70"/>
-      <c r="R11" s="70"/>
-      <c r="S11" s="172"/>
-      <c r="T11" s="173"/>
-      <c r="U11" s="173"/>
-      <c r="V11" s="173"/>
-      <c r="W11" s="173"/>
-      <c r="X11" s="173"/>
-      <c r="Y11" s="173"/>
-      <c r="Z11" s="173"/>
-      <c r="AA11" s="173"/>
-      <c r="AB11" s="173"/>
-      <c r="AC11" s="173"/>
-      <c r="AD11" s="173"/>
-      <c r="AE11" s="173"/>
-      <c r="AF11" s="174"/>
-      <c r="AG11" s="70"/>
-      <c r="AH11" s="70"/>
-      <c r="AI11" s="70"/>
-      <c r="AJ11" s="75"/>
-      <c r="AK11" s="76"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="69"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="69"/>
+      <c r="J11" s="69"/>
+      <c r="K11" s="69"/>
+      <c r="L11" s="69"/>
+      <c r="M11" s="69"/>
+      <c r="N11" s="69"/>
+      <c r="O11" s="69"/>
+      <c r="P11" s="69"/>
+      <c r="Q11" s="69"/>
+      <c r="R11" s="69"/>
+      <c r="S11" s="178"/>
+      <c r="T11" s="179"/>
+      <c r="U11" s="179"/>
+      <c r="V11" s="179"/>
+      <c r="W11" s="179"/>
+      <c r="X11" s="179"/>
+      <c r="Y11" s="179"/>
+      <c r="Z11" s="179"/>
+      <c r="AA11" s="179"/>
+      <c r="AB11" s="179"/>
+      <c r="AC11" s="179"/>
+      <c r="AD11" s="179"/>
+      <c r="AE11" s="179"/>
+      <c r="AF11" s="180"/>
+      <c r="AG11" s="69"/>
+      <c r="AH11" s="69"/>
+      <c r="AI11" s="69"/>
+      <c r="AJ11" s="70"/>
+      <c r="AK11" s="71"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
@@ -16987,46 +17138,46 @@
       <c r="A12" s="37">
         <v>1</v>
       </c>
-      <c r="B12" s="123" t="s">
+      <c r="B12" s="147" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="124"/>
-      <c r="D12" s="97" t="s">
+      <c r="C12" s="148"/>
+      <c r="D12" s="92" t="s">
         <v>108</v>
       </c>
       <c r="E12" s="40"/>
       <c r="F12" s="36"/>
-      <c r="G12" s="70"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="70"/>
-      <c r="J12" s="70"/>
-      <c r="K12" s="70"/>
-      <c r="L12" s="70"/>
-      <c r="M12" s="70"/>
-      <c r="N12" s="70"/>
-      <c r="O12" s="70"/>
-      <c r="P12" s="70"/>
-      <c r="Q12" s="70"/>
-      <c r="R12" s="70"/>
-      <c r="S12" s="161"/>
-      <c r="T12" s="162"/>
-      <c r="U12" s="162"/>
-      <c r="V12" s="162"/>
-      <c r="W12" s="162"/>
-      <c r="X12" s="162"/>
-      <c r="Y12" s="162"/>
-      <c r="Z12" s="162"/>
-      <c r="AA12" s="162"/>
-      <c r="AB12" s="162"/>
-      <c r="AC12" s="162"/>
-      <c r="AD12" s="162"/>
-      <c r="AE12" s="162"/>
-      <c r="AF12" s="163"/>
-      <c r="AG12" s="70"/>
-      <c r="AH12" s="70"/>
-      <c r="AI12" s="70"/>
-      <c r="AJ12" s="75"/>
-      <c r="AK12" s="76"/>
+      <c r="G12" s="69"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="69"/>
+      <c r="J12" s="69"/>
+      <c r="K12" s="69"/>
+      <c r="L12" s="69"/>
+      <c r="M12" s="69"/>
+      <c r="N12" s="69"/>
+      <c r="O12" s="69"/>
+      <c r="P12" s="69"/>
+      <c r="Q12" s="69"/>
+      <c r="R12" s="69"/>
+      <c r="S12" s="159"/>
+      <c r="T12" s="160"/>
+      <c r="U12" s="160"/>
+      <c r="V12" s="160"/>
+      <c r="W12" s="160"/>
+      <c r="X12" s="160"/>
+      <c r="Y12" s="160"/>
+      <c r="Z12" s="160"/>
+      <c r="AA12" s="160"/>
+      <c r="AB12" s="160"/>
+      <c r="AC12" s="160"/>
+      <c r="AD12" s="160"/>
+      <c r="AE12" s="160"/>
+      <c r="AF12" s="161"/>
+      <c r="AG12" s="69"/>
+      <c r="AH12" s="69"/>
+      <c r="AI12" s="69"/>
+      <c r="AJ12" s="70"/>
+      <c r="AK12" s="71"/>
       <c r="AN12" s="3"/>
       <c r="AO12" s="3"/>
       <c r="AP12" s="3"/>
@@ -17247,46 +17398,46 @@
       <c r="A13" s="37">
         <v>2</v>
       </c>
-      <c r="B13" s="123" t="s">
+      <c r="B13" s="147" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="124"/>
-      <c r="D13" s="97" t="s">
+      <c r="C13" s="148"/>
+      <c r="D13" s="92" t="s">
         <v>107</v>
       </c>
       <c r="E13" s="40"/>
       <c r="F13" s="36"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
-      <c r="I13" s="70"/>
-      <c r="J13" s="70"/>
-      <c r="K13" s="70"/>
-      <c r="L13" s="70"/>
-      <c r="M13" s="70"/>
-      <c r="N13" s="70"/>
-      <c r="O13" s="70"/>
-      <c r="P13" s="70"/>
-      <c r="Q13" s="70"/>
-      <c r="R13" s="70"/>
-      <c r="S13" s="161"/>
-      <c r="T13" s="162"/>
-      <c r="U13" s="162"/>
-      <c r="V13" s="162"/>
-      <c r="W13" s="162"/>
-      <c r="X13" s="162"/>
-      <c r="Y13" s="162"/>
-      <c r="Z13" s="162"/>
-      <c r="AA13" s="162"/>
-      <c r="AB13" s="162"/>
-      <c r="AC13" s="162"/>
-      <c r="AD13" s="162"/>
-      <c r="AE13" s="162"/>
-      <c r="AF13" s="163"/>
-      <c r="AG13" s="70"/>
-      <c r="AH13" s="70"/>
-      <c r="AI13" s="70"/>
-      <c r="AJ13" s="75"/>
-      <c r="AK13" s="76"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="69"/>
+      <c r="I13" s="69"/>
+      <c r="J13" s="69"/>
+      <c r="K13" s="69"/>
+      <c r="L13" s="69"/>
+      <c r="M13" s="69"/>
+      <c r="N13" s="69"/>
+      <c r="O13" s="69"/>
+      <c r="P13" s="69"/>
+      <c r="Q13" s="69"/>
+      <c r="R13" s="69"/>
+      <c r="S13" s="159"/>
+      <c r="T13" s="160"/>
+      <c r="U13" s="160"/>
+      <c r="V13" s="160"/>
+      <c r="W13" s="160"/>
+      <c r="X13" s="160"/>
+      <c r="Y13" s="160"/>
+      <c r="Z13" s="160"/>
+      <c r="AA13" s="160"/>
+      <c r="AB13" s="160"/>
+      <c r="AC13" s="160"/>
+      <c r="AD13" s="160"/>
+      <c r="AE13" s="160"/>
+      <c r="AF13" s="161"/>
+      <c r="AG13" s="69"/>
+      <c r="AH13" s="69"/>
+      <c r="AI13" s="69"/>
+      <c r="AJ13" s="70"/>
+      <c r="AK13" s="71"/>
       <c r="AN13" s="3"/>
       <c r="AO13" s="3"/>
       <c r="AP13" s="3"/>
@@ -17507,46 +17658,46 @@
       <c r="A14" s="37">
         <v>3</v>
       </c>
-      <c r="B14" s="123" t="s">
+      <c r="B14" s="147" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="124"/>
-      <c r="D14" s="97" t="s">
+      <c r="C14" s="148"/>
+      <c r="D14" s="92" t="s">
         <v>107</v>
       </c>
       <c r="E14" s="40"/>
       <c r="F14" s="36"/>
-      <c r="G14" s="70"/>
-      <c r="H14" s="70"/>
-      <c r="I14" s="70"/>
-      <c r="J14" s="70"/>
-      <c r="K14" s="70"/>
-      <c r="L14" s="70"/>
-      <c r="M14" s="70"/>
-      <c r="N14" s="70"/>
-      <c r="O14" s="70"/>
-      <c r="P14" s="70"/>
-      <c r="Q14" s="70"/>
-      <c r="R14" s="70"/>
-      <c r="S14" s="161"/>
-      <c r="T14" s="162"/>
-      <c r="U14" s="162"/>
-      <c r="V14" s="162"/>
-      <c r="W14" s="162"/>
-      <c r="X14" s="162"/>
-      <c r="Y14" s="162"/>
-      <c r="Z14" s="162"/>
-      <c r="AA14" s="162"/>
-      <c r="AB14" s="162"/>
-      <c r="AC14" s="162"/>
-      <c r="AD14" s="162"/>
-      <c r="AE14" s="162"/>
-      <c r="AF14" s="163"/>
-      <c r="AG14" s="70"/>
-      <c r="AH14" s="70"/>
-      <c r="AI14" s="70"/>
-      <c r="AJ14" s="75"/>
-      <c r="AK14" s="76"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="69"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="69"/>
+      <c r="L14" s="69"/>
+      <c r="M14" s="69"/>
+      <c r="N14" s="69"/>
+      <c r="O14" s="69"/>
+      <c r="P14" s="69"/>
+      <c r="Q14" s="69"/>
+      <c r="R14" s="69"/>
+      <c r="S14" s="159"/>
+      <c r="T14" s="160"/>
+      <c r="U14" s="160"/>
+      <c r="V14" s="160"/>
+      <c r="W14" s="160"/>
+      <c r="X14" s="160"/>
+      <c r="Y14" s="160"/>
+      <c r="Z14" s="160"/>
+      <c r="AA14" s="160"/>
+      <c r="AB14" s="160"/>
+      <c r="AC14" s="160"/>
+      <c r="AD14" s="160"/>
+      <c r="AE14" s="160"/>
+      <c r="AF14" s="161"/>
+      <c r="AG14" s="69"/>
+      <c r="AH14" s="69"/>
+      <c r="AI14" s="69"/>
+      <c r="AJ14" s="70"/>
+      <c r="AK14" s="71"/>
       <c r="AN14" s="3"/>
       <c r="AO14" s="3"/>
       <c r="AP14" s="3"/>
@@ -17767,46 +17918,46 @@
       <c r="A15" s="37">
         <v>4</v>
       </c>
-      <c r="B15" s="123" t="s">
+      <c r="B15" s="147" t="s">
         <v>82</v>
       </c>
-      <c r="C15" s="124"/>
-      <c r="D15" s="97" t="s">
+      <c r="C15" s="148"/>
+      <c r="D15" s="92" t="s">
         <v>108</v>
       </c>
       <c r="E15" s="40"/>
       <c r="F15" s="36"/>
-      <c r="G15" s="70"/>
-      <c r="H15" s="70"/>
-      <c r="I15" s="70"/>
-      <c r="J15" s="70"/>
-      <c r="K15" s="70"/>
-      <c r="L15" s="70"/>
-      <c r="M15" s="70"/>
-      <c r="N15" s="70"/>
-      <c r="O15" s="70"/>
-      <c r="P15" s="70"/>
-      <c r="Q15" s="70"/>
-      <c r="R15" s="70"/>
-      <c r="S15" s="161"/>
-      <c r="T15" s="162"/>
-      <c r="U15" s="162"/>
-      <c r="V15" s="162"/>
-      <c r="W15" s="162"/>
-      <c r="X15" s="162"/>
-      <c r="Y15" s="162"/>
-      <c r="Z15" s="162"/>
-      <c r="AA15" s="162"/>
-      <c r="AB15" s="162"/>
-      <c r="AC15" s="162"/>
-      <c r="AD15" s="162"/>
-      <c r="AE15" s="162"/>
-      <c r="AF15" s="163"/>
-      <c r="AG15" s="70"/>
-      <c r="AH15" s="70"/>
-      <c r="AI15" s="70"/>
-      <c r="AJ15" s="75"/>
-      <c r="AK15" s="76"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="69"/>
+      <c r="J15" s="69"/>
+      <c r="K15" s="69"/>
+      <c r="L15" s="69"/>
+      <c r="M15" s="69"/>
+      <c r="N15" s="69"/>
+      <c r="O15" s="69"/>
+      <c r="P15" s="69"/>
+      <c r="Q15" s="69"/>
+      <c r="R15" s="69"/>
+      <c r="S15" s="159"/>
+      <c r="T15" s="160"/>
+      <c r="U15" s="160"/>
+      <c r="V15" s="160"/>
+      <c r="W15" s="160"/>
+      <c r="X15" s="160"/>
+      <c r="Y15" s="160"/>
+      <c r="Z15" s="160"/>
+      <c r="AA15" s="160"/>
+      <c r="AB15" s="160"/>
+      <c r="AC15" s="160"/>
+      <c r="AD15" s="160"/>
+      <c r="AE15" s="160"/>
+      <c r="AF15" s="161"/>
+      <c r="AG15" s="69"/>
+      <c r="AH15" s="69"/>
+      <c r="AI15" s="69"/>
+      <c r="AJ15" s="70"/>
+      <c r="AK15" s="71"/>
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
       <c r="AP15" s="3"/>
@@ -18027,46 +18178,46 @@
       <c r="A16" s="37">
         <v>5</v>
       </c>
-      <c r="B16" s="123" t="s">
+      <c r="B16" s="147" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="124"/>
-      <c r="D16" s="97" t="s">
+      <c r="C16" s="148"/>
+      <c r="D16" s="92" t="s">
         <v>108</v>
       </c>
       <c r="E16" s="40"/>
       <c r="F16" s="36"/>
-      <c r="G16" s="70"/>
-      <c r="H16" s="70"/>
-      <c r="I16" s="70"/>
-      <c r="J16" s="70"/>
-      <c r="K16" s="70"/>
-      <c r="L16" s="70"/>
-      <c r="M16" s="70"/>
-      <c r="N16" s="70"/>
-      <c r="O16" s="70"/>
-      <c r="P16" s="70"/>
-      <c r="Q16" s="70"/>
-      <c r="R16" s="70"/>
-      <c r="S16" s="161"/>
-      <c r="T16" s="162"/>
-      <c r="U16" s="162"/>
-      <c r="V16" s="162"/>
-      <c r="W16" s="162"/>
-      <c r="X16" s="162"/>
-      <c r="Y16" s="162"/>
-      <c r="Z16" s="162"/>
-      <c r="AA16" s="162"/>
-      <c r="AB16" s="162"/>
-      <c r="AC16" s="162"/>
-      <c r="AD16" s="162"/>
-      <c r="AE16" s="162"/>
-      <c r="AF16" s="163"/>
-      <c r="AG16" s="70"/>
-      <c r="AH16" s="70"/>
-      <c r="AI16" s="70"/>
-      <c r="AJ16" s="75"/>
-      <c r="AK16" s="76"/>
+      <c r="G16" s="69"/>
+      <c r="H16" s="69"/>
+      <c r="I16" s="69"/>
+      <c r="J16" s="69"/>
+      <c r="K16" s="69"/>
+      <c r="L16" s="69"/>
+      <c r="M16" s="69"/>
+      <c r="N16" s="69"/>
+      <c r="O16" s="69"/>
+      <c r="P16" s="69"/>
+      <c r="Q16" s="69"/>
+      <c r="R16" s="69"/>
+      <c r="S16" s="159"/>
+      <c r="T16" s="160"/>
+      <c r="U16" s="160"/>
+      <c r="V16" s="160"/>
+      <c r="W16" s="160"/>
+      <c r="X16" s="160"/>
+      <c r="Y16" s="160"/>
+      <c r="Z16" s="160"/>
+      <c r="AA16" s="160"/>
+      <c r="AB16" s="160"/>
+      <c r="AC16" s="160"/>
+      <c r="AD16" s="160"/>
+      <c r="AE16" s="160"/>
+      <c r="AF16" s="161"/>
+      <c r="AG16" s="69"/>
+      <c r="AH16" s="69"/>
+      <c r="AI16" s="69"/>
+      <c r="AJ16" s="70"/>
+      <c r="AK16" s="71"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
@@ -18287,46 +18438,46 @@
       <c r="A17" s="37">
         <v>6</v>
       </c>
-      <c r="B17" s="123" t="s">
+      <c r="B17" s="147" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="124"/>
-      <c r="D17" s="97" t="s">
+      <c r="C17" s="148"/>
+      <c r="D17" s="92" t="s">
         <v>108</v>
       </c>
       <c r="E17" s="40"/>
       <c r="F17" s="36"/>
-      <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
-      <c r="I17" s="70"/>
-      <c r="J17" s="70"/>
-      <c r="K17" s="70"/>
-      <c r="L17" s="70"/>
-      <c r="M17" s="70"/>
-      <c r="N17" s="70"/>
-      <c r="O17" s="70"/>
-      <c r="P17" s="70"/>
-      <c r="Q17" s="70"/>
-      <c r="R17" s="70"/>
-      <c r="S17" s="161"/>
-      <c r="T17" s="162"/>
-      <c r="U17" s="162"/>
-      <c r="V17" s="162"/>
-      <c r="W17" s="162"/>
-      <c r="X17" s="162"/>
-      <c r="Y17" s="162"/>
-      <c r="Z17" s="162"/>
-      <c r="AA17" s="162"/>
-      <c r="AB17" s="162"/>
-      <c r="AC17" s="162"/>
-      <c r="AD17" s="162"/>
-      <c r="AE17" s="162"/>
-      <c r="AF17" s="163"/>
-      <c r="AG17" s="70"/>
-      <c r="AH17" s="70"/>
-      <c r="AI17" s="70"/>
-      <c r="AJ17" s="75"/>
-      <c r="AK17" s="76"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="69"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="69"/>
+      <c r="K17" s="69"/>
+      <c r="L17" s="69"/>
+      <c r="M17" s="69"/>
+      <c r="N17" s="69"/>
+      <c r="O17" s="69"/>
+      <c r="P17" s="69"/>
+      <c r="Q17" s="69"/>
+      <c r="R17" s="69"/>
+      <c r="S17" s="159"/>
+      <c r="T17" s="160"/>
+      <c r="U17" s="160"/>
+      <c r="V17" s="160"/>
+      <c r="W17" s="160"/>
+      <c r="X17" s="160"/>
+      <c r="Y17" s="160"/>
+      <c r="Z17" s="160"/>
+      <c r="AA17" s="160"/>
+      <c r="AB17" s="160"/>
+      <c r="AC17" s="160"/>
+      <c r="AD17" s="160"/>
+      <c r="AE17" s="160"/>
+      <c r="AF17" s="161"/>
+      <c r="AG17" s="69"/>
+      <c r="AH17" s="69"/>
+      <c r="AI17" s="69"/>
+      <c r="AJ17" s="70"/>
+      <c r="AK17" s="71"/>
       <c r="AN17" s="3"/>
       <c r="AO17" s="3"/>
       <c r="AP17" s="3"/>
@@ -18547,46 +18698,46 @@
       <c r="A18" s="37">
         <v>7</v>
       </c>
-      <c r="B18" s="123" t="s">
+      <c r="B18" s="147" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="124"/>
-      <c r="D18" s="97" t="s">
+      <c r="C18" s="148"/>
+      <c r="D18" s="92" t="s">
         <v>108</v>
       </c>
       <c r="E18" s="40"/>
       <c r="F18" s="36"/>
-      <c r="G18" s="70"/>
-      <c r="H18" s="70"/>
-      <c r="I18" s="70"/>
-      <c r="J18" s="70"/>
-      <c r="K18" s="70"/>
-      <c r="L18" s="70"/>
-      <c r="M18" s="70"/>
-      <c r="N18" s="70"/>
-      <c r="O18" s="70"/>
-      <c r="P18" s="70"/>
-      <c r="Q18" s="70"/>
-      <c r="R18" s="70"/>
-      <c r="S18" s="161"/>
-      <c r="T18" s="162"/>
-      <c r="U18" s="162"/>
-      <c r="V18" s="162"/>
-      <c r="W18" s="162"/>
-      <c r="X18" s="162"/>
-      <c r="Y18" s="162"/>
-      <c r="Z18" s="162"/>
-      <c r="AA18" s="162"/>
-      <c r="AB18" s="162"/>
-      <c r="AC18" s="162"/>
-      <c r="AD18" s="162"/>
-      <c r="AE18" s="162"/>
-      <c r="AF18" s="163"/>
-      <c r="AG18" s="70"/>
-      <c r="AH18" s="70"/>
-      <c r="AI18" s="70"/>
-      <c r="AJ18" s="75"/>
-      <c r="AK18" s="76"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="69"/>
+      <c r="K18" s="69"/>
+      <c r="L18" s="69"/>
+      <c r="M18" s="69"/>
+      <c r="N18" s="69"/>
+      <c r="O18" s="69"/>
+      <c r="P18" s="69"/>
+      <c r="Q18" s="69"/>
+      <c r="R18" s="69"/>
+      <c r="S18" s="159"/>
+      <c r="T18" s="160"/>
+      <c r="U18" s="160"/>
+      <c r="V18" s="160"/>
+      <c r="W18" s="160"/>
+      <c r="X18" s="160"/>
+      <c r="Y18" s="160"/>
+      <c r="Z18" s="160"/>
+      <c r="AA18" s="160"/>
+      <c r="AB18" s="160"/>
+      <c r="AC18" s="160"/>
+      <c r="AD18" s="160"/>
+      <c r="AE18" s="160"/>
+      <c r="AF18" s="161"/>
+      <c r="AG18" s="69"/>
+      <c r="AH18" s="69"/>
+      <c r="AI18" s="69"/>
+      <c r="AJ18" s="70"/>
+      <c r="AK18" s="71"/>
       <c r="AN18" s="3"/>
       <c r="AO18" s="3"/>
       <c r="AP18" s="3"/>
@@ -18807,46 +18958,46 @@
       <c r="A19" s="37">
         <v>8</v>
       </c>
-      <c r="B19" s="123" t="s">
+      <c r="B19" s="147" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="124"/>
-      <c r="D19" s="97" t="s">
+      <c r="C19" s="148"/>
+      <c r="D19" s="92" t="s">
         <v>108</v>
       </c>
       <c r="E19" s="40"/>
       <c r="F19" s="36"/>
-      <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
-      <c r="I19" s="70"/>
-      <c r="J19" s="70"/>
-      <c r="K19" s="70"/>
-      <c r="L19" s="70"/>
-      <c r="M19" s="70"/>
-      <c r="N19" s="70"/>
-      <c r="O19" s="70"/>
-      <c r="P19" s="70"/>
-      <c r="Q19" s="70"/>
-      <c r="R19" s="70"/>
-      <c r="S19" s="161"/>
-      <c r="T19" s="162"/>
-      <c r="U19" s="162"/>
-      <c r="V19" s="162"/>
-      <c r="W19" s="162"/>
-      <c r="X19" s="162"/>
-      <c r="Y19" s="162"/>
-      <c r="Z19" s="162"/>
-      <c r="AA19" s="162"/>
-      <c r="AB19" s="162"/>
-      <c r="AC19" s="162"/>
-      <c r="AD19" s="162"/>
-      <c r="AE19" s="162"/>
-      <c r="AF19" s="163"/>
-      <c r="AG19" s="70"/>
-      <c r="AH19" s="70"/>
-      <c r="AI19" s="70"/>
-      <c r="AJ19" s="75"/>
-      <c r="AK19" s="76"/>
+      <c r="G19" s="69"/>
+      <c r="H19" s="69"/>
+      <c r="I19" s="69"/>
+      <c r="J19" s="69"/>
+      <c r="K19" s="69"/>
+      <c r="L19" s="69"/>
+      <c r="M19" s="69"/>
+      <c r="N19" s="69"/>
+      <c r="O19" s="69"/>
+      <c r="P19" s="69"/>
+      <c r="Q19" s="69"/>
+      <c r="R19" s="69"/>
+      <c r="S19" s="159"/>
+      <c r="T19" s="160"/>
+      <c r="U19" s="160"/>
+      <c r="V19" s="160"/>
+      <c r="W19" s="160"/>
+      <c r="X19" s="160"/>
+      <c r="Y19" s="160"/>
+      <c r="Z19" s="160"/>
+      <c r="AA19" s="160"/>
+      <c r="AB19" s="160"/>
+      <c r="AC19" s="160"/>
+      <c r="AD19" s="160"/>
+      <c r="AE19" s="160"/>
+      <c r="AF19" s="161"/>
+      <c r="AG19" s="69"/>
+      <c r="AH19" s="69"/>
+      <c r="AI19" s="69"/>
+      <c r="AJ19" s="70"/>
+      <c r="AK19" s="71"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
@@ -19065,10 +19216,10 @@
     </row>
     <row r="20" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A20" s="34"/>
-      <c r="B20" s="170" t="s">
+      <c r="B20" s="176" t="s">
         <v>120</v>
       </c>
-      <c r="C20" s="171"/>
+      <c r="C20" s="177"/>
       <c r="D20" s="35"/>
       <c r="E20" s="35"/>
       <c r="F20" s="36"/>
@@ -19084,20 +19235,20 @@
       <c r="P20" s="68"/>
       <c r="Q20" s="68"/>
       <c r="R20" s="68"/>
-      <c r="S20" s="161"/>
-      <c r="T20" s="162"/>
-      <c r="U20" s="162"/>
-      <c r="V20" s="162"/>
-      <c r="W20" s="162"/>
-      <c r="X20" s="162"/>
-      <c r="Y20" s="162"/>
-      <c r="Z20" s="162"/>
-      <c r="AA20" s="162"/>
-      <c r="AB20" s="162"/>
-      <c r="AC20" s="162"/>
-      <c r="AD20" s="162"/>
-      <c r="AE20" s="162"/>
-      <c r="AF20" s="163"/>
+      <c r="S20" s="159"/>
+      <c r="T20" s="160"/>
+      <c r="U20" s="160"/>
+      <c r="V20" s="160"/>
+      <c r="W20" s="160"/>
+      <c r="X20" s="160"/>
+      <c r="Y20" s="160"/>
+      <c r="Z20" s="160"/>
+      <c r="AA20" s="160"/>
+      <c r="AB20" s="160"/>
+      <c r="AC20" s="160"/>
+      <c r="AD20" s="160"/>
+      <c r="AE20" s="160"/>
+      <c r="AF20" s="161"/>
       <c r="AI20" s="3"/>
       <c r="AJ20" s="3"/>
       <c r="AK20" s="3"/>
@@ -19318,41 +19469,41 @@
       <c r="A21" s="37">
         <v>1</v>
       </c>
-      <c r="B21" s="112" t="s">
+      <c r="B21" s="104" t="s">
         <v>87</v>
       </c>
-      <c r="C21" s="113"/>
-      <c r="D21" s="97"/>
-      <c r="E21" s="97" t="s">
+      <c r="C21" s="105"/>
+      <c r="D21" s="92"/>
+      <c r="E21" s="92" t="s">
         <v>42</v>
       </c>
       <c r="F21" s="36"/>
-      <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
-      <c r="I21" s="70"/>
-      <c r="J21" s="70"/>
-      <c r="K21" s="70"/>
-      <c r="L21" s="70"/>
-      <c r="M21" s="70"/>
-      <c r="N21" s="70"/>
-      <c r="O21" s="70"/>
-      <c r="P21" s="70"/>
-      <c r="Q21" s="70"/>
-      <c r="R21" s="70"/>
-      <c r="S21" s="161"/>
-      <c r="T21" s="162"/>
-      <c r="U21" s="162"/>
-      <c r="V21" s="162"/>
-      <c r="W21" s="162"/>
-      <c r="X21" s="162"/>
-      <c r="Y21" s="162"/>
-      <c r="Z21" s="162"/>
-      <c r="AA21" s="162"/>
-      <c r="AB21" s="162"/>
-      <c r="AC21" s="162"/>
-      <c r="AD21" s="162"/>
-      <c r="AE21" s="162"/>
-      <c r="AF21" s="163"/>
+      <c r="G21" s="69"/>
+      <c r="H21" s="69"/>
+      <c r="I21" s="69"/>
+      <c r="J21" s="69"/>
+      <c r="K21" s="69"/>
+      <c r="L21" s="69"/>
+      <c r="M21" s="69"/>
+      <c r="N21" s="69"/>
+      <c r="O21" s="69"/>
+      <c r="P21" s="69"/>
+      <c r="Q21" s="69"/>
+      <c r="R21" s="69"/>
+      <c r="S21" s="159"/>
+      <c r="T21" s="160"/>
+      <c r="U21" s="160"/>
+      <c r="V21" s="160"/>
+      <c r="W21" s="160"/>
+      <c r="X21" s="160"/>
+      <c r="Y21" s="160"/>
+      <c r="Z21" s="160"/>
+      <c r="AA21" s="160"/>
+      <c r="AB21" s="160"/>
+      <c r="AC21" s="160"/>
+      <c r="AD21" s="160"/>
+      <c r="AE21" s="160"/>
+      <c r="AF21" s="161"/>
       <c r="AI21" s="3"/>
       <c r="AJ21" s="3"/>
       <c r="AK21" s="3"/>
@@ -19573,41 +19724,41 @@
       <c r="A22" s="37">
         <v>2</v>
       </c>
-      <c r="B22" s="112" t="s">
+      <c r="B22" s="104" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="113"/>
-      <c r="D22" s="97"/>
-      <c r="E22" s="97" t="s">
+      <c r="C22" s="105"/>
+      <c r="D22" s="92"/>
+      <c r="E22" s="92" t="s">
         <v>43</v>
       </c>
       <c r="F22" s="36"/>
-      <c r="G22" s="70"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
-      <c r="J22" s="70"/>
-      <c r="K22" s="70"/>
-      <c r="L22" s="70"/>
-      <c r="M22" s="70"/>
-      <c r="N22" s="70"/>
-      <c r="O22" s="70"/>
-      <c r="P22" s="70"/>
-      <c r="Q22" s="70"/>
-      <c r="R22" s="70"/>
-      <c r="S22" s="161"/>
-      <c r="T22" s="162"/>
-      <c r="U22" s="162"/>
-      <c r="V22" s="162"/>
-      <c r="W22" s="162"/>
-      <c r="X22" s="162"/>
-      <c r="Y22" s="162"/>
-      <c r="Z22" s="162"/>
-      <c r="AA22" s="162"/>
-      <c r="AB22" s="162"/>
-      <c r="AC22" s="162"/>
-      <c r="AD22" s="162"/>
-      <c r="AE22" s="162"/>
-      <c r="AF22" s="163"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="69"/>
+      <c r="J22" s="69"/>
+      <c r="K22" s="69"/>
+      <c r="L22" s="69"/>
+      <c r="M22" s="69"/>
+      <c r="N22" s="69"/>
+      <c r="O22" s="69"/>
+      <c r="P22" s="69"/>
+      <c r="Q22" s="69"/>
+      <c r="R22" s="69"/>
+      <c r="S22" s="159"/>
+      <c r="T22" s="160"/>
+      <c r="U22" s="160"/>
+      <c r="V22" s="160"/>
+      <c r="W22" s="160"/>
+      <c r="X22" s="160"/>
+      <c r="Y22" s="160"/>
+      <c r="Z22" s="160"/>
+      <c r="AA22" s="160"/>
+      <c r="AB22" s="160"/>
+      <c r="AC22" s="160"/>
+      <c r="AD22" s="160"/>
+      <c r="AE22" s="160"/>
+      <c r="AF22" s="161"/>
       <c r="AI22" s="3"/>
       <c r="AJ22" s="3"/>
       <c r="AK22" s="3"/>
@@ -19825,46 +19976,46 @@
       <c r="IO22" s="3"/>
     </row>
     <row r="23" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A23" s="109" t="s">
+      <c r="A23" s="101" t="s">
         <v>111</v>
       </c>
-      <c r="B23" s="175" t="s">
+      <c r="B23" s="168" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="176"/>
-      <c r="D23" s="97" t="s">
+      <c r="C23" s="169"/>
+      <c r="D23" s="92" t="s">
         <v>110</v>
       </c>
-      <c r="E23" s="97" t="s">
+      <c r="E23" s="92" t="s">
         <v>44</v>
       </c>
       <c r="F23" s="36"/>
-      <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="70"/>
-      <c r="J23" s="70"/>
-      <c r="K23" s="70"/>
-      <c r="L23" s="70"/>
-      <c r="M23" s="70"/>
-      <c r="N23" s="70"/>
-      <c r="O23" s="70"/>
-      <c r="P23" s="70"/>
-      <c r="Q23" s="70"/>
-      <c r="R23" s="70"/>
-      <c r="S23" s="161"/>
-      <c r="T23" s="162"/>
-      <c r="U23" s="162"/>
-      <c r="V23" s="162"/>
-      <c r="W23" s="162"/>
-      <c r="X23" s="162"/>
-      <c r="Y23" s="162"/>
-      <c r="Z23" s="162"/>
-      <c r="AA23" s="162"/>
-      <c r="AB23" s="162"/>
-      <c r="AC23" s="162"/>
-      <c r="AD23" s="162"/>
-      <c r="AE23" s="162"/>
-      <c r="AF23" s="163"/>
+      <c r="G23" s="69"/>
+      <c r="H23" s="69"/>
+      <c r="I23" s="69"/>
+      <c r="J23" s="69"/>
+      <c r="K23" s="69"/>
+      <c r="L23" s="69"/>
+      <c r="M23" s="69"/>
+      <c r="N23" s="69"/>
+      <c r="O23" s="69"/>
+      <c r="P23" s="69"/>
+      <c r="Q23" s="69"/>
+      <c r="R23" s="69"/>
+      <c r="S23" s="159"/>
+      <c r="T23" s="160"/>
+      <c r="U23" s="160"/>
+      <c r="V23" s="160"/>
+      <c r="W23" s="160"/>
+      <c r="X23" s="160"/>
+      <c r="Y23" s="160"/>
+      <c r="Z23" s="160"/>
+      <c r="AA23" s="160"/>
+      <c r="AB23" s="160"/>
+      <c r="AC23" s="160"/>
+      <c r="AD23" s="160"/>
+      <c r="AE23" s="160"/>
+      <c r="AF23" s="161"/>
       <c r="AI23" s="3"/>
       <c r="AJ23" s="3"/>
       <c r="AK23" s="3"/>
@@ -20082,46 +20233,46 @@
       <c r="IO23" s="3"/>
     </row>
     <row r="24" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A24" s="109" t="s">
+      <c r="A24" s="101" t="s">
         <v>112</v>
       </c>
-      <c r="B24" s="112" t="s">
+      <c r="B24" s="104" t="s">
         <v>113</v>
       </c>
-      <c r="C24" s="113"/>
-      <c r="D24" s="97" t="s">
+      <c r="C24" s="105"/>
+      <c r="D24" s="92" t="s">
         <v>110</v>
       </c>
-      <c r="E24" s="97" t="s">
+      <c r="E24" s="92" t="s">
         <v>44</v>
       </c>
       <c r="F24" s="36"/>
-      <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="70"/>
-      <c r="J24" s="70"/>
-      <c r="K24" s="70"/>
-      <c r="L24" s="70"/>
-      <c r="M24" s="70"/>
-      <c r="N24" s="70"/>
-      <c r="O24" s="70"/>
-      <c r="P24" s="70"/>
-      <c r="Q24" s="70"/>
-      <c r="R24" s="70"/>
-      <c r="S24" s="161"/>
-      <c r="T24" s="162"/>
-      <c r="U24" s="162"/>
-      <c r="V24" s="162"/>
-      <c r="W24" s="162"/>
-      <c r="X24" s="162"/>
-      <c r="Y24" s="162"/>
-      <c r="Z24" s="162"/>
-      <c r="AA24" s="162"/>
-      <c r="AB24" s="162"/>
-      <c r="AC24" s="162"/>
-      <c r="AD24" s="162"/>
-      <c r="AE24" s="162"/>
-      <c r="AF24" s="163"/>
+      <c r="G24" s="69"/>
+      <c r="H24" s="69"/>
+      <c r="I24" s="69"/>
+      <c r="J24" s="69"/>
+      <c r="K24" s="69"/>
+      <c r="L24" s="69"/>
+      <c r="M24" s="69"/>
+      <c r="N24" s="69"/>
+      <c r="O24" s="69"/>
+      <c r="P24" s="69"/>
+      <c r="Q24" s="69"/>
+      <c r="R24" s="69"/>
+      <c r="S24" s="159"/>
+      <c r="T24" s="160"/>
+      <c r="U24" s="160"/>
+      <c r="V24" s="160"/>
+      <c r="W24" s="160"/>
+      <c r="X24" s="160"/>
+      <c r="Y24" s="160"/>
+      <c r="Z24" s="160"/>
+      <c r="AA24" s="160"/>
+      <c r="AB24" s="160"/>
+      <c r="AC24" s="160"/>
+      <c r="AD24" s="160"/>
+      <c r="AE24" s="160"/>
+      <c r="AF24" s="161"/>
       <c r="AI24" s="3"/>
       <c r="AJ24" s="3"/>
       <c r="AK24" s="3"/>
@@ -20342,41 +20493,41 @@
       <c r="A25" s="37">
         <v>4</v>
       </c>
-      <c r="B25" s="112" t="s">
+      <c r="B25" s="104" t="s">
         <v>89</v>
       </c>
-      <c r="C25" s="113"/>
-      <c r="D25" s="97"/>
-      <c r="E25" s="97" t="s">
+      <c r="C25" s="105"/>
+      <c r="D25" s="92"/>
+      <c r="E25" s="92" t="s">
         <v>45</v>
       </c>
       <c r="F25" s="36"/>
-      <c r="G25" s="70"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="70"/>
-      <c r="J25" s="70"/>
-      <c r="K25" s="70"/>
-      <c r="L25" s="70"/>
-      <c r="M25" s="70"/>
-      <c r="N25" s="70"/>
-      <c r="O25" s="70"/>
-      <c r="P25" s="70"/>
-      <c r="Q25" s="70"/>
-      <c r="R25" s="70"/>
-      <c r="S25" s="161"/>
-      <c r="T25" s="162"/>
-      <c r="U25" s="162"/>
-      <c r="V25" s="162"/>
-      <c r="W25" s="162"/>
-      <c r="X25" s="162"/>
-      <c r="Y25" s="162"/>
-      <c r="Z25" s="162"/>
-      <c r="AA25" s="162"/>
-      <c r="AB25" s="162"/>
-      <c r="AC25" s="162"/>
-      <c r="AD25" s="162"/>
-      <c r="AE25" s="162"/>
-      <c r="AF25" s="163"/>
+      <c r="G25" s="69"/>
+      <c r="H25" s="69"/>
+      <c r="I25" s="69"/>
+      <c r="J25" s="69"/>
+      <c r="K25" s="69"/>
+      <c r="L25" s="69"/>
+      <c r="M25" s="69"/>
+      <c r="N25" s="69"/>
+      <c r="O25" s="69"/>
+      <c r="P25" s="69"/>
+      <c r="Q25" s="69"/>
+      <c r="R25" s="69"/>
+      <c r="S25" s="159"/>
+      <c r="T25" s="160"/>
+      <c r="U25" s="160"/>
+      <c r="V25" s="160"/>
+      <c r="W25" s="160"/>
+      <c r="X25" s="160"/>
+      <c r="Y25" s="160"/>
+      <c r="Z25" s="160"/>
+      <c r="AA25" s="160"/>
+      <c r="AB25" s="160"/>
+      <c r="AC25" s="160"/>
+      <c r="AD25" s="160"/>
+      <c r="AE25" s="160"/>
+      <c r="AF25" s="161"/>
       <c r="AI25" s="3"/>
       <c r="AJ25" s="3"/>
       <c r="AK25" s="3"/>
@@ -20597,41 +20748,41 @@
       <c r="A26" s="37">
         <v>5</v>
       </c>
-      <c r="B26" s="112" t="s">
+      <c r="B26" s="104" t="s">
         <v>114</v>
       </c>
-      <c r="C26" s="113"/>
-      <c r="D26" s="97"/>
-      <c r="E26" s="97" t="s">
+      <c r="C26" s="105"/>
+      <c r="D26" s="92"/>
+      <c r="E26" s="92" t="s">
         <v>41</v>
       </c>
       <c r="F26" s="36"/>
-      <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="70"/>
-      <c r="J26" s="70"/>
-      <c r="K26" s="70"/>
-      <c r="L26" s="70"/>
-      <c r="M26" s="70"/>
-      <c r="N26" s="70"/>
-      <c r="O26" s="70"/>
-      <c r="P26" s="70"/>
-      <c r="Q26" s="70"/>
-      <c r="R26" s="70"/>
-      <c r="S26" s="161"/>
-      <c r="T26" s="162"/>
-      <c r="U26" s="162"/>
-      <c r="V26" s="162"/>
-      <c r="W26" s="162"/>
-      <c r="X26" s="162"/>
-      <c r="Y26" s="162"/>
-      <c r="Z26" s="162"/>
-      <c r="AA26" s="162"/>
-      <c r="AB26" s="162"/>
-      <c r="AC26" s="162"/>
-      <c r="AD26" s="162"/>
-      <c r="AE26" s="162"/>
-      <c r="AF26" s="163"/>
+      <c r="G26" s="69"/>
+      <c r="H26" s="69"/>
+      <c r="I26" s="69"/>
+      <c r="J26" s="69"/>
+      <c r="K26" s="69"/>
+      <c r="L26" s="69"/>
+      <c r="M26" s="69"/>
+      <c r="N26" s="69"/>
+      <c r="O26" s="69"/>
+      <c r="P26" s="69"/>
+      <c r="Q26" s="69"/>
+      <c r="R26" s="69"/>
+      <c r="S26" s="159"/>
+      <c r="T26" s="160"/>
+      <c r="U26" s="160"/>
+      <c r="V26" s="160"/>
+      <c r="W26" s="160"/>
+      <c r="X26" s="160"/>
+      <c r="Y26" s="160"/>
+      <c r="Z26" s="160"/>
+      <c r="AA26" s="160"/>
+      <c r="AB26" s="160"/>
+      <c r="AC26" s="160"/>
+      <c r="AD26" s="160"/>
+      <c r="AE26" s="160"/>
+      <c r="AF26" s="161"/>
       <c r="AI26" s="3"/>
       <c r="AJ26" s="3"/>
       <c r="AK26" s="3"/>
@@ -20852,41 +21003,41 @@
       <c r="A27" s="37">
         <v>6</v>
       </c>
-      <c r="B27" s="112" t="s">
+      <c r="B27" s="104" t="s">
         <v>116</v>
       </c>
-      <c r="C27" s="113"/>
-      <c r="D27" s="97"/>
-      <c r="E27" s="97" t="s">
+      <c r="C27" s="105"/>
+      <c r="D27" s="92"/>
+      <c r="E27" s="92" t="s">
         <v>41</v>
       </c>
       <c r="F27" s="36"/>
-      <c r="G27" s="70"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="70"/>
-      <c r="J27" s="70"/>
-      <c r="K27" s="70"/>
-      <c r="L27" s="70"/>
-      <c r="M27" s="70"/>
-      <c r="N27" s="70"/>
-      <c r="O27" s="70"/>
-      <c r="P27" s="70"/>
-      <c r="Q27" s="70"/>
-      <c r="R27" s="70"/>
-      <c r="S27" s="161"/>
-      <c r="T27" s="162"/>
-      <c r="U27" s="162"/>
-      <c r="V27" s="162"/>
-      <c r="W27" s="162"/>
-      <c r="X27" s="162"/>
-      <c r="Y27" s="162"/>
-      <c r="Z27" s="162"/>
-      <c r="AA27" s="162"/>
-      <c r="AB27" s="162"/>
-      <c r="AC27" s="162"/>
-      <c r="AD27" s="162"/>
-      <c r="AE27" s="162"/>
-      <c r="AF27" s="163"/>
+      <c r="G27" s="69"/>
+      <c r="H27" s="69"/>
+      <c r="I27" s="69"/>
+      <c r="J27" s="69"/>
+      <c r="K27" s="69"/>
+      <c r="L27" s="69"/>
+      <c r="M27" s="69"/>
+      <c r="N27" s="69"/>
+      <c r="O27" s="69"/>
+      <c r="P27" s="69"/>
+      <c r="Q27" s="69"/>
+      <c r="R27" s="69"/>
+      <c r="S27" s="159"/>
+      <c r="T27" s="160"/>
+      <c r="U27" s="160"/>
+      <c r="V27" s="160"/>
+      <c r="W27" s="160"/>
+      <c r="X27" s="160"/>
+      <c r="Y27" s="160"/>
+      <c r="Z27" s="160"/>
+      <c r="AA27" s="160"/>
+      <c r="AB27" s="160"/>
+      <c r="AC27" s="160"/>
+      <c r="AD27" s="160"/>
+      <c r="AE27" s="160"/>
+      <c r="AF27" s="161"/>
       <c r="AI27" s="3"/>
       <c r="AJ27" s="3"/>
       <c r="AK27" s="3"/>
@@ -21107,41 +21258,41 @@
       <c r="A28" s="37">
         <v>7</v>
       </c>
-      <c r="B28" s="112" t="s">
+      <c r="B28" s="104" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="113"/>
-      <c r="D28" s="97"/>
-      <c r="E28" s="97" t="s">
+      <c r="C28" s="105"/>
+      <c r="D28" s="92"/>
+      <c r="E28" s="92" t="s">
         <v>40</v>
       </c>
       <c r="F28" s="36"/>
-      <c r="G28" s="70"/>
-      <c r="H28" s="70"/>
-      <c r="I28" s="70"/>
-      <c r="J28" s="70"/>
-      <c r="K28" s="70"/>
-      <c r="L28" s="70"/>
-      <c r="M28" s="70"/>
-      <c r="N28" s="70"/>
-      <c r="O28" s="70"/>
-      <c r="P28" s="70"/>
-      <c r="Q28" s="70"/>
-      <c r="R28" s="70"/>
-      <c r="S28" s="161"/>
-      <c r="T28" s="162"/>
-      <c r="U28" s="162"/>
-      <c r="V28" s="162"/>
-      <c r="W28" s="162"/>
-      <c r="X28" s="162"/>
-      <c r="Y28" s="162"/>
-      <c r="Z28" s="162"/>
-      <c r="AA28" s="162"/>
-      <c r="AB28" s="162"/>
-      <c r="AC28" s="162"/>
-      <c r="AD28" s="162"/>
-      <c r="AE28" s="162"/>
-      <c r="AF28" s="163"/>
+      <c r="G28" s="69"/>
+      <c r="H28" s="69"/>
+      <c r="I28" s="69"/>
+      <c r="J28" s="69"/>
+      <c r="K28" s="69"/>
+      <c r="L28" s="69"/>
+      <c r="M28" s="69"/>
+      <c r="N28" s="69"/>
+      <c r="O28" s="69"/>
+      <c r="P28" s="69"/>
+      <c r="Q28" s="69"/>
+      <c r="R28" s="69"/>
+      <c r="S28" s="159"/>
+      <c r="T28" s="160"/>
+      <c r="U28" s="160"/>
+      <c r="V28" s="160"/>
+      <c r="W28" s="160"/>
+      <c r="X28" s="160"/>
+      <c r="Y28" s="160"/>
+      <c r="Z28" s="160"/>
+      <c r="AA28" s="160"/>
+      <c r="AB28" s="160"/>
+      <c r="AC28" s="160"/>
+      <c r="AD28" s="160"/>
+      <c r="AE28" s="160"/>
+      <c r="AF28" s="161"/>
       <c r="AI28" s="3"/>
       <c r="AJ28" s="3"/>
       <c r="AK28" s="3"/>
@@ -21360,39 +21511,39 @@
     </row>
     <row r="29" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A29" s="37"/>
-      <c r="B29" s="112"/>
-      <c r="C29" s="113"/>
-      <c r="D29" s="97"/>
-      <c r="E29" s="97" t="s">
+      <c r="B29" s="104"/>
+      <c r="C29" s="105"/>
+      <c r="D29" s="92"/>
+      <c r="E29" s="92" t="s">
         <v>40</v>
       </c>
       <c r="F29" s="36"/>
-      <c r="G29" s="70"/>
-      <c r="H29" s="70"/>
-      <c r="I29" s="70"/>
-      <c r="J29" s="70"/>
-      <c r="K29" s="70"/>
-      <c r="L29" s="70"/>
-      <c r="M29" s="70"/>
-      <c r="N29" s="70"/>
-      <c r="O29" s="70"/>
-      <c r="P29" s="70"/>
-      <c r="Q29" s="70"/>
-      <c r="R29" s="70"/>
-      <c r="S29" s="161"/>
-      <c r="T29" s="162"/>
-      <c r="U29" s="162"/>
-      <c r="V29" s="162"/>
-      <c r="W29" s="162"/>
-      <c r="X29" s="162"/>
-      <c r="Y29" s="162"/>
-      <c r="Z29" s="162"/>
-      <c r="AA29" s="162"/>
-      <c r="AB29" s="162"/>
-      <c r="AC29" s="162"/>
-      <c r="AD29" s="162"/>
-      <c r="AE29" s="162"/>
-      <c r="AF29" s="163"/>
+      <c r="G29" s="69"/>
+      <c r="H29" s="69"/>
+      <c r="I29" s="69"/>
+      <c r="J29" s="69"/>
+      <c r="K29" s="69"/>
+      <c r="L29" s="69"/>
+      <c r="M29" s="69"/>
+      <c r="N29" s="69"/>
+      <c r="O29" s="69"/>
+      <c r="P29" s="69"/>
+      <c r="Q29" s="69"/>
+      <c r="R29" s="69"/>
+      <c r="S29" s="159"/>
+      <c r="T29" s="160"/>
+      <c r="U29" s="160"/>
+      <c r="V29" s="160"/>
+      <c r="W29" s="160"/>
+      <c r="X29" s="160"/>
+      <c r="Y29" s="160"/>
+      <c r="Z29" s="160"/>
+      <c r="AA29" s="160"/>
+      <c r="AB29" s="160"/>
+      <c r="AC29" s="160"/>
+      <c r="AD29" s="160"/>
+      <c r="AE29" s="160"/>
+      <c r="AF29" s="161"/>
       <c r="AI29" s="3"/>
       <c r="AJ29" s="3"/>
       <c r="AK29" s="3"/>
@@ -21611,39 +21762,39 @@
     </row>
     <row r="30" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A30" s="37"/>
-      <c r="B30" s="125" t="s">
+      <c r="B30" s="143" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="126"/>
-      <c r="D30" s="97"/>
-      <c r="E30" s="97"/>
+      <c r="C30" s="144"/>
+      <c r="D30" s="92"/>
+      <c r="E30" s="92"/>
       <c r="F30" s="36"/>
-      <c r="G30" s="70"/>
-      <c r="H30" s="70"/>
-      <c r="I30" s="70"/>
-      <c r="J30" s="70"/>
-      <c r="K30" s="70"/>
-      <c r="L30" s="70"/>
-      <c r="M30" s="70"/>
-      <c r="N30" s="70"/>
-      <c r="O30" s="70"/>
-      <c r="P30" s="70"/>
-      <c r="Q30" s="70"/>
-      <c r="R30" s="70"/>
-      <c r="S30" s="161"/>
-      <c r="T30" s="162"/>
-      <c r="U30" s="162"/>
-      <c r="V30" s="162"/>
-      <c r="W30" s="162"/>
-      <c r="X30" s="162"/>
-      <c r="Y30" s="162"/>
-      <c r="Z30" s="162"/>
-      <c r="AA30" s="162"/>
-      <c r="AB30" s="162"/>
-      <c r="AC30" s="162"/>
-      <c r="AD30" s="162"/>
-      <c r="AE30" s="162"/>
-      <c r="AF30" s="163"/>
+      <c r="G30" s="69"/>
+      <c r="H30" s="69"/>
+      <c r="I30" s="69"/>
+      <c r="J30" s="69"/>
+      <c r="K30" s="69"/>
+      <c r="L30" s="69"/>
+      <c r="M30" s="69"/>
+      <c r="N30" s="69"/>
+      <c r="O30" s="69"/>
+      <c r="P30" s="69"/>
+      <c r="Q30" s="69"/>
+      <c r="R30" s="69"/>
+      <c r="S30" s="159"/>
+      <c r="T30" s="160"/>
+      <c r="U30" s="160"/>
+      <c r="V30" s="160"/>
+      <c r="W30" s="160"/>
+      <c r="X30" s="160"/>
+      <c r="Y30" s="160"/>
+      <c r="Z30" s="160"/>
+      <c r="AA30" s="160"/>
+      <c r="AB30" s="160"/>
+      <c r="AC30" s="160"/>
+      <c r="AD30" s="160"/>
+      <c r="AE30" s="160"/>
+      <c r="AF30" s="161"/>
       <c r="AI30" s="3"/>
       <c r="AJ30" s="3"/>
       <c r="AK30" s="3"/>
@@ -21862,41 +22013,41 @@
     </row>
     <row r="31" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A31" s="37"/>
-      <c r="B31" s="112" t="s">
+      <c r="B31" s="104" t="s">
         <v>92</v>
       </c>
-      <c r="C31" s="113"/>
-      <c r="D31" s="116" t="s">
+      <c r="C31" s="105"/>
+      <c r="D31" s="158" t="s">
         <v>117</v>
       </c>
-      <c r="E31" s="97"/>
+      <c r="E31" s="92"/>
       <c r="F31" s="36"/>
-      <c r="G31" s="70"/>
-      <c r="H31" s="70"/>
-      <c r="I31" s="70"/>
-      <c r="J31" s="70"/>
-      <c r="K31" s="70"/>
-      <c r="L31" s="70"/>
-      <c r="M31" s="70"/>
-      <c r="N31" s="70"/>
-      <c r="O31" s="70"/>
-      <c r="P31" s="70"/>
-      <c r="Q31" s="70"/>
-      <c r="R31" s="70"/>
-      <c r="S31" s="161"/>
-      <c r="T31" s="162"/>
-      <c r="U31" s="162"/>
-      <c r="V31" s="162"/>
-      <c r="W31" s="162"/>
-      <c r="X31" s="162"/>
-      <c r="Y31" s="162"/>
-      <c r="Z31" s="162"/>
-      <c r="AA31" s="162"/>
-      <c r="AB31" s="162"/>
-      <c r="AC31" s="162"/>
-      <c r="AD31" s="162"/>
-      <c r="AE31" s="162"/>
-      <c r="AF31" s="163"/>
+      <c r="G31" s="69"/>
+      <c r="H31" s="69"/>
+      <c r="I31" s="69"/>
+      <c r="J31" s="69"/>
+      <c r="K31" s="69"/>
+      <c r="L31" s="69"/>
+      <c r="M31" s="69"/>
+      <c r="N31" s="69"/>
+      <c r="O31" s="69"/>
+      <c r="P31" s="69"/>
+      <c r="Q31" s="69"/>
+      <c r="R31" s="69"/>
+      <c r="S31" s="159"/>
+      <c r="T31" s="160"/>
+      <c r="U31" s="160"/>
+      <c r="V31" s="160"/>
+      <c r="W31" s="160"/>
+      <c r="X31" s="160"/>
+      <c r="Y31" s="160"/>
+      <c r="Z31" s="160"/>
+      <c r="AA31" s="160"/>
+      <c r="AB31" s="160"/>
+      <c r="AC31" s="160"/>
+      <c r="AD31" s="160"/>
+      <c r="AE31" s="160"/>
+      <c r="AF31" s="161"/>
       <c r="AI31" s="3"/>
       <c r="AJ31" s="3"/>
       <c r="AK31" s="3"/>
@@ -22115,12 +22266,12 @@
     </row>
     <row r="32" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A32" s="37"/>
-      <c r="B32" s="112" t="s">
+      <c r="B32" s="104" t="s">
         <v>93</v>
       </c>
-      <c r="C32" s="113"/>
-      <c r="D32" s="117"/>
-      <c r="E32" s="97" t="s">
+      <c r="C32" s="105"/>
+      <c r="D32" s="106"/>
+      <c r="E32" s="92" t="s">
         <v>47</v>
       </c>
       <c r="F32" s="36"/>
@@ -22136,20 +22287,20 @@
       <c r="P32" s="68"/>
       <c r="Q32" s="68"/>
       <c r="R32" s="68"/>
-      <c r="S32" s="161"/>
-      <c r="T32" s="162"/>
-      <c r="U32" s="162"/>
-      <c r="V32" s="162"/>
-      <c r="W32" s="162"/>
-      <c r="X32" s="162"/>
-      <c r="Y32" s="162"/>
-      <c r="Z32" s="162"/>
-      <c r="AA32" s="162"/>
-      <c r="AB32" s="162"/>
-      <c r="AC32" s="162"/>
-      <c r="AD32" s="162"/>
-      <c r="AE32" s="162"/>
-      <c r="AF32" s="163"/>
+      <c r="S32" s="159"/>
+      <c r="T32" s="160"/>
+      <c r="U32" s="160"/>
+      <c r="V32" s="160"/>
+      <c r="W32" s="160"/>
+      <c r="X32" s="160"/>
+      <c r="Y32" s="160"/>
+      <c r="Z32" s="160"/>
+      <c r="AA32" s="160"/>
+      <c r="AB32" s="160"/>
+      <c r="AC32" s="160"/>
+      <c r="AD32" s="160"/>
+      <c r="AE32" s="160"/>
+      <c r="AF32" s="161"/>
       <c r="AI32" s="3"/>
       <c r="AJ32" s="3"/>
       <c r="AK32" s="3"/>
@@ -22368,12 +22519,12 @@
     </row>
     <row r="33" spans="1:249" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A33" s="37"/>
-      <c r="B33" s="112" t="s">
+      <c r="B33" s="104" t="s">
         <v>94</v>
       </c>
-      <c r="C33" s="113"/>
-      <c r="D33" s="127"/>
-      <c r="E33" s="97"/>
+      <c r="C33" s="105"/>
+      <c r="D33" s="107"/>
+      <c r="E33" s="92"/>
       <c r="F33" s="36"/>
       <c r="G33" s="68"/>
       <c r="H33" s="68"/>
@@ -22387,20 +22538,20 @@
       <c r="P33" s="68"/>
       <c r="Q33" s="68"/>
       <c r="R33" s="68"/>
-      <c r="S33" s="161"/>
-      <c r="T33" s="162"/>
-      <c r="U33" s="162"/>
-      <c r="V33" s="162"/>
-      <c r="W33" s="162"/>
-      <c r="X33" s="162"/>
-      <c r="Y33" s="162"/>
-      <c r="Z33" s="162"/>
-      <c r="AA33" s="162"/>
-      <c r="AB33" s="162"/>
-      <c r="AC33" s="162"/>
-      <c r="AD33" s="162"/>
-      <c r="AE33" s="162"/>
-      <c r="AF33" s="163"/>
+      <c r="S33" s="159"/>
+      <c r="T33" s="160"/>
+      <c r="U33" s="160"/>
+      <c r="V33" s="160"/>
+      <c r="W33" s="160"/>
+      <c r="X33" s="160"/>
+      <c r="Y33" s="160"/>
+      <c r="Z33" s="160"/>
+      <c r="AA33" s="160"/>
+      <c r="AB33" s="160"/>
+      <c r="AC33" s="160"/>
+      <c r="AD33" s="160"/>
+      <c r="AE33" s="160"/>
+      <c r="AF33" s="161"/>
       <c r="AI33" s="3"/>
       <c r="AJ33" s="3"/>
       <c r="AK33" s="3"/>
@@ -22619,10 +22770,10 @@
     </row>
     <row r="34" spans="1:249" s="2" customFormat="1" ht="28.25" customHeight="1">
       <c r="A34" s="38"/>
-      <c r="B34" s="125" t="s">
+      <c r="B34" s="143" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="126"/>
+      <c r="C34" s="144"/>
       <c r="D34" s="35"/>
       <c r="E34" s="35"/>
       <c r="F34" s="39"/>
@@ -22638,20 +22789,20 @@
       <c r="P34" s="68"/>
       <c r="Q34" s="68"/>
       <c r="R34" s="68"/>
-      <c r="S34" s="161"/>
-      <c r="T34" s="162"/>
-      <c r="U34" s="162"/>
-      <c r="V34" s="162"/>
-      <c r="W34" s="162"/>
-      <c r="X34" s="162"/>
-      <c r="Y34" s="162"/>
-      <c r="Z34" s="162"/>
-      <c r="AA34" s="162"/>
-      <c r="AB34" s="162"/>
-      <c r="AC34" s="162"/>
-      <c r="AD34" s="162"/>
-      <c r="AE34" s="162"/>
-      <c r="AF34" s="163"/>
+      <c r="S34" s="159"/>
+      <c r="T34" s="160"/>
+      <c r="U34" s="160"/>
+      <c r="V34" s="160"/>
+      <c r="W34" s="160"/>
+      <c r="X34" s="160"/>
+      <c r="Y34" s="160"/>
+      <c r="Z34" s="160"/>
+      <c r="AA34" s="160"/>
+      <c r="AB34" s="160"/>
+      <c r="AC34" s="160"/>
+      <c r="AD34" s="160"/>
+      <c r="AE34" s="160"/>
+      <c r="AF34" s="161"/>
       <c r="AI34" s="3"/>
       <c r="AJ34" s="3"/>
       <c r="AK34" s="3"/>
@@ -22872,43 +23023,43 @@
       <c r="A35" s="37">
         <v>1</v>
       </c>
-      <c r="B35" s="114" t="s">
+      <c r="B35" s="141" t="s">
         <v>104</v>
       </c>
-      <c r="C35" s="115"/>
-      <c r="D35" s="101"/>
-      <c r="E35" s="97" t="s">
+      <c r="C35" s="142"/>
+      <c r="D35" s="96"/>
+      <c r="E35" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="F35" s="116" t="s">
+      <c r="F35" s="158" t="s">
         <v>95</v>
       </c>
-      <c r="G35" s="70"/>
-      <c r="H35" s="70"/>
-      <c r="I35" s="70"/>
-      <c r="J35" s="70"/>
-      <c r="K35" s="70"/>
-      <c r="L35" s="70"/>
-      <c r="M35" s="70"/>
-      <c r="N35" s="70"/>
-      <c r="O35" s="70"/>
-      <c r="P35" s="70"/>
-      <c r="Q35" s="70"/>
-      <c r="R35" s="70"/>
-      <c r="S35" s="161"/>
-      <c r="T35" s="162"/>
-      <c r="U35" s="162"/>
-      <c r="V35" s="162"/>
-      <c r="W35" s="162"/>
-      <c r="X35" s="162"/>
-      <c r="Y35" s="162"/>
-      <c r="Z35" s="162"/>
-      <c r="AA35" s="162"/>
-      <c r="AB35" s="162"/>
-      <c r="AC35" s="162"/>
-      <c r="AD35" s="162"/>
-      <c r="AE35" s="162"/>
-      <c r="AF35" s="163"/>
+      <c r="G35" s="69"/>
+      <c r="H35" s="69"/>
+      <c r="I35" s="69"/>
+      <c r="J35" s="69"/>
+      <c r="K35" s="69"/>
+      <c r="L35" s="69"/>
+      <c r="M35" s="69"/>
+      <c r="N35" s="69"/>
+      <c r="O35" s="69"/>
+      <c r="P35" s="69"/>
+      <c r="Q35" s="69"/>
+      <c r="R35" s="69"/>
+      <c r="S35" s="159"/>
+      <c r="T35" s="160"/>
+      <c r="U35" s="160"/>
+      <c r="V35" s="160"/>
+      <c r="W35" s="160"/>
+      <c r="X35" s="160"/>
+      <c r="Y35" s="160"/>
+      <c r="Z35" s="160"/>
+      <c r="AA35" s="160"/>
+      <c r="AB35" s="160"/>
+      <c r="AC35" s="160"/>
+      <c r="AD35" s="160"/>
+      <c r="AE35" s="160"/>
+      <c r="AF35" s="161"/>
       <c r="AI35" s="3"/>
       <c r="AJ35" s="3"/>
       <c r="AK35" s="3"/>
@@ -23129,13 +23280,13 @@
       <c r="A36" s="37">
         <v>2</v>
       </c>
-      <c r="B36" s="112"/>
-      <c r="C36" s="113"/>
-      <c r="D36" s="101"/>
-      <c r="E36" s="97" t="s">
+      <c r="B36" s="104"/>
+      <c r="C36" s="105"/>
+      <c r="D36" s="96"/>
+      <c r="E36" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="F36" s="117"/>
+      <c r="F36" s="106"/>
       <c r="G36" s="68"/>
       <c r="H36" s="68"/>
       <c r="I36" s="68"/>
@@ -23148,20 +23299,20 @@
       <c r="P36" s="68"/>
       <c r="Q36" s="68"/>
       <c r="R36" s="68"/>
-      <c r="S36" s="161"/>
-      <c r="T36" s="162"/>
-      <c r="U36" s="162"/>
-      <c r="V36" s="162"/>
-      <c r="W36" s="162"/>
-      <c r="X36" s="162"/>
-      <c r="Y36" s="162"/>
-      <c r="Z36" s="162"/>
-      <c r="AA36" s="162"/>
-      <c r="AB36" s="162"/>
-      <c r="AC36" s="162"/>
-      <c r="AD36" s="162"/>
-      <c r="AE36" s="162"/>
-      <c r="AF36" s="163"/>
+      <c r="S36" s="159"/>
+      <c r="T36" s="160"/>
+      <c r="U36" s="160"/>
+      <c r="V36" s="160"/>
+      <c r="W36" s="160"/>
+      <c r="X36" s="160"/>
+      <c r="Y36" s="160"/>
+      <c r="Z36" s="160"/>
+      <c r="AA36" s="160"/>
+      <c r="AB36" s="160"/>
+      <c r="AC36" s="160"/>
+      <c r="AD36" s="160"/>
+      <c r="AE36" s="160"/>
+      <c r="AF36" s="161"/>
       <c r="AI36" s="3"/>
       <c r="AJ36" s="3"/>
       <c r="AK36" s="3"/>
@@ -23382,11 +23533,11 @@
       <c r="A37" s="37">
         <v>3</v>
       </c>
-      <c r="B37" s="114"/>
-      <c r="C37" s="115"/>
-      <c r="D37" s="97"/>
+      <c r="B37" s="141"/>
+      <c r="C37" s="142"/>
+      <c r="D37" s="92"/>
       <c r="E37" s="35"/>
-      <c r="F37" s="117"/>
+      <c r="F37" s="106"/>
       <c r="G37" s="68"/>
       <c r="H37" s="68"/>
       <c r="I37" s="68"/>
@@ -23399,20 +23550,20 @@
       <c r="P37" s="68"/>
       <c r="Q37" s="68"/>
       <c r="R37" s="68"/>
-      <c r="S37" s="161"/>
-      <c r="T37" s="162"/>
-      <c r="U37" s="162"/>
-      <c r="V37" s="162"/>
-      <c r="W37" s="162"/>
-      <c r="X37" s="162"/>
-      <c r="Y37" s="162"/>
-      <c r="Z37" s="162"/>
-      <c r="AA37" s="162"/>
-      <c r="AB37" s="162"/>
-      <c r="AC37" s="162"/>
-      <c r="AD37" s="162"/>
-      <c r="AE37" s="162"/>
-      <c r="AF37" s="163"/>
+      <c r="S37" s="159"/>
+      <c r="T37" s="160"/>
+      <c r="U37" s="160"/>
+      <c r="V37" s="160"/>
+      <c r="W37" s="160"/>
+      <c r="X37" s="160"/>
+      <c r="Y37" s="160"/>
+      <c r="Z37" s="160"/>
+      <c r="AA37" s="160"/>
+      <c r="AB37" s="160"/>
+      <c r="AC37" s="160"/>
+      <c r="AD37" s="160"/>
+      <c r="AE37" s="160"/>
+      <c r="AF37" s="161"/>
       <c r="AI37" s="3"/>
       <c r="AJ37" s="3"/>
       <c r="AK37" s="3"/>
@@ -23631,41 +23782,41 @@
     </row>
     <row r="38" spans="1:249" s="2" customFormat="1" ht="42" customHeight="1" thickBot="1">
       <c r="A38" s="41"/>
-      <c r="B38" s="121" t="s">
+      <c r="B38" s="145" t="s">
         <v>63</v>
       </c>
-      <c r="C38" s="122"/>
+      <c r="C38" s="146"/>
       <c r="D38" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="E38" s="100"/>
+      <c r="E38" s="95"/>
       <c r="F38" s="43"/>
-      <c r="G38" s="77"/>
-      <c r="H38" s="77"/>
-      <c r="I38" s="77"/>
-      <c r="J38" s="77"/>
-      <c r="K38" s="77"/>
-      <c r="L38" s="77"/>
-      <c r="M38" s="77"/>
-      <c r="N38" s="77"/>
-      <c r="O38" s="77"/>
-      <c r="P38" s="77"/>
-      <c r="Q38" s="77"/>
-      <c r="R38" s="77"/>
-      <c r="S38" s="77"/>
-      <c r="T38" s="77"/>
-      <c r="U38" s="77"/>
-      <c r="V38" s="77"/>
-      <c r="W38" s="77"/>
-      <c r="X38" s="77"/>
-      <c r="Y38" s="77"/>
-      <c r="Z38" s="77"/>
-      <c r="AA38" s="77"/>
-      <c r="AB38" s="77"/>
-      <c r="AC38" s="77"/>
-      <c r="AD38" s="77"/>
-      <c r="AE38" s="78"/>
-      <c r="AF38" s="79"/>
+      <c r="G38" s="72"/>
+      <c r="H38" s="72"/>
+      <c r="I38" s="72"/>
+      <c r="J38" s="72"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="72"/>
+      <c r="M38" s="72"/>
+      <c r="N38" s="72"/>
+      <c r="O38" s="72"/>
+      <c r="P38" s="72"/>
+      <c r="Q38" s="72"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="72"/>
+      <c r="T38" s="72"/>
+      <c r="U38" s="72"/>
+      <c r="V38" s="72"/>
+      <c r="W38" s="72"/>
+      <c r="X38" s="72"/>
+      <c r="Y38" s="72"/>
+      <c r="Z38" s="72"/>
+      <c r="AA38" s="72"/>
+      <c r="AB38" s="72"/>
+      <c r="AC38" s="72"/>
+      <c r="AD38" s="72"/>
+      <c r="AE38" s="73"/>
+      <c r="AF38" s="74"/>
       <c r="AI38" s="3"/>
       <c r="AJ38" s="3"/>
       <c r="AK38" s="3"/>
@@ -23891,30 +24042,30 @@
       <c r="D39" s="44"/>
       <c r="E39" s="44"/>
       <c r="F39" s="57"/>
-      <c r="G39" s="80"/>
-      <c r="H39" s="119"/>
-      <c r="I39" s="119"/>
-      <c r="J39" s="119"/>
-      <c r="K39" s="119"/>
-      <c r="L39" s="81"/>
-      <c r="M39" s="80"/>
-      <c r="N39" s="119"/>
-      <c r="O39" s="119"/>
-      <c r="P39" s="119"/>
-      <c r="Q39" s="119"/>
-      <c r="R39" s="81"/>
-      <c r="S39" s="80"/>
-      <c r="T39" s="119"/>
-      <c r="U39" s="119"/>
-      <c r="V39" s="119"/>
-      <c r="W39" s="80"/>
-      <c r="X39" s="119"/>
-      <c r="Y39" s="119"/>
-      <c r="Z39" s="119"/>
-      <c r="AA39" s="81"/>
-      <c r="AB39" s="80"/>
-      <c r="AC39" s="119"/>
-      <c r="AD39" s="119"/>
+      <c r="G39" s="75"/>
+      <c r="H39" s="167"/>
+      <c r="I39" s="167"/>
+      <c r="J39" s="167"/>
+      <c r="K39" s="167"/>
+      <c r="L39" s="76"/>
+      <c r="M39" s="75"/>
+      <c r="N39" s="167"/>
+      <c r="O39" s="167"/>
+      <c r="P39" s="167"/>
+      <c r="Q39" s="167"/>
+      <c r="R39" s="76"/>
+      <c r="S39" s="75"/>
+      <c r="T39" s="167"/>
+      <c r="U39" s="167"/>
+      <c r="V39" s="167"/>
+      <c r="W39" s="75"/>
+      <c r="X39" s="167"/>
+      <c r="Y39" s="167"/>
+      <c r="Z39" s="167"/>
+      <c r="AA39" s="76"/>
+      <c r="AB39" s="75"/>
+      <c r="AC39" s="167"/>
+      <c r="AD39" s="167"/>
       <c r="AE39" s="55"/>
       <c r="AF39" s="56"/>
       <c r="AI39" s="3"/>
@@ -24136,40 +24287,40 @@
     <row r="40" spans="1:249" s="2" customFormat="1" ht="23" hidden="1" customHeight="1">
       <c r="A40" s="45"/>
       <c r="B40" s="46"/>
-      <c r="C40" s="93" t="s">
+      <c r="C40" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="D40" s="95" t="s">
+      <c r="D40" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="E40" s="95"/>
+      <c r="E40" s="90"/>
       <c r="F40" s="58"/>
-      <c r="G40" s="82"/>
-      <c r="H40" s="120"/>
-      <c r="I40" s="120"/>
-      <c r="J40" s="120"/>
-      <c r="K40" s="120"/>
-      <c r="L40" s="83"/>
-      <c r="M40" s="82"/>
-      <c r="N40" s="120"/>
-      <c r="O40" s="120"/>
-      <c r="P40" s="120"/>
-      <c r="Q40" s="120"/>
-      <c r="R40" s="83"/>
-      <c r="S40" s="82"/>
-      <c r="T40" s="120"/>
-      <c r="U40" s="120"/>
-      <c r="V40" s="120"/>
-      <c r="W40" s="82"/>
-      <c r="X40" s="120"/>
-      <c r="Y40" s="120"/>
-      <c r="Z40" s="120"/>
-      <c r="AA40" s="83"/>
-      <c r="AB40" s="82"/>
-      <c r="AC40" s="120"/>
-      <c r="AD40" s="120"/>
+      <c r="G40" s="77"/>
+      <c r="H40" s="166"/>
+      <c r="I40" s="166"/>
+      <c r="J40" s="166"/>
+      <c r="K40" s="166"/>
+      <c r="L40" s="78"/>
+      <c r="M40" s="77"/>
+      <c r="N40" s="166"/>
+      <c r="O40" s="166"/>
+      <c r="P40" s="166"/>
+      <c r="Q40" s="166"/>
+      <c r="R40" s="78"/>
+      <c r="S40" s="77"/>
+      <c r="T40" s="166"/>
+      <c r="U40" s="166"/>
+      <c r="V40" s="166"/>
+      <c r="W40" s="77"/>
+      <c r="X40" s="166"/>
+      <c r="Y40" s="166"/>
+      <c r="Z40" s="166"/>
+      <c r="AA40" s="78"/>
+      <c r="AB40" s="77"/>
+      <c r="AC40" s="166"/>
+      <c r="AD40" s="166"/>
       <c r="AE40" s="61"/>
-      <c r="AF40" s="84"/>
+      <c r="AF40" s="79"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
@@ -24389,40 +24540,40 @@
     <row r="41" spans="1:249" s="2" customFormat="1" ht="23" hidden="1" customHeight="1">
       <c r="A41" s="47"/>
       <c r="B41" s="46"/>
-      <c r="C41" s="94" t="s">
+      <c r="C41" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="D41" s="96" t="s">
+      <c r="D41" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="E41" s="96"/>
+      <c r="E41" s="91"/>
       <c r="F41" s="59"/>
-      <c r="G41" s="82"/>
-      <c r="H41" s="120"/>
-      <c r="I41" s="120"/>
-      <c r="J41" s="120"/>
-      <c r="K41" s="120"/>
-      <c r="L41" s="85"/>
-      <c r="M41" s="82"/>
-      <c r="N41" s="120"/>
-      <c r="O41" s="120"/>
-      <c r="P41" s="120"/>
-      <c r="Q41" s="120"/>
-      <c r="R41" s="85"/>
-      <c r="S41" s="82"/>
-      <c r="T41" s="120"/>
-      <c r="U41" s="120"/>
-      <c r="V41" s="120"/>
-      <c r="W41" s="82"/>
-      <c r="X41" s="120"/>
-      <c r="Y41" s="120"/>
-      <c r="Z41" s="120"/>
-      <c r="AA41" s="85"/>
-      <c r="AB41" s="82"/>
-      <c r="AC41" s="120"/>
-      <c r="AD41" s="120"/>
+      <c r="G41" s="77"/>
+      <c r="H41" s="166"/>
+      <c r="I41" s="166"/>
+      <c r="J41" s="166"/>
+      <c r="K41" s="166"/>
+      <c r="L41" s="80"/>
+      <c r="M41" s="77"/>
+      <c r="N41" s="166"/>
+      <c r="O41" s="166"/>
+      <c r="P41" s="166"/>
+      <c r="Q41" s="166"/>
+      <c r="R41" s="80"/>
+      <c r="S41" s="77"/>
+      <c r="T41" s="166"/>
+      <c r="U41" s="166"/>
+      <c r="V41" s="166"/>
+      <c r="W41" s="77"/>
+      <c r="X41" s="166"/>
+      <c r="Y41" s="166"/>
+      <c r="Z41" s="166"/>
+      <c r="AA41" s="80"/>
+      <c r="AB41" s="77"/>
+      <c r="AC41" s="166"/>
+      <c r="AD41" s="166"/>
       <c r="AE41" s="62"/>
-      <c r="AF41" s="86"/>
+      <c r="AF41" s="81"/>
       <c r="AI41" s="3"/>
       <c r="AJ41" s="3"/>
       <c r="AK41" s="3"/>
@@ -24642,40 +24793,40 @@
     <row r="42" spans="1:249" s="2" customFormat="1" ht="23" hidden="1" customHeight="1">
       <c r="A42" s="48"/>
       <c r="B42" s="46"/>
-      <c r="C42" s="94" t="s">
+      <c r="C42" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="D42" s="96" t="s">
+      <c r="D42" s="91" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="96"/>
+      <c r="E42" s="91"/>
       <c r="F42" s="59"/>
-      <c r="G42" s="82"/>
-      <c r="H42" s="120"/>
-      <c r="I42" s="120"/>
-      <c r="J42" s="120"/>
-      <c r="K42" s="120"/>
-      <c r="L42" s="85"/>
-      <c r="M42" s="82"/>
-      <c r="N42" s="120"/>
-      <c r="O42" s="120"/>
-      <c r="P42" s="120"/>
-      <c r="Q42" s="120"/>
-      <c r="R42" s="85"/>
-      <c r="S42" s="82"/>
-      <c r="T42" s="120"/>
-      <c r="U42" s="120"/>
-      <c r="V42" s="120"/>
-      <c r="W42" s="82"/>
-      <c r="X42" s="120"/>
-      <c r="Y42" s="120"/>
-      <c r="Z42" s="120"/>
-      <c r="AA42" s="85"/>
-      <c r="AB42" s="82"/>
-      <c r="AC42" s="120"/>
-      <c r="AD42" s="120"/>
+      <c r="G42" s="77"/>
+      <c r="H42" s="166"/>
+      <c r="I42" s="166"/>
+      <c r="J42" s="166"/>
+      <c r="K42" s="166"/>
+      <c r="L42" s="80"/>
+      <c r="M42" s="77"/>
+      <c r="N42" s="166"/>
+      <c r="O42" s="166"/>
+      <c r="P42" s="166"/>
+      <c r="Q42" s="166"/>
+      <c r="R42" s="80"/>
+      <c r="S42" s="77"/>
+      <c r="T42" s="166"/>
+      <c r="U42" s="166"/>
+      <c r="V42" s="166"/>
+      <c r="W42" s="77"/>
+      <c r="X42" s="166"/>
+      <c r="Y42" s="166"/>
+      <c r="Z42" s="166"/>
+      <c r="AA42" s="80"/>
+      <c r="AB42" s="77"/>
+      <c r="AC42" s="166"/>
+      <c r="AD42" s="166"/>
       <c r="AE42" s="62"/>
-      <c r="AF42" s="86"/>
+      <c r="AF42" s="81"/>
       <c r="AI42" s="3"/>
       <c r="AJ42" s="3"/>
       <c r="AK42" s="3"/>
@@ -24899,32 +25050,32 @@
       <c r="D43" s="50"/>
       <c r="E43" s="50"/>
       <c r="F43" s="60"/>
-      <c r="G43" s="87"/>
-      <c r="H43" s="118"/>
-      <c r="I43" s="118"/>
-      <c r="J43" s="118"/>
-      <c r="K43" s="118"/>
-      <c r="L43" s="88"/>
-      <c r="M43" s="87"/>
-      <c r="N43" s="118"/>
-      <c r="O43" s="118"/>
-      <c r="P43" s="118"/>
-      <c r="Q43" s="118"/>
-      <c r="R43" s="88"/>
-      <c r="S43" s="87"/>
-      <c r="T43" s="118"/>
-      <c r="U43" s="118"/>
-      <c r="V43" s="118"/>
-      <c r="W43" s="87"/>
-      <c r="X43" s="118"/>
-      <c r="Y43" s="118"/>
-      <c r="Z43" s="118"/>
-      <c r="AA43" s="88"/>
-      <c r="AB43" s="87"/>
-      <c r="AC43" s="118"/>
-      <c r="AD43" s="118"/>
+      <c r="G43" s="82"/>
+      <c r="H43" s="162"/>
+      <c r="I43" s="162"/>
+      <c r="J43" s="162"/>
+      <c r="K43" s="162"/>
+      <c r="L43" s="83"/>
+      <c r="M43" s="82"/>
+      <c r="N43" s="162"/>
+      <c r="O43" s="162"/>
+      <c r="P43" s="162"/>
+      <c r="Q43" s="162"/>
+      <c r="R43" s="83"/>
+      <c r="S43" s="82"/>
+      <c r="T43" s="162"/>
+      <c r="U43" s="162"/>
+      <c r="V43" s="162"/>
+      <c r="W43" s="82"/>
+      <c r="X43" s="162"/>
+      <c r="Y43" s="162"/>
+      <c r="Z43" s="162"/>
+      <c r="AA43" s="83"/>
+      <c r="AB43" s="82"/>
+      <c r="AC43" s="162"/>
+      <c r="AD43" s="162"/>
       <c r="AE43" s="63"/>
-      <c r="AF43" s="89"/>
+      <c r="AF43" s="84"/>
       <c r="AI43" s="3"/>
       <c r="AJ43" s="3"/>
       <c r="AK43" s="3"/>
@@ -25186,20 +25337,78 @@
     </row>
   </sheetData>
   <mergeCells count="100">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:AF1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="T3:AF3"/>
+    <mergeCell ref="T5:W7"/>
+    <mergeCell ref="AD4:AF4"/>
+    <mergeCell ref="AD5:AF7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="S11:AF11"/>
+    <mergeCell ref="S12:AF12"/>
+    <mergeCell ref="S13:AF13"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="T4:W4"/>
+    <mergeCell ref="X4:Z4"/>
+    <mergeCell ref="AA4:AC4"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="S14:AF14"/>
+    <mergeCell ref="S15:AF15"/>
+    <mergeCell ref="S16:AF16"/>
+    <mergeCell ref="S17:AF17"/>
+    <mergeCell ref="S18:AF18"/>
+    <mergeCell ref="S19:AF19"/>
+    <mergeCell ref="S25:AF25"/>
+    <mergeCell ref="S24:AF24"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="S32:AF32"/>
-    <mergeCell ref="S33:AF33"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="AC39:AD39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="H39:K39"/>
+    <mergeCell ref="N39:Q39"/>
     <mergeCell ref="S36:AF36"/>
     <mergeCell ref="S37:AF37"/>
-    <mergeCell ref="S25:AF25"/>
-    <mergeCell ref="S26:AF26"/>
-    <mergeCell ref="S28:AF28"/>
-    <mergeCell ref="S29:AF29"/>
-    <mergeCell ref="S30:AF30"/>
-    <mergeCell ref="S31:AF31"/>
-    <mergeCell ref="S27:AF27"/>
+    <mergeCell ref="H40:K40"/>
+    <mergeCell ref="N40:Q40"/>
+    <mergeCell ref="T40:V40"/>
+    <mergeCell ref="X40:Z40"/>
+    <mergeCell ref="AC40:AD40"/>
+    <mergeCell ref="H43:K43"/>
+    <mergeCell ref="N43:Q43"/>
+    <mergeCell ref="T43:V43"/>
+    <mergeCell ref="X43:Z43"/>
+    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="N41:Q41"/>
+    <mergeCell ref="H42:K42"/>
+    <mergeCell ref="N42:Q42"/>
     <mergeCell ref="AC43:AD43"/>
     <mergeCell ref="S9:AF9"/>
     <mergeCell ref="S20:AF20"/>
@@ -25216,80 +25425,22 @@
     <mergeCell ref="X39:Z39"/>
     <mergeCell ref="S34:AF34"/>
     <mergeCell ref="S35:AF35"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="H43:K43"/>
-    <mergeCell ref="N43:Q43"/>
-    <mergeCell ref="T43:V43"/>
-    <mergeCell ref="X43:Z43"/>
-    <mergeCell ref="H41:K41"/>
-    <mergeCell ref="N41:Q41"/>
-    <mergeCell ref="H42:K42"/>
-    <mergeCell ref="N42:Q42"/>
-    <mergeCell ref="H39:K39"/>
-    <mergeCell ref="N39:Q39"/>
-    <mergeCell ref="AC39:AD39"/>
-    <mergeCell ref="H40:K40"/>
-    <mergeCell ref="N40:Q40"/>
-    <mergeCell ref="T40:V40"/>
-    <mergeCell ref="X40:Z40"/>
-    <mergeCell ref="AC40:AD40"/>
+    <mergeCell ref="S26:AF26"/>
+    <mergeCell ref="S28:AF28"/>
+    <mergeCell ref="S29:AF29"/>
+    <mergeCell ref="S30:AF30"/>
+    <mergeCell ref="S31:AF31"/>
+    <mergeCell ref="S27:AF27"/>
+    <mergeCell ref="S32:AF32"/>
+    <mergeCell ref="S33:AF33"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="F35:F37"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="D31:D33"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="AA4:AC4"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="S14:AF14"/>
-    <mergeCell ref="S15:AF15"/>
-    <mergeCell ref="S16:AF16"/>
-    <mergeCell ref="S17:AF17"/>
-    <mergeCell ref="S18:AF18"/>
-    <mergeCell ref="S19:AF19"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="S24:AF24"/>
-    <mergeCell ref="T5:W7"/>
-    <mergeCell ref="AD4:AF4"/>
-    <mergeCell ref="AD5:AF7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="S11:AF11"/>
-    <mergeCell ref="S12:AF12"/>
-    <mergeCell ref="S13:AF13"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="T4:W4"/>
-    <mergeCell ref="X4:Z4"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="F1:AF1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="T3:AF3"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="G11:R19 AG11:AK19">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>TEXT(G11,"aaa")="日"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/設備点検表.xlsx
+++ b/設備点検表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kosuk\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A366A603-2684-417E-AFEF-0C428427669C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77645DFE-6B25-48CC-B9C0-FCEAAB349713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6C56CF13-AF7F-4C1F-982C-EF388A11F51A}"/>
   </bookViews>
@@ -2720,11 +2720,68 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="77" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2732,65 +2789,41 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2831,92 +2864,65 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="71" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="72" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="73" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="67" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="74" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="178" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2951,43 +2957,37 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="71" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="72" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="73" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="67" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="77" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="74" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2995,7 +2995,7 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準_設備点検表書式" xfId="1" xr:uid="{15F629F0-A893-4DD8-8A94-9D447F97F79C}"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="10">
     <dxf>
       <font>
         <strike val="0"/>
@@ -3027,7 +3027,7 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
+        <strike/>
         <color theme="1"/>
       </font>
       <fill>
@@ -3045,7 +3045,7 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
+        <strike/>
         <color theme="1"/>
       </font>
       <fill>
@@ -3062,24 +3062,6 @@
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3432,45 +3414,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:254" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="155" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="108"/>
+      <c r="B1" s="155"/>
       <c r="C1" s="85"/>
-      <c r="F1" s="109" t="s">
+      <c r="F1" s="156" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
-      <c r="V1" s="109"/>
-      <c r="W1" s="109"/>
-      <c r="X1" s="109"/>
-      <c r="Y1" s="109"/>
-      <c r="Z1" s="109"/>
-      <c r="AA1" s="109"/>
-      <c r="AB1" s="109"/>
-      <c r="AC1" s="109"/>
-      <c r="AD1" s="109"/>
-      <c r="AE1" s="109"/>
-      <c r="AF1" s="109"/>
-      <c r="AG1" s="109"/>
-      <c r="AH1" s="109"/>
-      <c r="AI1" s="109"/>
-      <c r="AJ1" s="109"/>
-      <c r="AK1" s="109"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+      <c r="L1" s="156"/>
+      <c r="M1" s="156"/>
+      <c r="N1" s="156"/>
+      <c r="O1" s="156"/>
+      <c r="P1" s="156"/>
+      <c r="Q1" s="156"/>
+      <c r="R1" s="156"/>
+      <c r="S1" s="156"/>
+      <c r="T1" s="156"/>
+      <c r="U1" s="156"/>
+      <c r="V1" s="156"/>
+      <c r="W1" s="156"/>
+      <c r="X1" s="156"/>
+      <c r="Y1" s="156"/>
+      <c r="Z1" s="156"/>
+      <c r="AA1" s="156"/>
+      <c r="AB1" s="156"/>
+      <c r="AC1" s="156"/>
+      <c r="AD1" s="156"/>
+      <c r="AE1" s="156"/>
+      <c r="AF1" s="156"/>
+      <c r="AG1" s="156"/>
+      <c r="AH1" s="156"/>
+      <c r="AI1" s="156"/>
+      <c r="AJ1" s="156"/>
+      <c r="AK1" s="156"/>
       <c r="AN1" s="3"/>
       <c r="AO1" s="3"/>
       <c r="AP1" s="3"/>
@@ -3941,52 +3923,52 @@
       <c r="IT2" s="3"/>
     </row>
     <row r="3" spans="1:254" s="2" customFormat="1" ht="20" customHeight="1" thickBot="1">
-      <c r="A3" s="110" t="s">
+      <c r="A3" s="157" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="111"/>
-      <c r="C3" s="111"/>
-      <c r="D3" s="112"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
       <c r="E3" s="94"/>
       <c r="G3" s="51"/>
       <c r="H3" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="113" t="s">
+      <c r="K3" s="160" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="113"/>
-      <c r="M3" s="113" t="s">
+      <c r="L3" s="160"/>
+      <c r="M3" s="160" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="113"/>
-      <c r="O3" s="113"/>
-      <c r="P3" s="113" t="s">
+      <c r="N3" s="160"/>
+      <c r="O3" s="160"/>
+      <c r="P3" s="160" t="s">
         <v>2</v>
       </c>
-      <c r="Q3" s="113"/>
-      <c r="R3" s="113"/>
+      <c r="Q3" s="160"/>
+      <c r="R3" s="160"/>
       <c r="S3" s="3"/>
-      <c r="T3" s="114" t="s">
+      <c r="T3" s="161" t="s">
         <v>3</v>
       </c>
-      <c r="U3" s="115"/>
-      <c r="V3" s="115"/>
-      <c r="W3" s="115"/>
-      <c r="X3" s="115"/>
-      <c r="Y3" s="115"/>
-      <c r="Z3" s="115"/>
-      <c r="AA3" s="115"/>
-      <c r="AB3" s="115"/>
-      <c r="AC3" s="115"/>
-      <c r="AD3" s="115"/>
-      <c r="AE3" s="115"/>
-      <c r="AF3" s="115"/>
-      <c r="AG3" s="115"/>
-      <c r="AH3" s="115"/>
-      <c r="AI3" s="115"/>
-      <c r="AJ3" s="115"/>
-      <c r="AK3" s="116"/>
+      <c r="U3" s="162"/>
+      <c r="V3" s="162"/>
+      <c r="W3" s="162"/>
+      <c r="X3" s="162"/>
+      <c r="Y3" s="162"/>
+      <c r="Z3" s="162"/>
+      <c r="AA3" s="162"/>
+      <c r="AB3" s="162"/>
+      <c r="AC3" s="162"/>
+      <c r="AD3" s="162"/>
+      <c r="AE3" s="162"/>
+      <c r="AF3" s="162"/>
+      <c r="AG3" s="162"/>
+      <c r="AH3" s="162"/>
+      <c r="AI3" s="162"/>
+      <c r="AJ3" s="162"/>
+      <c r="AK3" s="163"/>
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
@@ -4215,47 +4197,47 @@
       <c r="H4" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="113" t="s">
+      <c r="K4" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="113"/>
-      <c r="M4" s="119">
+      <c r="L4" s="160"/>
+      <c r="M4" s="166">
         <v>46113</v>
       </c>
-      <c r="N4" s="119"/>
-      <c r="O4" s="119"/>
-      <c r="P4" s="113" t="s">
+      <c r="N4" s="166"/>
+      <c r="O4" s="166"/>
+      <c r="P4" s="160" t="s">
         <v>50</v>
       </c>
-      <c r="Q4" s="113"/>
-      <c r="R4" s="113"/>
+      <c r="Q4" s="160"/>
+      <c r="R4" s="160"/>
       <c r="S4" s="3"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="152" t="s">
         <v>5</v>
       </c>
-      <c r="U4" s="121"/>
-      <c r="V4" s="121"/>
-      <c r="W4" s="121"/>
-      <c r="X4" s="121"/>
-      <c r="Y4" s="122"/>
-      <c r="Z4" s="120" t="s">
+      <c r="U4" s="153"/>
+      <c r="V4" s="153"/>
+      <c r="W4" s="153"/>
+      <c r="X4" s="153"/>
+      <c r="Y4" s="154"/>
+      <c r="Z4" s="152" t="s">
         <v>6</v>
       </c>
-      <c r="AA4" s="121"/>
-      <c r="AB4" s="121"/>
-      <c r="AC4" s="122"/>
-      <c r="AD4" s="120" t="s">
+      <c r="AA4" s="153"/>
+      <c r="AB4" s="153"/>
+      <c r="AC4" s="154"/>
+      <c r="AD4" s="152" t="s">
         <v>7</v>
       </c>
-      <c r="AE4" s="121"/>
-      <c r="AF4" s="121"/>
-      <c r="AG4" s="122"/>
-      <c r="AH4" s="120" t="s">
+      <c r="AE4" s="153"/>
+      <c r="AF4" s="153"/>
+      <c r="AG4" s="154"/>
+      <c r="AH4" s="152" t="s">
         <v>8</v>
       </c>
-      <c r="AI4" s="121"/>
-      <c r="AJ4" s="121"/>
-      <c r="AK4" s="122"/>
+      <c r="AI4" s="153"/>
+      <c r="AJ4" s="153"/>
+      <c r="AK4" s="154"/>
       <c r="AN4" s="3"/>
       <c r="AO4" s="3"/>
       <c r="AP4" s="3"/>
@@ -4483,16 +4465,16 @@
         <v>23</v>
       </c>
       <c r="S5" s="3"/>
-      <c r="T5" s="123" t="s">
+      <c r="T5" s="167" t="s">
         <v>64</v>
       </c>
-      <c r="U5" s="124"/>
-      <c r="V5" s="124"/>
-      <c r="W5" s="128">
+      <c r="U5" s="168"/>
+      <c r="V5" s="168"/>
+      <c r="W5" s="139">
         <v>7</v>
       </c>
-      <c r="X5" s="129"/>
-      <c r="Y5" s="130"/>
+      <c r="X5" s="140"/>
+      <c r="Y5" s="141"/>
       <c r="Z5" s="11"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
@@ -4501,10 +4483,10 @@
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
       <c r="AG5" s="12"/>
-      <c r="AH5" s="133"/>
-      <c r="AI5" s="134"/>
-      <c r="AJ5" s="134"/>
-      <c r="AK5" s="135"/>
+      <c r="AH5" s="144"/>
+      <c r="AI5" s="145"/>
+      <c r="AJ5" s="145"/>
+      <c r="AK5" s="146"/>
       <c r="AN5" s="3"/>
       <c r="AO5" s="3"/>
       <c r="AP5" s="3"/>
@@ -4736,12 +4718,12 @@
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
-      <c r="T6" s="125"/>
-      <c r="U6" s="124"/>
-      <c r="V6" s="124"/>
-      <c r="W6" s="129"/>
-      <c r="X6" s="129"/>
-      <c r="Y6" s="130"/>
+      <c r="T6" s="169"/>
+      <c r="U6" s="168"/>
+      <c r="V6" s="168"/>
+      <c r="W6" s="140"/>
+      <c r="X6" s="140"/>
+      <c r="Y6" s="141"/>
       <c r="Z6" s="11"/>
       <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
@@ -4750,10 +4732,10 @@
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
       <c r="AG6" s="12"/>
-      <c r="AH6" s="133"/>
-      <c r="AI6" s="134"/>
-      <c r="AJ6" s="134"/>
-      <c r="AK6" s="135"/>
+      <c r="AH6" s="144"/>
+      <c r="AI6" s="145"/>
+      <c r="AJ6" s="145"/>
+      <c r="AK6" s="146"/>
       <c r="AN6" s="3"/>
       <c r="AO6" s="3"/>
       <c r="AP6" s="3"/>
@@ -4985,12 +4967,12 @@
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
-      <c r="T7" s="126"/>
-      <c r="U7" s="127"/>
-      <c r="V7" s="127"/>
-      <c r="W7" s="131"/>
-      <c r="X7" s="131"/>
-      <c r="Y7" s="132"/>
+      <c r="T7" s="170"/>
+      <c r="U7" s="171"/>
+      <c r="V7" s="171"/>
+      <c r="W7" s="142"/>
+      <c r="X7" s="142"/>
+      <c r="Y7" s="143"/>
       <c r="Z7" s="21"/>
       <c r="AA7" s="22"/>
       <c r="AB7" s="22"/>
@@ -4999,10 +4981,10 @@
       <c r="AE7" s="22"/>
       <c r="AF7" s="22"/>
       <c r="AG7" s="23"/>
-      <c r="AH7" s="136"/>
-      <c r="AI7" s="137"/>
-      <c r="AJ7" s="137"/>
-      <c r="AK7" s="138"/>
+      <c r="AH7" s="147"/>
+      <c r="AI7" s="148"/>
+      <c r="AJ7" s="148"/>
+      <c r="AK7" s="149"/>
       <c r="AL7" s="86"/>
       <c r="AN7" s="3"/>
       <c r="AO7" s="3"/>
@@ -5663,7 +5645,7 @@
         <f t="shared" si="1"/>
         <v>46233</v>
       </c>
-      <c r="AK9" s="193">
+      <c r="AK9" s="116">
         <f t="shared" si="1"/>
         <v>46234</v>
       </c>
@@ -5885,8 +5867,8 @@
     </row>
     <row r="10" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A10" s="29"/>
-      <c r="B10" s="139"/>
-      <c r="C10" s="140"/>
+      <c r="B10" s="150"/>
+      <c r="C10" s="151"/>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="31" t="s">
@@ -6234,46 +6216,46 @@
     </row>
     <row r="11" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A11" s="34"/>
-      <c r="B11" s="117" t="s">
+      <c r="B11" s="164" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="118"/>
+      <c r="C11" s="165"/>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
       <c r="F11" s="102" t="s">
         <v>122</v>
       </c>
-      <c r="G11" s="181"/>
-      <c r="H11" s="181"/>
-      <c r="I11" s="181"/>
-      <c r="J11" s="181"/>
-      <c r="K11" s="181"/>
-      <c r="L11" s="181"/>
-      <c r="M11" s="181"/>
-      <c r="N11" s="181"/>
-      <c r="O11" s="181"/>
-      <c r="P11" s="181"/>
-      <c r="Q11" s="181"/>
-      <c r="R11" s="181"/>
-      <c r="S11" s="181"/>
-      <c r="T11" s="181"/>
-      <c r="U11" s="181"/>
-      <c r="V11" s="181"/>
-      <c r="W11" s="181"/>
-      <c r="X11" s="181"/>
-      <c r="Y11" s="181"/>
-      <c r="Z11" s="181"/>
-      <c r="AA11" s="181"/>
-      <c r="AB11" s="181"/>
-      <c r="AC11" s="181"/>
-      <c r="AD11" s="181"/>
-      <c r="AE11" s="181"/>
-      <c r="AF11" s="181"/>
-      <c r="AG11" s="181"/>
-      <c r="AH11" s="181"/>
-      <c r="AI11" s="181"/>
-      <c r="AJ11" s="181"/>
-      <c r="AK11" s="182"/>
+      <c r="G11" s="104"/>
+      <c r="H11" s="104"/>
+      <c r="I11" s="104"/>
+      <c r="J11" s="104"/>
+      <c r="K11" s="104"/>
+      <c r="L11" s="104"/>
+      <c r="M11" s="104"/>
+      <c r="N11" s="104"/>
+      <c r="O11" s="104"/>
+      <c r="P11" s="104"/>
+      <c r="Q11" s="104"/>
+      <c r="R11" s="104"/>
+      <c r="S11" s="104"/>
+      <c r="T11" s="104"/>
+      <c r="U11" s="104"/>
+      <c r="V11" s="104"/>
+      <c r="W11" s="104"/>
+      <c r="X11" s="104"/>
+      <c r="Y11" s="104"/>
+      <c r="Z11" s="104"/>
+      <c r="AA11" s="104"/>
+      <c r="AB11" s="104"/>
+      <c r="AC11" s="104"/>
+      <c r="AD11" s="104"/>
+      <c r="AE11" s="104"/>
+      <c r="AF11" s="104"/>
+      <c r="AG11" s="104"/>
+      <c r="AH11" s="104"/>
+      <c r="AI11" s="104"/>
+      <c r="AJ11" s="104"/>
+      <c r="AK11" s="105"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
@@ -6494,50 +6476,50 @@
       <c r="A12" s="99">
         <v>1</v>
       </c>
-      <c r="B12" s="104" t="s">
+      <c r="B12" s="117" t="s">
         <v>119</v>
       </c>
-      <c r="C12" s="105"/>
+      <c r="C12" s="118"/>
       <c r="D12" s="92" t="s">
         <v>99</v>
       </c>
       <c r="E12" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="158" t="s">
+      <c r="F12" s="124" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="183"/>
-      <c r="H12" s="183"/>
-      <c r="I12" s="183"/>
-      <c r="J12" s="183"/>
-      <c r="K12" s="183"/>
-      <c r="L12" s="183"/>
-      <c r="M12" s="183"/>
-      <c r="N12" s="183"/>
-      <c r="O12" s="183"/>
-      <c r="P12" s="183"/>
-      <c r="Q12" s="183"/>
-      <c r="R12" s="183"/>
-      <c r="S12" s="183"/>
-      <c r="T12" s="183"/>
-      <c r="U12" s="183"/>
-      <c r="V12" s="183"/>
-      <c r="W12" s="183"/>
-      <c r="X12" s="183"/>
-      <c r="Y12" s="183"/>
-      <c r="Z12" s="183"/>
-      <c r="AA12" s="183"/>
-      <c r="AB12" s="183"/>
-      <c r="AC12" s="183"/>
-      <c r="AD12" s="183"/>
-      <c r="AE12" s="183"/>
-      <c r="AF12" s="183"/>
-      <c r="AG12" s="183"/>
-      <c r="AH12" s="183"/>
-      <c r="AI12" s="183"/>
-      <c r="AJ12" s="183"/>
-      <c r="AK12" s="184"/>
+      <c r="G12" s="106"/>
+      <c r="H12" s="106"/>
+      <c r="I12" s="106"/>
+      <c r="J12" s="106"/>
+      <c r="K12" s="106"/>
+      <c r="L12" s="106"/>
+      <c r="M12" s="106"/>
+      <c r="N12" s="106"/>
+      <c r="O12" s="106"/>
+      <c r="P12" s="106"/>
+      <c r="Q12" s="106"/>
+      <c r="R12" s="106"/>
+      <c r="S12" s="106"/>
+      <c r="T12" s="106"/>
+      <c r="U12" s="106"/>
+      <c r="V12" s="106"/>
+      <c r="W12" s="106"/>
+      <c r="X12" s="106"/>
+      <c r="Y12" s="106"/>
+      <c r="Z12" s="106"/>
+      <c r="AA12" s="106"/>
+      <c r="AB12" s="106"/>
+      <c r="AC12" s="106"/>
+      <c r="AD12" s="106"/>
+      <c r="AE12" s="106"/>
+      <c r="AF12" s="106"/>
+      <c r="AG12" s="106"/>
+      <c r="AH12" s="106"/>
+      <c r="AI12" s="106"/>
+      <c r="AJ12" s="106"/>
+      <c r="AK12" s="107"/>
       <c r="AN12" s="3"/>
       <c r="AO12" s="3"/>
       <c r="AP12" s="3"/>
@@ -6758,46 +6740,46 @@
       <c r="A13" s="99">
         <v>2</v>
       </c>
-      <c r="B13" s="104" t="s">
+      <c r="B13" s="117" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="105"/>
+      <c r="C13" s="118"/>
       <c r="D13" s="92" t="s">
         <v>99</v>
       </c>
       <c r="E13" s="92"/>
-      <c r="F13" s="106"/>
-      <c r="G13" s="183"/>
-      <c r="H13" s="183"/>
-      <c r="I13" s="183"/>
-      <c r="J13" s="183"/>
-      <c r="K13" s="183"/>
-      <c r="L13" s="183"/>
-      <c r="M13" s="183"/>
-      <c r="N13" s="183"/>
-      <c r="O13" s="183"/>
-      <c r="P13" s="183"/>
-      <c r="Q13" s="183"/>
-      <c r="R13" s="183"/>
-      <c r="S13" s="183"/>
-      <c r="T13" s="183"/>
-      <c r="U13" s="183"/>
-      <c r="V13" s="183"/>
-      <c r="W13" s="183"/>
-      <c r="X13" s="183"/>
-      <c r="Y13" s="183"/>
-      <c r="Z13" s="183"/>
-      <c r="AA13" s="183"/>
-      <c r="AB13" s="183"/>
-      <c r="AC13" s="183"/>
-      <c r="AD13" s="183"/>
-      <c r="AE13" s="183"/>
-      <c r="AF13" s="183"/>
-      <c r="AG13" s="183"/>
-      <c r="AH13" s="183"/>
-      <c r="AI13" s="183"/>
-      <c r="AJ13" s="183"/>
-      <c r="AK13" s="184"/>
+      <c r="F13" s="125"/>
+      <c r="G13" s="106"/>
+      <c r="H13" s="106"/>
+      <c r="I13" s="106"/>
+      <c r="J13" s="106"/>
+      <c r="K13" s="106"/>
+      <c r="L13" s="106"/>
+      <c r="M13" s="106"/>
+      <c r="N13" s="106"/>
+      <c r="O13" s="106"/>
+      <c r="P13" s="106"/>
+      <c r="Q13" s="106"/>
+      <c r="R13" s="106"/>
+      <c r="S13" s="106"/>
+      <c r="T13" s="106"/>
+      <c r="U13" s="106"/>
+      <c r="V13" s="106"/>
+      <c r="W13" s="106"/>
+      <c r="X13" s="106"/>
+      <c r="Y13" s="106"/>
+      <c r="Z13" s="106"/>
+      <c r="AA13" s="106"/>
+      <c r="AB13" s="106"/>
+      <c r="AC13" s="106"/>
+      <c r="AD13" s="106"/>
+      <c r="AE13" s="106"/>
+      <c r="AF13" s="106"/>
+      <c r="AG13" s="106"/>
+      <c r="AH13" s="106"/>
+      <c r="AI13" s="106"/>
+      <c r="AJ13" s="106"/>
+      <c r="AK13" s="107"/>
       <c r="AN13" s="3"/>
       <c r="AO13" s="3"/>
       <c r="AP13" s="3"/>
@@ -7018,48 +7000,48 @@
       <c r="A14" s="99">
         <v>3</v>
       </c>
-      <c r="B14" s="104" t="s">
+      <c r="B14" s="117" t="s">
         <v>130</v>
       </c>
-      <c r="C14" s="105"/>
+      <c r="C14" s="118"/>
       <c r="D14" s="92" t="s">
         <v>99</v>
       </c>
       <c r="E14" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="106"/>
-      <c r="G14" s="183"/>
-      <c r="H14" s="183"/>
-      <c r="I14" s="183"/>
-      <c r="J14" s="183"/>
-      <c r="K14" s="183"/>
-      <c r="L14" s="183"/>
-      <c r="M14" s="183"/>
-      <c r="N14" s="183"/>
-      <c r="O14" s="183"/>
-      <c r="P14" s="183"/>
-      <c r="Q14" s="183"/>
-      <c r="R14" s="183"/>
-      <c r="S14" s="183"/>
-      <c r="T14" s="183"/>
-      <c r="U14" s="183"/>
-      <c r="V14" s="183"/>
-      <c r="W14" s="183"/>
-      <c r="X14" s="183"/>
-      <c r="Y14" s="183"/>
-      <c r="Z14" s="183"/>
-      <c r="AA14" s="183"/>
-      <c r="AB14" s="183"/>
-      <c r="AC14" s="183"/>
-      <c r="AD14" s="183"/>
-      <c r="AE14" s="183"/>
-      <c r="AF14" s="183"/>
-      <c r="AG14" s="183"/>
-      <c r="AH14" s="183"/>
-      <c r="AI14" s="183"/>
-      <c r="AJ14" s="183"/>
-      <c r="AK14" s="184"/>
+      <c r="F14" s="125"/>
+      <c r="G14" s="106"/>
+      <c r="H14" s="106"/>
+      <c r="I14" s="106"/>
+      <c r="J14" s="106"/>
+      <c r="K14" s="106"/>
+      <c r="L14" s="106"/>
+      <c r="M14" s="106"/>
+      <c r="N14" s="106"/>
+      <c r="O14" s="106"/>
+      <c r="P14" s="106"/>
+      <c r="Q14" s="106"/>
+      <c r="R14" s="106"/>
+      <c r="S14" s="106"/>
+      <c r="T14" s="106"/>
+      <c r="U14" s="106"/>
+      <c r="V14" s="106"/>
+      <c r="W14" s="106"/>
+      <c r="X14" s="106"/>
+      <c r="Y14" s="106"/>
+      <c r="Z14" s="106"/>
+      <c r="AA14" s="106"/>
+      <c r="AB14" s="106"/>
+      <c r="AC14" s="106"/>
+      <c r="AD14" s="106"/>
+      <c r="AE14" s="106"/>
+      <c r="AF14" s="106"/>
+      <c r="AG14" s="106"/>
+      <c r="AH14" s="106"/>
+      <c r="AI14" s="106"/>
+      <c r="AJ14" s="106"/>
+      <c r="AK14" s="107"/>
       <c r="AN14" s="3"/>
       <c r="AO14" s="3"/>
       <c r="AP14" s="3"/>
@@ -7280,48 +7262,48 @@
       <c r="A15" s="99">
         <v>4</v>
       </c>
-      <c r="B15" s="104" t="s">
+      <c r="B15" s="117" t="s">
         <v>131</v>
       </c>
-      <c r="C15" s="105"/>
+      <c r="C15" s="118"/>
       <c r="D15" s="92" t="s">
         <v>99</v>
       </c>
       <c r="E15" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="106"/>
-      <c r="G15" s="183"/>
-      <c r="H15" s="183"/>
-      <c r="I15" s="183"/>
-      <c r="J15" s="183"/>
-      <c r="K15" s="183"/>
-      <c r="L15" s="183"/>
-      <c r="M15" s="183"/>
-      <c r="N15" s="183"/>
-      <c r="O15" s="183"/>
-      <c r="P15" s="183"/>
-      <c r="Q15" s="183"/>
-      <c r="R15" s="183"/>
-      <c r="S15" s="183"/>
-      <c r="T15" s="183"/>
-      <c r="U15" s="183"/>
-      <c r="V15" s="183"/>
-      <c r="W15" s="183"/>
-      <c r="X15" s="183"/>
-      <c r="Y15" s="183"/>
-      <c r="Z15" s="183"/>
-      <c r="AA15" s="183"/>
-      <c r="AB15" s="183"/>
-      <c r="AC15" s="183"/>
-      <c r="AD15" s="183"/>
-      <c r="AE15" s="183"/>
-      <c r="AF15" s="183"/>
-      <c r="AG15" s="183"/>
-      <c r="AH15" s="183"/>
-      <c r="AI15" s="183"/>
-      <c r="AJ15" s="183"/>
-      <c r="AK15" s="184"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="106"/>
+      <c r="H15" s="106"/>
+      <c r="I15" s="106"/>
+      <c r="J15" s="106"/>
+      <c r="K15" s="106"/>
+      <c r="L15" s="106"/>
+      <c r="M15" s="106"/>
+      <c r="N15" s="106"/>
+      <c r="O15" s="106"/>
+      <c r="P15" s="106"/>
+      <c r="Q15" s="106"/>
+      <c r="R15" s="106"/>
+      <c r="S15" s="106"/>
+      <c r="T15" s="106"/>
+      <c r="U15" s="106"/>
+      <c r="V15" s="106"/>
+      <c r="W15" s="106"/>
+      <c r="X15" s="106"/>
+      <c r="Y15" s="106"/>
+      <c r="Z15" s="106"/>
+      <c r="AA15" s="106"/>
+      <c r="AB15" s="106"/>
+      <c r="AC15" s="106"/>
+      <c r="AD15" s="106"/>
+      <c r="AE15" s="106"/>
+      <c r="AF15" s="106"/>
+      <c r="AG15" s="106"/>
+      <c r="AH15" s="106"/>
+      <c r="AI15" s="106"/>
+      <c r="AJ15" s="106"/>
+      <c r="AK15" s="107"/>
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
       <c r="AP15" s="3"/>
@@ -7542,48 +7524,48 @@
       <c r="A16" s="99">
         <v>5</v>
       </c>
-      <c r="B16" s="104" t="s">
+      <c r="B16" s="117" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="105"/>
+      <c r="C16" s="118"/>
       <c r="D16" s="92" t="s">
         <v>133</v>
       </c>
       <c r="E16" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="106"/>
-      <c r="G16" s="183"/>
-      <c r="H16" s="183"/>
-      <c r="I16" s="183"/>
-      <c r="J16" s="183"/>
-      <c r="K16" s="183"/>
-      <c r="L16" s="183"/>
-      <c r="M16" s="183"/>
-      <c r="N16" s="183"/>
-      <c r="O16" s="183"/>
-      <c r="P16" s="183"/>
-      <c r="Q16" s="183"/>
-      <c r="R16" s="183"/>
-      <c r="S16" s="183"/>
-      <c r="T16" s="183"/>
-      <c r="U16" s="183"/>
-      <c r="V16" s="183"/>
-      <c r="W16" s="183"/>
-      <c r="X16" s="183"/>
-      <c r="Y16" s="183"/>
-      <c r="Z16" s="183"/>
-      <c r="AA16" s="183"/>
-      <c r="AB16" s="183"/>
-      <c r="AC16" s="183"/>
-      <c r="AD16" s="183"/>
-      <c r="AE16" s="183"/>
-      <c r="AF16" s="183"/>
-      <c r="AG16" s="183"/>
-      <c r="AH16" s="183"/>
-      <c r="AI16" s="183"/>
-      <c r="AJ16" s="183"/>
-      <c r="AK16" s="184"/>
+      <c r="F16" s="125"/>
+      <c r="G16" s="106"/>
+      <c r="H16" s="106"/>
+      <c r="I16" s="106"/>
+      <c r="J16" s="106"/>
+      <c r="K16" s="106"/>
+      <c r="L16" s="106"/>
+      <c r="M16" s="106"/>
+      <c r="N16" s="106"/>
+      <c r="O16" s="106"/>
+      <c r="P16" s="106"/>
+      <c r="Q16" s="106"/>
+      <c r="R16" s="106"/>
+      <c r="S16" s="106"/>
+      <c r="T16" s="106"/>
+      <c r="U16" s="106"/>
+      <c r="V16" s="106"/>
+      <c r="W16" s="106"/>
+      <c r="X16" s="106"/>
+      <c r="Y16" s="106"/>
+      <c r="Z16" s="106"/>
+      <c r="AA16" s="106"/>
+      <c r="AB16" s="106"/>
+      <c r="AC16" s="106"/>
+      <c r="AD16" s="106"/>
+      <c r="AE16" s="106"/>
+      <c r="AF16" s="106"/>
+      <c r="AG16" s="106"/>
+      <c r="AH16" s="106"/>
+      <c r="AI16" s="106"/>
+      <c r="AJ16" s="106"/>
+      <c r="AK16" s="107"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
@@ -7804,48 +7786,48 @@
       <c r="A17" s="99">
         <v>6</v>
       </c>
-      <c r="B17" s="104" t="s">
+      <c r="B17" s="117" t="s">
         <v>134</v>
       </c>
-      <c r="C17" s="105"/>
+      <c r="C17" s="118"/>
       <c r="D17" s="92" t="s">
         <v>99</v>
       </c>
       <c r="E17" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="106"/>
-      <c r="G17" s="183"/>
-      <c r="H17" s="183"/>
-      <c r="I17" s="183"/>
-      <c r="J17" s="183"/>
-      <c r="K17" s="183"/>
-      <c r="L17" s="183"/>
-      <c r="M17" s="183"/>
-      <c r="N17" s="183"/>
-      <c r="O17" s="183"/>
-      <c r="P17" s="183"/>
-      <c r="Q17" s="183"/>
-      <c r="R17" s="183"/>
-      <c r="S17" s="183"/>
-      <c r="T17" s="183"/>
-      <c r="U17" s="183"/>
-      <c r="V17" s="183"/>
-      <c r="W17" s="183"/>
-      <c r="X17" s="183"/>
-      <c r="Y17" s="183"/>
-      <c r="Z17" s="183"/>
-      <c r="AA17" s="183"/>
-      <c r="AB17" s="183"/>
-      <c r="AC17" s="183"/>
-      <c r="AD17" s="183"/>
-      <c r="AE17" s="183"/>
-      <c r="AF17" s="183"/>
-      <c r="AG17" s="183"/>
-      <c r="AH17" s="183"/>
-      <c r="AI17" s="183"/>
-      <c r="AJ17" s="183"/>
-      <c r="AK17" s="184"/>
+      <c r="F17" s="125"/>
+      <c r="G17" s="106"/>
+      <c r="H17" s="106"/>
+      <c r="I17" s="106"/>
+      <c r="J17" s="106"/>
+      <c r="K17" s="106"/>
+      <c r="L17" s="106"/>
+      <c r="M17" s="106"/>
+      <c r="N17" s="106"/>
+      <c r="O17" s="106"/>
+      <c r="P17" s="106"/>
+      <c r="Q17" s="106"/>
+      <c r="R17" s="106"/>
+      <c r="S17" s="106"/>
+      <c r="T17" s="106"/>
+      <c r="U17" s="106"/>
+      <c r="V17" s="106"/>
+      <c r="W17" s="106"/>
+      <c r="X17" s="106"/>
+      <c r="Y17" s="106"/>
+      <c r="Z17" s="106"/>
+      <c r="AA17" s="106"/>
+      <c r="AB17" s="106"/>
+      <c r="AC17" s="106"/>
+      <c r="AD17" s="106"/>
+      <c r="AE17" s="106"/>
+      <c r="AF17" s="106"/>
+      <c r="AG17" s="106"/>
+      <c r="AH17" s="106"/>
+      <c r="AI17" s="106"/>
+      <c r="AJ17" s="106"/>
+      <c r="AK17" s="107"/>
       <c r="AN17" s="3"/>
       <c r="AO17" s="3"/>
       <c r="AP17" s="3"/>
@@ -8066,48 +8048,48 @@
       <c r="A18" s="99">
         <v>7</v>
       </c>
-      <c r="B18" s="104" t="s">
+      <c r="B18" s="117" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="105"/>
+      <c r="C18" s="118"/>
       <c r="D18" s="92" t="s">
         <v>99</v>
       </c>
       <c r="E18" s="92" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="106"/>
-      <c r="G18" s="183"/>
-      <c r="H18" s="183"/>
-      <c r="I18" s="183"/>
-      <c r="J18" s="183"/>
-      <c r="K18" s="183"/>
-      <c r="L18" s="183"/>
-      <c r="M18" s="183"/>
-      <c r="N18" s="183"/>
-      <c r="O18" s="183"/>
-      <c r="P18" s="183"/>
-      <c r="Q18" s="183"/>
-      <c r="R18" s="183"/>
-      <c r="S18" s="183"/>
-      <c r="T18" s="183"/>
-      <c r="U18" s="183"/>
-      <c r="V18" s="183"/>
-      <c r="W18" s="183"/>
-      <c r="X18" s="183"/>
-      <c r="Y18" s="183"/>
-      <c r="Z18" s="183"/>
-      <c r="AA18" s="183"/>
-      <c r="AB18" s="183"/>
-      <c r="AC18" s="183"/>
-      <c r="AD18" s="183"/>
-      <c r="AE18" s="183"/>
-      <c r="AF18" s="183"/>
-      <c r="AG18" s="183"/>
-      <c r="AH18" s="183"/>
-      <c r="AI18" s="183"/>
-      <c r="AJ18" s="183"/>
-      <c r="AK18" s="184"/>
+      <c r="F18" s="125"/>
+      <c r="G18" s="106"/>
+      <c r="H18" s="106"/>
+      <c r="I18" s="106"/>
+      <c r="J18" s="106"/>
+      <c r="K18" s="106"/>
+      <c r="L18" s="106"/>
+      <c r="M18" s="106"/>
+      <c r="N18" s="106"/>
+      <c r="O18" s="106"/>
+      <c r="P18" s="106"/>
+      <c r="Q18" s="106"/>
+      <c r="R18" s="106"/>
+      <c r="S18" s="106"/>
+      <c r="T18" s="106"/>
+      <c r="U18" s="106"/>
+      <c r="V18" s="106"/>
+      <c r="W18" s="106"/>
+      <c r="X18" s="106"/>
+      <c r="Y18" s="106"/>
+      <c r="Z18" s="106"/>
+      <c r="AA18" s="106"/>
+      <c r="AB18" s="106"/>
+      <c r="AC18" s="106"/>
+      <c r="AD18" s="106"/>
+      <c r="AE18" s="106"/>
+      <c r="AF18" s="106"/>
+      <c r="AG18" s="106"/>
+      <c r="AH18" s="106"/>
+      <c r="AI18" s="106"/>
+      <c r="AJ18" s="106"/>
+      <c r="AK18" s="107"/>
       <c r="AN18" s="3"/>
       <c r="AO18" s="3"/>
       <c r="AP18" s="3"/>
@@ -8328,48 +8310,48 @@
       <c r="A19" s="99">
         <v>8</v>
       </c>
-      <c r="B19" s="104" t="s">
+      <c r="B19" s="117" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="105"/>
+      <c r="C19" s="118"/>
       <c r="D19" s="92" t="s">
         <v>99</v>
       </c>
       <c r="E19" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="F19" s="106"/>
-      <c r="G19" s="183"/>
-      <c r="H19" s="183"/>
-      <c r="I19" s="183"/>
-      <c r="J19" s="183"/>
-      <c r="K19" s="183"/>
-      <c r="L19" s="183"/>
-      <c r="M19" s="183"/>
-      <c r="N19" s="183"/>
-      <c r="O19" s="183"/>
-      <c r="P19" s="183"/>
-      <c r="Q19" s="183"/>
-      <c r="R19" s="183"/>
-      <c r="S19" s="183"/>
-      <c r="T19" s="183"/>
-      <c r="U19" s="183"/>
-      <c r="V19" s="183"/>
-      <c r="W19" s="183"/>
-      <c r="X19" s="183"/>
-      <c r="Y19" s="183"/>
-      <c r="Z19" s="183"/>
-      <c r="AA19" s="183"/>
-      <c r="AB19" s="183"/>
-      <c r="AC19" s="183"/>
-      <c r="AD19" s="183"/>
-      <c r="AE19" s="183"/>
-      <c r="AF19" s="183"/>
-      <c r="AG19" s="183"/>
-      <c r="AH19" s="183"/>
-      <c r="AI19" s="183"/>
-      <c r="AJ19" s="183"/>
-      <c r="AK19" s="184"/>
+      <c r="F19" s="125"/>
+      <c r="G19" s="106"/>
+      <c r="H19" s="106"/>
+      <c r="I19" s="106"/>
+      <c r="J19" s="106"/>
+      <c r="K19" s="106"/>
+      <c r="L19" s="106"/>
+      <c r="M19" s="106"/>
+      <c r="N19" s="106"/>
+      <c r="O19" s="106"/>
+      <c r="P19" s="106"/>
+      <c r="Q19" s="106"/>
+      <c r="R19" s="106"/>
+      <c r="S19" s="106"/>
+      <c r="T19" s="106"/>
+      <c r="U19" s="106"/>
+      <c r="V19" s="106"/>
+      <c r="W19" s="106"/>
+      <c r="X19" s="106"/>
+      <c r="Y19" s="106"/>
+      <c r="Z19" s="106"/>
+      <c r="AA19" s="106"/>
+      <c r="AB19" s="106"/>
+      <c r="AC19" s="106"/>
+      <c r="AD19" s="106"/>
+      <c r="AE19" s="106"/>
+      <c r="AF19" s="106"/>
+      <c r="AG19" s="106"/>
+      <c r="AH19" s="106"/>
+      <c r="AI19" s="106"/>
+      <c r="AJ19" s="106"/>
+      <c r="AK19" s="107"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
@@ -8590,48 +8572,48 @@
       <c r="A20" s="99">
         <v>9</v>
       </c>
-      <c r="B20" s="104" t="s">
+      <c r="B20" s="117" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="105"/>
+      <c r="C20" s="118"/>
       <c r="D20" s="92" t="s">
         <v>99</v>
       </c>
       <c r="E20" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="F20" s="106"/>
-      <c r="G20" s="183"/>
-      <c r="H20" s="183"/>
-      <c r="I20" s="183"/>
-      <c r="J20" s="183"/>
-      <c r="K20" s="183"/>
-      <c r="L20" s="183"/>
-      <c r="M20" s="183"/>
-      <c r="N20" s="183"/>
-      <c r="O20" s="183"/>
-      <c r="P20" s="183"/>
-      <c r="Q20" s="183"/>
-      <c r="R20" s="183"/>
-      <c r="S20" s="183"/>
-      <c r="T20" s="183"/>
-      <c r="U20" s="183"/>
-      <c r="V20" s="183"/>
-      <c r="W20" s="183"/>
-      <c r="X20" s="183"/>
-      <c r="Y20" s="183"/>
-      <c r="Z20" s="183"/>
-      <c r="AA20" s="183"/>
-      <c r="AB20" s="183"/>
-      <c r="AC20" s="183"/>
-      <c r="AD20" s="183"/>
-      <c r="AE20" s="183"/>
-      <c r="AF20" s="183"/>
-      <c r="AG20" s="183"/>
-      <c r="AH20" s="183"/>
-      <c r="AI20" s="183"/>
-      <c r="AJ20" s="183"/>
-      <c r="AK20" s="184"/>
+      <c r="F20" s="125"/>
+      <c r="G20" s="106"/>
+      <c r="H20" s="106"/>
+      <c r="I20" s="106"/>
+      <c r="J20" s="106"/>
+      <c r="K20" s="106"/>
+      <c r="L20" s="106"/>
+      <c r="M20" s="106"/>
+      <c r="N20" s="106"/>
+      <c r="O20" s="106"/>
+      <c r="P20" s="106"/>
+      <c r="Q20" s="106"/>
+      <c r="R20" s="106"/>
+      <c r="S20" s="106"/>
+      <c r="T20" s="106"/>
+      <c r="U20" s="106"/>
+      <c r="V20" s="106"/>
+      <c r="W20" s="106"/>
+      <c r="X20" s="106"/>
+      <c r="Y20" s="106"/>
+      <c r="Z20" s="106"/>
+      <c r="AA20" s="106"/>
+      <c r="AB20" s="106"/>
+      <c r="AC20" s="106"/>
+      <c r="AD20" s="106"/>
+      <c r="AE20" s="106"/>
+      <c r="AF20" s="106"/>
+      <c r="AG20" s="106"/>
+      <c r="AH20" s="106"/>
+      <c r="AI20" s="106"/>
+      <c r="AJ20" s="106"/>
+      <c r="AK20" s="107"/>
       <c r="AN20" s="3"/>
       <c r="AO20" s="3"/>
       <c r="AP20" s="3"/>
@@ -8852,46 +8834,46 @@
       <c r="A21" s="99">
         <v>10</v>
       </c>
-      <c r="B21" s="104" t="s">
+      <c r="B21" s="117" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="105"/>
+      <c r="C21" s="118"/>
       <c r="D21" s="92" t="s">
         <v>100</v>
       </c>
       <c r="E21" s="92"/>
-      <c r="F21" s="106"/>
-      <c r="G21" s="183"/>
-      <c r="H21" s="183"/>
-      <c r="I21" s="183"/>
-      <c r="J21" s="183"/>
-      <c r="K21" s="183"/>
-      <c r="L21" s="183"/>
-      <c r="M21" s="183"/>
-      <c r="N21" s="183"/>
-      <c r="O21" s="183"/>
-      <c r="P21" s="183"/>
-      <c r="Q21" s="183"/>
-      <c r="R21" s="183"/>
-      <c r="S21" s="183"/>
-      <c r="T21" s="183"/>
-      <c r="U21" s="183"/>
-      <c r="V21" s="183"/>
-      <c r="W21" s="183"/>
-      <c r="X21" s="183"/>
-      <c r="Y21" s="183"/>
-      <c r="Z21" s="183"/>
-      <c r="AA21" s="183"/>
-      <c r="AB21" s="183"/>
-      <c r="AC21" s="183"/>
-      <c r="AD21" s="183"/>
-      <c r="AE21" s="183"/>
-      <c r="AF21" s="183"/>
-      <c r="AG21" s="183"/>
-      <c r="AH21" s="183"/>
-      <c r="AI21" s="183"/>
-      <c r="AJ21" s="183"/>
-      <c r="AK21" s="184"/>
+      <c r="F21" s="125"/>
+      <c r="G21" s="106"/>
+      <c r="H21" s="106"/>
+      <c r="I21" s="106"/>
+      <c r="J21" s="106"/>
+      <c r="K21" s="106"/>
+      <c r="L21" s="106"/>
+      <c r="M21" s="106"/>
+      <c r="N21" s="106"/>
+      <c r="O21" s="106"/>
+      <c r="P21" s="106"/>
+      <c r="Q21" s="106"/>
+      <c r="R21" s="106"/>
+      <c r="S21" s="106"/>
+      <c r="T21" s="106"/>
+      <c r="U21" s="106"/>
+      <c r="V21" s="106"/>
+      <c r="W21" s="106"/>
+      <c r="X21" s="106"/>
+      <c r="Y21" s="106"/>
+      <c r="Z21" s="106"/>
+      <c r="AA21" s="106"/>
+      <c r="AB21" s="106"/>
+      <c r="AC21" s="106"/>
+      <c r="AD21" s="106"/>
+      <c r="AE21" s="106"/>
+      <c r="AF21" s="106"/>
+      <c r="AG21" s="106"/>
+      <c r="AH21" s="106"/>
+      <c r="AI21" s="106"/>
+      <c r="AJ21" s="106"/>
+      <c r="AK21" s="107"/>
       <c r="AN21" s="3"/>
       <c r="AO21" s="3"/>
       <c r="AP21" s="3"/>
@@ -9112,48 +9094,48 @@
       <c r="A22" s="99">
         <v>11</v>
       </c>
-      <c r="B22" s="104" t="s">
+      <c r="B22" s="117" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="105"/>
+      <c r="C22" s="118"/>
       <c r="D22" s="92" t="s">
         <v>38</v>
       </c>
       <c r="E22" s="92"/>
-      <c r="F22" s="106" t="s">
+      <c r="F22" s="125" t="s">
         <v>135</v>
       </c>
-      <c r="G22" s="183"/>
-      <c r="H22" s="183"/>
-      <c r="I22" s="183"/>
-      <c r="J22" s="183"/>
-      <c r="K22" s="183"/>
-      <c r="L22" s="183"/>
-      <c r="M22" s="183"/>
-      <c r="N22" s="183"/>
-      <c r="O22" s="183"/>
-      <c r="P22" s="183"/>
-      <c r="Q22" s="183"/>
-      <c r="R22" s="183"/>
-      <c r="S22" s="183"/>
-      <c r="T22" s="183"/>
-      <c r="U22" s="183"/>
-      <c r="V22" s="183"/>
-      <c r="W22" s="183"/>
-      <c r="X22" s="183"/>
-      <c r="Y22" s="183"/>
-      <c r="Z22" s="183"/>
-      <c r="AA22" s="183"/>
-      <c r="AB22" s="183"/>
-      <c r="AC22" s="183"/>
-      <c r="AD22" s="183"/>
-      <c r="AE22" s="183"/>
-      <c r="AF22" s="183"/>
-      <c r="AG22" s="183"/>
-      <c r="AH22" s="183"/>
-      <c r="AI22" s="183"/>
-      <c r="AJ22" s="183"/>
-      <c r="AK22" s="184"/>
+      <c r="G22" s="106"/>
+      <c r="H22" s="106"/>
+      <c r="I22" s="106"/>
+      <c r="J22" s="106"/>
+      <c r="K22" s="106"/>
+      <c r="L22" s="106"/>
+      <c r="M22" s="106"/>
+      <c r="N22" s="106"/>
+      <c r="O22" s="106"/>
+      <c r="P22" s="106"/>
+      <c r="Q22" s="106"/>
+      <c r="R22" s="106"/>
+      <c r="S22" s="106"/>
+      <c r="T22" s="106"/>
+      <c r="U22" s="106"/>
+      <c r="V22" s="106"/>
+      <c r="W22" s="106"/>
+      <c r="X22" s="106"/>
+      <c r="Y22" s="106"/>
+      <c r="Z22" s="106"/>
+      <c r="AA22" s="106"/>
+      <c r="AB22" s="106"/>
+      <c r="AC22" s="106"/>
+      <c r="AD22" s="106"/>
+      <c r="AE22" s="106"/>
+      <c r="AF22" s="106"/>
+      <c r="AG22" s="106"/>
+      <c r="AH22" s="106"/>
+      <c r="AI22" s="106"/>
+      <c r="AJ22" s="106"/>
+      <c r="AK22" s="107"/>
       <c r="AN22" s="3"/>
       <c r="AO22" s="3"/>
       <c r="AP22" s="3"/>
@@ -9374,48 +9356,48 @@
       <c r="A23" s="99">
         <v>13</v>
       </c>
-      <c r="B23" s="104" t="s">
+      <c r="B23" s="117" t="s">
         <v>132</v>
       </c>
-      <c r="C23" s="105"/>
+      <c r="C23" s="118"/>
       <c r="D23" s="92" t="s">
         <v>99</v>
       </c>
       <c r="E23" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="F23" s="107"/>
-      <c r="G23" s="181"/>
-      <c r="H23" s="181"/>
-      <c r="I23" s="181"/>
-      <c r="J23" s="181"/>
-      <c r="K23" s="181"/>
-      <c r="L23" s="181"/>
-      <c r="M23" s="181"/>
-      <c r="N23" s="181"/>
-      <c r="O23" s="181"/>
-      <c r="P23" s="181"/>
-      <c r="Q23" s="181"/>
-      <c r="R23" s="181"/>
-      <c r="S23" s="181"/>
-      <c r="T23" s="181"/>
-      <c r="U23" s="181"/>
-      <c r="V23" s="181"/>
-      <c r="W23" s="181"/>
-      <c r="X23" s="181"/>
-      <c r="Y23" s="181"/>
-      <c r="Z23" s="181"/>
-      <c r="AA23" s="181"/>
-      <c r="AB23" s="181"/>
-      <c r="AC23" s="181"/>
-      <c r="AD23" s="181"/>
-      <c r="AE23" s="181"/>
-      <c r="AF23" s="181"/>
-      <c r="AG23" s="181"/>
-      <c r="AH23" s="181"/>
-      <c r="AI23" s="181"/>
-      <c r="AJ23" s="181"/>
-      <c r="AK23" s="182"/>
+      <c r="F23" s="126"/>
+      <c r="G23" s="104"/>
+      <c r="H23" s="104"/>
+      <c r="I23" s="104"/>
+      <c r="J23" s="104"/>
+      <c r="K23" s="104"/>
+      <c r="L23" s="104"/>
+      <c r="M23" s="104"/>
+      <c r="N23" s="104"/>
+      <c r="O23" s="104"/>
+      <c r="P23" s="104"/>
+      <c r="Q23" s="104"/>
+      <c r="R23" s="104"/>
+      <c r="S23" s="104"/>
+      <c r="T23" s="104"/>
+      <c r="U23" s="104"/>
+      <c r="V23" s="104"/>
+      <c r="W23" s="104"/>
+      <c r="X23" s="104"/>
+      <c r="Y23" s="104"/>
+      <c r="Z23" s="104"/>
+      <c r="AA23" s="104"/>
+      <c r="AB23" s="104"/>
+      <c r="AC23" s="104"/>
+      <c r="AD23" s="104"/>
+      <c r="AE23" s="104"/>
+      <c r="AF23" s="104"/>
+      <c r="AG23" s="104"/>
+      <c r="AH23" s="104"/>
+      <c r="AI23" s="104"/>
+      <c r="AJ23" s="104"/>
+      <c r="AK23" s="105"/>
       <c r="AN23" s="3"/>
       <c r="AO23" s="3"/>
       <c r="AP23" s="3"/>
@@ -9636,10 +9618,10 @@
       <c r="A24" s="99">
         <v>12</v>
       </c>
-      <c r="B24" s="104" t="s">
+      <c r="B24" s="117" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="105"/>
+      <c r="C24" s="118"/>
       <c r="D24" s="92" t="s">
         <v>49</v>
       </c>
@@ -9649,37 +9631,37 @@
       <c r="F24" s="93" t="s">
         <v>39</v>
       </c>
-      <c r="G24" s="181"/>
-      <c r="H24" s="181"/>
-      <c r="I24" s="181"/>
-      <c r="J24" s="181"/>
-      <c r="K24" s="181"/>
-      <c r="L24" s="181"/>
-      <c r="M24" s="181"/>
-      <c r="N24" s="181"/>
-      <c r="O24" s="181"/>
-      <c r="P24" s="181"/>
-      <c r="Q24" s="181"/>
-      <c r="R24" s="181"/>
-      <c r="S24" s="181"/>
-      <c r="T24" s="181"/>
-      <c r="U24" s="181"/>
-      <c r="V24" s="181"/>
-      <c r="W24" s="181"/>
-      <c r="X24" s="181"/>
-      <c r="Y24" s="181"/>
-      <c r="Z24" s="181"/>
-      <c r="AA24" s="181"/>
-      <c r="AB24" s="181"/>
-      <c r="AC24" s="181"/>
-      <c r="AD24" s="181"/>
-      <c r="AE24" s="181"/>
-      <c r="AF24" s="181"/>
-      <c r="AG24" s="181"/>
-      <c r="AH24" s="181"/>
-      <c r="AI24" s="181"/>
-      <c r="AJ24" s="181"/>
-      <c r="AK24" s="182"/>
+      <c r="G24" s="104"/>
+      <c r="H24" s="104"/>
+      <c r="I24" s="104"/>
+      <c r="J24" s="104"/>
+      <c r="K24" s="104"/>
+      <c r="L24" s="104"/>
+      <c r="M24" s="104"/>
+      <c r="N24" s="104"/>
+      <c r="O24" s="104"/>
+      <c r="P24" s="104"/>
+      <c r="Q24" s="104"/>
+      <c r="R24" s="104"/>
+      <c r="S24" s="104"/>
+      <c r="T24" s="104"/>
+      <c r="U24" s="104"/>
+      <c r="V24" s="104"/>
+      <c r="W24" s="104"/>
+      <c r="X24" s="104"/>
+      <c r="Y24" s="104"/>
+      <c r="Z24" s="104"/>
+      <c r="AA24" s="104"/>
+      <c r="AB24" s="104"/>
+      <c r="AC24" s="104"/>
+      <c r="AD24" s="104"/>
+      <c r="AE24" s="104"/>
+      <c r="AF24" s="104"/>
+      <c r="AG24" s="104"/>
+      <c r="AH24" s="104"/>
+      <c r="AI24" s="104"/>
+      <c r="AJ24" s="104"/>
+      <c r="AK24" s="105"/>
       <c r="AN24" s="3"/>
       <c r="AO24" s="3"/>
       <c r="AP24" s="3"/>
@@ -9898,42 +9880,42 @@
     </row>
     <row r="25" spans="1:254" s="2" customFormat="1" ht="10" customHeight="1">
       <c r="A25" s="37"/>
-      <c r="B25" s="104"/>
-      <c r="C25" s="105"/>
+      <c r="B25" s="117"/>
+      <c r="C25" s="118"/>
       <c r="D25" s="92"/>
       <c r="E25" s="92"/>
       <c r="F25" s="36"/>
-      <c r="G25" s="181"/>
-      <c r="H25" s="181"/>
-      <c r="I25" s="181"/>
-      <c r="J25" s="181"/>
-      <c r="K25" s="181"/>
-      <c r="L25" s="181"/>
-      <c r="M25" s="181"/>
-      <c r="N25" s="181"/>
-      <c r="O25" s="181"/>
-      <c r="P25" s="181"/>
-      <c r="Q25" s="181"/>
-      <c r="R25" s="181"/>
-      <c r="S25" s="181"/>
-      <c r="T25" s="181"/>
-      <c r="U25" s="181"/>
-      <c r="V25" s="181"/>
-      <c r="W25" s="181"/>
-      <c r="X25" s="181"/>
-      <c r="Y25" s="181"/>
-      <c r="Z25" s="181"/>
-      <c r="AA25" s="181"/>
-      <c r="AB25" s="181"/>
-      <c r="AC25" s="181"/>
-      <c r="AD25" s="181"/>
-      <c r="AE25" s="181"/>
-      <c r="AF25" s="181"/>
-      <c r="AG25" s="181"/>
-      <c r="AH25" s="181"/>
-      <c r="AI25" s="181"/>
-      <c r="AJ25" s="181"/>
-      <c r="AK25" s="182"/>
+      <c r="G25" s="104"/>
+      <c r="H25" s="104"/>
+      <c r="I25" s="104"/>
+      <c r="J25" s="104"/>
+      <c r="K25" s="104"/>
+      <c r="L25" s="104"/>
+      <c r="M25" s="104"/>
+      <c r="N25" s="104"/>
+      <c r="O25" s="104"/>
+      <c r="P25" s="104"/>
+      <c r="Q25" s="104"/>
+      <c r="R25" s="104"/>
+      <c r="S25" s="104"/>
+      <c r="T25" s="104"/>
+      <c r="U25" s="104"/>
+      <c r="V25" s="104"/>
+      <c r="W25" s="104"/>
+      <c r="X25" s="104"/>
+      <c r="Y25" s="104"/>
+      <c r="Z25" s="104"/>
+      <c r="AA25" s="104"/>
+      <c r="AB25" s="104"/>
+      <c r="AC25" s="104"/>
+      <c r="AD25" s="104"/>
+      <c r="AE25" s="104"/>
+      <c r="AF25" s="104"/>
+      <c r="AG25" s="104"/>
+      <c r="AH25" s="104"/>
+      <c r="AI25" s="104"/>
+      <c r="AJ25" s="104"/>
+      <c r="AK25" s="105"/>
       <c r="AN25" s="3"/>
       <c r="AO25" s="3"/>
       <c r="AP25" s="3"/>
@@ -10152,44 +10134,44 @@
     </row>
     <row r="26" spans="1:254" s="2" customFormat="1" ht="28.25" customHeight="1">
       <c r="A26" s="38"/>
-      <c r="B26" s="143" t="s">
+      <c r="B26" s="137" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="144"/>
+      <c r="C26" s="138"/>
       <c r="D26" s="35"/>
       <c r="E26" s="35"/>
       <c r="F26" s="39"/>
-      <c r="G26" s="181"/>
-      <c r="H26" s="181"/>
-      <c r="I26" s="181"/>
-      <c r="J26" s="181"/>
-      <c r="K26" s="181"/>
-      <c r="L26" s="181"/>
-      <c r="M26" s="181"/>
-      <c r="N26" s="181"/>
-      <c r="O26" s="181"/>
-      <c r="P26" s="181"/>
-      <c r="Q26" s="181"/>
-      <c r="R26" s="181"/>
-      <c r="S26" s="181"/>
-      <c r="T26" s="181"/>
-      <c r="U26" s="181"/>
-      <c r="V26" s="181"/>
-      <c r="W26" s="181"/>
-      <c r="X26" s="181"/>
-      <c r="Y26" s="181"/>
-      <c r="Z26" s="181"/>
-      <c r="AA26" s="181"/>
-      <c r="AB26" s="181"/>
-      <c r="AC26" s="181"/>
-      <c r="AD26" s="181"/>
-      <c r="AE26" s="181"/>
-      <c r="AF26" s="181"/>
-      <c r="AG26" s="181"/>
-      <c r="AH26" s="181"/>
-      <c r="AI26" s="181"/>
-      <c r="AJ26" s="181"/>
-      <c r="AK26" s="182"/>
+      <c r="G26" s="104"/>
+      <c r="H26" s="104"/>
+      <c r="I26" s="104"/>
+      <c r="J26" s="104"/>
+      <c r="K26" s="104"/>
+      <c r="L26" s="104"/>
+      <c r="M26" s="104"/>
+      <c r="N26" s="104"/>
+      <c r="O26" s="104"/>
+      <c r="P26" s="104"/>
+      <c r="Q26" s="104"/>
+      <c r="R26" s="104"/>
+      <c r="S26" s="104"/>
+      <c r="T26" s="104"/>
+      <c r="U26" s="104"/>
+      <c r="V26" s="104"/>
+      <c r="W26" s="104"/>
+      <c r="X26" s="104"/>
+      <c r="Y26" s="104"/>
+      <c r="Z26" s="104"/>
+      <c r="AA26" s="104"/>
+      <c r="AB26" s="104"/>
+      <c r="AC26" s="104"/>
+      <c r="AD26" s="104"/>
+      <c r="AE26" s="104"/>
+      <c r="AF26" s="104"/>
+      <c r="AG26" s="104"/>
+      <c r="AH26" s="104"/>
+      <c r="AI26" s="104"/>
+      <c r="AJ26" s="104"/>
+      <c r="AK26" s="105"/>
       <c r="AN26" s="3"/>
       <c r="AO26" s="3"/>
       <c r="AP26" s="3"/>
@@ -10410,50 +10392,50 @@
       <c r="A27" s="37">
         <v>1</v>
       </c>
-      <c r="B27" s="141" t="s">
+      <c r="B27" s="122" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="142"/>
+      <c r="C27" s="123"/>
       <c r="D27" s="92" t="s">
         <v>99</v>
       </c>
       <c r="E27" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="158" t="s">
+      <c r="F27" s="124" t="s">
         <v>15</v>
       </c>
-      <c r="G27" s="183"/>
-      <c r="H27" s="183"/>
-      <c r="I27" s="183"/>
-      <c r="J27" s="183"/>
-      <c r="K27" s="183"/>
-      <c r="L27" s="183"/>
-      <c r="M27" s="183"/>
-      <c r="N27" s="183"/>
-      <c r="O27" s="183"/>
-      <c r="P27" s="183"/>
-      <c r="Q27" s="183"/>
-      <c r="R27" s="183"/>
-      <c r="S27" s="183"/>
-      <c r="T27" s="183"/>
-      <c r="U27" s="183"/>
-      <c r="V27" s="183"/>
-      <c r="W27" s="183"/>
-      <c r="X27" s="183"/>
-      <c r="Y27" s="183"/>
-      <c r="Z27" s="183"/>
-      <c r="AA27" s="183"/>
-      <c r="AB27" s="183"/>
-      <c r="AC27" s="183"/>
-      <c r="AD27" s="183"/>
-      <c r="AE27" s="183"/>
-      <c r="AF27" s="183"/>
-      <c r="AG27" s="183"/>
-      <c r="AH27" s="183"/>
-      <c r="AI27" s="183"/>
-      <c r="AJ27" s="183"/>
-      <c r="AK27" s="184"/>
+      <c r="G27" s="106"/>
+      <c r="H27" s="106"/>
+      <c r="I27" s="106"/>
+      <c r="J27" s="106"/>
+      <c r="K27" s="106"/>
+      <c r="L27" s="106"/>
+      <c r="M27" s="106"/>
+      <c r="N27" s="106"/>
+      <c r="O27" s="106"/>
+      <c r="P27" s="106"/>
+      <c r="Q27" s="106"/>
+      <c r="R27" s="106"/>
+      <c r="S27" s="106"/>
+      <c r="T27" s="106"/>
+      <c r="U27" s="106"/>
+      <c r="V27" s="106"/>
+      <c r="W27" s="106"/>
+      <c r="X27" s="106"/>
+      <c r="Y27" s="106"/>
+      <c r="Z27" s="106"/>
+      <c r="AA27" s="106"/>
+      <c r="AB27" s="106"/>
+      <c r="AC27" s="106"/>
+      <c r="AD27" s="106"/>
+      <c r="AE27" s="106"/>
+      <c r="AF27" s="106"/>
+      <c r="AG27" s="106"/>
+      <c r="AH27" s="106"/>
+      <c r="AI27" s="106"/>
+      <c r="AJ27" s="106"/>
+      <c r="AK27" s="107"/>
       <c r="AN27" s="3"/>
       <c r="AO27" s="3"/>
       <c r="AP27" s="3"/>
@@ -10674,46 +10656,46 @@
       <c r="A28" s="37">
         <v>2</v>
       </c>
-      <c r="B28" s="141" t="s">
+      <c r="B28" s="122" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="142"/>
+      <c r="C28" s="123"/>
       <c r="D28" s="35" t="s">
         <v>77</v>
       </c>
       <c r="E28" s="35"/>
-      <c r="F28" s="106"/>
-      <c r="G28" s="183"/>
-      <c r="H28" s="183"/>
-      <c r="I28" s="183"/>
-      <c r="J28" s="183"/>
-      <c r="K28" s="183"/>
-      <c r="L28" s="183"/>
-      <c r="M28" s="183"/>
-      <c r="N28" s="183"/>
-      <c r="O28" s="183"/>
-      <c r="P28" s="183"/>
-      <c r="Q28" s="183"/>
-      <c r="R28" s="183"/>
-      <c r="S28" s="183"/>
-      <c r="T28" s="183"/>
-      <c r="U28" s="183"/>
-      <c r="V28" s="183"/>
-      <c r="W28" s="183"/>
-      <c r="X28" s="183"/>
-      <c r="Y28" s="183"/>
-      <c r="Z28" s="183"/>
-      <c r="AA28" s="183"/>
-      <c r="AB28" s="183"/>
-      <c r="AC28" s="183"/>
-      <c r="AD28" s="183"/>
-      <c r="AE28" s="183"/>
-      <c r="AF28" s="183"/>
-      <c r="AG28" s="183"/>
-      <c r="AH28" s="183"/>
-      <c r="AI28" s="183"/>
-      <c r="AJ28" s="183"/>
-      <c r="AK28" s="184"/>
+      <c r="F28" s="125"/>
+      <c r="G28" s="106"/>
+      <c r="H28" s="106"/>
+      <c r="I28" s="106"/>
+      <c r="J28" s="106"/>
+      <c r="K28" s="106"/>
+      <c r="L28" s="106"/>
+      <c r="M28" s="106"/>
+      <c r="N28" s="106"/>
+      <c r="O28" s="106"/>
+      <c r="P28" s="106"/>
+      <c r="Q28" s="106"/>
+      <c r="R28" s="106"/>
+      <c r="S28" s="106"/>
+      <c r="T28" s="106"/>
+      <c r="U28" s="106"/>
+      <c r="V28" s="106"/>
+      <c r="W28" s="106"/>
+      <c r="X28" s="106"/>
+      <c r="Y28" s="106"/>
+      <c r="Z28" s="106"/>
+      <c r="AA28" s="106"/>
+      <c r="AB28" s="106"/>
+      <c r="AC28" s="106"/>
+      <c r="AD28" s="106"/>
+      <c r="AE28" s="106"/>
+      <c r="AF28" s="106"/>
+      <c r="AG28" s="106"/>
+      <c r="AH28" s="106"/>
+      <c r="AI28" s="106"/>
+      <c r="AJ28" s="106"/>
+      <c r="AK28" s="107"/>
       <c r="AN28" s="3"/>
       <c r="AO28" s="3"/>
       <c r="AP28" s="3"/>
@@ -10934,46 +10916,46 @@
       <c r="A29" s="37">
         <v>3</v>
       </c>
-      <c r="B29" s="104" t="s">
+      <c r="B29" s="117" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="105"/>
+      <c r="C29" s="118"/>
       <c r="D29" s="35" t="s">
         <v>77</v>
       </c>
       <c r="E29" s="35"/>
-      <c r="F29" s="106"/>
-      <c r="G29" s="183"/>
-      <c r="H29" s="183"/>
-      <c r="I29" s="183"/>
-      <c r="J29" s="183"/>
-      <c r="K29" s="183"/>
-      <c r="L29" s="183"/>
-      <c r="M29" s="183"/>
-      <c r="N29" s="183"/>
-      <c r="O29" s="183"/>
-      <c r="P29" s="183"/>
-      <c r="Q29" s="183"/>
-      <c r="R29" s="183"/>
-      <c r="S29" s="183"/>
-      <c r="T29" s="183"/>
-      <c r="U29" s="183"/>
-      <c r="V29" s="183"/>
-      <c r="W29" s="183"/>
-      <c r="X29" s="183"/>
-      <c r="Y29" s="183"/>
-      <c r="Z29" s="183"/>
-      <c r="AA29" s="183"/>
-      <c r="AB29" s="183"/>
-      <c r="AC29" s="183"/>
-      <c r="AD29" s="183"/>
-      <c r="AE29" s="183"/>
-      <c r="AF29" s="183"/>
-      <c r="AG29" s="183"/>
-      <c r="AH29" s="183"/>
-      <c r="AI29" s="183"/>
-      <c r="AJ29" s="183"/>
-      <c r="AK29" s="185"/>
+      <c r="F29" s="125"/>
+      <c r="G29" s="106"/>
+      <c r="H29" s="106"/>
+      <c r="I29" s="106"/>
+      <c r="J29" s="106"/>
+      <c r="K29" s="106"/>
+      <c r="L29" s="106"/>
+      <c r="M29" s="106"/>
+      <c r="N29" s="106"/>
+      <c r="O29" s="106"/>
+      <c r="P29" s="106"/>
+      <c r="Q29" s="106"/>
+      <c r="R29" s="106"/>
+      <c r="S29" s="106"/>
+      <c r="T29" s="106"/>
+      <c r="U29" s="106"/>
+      <c r="V29" s="106"/>
+      <c r="W29" s="106"/>
+      <c r="X29" s="106"/>
+      <c r="Y29" s="106"/>
+      <c r="Z29" s="106"/>
+      <c r="AA29" s="106"/>
+      <c r="AB29" s="106"/>
+      <c r="AC29" s="106"/>
+      <c r="AD29" s="106"/>
+      <c r="AE29" s="106"/>
+      <c r="AF29" s="106"/>
+      <c r="AG29" s="106"/>
+      <c r="AH29" s="106"/>
+      <c r="AI29" s="106"/>
+      <c r="AJ29" s="106"/>
+      <c r="AK29" s="108"/>
       <c r="AN29" s="3"/>
       <c r="AO29" s="3"/>
       <c r="AP29" s="3"/>
@@ -11194,48 +11176,48 @@
       <c r="A30" s="37">
         <v>4</v>
       </c>
-      <c r="B30" s="104" t="s">
+      <c r="B30" s="117" t="s">
         <v>54</v>
       </c>
-      <c r="C30" s="105"/>
+      <c r="C30" s="118"/>
       <c r="D30" s="96" t="s">
         <v>103</v>
       </c>
       <c r="E30" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="F30" s="106"/>
-      <c r="G30" s="181"/>
-      <c r="H30" s="181"/>
-      <c r="I30" s="181"/>
-      <c r="J30" s="181"/>
-      <c r="K30" s="181"/>
-      <c r="L30" s="181"/>
-      <c r="M30" s="181"/>
-      <c r="N30" s="181"/>
-      <c r="O30" s="181"/>
-      <c r="P30" s="181"/>
-      <c r="Q30" s="181"/>
-      <c r="R30" s="181"/>
-      <c r="S30" s="181"/>
-      <c r="T30" s="181"/>
-      <c r="U30" s="181"/>
-      <c r="V30" s="181"/>
-      <c r="W30" s="181"/>
-      <c r="X30" s="181"/>
-      <c r="Y30" s="181"/>
-      <c r="Z30" s="181"/>
-      <c r="AA30" s="181"/>
-      <c r="AB30" s="181"/>
-      <c r="AC30" s="181"/>
-      <c r="AD30" s="181"/>
-      <c r="AE30" s="181"/>
-      <c r="AF30" s="181"/>
-      <c r="AG30" s="181"/>
-      <c r="AH30" s="181"/>
-      <c r="AI30" s="181"/>
-      <c r="AJ30" s="181"/>
-      <c r="AK30" s="182"/>
+      <c r="F30" s="125"/>
+      <c r="G30" s="104"/>
+      <c r="H30" s="104"/>
+      <c r="I30" s="104"/>
+      <c r="J30" s="104"/>
+      <c r="K30" s="104"/>
+      <c r="L30" s="104"/>
+      <c r="M30" s="104"/>
+      <c r="N30" s="104"/>
+      <c r="O30" s="104"/>
+      <c r="P30" s="104"/>
+      <c r="Q30" s="104"/>
+      <c r="R30" s="104"/>
+      <c r="S30" s="104"/>
+      <c r="T30" s="104"/>
+      <c r="U30" s="104"/>
+      <c r="V30" s="104"/>
+      <c r="W30" s="104"/>
+      <c r="X30" s="104"/>
+      <c r="Y30" s="104"/>
+      <c r="Z30" s="104"/>
+      <c r="AA30" s="104"/>
+      <c r="AB30" s="104"/>
+      <c r="AC30" s="104"/>
+      <c r="AD30" s="104"/>
+      <c r="AE30" s="104"/>
+      <c r="AF30" s="104"/>
+      <c r="AG30" s="104"/>
+      <c r="AH30" s="104"/>
+      <c r="AI30" s="104"/>
+      <c r="AJ30" s="104"/>
+      <c r="AK30" s="105"/>
       <c r="AN30" s="3"/>
       <c r="AO30" s="3"/>
       <c r="AP30" s="3"/>
@@ -11456,46 +11438,46 @@
       <c r="A31" s="37">
         <v>5</v>
       </c>
-      <c r="B31" s="141" t="s">
+      <c r="B31" s="122" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="142"/>
+      <c r="C31" s="123"/>
       <c r="D31" s="92" t="s">
         <v>80</v>
       </c>
       <c r="E31" s="35"/>
-      <c r="F31" s="106"/>
-      <c r="G31" s="181"/>
-      <c r="H31" s="181"/>
-      <c r="I31" s="181"/>
-      <c r="J31" s="181"/>
-      <c r="K31" s="181"/>
-      <c r="L31" s="181"/>
-      <c r="M31" s="181"/>
-      <c r="N31" s="181"/>
-      <c r="O31" s="181"/>
-      <c r="P31" s="181"/>
-      <c r="Q31" s="181"/>
-      <c r="R31" s="181"/>
-      <c r="S31" s="181"/>
-      <c r="T31" s="181"/>
-      <c r="U31" s="181"/>
-      <c r="V31" s="181"/>
-      <c r="W31" s="181"/>
-      <c r="X31" s="181"/>
-      <c r="Y31" s="181"/>
-      <c r="Z31" s="181"/>
-      <c r="AA31" s="181"/>
-      <c r="AB31" s="181"/>
-      <c r="AC31" s="181"/>
-      <c r="AD31" s="181"/>
-      <c r="AE31" s="181"/>
-      <c r="AF31" s="181"/>
-      <c r="AG31" s="181"/>
-      <c r="AH31" s="181"/>
-      <c r="AI31" s="181"/>
-      <c r="AJ31" s="181"/>
-      <c r="AK31" s="182"/>
+      <c r="F31" s="125"/>
+      <c r="G31" s="104"/>
+      <c r="H31" s="104"/>
+      <c r="I31" s="104"/>
+      <c r="J31" s="104"/>
+      <c r="K31" s="104"/>
+      <c r="L31" s="104"/>
+      <c r="M31" s="104"/>
+      <c r="N31" s="104"/>
+      <c r="O31" s="104"/>
+      <c r="P31" s="104"/>
+      <c r="Q31" s="104"/>
+      <c r="R31" s="104"/>
+      <c r="S31" s="104"/>
+      <c r="T31" s="104"/>
+      <c r="U31" s="104"/>
+      <c r="V31" s="104"/>
+      <c r="W31" s="104"/>
+      <c r="X31" s="104"/>
+      <c r="Y31" s="104"/>
+      <c r="Z31" s="104"/>
+      <c r="AA31" s="104"/>
+      <c r="AB31" s="104"/>
+      <c r="AC31" s="104"/>
+      <c r="AD31" s="104"/>
+      <c r="AE31" s="104"/>
+      <c r="AF31" s="104"/>
+      <c r="AG31" s="104"/>
+      <c r="AH31" s="104"/>
+      <c r="AI31" s="104"/>
+      <c r="AJ31" s="104"/>
+      <c r="AK31" s="105"/>
       <c r="AN31" s="3"/>
       <c r="AO31" s="3"/>
       <c r="AP31" s="3"/>
@@ -11716,46 +11698,46 @@
       <c r="A32" s="37">
         <v>6</v>
       </c>
-      <c r="B32" s="104" t="s">
+      <c r="B32" s="117" t="s">
         <v>57</v>
       </c>
-      <c r="C32" s="105"/>
+      <c r="C32" s="118"/>
       <c r="D32" s="92" t="s">
         <v>118</v>
       </c>
       <c r="E32" s="35"/>
-      <c r="F32" s="106"/>
-      <c r="G32" s="181"/>
-      <c r="H32" s="181"/>
-      <c r="I32" s="181"/>
-      <c r="J32" s="181"/>
-      <c r="K32" s="181"/>
-      <c r="L32" s="181"/>
-      <c r="M32" s="181"/>
-      <c r="N32" s="181"/>
-      <c r="O32" s="181"/>
-      <c r="P32" s="181"/>
-      <c r="Q32" s="181"/>
-      <c r="R32" s="181"/>
-      <c r="S32" s="181"/>
-      <c r="T32" s="181"/>
-      <c r="U32" s="181"/>
-      <c r="V32" s="181"/>
-      <c r="W32" s="181"/>
-      <c r="X32" s="181"/>
-      <c r="Y32" s="181"/>
-      <c r="Z32" s="181"/>
-      <c r="AA32" s="181"/>
-      <c r="AB32" s="181"/>
-      <c r="AC32" s="181"/>
-      <c r="AD32" s="181"/>
-      <c r="AE32" s="181"/>
-      <c r="AF32" s="181"/>
-      <c r="AG32" s="181"/>
-      <c r="AH32" s="181"/>
-      <c r="AI32" s="181"/>
-      <c r="AJ32" s="186"/>
-      <c r="AK32" s="187"/>
+      <c r="F32" s="125"/>
+      <c r="G32" s="104"/>
+      <c r="H32" s="104"/>
+      <c r="I32" s="104"/>
+      <c r="J32" s="104"/>
+      <c r="K32" s="104"/>
+      <c r="L32" s="104"/>
+      <c r="M32" s="104"/>
+      <c r="N32" s="104"/>
+      <c r="O32" s="104"/>
+      <c r="P32" s="104"/>
+      <c r="Q32" s="104"/>
+      <c r="R32" s="104"/>
+      <c r="S32" s="104"/>
+      <c r="T32" s="104"/>
+      <c r="U32" s="104"/>
+      <c r="V32" s="104"/>
+      <c r="W32" s="104"/>
+      <c r="X32" s="104"/>
+      <c r="Y32" s="104"/>
+      <c r="Z32" s="104"/>
+      <c r="AA32" s="104"/>
+      <c r="AB32" s="104"/>
+      <c r="AC32" s="104"/>
+      <c r="AD32" s="104"/>
+      <c r="AE32" s="104"/>
+      <c r="AF32" s="104"/>
+      <c r="AG32" s="104"/>
+      <c r="AH32" s="104"/>
+      <c r="AI32" s="104"/>
+      <c r="AJ32" s="109"/>
+      <c r="AK32" s="110"/>
       <c r="AN32" s="3"/>
       <c r="AO32" s="3"/>
       <c r="AP32" s="3"/>
@@ -11976,46 +11958,46 @@
       <c r="A33" s="37">
         <v>7</v>
       </c>
-      <c r="B33" s="104" t="s">
+      <c r="B33" s="117" t="s">
         <v>58</v>
       </c>
-      <c r="C33" s="105"/>
+      <c r="C33" s="118"/>
       <c r="D33" s="92" t="s">
         <v>118</v>
       </c>
       <c r="E33" s="35"/>
-      <c r="F33" s="106"/>
-      <c r="G33" s="181"/>
-      <c r="H33" s="181"/>
-      <c r="I33" s="181"/>
-      <c r="J33" s="181"/>
-      <c r="K33" s="181"/>
-      <c r="L33" s="181"/>
-      <c r="M33" s="181"/>
-      <c r="N33" s="181"/>
-      <c r="O33" s="181"/>
-      <c r="P33" s="181"/>
-      <c r="Q33" s="181"/>
-      <c r="R33" s="181"/>
-      <c r="S33" s="181"/>
-      <c r="T33" s="181"/>
-      <c r="U33" s="181"/>
-      <c r="V33" s="181"/>
-      <c r="W33" s="181"/>
-      <c r="X33" s="181"/>
-      <c r="Y33" s="181"/>
-      <c r="Z33" s="181"/>
-      <c r="AA33" s="181"/>
-      <c r="AB33" s="181"/>
-      <c r="AC33" s="181"/>
-      <c r="AD33" s="181"/>
-      <c r="AE33" s="181"/>
-      <c r="AF33" s="181"/>
-      <c r="AG33" s="181"/>
-      <c r="AH33" s="181"/>
-      <c r="AI33" s="181"/>
-      <c r="AJ33" s="186"/>
-      <c r="AK33" s="187"/>
+      <c r="F33" s="125"/>
+      <c r="G33" s="104"/>
+      <c r="H33" s="104"/>
+      <c r="I33" s="104"/>
+      <c r="J33" s="104"/>
+      <c r="K33" s="104"/>
+      <c r="L33" s="104"/>
+      <c r="M33" s="104"/>
+      <c r="N33" s="104"/>
+      <c r="O33" s="104"/>
+      <c r="P33" s="104"/>
+      <c r="Q33" s="104"/>
+      <c r="R33" s="104"/>
+      <c r="S33" s="104"/>
+      <c r="T33" s="104"/>
+      <c r="U33" s="104"/>
+      <c r="V33" s="104"/>
+      <c r="W33" s="104"/>
+      <c r="X33" s="104"/>
+      <c r="Y33" s="104"/>
+      <c r="Z33" s="104"/>
+      <c r="AA33" s="104"/>
+      <c r="AB33" s="104"/>
+      <c r="AC33" s="104"/>
+      <c r="AD33" s="104"/>
+      <c r="AE33" s="104"/>
+      <c r="AF33" s="104"/>
+      <c r="AG33" s="104"/>
+      <c r="AH33" s="104"/>
+      <c r="AI33" s="104"/>
+      <c r="AJ33" s="109"/>
+      <c r="AK33" s="110"/>
       <c r="AN33" s="3"/>
       <c r="AO33" s="3"/>
       <c r="AP33" s="3"/>
@@ -12236,46 +12218,46 @@
       <c r="A34" s="37">
         <v>8</v>
       </c>
-      <c r="B34" s="141" t="s">
+      <c r="B34" s="122" t="s">
         <v>59</v>
       </c>
-      <c r="C34" s="142"/>
+      <c r="C34" s="123"/>
       <c r="D34" s="92" t="s">
         <v>99</v>
       </c>
       <c r="E34" s="40"/>
-      <c r="F34" s="106"/>
-      <c r="G34" s="183"/>
-      <c r="H34" s="183"/>
-      <c r="I34" s="183"/>
-      <c r="J34" s="183"/>
-      <c r="K34" s="183"/>
-      <c r="L34" s="183"/>
-      <c r="M34" s="183"/>
-      <c r="N34" s="183"/>
-      <c r="O34" s="183"/>
-      <c r="P34" s="183"/>
-      <c r="Q34" s="183"/>
-      <c r="R34" s="183"/>
-      <c r="S34" s="183"/>
-      <c r="T34" s="183"/>
-      <c r="U34" s="183"/>
-      <c r="V34" s="183"/>
-      <c r="W34" s="183"/>
-      <c r="X34" s="183"/>
-      <c r="Y34" s="183"/>
-      <c r="Z34" s="183"/>
-      <c r="AA34" s="183"/>
-      <c r="AB34" s="183"/>
-      <c r="AC34" s="183"/>
-      <c r="AD34" s="183"/>
-      <c r="AE34" s="183"/>
-      <c r="AF34" s="183"/>
-      <c r="AG34" s="183"/>
-      <c r="AH34" s="183"/>
-      <c r="AI34" s="183"/>
-      <c r="AJ34" s="188"/>
-      <c r="AK34" s="189"/>
+      <c r="F34" s="125"/>
+      <c r="G34" s="106"/>
+      <c r="H34" s="106"/>
+      <c r="I34" s="106"/>
+      <c r="J34" s="106"/>
+      <c r="K34" s="106"/>
+      <c r="L34" s="106"/>
+      <c r="M34" s="106"/>
+      <c r="N34" s="106"/>
+      <c r="O34" s="106"/>
+      <c r="P34" s="106"/>
+      <c r="Q34" s="106"/>
+      <c r="R34" s="106"/>
+      <c r="S34" s="106"/>
+      <c r="T34" s="106"/>
+      <c r="U34" s="106"/>
+      <c r="V34" s="106"/>
+      <c r="W34" s="106"/>
+      <c r="X34" s="106"/>
+      <c r="Y34" s="106"/>
+      <c r="Z34" s="106"/>
+      <c r="AA34" s="106"/>
+      <c r="AB34" s="106"/>
+      <c r="AC34" s="106"/>
+      <c r="AD34" s="106"/>
+      <c r="AE34" s="106"/>
+      <c r="AF34" s="106"/>
+      <c r="AG34" s="106"/>
+      <c r="AH34" s="106"/>
+      <c r="AI34" s="106"/>
+      <c r="AJ34" s="111"/>
+      <c r="AK34" s="112"/>
       <c r="AN34" s="3"/>
       <c r="AO34" s="3"/>
       <c r="AP34" s="3"/>
@@ -12496,46 +12478,46 @@
       <c r="A35" s="37">
         <v>9</v>
       </c>
-      <c r="B35" s="141" t="s">
+      <c r="B35" s="122" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="142"/>
+      <c r="C35" s="123"/>
       <c r="D35" s="92" t="s">
         <v>49</v>
       </c>
       <c r="E35" s="40"/>
-      <c r="F35" s="107"/>
-      <c r="G35" s="183"/>
-      <c r="H35" s="183"/>
-      <c r="I35" s="183"/>
-      <c r="J35" s="183"/>
-      <c r="K35" s="183"/>
-      <c r="L35" s="183"/>
-      <c r="M35" s="183"/>
-      <c r="N35" s="183"/>
-      <c r="O35" s="183"/>
-      <c r="P35" s="183"/>
-      <c r="Q35" s="183"/>
-      <c r="R35" s="183"/>
-      <c r="S35" s="183"/>
-      <c r="T35" s="183"/>
-      <c r="U35" s="183"/>
-      <c r="V35" s="183"/>
-      <c r="W35" s="183"/>
-      <c r="X35" s="183"/>
-      <c r="Y35" s="183"/>
-      <c r="Z35" s="183"/>
-      <c r="AA35" s="183"/>
-      <c r="AB35" s="183"/>
-      <c r="AC35" s="183"/>
-      <c r="AD35" s="183"/>
-      <c r="AE35" s="183"/>
-      <c r="AF35" s="183"/>
-      <c r="AG35" s="183"/>
-      <c r="AH35" s="183"/>
-      <c r="AI35" s="183"/>
-      <c r="AJ35" s="188"/>
-      <c r="AK35" s="189"/>
+      <c r="F35" s="126"/>
+      <c r="G35" s="106"/>
+      <c r="H35" s="106"/>
+      <c r="I35" s="106"/>
+      <c r="J35" s="106"/>
+      <c r="K35" s="106"/>
+      <c r="L35" s="106"/>
+      <c r="M35" s="106"/>
+      <c r="N35" s="106"/>
+      <c r="O35" s="106"/>
+      <c r="P35" s="106"/>
+      <c r="Q35" s="106"/>
+      <c r="R35" s="106"/>
+      <c r="S35" s="106"/>
+      <c r="T35" s="106"/>
+      <c r="U35" s="106"/>
+      <c r="V35" s="106"/>
+      <c r="W35" s="106"/>
+      <c r="X35" s="106"/>
+      <c r="Y35" s="106"/>
+      <c r="Z35" s="106"/>
+      <c r="AA35" s="106"/>
+      <c r="AB35" s="106"/>
+      <c r="AC35" s="106"/>
+      <c r="AD35" s="106"/>
+      <c r="AE35" s="106"/>
+      <c r="AF35" s="106"/>
+      <c r="AG35" s="106"/>
+      <c r="AH35" s="106"/>
+      <c r="AI35" s="106"/>
+      <c r="AJ35" s="111"/>
+      <c r="AK35" s="112"/>
       <c r="AN35" s="3"/>
       <c r="AO35" s="3"/>
       <c r="AP35" s="3"/>
@@ -12754,44 +12736,44 @@
     </row>
     <row r="36" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A36" s="37"/>
-      <c r="B36" s="143" t="s">
+      <c r="B36" s="137" t="s">
         <v>127</v>
       </c>
-      <c r="C36" s="144"/>
+      <c r="C36" s="138"/>
       <c r="D36" s="92"/>
       <c r="E36" s="40"/>
       <c r="F36" s="93"/>
-      <c r="G36" s="183"/>
-      <c r="H36" s="183"/>
-      <c r="I36" s="183"/>
-      <c r="J36" s="183"/>
-      <c r="K36" s="183"/>
-      <c r="L36" s="183"/>
-      <c r="M36" s="183"/>
-      <c r="N36" s="183"/>
-      <c r="O36" s="183"/>
-      <c r="P36" s="183"/>
-      <c r="Q36" s="183"/>
-      <c r="R36" s="183"/>
-      <c r="S36" s="183"/>
-      <c r="T36" s="183"/>
-      <c r="U36" s="183"/>
-      <c r="V36" s="183"/>
-      <c r="W36" s="183"/>
-      <c r="X36" s="183"/>
-      <c r="Y36" s="183"/>
-      <c r="Z36" s="183"/>
-      <c r="AA36" s="183"/>
-      <c r="AB36" s="183"/>
-      <c r="AC36" s="183"/>
-      <c r="AD36" s="183"/>
-      <c r="AE36" s="183"/>
-      <c r="AF36" s="183"/>
-      <c r="AG36" s="183"/>
-      <c r="AH36" s="183"/>
-      <c r="AI36" s="183"/>
-      <c r="AJ36" s="188"/>
-      <c r="AK36" s="189"/>
+      <c r="G36" s="106"/>
+      <c r="H36" s="106"/>
+      <c r="I36" s="106"/>
+      <c r="J36" s="106"/>
+      <c r="K36" s="106"/>
+      <c r="L36" s="106"/>
+      <c r="M36" s="106"/>
+      <c r="N36" s="106"/>
+      <c r="O36" s="106"/>
+      <c r="P36" s="106"/>
+      <c r="Q36" s="106"/>
+      <c r="R36" s="106"/>
+      <c r="S36" s="106"/>
+      <c r="T36" s="106"/>
+      <c r="U36" s="106"/>
+      <c r="V36" s="106"/>
+      <c r="W36" s="106"/>
+      <c r="X36" s="106"/>
+      <c r="Y36" s="106"/>
+      <c r="Z36" s="106"/>
+      <c r="AA36" s="106"/>
+      <c r="AB36" s="106"/>
+      <c r="AC36" s="106"/>
+      <c r="AD36" s="106"/>
+      <c r="AE36" s="106"/>
+      <c r="AF36" s="106"/>
+      <c r="AG36" s="106"/>
+      <c r="AH36" s="106"/>
+      <c r="AI36" s="106"/>
+      <c r="AJ36" s="111"/>
+      <c r="AK36" s="112"/>
       <c r="AN36" s="3"/>
       <c r="AO36" s="3"/>
       <c r="AP36" s="3"/>
@@ -13010,44 +12992,44 @@
     </row>
     <row r="37" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A37" s="37"/>
-      <c r="B37" s="141" t="s">
+      <c r="B37" s="122" t="s">
         <v>128</v>
       </c>
-      <c r="C37" s="142"/>
+      <c r="C37" s="123"/>
       <c r="D37" s="92"/>
       <c r="E37" s="40"/>
       <c r="F37" s="93"/>
-      <c r="G37" s="183"/>
-      <c r="H37" s="183"/>
-      <c r="I37" s="183"/>
-      <c r="J37" s="183"/>
-      <c r="K37" s="183"/>
-      <c r="L37" s="183"/>
-      <c r="M37" s="183"/>
-      <c r="N37" s="183"/>
-      <c r="O37" s="183"/>
-      <c r="P37" s="183"/>
-      <c r="Q37" s="183"/>
-      <c r="R37" s="183"/>
-      <c r="S37" s="183"/>
-      <c r="T37" s="183"/>
-      <c r="U37" s="183"/>
-      <c r="V37" s="183"/>
-      <c r="W37" s="183"/>
-      <c r="X37" s="183"/>
-      <c r="Y37" s="183"/>
-      <c r="Z37" s="183"/>
-      <c r="AA37" s="183"/>
-      <c r="AB37" s="183"/>
-      <c r="AC37" s="183"/>
-      <c r="AD37" s="183"/>
-      <c r="AE37" s="183"/>
-      <c r="AF37" s="183"/>
-      <c r="AG37" s="183"/>
-      <c r="AH37" s="183"/>
-      <c r="AI37" s="183"/>
-      <c r="AJ37" s="188"/>
-      <c r="AK37" s="189"/>
+      <c r="G37" s="106"/>
+      <c r="H37" s="106"/>
+      <c r="I37" s="106"/>
+      <c r="J37" s="106"/>
+      <c r="K37" s="106"/>
+      <c r="L37" s="106"/>
+      <c r="M37" s="106"/>
+      <c r="N37" s="106"/>
+      <c r="O37" s="106"/>
+      <c r="P37" s="106"/>
+      <c r="Q37" s="106"/>
+      <c r="R37" s="106"/>
+      <c r="S37" s="106"/>
+      <c r="T37" s="106"/>
+      <c r="U37" s="106"/>
+      <c r="V37" s="106"/>
+      <c r="W37" s="106"/>
+      <c r="X37" s="106"/>
+      <c r="Y37" s="106"/>
+      <c r="Z37" s="106"/>
+      <c r="AA37" s="106"/>
+      <c r="AB37" s="106"/>
+      <c r="AC37" s="106"/>
+      <c r="AD37" s="106"/>
+      <c r="AE37" s="106"/>
+      <c r="AF37" s="106"/>
+      <c r="AG37" s="106"/>
+      <c r="AH37" s="106"/>
+      <c r="AI37" s="106"/>
+      <c r="AJ37" s="111"/>
+      <c r="AK37" s="112"/>
       <c r="AN37" s="3"/>
       <c r="AO37" s="3"/>
       <c r="AP37" s="3"/>
@@ -13266,44 +13248,44 @@
     </row>
     <row r="38" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A38" s="37"/>
-      <c r="B38" s="147" t="s">
+      <c r="B38" s="135" t="s">
         <v>129</v>
       </c>
-      <c r="C38" s="148"/>
+      <c r="C38" s="136"/>
       <c r="D38" s="92"/>
       <c r="E38" s="40"/>
       <c r="F38" s="93"/>
-      <c r="G38" s="183"/>
-      <c r="H38" s="183"/>
-      <c r="I38" s="183"/>
-      <c r="J38" s="183"/>
-      <c r="K38" s="183"/>
-      <c r="L38" s="183"/>
-      <c r="M38" s="183"/>
-      <c r="N38" s="183"/>
-      <c r="O38" s="183"/>
-      <c r="P38" s="183"/>
-      <c r="Q38" s="183"/>
-      <c r="R38" s="183"/>
-      <c r="S38" s="183"/>
-      <c r="T38" s="183"/>
-      <c r="U38" s="183"/>
-      <c r="V38" s="183"/>
-      <c r="W38" s="183"/>
-      <c r="X38" s="183"/>
-      <c r="Y38" s="183"/>
-      <c r="Z38" s="183"/>
-      <c r="AA38" s="183"/>
-      <c r="AB38" s="183"/>
-      <c r="AC38" s="183"/>
-      <c r="AD38" s="183"/>
-      <c r="AE38" s="183"/>
-      <c r="AF38" s="183"/>
-      <c r="AG38" s="183"/>
-      <c r="AH38" s="183"/>
-      <c r="AI38" s="183"/>
-      <c r="AJ38" s="188"/>
-      <c r="AK38" s="189"/>
+      <c r="G38" s="106"/>
+      <c r="H38" s="106"/>
+      <c r="I38" s="106"/>
+      <c r="J38" s="106"/>
+      <c r="K38" s="106"/>
+      <c r="L38" s="106"/>
+      <c r="M38" s="106"/>
+      <c r="N38" s="106"/>
+      <c r="O38" s="106"/>
+      <c r="P38" s="106"/>
+      <c r="Q38" s="106"/>
+      <c r="R38" s="106"/>
+      <c r="S38" s="106"/>
+      <c r="T38" s="106"/>
+      <c r="U38" s="106"/>
+      <c r="V38" s="106"/>
+      <c r="W38" s="106"/>
+      <c r="X38" s="106"/>
+      <c r="Y38" s="106"/>
+      <c r="Z38" s="106"/>
+      <c r="AA38" s="106"/>
+      <c r="AB38" s="106"/>
+      <c r="AC38" s="106"/>
+      <c r="AD38" s="106"/>
+      <c r="AE38" s="106"/>
+      <c r="AF38" s="106"/>
+      <c r="AG38" s="106"/>
+      <c r="AH38" s="106"/>
+      <c r="AI38" s="106"/>
+      <c r="AJ38" s="111"/>
+      <c r="AK38" s="112"/>
       <c r="AN38" s="3"/>
       <c r="AO38" s="3"/>
       <c r="AP38" s="3"/>
@@ -13522,42 +13504,42 @@
     </row>
     <row r="39" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A39" s="37"/>
-      <c r="B39" s="147"/>
-      <c r="C39" s="148"/>
+      <c r="B39" s="135"/>
+      <c r="C39" s="136"/>
       <c r="D39" s="92"/>
       <c r="E39" s="40"/>
       <c r="F39" s="93"/>
-      <c r="G39" s="183"/>
-      <c r="H39" s="183"/>
-      <c r="I39" s="183"/>
-      <c r="J39" s="183"/>
-      <c r="K39" s="183"/>
-      <c r="L39" s="183"/>
-      <c r="M39" s="183"/>
-      <c r="N39" s="183"/>
-      <c r="O39" s="183"/>
-      <c r="P39" s="183"/>
-      <c r="Q39" s="183"/>
-      <c r="R39" s="183"/>
-      <c r="S39" s="183"/>
-      <c r="T39" s="183"/>
-      <c r="U39" s="183"/>
-      <c r="V39" s="183"/>
-      <c r="W39" s="183"/>
-      <c r="X39" s="183"/>
-      <c r="Y39" s="183"/>
-      <c r="Z39" s="183"/>
-      <c r="AA39" s="183"/>
-      <c r="AB39" s="183"/>
-      <c r="AC39" s="183"/>
-      <c r="AD39" s="183"/>
-      <c r="AE39" s="183"/>
-      <c r="AF39" s="183"/>
-      <c r="AG39" s="183"/>
-      <c r="AH39" s="183"/>
-      <c r="AI39" s="183"/>
-      <c r="AJ39" s="188"/>
-      <c r="AK39" s="189"/>
+      <c r="G39" s="106"/>
+      <c r="H39" s="106"/>
+      <c r="I39" s="106"/>
+      <c r="J39" s="106"/>
+      <c r="K39" s="106"/>
+      <c r="L39" s="106"/>
+      <c r="M39" s="106"/>
+      <c r="N39" s="106"/>
+      <c r="O39" s="106"/>
+      <c r="P39" s="106"/>
+      <c r="Q39" s="106"/>
+      <c r="R39" s="106"/>
+      <c r="S39" s="106"/>
+      <c r="T39" s="106"/>
+      <c r="U39" s="106"/>
+      <c r="V39" s="106"/>
+      <c r="W39" s="106"/>
+      <c r="X39" s="106"/>
+      <c r="Y39" s="106"/>
+      <c r="Z39" s="106"/>
+      <c r="AA39" s="106"/>
+      <c r="AB39" s="106"/>
+      <c r="AC39" s="106"/>
+      <c r="AD39" s="106"/>
+      <c r="AE39" s="106"/>
+      <c r="AF39" s="106"/>
+      <c r="AG39" s="106"/>
+      <c r="AH39" s="106"/>
+      <c r="AI39" s="106"/>
+      <c r="AJ39" s="111"/>
+      <c r="AK39" s="112"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
@@ -13776,46 +13758,46 @@
     </row>
     <row r="40" spans="1:254" s="2" customFormat="1" ht="42" customHeight="1" thickBot="1">
       <c r="A40" s="41"/>
-      <c r="B40" s="145" t="s">
+      <c r="B40" s="133" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="146"/>
+      <c r="C40" s="134"/>
       <c r="D40" s="42" t="s">
         <v>16</v>
       </c>
       <c r="E40" s="95"/>
       <c r="F40" s="43"/>
-      <c r="G40" s="190"/>
-      <c r="H40" s="190"/>
-      <c r="I40" s="190"/>
-      <c r="J40" s="190"/>
-      <c r="K40" s="190"/>
-      <c r="L40" s="190"/>
-      <c r="M40" s="190"/>
-      <c r="N40" s="190"/>
-      <c r="O40" s="190"/>
-      <c r="P40" s="190"/>
-      <c r="Q40" s="190"/>
-      <c r="R40" s="190"/>
-      <c r="S40" s="190"/>
-      <c r="T40" s="190"/>
-      <c r="U40" s="190"/>
-      <c r="V40" s="190"/>
-      <c r="W40" s="190"/>
-      <c r="X40" s="190"/>
-      <c r="Y40" s="190"/>
-      <c r="Z40" s="190"/>
-      <c r="AA40" s="190"/>
-      <c r="AB40" s="190"/>
-      <c r="AC40" s="190"/>
-      <c r="AD40" s="190"/>
-      <c r="AE40" s="190"/>
-      <c r="AF40" s="190"/>
-      <c r="AG40" s="190"/>
-      <c r="AH40" s="190"/>
-      <c r="AI40" s="190"/>
-      <c r="AJ40" s="191"/>
-      <c r="AK40" s="192"/>
+      <c r="G40" s="113"/>
+      <c r="H40" s="113"/>
+      <c r="I40" s="113"/>
+      <c r="J40" s="113"/>
+      <c r="K40" s="113"/>
+      <c r="L40" s="113"/>
+      <c r="M40" s="113"/>
+      <c r="N40" s="113"/>
+      <c r="O40" s="113"/>
+      <c r="P40" s="113"/>
+      <c r="Q40" s="113"/>
+      <c r="R40" s="113"/>
+      <c r="S40" s="113"/>
+      <c r="T40" s="113"/>
+      <c r="U40" s="113"/>
+      <c r="V40" s="113"/>
+      <c r="W40" s="113"/>
+      <c r="X40" s="113"/>
+      <c r="Y40" s="113"/>
+      <c r="Z40" s="113"/>
+      <c r="AA40" s="113"/>
+      <c r="AB40" s="113"/>
+      <c r="AC40" s="113"/>
+      <c r="AD40" s="113"/>
+      <c r="AE40" s="113"/>
+      <c r="AF40" s="113"/>
+      <c r="AG40" s="113"/>
+      <c r="AH40" s="113"/>
+      <c r="AI40" s="113"/>
+      <c r="AJ40" s="114"/>
+      <c r="AK40" s="115"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
@@ -14043,37 +14025,37 @@
         <v>96</v>
       </c>
       <c r="F41" s="75"/>
-      <c r="G41" s="149"/>
-      <c r="H41" s="149"/>
-      <c r="I41" s="149"/>
-      <c r="J41" s="149"/>
-      <c r="K41" s="149"/>
-      <c r="L41" s="149"/>
-      <c r="M41" s="149"/>
-      <c r="N41" s="149"/>
-      <c r="O41" s="149"/>
-      <c r="P41" s="149"/>
-      <c r="Q41" s="149"/>
-      <c r="R41" s="149"/>
-      <c r="S41" s="149"/>
-      <c r="T41" s="149"/>
-      <c r="U41" s="149"/>
-      <c r="V41" s="149"/>
-      <c r="W41" s="149"/>
-      <c r="X41" s="149"/>
-      <c r="Y41" s="149"/>
-      <c r="Z41" s="149"/>
-      <c r="AA41" s="150"/>
-      <c r="AB41" s="150"/>
-      <c r="AC41" s="150"/>
-      <c r="AD41" s="150"/>
-      <c r="AE41" s="150"/>
-      <c r="AF41" s="150"/>
-      <c r="AG41" s="150"/>
-      <c r="AH41" s="150"/>
-      <c r="AI41" s="150"/>
-      <c r="AJ41" s="150"/>
-      <c r="AK41" s="151"/>
+      <c r="G41" s="127"/>
+      <c r="H41" s="127"/>
+      <c r="I41" s="127"/>
+      <c r="J41" s="127"/>
+      <c r="K41" s="127"/>
+      <c r="L41" s="127"/>
+      <c r="M41" s="127"/>
+      <c r="N41" s="127"/>
+      <c r="O41" s="127"/>
+      <c r="P41" s="127"/>
+      <c r="Q41" s="127"/>
+      <c r="R41" s="127"/>
+      <c r="S41" s="127"/>
+      <c r="T41" s="127"/>
+      <c r="U41" s="127"/>
+      <c r="V41" s="127"/>
+      <c r="W41" s="127"/>
+      <c r="X41" s="127"/>
+      <c r="Y41" s="127"/>
+      <c r="Z41" s="127"/>
+      <c r="AA41" s="128"/>
+      <c r="AB41" s="128"/>
+      <c r="AC41" s="128"/>
+      <c r="AD41" s="128"/>
+      <c r="AE41" s="128"/>
+      <c r="AF41" s="128"/>
+      <c r="AG41" s="128"/>
+      <c r="AH41" s="128"/>
+      <c r="AI41" s="128"/>
+      <c r="AJ41" s="128"/>
+      <c r="AK41" s="129"/>
     </row>
     <row r="42" spans="1:254" ht="23" customHeight="1">
       <c r="A42" s="45"/>
@@ -14084,37 +14066,37 @@
         <v>97</v>
       </c>
       <c r="F42" s="77"/>
-      <c r="G42" s="152"/>
-      <c r="H42" s="152"/>
-      <c r="I42" s="152"/>
-      <c r="J42" s="152"/>
-      <c r="K42" s="152"/>
-      <c r="L42" s="152"/>
-      <c r="M42" s="152"/>
-      <c r="N42" s="152"/>
-      <c r="O42" s="152"/>
-      <c r="P42" s="152"/>
-      <c r="Q42" s="154"/>
-      <c r="R42" s="154"/>
-      <c r="S42" s="154"/>
-      <c r="T42" s="154"/>
-      <c r="U42" s="154"/>
-      <c r="V42" s="154"/>
-      <c r="W42" s="154"/>
-      <c r="X42" s="154"/>
-      <c r="Y42" s="154"/>
-      <c r="Z42" s="154"/>
-      <c r="AA42" s="152"/>
-      <c r="AB42" s="152"/>
-      <c r="AC42" s="152"/>
-      <c r="AD42" s="152"/>
-      <c r="AE42" s="152"/>
-      <c r="AF42" s="152"/>
-      <c r="AG42" s="152"/>
-      <c r="AH42" s="152"/>
-      <c r="AI42" s="152"/>
-      <c r="AJ42" s="152"/>
-      <c r="AK42" s="153"/>
+      <c r="G42" s="130"/>
+      <c r="H42" s="130"/>
+      <c r="I42" s="130"/>
+      <c r="J42" s="130"/>
+      <c r="K42" s="130"/>
+      <c r="L42" s="130"/>
+      <c r="M42" s="130"/>
+      <c r="N42" s="130"/>
+      <c r="O42" s="130"/>
+      <c r="P42" s="130"/>
+      <c r="Q42" s="132"/>
+      <c r="R42" s="132"/>
+      <c r="S42" s="132"/>
+      <c r="T42" s="132"/>
+      <c r="U42" s="132"/>
+      <c r="V42" s="132"/>
+      <c r="W42" s="132"/>
+      <c r="X42" s="132"/>
+      <c r="Y42" s="132"/>
+      <c r="Z42" s="132"/>
+      <c r="AA42" s="130"/>
+      <c r="AB42" s="130"/>
+      <c r="AC42" s="130"/>
+      <c r="AD42" s="130"/>
+      <c r="AE42" s="130"/>
+      <c r="AF42" s="130"/>
+      <c r="AG42" s="130"/>
+      <c r="AH42" s="130"/>
+      <c r="AI42" s="130"/>
+      <c r="AJ42" s="130"/>
+      <c r="AK42" s="131"/>
     </row>
     <row r="43" spans="1:254" ht="23" customHeight="1" thickBot="1">
       <c r="A43" s="49"/>
@@ -14125,37 +14107,37 @@
         <v>98</v>
       </c>
       <c r="F43" s="82"/>
-      <c r="G43" s="155"/>
-      <c r="H43" s="155"/>
-      <c r="I43" s="155"/>
-      <c r="J43" s="155"/>
-      <c r="K43" s="155"/>
-      <c r="L43" s="155"/>
-      <c r="M43" s="155"/>
-      <c r="N43" s="155"/>
-      <c r="O43" s="155"/>
-      <c r="P43" s="155"/>
-      <c r="Q43" s="157"/>
-      <c r="R43" s="157"/>
-      <c r="S43" s="157"/>
-      <c r="T43" s="157"/>
-      <c r="U43" s="157"/>
-      <c r="V43" s="157"/>
-      <c r="W43" s="157"/>
-      <c r="X43" s="157"/>
-      <c r="Y43" s="157"/>
-      <c r="Z43" s="157"/>
-      <c r="AA43" s="155"/>
-      <c r="AB43" s="155"/>
-      <c r="AC43" s="155"/>
-      <c r="AD43" s="155"/>
-      <c r="AE43" s="155"/>
-      <c r="AF43" s="155"/>
-      <c r="AG43" s="155"/>
-      <c r="AH43" s="155"/>
-      <c r="AI43" s="155"/>
-      <c r="AJ43" s="155"/>
-      <c r="AK43" s="156"/>
+      <c r="G43" s="119"/>
+      <c r="H43" s="119"/>
+      <c r="I43" s="119"/>
+      <c r="J43" s="119"/>
+      <c r="K43" s="119"/>
+      <c r="L43" s="119"/>
+      <c r="M43" s="119"/>
+      <c r="N43" s="119"/>
+      <c r="O43" s="119"/>
+      <c r="P43" s="119"/>
+      <c r="Q43" s="121"/>
+      <c r="R43" s="121"/>
+      <c r="S43" s="121"/>
+      <c r="T43" s="121"/>
+      <c r="U43" s="121"/>
+      <c r="V43" s="121"/>
+      <c r="W43" s="121"/>
+      <c r="X43" s="121"/>
+      <c r="Y43" s="121"/>
+      <c r="Z43" s="121"/>
+      <c r="AA43" s="119"/>
+      <c r="AB43" s="119"/>
+      <c r="AC43" s="119"/>
+      <c r="AD43" s="119"/>
+      <c r="AE43" s="119"/>
+      <c r="AF43" s="119"/>
+      <c r="AG43" s="119"/>
+      <c r="AH43" s="119"/>
+      <c r="AI43" s="119"/>
+      <c r="AJ43" s="119"/>
+      <c r="AK43" s="120"/>
     </row>
     <row r="44" spans="1:254">
       <c r="A44" s="52"/>
@@ -14171,50 +14153,6 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="AA43:AK43"/>
-    <mergeCell ref="Q43:Z43"/>
-    <mergeCell ref="G43:P43"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="F12:F21"/>
-    <mergeCell ref="F27:F35"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="Q41:Z41"/>
-    <mergeCell ref="AA41:AK41"/>
-    <mergeCell ref="AA42:AK42"/>
-    <mergeCell ref="Q42:Z42"/>
-    <mergeCell ref="G42:P42"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="G41:P41"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="W5:Y7"/>
-    <mergeCell ref="AH5:AK7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="Z4:AC4"/>
-    <mergeCell ref="AD4:AG4"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="F22:F23"/>
     <mergeCell ref="A1:B1"/>
@@ -14231,20 +14169,64 @@
     <mergeCell ref="T4:Y4"/>
     <mergeCell ref="AH4:AK4"/>
     <mergeCell ref="T5:V7"/>
+    <mergeCell ref="W5:Y7"/>
+    <mergeCell ref="AH5:AK7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="Z4:AC4"/>
+    <mergeCell ref="AD4:AG4"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="F12:F21"/>
+    <mergeCell ref="F27:F35"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="AA43:AK43"/>
+    <mergeCell ref="Q43:Z43"/>
+    <mergeCell ref="G43:P43"/>
+    <mergeCell ref="Q41:Z41"/>
+    <mergeCell ref="AA41:AK41"/>
+    <mergeCell ref="AA42:AK42"/>
+    <mergeCell ref="Q42:Z42"/>
+    <mergeCell ref="G42:P42"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="G41:P41"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="G9:AK10">
-    <cfRule type="expression" dxfId="5" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>TEXT(G9,"aaa")="土"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9:AK40">
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>TEXT(G9,"aaa")="日"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:AK40">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>G$11="－"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14269,40 +14251,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:254" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="155" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="108"/>
+      <c r="B1" s="155"/>
       <c r="C1" s="85"/>
-      <c r="F1" s="109" t="s">
+      <c r="F1" s="156" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
-      <c r="V1" s="109"/>
-      <c r="W1" s="109"/>
-      <c r="X1" s="109"/>
-      <c r="Y1" s="109"/>
-      <c r="Z1" s="109"/>
-      <c r="AA1" s="109"/>
-      <c r="AB1" s="109"/>
-      <c r="AC1" s="109"/>
-      <c r="AD1" s="109"/>
-      <c r="AE1" s="109"/>
-      <c r="AF1" s="109"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+      <c r="L1" s="156"/>
+      <c r="M1" s="156"/>
+      <c r="N1" s="156"/>
+      <c r="O1" s="156"/>
+      <c r="P1" s="156"/>
+      <c r="Q1" s="156"/>
+      <c r="R1" s="156"/>
+      <c r="S1" s="156"/>
+      <c r="T1" s="156"/>
+      <c r="U1" s="156"/>
+      <c r="V1" s="156"/>
+      <c r="W1" s="156"/>
+      <c r="X1" s="156"/>
+      <c r="Y1" s="156"/>
+      <c r="Z1" s="156"/>
+      <c r="AA1" s="156"/>
+      <c r="AB1" s="156"/>
+      <c r="AC1" s="156"/>
+      <c r="AD1" s="156"/>
+      <c r="AE1" s="156"/>
+      <c r="AF1" s="156"/>
       <c r="AI1" s="3"/>
       <c r="AJ1" s="3"/>
       <c r="AK1" s="3"/>
@@ -14768,47 +14750,47 @@
       <c r="IO2" s="3"/>
     </row>
     <row r="3" spans="1:254" s="2" customFormat="1" ht="20" customHeight="1" thickBot="1">
-      <c r="A3" s="110" t="s">
+      <c r="A3" s="157" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="111"/>
-      <c r="C3" s="111"/>
-      <c r="D3" s="112"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
       <c r="E3" s="94"/>
       <c r="G3" s="51"/>
       <c r="H3" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="113" t="s">
+      <c r="K3" s="160" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="113"/>
-      <c r="M3" s="113" t="s">
+      <c r="L3" s="160"/>
+      <c r="M3" s="160" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="113"/>
-      <c r="O3" s="113"/>
-      <c r="P3" s="113" t="s">
+      <c r="N3" s="160"/>
+      <c r="O3" s="160"/>
+      <c r="P3" s="160" t="s">
         <v>2</v>
       </c>
-      <c r="Q3" s="113"/>
-      <c r="R3" s="113"/>
+      <c r="Q3" s="160"/>
+      <c r="R3" s="160"/>
       <c r="S3" s="3"/>
-      <c r="T3" s="114" t="s">
+      <c r="T3" s="161" t="s">
         <v>3</v>
       </c>
-      <c r="U3" s="115"/>
-      <c r="V3" s="115"/>
-      <c r="W3" s="115"/>
-      <c r="X3" s="115"/>
-      <c r="Y3" s="115"/>
-      <c r="Z3" s="115"/>
-      <c r="AA3" s="115"/>
-      <c r="AB3" s="115"/>
-      <c r="AC3" s="115"/>
-      <c r="AD3" s="115"/>
-      <c r="AE3" s="115"/>
-      <c r="AF3" s="116"/>
+      <c r="U3" s="162"/>
+      <c r="V3" s="162"/>
+      <c r="W3" s="162"/>
+      <c r="X3" s="162"/>
+      <c r="Y3" s="162"/>
+      <c r="Z3" s="162"/>
+      <c r="AA3" s="162"/>
+      <c r="AB3" s="162"/>
+      <c r="AC3" s="162"/>
+      <c r="AD3" s="162"/>
+      <c r="AE3" s="162"/>
+      <c r="AF3" s="163"/>
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
       <c r="AK3" s="3"/>
@@ -15037,42 +15019,42 @@
       <c r="H4" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="113" t="s">
+      <c r="K4" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="113"/>
-      <c r="M4" s="119">
+      <c r="L4" s="160"/>
+      <c r="M4" s="166">
         <v>46113</v>
       </c>
-      <c r="N4" s="119"/>
-      <c r="O4" s="119"/>
-      <c r="P4" s="113" t="s">
+      <c r="N4" s="166"/>
+      <c r="O4" s="166"/>
+      <c r="P4" s="160" t="s">
         <v>50</v>
       </c>
-      <c r="Q4" s="113"/>
-      <c r="R4" s="113"/>
+      <c r="Q4" s="160"/>
+      <c r="R4" s="160"/>
       <c r="S4" s="3"/>
-      <c r="T4" s="120" t="s">
+      <c r="T4" s="152" t="s">
         <v>5</v>
       </c>
-      <c r="U4" s="121"/>
-      <c r="V4" s="121"/>
-      <c r="W4" s="122"/>
-      <c r="X4" s="120" t="s">
+      <c r="U4" s="153"/>
+      <c r="V4" s="153"/>
+      <c r="W4" s="154"/>
+      <c r="X4" s="152" t="s">
         <v>6</v>
       </c>
-      <c r="Y4" s="121"/>
-      <c r="Z4" s="122"/>
-      <c r="AA4" s="120" t="s">
+      <c r="Y4" s="153"/>
+      <c r="Z4" s="154"/>
+      <c r="AA4" s="152" t="s">
         <v>7</v>
       </c>
-      <c r="AB4" s="121"/>
-      <c r="AC4" s="122"/>
-      <c r="AD4" s="120" t="s">
+      <c r="AB4" s="153"/>
+      <c r="AC4" s="154"/>
+      <c r="AD4" s="152" t="s">
         <v>8</v>
       </c>
-      <c r="AE4" s="121"/>
-      <c r="AF4" s="122"/>
+      <c r="AE4" s="153"/>
+      <c r="AF4" s="154"/>
       <c r="AI4" s="3"/>
       <c r="AJ4" s="3"/>
       <c r="AK4" s="3"/>
@@ -15300,21 +15282,21 @@
         <v>23</v>
       </c>
       <c r="S5" s="3"/>
-      <c r="T5" s="170" t="s">
+      <c r="T5" s="172" t="s">
         <v>64</v>
       </c>
-      <c r="U5" s="171"/>
-      <c r="V5" s="171"/>
-      <c r="W5" s="172"/>
+      <c r="U5" s="173"/>
+      <c r="V5" s="173"/>
+      <c r="W5" s="174"/>
       <c r="X5" s="11"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="12"/>
       <c r="AA5" s="11"/>
       <c r="AB5" s="3"/>
       <c r="AC5" s="12"/>
-      <c r="AD5" s="133"/>
-      <c r="AE5" s="134"/>
-      <c r="AF5" s="135"/>
+      <c r="AD5" s="144"/>
+      <c r="AE5" s="145"/>
+      <c r="AF5" s="146"/>
       <c r="AI5" s="3"/>
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3"/>
@@ -15546,19 +15528,19 @@
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
-      <c r="T6" s="170"/>
-      <c r="U6" s="171"/>
-      <c r="V6" s="171"/>
-      <c r="W6" s="172"/>
+      <c r="T6" s="172"/>
+      <c r="U6" s="173"/>
+      <c r="V6" s="173"/>
+      <c r="W6" s="174"/>
       <c r="X6" s="11"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="12"/>
       <c r="AA6" s="11"/>
       <c r="AB6" s="3"/>
       <c r="AC6" s="12"/>
-      <c r="AD6" s="133"/>
-      <c r="AE6" s="134"/>
-      <c r="AF6" s="135"/>
+      <c r="AD6" s="144"/>
+      <c r="AE6" s="145"/>
+      <c r="AF6" s="146"/>
       <c r="AI6" s="3"/>
       <c r="AJ6" s="3"/>
       <c r="AK6" s="3"/>
@@ -15790,19 +15772,19 @@
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
-      <c r="T7" s="173"/>
-      <c r="U7" s="174"/>
-      <c r="V7" s="174"/>
-      <c r="W7" s="175"/>
+      <c r="T7" s="175"/>
+      <c r="U7" s="176"/>
+      <c r="V7" s="176"/>
+      <c r="W7" s="177"/>
       <c r="X7" s="21"/>
       <c r="Y7" s="22"/>
       <c r="Z7" s="23"/>
       <c r="AA7" s="21"/>
       <c r="AB7" s="22"/>
       <c r="AC7" s="23"/>
-      <c r="AD7" s="136"/>
-      <c r="AE7" s="137"/>
-      <c r="AF7" s="138"/>
+      <c r="AD7" s="147"/>
+      <c r="AE7" s="148"/>
+      <c r="AF7" s="149"/>
       <c r="AG7" s="86"/>
       <c r="AI7" s="3"/>
       <c r="AJ7" s="3"/>
@@ -16319,22 +16301,22 @@
       <c r="R9" s="97" t="s">
         <v>76</v>
       </c>
-      <c r="S9" s="163" t="s">
+      <c r="S9" s="191" t="s">
         <v>78</v>
       </c>
-      <c r="T9" s="164"/>
-      <c r="U9" s="164"/>
-      <c r="V9" s="164"/>
-      <c r="W9" s="164"/>
-      <c r="X9" s="164"/>
-      <c r="Y9" s="164"/>
-      <c r="Z9" s="164"/>
-      <c r="AA9" s="164"/>
-      <c r="AB9" s="164"/>
-      <c r="AC9" s="164"/>
-      <c r="AD9" s="164"/>
-      <c r="AE9" s="164"/>
-      <c r="AF9" s="165"/>
+      <c r="T9" s="192"/>
+      <c r="U9" s="192"/>
+      <c r="V9" s="192"/>
+      <c r="W9" s="192"/>
+      <c r="X9" s="192"/>
+      <c r="Y9" s="192"/>
+      <c r="Z9" s="192"/>
+      <c r="AA9" s="192"/>
+      <c r="AB9" s="192"/>
+      <c r="AC9" s="192"/>
+      <c r="AD9" s="192"/>
+      <c r="AE9" s="192"/>
+      <c r="AF9" s="193"/>
       <c r="AI9" s="3"/>
       <c r="AJ9" s="3"/>
       <c r="AK9" s="3"/>
@@ -16553,8 +16535,8 @@
     </row>
     <row r="10" spans="1:254" s="2" customFormat="1" ht="23" hidden="1" customHeight="1">
       <c r="A10" s="29"/>
-      <c r="B10" s="139"/>
-      <c r="C10" s="140"/>
+      <c r="B10" s="150"/>
+      <c r="C10" s="151"/>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="31"/>
@@ -16880,10 +16862,10 @@
     </row>
     <row r="11" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A11" s="37"/>
-      <c r="B11" s="143" t="s">
+      <c r="B11" s="137" t="s">
         <v>105</v>
       </c>
-      <c r="C11" s="144"/>
+      <c r="C11" s="138"/>
       <c r="D11" s="92"/>
       <c r="E11" s="40"/>
       <c r="F11" s="93"/>
@@ -16899,20 +16881,20 @@
       <c r="P11" s="69"/>
       <c r="Q11" s="69"/>
       <c r="R11" s="69"/>
-      <c r="S11" s="178"/>
-      <c r="T11" s="179"/>
-      <c r="U11" s="179"/>
-      <c r="V11" s="179"/>
-      <c r="W11" s="179"/>
-      <c r="X11" s="179"/>
-      <c r="Y11" s="179"/>
-      <c r="Z11" s="179"/>
-      <c r="AA11" s="179"/>
-      <c r="AB11" s="179"/>
-      <c r="AC11" s="179"/>
-      <c r="AD11" s="179"/>
-      <c r="AE11" s="179"/>
-      <c r="AF11" s="180"/>
+      <c r="S11" s="180"/>
+      <c r="T11" s="181"/>
+      <c r="U11" s="181"/>
+      <c r="V11" s="181"/>
+      <c r="W11" s="181"/>
+      <c r="X11" s="181"/>
+      <c r="Y11" s="181"/>
+      <c r="Z11" s="181"/>
+      <c r="AA11" s="181"/>
+      <c r="AB11" s="181"/>
+      <c r="AC11" s="181"/>
+      <c r="AD11" s="181"/>
+      <c r="AE11" s="181"/>
+      <c r="AF11" s="182"/>
       <c r="AG11" s="69"/>
       <c r="AH11" s="69"/>
       <c r="AI11" s="69"/>
@@ -17138,10 +17120,10 @@
       <c r="A12" s="37">
         <v>1</v>
       </c>
-      <c r="B12" s="147" t="s">
+      <c r="B12" s="135" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="148"/>
+      <c r="C12" s="136"/>
       <c r="D12" s="92" t="s">
         <v>108</v>
       </c>
@@ -17159,20 +17141,20 @@
       <c r="P12" s="69"/>
       <c r="Q12" s="69"/>
       <c r="R12" s="69"/>
-      <c r="S12" s="159"/>
-      <c r="T12" s="160"/>
-      <c r="U12" s="160"/>
-      <c r="V12" s="160"/>
-      <c r="W12" s="160"/>
-      <c r="X12" s="160"/>
-      <c r="Y12" s="160"/>
-      <c r="Z12" s="160"/>
-      <c r="AA12" s="160"/>
-      <c r="AB12" s="160"/>
-      <c r="AC12" s="160"/>
-      <c r="AD12" s="160"/>
-      <c r="AE12" s="160"/>
-      <c r="AF12" s="161"/>
+      <c r="S12" s="183"/>
+      <c r="T12" s="184"/>
+      <c r="U12" s="184"/>
+      <c r="V12" s="184"/>
+      <c r="W12" s="184"/>
+      <c r="X12" s="184"/>
+      <c r="Y12" s="184"/>
+      <c r="Z12" s="184"/>
+      <c r="AA12" s="184"/>
+      <c r="AB12" s="184"/>
+      <c r="AC12" s="184"/>
+      <c r="AD12" s="184"/>
+      <c r="AE12" s="184"/>
+      <c r="AF12" s="185"/>
       <c r="AG12" s="69"/>
       <c r="AH12" s="69"/>
       <c r="AI12" s="69"/>
@@ -17398,10 +17380,10 @@
       <c r="A13" s="37">
         <v>2</v>
       </c>
-      <c r="B13" s="147" t="s">
+      <c r="B13" s="135" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="148"/>
+      <c r="C13" s="136"/>
       <c r="D13" s="92" t="s">
         <v>107</v>
       </c>
@@ -17419,20 +17401,20 @@
       <c r="P13" s="69"/>
       <c r="Q13" s="69"/>
       <c r="R13" s="69"/>
-      <c r="S13" s="159"/>
-      <c r="T13" s="160"/>
-      <c r="U13" s="160"/>
-      <c r="V13" s="160"/>
-      <c r="W13" s="160"/>
-      <c r="X13" s="160"/>
-      <c r="Y13" s="160"/>
-      <c r="Z13" s="160"/>
-      <c r="AA13" s="160"/>
-      <c r="AB13" s="160"/>
-      <c r="AC13" s="160"/>
-      <c r="AD13" s="160"/>
-      <c r="AE13" s="160"/>
-      <c r="AF13" s="161"/>
+      <c r="S13" s="183"/>
+      <c r="T13" s="184"/>
+      <c r="U13" s="184"/>
+      <c r="V13" s="184"/>
+      <c r="W13" s="184"/>
+      <c r="X13" s="184"/>
+      <c r="Y13" s="184"/>
+      <c r="Z13" s="184"/>
+      <c r="AA13" s="184"/>
+      <c r="AB13" s="184"/>
+      <c r="AC13" s="184"/>
+      <c r="AD13" s="184"/>
+      <c r="AE13" s="184"/>
+      <c r="AF13" s="185"/>
       <c r="AG13" s="69"/>
       <c r="AH13" s="69"/>
       <c r="AI13" s="69"/>
@@ -17658,10 +17640,10 @@
       <c r="A14" s="37">
         <v>3</v>
       </c>
-      <c r="B14" s="147" t="s">
+      <c r="B14" s="135" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="148"/>
+      <c r="C14" s="136"/>
       <c r="D14" s="92" t="s">
         <v>107</v>
       </c>
@@ -17679,20 +17661,20 @@
       <c r="P14" s="69"/>
       <c r="Q14" s="69"/>
       <c r="R14" s="69"/>
-      <c r="S14" s="159"/>
-      <c r="T14" s="160"/>
-      <c r="U14" s="160"/>
-      <c r="V14" s="160"/>
-      <c r="W14" s="160"/>
-      <c r="X14" s="160"/>
-      <c r="Y14" s="160"/>
-      <c r="Z14" s="160"/>
-      <c r="AA14" s="160"/>
-      <c r="AB14" s="160"/>
-      <c r="AC14" s="160"/>
-      <c r="AD14" s="160"/>
-      <c r="AE14" s="160"/>
-      <c r="AF14" s="161"/>
+      <c r="S14" s="183"/>
+      <c r="T14" s="184"/>
+      <c r="U14" s="184"/>
+      <c r="V14" s="184"/>
+      <c r="W14" s="184"/>
+      <c r="X14" s="184"/>
+      <c r="Y14" s="184"/>
+      <c r="Z14" s="184"/>
+      <c r="AA14" s="184"/>
+      <c r="AB14" s="184"/>
+      <c r="AC14" s="184"/>
+      <c r="AD14" s="184"/>
+      <c r="AE14" s="184"/>
+      <c r="AF14" s="185"/>
       <c r="AG14" s="69"/>
       <c r="AH14" s="69"/>
       <c r="AI14" s="69"/>
@@ -17918,10 +17900,10 @@
       <c r="A15" s="37">
         <v>4</v>
       </c>
-      <c r="B15" s="147" t="s">
+      <c r="B15" s="135" t="s">
         <v>82</v>
       </c>
-      <c r="C15" s="148"/>
+      <c r="C15" s="136"/>
       <c r="D15" s="92" t="s">
         <v>108</v>
       </c>
@@ -17939,20 +17921,20 @@
       <c r="P15" s="69"/>
       <c r="Q15" s="69"/>
       <c r="R15" s="69"/>
-      <c r="S15" s="159"/>
-      <c r="T15" s="160"/>
-      <c r="U15" s="160"/>
-      <c r="V15" s="160"/>
-      <c r="W15" s="160"/>
-      <c r="X15" s="160"/>
-      <c r="Y15" s="160"/>
-      <c r="Z15" s="160"/>
-      <c r="AA15" s="160"/>
-      <c r="AB15" s="160"/>
-      <c r="AC15" s="160"/>
-      <c r="AD15" s="160"/>
-      <c r="AE15" s="160"/>
-      <c r="AF15" s="161"/>
+      <c r="S15" s="183"/>
+      <c r="T15" s="184"/>
+      <c r="U15" s="184"/>
+      <c r="V15" s="184"/>
+      <c r="W15" s="184"/>
+      <c r="X15" s="184"/>
+      <c r="Y15" s="184"/>
+      <c r="Z15" s="184"/>
+      <c r="AA15" s="184"/>
+      <c r="AB15" s="184"/>
+      <c r="AC15" s="184"/>
+      <c r="AD15" s="184"/>
+      <c r="AE15" s="184"/>
+      <c r="AF15" s="185"/>
       <c r="AG15" s="69"/>
       <c r="AH15" s="69"/>
       <c r="AI15" s="69"/>
@@ -18178,10 +18160,10 @@
       <c r="A16" s="37">
         <v>5</v>
       </c>
-      <c r="B16" s="147" t="s">
+      <c r="B16" s="135" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="148"/>
+      <c r="C16" s="136"/>
       <c r="D16" s="92" t="s">
         <v>108</v>
       </c>
@@ -18199,20 +18181,20 @@
       <c r="P16" s="69"/>
       <c r="Q16" s="69"/>
       <c r="R16" s="69"/>
-      <c r="S16" s="159"/>
-      <c r="T16" s="160"/>
-      <c r="U16" s="160"/>
-      <c r="V16" s="160"/>
-      <c r="W16" s="160"/>
-      <c r="X16" s="160"/>
-      <c r="Y16" s="160"/>
-      <c r="Z16" s="160"/>
-      <c r="AA16" s="160"/>
-      <c r="AB16" s="160"/>
-      <c r="AC16" s="160"/>
-      <c r="AD16" s="160"/>
-      <c r="AE16" s="160"/>
-      <c r="AF16" s="161"/>
+      <c r="S16" s="183"/>
+      <c r="T16" s="184"/>
+      <c r="U16" s="184"/>
+      <c r="V16" s="184"/>
+      <c r="W16" s="184"/>
+      <c r="X16" s="184"/>
+      <c r="Y16" s="184"/>
+      <c r="Z16" s="184"/>
+      <c r="AA16" s="184"/>
+      <c r="AB16" s="184"/>
+      <c r="AC16" s="184"/>
+      <c r="AD16" s="184"/>
+      <c r="AE16" s="184"/>
+      <c r="AF16" s="185"/>
       <c r="AG16" s="69"/>
       <c r="AH16" s="69"/>
       <c r="AI16" s="69"/>
@@ -18438,10 +18420,10 @@
       <c r="A17" s="37">
         <v>6</v>
       </c>
-      <c r="B17" s="147" t="s">
+      <c r="B17" s="135" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="148"/>
+      <c r="C17" s="136"/>
       <c r="D17" s="92" t="s">
         <v>108</v>
       </c>
@@ -18459,20 +18441,20 @@
       <c r="P17" s="69"/>
       <c r="Q17" s="69"/>
       <c r="R17" s="69"/>
-      <c r="S17" s="159"/>
-      <c r="T17" s="160"/>
-      <c r="U17" s="160"/>
-      <c r="V17" s="160"/>
-      <c r="W17" s="160"/>
-      <c r="X17" s="160"/>
-      <c r="Y17" s="160"/>
-      <c r="Z17" s="160"/>
-      <c r="AA17" s="160"/>
-      <c r="AB17" s="160"/>
-      <c r="AC17" s="160"/>
-      <c r="AD17" s="160"/>
-      <c r="AE17" s="160"/>
-      <c r="AF17" s="161"/>
+      <c r="S17" s="183"/>
+      <c r="T17" s="184"/>
+      <c r="U17" s="184"/>
+      <c r="V17" s="184"/>
+      <c r="W17" s="184"/>
+      <c r="X17" s="184"/>
+      <c r="Y17" s="184"/>
+      <c r="Z17" s="184"/>
+      <c r="AA17" s="184"/>
+      <c r="AB17" s="184"/>
+      <c r="AC17" s="184"/>
+      <c r="AD17" s="184"/>
+      <c r="AE17" s="184"/>
+      <c r="AF17" s="185"/>
       <c r="AG17" s="69"/>
       <c r="AH17" s="69"/>
       <c r="AI17" s="69"/>
@@ -18698,10 +18680,10 @@
       <c r="A18" s="37">
         <v>7</v>
       </c>
-      <c r="B18" s="147" t="s">
+      <c r="B18" s="135" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="148"/>
+      <c r="C18" s="136"/>
       <c r="D18" s="92" t="s">
         <v>108</v>
       </c>
@@ -18719,20 +18701,20 @@
       <c r="P18" s="69"/>
       <c r="Q18" s="69"/>
       <c r="R18" s="69"/>
-      <c r="S18" s="159"/>
-      <c r="T18" s="160"/>
-      <c r="U18" s="160"/>
-      <c r="V18" s="160"/>
-      <c r="W18" s="160"/>
-      <c r="X18" s="160"/>
-      <c r="Y18" s="160"/>
-      <c r="Z18" s="160"/>
-      <c r="AA18" s="160"/>
-      <c r="AB18" s="160"/>
-      <c r="AC18" s="160"/>
-      <c r="AD18" s="160"/>
-      <c r="AE18" s="160"/>
-      <c r="AF18" s="161"/>
+      <c r="S18" s="183"/>
+      <c r="T18" s="184"/>
+      <c r="U18" s="184"/>
+      <c r="V18" s="184"/>
+      <c r="W18" s="184"/>
+      <c r="X18" s="184"/>
+      <c r="Y18" s="184"/>
+      <c r="Z18" s="184"/>
+      <c r="AA18" s="184"/>
+      <c r="AB18" s="184"/>
+      <c r="AC18" s="184"/>
+      <c r="AD18" s="184"/>
+      <c r="AE18" s="184"/>
+      <c r="AF18" s="185"/>
       <c r="AG18" s="69"/>
       <c r="AH18" s="69"/>
       <c r="AI18" s="69"/>
@@ -18958,10 +18940,10 @@
       <c r="A19" s="37">
         <v>8</v>
       </c>
-      <c r="B19" s="147" t="s">
+      <c r="B19" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="148"/>
+      <c r="C19" s="136"/>
       <c r="D19" s="92" t="s">
         <v>108</v>
       </c>
@@ -18979,20 +18961,20 @@
       <c r="P19" s="69"/>
       <c r="Q19" s="69"/>
       <c r="R19" s="69"/>
-      <c r="S19" s="159"/>
-      <c r="T19" s="160"/>
-      <c r="U19" s="160"/>
-      <c r="V19" s="160"/>
-      <c r="W19" s="160"/>
-      <c r="X19" s="160"/>
-      <c r="Y19" s="160"/>
-      <c r="Z19" s="160"/>
-      <c r="AA19" s="160"/>
-      <c r="AB19" s="160"/>
-      <c r="AC19" s="160"/>
-      <c r="AD19" s="160"/>
-      <c r="AE19" s="160"/>
-      <c r="AF19" s="161"/>
+      <c r="S19" s="183"/>
+      <c r="T19" s="184"/>
+      <c r="U19" s="184"/>
+      <c r="V19" s="184"/>
+      <c r="W19" s="184"/>
+      <c r="X19" s="184"/>
+      <c r="Y19" s="184"/>
+      <c r="Z19" s="184"/>
+      <c r="AA19" s="184"/>
+      <c r="AB19" s="184"/>
+      <c r="AC19" s="184"/>
+      <c r="AD19" s="184"/>
+      <c r="AE19" s="184"/>
+      <c r="AF19" s="185"/>
       <c r="AG19" s="69"/>
       <c r="AH19" s="69"/>
       <c r="AI19" s="69"/>
@@ -19216,10 +19198,10 @@
     </row>
     <row r="20" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A20" s="34"/>
-      <c r="B20" s="176" t="s">
+      <c r="B20" s="178" t="s">
         <v>120</v>
       </c>
-      <c r="C20" s="177"/>
+      <c r="C20" s="179"/>
       <c r="D20" s="35"/>
       <c r="E20" s="35"/>
       <c r="F20" s="36"/>
@@ -19235,20 +19217,20 @@
       <c r="P20" s="68"/>
       <c r="Q20" s="68"/>
       <c r="R20" s="68"/>
-      <c r="S20" s="159"/>
-      <c r="T20" s="160"/>
-      <c r="U20" s="160"/>
-      <c r="V20" s="160"/>
-      <c r="W20" s="160"/>
-      <c r="X20" s="160"/>
-      <c r="Y20" s="160"/>
-      <c r="Z20" s="160"/>
-      <c r="AA20" s="160"/>
-      <c r="AB20" s="160"/>
-      <c r="AC20" s="160"/>
-      <c r="AD20" s="160"/>
-      <c r="AE20" s="160"/>
-      <c r="AF20" s="161"/>
+      <c r="S20" s="183"/>
+      <c r="T20" s="184"/>
+      <c r="U20" s="184"/>
+      <c r="V20" s="184"/>
+      <c r="W20" s="184"/>
+      <c r="X20" s="184"/>
+      <c r="Y20" s="184"/>
+      <c r="Z20" s="184"/>
+      <c r="AA20" s="184"/>
+      <c r="AB20" s="184"/>
+      <c r="AC20" s="184"/>
+      <c r="AD20" s="184"/>
+      <c r="AE20" s="184"/>
+      <c r="AF20" s="185"/>
       <c r="AI20" s="3"/>
       <c r="AJ20" s="3"/>
       <c r="AK20" s="3"/>
@@ -19469,10 +19451,10 @@
       <c r="A21" s="37">
         <v>1</v>
       </c>
-      <c r="B21" s="104" t="s">
+      <c r="B21" s="117" t="s">
         <v>87</v>
       </c>
-      <c r="C21" s="105"/>
+      <c r="C21" s="118"/>
       <c r="D21" s="92"/>
       <c r="E21" s="92" t="s">
         <v>42</v>
@@ -19490,20 +19472,20 @@
       <c r="P21" s="69"/>
       <c r="Q21" s="69"/>
       <c r="R21" s="69"/>
-      <c r="S21" s="159"/>
-      <c r="T21" s="160"/>
-      <c r="U21" s="160"/>
-      <c r="V21" s="160"/>
-      <c r="W21" s="160"/>
-      <c r="X21" s="160"/>
-      <c r="Y21" s="160"/>
-      <c r="Z21" s="160"/>
-      <c r="AA21" s="160"/>
-      <c r="AB21" s="160"/>
-      <c r="AC21" s="160"/>
-      <c r="AD21" s="160"/>
-      <c r="AE21" s="160"/>
-      <c r="AF21" s="161"/>
+      <c r="S21" s="183"/>
+      <c r="T21" s="184"/>
+      <c r="U21" s="184"/>
+      <c r="V21" s="184"/>
+      <c r="W21" s="184"/>
+      <c r="X21" s="184"/>
+      <c r="Y21" s="184"/>
+      <c r="Z21" s="184"/>
+      <c r="AA21" s="184"/>
+      <c r="AB21" s="184"/>
+      <c r="AC21" s="184"/>
+      <c r="AD21" s="184"/>
+      <c r="AE21" s="184"/>
+      <c r="AF21" s="185"/>
       <c r="AI21" s="3"/>
       <c r="AJ21" s="3"/>
       <c r="AK21" s="3"/>
@@ -19724,10 +19706,10 @@
       <c r="A22" s="37">
         <v>2</v>
       </c>
-      <c r="B22" s="104" t="s">
+      <c r="B22" s="117" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="105"/>
+      <c r="C22" s="118"/>
       <c r="D22" s="92"/>
       <c r="E22" s="92" t="s">
         <v>43</v>
@@ -19745,20 +19727,20 @@
       <c r="P22" s="69"/>
       <c r="Q22" s="69"/>
       <c r="R22" s="69"/>
-      <c r="S22" s="159"/>
-      <c r="T22" s="160"/>
-      <c r="U22" s="160"/>
-      <c r="V22" s="160"/>
-      <c r="W22" s="160"/>
-      <c r="X22" s="160"/>
-      <c r="Y22" s="160"/>
-      <c r="Z22" s="160"/>
-      <c r="AA22" s="160"/>
-      <c r="AB22" s="160"/>
-      <c r="AC22" s="160"/>
-      <c r="AD22" s="160"/>
-      <c r="AE22" s="160"/>
-      <c r="AF22" s="161"/>
+      <c r="S22" s="183"/>
+      <c r="T22" s="184"/>
+      <c r="U22" s="184"/>
+      <c r="V22" s="184"/>
+      <c r="W22" s="184"/>
+      <c r="X22" s="184"/>
+      <c r="Y22" s="184"/>
+      <c r="Z22" s="184"/>
+      <c r="AA22" s="184"/>
+      <c r="AB22" s="184"/>
+      <c r="AC22" s="184"/>
+      <c r="AD22" s="184"/>
+      <c r="AE22" s="184"/>
+      <c r="AF22" s="185"/>
       <c r="AI22" s="3"/>
       <c r="AJ22" s="3"/>
       <c r="AK22" s="3"/>
@@ -19979,10 +19961,10 @@
       <c r="A23" s="101" t="s">
         <v>111</v>
       </c>
-      <c r="B23" s="168" t="s">
+      <c r="B23" s="186" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="169"/>
+      <c r="C23" s="187"/>
       <c r="D23" s="92" t="s">
         <v>110</v>
       </c>
@@ -20002,20 +19984,20 @@
       <c r="P23" s="69"/>
       <c r="Q23" s="69"/>
       <c r="R23" s="69"/>
-      <c r="S23" s="159"/>
-      <c r="T23" s="160"/>
-      <c r="U23" s="160"/>
-      <c r="V23" s="160"/>
-      <c r="W23" s="160"/>
-      <c r="X23" s="160"/>
-      <c r="Y23" s="160"/>
-      <c r="Z23" s="160"/>
-      <c r="AA23" s="160"/>
-      <c r="AB23" s="160"/>
-      <c r="AC23" s="160"/>
-      <c r="AD23" s="160"/>
-      <c r="AE23" s="160"/>
-      <c r="AF23" s="161"/>
+      <c r="S23" s="183"/>
+      <c r="T23" s="184"/>
+      <c r="U23" s="184"/>
+      <c r="V23" s="184"/>
+      <c r="W23" s="184"/>
+      <c r="X23" s="184"/>
+      <c r="Y23" s="184"/>
+      <c r="Z23" s="184"/>
+      <c r="AA23" s="184"/>
+      <c r="AB23" s="184"/>
+      <c r="AC23" s="184"/>
+      <c r="AD23" s="184"/>
+      <c r="AE23" s="184"/>
+      <c r="AF23" s="185"/>
       <c r="AI23" s="3"/>
       <c r="AJ23" s="3"/>
       <c r="AK23" s="3"/>
@@ -20236,10 +20218,10 @@
       <c r="A24" s="101" t="s">
         <v>112</v>
       </c>
-      <c r="B24" s="104" t="s">
+      <c r="B24" s="117" t="s">
         <v>113</v>
       </c>
-      <c r="C24" s="105"/>
+      <c r="C24" s="118"/>
       <c r="D24" s="92" t="s">
         <v>110</v>
       </c>
@@ -20259,20 +20241,20 @@
       <c r="P24" s="69"/>
       <c r="Q24" s="69"/>
       <c r="R24" s="69"/>
-      <c r="S24" s="159"/>
-      <c r="T24" s="160"/>
-      <c r="U24" s="160"/>
-      <c r="V24" s="160"/>
-      <c r="W24" s="160"/>
-      <c r="X24" s="160"/>
-      <c r="Y24" s="160"/>
-      <c r="Z24" s="160"/>
-      <c r="AA24" s="160"/>
-      <c r="AB24" s="160"/>
-      <c r="AC24" s="160"/>
-      <c r="AD24" s="160"/>
-      <c r="AE24" s="160"/>
-      <c r="AF24" s="161"/>
+      <c r="S24" s="183"/>
+      <c r="T24" s="184"/>
+      <c r="U24" s="184"/>
+      <c r="V24" s="184"/>
+      <c r="W24" s="184"/>
+      <c r="X24" s="184"/>
+      <c r="Y24" s="184"/>
+      <c r="Z24" s="184"/>
+      <c r="AA24" s="184"/>
+      <c r="AB24" s="184"/>
+      <c r="AC24" s="184"/>
+      <c r="AD24" s="184"/>
+      <c r="AE24" s="184"/>
+      <c r="AF24" s="185"/>
       <c r="AI24" s="3"/>
       <c r="AJ24" s="3"/>
       <c r="AK24" s="3"/>
@@ -20493,10 +20475,10 @@
       <c r="A25" s="37">
         <v>4</v>
       </c>
-      <c r="B25" s="104" t="s">
+      <c r="B25" s="117" t="s">
         <v>89</v>
       </c>
-      <c r="C25" s="105"/>
+      <c r="C25" s="118"/>
       <c r="D25" s="92"/>
       <c r="E25" s="92" t="s">
         <v>45</v>
@@ -20514,20 +20496,20 @@
       <c r="P25" s="69"/>
       <c r="Q25" s="69"/>
       <c r="R25" s="69"/>
-      <c r="S25" s="159"/>
-      <c r="T25" s="160"/>
-      <c r="U25" s="160"/>
-      <c r="V25" s="160"/>
-      <c r="W25" s="160"/>
-      <c r="X25" s="160"/>
-      <c r="Y25" s="160"/>
-      <c r="Z25" s="160"/>
-      <c r="AA25" s="160"/>
-      <c r="AB25" s="160"/>
-      <c r="AC25" s="160"/>
-      <c r="AD25" s="160"/>
-      <c r="AE25" s="160"/>
-      <c r="AF25" s="161"/>
+      <c r="S25" s="183"/>
+      <c r="T25" s="184"/>
+      <c r="U25" s="184"/>
+      <c r="V25" s="184"/>
+      <c r="W25" s="184"/>
+      <c r="X25" s="184"/>
+      <c r="Y25" s="184"/>
+      <c r="Z25" s="184"/>
+      <c r="AA25" s="184"/>
+      <c r="AB25" s="184"/>
+      <c r="AC25" s="184"/>
+      <c r="AD25" s="184"/>
+      <c r="AE25" s="184"/>
+      <c r="AF25" s="185"/>
       <c r="AI25" s="3"/>
       <c r="AJ25" s="3"/>
       <c r="AK25" s="3"/>
@@ -20748,10 +20730,10 @@
       <c r="A26" s="37">
         <v>5</v>
       </c>
-      <c r="B26" s="104" t="s">
+      <c r="B26" s="117" t="s">
         <v>114</v>
       </c>
-      <c r="C26" s="105"/>
+      <c r="C26" s="118"/>
       <c r="D26" s="92"/>
       <c r="E26" s="92" t="s">
         <v>41</v>
@@ -20769,20 +20751,20 @@
       <c r="P26" s="69"/>
       <c r="Q26" s="69"/>
       <c r="R26" s="69"/>
-      <c r="S26" s="159"/>
-      <c r="T26" s="160"/>
-      <c r="U26" s="160"/>
-      <c r="V26" s="160"/>
-      <c r="W26" s="160"/>
-      <c r="X26" s="160"/>
-      <c r="Y26" s="160"/>
-      <c r="Z26" s="160"/>
-      <c r="AA26" s="160"/>
-      <c r="AB26" s="160"/>
-      <c r="AC26" s="160"/>
-      <c r="AD26" s="160"/>
-      <c r="AE26" s="160"/>
-      <c r="AF26" s="161"/>
+      <c r="S26" s="183"/>
+      <c r="T26" s="184"/>
+      <c r="U26" s="184"/>
+      <c r="V26" s="184"/>
+      <c r="W26" s="184"/>
+      <c r="X26" s="184"/>
+      <c r="Y26" s="184"/>
+      <c r="Z26" s="184"/>
+      <c r="AA26" s="184"/>
+      <c r="AB26" s="184"/>
+      <c r="AC26" s="184"/>
+      <c r="AD26" s="184"/>
+      <c r="AE26" s="184"/>
+      <c r="AF26" s="185"/>
       <c r="AI26" s="3"/>
       <c r="AJ26" s="3"/>
       <c r="AK26" s="3"/>
@@ -21003,10 +20985,10 @@
       <c r="A27" s="37">
         <v>6</v>
       </c>
-      <c r="B27" s="104" t="s">
+      <c r="B27" s="117" t="s">
         <v>116</v>
       </c>
-      <c r="C27" s="105"/>
+      <c r="C27" s="118"/>
       <c r="D27" s="92"/>
       <c r="E27" s="92" t="s">
         <v>41</v>
@@ -21024,20 +21006,20 @@
       <c r="P27" s="69"/>
       <c r="Q27" s="69"/>
       <c r="R27" s="69"/>
-      <c r="S27" s="159"/>
-      <c r="T27" s="160"/>
-      <c r="U27" s="160"/>
-      <c r="V27" s="160"/>
-      <c r="W27" s="160"/>
-      <c r="X27" s="160"/>
-      <c r="Y27" s="160"/>
-      <c r="Z27" s="160"/>
-      <c r="AA27" s="160"/>
-      <c r="AB27" s="160"/>
-      <c r="AC27" s="160"/>
-      <c r="AD27" s="160"/>
-      <c r="AE27" s="160"/>
-      <c r="AF27" s="161"/>
+      <c r="S27" s="183"/>
+      <c r="T27" s="184"/>
+      <c r="U27" s="184"/>
+      <c r="V27" s="184"/>
+      <c r="W27" s="184"/>
+      <c r="X27" s="184"/>
+      <c r="Y27" s="184"/>
+      <c r="Z27" s="184"/>
+      <c r="AA27" s="184"/>
+      <c r="AB27" s="184"/>
+      <c r="AC27" s="184"/>
+      <c r="AD27" s="184"/>
+      <c r="AE27" s="184"/>
+      <c r="AF27" s="185"/>
       <c r="AI27" s="3"/>
       <c r="AJ27" s="3"/>
       <c r="AK27" s="3"/>
@@ -21258,10 +21240,10 @@
       <c r="A28" s="37">
         <v>7</v>
       </c>
-      <c r="B28" s="104" t="s">
+      <c r="B28" s="117" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="105"/>
+      <c r="C28" s="118"/>
       <c r="D28" s="92"/>
       <c r="E28" s="92" t="s">
         <v>40</v>
@@ -21279,20 +21261,20 @@
       <c r="P28" s="69"/>
       <c r="Q28" s="69"/>
       <c r="R28" s="69"/>
-      <c r="S28" s="159"/>
-      <c r="T28" s="160"/>
-      <c r="U28" s="160"/>
-      <c r="V28" s="160"/>
-      <c r="W28" s="160"/>
-      <c r="X28" s="160"/>
-      <c r="Y28" s="160"/>
-      <c r="Z28" s="160"/>
-      <c r="AA28" s="160"/>
-      <c r="AB28" s="160"/>
-      <c r="AC28" s="160"/>
-      <c r="AD28" s="160"/>
-      <c r="AE28" s="160"/>
-      <c r="AF28" s="161"/>
+      <c r="S28" s="183"/>
+      <c r="T28" s="184"/>
+      <c r="U28" s="184"/>
+      <c r="V28" s="184"/>
+      <c r="W28" s="184"/>
+      <c r="X28" s="184"/>
+      <c r="Y28" s="184"/>
+      <c r="Z28" s="184"/>
+      <c r="AA28" s="184"/>
+      <c r="AB28" s="184"/>
+      <c r="AC28" s="184"/>
+      <c r="AD28" s="184"/>
+      <c r="AE28" s="184"/>
+      <c r="AF28" s="185"/>
       <c r="AI28" s="3"/>
       <c r="AJ28" s="3"/>
       <c r="AK28" s="3"/>
@@ -21511,8 +21493,8 @@
     </row>
     <row r="29" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A29" s="37"/>
-      <c r="B29" s="104"/>
-      <c r="C29" s="105"/>
+      <c r="B29" s="117"/>
+      <c r="C29" s="118"/>
       <c r="D29" s="92"/>
       <c r="E29" s="92" t="s">
         <v>40</v>
@@ -21530,20 +21512,20 @@
       <c r="P29" s="69"/>
       <c r="Q29" s="69"/>
       <c r="R29" s="69"/>
-      <c r="S29" s="159"/>
-      <c r="T29" s="160"/>
-      <c r="U29" s="160"/>
-      <c r="V29" s="160"/>
-      <c r="W29" s="160"/>
-      <c r="X29" s="160"/>
-      <c r="Y29" s="160"/>
-      <c r="Z29" s="160"/>
-      <c r="AA29" s="160"/>
-      <c r="AB29" s="160"/>
-      <c r="AC29" s="160"/>
-      <c r="AD29" s="160"/>
-      <c r="AE29" s="160"/>
-      <c r="AF29" s="161"/>
+      <c r="S29" s="183"/>
+      <c r="T29" s="184"/>
+      <c r="U29" s="184"/>
+      <c r="V29" s="184"/>
+      <c r="W29" s="184"/>
+      <c r="X29" s="184"/>
+      <c r="Y29" s="184"/>
+      <c r="Z29" s="184"/>
+      <c r="AA29" s="184"/>
+      <c r="AB29" s="184"/>
+      <c r="AC29" s="184"/>
+      <c r="AD29" s="184"/>
+      <c r="AE29" s="184"/>
+      <c r="AF29" s="185"/>
       <c r="AI29" s="3"/>
       <c r="AJ29" s="3"/>
       <c r="AK29" s="3"/>
@@ -21762,10 +21744,10 @@
     </row>
     <row r="30" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A30" s="37"/>
-      <c r="B30" s="143" t="s">
+      <c r="B30" s="137" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="144"/>
+      <c r="C30" s="138"/>
       <c r="D30" s="92"/>
       <c r="E30" s="92"/>
       <c r="F30" s="36"/>
@@ -21781,20 +21763,20 @@
       <c r="P30" s="69"/>
       <c r="Q30" s="69"/>
       <c r="R30" s="69"/>
-      <c r="S30" s="159"/>
-      <c r="T30" s="160"/>
-      <c r="U30" s="160"/>
-      <c r="V30" s="160"/>
-      <c r="W30" s="160"/>
-      <c r="X30" s="160"/>
-      <c r="Y30" s="160"/>
-      <c r="Z30" s="160"/>
-      <c r="AA30" s="160"/>
-      <c r="AB30" s="160"/>
-      <c r="AC30" s="160"/>
-      <c r="AD30" s="160"/>
-      <c r="AE30" s="160"/>
-      <c r="AF30" s="161"/>
+      <c r="S30" s="183"/>
+      <c r="T30" s="184"/>
+      <c r="U30" s="184"/>
+      <c r="V30" s="184"/>
+      <c r="W30" s="184"/>
+      <c r="X30" s="184"/>
+      <c r="Y30" s="184"/>
+      <c r="Z30" s="184"/>
+      <c r="AA30" s="184"/>
+      <c r="AB30" s="184"/>
+      <c r="AC30" s="184"/>
+      <c r="AD30" s="184"/>
+      <c r="AE30" s="184"/>
+      <c r="AF30" s="185"/>
       <c r="AI30" s="3"/>
       <c r="AJ30" s="3"/>
       <c r="AK30" s="3"/>
@@ -22013,11 +21995,11 @@
     </row>
     <row r="31" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A31" s="37"/>
-      <c r="B31" s="104" t="s">
+      <c r="B31" s="117" t="s">
         <v>92</v>
       </c>
-      <c r="C31" s="105"/>
-      <c r="D31" s="158" t="s">
+      <c r="C31" s="118"/>
+      <c r="D31" s="124" t="s">
         <v>117</v>
       </c>
       <c r="E31" s="92"/>
@@ -22034,20 +22016,20 @@
       <c r="P31" s="69"/>
       <c r="Q31" s="69"/>
       <c r="R31" s="69"/>
-      <c r="S31" s="159"/>
-      <c r="T31" s="160"/>
-      <c r="U31" s="160"/>
-      <c r="V31" s="160"/>
-      <c r="W31" s="160"/>
-      <c r="X31" s="160"/>
-      <c r="Y31" s="160"/>
-      <c r="Z31" s="160"/>
-      <c r="AA31" s="160"/>
-      <c r="AB31" s="160"/>
-      <c r="AC31" s="160"/>
-      <c r="AD31" s="160"/>
-      <c r="AE31" s="160"/>
-      <c r="AF31" s="161"/>
+      <c r="S31" s="183"/>
+      <c r="T31" s="184"/>
+      <c r="U31" s="184"/>
+      <c r="V31" s="184"/>
+      <c r="W31" s="184"/>
+      <c r="X31" s="184"/>
+      <c r="Y31" s="184"/>
+      <c r="Z31" s="184"/>
+      <c r="AA31" s="184"/>
+      <c r="AB31" s="184"/>
+      <c r="AC31" s="184"/>
+      <c r="AD31" s="184"/>
+      <c r="AE31" s="184"/>
+      <c r="AF31" s="185"/>
       <c r="AI31" s="3"/>
       <c r="AJ31" s="3"/>
       <c r="AK31" s="3"/>
@@ -22266,11 +22248,11 @@
     </row>
     <row r="32" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A32" s="37"/>
-      <c r="B32" s="104" t="s">
+      <c r="B32" s="117" t="s">
         <v>93</v>
       </c>
-      <c r="C32" s="105"/>
-      <c r="D32" s="106"/>
+      <c r="C32" s="118"/>
+      <c r="D32" s="125"/>
       <c r="E32" s="92" t="s">
         <v>47</v>
       </c>
@@ -22287,20 +22269,20 @@
       <c r="P32" s="68"/>
       <c r="Q32" s="68"/>
       <c r="R32" s="68"/>
-      <c r="S32" s="159"/>
-      <c r="T32" s="160"/>
-      <c r="U32" s="160"/>
-      <c r="V32" s="160"/>
-      <c r="W32" s="160"/>
-      <c r="X32" s="160"/>
-      <c r="Y32" s="160"/>
-      <c r="Z32" s="160"/>
-      <c r="AA32" s="160"/>
-      <c r="AB32" s="160"/>
-      <c r="AC32" s="160"/>
-      <c r="AD32" s="160"/>
-      <c r="AE32" s="160"/>
-      <c r="AF32" s="161"/>
+      <c r="S32" s="183"/>
+      <c r="T32" s="184"/>
+      <c r="U32" s="184"/>
+      <c r="V32" s="184"/>
+      <c r="W32" s="184"/>
+      <c r="X32" s="184"/>
+      <c r="Y32" s="184"/>
+      <c r="Z32" s="184"/>
+      <c r="AA32" s="184"/>
+      <c r="AB32" s="184"/>
+      <c r="AC32" s="184"/>
+      <c r="AD32" s="184"/>
+      <c r="AE32" s="184"/>
+      <c r="AF32" s="185"/>
       <c r="AI32" s="3"/>
       <c r="AJ32" s="3"/>
       <c r="AK32" s="3"/>
@@ -22519,11 +22501,11 @@
     </row>
     <row r="33" spans="1:249" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A33" s="37"/>
-      <c r="B33" s="104" t="s">
+      <c r="B33" s="117" t="s">
         <v>94</v>
       </c>
-      <c r="C33" s="105"/>
-      <c r="D33" s="107"/>
+      <c r="C33" s="118"/>
+      <c r="D33" s="126"/>
       <c r="E33" s="92"/>
       <c r="F33" s="36"/>
       <c r="G33" s="68"/>
@@ -22538,20 +22520,20 @@
       <c r="P33" s="68"/>
       <c r="Q33" s="68"/>
       <c r="R33" s="68"/>
-      <c r="S33" s="159"/>
-      <c r="T33" s="160"/>
-      <c r="U33" s="160"/>
-      <c r="V33" s="160"/>
-      <c r="W33" s="160"/>
-      <c r="X33" s="160"/>
-      <c r="Y33" s="160"/>
-      <c r="Z33" s="160"/>
-      <c r="AA33" s="160"/>
-      <c r="AB33" s="160"/>
-      <c r="AC33" s="160"/>
-      <c r="AD33" s="160"/>
-      <c r="AE33" s="160"/>
-      <c r="AF33" s="161"/>
+      <c r="S33" s="183"/>
+      <c r="T33" s="184"/>
+      <c r="U33" s="184"/>
+      <c r="V33" s="184"/>
+      <c r="W33" s="184"/>
+      <c r="X33" s="184"/>
+      <c r="Y33" s="184"/>
+      <c r="Z33" s="184"/>
+      <c r="AA33" s="184"/>
+      <c r="AB33" s="184"/>
+      <c r="AC33" s="184"/>
+      <c r="AD33" s="184"/>
+      <c r="AE33" s="184"/>
+      <c r="AF33" s="185"/>
       <c r="AI33" s="3"/>
       <c r="AJ33" s="3"/>
       <c r="AK33" s="3"/>
@@ -22770,10 +22752,10 @@
     </row>
     <row r="34" spans="1:249" s="2" customFormat="1" ht="28.25" customHeight="1">
       <c r="A34" s="38"/>
-      <c r="B34" s="143" t="s">
+      <c r="B34" s="137" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="144"/>
+      <c r="C34" s="138"/>
       <c r="D34" s="35"/>
       <c r="E34" s="35"/>
       <c r="F34" s="39"/>
@@ -22789,20 +22771,20 @@
       <c r="P34" s="68"/>
       <c r="Q34" s="68"/>
       <c r="R34" s="68"/>
-      <c r="S34" s="159"/>
-      <c r="T34" s="160"/>
-      <c r="U34" s="160"/>
-      <c r="V34" s="160"/>
-      <c r="W34" s="160"/>
-      <c r="X34" s="160"/>
-      <c r="Y34" s="160"/>
-      <c r="Z34" s="160"/>
-      <c r="AA34" s="160"/>
-      <c r="AB34" s="160"/>
-      <c r="AC34" s="160"/>
-      <c r="AD34" s="160"/>
-      <c r="AE34" s="160"/>
-      <c r="AF34" s="161"/>
+      <c r="S34" s="183"/>
+      <c r="T34" s="184"/>
+      <c r="U34" s="184"/>
+      <c r="V34" s="184"/>
+      <c r="W34" s="184"/>
+      <c r="X34" s="184"/>
+      <c r="Y34" s="184"/>
+      <c r="Z34" s="184"/>
+      <c r="AA34" s="184"/>
+      <c r="AB34" s="184"/>
+      <c r="AC34" s="184"/>
+      <c r="AD34" s="184"/>
+      <c r="AE34" s="184"/>
+      <c r="AF34" s="185"/>
       <c r="AI34" s="3"/>
       <c r="AJ34" s="3"/>
       <c r="AK34" s="3"/>
@@ -23023,15 +23005,15 @@
       <c r="A35" s="37">
         <v>1</v>
       </c>
-      <c r="B35" s="141" t="s">
+      <c r="B35" s="122" t="s">
         <v>104</v>
       </c>
-      <c r="C35" s="142"/>
+      <c r="C35" s="123"/>
       <c r="D35" s="96"/>
       <c r="E35" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="F35" s="158" t="s">
+      <c r="F35" s="124" t="s">
         <v>95</v>
       </c>
       <c r="G35" s="69"/>
@@ -23046,20 +23028,20 @@
       <c r="P35" s="69"/>
       <c r="Q35" s="69"/>
       <c r="R35" s="69"/>
-      <c r="S35" s="159"/>
-      <c r="T35" s="160"/>
-      <c r="U35" s="160"/>
-      <c r="V35" s="160"/>
-      <c r="W35" s="160"/>
-      <c r="X35" s="160"/>
-      <c r="Y35" s="160"/>
-      <c r="Z35" s="160"/>
-      <c r="AA35" s="160"/>
-      <c r="AB35" s="160"/>
-      <c r="AC35" s="160"/>
-      <c r="AD35" s="160"/>
-      <c r="AE35" s="160"/>
-      <c r="AF35" s="161"/>
+      <c r="S35" s="183"/>
+      <c r="T35" s="184"/>
+      <c r="U35" s="184"/>
+      <c r="V35" s="184"/>
+      <c r="W35" s="184"/>
+      <c r="X35" s="184"/>
+      <c r="Y35" s="184"/>
+      <c r="Z35" s="184"/>
+      <c r="AA35" s="184"/>
+      <c r="AB35" s="184"/>
+      <c r="AC35" s="184"/>
+      <c r="AD35" s="184"/>
+      <c r="AE35" s="184"/>
+      <c r="AF35" s="185"/>
       <c r="AI35" s="3"/>
       <c r="AJ35" s="3"/>
       <c r="AK35" s="3"/>
@@ -23280,13 +23262,13 @@
       <c r="A36" s="37">
         <v>2</v>
       </c>
-      <c r="B36" s="104"/>
-      <c r="C36" s="105"/>
+      <c r="B36" s="117"/>
+      <c r="C36" s="118"/>
       <c r="D36" s="96"/>
       <c r="E36" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="F36" s="106"/>
+      <c r="F36" s="125"/>
       <c r="G36" s="68"/>
       <c r="H36" s="68"/>
       <c r="I36" s="68"/>
@@ -23299,20 +23281,20 @@
       <c r="P36" s="68"/>
       <c r="Q36" s="68"/>
       <c r="R36" s="68"/>
-      <c r="S36" s="159"/>
-      <c r="T36" s="160"/>
-      <c r="U36" s="160"/>
-      <c r="V36" s="160"/>
-      <c r="W36" s="160"/>
-      <c r="X36" s="160"/>
-      <c r="Y36" s="160"/>
-      <c r="Z36" s="160"/>
-      <c r="AA36" s="160"/>
-      <c r="AB36" s="160"/>
-      <c r="AC36" s="160"/>
-      <c r="AD36" s="160"/>
-      <c r="AE36" s="160"/>
-      <c r="AF36" s="161"/>
+      <c r="S36" s="183"/>
+      <c r="T36" s="184"/>
+      <c r="U36" s="184"/>
+      <c r="V36" s="184"/>
+      <c r="W36" s="184"/>
+      <c r="X36" s="184"/>
+      <c r="Y36" s="184"/>
+      <c r="Z36" s="184"/>
+      <c r="AA36" s="184"/>
+      <c r="AB36" s="184"/>
+      <c r="AC36" s="184"/>
+      <c r="AD36" s="184"/>
+      <c r="AE36" s="184"/>
+      <c r="AF36" s="185"/>
       <c r="AI36" s="3"/>
       <c r="AJ36" s="3"/>
       <c r="AK36" s="3"/>
@@ -23533,11 +23515,11 @@
       <c r="A37" s="37">
         <v>3</v>
       </c>
-      <c r="B37" s="141"/>
-      <c r="C37" s="142"/>
+      <c r="B37" s="122"/>
+      <c r="C37" s="123"/>
       <c r="D37" s="92"/>
       <c r="E37" s="35"/>
-      <c r="F37" s="106"/>
+      <c r="F37" s="125"/>
       <c r="G37" s="68"/>
       <c r="H37" s="68"/>
       <c r="I37" s="68"/>
@@ -23550,20 +23532,20 @@
       <c r="P37" s="68"/>
       <c r="Q37" s="68"/>
       <c r="R37" s="68"/>
-      <c r="S37" s="159"/>
-      <c r="T37" s="160"/>
-      <c r="U37" s="160"/>
-      <c r="V37" s="160"/>
-      <c r="W37" s="160"/>
-      <c r="X37" s="160"/>
-      <c r="Y37" s="160"/>
-      <c r="Z37" s="160"/>
-      <c r="AA37" s="160"/>
-      <c r="AB37" s="160"/>
-      <c r="AC37" s="160"/>
-      <c r="AD37" s="160"/>
-      <c r="AE37" s="160"/>
-      <c r="AF37" s="161"/>
+      <c r="S37" s="183"/>
+      <c r="T37" s="184"/>
+      <c r="U37" s="184"/>
+      <c r="V37" s="184"/>
+      <c r="W37" s="184"/>
+      <c r="X37" s="184"/>
+      <c r="Y37" s="184"/>
+      <c r="Z37" s="184"/>
+      <c r="AA37" s="184"/>
+      <c r="AB37" s="184"/>
+      <c r="AC37" s="184"/>
+      <c r="AD37" s="184"/>
+      <c r="AE37" s="184"/>
+      <c r="AF37" s="185"/>
       <c r="AI37" s="3"/>
       <c r="AJ37" s="3"/>
       <c r="AK37" s="3"/>
@@ -23782,10 +23764,10 @@
     </row>
     <row r="38" spans="1:249" s="2" customFormat="1" ht="42" customHeight="1" thickBot="1">
       <c r="A38" s="41"/>
-      <c r="B38" s="145" t="s">
+      <c r="B38" s="133" t="s">
         <v>63</v>
       </c>
-      <c r="C38" s="146"/>
+      <c r="C38" s="134"/>
       <c r="D38" s="42" t="s">
         <v>16</v>
       </c>
@@ -24043,29 +24025,29 @@
       <c r="E39" s="44"/>
       <c r="F39" s="57"/>
       <c r="G39" s="75"/>
-      <c r="H39" s="167"/>
-      <c r="I39" s="167"/>
-      <c r="J39" s="167"/>
-      <c r="K39" s="167"/>
+      <c r="H39" s="188"/>
+      <c r="I39" s="188"/>
+      <c r="J39" s="188"/>
+      <c r="K39" s="188"/>
       <c r="L39" s="76"/>
       <c r="M39" s="75"/>
-      <c r="N39" s="167"/>
-      <c r="O39" s="167"/>
-      <c r="P39" s="167"/>
-      <c r="Q39" s="167"/>
+      <c r="N39" s="188"/>
+      <c r="O39" s="188"/>
+      <c r="P39" s="188"/>
+      <c r="Q39" s="188"/>
       <c r="R39" s="76"/>
       <c r="S39" s="75"/>
-      <c r="T39" s="167"/>
-      <c r="U39" s="167"/>
-      <c r="V39" s="167"/>
+      <c r="T39" s="188"/>
+      <c r="U39" s="188"/>
+      <c r="V39" s="188"/>
       <c r="W39" s="75"/>
-      <c r="X39" s="167"/>
-      <c r="Y39" s="167"/>
-      <c r="Z39" s="167"/>
+      <c r="X39" s="188"/>
+      <c r="Y39" s="188"/>
+      <c r="Z39" s="188"/>
       <c r="AA39" s="76"/>
       <c r="AB39" s="75"/>
-      <c r="AC39" s="167"/>
-      <c r="AD39" s="167"/>
+      <c r="AC39" s="188"/>
+      <c r="AD39" s="188"/>
       <c r="AE39" s="55"/>
       <c r="AF39" s="56"/>
       <c r="AI39" s="3"/>
@@ -24296,29 +24278,29 @@
       <c r="E40" s="90"/>
       <c r="F40" s="58"/>
       <c r="G40" s="77"/>
-      <c r="H40" s="166"/>
-      <c r="I40" s="166"/>
-      <c r="J40" s="166"/>
-      <c r="K40" s="166"/>
+      <c r="H40" s="189"/>
+      <c r="I40" s="189"/>
+      <c r="J40" s="189"/>
+      <c r="K40" s="189"/>
       <c r="L40" s="78"/>
       <c r="M40" s="77"/>
-      <c r="N40" s="166"/>
-      <c r="O40" s="166"/>
-      <c r="P40" s="166"/>
-      <c r="Q40" s="166"/>
+      <c r="N40" s="189"/>
+      <c r="O40" s="189"/>
+      <c r="P40" s="189"/>
+      <c r="Q40" s="189"/>
       <c r="R40" s="78"/>
       <c r="S40" s="77"/>
-      <c r="T40" s="166"/>
-      <c r="U40" s="166"/>
-      <c r="V40" s="166"/>
+      <c r="T40" s="189"/>
+      <c r="U40" s="189"/>
+      <c r="V40" s="189"/>
       <c r="W40" s="77"/>
-      <c r="X40" s="166"/>
-      <c r="Y40" s="166"/>
-      <c r="Z40" s="166"/>
+      <c r="X40" s="189"/>
+      <c r="Y40" s="189"/>
+      <c r="Z40" s="189"/>
       <c r="AA40" s="78"/>
       <c r="AB40" s="77"/>
-      <c r="AC40" s="166"/>
-      <c r="AD40" s="166"/>
+      <c r="AC40" s="189"/>
+      <c r="AD40" s="189"/>
       <c r="AE40" s="61"/>
       <c r="AF40" s="79"/>
       <c r="AI40" s="3"/>
@@ -24549,29 +24531,29 @@
       <c r="E41" s="91"/>
       <c r="F41" s="59"/>
       <c r="G41" s="77"/>
-      <c r="H41" s="166"/>
-      <c r="I41" s="166"/>
-      <c r="J41" s="166"/>
-      <c r="K41" s="166"/>
+      <c r="H41" s="189"/>
+      <c r="I41" s="189"/>
+      <c r="J41" s="189"/>
+      <c r="K41" s="189"/>
       <c r="L41" s="80"/>
       <c r="M41" s="77"/>
-      <c r="N41" s="166"/>
-      <c r="O41" s="166"/>
-      <c r="P41" s="166"/>
-      <c r="Q41" s="166"/>
+      <c r="N41" s="189"/>
+      <c r="O41" s="189"/>
+      <c r="P41" s="189"/>
+      <c r="Q41" s="189"/>
       <c r="R41" s="80"/>
       <c r="S41" s="77"/>
-      <c r="T41" s="166"/>
-      <c r="U41" s="166"/>
-      <c r="V41" s="166"/>
+      <c r="T41" s="189"/>
+      <c r="U41" s="189"/>
+      <c r="V41" s="189"/>
       <c r="W41" s="77"/>
-      <c r="X41" s="166"/>
-      <c r="Y41" s="166"/>
-      <c r="Z41" s="166"/>
+      <c r="X41" s="189"/>
+      <c r="Y41" s="189"/>
+      <c r="Z41" s="189"/>
       <c r="AA41" s="80"/>
       <c r="AB41" s="77"/>
-      <c r="AC41" s="166"/>
-      <c r="AD41" s="166"/>
+      <c r="AC41" s="189"/>
+      <c r="AD41" s="189"/>
       <c r="AE41" s="62"/>
       <c r="AF41" s="81"/>
       <c r="AI41" s="3"/>
@@ -24802,29 +24784,29 @@
       <c r="E42" s="91"/>
       <c r="F42" s="59"/>
       <c r="G42" s="77"/>
-      <c r="H42" s="166"/>
-      <c r="I42" s="166"/>
-      <c r="J42" s="166"/>
-      <c r="K42" s="166"/>
+      <c r="H42" s="189"/>
+      <c r="I42" s="189"/>
+      <c r="J42" s="189"/>
+      <c r="K42" s="189"/>
       <c r="L42" s="80"/>
       <c r="M42" s="77"/>
-      <c r="N42" s="166"/>
-      <c r="O42" s="166"/>
-      <c r="P42" s="166"/>
-      <c r="Q42" s="166"/>
+      <c r="N42" s="189"/>
+      <c r="O42" s="189"/>
+      <c r="P42" s="189"/>
+      <c r="Q42" s="189"/>
       <c r="R42" s="80"/>
       <c r="S42" s="77"/>
-      <c r="T42" s="166"/>
-      <c r="U42" s="166"/>
-      <c r="V42" s="166"/>
+      <c r="T42" s="189"/>
+      <c r="U42" s="189"/>
+      <c r="V42" s="189"/>
       <c r="W42" s="77"/>
-      <c r="X42" s="166"/>
-      <c r="Y42" s="166"/>
-      <c r="Z42" s="166"/>
+      <c r="X42" s="189"/>
+      <c r="Y42" s="189"/>
+      <c r="Z42" s="189"/>
       <c r="AA42" s="80"/>
       <c r="AB42" s="77"/>
-      <c r="AC42" s="166"/>
-      <c r="AD42" s="166"/>
+      <c r="AC42" s="189"/>
+      <c r="AD42" s="189"/>
       <c r="AE42" s="62"/>
       <c r="AF42" s="81"/>
       <c r="AI42" s="3"/>
@@ -25051,29 +25033,29 @@
       <c r="E43" s="50"/>
       <c r="F43" s="60"/>
       <c r="G43" s="82"/>
-      <c r="H43" s="162"/>
-      <c r="I43" s="162"/>
-      <c r="J43" s="162"/>
-      <c r="K43" s="162"/>
+      <c r="H43" s="190"/>
+      <c r="I43" s="190"/>
+      <c r="J43" s="190"/>
+      <c r="K43" s="190"/>
       <c r="L43" s="83"/>
       <c r="M43" s="82"/>
-      <c r="N43" s="162"/>
-      <c r="O43" s="162"/>
-      <c r="P43" s="162"/>
-      <c r="Q43" s="162"/>
+      <c r="N43" s="190"/>
+      <c r="O43" s="190"/>
+      <c r="P43" s="190"/>
+      <c r="Q43" s="190"/>
       <c r="R43" s="83"/>
       <c r="S43" s="82"/>
-      <c r="T43" s="162"/>
-      <c r="U43" s="162"/>
-      <c r="V43" s="162"/>
+      <c r="T43" s="190"/>
+      <c r="U43" s="190"/>
+      <c r="V43" s="190"/>
       <c r="W43" s="82"/>
-      <c r="X43" s="162"/>
-      <c r="Y43" s="162"/>
-      <c r="Z43" s="162"/>
+      <c r="X43" s="190"/>
+      <c r="Y43" s="190"/>
+      <c r="Z43" s="190"/>
       <c r="AA43" s="83"/>
       <c r="AB43" s="82"/>
-      <c r="AC43" s="162"/>
-      <c r="AD43" s="162"/>
+      <c r="AC43" s="190"/>
+      <c r="AD43" s="190"/>
       <c r="AE43" s="63"/>
       <c r="AF43" s="84"/>
       <c r="AI43" s="3"/>
@@ -25337,13 +25319,83 @@
     </row>
   </sheetData>
   <mergeCells count="100">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="F1:AF1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="T3:AF3"/>
+    <mergeCell ref="S32:AF32"/>
+    <mergeCell ref="S33:AF33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="S26:AF26"/>
+    <mergeCell ref="S28:AF28"/>
+    <mergeCell ref="S29:AF29"/>
+    <mergeCell ref="S30:AF30"/>
+    <mergeCell ref="S31:AF31"/>
+    <mergeCell ref="S27:AF27"/>
+    <mergeCell ref="AC43:AD43"/>
+    <mergeCell ref="S9:AF9"/>
+    <mergeCell ref="S20:AF20"/>
+    <mergeCell ref="S21:AF21"/>
+    <mergeCell ref="S22:AF22"/>
+    <mergeCell ref="S23:AF23"/>
+    <mergeCell ref="T41:V41"/>
+    <mergeCell ref="X41:Z41"/>
+    <mergeCell ref="AC41:AD41"/>
+    <mergeCell ref="T42:V42"/>
+    <mergeCell ref="X42:Z42"/>
+    <mergeCell ref="AC42:AD42"/>
+    <mergeCell ref="T39:V39"/>
+    <mergeCell ref="X39:Z39"/>
+    <mergeCell ref="S34:AF34"/>
+    <mergeCell ref="S35:AF35"/>
+    <mergeCell ref="H43:K43"/>
+    <mergeCell ref="N43:Q43"/>
+    <mergeCell ref="T43:V43"/>
+    <mergeCell ref="X43:Z43"/>
+    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="N41:Q41"/>
+    <mergeCell ref="H42:K42"/>
+    <mergeCell ref="N42:Q42"/>
+    <mergeCell ref="H40:K40"/>
+    <mergeCell ref="N40:Q40"/>
+    <mergeCell ref="T40:V40"/>
+    <mergeCell ref="X40:Z40"/>
+    <mergeCell ref="AC40:AD40"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="AC39:AD39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="H39:K39"/>
+    <mergeCell ref="N39:Q39"/>
+    <mergeCell ref="S36:AF36"/>
+    <mergeCell ref="S37:AF37"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="S14:AF14"/>
+    <mergeCell ref="S15:AF15"/>
+    <mergeCell ref="S16:AF16"/>
+    <mergeCell ref="S17:AF17"/>
+    <mergeCell ref="S18:AF18"/>
+    <mergeCell ref="S19:AF19"/>
+    <mergeCell ref="S25:AF25"/>
+    <mergeCell ref="S24:AF24"/>
     <mergeCell ref="T5:W7"/>
     <mergeCell ref="AD4:AF4"/>
     <mergeCell ref="AD5:AF7"/>
@@ -25360,87 +25412,17 @@
     <mergeCell ref="X4:Z4"/>
     <mergeCell ref="AA4:AC4"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="S14:AF14"/>
-    <mergeCell ref="S15:AF15"/>
-    <mergeCell ref="S16:AF16"/>
-    <mergeCell ref="S17:AF17"/>
-    <mergeCell ref="S18:AF18"/>
-    <mergeCell ref="S19:AF19"/>
-    <mergeCell ref="S25:AF25"/>
-    <mergeCell ref="S24:AF24"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="F35:F37"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="AC39:AD39"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="H39:K39"/>
-    <mergeCell ref="N39:Q39"/>
-    <mergeCell ref="S36:AF36"/>
-    <mergeCell ref="S37:AF37"/>
-    <mergeCell ref="H40:K40"/>
-    <mergeCell ref="N40:Q40"/>
-    <mergeCell ref="T40:V40"/>
-    <mergeCell ref="X40:Z40"/>
-    <mergeCell ref="AC40:AD40"/>
-    <mergeCell ref="H43:K43"/>
-    <mergeCell ref="N43:Q43"/>
-    <mergeCell ref="T43:V43"/>
-    <mergeCell ref="X43:Z43"/>
-    <mergeCell ref="H41:K41"/>
-    <mergeCell ref="N41:Q41"/>
-    <mergeCell ref="H42:K42"/>
-    <mergeCell ref="N42:Q42"/>
-    <mergeCell ref="AC43:AD43"/>
-    <mergeCell ref="S9:AF9"/>
-    <mergeCell ref="S20:AF20"/>
-    <mergeCell ref="S21:AF21"/>
-    <mergeCell ref="S22:AF22"/>
-    <mergeCell ref="S23:AF23"/>
-    <mergeCell ref="T41:V41"/>
-    <mergeCell ref="X41:Z41"/>
-    <mergeCell ref="AC41:AD41"/>
-    <mergeCell ref="T42:V42"/>
-    <mergeCell ref="X42:Z42"/>
-    <mergeCell ref="AC42:AD42"/>
-    <mergeCell ref="T39:V39"/>
-    <mergeCell ref="X39:Z39"/>
-    <mergeCell ref="S34:AF34"/>
-    <mergeCell ref="S35:AF35"/>
-    <mergeCell ref="S26:AF26"/>
-    <mergeCell ref="S28:AF28"/>
-    <mergeCell ref="S29:AF29"/>
-    <mergeCell ref="S30:AF30"/>
-    <mergeCell ref="S31:AF31"/>
-    <mergeCell ref="S27:AF27"/>
-    <mergeCell ref="S32:AF32"/>
-    <mergeCell ref="S33:AF33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:AF1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="T3:AF3"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="G11:R19 AG11:AK19">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>TEXT(G11,"aaa")="日"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/設備点検表.xlsx
+++ b/設備点検表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kosuk\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77645DFE-6B25-48CC-B9C0-FCEAAB349713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8BABDBF-EEC3-4D88-91B1-594215637DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6C56CF13-AF7F-4C1F-982C-EF388A11F51A}"/>
   </bookViews>
@@ -2765,65 +2765,71 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2864,65 +2870,92 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="71" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="72" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="73" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="67" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="74" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2957,45 +2990,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="71" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="72" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="73" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="67" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="74" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準_設備点検表書式" xfId="1" xr:uid="{15F629F0-A893-4DD8-8A94-9D447F97F79C}"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="7">
     <dxf>
       <font>
         <strike val="0"/>
@@ -3026,31 +3026,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <strike/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3062,13 +3040,6 @@
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3414,45 +3385,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:254" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A1" s="155" t="s">
+      <c r="A1" s="121" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="155"/>
+      <c r="B1" s="121"/>
       <c r="C1" s="85"/>
-      <c r="F1" s="156" t="s">
+      <c r="F1" s="122" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
-      <c r="L1" s="156"/>
-      <c r="M1" s="156"/>
-      <c r="N1" s="156"/>
-      <c r="O1" s="156"/>
-      <c r="P1" s="156"/>
-      <c r="Q1" s="156"/>
-      <c r="R1" s="156"/>
-      <c r="S1" s="156"/>
-      <c r="T1" s="156"/>
-      <c r="U1" s="156"/>
-      <c r="V1" s="156"/>
-      <c r="W1" s="156"/>
-      <c r="X1" s="156"/>
-      <c r="Y1" s="156"/>
-      <c r="Z1" s="156"/>
-      <c r="AA1" s="156"/>
-      <c r="AB1" s="156"/>
-      <c r="AC1" s="156"/>
-      <c r="AD1" s="156"/>
-      <c r="AE1" s="156"/>
-      <c r="AF1" s="156"/>
-      <c r="AG1" s="156"/>
-      <c r="AH1" s="156"/>
-      <c r="AI1" s="156"/>
-      <c r="AJ1" s="156"/>
-      <c r="AK1" s="156"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
+      <c r="AC1" s="122"/>
+      <c r="AD1" s="122"/>
+      <c r="AE1" s="122"/>
+      <c r="AF1" s="122"/>
+      <c r="AG1" s="122"/>
+      <c r="AH1" s="122"/>
+      <c r="AI1" s="122"/>
+      <c r="AJ1" s="122"/>
+      <c r="AK1" s="122"/>
       <c r="AN1" s="3"/>
       <c r="AO1" s="3"/>
       <c r="AP1" s="3"/>
@@ -3923,52 +3894,52 @@
       <c r="IT2" s="3"/>
     </row>
     <row r="3" spans="1:254" s="2" customFormat="1" ht="20" customHeight="1" thickBot="1">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="123" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="125"/>
       <c r="E3" s="94"/>
       <c r="G3" s="51"/>
       <c r="H3" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="160" t="s">
+      <c r="K3" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="160"/>
-      <c r="M3" s="160" t="s">
+      <c r="L3" s="126"/>
+      <c r="M3" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="160"/>
-      <c r="O3" s="160"/>
-      <c r="P3" s="160" t="s">
+      <c r="N3" s="126"/>
+      <c r="O3" s="126"/>
+      <c r="P3" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="Q3" s="160"/>
-      <c r="R3" s="160"/>
+      <c r="Q3" s="126"/>
+      <c r="R3" s="126"/>
       <c r="S3" s="3"/>
-      <c r="T3" s="161" t="s">
+      <c r="T3" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="U3" s="162"/>
-      <c r="V3" s="162"/>
-      <c r="W3" s="162"/>
-      <c r="X3" s="162"/>
-      <c r="Y3" s="162"/>
-      <c r="Z3" s="162"/>
-      <c r="AA3" s="162"/>
-      <c r="AB3" s="162"/>
-      <c r="AC3" s="162"/>
-      <c r="AD3" s="162"/>
-      <c r="AE3" s="162"/>
-      <c r="AF3" s="162"/>
-      <c r="AG3" s="162"/>
-      <c r="AH3" s="162"/>
-      <c r="AI3" s="162"/>
-      <c r="AJ3" s="162"/>
-      <c r="AK3" s="163"/>
+      <c r="U3" s="128"/>
+      <c r="V3" s="128"/>
+      <c r="W3" s="128"/>
+      <c r="X3" s="128"/>
+      <c r="Y3" s="128"/>
+      <c r="Z3" s="128"/>
+      <c r="AA3" s="128"/>
+      <c r="AB3" s="128"/>
+      <c r="AC3" s="128"/>
+      <c r="AD3" s="128"/>
+      <c r="AE3" s="128"/>
+      <c r="AF3" s="128"/>
+      <c r="AG3" s="128"/>
+      <c r="AH3" s="128"/>
+      <c r="AI3" s="128"/>
+      <c r="AJ3" s="128"/>
+      <c r="AK3" s="129"/>
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
@@ -4197,47 +4168,47 @@
       <c r="H4" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="160" t="s">
+      <c r="K4" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="160"/>
-      <c r="M4" s="166">
+      <c r="L4" s="126"/>
+      <c r="M4" s="132">
         <v>46113</v>
       </c>
-      <c r="N4" s="166"/>
-      <c r="O4" s="166"/>
-      <c r="P4" s="160" t="s">
+      <c r="N4" s="132"/>
+      <c r="O4" s="132"/>
+      <c r="P4" s="126" t="s">
         <v>50</v>
       </c>
-      <c r="Q4" s="160"/>
-      <c r="R4" s="160"/>
+      <c r="Q4" s="126"/>
+      <c r="R4" s="126"/>
       <c r="S4" s="3"/>
-      <c r="T4" s="152" t="s">
+      <c r="T4" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="U4" s="153"/>
-      <c r="V4" s="153"/>
-      <c r="W4" s="153"/>
-      <c r="X4" s="153"/>
-      <c r="Y4" s="154"/>
-      <c r="Z4" s="152" t="s">
+      <c r="U4" s="134"/>
+      <c r="V4" s="134"/>
+      <c r="W4" s="134"/>
+      <c r="X4" s="134"/>
+      <c r="Y4" s="135"/>
+      <c r="Z4" s="133" t="s">
         <v>6</v>
       </c>
-      <c r="AA4" s="153"/>
-      <c r="AB4" s="153"/>
-      <c r="AC4" s="154"/>
-      <c r="AD4" s="152" t="s">
+      <c r="AA4" s="134"/>
+      <c r="AB4" s="134"/>
+      <c r="AC4" s="135"/>
+      <c r="AD4" s="133" t="s">
         <v>7</v>
       </c>
-      <c r="AE4" s="153"/>
-      <c r="AF4" s="153"/>
-      <c r="AG4" s="154"/>
-      <c r="AH4" s="152" t="s">
+      <c r="AE4" s="134"/>
+      <c r="AF4" s="134"/>
+      <c r="AG4" s="135"/>
+      <c r="AH4" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="AI4" s="153"/>
-      <c r="AJ4" s="153"/>
-      <c r="AK4" s="154"/>
+      <c r="AI4" s="134"/>
+      <c r="AJ4" s="134"/>
+      <c r="AK4" s="135"/>
       <c r="AN4" s="3"/>
       <c r="AO4" s="3"/>
       <c r="AP4" s="3"/>
@@ -4465,16 +4436,16 @@
         <v>23</v>
       </c>
       <c r="S5" s="3"/>
-      <c r="T5" s="167" t="s">
+      <c r="T5" s="136" t="s">
         <v>64</v>
       </c>
-      <c r="U5" s="168"/>
-      <c r="V5" s="168"/>
-      <c r="W5" s="139">
+      <c r="U5" s="137"/>
+      <c r="V5" s="137"/>
+      <c r="W5" s="141">
         <v>7</v>
       </c>
-      <c r="X5" s="140"/>
-      <c r="Y5" s="141"/>
+      <c r="X5" s="142"/>
+      <c r="Y5" s="143"/>
       <c r="Z5" s="11"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
@@ -4483,10 +4454,10 @@
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
       <c r="AG5" s="12"/>
-      <c r="AH5" s="144"/>
-      <c r="AI5" s="145"/>
-      <c r="AJ5" s="145"/>
-      <c r="AK5" s="146"/>
+      <c r="AH5" s="146"/>
+      <c r="AI5" s="147"/>
+      <c r="AJ5" s="147"/>
+      <c r="AK5" s="148"/>
       <c r="AN5" s="3"/>
       <c r="AO5" s="3"/>
       <c r="AP5" s="3"/>
@@ -4718,12 +4689,12 @@
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
-      <c r="T6" s="169"/>
-      <c r="U6" s="168"/>
-      <c r="V6" s="168"/>
-      <c r="W6" s="140"/>
-      <c r="X6" s="140"/>
-      <c r="Y6" s="141"/>
+      <c r="T6" s="138"/>
+      <c r="U6" s="137"/>
+      <c r="V6" s="137"/>
+      <c r="W6" s="142"/>
+      <c r="X6" s="142"/>
+      <c r="Y6" s="143"/>
       <c r="Z6" s="11"/>
       <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
@@ -4732,10 +4703,10 @@
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
       <c r="AG6" s="12"/>
-      <c r="AH6" s="144"/>
-      <c r="AI6" s="145"/>
-      <c r="AJ6" s="145"/>
-      <c r="AK6" s="146"/>
+      <c r="AH6" s="146"/>
+      <c r="AI6" s="147"/>
+      <c r="AJ6" s="147"/>
+      <c r="AK6" s="148"/>
       <c r="AN6" s="3"/>
       <c r="AO6" s="3"/>
       <c r="AP6" s="3"/>
@@ -4967,12 +4938,12 @@
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
-      <c r="T7" s="170"/>
-      <c r="U7" s="171"/>
-      <c r="V7" s="171"/>
-      <c r="W7" s="142"/>
-      <c r="X7" s="142"/>
-      <c r="Y7" s="143"/>
+      <c r="T7" s="139"/>
+      <c r="U7" s="140"/>
+      <c r="V7" s="140"/>
+      <c r="W7" s="144"/>
+      <c r="X7" s="144"/>
+      <c r="Y7" s="145"/>
       <c r="Z7" s="21"/>
       <c r="AA7" s="22"/>
       <c r="AB7" s="22"/>
@@ -4981,10 +4952,10 @@
       <c r="AE7" s="22"/>
       <c r="AF7" s="22"/>
       <c r="AG7" s="23"/>
-      <c r="AH7" s="147"/>
-      <c r="AI7" s="148"/>
-      <c r="AJ7" s="148"/>
-      <c r="AK7" s="149"/>
+      <c r="AH7" s="149"/>
+      <c r="AI7" s="150"/>
+      <c r="AJ7" s="150"/>
+      <c r="AK7" s="151"/>
       <c r="AL7" s="86"/>
       <c r="AN7" s="3"/>
       <c r="AO7" s="3"/>
@@ -5867,8 +5838,8 @@
     </row>
     <row r="10" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A10" s="29"/>
-      <c r="B10" s="150"/>
-      <c r="C10" s="151"/>
+      <c r="B10" s="152"/>
+      <c r="C10" s="153"/>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="31" t="s">
@@ -6216,10 +6187,10 @@
     </row>
     <row r="11" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A11" s="34"/>
-      <c r="B11" s="164" t="s">
+      <c r="B11" s="130" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="165"/>
+      <c r="C11" s="131"/>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
       <c r="F11" s="102" t="s">
@@ -6486,7 +6457,7 @@
       <c r="E12" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="124" t="s">
+      <c r="F12" s="158" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="106"/>
@@ -6748,7 +6719,7 @@
         <v>99</v>
       </c>
       <c r="E13" s="92"/>
-      <c r="F13" s="125"/>
+      <c r="F13" s="119"/>
       <c r="G13" s="106"/>
       <c r="H13" s="106"/>
       <c r="I13" s="106"/>
@@ -7010,7 +6981,7 @@
       <c r="E14" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="125"/>
+      <c r="F14" s="119"/>
       <c r="G14" s="106"/>
       <c r="H14" s="106"/>
       <c r="I14" s="106"/>
@@ -7272,7 +7243,7 @@
       <c r="E15" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="125"/>
+      <c r="F15" s="119"/>
       <c r="G15" s="106"/>
       <c r="H15" s="106"/>
       <c r="I15" s="106"/>
@@ -7534,7 +7505,7 @@
       <c r="E16" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="125"/>
+      <c r="F16" s="119"/>
       <c r="G16" s="106"/>
       <c r="H16" s="106"/>
       <c r="I16" s="106"/>
@@ -7796,7 +7767,7 @@
       <c r="E17" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="125"/>
+      <c r="F17" s="119"/>
       <c r="G17" s="106"/>
       <c r="H17" s="106"/>
       <c r="I17" s="106"/>
@@ -8058,7 +8029,7 @@
       <c r="E18" s="92" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="125"/>
+      <c r="F18" s="119"/>
       <c r="G18" s="106"/>
       <c r="H18" s="106"/>
       <c r="I18" s="106"/>
@@ -8320,7 +8291,7 @@
       <c r="E19" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="F19" s="125"/>
+      <c r="F19" s="119"/>
       <c r="G19" s="106"/>
       <c r="H19" s="106"/>
       <c r="I19" s="106"/>
@@ -8582,7 +8553,7 @@
       <c r="E20" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="F20" s="125"/>
+      <c r="F20" s="119"/>
       <c r="G20" s="106"/>
       <c r="H20" s="106"/>
       <c r="I20" s="106"/>
@@ -8842,7 +8813,7 @@
         <v>100</v>
       </c>
       <c r="E21" s="92"/>
-      <c r="F21" s="125"/>
+      <c r="F21" s="119"/>
       <c r="G21" s="106"/>
       <c r="H21" s="106"/>
       <c r="I21" s="106"/>
@@ -9102,7 +9073,7 @@
         <v>38</v>
       </c>
       <c r="E22" s="92"/>
-      <c r="F22" s="125" t="s">
+      <c r="F22" s="119" t="s">
         <v>135</v>
       </c>
       <c r="G22" s="106"/>
@@ -9366,7 +9337,7 @@
       <c r="E23" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="F23" s="126"/>
+      <c r="F23" s="120"/>
       <c r="G23" s="104"/>
       <c r="H23" s="104"/>
       <c r="I23" s="104"/>
@@ -10134,10 +10105,10 @@
     </row>
     <row r="26" spans="1:254" s="2" customFormat="1" ht="28.25" customHeight="1">
       <c r="A26" s="38"/>
-      <c r="B26" s="137" t="s">
+      <c r="B26" s="154" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="138"/>
+      <c r="C26" s="155"/>
       <c r="D26" s="35"/>
       <c r="E26" s="35"/>
       <c r="F26" s="39"/>
@@ -10392,17 +10363,17 @@
       <c r="A27" s="37">
         <v>1</v>
       </c>
-      <c r="B27" s="122" t="s">
+      <c r="B27" s="156" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="123"/>
+      <c r="C27" s="157"/>
       <c r="D27" s="92" t="s">
         <v>99</v>
       </c>
       <c r="E27" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="124" t="s">
+      <c r="F27" s="158" t="s">
         <v>15</v>
       </c>
       <c r="G27" s="106"/>
@@ -10656,15 +10627,15 @@
       <c r="A28" s="37">
         <v>2</v>
       </c>
-      <c r="B28" s="122" t="s">
+      <c r="B28" s="156" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="123"/>
+      <c r="C28" s="157"/>
       <c r="D28" s="35" t="s">
         <v>77</v>
       </c>
       <c r="E28" s="35"/>
-      <c r="F28" s="125"/>
+      <c r="F28" s="119"/>
       <c r="G28" s="106"/>
       <c r="H28" s="106"/>
       <c r="I28" s="106"/>
@@ -10924,7 +10895,7 @@
         <v>77</v>
       </c>
       <c r="E29" s="35"/>
-      <c r="F29" s="125"/>
+      <c r="F29" s="119"/>
       <c r="G29" s="106"/>
       <c r="H29" s="106"/>
       <c r="I29" s="106"/>
@@ -11186,7 +11157,7 @@
       <c r="E30" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="F30" s="125"/>
+      <c r="F30" s="119"/>
       <c r="G30" s="104"/>
       <c r="H30" s="104"/>
       <c r="I30" s="104"/>
@@ -11438,15 +11409,15 @@
       <c r="A31" s="37">
         <v>5</v>
       </c>
-      <c r="B31" s="122" t="s">
+      <c r="B31" s="156" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="123"/>
+      <c r="C31" s="157"/>
       <c r="D31" s="92" t="s">
         <v>80</v>
       </c>
       <c r="E31" s="35"/>
-      <c r="F31" s="125"/>
+      <c r="F31" s="119"/>
       <c r="G31" s="104"/>
       <c r="H31" s="104"/>
       <c r="I31" s="104"/>
@@ -11706,7 +11677,7 @@
         <v>118</v>
       </c>
       <c r="E32" s="35"/>
-      <c r="F32" s="125"/>
+      <c r="F32" s="119"/>
       <c r="G32" s="104"/>
       <c r="H32" s="104"/>
       <c r="I32" s="104"/>
@@ -11966,7 +11937,7 @@
         <v>118</v>
       </c>
       <c r="E33" s="35"/>
-      <c r="F33" s="125"/>
+      <c r="F33" s="119"/>
       <c r="G33" s="104"/>
       <c r="H33" s="104"/>
       <c r="I33" s="104"/>
@@ -12218,15 +12189,15 @@
       <c r="A34" s="37">
         <v>8</v>
       </c>
-      <c r="B34" s="122" t="s">
+      <c r="B34" s="156" t="s">
         <v>59</v>
       </c>
-      <c r="C34" s="123"/>
+      <c r="C34" s="157"/>
       <c r="D34" s="92" t="s">
         <v>99</v>
       </c>
       <c r="E34" s="40"/>
-      <c r="F34" s="125"/>
+      <c r="F34" s="119"/>
       <c r="G34" s="106"/>
       <c r="H34" s="106"/>
       <c r="I34" s="106"/>
@@ -12478,15 +12449,15 @@
       <c r="A35" s="37">
         <v>9</v>
       </c>
-      <c r="B35" s="122" t="s">
+      <c r="B35" s="156" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="123"/>
+      <c r="C35" s="157"/>
       <c r="D35" s="92" t="s">
         <v>49</v>
       </c>
       <c r="E35" s="40"/>
-      <c r="F35" s="126"/>
+      <c r="F35" s="120"/>
       <c r="G35" s="106"/>
       <c r="H35" s="106"/>
       <c r="I35" s="106"/>
@@ -12736,10 +12707,10 @@
     </row>
     <row r="36" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A36" s="37"/>
-      <c r="B36" s="137" t="s">
+      <c r="B36" s="154" t="s">
         <v>127</v>
       </c>
-      <c r="C36" s="138"/>
+      <c r="C36" s="155"/>
       <c r="D36" s="92"/>
       <c r="E36" s="40"/>
       <c r="F36" s="93"/>
@@ -12992,10 +12963,10 @@
     </row>
     <row r="37" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A37" s="37"/>
-      <c r="B37" s="122" t="s">
+      <c r="B37" s="156" t="s">
         <v>128</v>
       </c>
-      <c r="C37" s="123"/>
+      <c r="C37" s="157"/>
       <c r="D37" s="92"/>
       <c r="E37" s="40"/>
       <c r="F37" s="93"/>
@@ -13248,10 +13219,10 @@
     </row>
     <row r="38" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A38" s="37"/>
-      <c r="B38" s="135" t="s">
+      <c r="B38" s="170" t="s">
         <v>129</v>
       </c>
-      <c r="C38" s="136"/>
+      <c r="C38" s="171"/>
       <c r="D38" s="92"/>
       <c r="E38" s="40"/>
       <c r="F38" s="93"/>
@@ -13504,8 +13475,8 @@
     </row>
     <row r="39" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A39" s="37"/>
-      <c r="B39" s="135"/>
-      <c r="C39" s="136"/>
+      <c r="B39" s="170"/>
+      <c r="C39" s="171"/>
       <c r="D39" s="92"/>
       <c r="E39" s="40"/>
       <c r="F39" s="93"/>
@@ -13758,10 +13729,10 @@
     </row>
     <row r="40" spans="1:254" s="2" customFormat="1" ht="42" customHeight="1" thickBot="1">
       <c r="A40" s="41"/>
-      <c r="B40" s="133" t="s">
+      <c r="B40" s="168" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="134"/>
+      <c r="C40" s="169"/>
       <c r="D40" s="42" t="s">
         <v>16</v>
       </c>
@@ -14025,37 +13996,37 @@
         <v>96</v>
       </c>
       <c r="F41" s="75"/>
-      <c r="G41" s="127"/>
-      <c r="H41" s="127"/>
-      <c r="I41" s="127"/>
-      <c r="J41" s="127"/>
-      <c r="K41" s="127"/>
-      <c r="L41" s="127"/>
-      <c r="M41" s="127"/>
-      <c r="N41" s="127"/>
-      <c r="O41" s="127"/>
-      <c r="P41" s="127"/>
-      <c r="Q41" s="127"/>
-      <c r="R41" s="127"/>
-      <c r="S41" s="127"/>
-      <c r="T41" s="127"/>
-      <c r="U41" s="127"/>
-      <c r="V41" s="127"/>
-      <c r="W41" s="127"/>
-      <c r="X41" s="127"/>
-      <c r="Y41" s="127"/>
-      <c r="Z41" s="127"/>
-      <c r="AA41" s="128"/>
-      <c r="AB41" s="128"/>
-      <c r="AC41" s="128"/>
-      <c r="AD41" s="128"/>
-      <c r="AE41" s="128"/>
-      <c r="AF41" s="128"/>
-      <c r="AG41" s="128"/>
-      <c r="AH41" s="128"/>
-      <c r="AI41" s="128"/>
-      <c r="AJ41" s="128"/>
-      <c r="AK41" s="129"/>
+      <c r="G41" s="162"/>
+      <c r="H41" s="162"/>
+      <c r="I41" s="162"/>
+      <c r="J41" s="162"/>
+      <c r="K41" s="162"/>
+      <c r="L41" s="162"/>
+      <c r="M41" s="162"/>
+      <c r="N41" s="162"/>
+      <c r="O41" s="162"/>
+      <c r="P41" s="162"/>
+      <c r="Q41" s="162"/>
+      <c r="R41" s="162"/>
+      <c r="S41" s="162"/>
+      <c r="T41" s="162"/>
+      <c r="U41" s="162"/>
+      <c r="V41" s="162"/>
+      <c r="W41" s="162"/>
+      <c r="X41" s="162"/>
+      <c r="Y41" s="162"/>
+      <c r="Z41" s="162"/>
+      <c r="AA41" s="163"/>
+      <c r="AB41" s="163"/>
+      <c r="AC41" s="163"/>
+      <c r="AD41" s="163"/>
+      <c r="AE41" s="163"/>
+      <c r="AF41" s="163"/>
+      <c r="AG41" s="163"/>
+      <c r="AH41" s="163"/>
+      <c r="AI41" s="163"/>
+      <c r="AJ41" s="163"/>
+      <c r="AK41" s="164"/>
     </row>
     <row r="42" spans="1:254" ht="23" customHeight="1">
       <c r="A42" s="45"/>
@@ -14066,37 +14037,37 @@
         <v>97</v>
       </c>
       <c r="F42" s="77"/>
-      <c r="G42" s="130"/>
-      <c r="H42" s="130"/>
-      <c r="I42" s="130"/>
-      <c r="J42" s="130"/>
-      <c r="K42" s="130"/>
-      <c r="L42" s="130"/>
-      <c r="M42" s="130"/>
-      <c r="N42" s="130"/>
-      <c r="O42" s="130"/>
-      <c r="P42" s="130"/>
-      <c r="Q42" s="132"/>
-      <c r="R42" s="132"/>
-      <c r="S42" s="132"/>
-      <c r="T42" s="132"/>
-      <c r="U42" s="132"/>
-      <c r="V42" s="132"/>
-      <c r="W42" s="132"/>
-      <c r="X42" s="132"/>
-      <c r="Y42" s="132"/>
-      <c r="Z42" s="132"/>
-      <c r="AA42" s="130"/>
-      <c r="AB42" s="130"/>
-      <c r="AC42" s="130"/>
-      <c r="AD42" s="130"/>
-      <c r="AE42" s="130"/>
-      <c r="AF42" s="130"/>
-      <c r="AG42" s="130"/>
-      <c r="AH42" s="130"/>
-      <c r="AI42" s="130"/>
-      <c r="AJ42" s="130"/>
-      <c r="AK42" s="131"/>
+      <c r="G42" s="165"/>
+      <c r="H42" s="165"/>
+      <c r="I42" s="165"/>
+      <c r="J42" s="165"/>
+      <c r="K42" s="165"/>
+      <c r="L42" s="165"/>
+      <c r="M42" s="165"/>
+      <c r="N42" s="165"/>
+      <c r="O42" s="165"/>
+      <c r="P42" s="165"/>
+      <c r="Q42" s="167"/>
+      <c r="R42" s="167"/>
+      <c r="S42" s="167"/>
+      <c r="T42" s="167"/>
+      <c r="U42" s="167"/>
+      <c r="V42" s="167"/>
+      <c r="W42" s="167"/>
+      <c r="X42" s="167"/>
+      <c r="Y42" s="167"/>
+      <c r="Z42" s="167"/>
+      <c r="AA42" s="165"/>
+      <c r="AB42" s="165"/>
+      <c r="AC42" s="165"/>
+      <c r="AD42" s="165"/>
+      <c r="AE42" s="165"/>
+      <c r="AF42" s="165"/>
+      <c r="AG42" s="165"/>
+      <c r="AH42" s="165"/>
+      <c r="AI42" s="165"/>
+      <c r="AJ42" s="165"/>
+      <c r="AK42" s="166"/>
     </row>
     <row r="43" spans="1:254" ht="23" customHeight="1" thickBot="1">
       <c r="A43" s="49"/>
@@ -14107,37 +14078,37 @@
         <v>98</v>
       </c>
       <c r="F43" s="82"/>
-      <c r="G43" s="119"/>
-      <c r="H43" s="119"/>
-      <c r="I43" s="119"/>
-      <c r="J43" s="119"/>
-      <c r="K43" s="119"/>
-      <c r="L43" s="119"/>
-      <c r="M43" s="119"/>
-      <c r="N43" s="119"/>
-      <c r="O43" s="119"/>
-      <c r="P43" s="119"/>
-      <c r="Q43" s="121"/>
-      <c r="R43" s="121"/>
-      <c r="S43" s="121"/>
-      <c r="T43" s="121"/>
-      <c r="U43" s="121"/>
-      <c r="V43" s="121"/>
-      <c r="W43" s="121"/>
-      <c r="X43" s="121"/>
-      <c r="Y43" s="121"/>
-      <c r="Z43" s="121"/>
-      <c r="AA43" s="119"/>
-      <c r="AB43" s="119"/>
-      <c r="AC43" s="119"/>
-      <c r="AD43" s="119"/>
-      <c r="AE43" s="119"/>
-      <c r="AF43" s="119"/>
-      <c r="AG43" s="119"/>
-      <c r="AH43" s="119"/>
-      <c r="AI43" s="119"/>
-      <c r="AJ43" s="119"/>
-      <c r="AK43" s="120"/>
+      <c r="G43" s="159"/>
+      <c r="H43" s="159"/>
+      <c r="I43" s="159"/>
+      <c r="J43" s="159"/>
+      <c r="K43" s="159"/>
+      <c r="L43" s="159"/>
+      <c r="M43" s="159"/>
+      <c r="N43" s="159"/>
+      <c r="O43" s="159"/>
+      <c r="P43" s="159"/>
+      <c r="Q43" s="161"/>
+      <c r="R43" s="161"/>
+      <c r="S43" s="161"/>
+      <c r="T43" s="161"/>
+      <c r="U43" s="161"/>
+      <c r="V43" s="161"/>
+      <c r="W43" s="161"/>
+      <c r="X43" s="161"/>
+      <c r="Y43" s="161"/>
+      <c r="Z43" s="161"/>
+      <c r="AA43" s="159"/>
+      <c r="AB43" s="159"/>
+      <c r="AC43" s="159"/>
+      <c r="AD43" s="159"/>
+      <c r="AE43" s="159"/>
+      <c r="AF43" s="159"/>
+      <c r="AG43" s="159"/>
+      <c r="AH43" s="159"/>
+      <c r="AI43" s="159"/>
+      <c r="AJ43" s="159"/>
+      <c r="AK43" s="160"/>
     </row>
     <row r="44" spans="1:254">
       <c r="A44" s="52"/>
@@ -14153,6 +14124,50 @@
     </row>
   </sheetData>
   <mergeCells count="60">
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="AA43:AK43"/>
+    <mergeCell ref="Q43:Z43"/>
+    <mergeCell ref="G43:P43"/>
+    <mergeCell ref="Q41:Z41"/>
+    <mergeCell ref="AA41:AK41"/>
+    <mergeCell ref="AA42:AK42"/>
+    <mergeCell ref="Q42:Z42"/>
+    <mergeCell ref="G42:P42"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="G41:P41"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="F12:F21"/>
+    <mergeCell ref="F27:F35"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="W5:Y7"/>
+    <mergeCell ref="AH5:AK7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="Z4:AC4"/>
+    <mergeCell ref="AD4:AG4"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="F22:F23"/>
     <mergeCell ref="A1:B1"/>
@@ -14169,64 +14184,18 @@
     <mergeCell ref="T4:Y4"/>
     <mergeCell ref="AH4:AK4"/>
     <mergeCell ref="T5:V7"/>
-    <mergeCell ref="W5:Y7"/>
-    <mergeCell ref="AH5:AK7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="Z4:AC4"/>
-    <mergeCell ref="AD4:AG4"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="F12:F21"/>
-    <mergeCell ref="F27:F35"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="AA43:AK43"/>
-    <mergeCell ref="Q43:Z43"/>
-    <mergeCell ref="G43:P43"/>
-    <mergeCell ref="Q41:Z41"/>
-    <mergeCell ref="AA41:AK41"/>
-    <mergeCell ref="AA42:AK42"/>
-    <mergeCell ref="Q42:Z42"/>
-    <mergeCell ref="G42:P42"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="G41:P41"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="G9:AK10">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>TEXT(G9,"aaa")="土"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G9:AK40">
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>TEXT(G9,"aaa")="日"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:AK40">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>G$11="－"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14251,40 +14220,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:254" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A1" s="155" t="s">
+      <c r="A1" s="121" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="155"/>
+      <c r="B1" s="121"/>
       <c r="C1" s="85"/>
-      <c r="F1" s="156" t="s">
+      <c r="F1" s="122" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
-      <c r="L1" s="156"/>
-      <c r="M1" s="156"/>
-      <c r="N1" s="156"/>
-      <c r="O1" s="156"/>
-      <c r="P1" s="156"/>
-      <c r="Q1" s="156"/>
-      <c r="R1" s="156"/>
-      <c r="S1" s="156"/>
-      <c r="T1" s="156"/>
-      <c r="U1" s="156"/>
-      <c r="V1" s="156"/>
-      <c r="W1" s="156"/>
-      <c r="X1" s="156"/>
-      <c r="Y1" s="156"/>
-      <c r="Z1" s="156"/>
-      <c r="AA1" s="156"/>
-      <c r="AB1" s="156"/>
-      <c r="AC1" s="156"/>
-      <c r="AD1" s="156"/>
-      <c r="AE1" s="156"/>
-      <c r="AF1" s="156"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
+      <c r="AC1" s="122"/>
+      <c r="AD1" s="122"/>
+      <c r="AE1" s="122"/>
+      <c r="AF1" s="122"/>
       <c r="AI1" s="3"/>
       <c r="AJ1" s="3"/>
       <c r="AK1" s="3"/>
@@ -14750,47 +14719,47 @@
       <c r="IO2" s="3"/>
     </row>
     <row r="3" spans="1:254" s="2" customFormat="1" ht="20" customHeight="1" thickBot="1">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="123" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="125"/>
       <c r="E3" s="94"/>
       <c r="G3" s="51"/>
       <c r="H3" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="160" t="s">
+      <c r="K3" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="160"/>
-      <c r="M3" s="160" t="s">
+      <c r="L3" s="126"/>
+      <c r="M3" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="160"/>
-      <c r="O3" s="160"/>
-      <c r="P3" s="160" t="s">
+      <c r="N3" s="126"/>
+      <c r="O3" s="126"/>
+      <c r="P3" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="Q3" s="160"/>
-      <c r="R3" s="160"/>
+      <c r="Q3" s="126"/>
+      <c r="R3" s="126"/>
       <c r="S3" s="3"/>
-      <c r="T3" s="161" t="s">
+      <c r="T3" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="U3" s="162"/>
-      <c r="V3" s="162"/>
-      <c r="W3" s="162"/>
-      <c r="X3" s="162"/>
-      <c r="Y3" s="162"/>
-      <c r="Z3" s="162"/>
-      <c r="AA3" s="162"/>
-      <c r="AB3" s="162"/>
-      <c r="AC3" s="162"/>
-      <c r="AD3" s="162"/>
-      <c r="AE3" s="162"/>
-      <c r="AF3" s="163"/>
+      <c r="U3" s="128"/>
+      <c r="V3" s="128"/>
+      <c r="W3" s="128"/>
+      <c r="X3" s="128"/>
+      <c r="Y3" s="128"/>
+      <c r="Z3" s="128"/>
+      <c r="AA3" s="128"/>
+      <c r="AB3" s="128"/>
+      <c r="AC3" s="128"/>
+      <c r="AD3" s="128"/>
+      <c r="AE3" s="128"/>
+      <c r="AF3" s="129"/>
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
       <c r="AK3" s="3"/>
@@ -15019,42 +14988,42 @@
       <c r="H4" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="160" t="s">
+      <c r="K4" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="160"/>
-      <c r="M4" s="166">
+      <c r="L4" s="126"/>
+      <c r="M4" s="132">
         <v>46113</v>
       </c>
-      <c r="N4" s="166"/>
-      <c r="O4" s="166"/>
-      <c r="P4" s="160" t="s">
+      <c r="N4" s="132"/>
+      <c r="O4" s="132"/>
+      <c r="P4" s="126" t="s">
         <v>50</v>
       </c>
-      <c r="Q4" s="160"/>
-      <c r="R4" s="160"/>
+      <c r="Q4" s="126"/>
+      <c r="R4" s="126"/>
       <c r="S4" s="3"/>
-      <c r="T4" s="152" t="s">
+      <c r="T4" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="U4" s="153"/>
-      <c r="V4" s="153"/>
-      <c r="W4" s="154"/>
-      <c r="X4" s="152" t="s">
+      <c r="U4" s="134"/>
+      <c r="V4" s="134"/>
+      <c r="W4" s="135"/>
+      <c r="X4" s="133" t="s">
         <v>6</v>
       </c>
-      <c r="Y4" s="153"/>
-      <c r="Z4" s="154"/>
-      <c r="AA4" s="152" t="s">
+      <c r="Y4" s="134"/>
+      <c r="Z4" s="135"/>
+      <c r="AA4" s="133" t="s">
         <v>7</v>
       </c>
-      <c r="AB4" s="153"/>
-      <c r="AC4" s="154"/>
-      <c r="AD4" s="152" t="s">
+      <c r="AB4" s="134"/>
+      <c r="AC4" s="135"/>
+      <c r="AD4" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="AE4" s="153"/>
-      <c r="AF4" s="154"/>
+      <c r="AE4" s="134"/>
+      <c r="AF4" s="135"/>
       <c r="AI4" s="3"/>
       <c r="AJ4" s="3"/>
       <c r="AK4" s="3"/>
@@ -15282,21 +15251,21 @@
         <v>23</v>
       </c>
       <c r="S5" s="3"/>
-      <c r="T5" s="172" t="s">
+      <c r="T5" s="183" t="s">
         <v>64</v>
       </c>
-      <c r="U5" s="173"/>
-      <c r="V5" s="173"/>
-      <c r="W5" s="174"/>
+      <c r="U5" s="184"/>
+      <c r="V5" s="184"/>
+      <c r="W5" s="185"/>
       <c r="X5" s="11"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="12"/>
       <c r="AA5" s="11"/>
       <c r="AB5" s="3"/>
       <c r="AC5" s="12"/>
-      <c r="AD5" s="144"/>
-      <c r="AE5" s="145"/>
-      <c r="AF5" s="146"/>
+      <c r="AD5" s="146"/>
+      <c r="AE5" s="147"/>
+      <c r="AF5" s="148"/>
       <c r="AI5" s="3"/>
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3"/>
@@ -15528,19 +15497,19 @@
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
-      <c r="T6" s="172"/>
-      <c r="U6" s="173"/>
-      <c r="V6" s="173"/>
-      <c r="W6" s="174"/>
+      <c r="T6" s="183"/>
+      <c r="U6" s="184"/>
+      <c r="V6" s="184"/>
+      <c r="W6" s="185"/>
       <c r="X6" s="11"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="12"/>
       <c r="AA6" s="11"/>
       <c r="AB6" s="3"/>
       <c r="AC6" s="12"/>
-      <c r="AD6" s="144"/>
-      <c r="AE6" s="145"/>
-      <c r="AF6" s="146"/>
+      <c r="AD6" s="146"/>
+      <c r="AE6" s="147"/>
+      <c r="AF6" s="148"/>
       <c r="AI6" s="3"/>
       <c r="AJ6" s="3"/>
       <c r="AK6" s="3"/>
@@ -15772,19 +15741,19 @@
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
-      <c r="T7" s="175"/>
-      <c r="U7" s="176"/>
-      <c r="V7" s="176"/>
-      <c r="W7" s="177"/>
+      <c r="T7" s="186"/>
+      <c r="U7" s="187"/>
+      <c r="V7" s="187"/>
+      <c r="W7" s="188"/>
       <c r="X7" s="21"/>
       <c r="Y7" s="22"/>
       <c r="Z7" s="23"/>
       <c r="AA7" s="21"/>
       <c r="AB7" s="22"/>
       <c r="AC7" s="23"/>
-      <c r="AD7" s="147"/>
-      <c r="AE7" s="148"/>
-      <c r="AF7" s="149"/>
+      <c r="AD7" s="149"/>
+      <c r="AE7" s="150"/>
+      <c r="AF7" s="151"/>
       <c r="AG7" s="86"/>
       <c r="AI7" s="3"/>
       <c r="AJ7" s="3"/>
@@ -16301,22 +16270,22 @@
       <c r="R9" s="97" t="s">
         <v>76</v>
       </c>
-      <c r="S9" s="191" t="s">
+      <c r="S9" s="176" t="s">
         <v>78</v>
       </c>
-      <c r="T9" s="192"/>
-      <c r="U9" s="192"/>
-      <c r="V9" s="192"/>
-      <c r="W9" s="192"/>
-      <c r="X9" s="192"/>
-      <c r="Y9" s="192"/>
-      <c r="Z9" s="192"/>
-      <c r="AA9" s="192"/>
-      <c r="AB9" s="192"/>
-      <c r="AC9" s="192"/>
-      <c r="AD9" s="192"/>
-      <c r="AE9" s="192"/>
-      <c r="AF9" s="193"/>
+      <c r="T9" s="177"/>
+      <c r="U9" s="177"/>
+      <c r="V9" s="177"/>
+      <c r="W9" s="177"/>
+      <c r="X9" s="177"/>
+      <c r="Y9" s="177"/>
+      <c r="Z9" s="177"/>
+      <c r="AA9" s="177"/>
+      <c r="AB9" s="177"/>
+      <c r="AC9" s="177"/>
+      <c r="AD9" s="177"/>
+      <c r="AE9" s="177"/>
+      <c r="AF9" s="178"/>
       <c r="AI9" s="3"/>
       <c r="AJ9" s="3"/>
       <c r="AK9" s="3"/>
@@ -16535,8 +16504,8 @@
     </row>
     <row r="10" spans="1:254" s="2" customFormat="1" ht="23" hidden="1" customHeight="1">
       <c r="A10" s="29"/>
-      <c r="B10" s="150"/>
-      <c r="C10" s="151"/>
+      <c r="B10" s="152"/>
+      <c r="C10" s="153"/>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="31"/>
@@ -16862,10 +16831,10 @@
     </row>
     <row r="11" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A11" s="37"/>
-      <c r="B11" s="137" t="s">
+      <c r="B11" s="154" t="s">
         <v>105</v>
       </c>
-      <c r="C11" s="138"/>
+      <c r="C11" s="155"/>
       <c r="D11" s="92"/>
       <c r="E11" s="40"/>
       <c r="F11" s="93"/>
@@ -16881,20 +16850,20 @@
       <c r="P11" s="69"/>
       <c r="Q11" s="69"/>
       <c r="R11" s="69"/>
-      <c r="S11" s="180"/>
-      <c r="T11" s="181"/>
-      <c r="U11" s="181"/>
-      <c r="V11" s="181"/>
-      <c r="W11" s="181"/>
-      <c r="X11" s="181"/>
-      <c r="Y11" s="181"/>
-      <c r="Z11" s="181"/>
-      <c r="AA11" s="181"/>
-      <c r="AB11" s="181"/>
-      <c r="AC11" s="181"/>
-      <c r="AD11" s="181"/>
-      <c r="AE11" s="181"/>
-      <c r="AF11" s="182"/>
+      <c r="S11" s="191"/>
+      <c r="T11" s="192"/>
+      <c r="U11" s="192"/>
+      <c r="V11" s="192"/>
+      <c r="W11" s="192"/>
+      <c r="X11" s="192"/>
+      <c r="Y11" s="192"/>
+      <c r="Z11" s="192"/>
+      <c r="AA11" s="192"/>
+      <c r="AB11" s="192"/>
+      <c r="AC11" s="192"/>
+      <c r="AD11" s="192"/>
+      <c r="AE11" s="192"/>
+      <c r="AF11" s="193"/>
       <c r="AG11" s="69"/>
       <c r="AH11" s="69"/>
       <c r="AI11" s="69"/>
@@ -17120,10 +17089,10 @@
       <c r="A12" s="37">
         <v>1</v>
       </c>
-      <c r="B12" s="135" t="s">
+      <c r="B12" s="170" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="136"/>
+      <c r="C12" s="171"/>
       <c r="D12" s="92" t="s">
         <v>108</v>
       </c>
@@ -17141,20 +17110,20 @@
       <c r="P12" s="69"/>
       <c r="Q12" s="69"/>
       <c r="R12" s="69"/>
-      <c r="S12" s="183"/>
-      <c r="T12" s="184"/>
-      <c r="U12" s="184"/>
-      <c r="V12" s="184"/>
-      <c r="W12" s="184"/>
-      <c r="X12" s="184"/>
-      <c r="Y12" s="184"/>
-      <c r="Z12" s="184"/>
-      <c r="AA12" s="184"/>
-      <c r="AB12" s="184"/>
-      <c r="AC12" s="184"/>
-      <c r="AD12" s="184"/>
-      <c r="AE12" s="184"/>
-      <c r="AF12" s="185"/>
+      <c r="S12" s="172"/>
+      <c r="T12" s="173"/>
+      <c r="U12" s="173"/>
+      <c r="V12" s="173"/>
+      <c r="W12" s="173"/>
+      <c r="X12" s="173"/>
+      <c r="Y12" s="173"/>
+      <c r="Z12" s="173"/>
+      <c r="AA12" s="173"/>
+      <c r="AB12" s="173"/>
+      <c r="AC12" s="173"/>
+      <c r="AD12" s="173"/>
+      <c r="AE12" s="173"/>
+      <c r="AF12" s="174"/>
       <c r="AG12" s="69"/>
       <c r="AH12" s="69"/>
       <c r="AI12" s="69"/>
@@ -17380,10 +17349,10 @@
       <c r="A13" s="37">
         <v>2</v>
       </c>
-      <c r="B13" s="135" t="s">
+      <c r="B13" s="170" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="136"/>
+      <c r="C13" s="171"/>
       <c r="D13" s="92" t="s">
         <v>107</v>
       </c>
@@ -17401,20 +17370,20 @@
       <c r="P13" s="69"/>
       <c r="Q13" s="69"/>
       <c r="R13" s="69"/>
-      <c r="S13" s="183"/>
-      <c r="T13" s="184"/>
-      <c r="U13" s="184"/>
-      <c r="V13" s="184"/>
-      <c r="W13" s="184"/>
-      <c r="X13" s="184"/>
-      <c r="Y13" s="184"/>
-      <c r="Z13" s="184"/>
-      <c r="AA13" s="184"/>
-      <c r="AB13" s="184"/>
-      <c r="AC13" s="184"/>
-      <c r="AD13" s="184"/>
-      <c r="AE13" s="184"/>
-      <c r="AF13" s="185"/>
+      <c r="S13" s="172"/>
+      <c r="T13" s="173"/>
+      <c r="U13" s="173"/>
+      <c r="V13" s="173"/>
+      <c r="W13" s="173"/>
+      <c r="X13" s="173"/>
+      <c r="Y13" s="173"/>
+      <c r="Z13" s="173"/>
+      <c r="AA13" s="173"/>
+      <c r="AB13" s="173"/>
+      <c r="AC13" s="173"/>
+      <c r="AD13" s="173"/>
+      <c r="AE13" s="173"/>
+      <c r="AF13" s="174"/>
       <c r="AG13" s="69"/>
       <c r="AH13" s="69"/>
       <c r="AI13" s="69"/>
@@ -17640,10 +17609,10 @@
       <c r="A14" s="37">
         <v>3</v>
       </c>
-      <c r="B14" s="135" t="s">
+      <c r="B14" s="170" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="136"/>
+      <c r="C14" s="171"/>
       <c r="D14" s="92" t="s">
         <v>107</v>
       </c>
@@ -17661,20 +17630,20 @@
       <c r="P14" s="69"/>
       <c r="Q14" s="69"/>
       <c r="R14" s="69"/>
-      <c r="S14" s="183"/>
-      <c r="T14" s="184"/>
-      <c r="U14" s="184"/>
-      <c r="V14" s="184"/>
-      <c r="W14" s="184"/>
-      <c r="X14" s="184"/>
-      <c r="Y14" s="184"/>
-      <c r="Z14" s="184"/>
-      <c r="AA14" s="184"/>
-      <c r="AB14" s="184"/>
-      <c r="AC14" s="184"/>
-      <c r="AD14" s="184"/>
-      <c r="AE14" s="184"/>
-      <c r="AF14" s="185"/>
+      <c r="S14" s="172"/>
+      <c r="T14" s="173"/>
+      <c r="U14" s="173"/>
+      <c r="V14" s="173"/>
+      <c r="W14" s="173"/>
+      <c r="X14" s="173"/>
+      <c r="Y14" s="173"/>
+      <c r="Z14" s="173"/>
+      <c r="AA14" s="173"/>
+      <c r="AB14" s="173"/>
+      <c r="AC14" s="173"/>
+      <c r="AD14" s="173"/>
+      <c r="AE14" s="173"/>
+      <c r="AF14" s="174"/>
       <c r="AG14" s="69"/>
       <c r="AH14" s="69"/>
       <c r="AI14" s="69"/>
@@ -17900,10 +17869,10 @@
       <c r="A15" s="37">
         <v>4</v>
       </c>
-      <c r="B15" s="135" t="s">
+      <c r="B15" s="170" t="s">
         <v>82</v>
       </c>
-      <c r="C15" s="136"/>
+      <c r="C15" s="171"/>
       <c r="D15" s="92" t="s">
         <v>108</v>
       </c>
@@ -17921,20 +17890,20 @@
       <c r="P15" s="69"/>
       <c r="Q15" s="69"/>
       <c r="R15" s="69"/>
-      <c r="S15" s="183"/>
-      <c r="T15" s="184"/>
-      <c r="U15" s="184"/>
-      <c r="V15" s="184"/>
-      <c r="W15" s="184"/>
-      <c r="X15" s="184"/>
-      <c r="Y15" s="184"/>
-      <c r="Z15" s="184"/>
-      <c r="AA15" s="184"/>
-      <c r="AB15" s="184"/>
-      <c r="AC15" s="184"/>
-      <c r="AD15" s="184"/>
-      <c r="AE15" s="184"/>
-      <c r="AF15" s="185"/>
+      <c r="S15" s="172"/>
+      <c r="T15" s="173"/>
+      <c r="U15" s="173"/>
+      <c r="V15" s="173"/>
+      <c r="W15" s="173"/>
+      <c r="X15" s="173"/>
+      <c r="Y15" s="173"/>
+      <c r="Z15" s="173"/>
+      <c r="AA15" s="173"/>
+      <c r="AB15" s="173"/>
+      <c r="AC15" s="173"/>
+      <c r="AD15" s="173"/>
+      <c r="AE15" s="173"/>
+      <c r="AF15" s="174"/>
       <c r="AG15" s="69"/>
       <c r="AH15" s="69"/>
       <c r="AI15" s="69"/>
@@ -18160,10 +18129,10 @@
       <c r="A16" s="37">
         <v>5</v>
       </c>
-      <c r="B16" s="135" t="s">
+      <c r="B16" s="170" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="136"/>
+      <c r="C16" s="171"/>
       <c r="D16" s="92" t="s">
         <v>108</v>
       </c>
@@ -18181,20 +18150,20 @@
       <c r="P16" s="69"/>
       <c r="Q16" s="69"/>
       <c r="R16" s="69"/>
-      <c r="S16" s="183"/>
-      <c r="T16" s="184"/>
-      <c r="U16" s="184"/>
-      <c r="V16" s="184"/>
-      <c r="W16" s="184"/>
-      <c r="X16" s="184"/>
-      <c r="Y16" s="184"/>
-      <c r="Z16" s="184"/>
-      <c r="AA16" s="184"/>
-      <c r="AB16" s="184"/>
-      <c r="AC16" s="184"/>
-      <c r="AD16" s="184"/>
-      <c r="AE16" s="184"/>
-      <c r="AF16" s="185"/>
+      <c r="S16" s="172"/>
+      <c r="T16" s="173"/>
+      <c r="U16" s="173"/>
+      <c r="V16" s="173"/>
+      <c r="W16" s="173"/>
+      <c r="X16" s="173"/>
+      <c r="Y16" s="173"/>
+      <c r="Z16" s="173"/>
+      <c r="AA16" s="173"/>
+      <c r="AB16" s="173"/>
+      <c r="AC16" s="173"/>
+      <c r="AD16" s="173"/>
+      <c r="AE16" s="173"/>
+      <c r="AF16" s="174"/>
       <c r="AG16" s="69"/>
       <c r="AH16" s="69"/>
       <c r="AI16" s="69"/>
@@ -18420,10 +18389,10 @@
       <c r="A17" s="37">
         <v>6</v>
       </c>
-      <c r="B17" s="135" t="s">
+      <c r="B17" s="170" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="136"/>
+      <c r="C17" s="171"/>
       <c r="D17" s="92" t="s">
         <v>108</v>
       </c>
@@ -18441,20 +18410,20 @@
       <c r="P17" s="69"/>
       <c r="Q17" s="69"/>
       <c r="R17" s="69"/>
-      <c r="S17" s="183"/>
-      <c r="T17" s="184"/>
-      <c r="U17" s="184"/>
-      <c r="V17" s="184"/>
-      <c r="W17" s="184"/>
-      <c r="X17" s="184"/>
-      <c r="Y17" s="184"/>
-      <c r="Z17" s="184"/>
-      <c r="AA17" s="184"/>
-      <c r="AB17" s="184"/>
-      <c r="AC17" s="184"/>
-      <c r="AD17" s="184"/>
-      <c r="AE17" s="184"/>
-      <c r="AF17" s="185"/>
+      <c r="S17" s="172"/>
+      <c r="T17" s="173"/>
+      <c r="U17" s="173"/>
+      <c r="V17" s="173"/>
+      <c r="W17" s="173"/>
+      <c r="X17" s="173"/>
+      <c r="Y17" s="173"/>
+      <c r="Z17" s="173"/>
+      <c r="AA17" s="173"/>
+      <c r="AB17" s="173"/>
+      <c r="AC17" s="173"/>
+      <c r="AD17" s="173"/>
+      <c r="AE17" s="173"/>
+      <c r="AF17" s="174"/>
       <c r="AG17" s="69"/>
       <c r="AH17" s="69"/>
       <c r="AI17" s="69"/>
@@ -18680,10 +18649,10 @@
       <c r="A18" s="37">
         <v>7</v>
       </c>
-      <c r="B18" s="135" t="s">
+      <c r="B18" s="170" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="136"/>
+      <c r="C18" s="171"/>
       <c r="D18" s="92" t="s">
         <v>108</v>
       </c>
@@ -18701,20 +18670,20 @@
       <c r="P18" s="69"/>
       <c r="Q18" s="69"/>
       <c r="R18" s="69"/>
-      <c r="S18" s="183"/>
-      <c r="T18" s="184"/>
-      <c r="U18" s="184"/>
-      <c r="V18" s="184"/>
-      <c r="W18" s="184"/>
-      <c r="X18" s="184"/>
-      <c r="Y18" s="184"/>
-      <c r="Z18" s="184"/>
-      <c r="AA18" s="184"/>
-      <c r="AB18" s="184"/>
-      <c r="AC18" s="184"/>
-      <c r="AD18" s="184"/>
-      <c r="AE18" s="184"/>
-      <c r="AF18" s="185"/>
+      <c r="S18" s="172"/>
+      <c r="T18" s="173"/>
+      <c r="U18" s="173"/>
+      <c r="V18" s="173"/>
+      <c r="W18" s="173"/>
+      <c r="X18" s="173"/>
+      <c r="Y18" s="173"/>
+      <c r="Z18" s="173"/>
+      <c r="AA18" s="173"/>
+      <c r="AB18" s="173"/>
+      <c r="AC18" s="173"/>
+      <c r="AD18" s="173"/>
+      <c r="AE18" s="173"/>
+      <c r="AF18" s="174"/>
       <c r="AG18" s="69"/>
       <c r="AH18" s="69"/>
       <c r="AI18" s="69"/>
@@ -18940,10 +18909,10 @@
       <c r="A19" s="37">
         <v>8</v>
       </c>
-      <c r="B19" s="135" t="s">
+      <c r="B19" s="170" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="136"/>
+      <c r="C19" s="171"/>
       <c r="D19" s="92" t="s">
         <v>108</v>
       </c>
@@ -18961,20 +18930,20 @@
       <c r="P19" s="69"/>
       <c r="Q19" s="69"/>
       <c r="R19" s="69"/>
-      <c r="S19" s="183"/>
-      <c r="T19" s="184"/>
-      <c r="U19" s="184"/>
-      <c r="V19" s="184"/>
-      <c r="W19" s="184"/>
-      <c r="X19" s="184"/>
-      <c r="Y19" s="184"/>
-      <c r="Z19" s="184"/>
-      <c r="AA19" s="184"/>
-      <c r="AB19" s="184"/>
-      <c r="AC19" s="184"/>
-      <c r="AD19" s="184"/>
-      <c r="AE19" s="184"/>
-      <c r="AF19" s="185"/>
+      <c r="S19" s="172"/>
+      <c r="T19" s="173"/>
+      <c r="U19" s="173"/>
+      <c r="V19" s="173"/>
+      <c r="W19" s="173"/>
+      <c r="X19" s="173"/>
+      <c r="Y19" s="173"/>
+      <c r="Z19" s="173"/>
+      <c r="AA19" s="173"/>
+      <c r="AB19" s="173"/>
+      <c r="AC19" s="173"/>
+      <c r="AD19" s="173"/>
+      <c r="AE19" s="173"/>
+      <c r="AF19" s="174"/>
       <c r="AG19" s="69"/>
       <c r="AH19" s="69"/>
       <c r="AI19" s="69"/>
@@ -19198,10 +19167,10 @@
     </row>
     <row r="20" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A20" s="34"/>
-      <c r="B20" s="178" t="s">
+      <c r="B20" s="189" t="s">
         <v>120</v>
       </c>
-      <c r="C20" s="179"/>
+      <c r="C20" s="190"/>
       <c r="D20" s="35"/>
       <c r="E20" s="35"/>
       <c r="F20" s="36"/>
@@ -19217,20 +19186,20 @@
       <c r="P20" s="68"/>
       <c r="Q20" s="68"/>
       <c r="R20" s="68"/>
-      <c r="S20" s="183"/>
-      <c r="T20" s="184"/>
-      <c r="U20" s="184"/>
-      <c r="V20" s="184"/>
-      <c r="W20" s="184"/>
-      <c r="X20" s="184"/>
-      <c r="Y20" s="184"/>
-      <c r="Z20" s="184"/>
-      <c r="AA20" s="184"/>
-      <c r="AB20" s="184"/>
-      <c r="AC20" s="184"/>
-      <c r="AD20" s="184"/>
-      <c r="AE20" s="184"/>
-      <c r="AF20" s="185"/>
+      <c r="S20" s="172"/>
+      <c r="T20" s="173"/>
+      <c r="U20" s="173"/>
+      <c r="V20" s="173"/>
+      <c r="W20" s="173"/>
+      <c r="X20" s="173"/>
+      <c r="Y20" s="173"/>
+      <c r="Z20" s="173"/>
+      <c r="AA20" s="173"/>
+      <c r="AB20" s="173"/>
+      <c r="AC20" s="173"/>
+      <c r="AD20" s="173"/>
+      <c r="AE20" s="173"/>
+      <c r="AF20" s="174"/>
       <c r="AI20" s="3"/>
       <c r="AJ20" s="3"/>
       <c r="AK20" s="3"/>
@@ -19472,20 +19441,20 @@
       <c r="P21" s="69"/>
       <c r="Q21" s="69"/>
       <c r="R21" s="69"/>
-      <c r="S21" s="183"/>
-      <c r="T21" s="184"/>
-      <c r="U21" s="184"/>
-      <c r="V21" s="184"/>
-      <c r="W21" s="184"/>
-      <c r="X21" s="184"/>
-      <c r="Y21" s="184"/>
-      <c r="Z21" s="184"/>
-      <c r="AA21" s="184"/>
-      <c r="AB21" s="184"/>
-      <c r="AC21" s="184"/>
-      <c r="AD21" s="184"/>
-      <c r="AE21" s="184"/>
-      <c r="AF21" s="185"/>
+      <c r="S21" s="172"/>
+      <c r="T21" s="173"/>
+      <c r="U21" s="173"/>
+      <c r="V21" s="173"/>
+      <c r="W21" s="173"/>
+      <c r="X21" s="173"/>
+      <c r="Y21" s="173"/>
+      <c r="Z21" s="173"/>
+      <c r="AA21" s="173"/>
+      <c r="AB21" s="173"/>
+      <c r="AC21" s="173"/>
+      <c r="AD21" s="173"/>
+      <c r="AE21" s="173"/>
+      <c r="AF21" s="174"/>
       <c r="AI21" s="3"/>
       <c r="AJ21" s="3"/>
       <c r="AK21" s="3"/>
@@ -19727,20 +19696,20 @@
       <c r="P22" s="69"/>
       <c r="Q22" s="69"/>
       <c r="R22" s="69"/>
-      <c r="S22" s="183"/>
-      <c r="T22" s="184"/>
-      <c r="U22" s="184"/>
-      <c r="V22" s="184"/>
-      <c r="W22" s="184"/>
-      <c r="X22" s="184"/>
-      <c r="Y22" s="184"/>
-      <c r="Z22" s="184"/>
-      <c r="AA22" s="184"/>
-      <c r="AB22" s="184"/>
-      <c r="AC22" s="184"/>
-      <c r="AD22" s="184"/>
-      <c r="AE22" s="184"/>
-      <c r="AF22" s="185"/>
+      <c r="S22" s="172"/>
+      <c r="T22" s="173"/>
+      <c r="U22" s="173"/>
+      <c r="V22" s="173"/>
+      <c r="W22" s="173"/>
+      <c r="X22" s="173"/>
+      <c r="Y22" s="173"/>
+      <c r="Z22" s="173"/>
+      <c r="AA22" s="173"/>
+      <c r="AB22" s="173"/>
+      <c r="AC22" s="173"/>
+      <c r="AD22" s="173"/>
+      <c r="AE22" s="173"/>
+      <c r="AF22" s="174"/>
       <c r="AI22" s="3"/>
       <c r="AJ22" s="3"/>
       <c r="AK22" s="3"/>
@@ -19961,10 +19930,10 @@
       <c r="A23" s="101" t="s">
         <v>111</v>
       </c>
-      <c r="B23" s="186" t="s">
+      <c r="B23" s="181" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="187"/>
+      <c r="C23" s="182"/>
       <c r="D23" s="92" t="s">
         <v>110</v>
       </c>
@@ -19984,20 +19953,20 @@
       <c r="P23" s="69"/>
       <c r="Q23" s="69"/>
       <c r="R23" s="69"/>
-      <c r="S23" s="183"/>
-      <c r="T23" s="184"/>
-      <c r="U23" s="184"/>
-      <c r="V23" s="184"/>
-      <c r="W23" s="184"/>
-      <c r="X23" s="184"/>
-      <c r="Y23" s="184"/>
-      <c r="Z23" s="184"/>
-      <c r="AA23" s="184"/>
-      <c r="AB23" s="184"/>
-      <c r="AC23" s="184"/>
-      <c r="AD23" s="184"/>
-      <c r="AE23" s="184"/>
-      <c r="AF23" s="185"/>
+      <c r="S23" s="172"/>
+      <c r="T23" s="173"/>
+      <c r="U23" s="173"/>
+      <c r="V23" s="173"/>
+      <c r="W23" s="173"/>
+      <c r="X23" s="173"/>
+      <c r="Y23" s="173"/>
+      <c r="Z23" s="173"/>
+      <c r="AA23" s="173"/>
+      <c r="AB23" s="173"/>
+      <c r="AC23" s="173"/>
+      <c r="AD23" s="173"/>
+      <c r="AE23" s="173"/>
+      <c r="AF23" s="174"/>
       <c r="AI23" s="3"/>
       <c r="AJ23" s="3"/>
       <c r="AK23" s="3"/>
@@ -20241,20 +20210,20 @@
       <c r="P24" s="69"/>
       <c r="Q24" s="69"/>
       <c r="R24" s="69"/>
-      <c r="S24" s="183"/>
-      <c r="T24" s="184"/>
-      <c r="U24" s="184"/>
-      <c r="V24" s="184"/>
-      <c r="W24" s="184"/>
-      <c r="X24" s="184"/>
-      <c r="Y24" s="184"/>
-      <c r="Z24" s="184"/>
-      <c r="AA24" s="184"/>
-      <c r="AB24" s="184"/>
-      <c r="AC24" s="184"/>
-      <c r="AD24" s="184"/>
-      <c r="AE24" s="184"/>
-      <c r="AF24" s="185"/>
+      <c r="S24" s="172"/>
+      <c r="T24" s="173"/>
+      <c r="U24" s="173"/>
+      <c r="V24" s="173"/>
+      <c r="W24" s="173"/>
+      <c r="X24" s="173"/>
+      <c r="Y24" s="173"/>
+      <c r="Z24" s="173"/>
+      <c r="AA24" s="173"/>
+      <c r="AB24" s="173"/>
+      <c r="AC24" s="173"/>
+      <c r="AD24" s="173"/>
+      <c r="AE24" s="173"/>
+      <c r="AF24" s="174"/>
       <c r="AI24" s="3"/>
       <c r="AJ24" s="3"/>
       <c r="AK24" s="3"/>
@@ -20496,20 +20465,20 @@
       <c r="P25" s="69"/>
       <c r="Q25" s="69"/>
       <c r="R25" s="69"/>
-      <c r="S25" s="183"/>
-      <c r="T25" s="184"/>
-      <c r="U25" s="184"/>
-      <c r="V25" s="184"/>
-      <c r="W25" s="184"/>
-      <c r="X25" s="184"/>
-      <c r="Y25" s="184"/>
-      <c r="Z25" s="184"/>
-      <c r="AA25" s="184"/>
-      <c r="AB25" s="184"/>
-      <c r="AC25" s="184"/>
-      <c r="AD25" s="184"/>
-      <c r="AE25" s="184"/>
-      <c r="AF25" s="185"/>
+      <c r="S25" s="172"/>
+      <c r="T25" s="173"/>
+      <c r="U25" s="173"/>
+      <c r="V25" s="173"/>
+      <c r="W25" s="173"/>
+      <c r="X25" s="173"/>
+      <c r="Y25" s="173"/>
+      <c r="Z25" s="173"/>
+      <c r="AA25" s="173"/>
+      <c r="AB25" s="173"/>
+      <c r="AC25" s="173"/>
+      <c r="AD25" s="173"/>
+      <c r="AE25" s="173"/>
+      <c r="AF25" s="174"/>
       <c r="AI25" s="3"/>
       <c r="AJ25" s="3"/>
       <c r="AK25" s="3"/>
@@ -20751,20 +20720,20 @@
       <c r="P26" s="69"/>
       <c r="Q26" s="69"/>
       <c r="R26" s="69"/>
-      <c r="S26" s="183"/>
-      <c r="T26" s="184"/>
-      <c r="U26" s="184"/>
-      <c r="V26" s="184"/>
-      <c r="W26" s="184"/>
-      <c r="X26" s="184"/>
-      <c r="Y26" s="184"/>
-      <c r="Z26" s="184"/>
-      <c r="AA26" s="184"/>
-      <c r="AB26" s="184"/>
-      <c r="AC26" s="184"/>
-      <c r="AD26" s="184"/>
-      <c r="AE26" s="184"/>
-      <c r="AF26" s="185"/>
+      <c r="S26" s="172"/>
+      <c r="T26" s="173"/>
+      <c r="U26" s="173"/>
+      <c r="V26" s="173"/>
+      <c r="W26" s="173"/>
+      <c r="X26" s="173"/>
+      <c r="Y26" s="173"/>
+      <c r="Z26" s="173"/>
+      <c r="AA26" s="173"/>
+      <c r="AB26" s="173"/>
+      <c r="AC26" s="173"/>
+      <c r="AD26" s="173"/>
+      <c r="AE26" s="173"/>
+      <c r="AF26" s="174"/>
       <c r="AI26" s="3"/>
       <c r="AJ26" s="3"/>
       <c r="AK26" s="3"/>
@@ -21006,20 +20975,20 @@
       <c r="P27" s="69"/>
       <c r="Q27" s="69"/>
       <c r="R27" s="69"/>
-      <c r="S27" s="183"/>
-      <c r="T27" s="184"/>
-      <c r="U27" s="184"/>
-      <c r="V27" s="184"/>
-      <c r="W27" s="184"/>
-      <c r="X27" s="184"/>
-      <c r="Y27" s="184"/>
-      <c r="Z27" s="184"/>
-      <c r="AA27" s="184"/>
-      <c r="AB27" s="184"/>
-      <c r="AC27" s="184"/>
-      <c r="AD27" s="184"/>
-      <c r="AE27" s="184"/>
-      <c r="AF27" s="185"/>
+      <c r="S27" s="172"/>
+      <c r="T27" s="173"/>
+      <c r="U27" s="173"/>
+      <c r="V27" s="173"/>
+      <c r="W27" s="173"/>
+      <c r="X27" s="173"/>
+      <c r="Y27" s="173"/>
+      <c r="Z27" s="173"/>
+      <c r="AA27" s="173"/>
+      <c r="AB27" s="173"/>
+      <c r="AC27" s="173"/>
+      <c r="AD27" s="173"/>
+      <c r="AE27" s="173"/>
+      <c r="AF27" s="174"/>
       <c r="AI27" s="3"/>
       <c r="AJ27" s="3"/>
       <c r="AK27" s="3"/>
@@ -21261,20 +21230,20 @@
       <c r="P28" s="69"/>
       <c r="Q28" s="69"/>
       <c r="R28" s="69"/>
-      <c r="S28" s="183"/>
-      <c r="T28" s="184"/>
-      <c r="U28" s="184"/>
-      <c r="V28" s="184"/>
-      <c r="W28" s="184"/>
-      <c r="X28" s="184"/>
-      <c r="Y28" s="184"/>
-      <c r="Z28" s="184"/>
-      <c r="AA28" s="184"/>
-      <c r="AB28" s="184"/>
-      <c r="AC28" s="184"/>
-      <c r="AD28" s="184"/>
-      <c r="AE28" s="184"/>
-      <c r="AF28" s="185"/>
+      <c r="S28" s="172"/>
+      <c r="T28" s="173"/>
+      <c r="U28" s="173"/>
+      <c r="V28" s="173"/>
+      <c r="W28" s="173"/>
+      <c r="X28" s="173"/>
+      <c r="Y28" s="173"/>
+      <c r="Z28" s="173"/>
+      <c r="AA28" s="173"/>
+      <c r="AB28" s="173"/>
+      <c r="AC28" s="173"/>
+      <c r="AD28" s="173"/>
+      <c r="AE28" s="173"/>
+      <c r="AF28" s="174"/>
       <c r="AI28" s="3"/>
       <c r="AJ28" s="3"/>
       <c r="AK28" s="3"/>
@@ -21512,20 +21481,20 @@
       <c r="P29" s="69"/>
       <c r="Q29" s="69"/>
       <c r="R29" s="69"/>
-      <c r="S29" s="183"/>
-      <c r="T29" s="184"/>
-      <c r="U29" s="184"/>
-      <c r="V29" s="184"/>
-      <c r="W29" s="184"/>
-      <c r="X29" s="184"/>
-      <c r="Y29" s="184"/>
-      <c r="Z29" s="184"/>
-      <c r="AA29" s="184"/>
-      <c r="AB29" s="184"/>
-      <c r="AC29" s="184"/>
-      <c r="AD29" s="184"/>
-      <c r="AE29" s="184"/>
-      <c r="AF29" s="185"/>
+      <c r="S29" s="172"/>
+      <c r="T29" s="173"/>
+      <c r="U29" s="173"/>
+      <c r="V29" s="173"/>
+      <c r="W29" s="173"/>
+      <c r="X29" s="173"/>
+      <c r="Y29" s="173"/>
+      <c r="Z29" s="173"/>
+      <c r="AA29" s="173"/>
+      <c r="AB29" s="173"/>
+      <c r="AC29" s="173"/>
+      <c r="AD29" s="173"/>
+      <c r="AE29" s="173"/>
+      <c r="AF29" s="174"/>
       <c r="AI29" s="3"/>
       <c r="AJ29" s="3"/>
       <c r="AK29" s="3"/>
@@ -21744,10 +21713,10 @@
     </row>
     <row r="30" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A30" s="37"/>
-      <c r="B30" s="137" t="s">
+      <c r="B30" s="154" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="138"/>
+      <c r="C30" s="155"/>
       <c r="D30" s="92"/>
       <c r="E30" s="92"/>
       <c r="F30" s="36"/>
@@ -21763,20 +21732,20 @@
       <c r="P30" s="69"/>
       <c r="Q30" s="69"/>
       <c r="R30" s="69"/>
-      <c r="S30" s="183"/>
-      <c r="T30" s="184"/>
-      <c r="U30" s="184"/>
-      <c r="V30" s="184"/>
-      <c r="W30" s="184"/>
-      <c r="X30" s="184"/>
-      <c r="Y30" s="184"/>
-      <c r="Z30" s="184"/>
-      <c r="AA30" s="184"/>
-      <c r="AB30" s="184"/>
-      <c r="AC30" s="184"/>
-      <c r="AD30" s="184"/>
-      <c r="AE30" s="184"/>
-      <c r="AF30" s="185"/>
+      <c r="S30" s="172"/>
+      <c r="T30" s="173"/>
+      <c r="U30" s="173"/>
+      <c r="V30" s="173"/>
+      <c r="W30" s="173"/>
+      <c r="X30" s="173"/>
+      <c r="Y30" s="173"/>
+      <c r="Z30" s="173"/>
+      <c r="AA30" s="173"/>
+      <c r="AB30" s="173"/>
+      <c r="AC30" s="173"/>
+      <c r="AD30" s="173"/>
+      <c r="AE30" s="173"/>
+      <c r="AF30" s="174"/>
       <c r="AI30" s="3"/>
       <c r="AJ30" s="3"/>
       <c r="AK30" s="3"/>
@@ -21999,7 +21968,7 @@
         <v>92</v>
       </c>
       <c r="C31" s="118"/>
-      <c r="D31" s="124" t="s">
+      <c r="D31" s="158" t="s">
         <v>117</v>
       </c>
       <c r="E31" s="92"/>
@@ -22016,20 +21985,20 @@
       <c r="P31" s="69"/>
       <c r="Q31" s="69"/>
       <c r="R31" s="69"/>
-      <c r="S31" s="183"/>
-      <c r="T31" s="184"/>
-      <c r="U31" s="184"/>
-      <c r="V31" s="184"/>
-      <c r="W31" s="184"/>
-      <c r="X31" s="184"/>
-      <c r="Y31" s="184"/>
-      <c r="Z31" s="184"/>
-      <c r="AA31" s="184"/>
-      <c r="AB31" s="184"/>
-      <c r="AC31" s="184"/>
-      <c r="AD31" s="184"/>
-      <c r="AE31" s="184"/>
-      <c r="AF31" s="185"/>
+      <c r="S31" s="172"/>
+      <c r="T31" s="173"/>
+      <c r="U31" s="173"/>
+      <c r="V31" s="173"/>
+      <c r="W31" s="173"/>
+      <c r="X31" s="173"/>
+      <c r="Y31" s="173"/>
+      <c r="Z31" s="173"/>
+      <c r="AA31" s="173"/>
+      <c r="AB31" s="173"/>
+      <c r="AC31" s="173"/>
+      <c r="AD31" s="173"/>
+      <c r="AE31" s="173"/>
+      <c r="AF31" s="174"/>
       <c r="AI31" s="3"/>
       <c r="AJ31" s="3"/>
       <c r="AK31" s="3"/>
@@ -22252,7 +22221,7 @@
         <v>93</v>
       </c>
       <c r="C32" s="118"/>
-      <c r="D32" s="125"/>
+      <c r="D32" s="119"/>
       <c r="E32" s="92" t="s">
         <v>47</v>
       </c>
@@ -22269,20 +22238,20 @@
       <c r="P32" s="68"/>
       <c r="Q32" s="68"/>
       <c r="R32" s="68"/>
-      <c r="S32" s="183"/>
-      <c r="T32" s="184"/>
-      <c r="U32" s="184"/>
-      <c r="V32" s="184"/>
-      <c r="W32" s="184"/>
-      <c r="X32" s="184"/>
-      <c r="Y32" s="184"/>
-      <c r="Z32" s="184"/>
-      <c r="AA32" s="184"/>
-      <c r="AB32" s="184"/>
-      <c r="AC32" s="184"/>
-      <c r="AD32" s="184"/>
-      <c r="AE32" s="184"/>
-      <c r="AF32" s="185"/>
+      <c r="S32" s="172"/>
+      <c r="T32" s="173"/>
+      <c r="U32" s="173"/>
+      <c r="V32" s="173"/>
+      <c r="W32" s="173"/>
+      <c r="X32" s="173"/>
+      <c r="Y32" s="173"/>
+      <c r="Z32" s="173"/>
+      <c r="AA32" s="173"/>
+      <c r="AB32" s="173"/>
+      <c r="AC32" s="173"/>
+      <c r="AD32" s="173"/>
+      <c r="AE32" s="173"/>
+      <c r="AF32" s="174"/>
       <c r="AI32" s="3"/>
       <c r="AJ32" s="3"/>
       <c r="AK32" s="3"/>
@@ -22505,7 +22474,7 @@
         <v>94</v>
       </c>
       <c r="C33" s="118"/>
-      <c r="D33" s="126"/>
+      <c r="D33" s="120"/>
       <c r="E33" s="92"/>
       <c r="F33" s="36"/>
       <c r="G33" s="68"/>
@@ -22520,20 +22489,20 @@
       <c r="P33" s="68"/>
       <c r="Q33" s="68"/>
       <c r="R33" s="68"/>
-      <c r="S33" s="183"/>
-      <c r="T33" s="184"/>
-      <c r="U33" s="184"/>
-      <c r="V33" s="184"/>
-      <c r="W33" s="184"/>
-      <c r="X33" s="184"/>
-      <c r="Y33" s="184"/>
-      <c r="Z33" s="184"/>
-      <c r="AA33" s="184"/>
-      <c r="AB33" s="184"/>
-      <c r="AC33" s="184"/>
-      <c r="AD33" s="184"/>
-      <c r="AE33" s="184"/>
-      <c r="AF33" s="185"/>
+      <c r="S33" s="172"/>
+      <c r="T33" s="173"/>
+      <c r="U33" s="173"/>
+      <c r="V33" s="173"/>
+      <c r="W33" s="173"/>
+      <c r="X33" s="173"/>
+      <c r="Y33" s="173"/>
+      <c r="Z33" s="173"/>
+      <c r="AA33" s="173"/>
+      <c r="AB33" s="173"/>
+      <c r="AC33" s="173"/>
+      <c r="AD33" s="173"/>
+      <c r="AE33" s="173"/>
+      <c r="AF33" s="174"/>
       <c r="AI33" s="3"/>
       <c r="AJ33" s="3"/>
       <c r="AK33" s="3"/>
@@ -22752,10 +22721,10 @@
     </row>
     <row r="34" spans="1:249" s="2" customFormat="1" ht="28.25" customHeight="1">
       <c r="A34" s="38"/>
-      <c r="B34" s="137" t="s">
+      <c r="B34" s="154" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="138"/>
+      <c r="C34" s="155"/>
       <c r="D34" s="35"/>
       <c r="E34" s="35"/>
       <c r="F34" s="39"/>
@@ -22771,20 +22740,20 @@
       <c r="P34" s="68"/>
       <c r="Q34" s="68"/>
       <c r="R34" s="68"/>
-      <c r="S34" s="183"/>
-      <c r="T34" s="184"/>
-      <c r="U34" s="184"/>
-      <c r="V34" s="184"/>
-      <c r="W34" s="184"/>
-      <c r="X34" s="184"/>
-      <c r="Y34" s="184"/>
-      <c r="Z34" s="184"/>
-      <c r="AA34" s="184"/>
-      <c r="AB34" s="184"/>
-      <c r="AC34" s="184"/>
-      <c r="AD34" s="184"/>
-      <c r="AE34" s="184"/>
-      <c r="AF34" s="185"/>
+      <c r="S34" s="172"/>
+      <c r="T34" s="173"/>
+      <c r="U34" s="173"/>
+      <c r="V34" s="173"/>
+      <c r="W34" s="173"/>
+      <c r="X34" s="173"/>
+      <c r="Y34" s="173"/>
+      <c r="Z34" s="173"/>
+      <c r="AA34" s="173"/>
+      <c r="AB34" s="173"/>
+      <c r="AC34" s="173"/>
+      <c r="AD34" s="173"/>
+      <c r="AE34" s="173"/>
+      <c r="AF34" s="174"/>
       <c r="AI34" s="3"/>
       <c r="AJ34" s="3"/>
       <c r="AK34" s="3"/>
@@ -23005,15 +22974,15 @@
       <c r="A35" s="37">
         <v>1</v>
       </c>
-      <c r="B35" s="122" t="s">
+      <c r="B35" s="156" t="s">
         <v>104</v>
       </c>
-      <c r="C35" s="123"/>
+      <c r="C35" s="157"/>
       <c r="D35" s="96"/>
       <c r="E35" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="F35" s="124" t="s">
+      <c r="F35" s="158" t="s">
         <v>95</v>
       </c>
       <c r="G35" s="69"/>
@@ -23028,20 +22997,20 @@
       <c r="P35" s="69"/>
       <c r="Q35" s="69"/>
       <c r="R35" s="69"/>
-      <c r="S35" s="183"/>
-      <c r="T35" s="184"/>
-      <c r="U35" s="184"/>
-      <c r="V35" s="184"/>
-      <c r="W35" s="184"/>
-      <c r="X35" s="184"/>
-      <c r="Y35" s="184"/>
-      <c r="Z35" s="184"/>
-      <c r="AA35" s="184"/>
-      <c r="AB35" s="184"/>
-      <c r="AC35" s="184"/>
-      <c r="AD35" s="184"/>
-      <c r="AE35" s="184"/>
-      <c r="AF35" s="185"/>
+      <c r="S35" s="172"/>
+      <c r="T35" s="173"/>
+      <c r="U35" s="173"/>
+      <c r="V35" s="173"/>
+      <c r="W35" s="173"/>
+      <c r="X35" s="173"/>
+      <c r="Y35" s="173"/>
+      <c r="Z35" s="173"/>
+      <c r="AA35" s="173"/>
+      <c r="AB35" s="173"/>
+      <c r="AC35" s="173"/>
+      <c r="AD35" s="173"/>
+      <c r="AE35" s="173"/>
+      <c r="AF35" s="174"/>
       <c r="AI35" s="3"/>
       <c r="AJ35" s="3"/>
       <c r="AK35" s="3"/>
@@ -23268,7 +23237,7 @@
       <c r="E36" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="F36" s="125"/>
+      <c r="F36" s="119"/>
       <c r="G36" s="68"/>
       <c r="H36" s="68"/>
       <c r="I36" s="68"/>
@@ -23281,20 +23250,20 @@
       <c r="P36" s="68"/>
       <c r="Q36" s="68"/>
       <c r="R36" s="68"/>
-      <c r="S36" s="183"/>
-      <c r="T36" s="184"/>
-      <c r="U36" s="184"/>
-      <c r="V36" s="184"/>
-      <c r="W36" s="184"/>
-      <c r="X36" s="184"/>
-      <c r="Y36" s="184"/>
-      <c r="Z36" s="184"/>
-      <c r="AA36" s="184"/>
-      <c r="AB36" s="184"/>
-      <c r="AC36" s="184"/>
-      <c r="AD36" s="184"/>
-      <c r="AE36" s="184"/>
-      <c r="AF36" s="185"/>
+      <c r="S36" s="172"/>
+      <c r="T36" s="173"/>
+      <c r="U36" s="173"/>
+      <c r="V36" s="173"/>
+      <c r="W36" s="173"/>
+      <c r="X36" s="173"/>
+      <c r="Y36" s="173"/>
+      <c r="Z36" s="173"/>
+      <c r="AA36" s="173"/>
+      <c r="AB36" s="173"/>
+      <c r="AC36" s="173"/>
+      <c r="AD36" s="173"/>
+      <c r="AE36" s="173"/>
+      <c r="AF36" s="174"/>
       <c r="AI36" s="3"/>
       <c r="AJ36" s="3"/>
       <c r="AK36" s="3"/>
@@ -23515,11 +23484,11 @@
       <c r="A37" s="37">
         <v>3</v>
       </c>
-      <c r="B37" s="122"/>
-      <c r="C37" s="123"/>
+      <c r="B37" s="156"/>
+      <c r="C37" s="157"/>
       <c r="D37" s="92"/>
       <c r="E37" s="35"/>
-      <c r="F37" s="125"/>
+      <c r="F37" s="119"/>
       <c r="G37" s="68"/>
       <c r="H37" s="68"/>
       <c r="I37" s="68"/>
@@ -23532,20 +23501,20 @@
       <c r="P37" s="68"/>
       <c r="Q37" s="68"/>
       <c r="R37" s="68"/>
-      <c r="S37" s="183"/>
-      <c r="T37" s="184"/>
-      <c r="U37" s="184"/>
-      <c r="V37" s="184"/>
-      <c r="W37" s="184"/>
-      <c r="X37" s="184"/>
-      <c r="Y37" s="184"/>
-      <c r="Z37" s="184"/>
-      <c r="AA37" s="184"/>
-      <c r="AB37" s="184"/>
-      <c r="AC37" s="184"/>
-      <c r="AD37" s="184"/>
-      <c r="AE37" s="184"/>
-      <c r="AF37" s="185"/>
+      <c r="S37" s="172"/>
+      <c r="T37" s="173"/>
+      <c r="U37" s="173"/>
+      <c r="V37" s="173"/>
+      <c r="W37" s="173"/>
+      <c r="X37" s="173"/>
+      <c r="Y37" s="173"/>
+      <c r="Z37" s="173"/>
+      <c r="AA37" s="173"/>
+      <c r="AB37" s="173"/>
+      <c r="AC37" s="173"/>
+      <c r="AD37" s="173"/>
+      <c r="AE37" s="173"/>
+      <c r="AF37" s="174"/>
       <c r="AI37" s="3"/>
       <c r="AJ37" s="3"/>
       <c r="AK37" s="3"/>
@@ -23764,10 +23733,10 @@
     </row>
     <row r="38" spans="1:249" s="2" customFormat="1" ht="42" customHeight="1" thickBot="1">
       <c r="A38" s="41"/>
-      <c r="B38" s="133" t="s">
+      <c r="B38" s="168" t="s">
         <v>63</v>
       </c>
-      <c r="C38" s="134"/>
+      <c r="C38" s="169"/>
       <c r="D38" s="42" t="s">
         <v>16</v>
       </c>
@@ -24025,29 +23994,29 @@
       <c r="E39" s="44"/>
       <c r="F39" s="57"/>
       <c r="G39" s="75"/>
-      <c r="H39" s="188"/>
-      <c r="I39" s="188"/>
-      <c r="J39" s="188"/>
-      <c r="K39" s="188"/>
+      <c r="H39" s="180"/>
+      <c r="I39" s="180"/>
+      <c r="J39" s="180"/>
+      <c r="K39" s="180"/>
       <c r="L39" s="76"/>
       <c r="M39" s="75"/>
-      <c r="N39" s="188"/>
-      <c r="O39" s="188"/>
-      <c r="P39" s="188"/>
-      <c r="Q39" s="188"/>
+      <c r="N39" s="180"/>
+      <c r="O39" s="180"/>
+      <c r="P39" s="180"/>
+      <c r="Q39" s="180"/>
       <c r="R39" s="76"/>
       <c r="S39" s="75"/>
-      <c r="T39" s="188"/>
-      <c r="U39" s="188"/>
-      <c r="V39" s="188"/>
+      <c r="T39" s="180"/>
+      <c r="U39" s="180"/>
+      <c r="V39" s="180"/>
       <c r="W39" s="75"/>
-      <c r="X39" s="188"/>
-      <c r="Y39" s="188"/>
-      <c r="Z39" s="188"/>
+      <c r="X39" s="180"/>
+      <c r="Y39" s="180"/>
+      <c r="Z39" s="180"/>
       <c r="AA39" s="76"/>
       <c r="AB39" s="75"/>
-      <c r="AC39" s="188"/>
-      <c r="AD39" s="188"/>
+      <c r="AC39" s="180"/>
+      <c r="AD39" s="180"/>
       <c r="AE39" s="55"/>
       <c r="AF39" s="56"/>
       <c r="AI39" s="3"/>
@@ -24278,29 +24247,29 @@
       <c r="E40" s="90"/>
       <c r="F40" s="58"/>
       <c r="G40" s="77"/>
-      <c r="H40" s="189"/>
-      <c r="I40" s="189"/>
-      <c r="J40" s="189"/>
-      <c r="K40" s="189"/>
+      <c r="H40" s="179"/>
+      <c r="I40" s="179"/>
+      <c r="J40" s="179"/>
+      <c r="K40" s="179"/>
       <c r="L40" s="78"/>
       <c r="M40" s="77"/>
-      <c r="N40" s="189"/>
-      <c r="O40" s="189"/>
-      <c r="P40" s="189"/>
-      <c r="Q40" s="189"/>
+      <c r="N40" s="179"/>
+      <c r="O40" s="179"/>
+      <c r="P40" s="179"/>
+      <c r="Q40" s="179"/>
       <c r="R40" s="78"/>
       <c r="S40" s="77"/>
-      <c r="T40" s="189"/>
-      <c r="U40" s="189"/>
-      <c r="V40" s="189"/>
+      <c r="T40" s="179"/>
+      <c r="U40" s="179"/>
+      <c r="V40" s="179"/>
       <c r="W40" s="77"/>
-      <c r="X40" s="189"/>
-      <c r="Y40" s="189"/>
-      <c r="Z40" s="189"/>
+      <c r="X40" s="179"/>
+      <c r="Y40" s="179"/>
+      <c r="Z40" s="179"/>
       <c r="AA40" s="78"/>
       <c r="AB40" s="77"/>
-      <c r="AC40" s="189"/>
-      <c r="AD40" s="189"/>
+      <c r="AC40" s="179"/>
+      <c r="AD40" s="179"/>
       <c r="AE40" s="61"/>
       <c r="AF40" s="79"/>
       <c r="AI40" s="3"/>
@@ -24531,29 +24500,29 @@
       <c r="E41" s="91"/>
       <c r="F41" s="59"/>
       <c r="G41" s="77"/>
-      <c r="H41" s="189"/>
-      <c r="I41" s="189"/>
-      <c r="J41" s="189"/>
-      <c r="K41" s="189"/>
+      <c r="H41" s="179"/>
+      <c r="I41" s="179"/>
+      <c r="J41" s="179"/>
+      <c r="K41" s="179"/>
       <c r="L41" s="80"/>
       <c r="M41" s="77"/>
-      <c r="N41" s="189"/>
-      <c r="O41" s="189"/>
-      <c r="P41" s="189"/>
-      <c r="Q41" s="189"/>
+      <c r="N41" s="179"/>
+      <c r="O41" s="179"/>
+      <c r="P41" s="179"/>
+      <c r="Q41" s="179"/>
       <c r="R41" s="80"/>
       <c r="S41" s="77"/>
-      <c r="T41" s="189"/>
-      <c r="U41" s="189"/>
-      <c r="V41" s="189"/>
+      <c r="T41" s="179"/>
+      <c r="U41" s="179"/>
+      <c r="V41" s="179"/>
       <c r="W41" s="77"/>
-      <c r="X41" s="189"/>
-      <c r="Y41" s="189"/>
-      <c r="Z41" s="189"/>
+      <c r="X41" s="179"/>
+      <c r="Y41" s="179"/>
+      <c r="Z41" s="179"/>
       <c r="AA41" s="80"/>
       <c r="AB41" s="77"/>
-      <c r="AC41" s="189"/>
-      <c r="AD41" s="189"/>
+      <c r="AC41" s="179"/>
+      <c r="AD41" s="179"/>
       <c r="AE41" s="62"/>
       <c r="AF41" s="81"/>
       <c r="AI41" s="3"/>
@@ -24784,29 +24753,29 @@
       <c r="E42" s="91"/>
       <c r="F42" s="59"/>
       <c r="G42" s="77"/>
-      <c r="H42" s="189"/>
-      <c r="I42" s="189"/>
-      <c r="J42" s="189"/>
-      <c r="K42" s="189"/>
+      <c r="H42" s="179"/>
+      <c r="I42" s="179"/>
+      <c r="J42" s="179"/>
+      <c r="K42" s="179"/>
       <c r="L42" s="80"/>
       <c r="M42" s="77"/>
-      <c r="N42" s="189"/>
-      <c r="O42" s="189"/>
-      <c r="P42" s="189"/>
-      <c r="Q42" s="189"/>
+      <c r="N42" s="179"/>
+      <c r="O42" s="179"/>
+      <c r="P42" s="179"/>
+      <c r="Q42" s="179"/>
       <c r="R42" s="80"/>
       <c r="S42" s="77"/>
-      <c r="T42" s="189"/>
-      <c r="U42" s="189"/>
-      <c r="V42" s="189"/>
+      <c r="T42" s="179"/>
+      <c r="U42" s="179"/>
+      <c r="V42" s="179"/>
       <c r="W42" s="77"/>
-      <c r="X42" s="189"/>
-      <c r="Y42" s="189"/>
-      <c r="Z42" s="189"/>
+      <c r="X42" s="179"/>
+      <c r="Y42" s="179"/>
+      <c r="Z42" s="179"/>
       <c r="AA42" s="80"/>
       <c r="AB42" s="77"/>
-      <c r="AC42" s="189"/>
-      <c r="AD42" s="189"/>
+      <c r="AC42" s="179"/>
+      <c r="AD42" s="179"/>
       <c r="AE42" s="62"/>
       <c r="AF42" s="81"/>
       <c r="AI42" s="3"/>
@@ -25033,29 +25002,29 @@
       <c r="E43" s="50"/>
       <c r="F43" s="60"/>
       <c r="G43" s="82"/>
-      <c r="H43" s="190"/>
-      <c r="I43" s="190"/>
-      <c r="J43" s="190"/>
-      <c r="K43" s="190"/>
+      <c r="H43" s="175"/>
+      <c r="I43" s="175"/>
+      <c r="J43" s="175"/>
+      <c r="K43" s="175"/>
       <c r="L43" s="83"/>
       <c r="M43" s="82"/>
-      <c r="N43" s="190"/>
-      <c r="O43" s="190"/>
-      <c r="P43" s="190"/>
-      <c r="Q43" s="190"/>
+      <c r="N43" s="175"/>
+      <c r="O43" s="175"/>
+      <c r="P43" s="175"/>
+      <c r="Q43" s="175"/>
       <c r="R43" s="83"/>
       <c r="S43" s="82"/>
-      <c r="T43" s="190"/>
-      <c r="U43" s="190"/>
-      <c r="V43" s="190"/>
+      <c r="T43" s="175"/>
+      <c r="U43" s="175"/>
+      <c r="V43" s="175"/>
       <c r="W43" s="82"/>
-      <c r="X43" s="190"/>
-      <c r="Y43" s="190"/>
-      <c r="Z43" s="190"/>
+      <c r="X43" s="175"/>
+      <c r="Y43" s="175"/>
+      <c r="Z43" s="175"/>
       <c r="AA43" s="83"/>
       <c r="AB43" s="82"/>
-      <c r="AC43" s="190"/>
-      <c r="AD43" s="190"/>
+      <c r="AC43" s="175"/>
+      <c r="AD43" s="175"/>
       <c r="AE43" s="63"/>
       <c r="AF43" s="84"/>
       <c r="AI43" s="3"/>
@@ -25319,18 +25288,78 @@
     </row>
   </sheetData>
   <mergeCells count="100">
-    <mergeCell ref="S32:AF32"/>
-    <mergeCell ref="S33:AF33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="S26:AF26"/>
-    <mergeCell ref="S28:AF28"/>
-    <mergeCell ref="S29:AF29"/>
-    <mergeCell ref="S30:AF30"/>
-    <mergeCell ref="S31:AF31"/>
-    <mergeCell ref="S27:AF27"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:AF1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="T3:AF3"/>
+    <mergeCell ref="T5:W7"/>
+    <mergeCell ref="AD4:AF4"/>
+    <mergeCell ref="AD5:AF7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="S11:AF11"/>
+    <mergeCell ref="S12:AF12"/>
+    <mergeCell ref="S13:AF13"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="T4:W4"/>
+    <mergeCell ref="X4:Z4"/>
+    <mergeCell ref="AA4:AC4"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="S14:AF14"/>
+    <mergeCell ref="S15:AF15"/>
+    <mergeCell ref="S16:AF16"/>
+    <mergeCell ref="S17:AF17"/>
+    <mergeCell ref="S18:AF18"/>
+    <mergeCell ref="S19:AF19"/>
+    <mergeCell ref="S25:AF25"/>
+    <mergeCell ref="S24:AF24"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="AC39:AD39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="H39:K39"/>
+    <mergeCell ref="N39:Q39"/>
+    <mergeCell ref="S36:AF36"/>
+    <mergeCell ref="S37:AF37"/>
+    <mergeCell ref="H40:K40"/>
+    <mergeCell ref="N40:Q40"/>
+    <mergeCell ref="T40:V40"/>
+    <mergeCell ref="X40:Z40"/>
+    <mergeCell ref="AC40:AD40"/>
+    <mergeCell ref="H43:K43"/>
+    <mergeCell ref="N43:Q43"/>
+    <mergeCell ref="T43:V43"/>
+    <mergeCell ref="X43:Z43"/>
+    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="N41:Q41"/>
+    <mergeCell ref="H42:K42"/>
+    <mergeCell ref="N42:Q42"/>
     <mergeCell ref="AC43:AD43"/>
     <mergeCell ref="S9:AF9"/>
     <mergeCell ref="S20:AF20"/>
@@ -25347,82 +25376,22 @@
     <mergeCell ref="X39:Z39"/>
     <mergeCell ref="S34:AF34"/>
     <mergeCell ref="S35:AF35"/>
-    <mergeCell ref="H43:K43"/>
-    <mergeCell ref="N43:Q43"/>
-    <mergeCell ref="T43:V43"/>
-    <mergeCell ref="X43:Z43"/>
-    <mergeCell ref="H41:K41"/>
-    <mergeCell ref="N41:Q41"/>
-    <mergeCell ref="H42:K42"/>
-    <mergeCell ref="N42:Q42"/>
-    <mergeCell ref="H40:K40"/>
-    <mergeCell ref="N40:Q40"/>
-    <mergeCell ref="T40:V40"/>
-    <mergeCell ref="X40:Z40"/>
-    <mergeCell ref="AC40:AD40"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="F35:F37"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="AC39:AD39"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="H39:K39"/>
-    <mergeCell ref="N39:Q39"/>
-    <mergeCell ref="S36:AF36"/>
-    <mergeCell ref="S37:AF37"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="S14:AF14"/>
-    <mergeCell ref="S15:AF15"/>
-    <mergeCell ref="S16:AF16"/>
-    <mergeCell ref="S17:AF17"/>
-    <mergeCell ref="S18:AF18"/>
-    <mergeCell ref="S19:AF19"/>
-    <mergeCell ref="S25:AF25"/>
-    <mergeCell ref="S24:AF24"/>
-    <mergeCell ref="T5:W7"/>
-    <mergeCell ref="AD4:AF4"/>
-    <mergeCell ref="AD5:AF7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="S11:AF11"/>
-    <mergeCell ref="S12:AF12"/>
-    <mergeCell ref="S13:AF13"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="T4:W4"/>
-    <mergeCell ref="X4:Z4"/>
-    <mergeCell ref="AA4:AC4"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="F1:AF1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="T3:AF3"/>
+    <mergeCell ref="S26:AF26"/>
+    <mergeCell ref="S28:AF28"/>
+    <mergeCell ref="S29:AF29"/>
+    <mergeCell ref="S30:AF30"/>
+    <mergeCell ref="S31:AF31"/>
+    <mergeCell ref="S27:AF27"/>
+    <mergeCell ref="S32:AF32"/>
+    <mergeCell ref="S33:AF33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="B31:C31"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="G11:R19 AG11:AK19">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>TEXT(G11,"aaa")="日"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/設備点検表.xlsx
+++ b/設備点検表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kosuk\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8BABDBF-EEC3-4D88-91B1-594215637DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19409173-9DBE-4C7F-8154-6F4CE65B054C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6C56CF13-AF7F-4C1F-982C-EF388A11F51A}"/>
   </bookViews>
@@ -2765,71 +2765,65 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2870,92 +2864,65 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="71" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="72" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="73" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="67" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="74" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="178" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2990,23 +2957,45 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="71" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="72" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="73" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="67" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="74" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準_設備点検表書式" xfId="1" xr:uid="{15F629F0-A893-4DD8-8A94-9D447F97F79C}"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill>
@@ -3039,7 +3028,25 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3385,45 +3392,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:254" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="155" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="121"/>
+      <c r="B1" s="155"/>
       <c r="C1" s="85"/>
-      <c r="F1" s="122" t="s">
+      <c r="F1" s="156" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
-      <c r="AC1" s="122"/>
-      <c r="AD1" s="122"/>
-      <c r="AE1" s="122"/>
-      <c r="AF1" s="122"/>
-      <c r="AG1" s="122"/>
-      <c r="AH1" s="122"/>
-      <c r="AI1" s="122"/>
-      <c r="AJ1" s="122"/>
-      <c r="AK1" s="122"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+      <c r="L1" s="156"/>
+      <c r="M1" s="156"/>
+      <c r="N1" s="156"/>
+      <c r="O1" s="156"/>
+      <c r="P1" s="156"/>
+      <c r="Q1" s="156"/>
+      <c r="R1" s="156"/>
+      <c r="S1" s="156"/>
+      <c r="T1" s="156"/>
+      <c r="U1" s="156"/>
+      <c r="V1" s="156"/>
+      <c r="W1" s="156"/>
+      <c r="X1" s="156"/>
+      <c r="Y1" s="156"/>
+      <c r="Z1" s="156"/>
+      <c r="AA1" s="156"/>
+      <c r="AB1" s="156"/>
+      <c r="AC1" s="156"/>
+      <c r="AD1" s="156"/>
+      <c r="AE1" s="156"/>
+      <c r="AF1" s="156"/>
+      <c r="AG1" s="156"/>
+      <c r="AH1" s="156"/>
+      <c r="AI1" s="156"/>
+      <c r="AJ1" s="156"/>
+      <c r="AK1" s="156"/>
       <c r="AN1" s="3"/>
       <c r="AO1" s="3"/>
       <c r="AP1" s="3"/>
@@ -3894,52 +3901,52 @@
       <c r="IT2" s="3"/>
     </row>
     <row r="3" spans="1:254" s="2" customFormat="1" ht="20" customHeight="1" thickBot="1">
-      <c r="A3" s="123" t="s">
+      <c r="A3" s="157" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="125"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
       <c r="E3" s="94"/>
       <c r="G3" s="51"/>
       <c r="H3" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="126" t="s">
+      <c r="K3" s="160" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="126"/>
-      <c r="M3" s="126" t="s">
+      <c r="L3" s="160"/>
+      <c r="M3" s="160" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="126"/>
-      <c r="O3" s="126"/>
-      <c r="P3" s="126" t="s">
+      <c r="N3" s="160"/>
+      <c r="O3" s="160"/>
+      <c r="P3" s="160" t="s">
         <v>2</v>
       </c>
-      <c r="Q3" s="126"/>
-      <c r="R3" s="126"/>
+      <c r="Q3" s="160"/>
+      <c r="R3" s="160"/>
       <c r="S3" s="3"/>
-      <c r="T3" s="127" t="s">
+      <c r="T3" s="161" t="s">
         <v>3</v>
       </c>
-      <c r="U3" s="128"/>
-      <c r="V3" s="128"/>
-      <c r="W3" s="128"/>
-      <c r="X3" s="128"/>
-      <c r="Y3" s="128"/>
-      <c r="Z3" s="128"/>
-      <c r="AA3" s="128"/>
-      <c r="AB3" s="128"/>
-      <c r="AC3" s="128"/>
-      <c r="AD3" s="128"/>
-      <c r="AE3" s="128"/>
-      <c r="AF3" s="128"/>
-      <c r="AG3" s="128"/>
-      <c r="AH3" s="128"/>
-      <c r="AI3" s="128"/>
-      <c r="AJ3" s="128"/>
-      <c r="AK3" s="129"/>
+      <c r="U3" s="162"/>
+      <c r="V3" s="162"/>
+      <c r="W3" s="162"/>
+      <c r="X3" s="162"/>
+      <c r="Y3" s="162"/>
+      <c r="Z3" s="162"/>
+      <c r="AA3" s="162"/>
+      <c r="AB3" s="162"/>
+      <c r="AC3" s="162"/>
+      <c r="AD3" s="162"/>
+      <c r="AE3" s="162"/>
+      <c r="AF3" s="162"/>
+      <c r="AG3" s="162"/>
+      <c r="AH3" s="162"/>
+      <c r="AI3" s="162"/>
+      <c r="AJ3" s="162"/>
+      <c r="AK3" s="163"/>
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
@@ -4168,47 +4175,47 @@
       <c r="H4" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="126" t="s">
+      <c r="K4" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="126"/>
-      <c r="M4" s="132">
+      <c r="L4" s="160"/>
+      <c r="M4" s="166">
         <v>46113</v>
       </c>
-      <c r="N4" s="132"/>
-      <c r="O4" s="132"/>
-      <c r="P4" s="126" t="s">
+      <c r="N4" s="166"/>
+      <c r="O4" s="166"/>
+      <c r="P4" s="160" t="s">
         <v>50</v>
       </c>
-      <c r="Q4" s="126"/>
-      <c r="R4" s="126"/>
+      <c r="Q4" s="160"/>
+      <c r="R4" s="160"/>
       <c r="S4" s="3"/>
-      <c r="T4" s="133" t="s">
+      <c r="T4" s="152" t="s">
         <v>5</v>
       </c>
-      <c r="U4" s="134"/>
-      <c r="V4" s="134"/>
-      <c r="W4" s="134"/>
-      <c r="X4" s="134"/>
-      <c r="Y4" s="135"/>
-      <c r="Z4" s="133" t="s">
+      <c r="U4" s="153"/>
+      <c r="V4" s="153"/>
+      <c r="W4" s="153"/>
+      <c r="X4" s="153"/>
+      <c r="Y4" s="154"/>
+      <c r="Z4" s="152" t="s">
         <v>6</v>
       </c>
-      <c r="AA4" s="134"/>
-      <c r="AB4" s="134"/>
-      <c r="AC4" s="135"/>
-      <c r="AD4" s="133" t="s">
+      <c r="AA4" s="153"/>
+      <c r="AB4" s="153"/>
+      <c r="AC4" s="154"/>
+      <c r="AD4" s="152" t="s">
         <v>7</v>
       </c>
-      <c r="AE4" s="134"/>
-      <c r="AF4" s="134"/>
-      <c r="AG4" s="135"/>
-      <c r="AH4" s="133" t="s">
+      <c r="AE4" s="153"/>
+      <c r="AF4" s="153"/>
+      <c r="AG4" s="154"/>
+      <c r="AH4" s="152" t="s">
         <v>8</v>
       </c>
-      <c r="AI4" s="134"/>
-      <c r="AJ4" s="134"/>
-      <c r="AK4" s="135"/>
+      <c r="AI4" s="153"/>
+      <c r="AJ4" s="153"/>
+      <c r="AK4" s="154"/>
       <c r="AN4" s="3"/>
       <c r="AO4" s="3"/>
       <c r="AP4" s="3"/>
@@ -4436,16 +4443,16 @@
         <v>23</v>
       </c>
       <c r="S5" s="3"/>
-      <c r="T5" s="136" t="s">
+      <c r="T5" s="167" t="s">
         <v>64</v>
       </c>
-      <c r="U5" s="137"/>
-      <c r="V5" s="137"/>
-      <c r="W5" s="141">
+      <c r="U5" s="168"/>
+      <c r="V5" s="168"/>
+      <c r="W5" s="139">
         <v>7</v>
       </c>
-      <c r="X5" s="142"/>
-      <c r="Y5" s="143"/>
+      <c r="X5" s="140"/>
+      <c r="Y5" s="141"/>
       <c r="Z5" s="11"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
@@ -4454,10 +4461,10 @@
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
       <c r="AG5" s="12"/>
-      <c r="AH5" s="146"/>
-      <c r="AI5" s="147"/>
-      <c r="AJ5" s="147"/>
-      <c r="AK5" s="148"/>
+      <c r="AH5" s="144"/>
+      <c r="AI5" s="145"/>
+      <c r="AJ5" s="145"/>
+      <c r="AK5" s="146"/>
       <c r="AN5" s="3"/>
       <c r="AO5" s="3"/>
       <c r="AP5" s="3"/>
@@ -4689,12 +4696,12 @@
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
-      <c r="T6" s="138"/>
-      <c r="U6" s="137"/>
-      <c r="V6" s="137"/>
-      <c r="W6" s="142"/>
-      <c r="X6" s="142"/>
-      <c r="Y6" s="143"/>
+      <c r="T6" s="169"/>
+      <c r="U6" s="168"/>
+      <c r="V6" s="168"/>
+      <c r="W6" s="140"/>
+      <c r="X6" s="140"/>
+      <c r="Y6" s="141"/>
       <c r="Z6" s="11"/>
       <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
@@ -4703,10 +4710,10 @@
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
       <c r="AG6" s="12"/>
-      <c r="AH6" s="146"/>
-      <c r="AI6" s="147"/>
-      <c r="AJ6" s="147"/>
-      <c r="AK6" s="148"/>
+      <c r="AH6" s="144"/>
+      <c r="AI6" s="145"/>
+      <c r="AJ6" s="145"/>
+      <c r="AK6" s="146"/>
       <c r="AN6" s="3"/>
       <c r="AO6" s="3"/>
       <c r="AP6" s="3"/>
@@ -4938,12 +4945,12 @@
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
-      <c r="T7" s="139"/>
-      <c r="U7" s="140"/>
-      <c r="V7" s="140"/>
-      <c r="W7" s="144"/>
-      <c r="X7" s="144"/>
-      <c r="Y7" s="145"/>
+      <c r="T7" s="170"/>
+      <c r="U7" s="171"/>
+      <c r="V7" s="171"/>
+      <c r="W7" s="142"/>
+      <c r="X7" s="142"/>
+      <c r="Y7" s="143"/>
       <c r="Z7" s="21"/>
       <c r="AA7" s="22"/>
       <c r="AB7" s="22"/>
@@ -4952,10 +4959,10 @@
       <c r="AE7" s="22"/>
       <c r="AF7" s="22"/>
       <c r="AG7" s="23"/>
-      <c r="AH7" s="149"/>
-      <c r="AI7" s="150"/>
-      <c r="AJ7" s="150"/>
-      <c r="AK7" s="151"/>
+      <c r="AH7" s="147"/>
+      <c r="AI7" s="148"/>
+      <c r="AJ7" s="148"/>
+      <c r="AK7" s="149"/>
       <c r="AL7" s="86"/>
       <c r="AN7" s="3"/>
       <c r="AO7" s="3"/>
@@ -5838,8 +5845,8 @@
     </row>
     <row r="10" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A10" s="29"/>
-      <c r="B10" s="152"/>
-      <c r="C10" s="153"/>
+      <c r="B10" s="150"/>
+      <c r="C10" s="151"/>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="31" t="s">
@@ -6187,10 +6194,10 @@
     </row>
     <row r="11" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A11" s="34"/>
-      <c r="B11" s="130" t="s">
+      <c r="B11" s="164" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="131"/>
+      <c r="C11" s="165"/>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
       <c r="F11" s="102" t="s">
@@ -6457,7 +6464,7 @@
       <c r="E12" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="158" t="s">
+      <c r="F12" s="134" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="106"/>
@@ -6719,7 +6726,7 @@
         <v>99</v>
       </c>
       <c r="E13" s="92"/>
-      <c r="F13" s="119"/>
+      <c r="F13" s="135"/>
       <c r="G13" s="106"/>
       <c r="H13" s="106"/>
       <c r="I13" s="106"/>
@@ -6981,7 +6988,7 @@
       <c r="E14" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="119"/>
+      <c r="F14" s="135"/>
       <c r="G14" s="106"/>
       <c r="H14" s="106"/>
       <c r="I14" s="106"/>
@@ -7243,7 +7250,7 @@
       <c r="E15" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="119"/>
+      <c r="F15" s="135"/>
       <c r="G15" s="106"/>
       <c r="H15" s="106"/>
       <c r="I15" s="106"/>
@@ -7505,7 +7512,7 @@
       <c r="E16" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="119"/>
+      <c r="F16" s="135"/>
       <c r="G16" s="106"/>
       <c r="H16" s="106"/>
       <c r="I16" s="106"/>
@@ -7767,7 +7774,7 @@
       <c r="E17" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="119"/>
+      <c r="F17" s="135"/>
       <c r="G17" s="106"/>
       <c r="H17" s="106"/>
       <c r="I17" s="106"/>
@@ -8029,7 +8036,7 @@
       <c r="E18" s="92" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="119"/>
+      <c r="F18" s="135"/>
       <c r="G18" s="106"/>
       <c r="H18" s="106"/>
       <c r="I18" s="106"/>
@@ -8291,7 +8298,7 @@
       <c r="E19" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="F19" s="119"/>
+      <c r="F19" s="135"/>
       <c r="G19" s="106"/>
       <c r="H19" s="106"/>
       <c r="I19" s="106"/>
@@ -8553,7 +8560,7 @@
       <c r="E20" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="F20" s="119"/>
+      <c r="F20" s="135"/>
       <c r="G20" s="106"/>
       <c r="H20" s="106"/>
       <c r="I20" s="106"/>
@@ -8813,7 +8820,7 @@
         <v>100</v>
       </c>
       <c r="E21" s="92"/>
-      <c r="F21" s="119"/>
+      <c r="F21" s="135"/>
       <c r="G21" s="106"/>
       <c r="H21" s="106"/>
       <c r="I21" s="106"/>
@@ -9073,7 +9080,7 @@
         <v>38</v>
       </c>
       <c r="E22" s="92"/>
-      <c r="F22" s="119" t="s">
+      <c r="F22" s="135" t="s">
         <v>135</v>
       </c>
       <c r="G22" s="106"/>
@@ -9337,7 +9344,7 @@
       <c r="E23" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="F23" s="120"/>
+      <c r="F23" s="136"/>
       <c r="G23" s="104"/>
       <c r="H23" s="104"/>
       <c r="I23" s="104"/>
@@ -10105,10 +10112,10 @@
     </row>
     <row r="26" spans="1:254" s="2" customFormat="1" ht="28.25" customHeight="1">
       <c r="A26" s="38"/>
-      <c r="B26" s="154" t="s">
+      <c r="B26" s="137" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="155"/>
+      <c r="C26" s="138"/>
       <c r="D26" s="35"/>
       <c r="E26" s="35"/>
       <c r="F26" s="39"/>
@@ -10363,17 +10370,17 @@
       <c r="A27" s="37">
         <v>1</v>
       </c>
-      <c r="B27" s="156" t="s">
+      <c r="B27" s="130" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="157"/>
+      <c r="C27" s="131"/>
       <c r="D27" s="92" t="s">
         <v>99</v>
       </c>
       <c r="E27" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="158" t="s">
+      <c r="F27" s="134" t="s">
         <v>15</v>
       </c>
       <c r="G27" s="106"/>
@@ -10627,15 +10634,15 @@
       <c r="A28" s="37">
         <v>2</v>
       </c>
-      <c r="B28" s="156" t="s">
+      <c r="B28" s="130" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="157"/>
+      <c r="C28" s="131"/>
       <c r="D28" s="35" t="s">
         <v>77</v>
       </c>
       <c r="E28" s="35"/>
-      <c r="F28" s="119"/>
+      <c r="F28" s="135"/>
       <c r="G28" s="106"/>
       <c r="H28" s="106"/>
       <c r="I28" s="106"/>
@@ -10895,7 +10902,7 @@
         <v>77</v>
       </c>
       <c r="E29" s="35"/>
-      <c r="F29" s="119"/>
+      <c r="F29" s="135"/>
       <c r="G29" s="106"/>
       <c r="H29" s="106"/>
       <c r="I29" s="106"/>
@@ -11157,7 +11164,7 @@
       <c r="E30" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="F30" s="119"/>
+      <c r="F30" s="135"/>
       <c r="G30" s="104"/>
       <c r="H30" s="104"/>
       <c r="I30" s="104"/>
@@ -11409,15 +11416,15 @@
       <c r="A31" s="37">
         <v>5</v>
       </c>
-      <c r="B31" s="156" t="s">
+      <c r="B31" s="130" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="157"/>
+      <c r="C31" s="131"/>
       <c r="D31" s="92" t="s">
         <v>80</v>
       </c>
       <c r="E31" s="35"/>
-      <c r="F31" s="119"/>
+      <c r="F31" s="135"/>
       <c r="G31" s="104"/>
       <c r="H31" s="104"/>
       <c r="I31" s="104"/>
@@ -11677,7 +11684,7 @@
         <v>118</v>
       </c>
       <c r="E32" s="35"/>
-      <c r="F32" s="119"/>
+      <c r="F32" s="135"/>
       <c r="G32" s="104"/>
       <c r="H32" s="104"/>
       <c r="I32" s="104"/>
@@ -11937,7 +11944,7 @@
         <v>118</v>
       </c>
       <c r="E33" s="35"/>
-      <c r="F33" s="119"/>
+      <c r="F33" s="135"/>
       <c r="G33" s="104"/>
       <c r="H33" s="104"/>
       <c r="I33" s="104"/>
@@ -12189,15 +12196,15 @@
       <c r="A34" s="37">
         <v>8</v>
       </c>
-      <c r="B34" s="156" t="s">
+      <c r="B34" s="130" t="s">
         <v>59</v>
       </c>
-      <c r="C34" s="157"/>
+      <c r="C34" s="131"/>
       <c r="D34" s="92" t="s">
         <v>99</v>
       </c>
       <c r="E34" s="40"/>
-      <c r="F34" s="119"/>
+      <c r="F34" s="135"/>
       <c r="G34" s="106"/>
       <c r="H34" s="106"/>
       <c r="I34" s="106"/>
@@ -12449,15 +12456,15 @@
       <c r="A35" s="37">
         <v>9</v>
       </c>
-      <c r="B35" s="156" t="s">
+      <c r="B35" s="130" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="157"/>
+      <c r="C35" s="131"/>
       <c r="D35" s="92" t="s">
         <v>49</v>
       </c>
       <c r="E35" s="40"/>
-      <c r="F35" s="120"/>
+      <c r="F35" s="136"/>
       <c r="G35" s="106"/>
       <c r="H35" s="106"/>
       <c r="I35" s="106"/>
@@ -12707,10 +12714,10 @@
     </row>
     <row r="36" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A36" s="37"/>
-      <c r="B36" s="154" t="s">
+      <c r="B36" s="137" t="s">
         <v>127</v>
       </c>
-      <c r="C36" s="155"/>
+      <c r="C36" s="138"/>
       <c r="D36" s="92"/>
       <c r="E36" s="40"/>
       <c r="F36" s="93"/>
@@ -12963,10 +12970,10 @@
     </row>
     <row r="37" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A37" s="37"/>
-      <c r="B37" s="156" t="s">
+      <c r="B37" s="130" t="s">
         <v>128</v>
       </c>
-      <c r="C37" s="157"/>
+      <c r="C37" s="131"/>
       <c r="D37" s="92"/>
       <c r="E37" s="40"/>
       <c r="F37" s="93"/>
@@ -13219,10 +13226,10 @@
     </row>
     <row r="38" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A38" s="37"/>
-      <c r="B38" s="170" t="s">
+      <c r="B38" s="132" t="s">
         <v>129</v>
       </c>
-      <c r="C38" s="171"/>
+      <c r="C38" s="133"/>
       <c r="D38" s="92"/>
       <c r="E38" s="40"/>
       <c r="F38" s="93"/>
@@ -13475,8 +13482,8 @@
     </row>
     <row r="39" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A39" s="37"/>
-      <c r="B39" s="170"/>
-      <c r="C39" s="171"/>
+      <c r="B39" s="132"/>
+      <c r="C39" s="133"/>
       <c r="D39" s="92"/>
       <c r="E39" s="40"/>
       <c r="F39" s="93"/>
@@ -13729,10 +13736,10 @@
     </row>
     <row r="40" spans="1:254" s="2" customFormat="1" ht="42" customHeight="1" thickBot="1">
       <c r="A40" s="41"/>
-      <c r="B40" s="168" t="s">
+      <c r="B40" s="128" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="169"/>
+      <c r="C40" s="129"/>
       <c r="D40" s="42" t="s">
         <v>16</v>
       </c>
@@ -13996,37 +14003,37 @@
         <v>96</v>
       </c>
       <c r="F41" s="75"/>
-      <c r="G41" s="162"/>
-      <c r="H41" s="162"/>
-      <c r="I41" s="162"/>
-      <c r="J41" s="162"/>
-      <c r="K41" s="162"/>
-      <c r="L41" s="162"/>
-      <c r="M41" s="162"/>
-      <c r="N41" s="162"/>
-      <c r="O41" s="162"/>
-      <c r="P41" s="162"/>
-      <c r="Q41" s="162"/>
-      <c r="R41" s="162"/>
-      <c r="S41" s="162"/>
-      <c r="T41" s="162"/>
-      <c r="U41" s="162"/>
-      <c r="V41" s="162"/>
-      <c r="W41" s="162"/>
-      <c r="X41" s="162"/>
-      <c r="Y41" s="162"/>
-      <c r="Z41" s="162"/>
-      <c r="AA41" s="163"/>
-      <c r="AB41" s="163"/>
-      <c r="AC41" s="163"/>
-      <c r="AD41" s="163"/>
-      <c r="AE41" s="163"/>
-      <c r="AF41" s="163"/>
-      <c r="AG41" s="163"/>
-      <c r="AH41" s="163"/>
-      <c r="AI41" s="163"/>
-      <c r="AJ41" s="163"/>
-      <c r="AK41" s="164"/>
+      <c r="G41" s="122"/>
+      <c r="H41" s="122"/>
+      <c r="I41" s="122"/>
+      <c r="J41" s="122"/>
+      <c r="K41" s="122"/>
+      <c r="L41" s="122"/>
+      <c r="M41" s="122"/>
+      <c r="N41" s="122"/>
+      <c r="O41" s="122"/>
+      <c r="P41" s="122"/>
+      <c r="Q41" s="122"/>
+      <c r="R41" s="122"/>
+      <c r="S41" s="122"/>
+      <c r="T41" s="122"/>
+      <c r="U41" s="122"/>
+      <c r="V41" s="122"/>
+      <c r="W41" s="122"/>
+      <c r="X41" s="122"/>
+      <c r="Y41" s="122"/>
+      <c r="Z41" s="122"/>
+      <c r="AA41" s="123"/>
+      <c r="AB41" s="123"/>
+      <c r="AC41" s="123"/>
+      <c r="AD41" s="123"/>
+      <c r="AE41" s="123"/>
+      <c r="AF41" s="123"/>
+      <c r="AG41" s="123"/>
+      <c r="AH41" s="123"/>
+      <c r="AI41" s="123"/>
+      <c r="AJ41" s="123"/>
+      <c r="AK41" s="124"/>
     </row>
     <row r="42" spans="1:254" ht="23" customHeight="1">
       <c r="A42" s="45"/>
@@ -14037,37 +14044,37 @@
         <v>97</v>
       </c>
       <c r="F42" s="77"/>
-      <c r="G42" s="165"/>
-      <c r="H42" s="165"/>
-      <c r="I42" s="165"/>
-      <c r="J42" s="165"/>
-      <c r="K42" s="165"/>
-      <c r="L42" s="165"/>
-      <c r="M42" s="165"/>
-      <c r="N42" s="165"/>
-      <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
-      <c r="Q42" s="167"/>
-      <c r="R42" s="167"/>
-      <c r="S42" s="167"/>
-      <c r="T42" s="167"/>
-      <c r="U42" s="167"/>
-      <c r="V42" s="167"/>
-      <c r="W42" s="167"/>
-      <c r="X42" s="167"/>
-      <c r="Y42" s="167"/>
-      <c r="Z42" s="167"/>
-      <c r="AA42" s="165"/>
-      <c r="AB42" s="165"/>
-      <c r="AC42" s="165"/>
-      <c r="AD42" s="165"/>
-      <c r="AE42" s="165"/>
-      <c r="AF42" s="165"/>
-      <c r="AG42" s="165"/>
-      <c r="AH42" s="165"/>
-      <c r="AI42" s="165"/>
-      <c r="AJ42" s="165"/>
-      <c r="AK42" s="166"/>
+      <c r="G42" s="125"/>
+      <c r="H42" s="125"/>
+      <c r="I42" s="125"/>
+      <c r="J42" s="125"/>
+      <c r="K42" s="125"/>
+      <c r="L42" s="125"/>
+      <c r="M42" s="125"/>
+      <c r="N42" s="125"/>
+      <c r="O42" s="125"/>
+      <c r="P42" s="125"/>
+      <c r="Q42" s="127"/>
+      <c r="R42" s="127"/>
+      <c r="S42" s="127"/>
+      <c r="T42" s="127"/>
+      <c r="U42" s="127"/>
+      <c r="V42" s="127"/>
+      <c r="W42" s="127"/>
+      <c r="X42" s="127"/>
+      <c r="Y42" s="127"/>
+      <c r="Z42" s="127"/>
+      <c r="AA42" s="125"/>
+      <c r="AB42" s="125"/>
+      <c r="AC42" s="125"/>
+      <c r="AD42" s="125"/>
+      <c r="AE42" s="125"/>
+      <c r="AF42" s="125"/>
+      <c r="AG42" s="125"/>
+      <c r="AH42" s="125"/>
+      <c r="AI42" s="125"/>
+      <c r="AJ42" s="125"/>
+      <c r="AK42" s="126"/>
     </row>
     <row r="43" spans="1:254" ht="23" customHeight="1" thickBot="1">
       <c r="A43" s="49"/>
@@ -14078,37 +14085,37 @@
         <v>98</v>
       </c>
       <c r="F43" s="82"/>
-      <c r="G43" s="159"/>
-      <c r="H43" s="159"/>
-      <c r="I43" s="159"/>
-      <c r="J43" s="159"/>
-      <c r="K43" s="159"/>
-      <c r="L43" s="159"/>
-      <c r="M43" s="159"/>
-      <c r="N43" s="159"/>
-      <c r="O43" s="159"/>
-      <c r="P43" s="159"/>
-      <c r="Q43" s="161"/>
-      <c r="R43" s="161"/>
-      <c r="S43" s="161"/>
-      <c r="T43" s="161"/>
-      <c r="U43" s="161"/>
-      <c r="V43" s="161"/>
-      <c r="W43" s="161"/>
-      <c r="X43" s="161"/>
-      <c r="Y43" s="161"/>
-      <c r="Z43" s="161"/>
-      <c r="AA43" s="159"/>
-      <c r="AB43" s="159"/>
-      <c r="AC43" s="159"/>
-      <c r="AD43" s="159"/>
-      <c r="AE43" s="159"/>
-      <c r="AF43" s="159"/>
-      <c r="AG43" s="159"/>
-      <c r="AH43" s="159"/>
-      <c r="AI43" s="159"/>
-      <c r="AJ43" s="159"/>
-      <c r="AK43" s="160"/>
+      <c r="G43" s="119"/>
+      <c r="H43" s="119"/>
+      <c r="I43" s="119"/>
+      <c r="J43" s="119"/>
+      <c r="K43" s="119"/>
+      <c r="L43" s="119"/>
+      <c r="M43" s="119"/>
+      <c r="N43" s="119"/>
+      <c r="O43" s="119"/>
+      <c r="P43" s="119"/>
+      <c r="Q43" s="121"/>
+      <c r="R43" s="121"/>
+      <c r="S43" s="121"/>
+      <c r="T43" s="121"/>
+      <c r="U43" s="121"/>
+      <c r="V43" s="121"/>
+      <c r="W43" s="121"/>
+      <c r="X43" s="121"/>
+      <c r="Y43" s="121"/>
+      <c r="Z43" s="121"/>
+      <c r="AA43" s="119"/>
+      <c r="AB43" s="119"/>
+      <c r="AC43" s="119"/>
+      <c r="AD43" s="119"/>
+      <c r="AE43" s="119"/>
+      <c r="AF43" s="119"/>
+      <c r="AG43" s="119"/>
+      <c r="AH43" s="119"/>
+      <c r="AI43" s="119"/>
+      <c r="AJ43" s="119"/>
+      <c r="AK43" s="120"/>
     </row>
     <row r="44" spans="1:254">
       <c r="A44" s="52"/>
@@ -14124,6 +14131,50 @@
     </row>
   </sheetData>
   <mergeCells count="60">
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:AK1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="T3:AK3"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="T4:Y4"/>
+    <mergeCell ref="AH4:AK4"/>
+    <mergeCell ref="T5:V7"/>
+    <mergeCell ref="W5:Y7"/>
+    <mergeCell ref="AH5:AK7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="Z4:AC4"/>
+    <mergeCell ref="AD4:AG4"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="F12:F21"/>
+    <mergeCell ref="F27:F35"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B24:C24"/>
@@ -14140,63 +14191,16 @@
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="G41:P41"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="F12:F21"/>
-    <mergeCell ref="F27:F35"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="W5:Y7"/>
-    <mergeCell ref="AH5:AK7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="Z4:AC4"/>
-    <mergeCell ref="AD4:AG4"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="F1:AK1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="T3:AK3"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="T4:Y4"/>
-    <mergeCell ref="AH4:AK4"/>
-    <mergeCell ref="T5:V7"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="G9:AK10">
-    <cfRule type="expression" dxfId="5" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>TEXT(G9,"aaa")="土"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="3">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G9:AK40">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>TEXT(G9,"aaa")="日"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G11:AK40">
-    <cfRule type="expression" dxfId="4" priority="1">
-      <formula>G$11="－"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.23622047244094491" right="3.937007874015748E-2" top="0.55118110236220474" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -14220,40 +14224,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:254" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="155" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="121"/>
+      <c r="B1" s="155"/>
       <c r="C1" s="85"/>
-      <c r="F1" s="122" t="s">
+      <c r="F1" s="156" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
-      <c r="AC1" s="122"/>
-      <c r="AD1" s="122"/>
-      <c r="AE1" s="122"/>
-      <c r="AF1" s="122"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+      <c r="L1" s="156"/>
+      <c r="M1" s="156"/>
+      <c r="N1" s="156"/>
+      <c r="O1" s="156"/>
+      <c r="P1" s="156"/>
+      <c r="Q1" s="156"/>
+      <c r="R1" s="156"/>
+      <c r="S1" s="156"/>
+      <c r="T1" s="156"/>
+      <c r="U1" s="156"/>
+      <c r="V1" s="156"/>
+      <c r="W1" s="156"/>
+      <c r="X1" s="156"/>
+      <c r="Y1" s="156"/>
+      <c r="Z1" s="156"/>
+      <c r="AA1" s="156"/>
+      <c r="AB1" s="156"/>
+      <c r="AC1" s="156"/>
+      <c r="AD1" s="156"/>
+      <c r="AE1" s="156"/>
+      <c r="AF1" s="156"/>
       <c r="AI1" s="3"/>
       <c r="AJ1" s="3"/>
       <c r="AK1" s="3"/>
@@ -14719,47 +14723,47 @@
       <c r="IO2" s="3"/>
     </row>
     <row r="3" spans="1:254" s="2" customFormat="1" ht="20" customHeight="1" thickBot="1">
-      <c r="A3" s="123" t="s">
+      <c r="A3" s="157" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="125"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
       <c r="E3" s="94"/>
       <c r="G3" s="51"/>
       <c r="H3" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="126" t="s">
+      <c r="K3" s="160" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="126"/>
-      <c r="M3" s="126" t="s">
+      <c r="L3" s="160"/>
+      <c r="M3" s="160" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="126"/>
-      <c r="O3" s="126"/>
-      <c r="P3" s="126" t="s">
+      <c r="N3" s="160"/>
+      <c r="O3" s="160"/>
+      <c r="P3" s="160" t="s">
         <v>2</v>
       </c>
-      <c r="Q3" s="126"/>
-      <c r="R3" s="126"/>
+      <c r="Q3" s="160"/>
+      <c r="R3" s="160"/>
       <c r="S3" s="3"/>
-      <c r="T3" s="127" t="s">
+      <c r="T3" s="161" t="s">
         <v>3</v>
       </c>
-      <c r="U3" s="128"/>
-      <c r="V3" s="128"/>
-      <c r="W3" s="128"/>
-      <c r="X3" s="128"/>
-      <c r="Y3" s="128"/>
-      <c r="Z3" s="128"/>
-      <c r="AA3" s="128"/>
-      <c r="AB3" s="128"/>
-      <c r="AC3" s="128"/>
-      <c r="AD3" s="128"/>
-      <c r="AE3" s="128"/>
-      <c r="AF3" s="129"/>
+      <c r="U3" s="162"/>
+      <c r="V3" s="162"/>
+      <c r="W3" s="162"/>
+      <c r="X3" s="162"/>
+      <c r="Y3" s="162"/>
+      <c r="Z3" s="162"/>
+      <c r="AA3" s="162"/>
+      <c r="AB3" s="162"/>
+      <c r="AC3" s="162"/>
+      <c r="AD3" s="162"/>
+      <c r="AE3" s="162"/>
+      <c r="AF3" s="163"/>
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
       <c r="AK3" s="3"/>
@@ -14988,42 +14992,42 @@
       <c r="H4" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="126" t="s">
+      <c r="K4" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="126"/>
-      <c r="M4" s="132">
+      <c r="L4" s="160"/>
+      <c r="M4" s="166">
         <v>46113</v>
       </c>
-      <c r="N4" s="132"/>
-      <c r="O4" s="132"/>
-      <c r="P4" s="126" t="s">
+      <c r="N4" s="166"/>
+      <c r="O4" s="166"/>
+      <c r="P4" s="160" t="s">
         <v>50</v>
       </c>
-      <c r="Q4" s="126"/>
-      <c r="R4" s="126"/>
+      <c r="Q4" s="160"/>
+      <c r="R4" s="160"/>
       <c r="S4" s="3"/>
-      <c r="T4" s="133" t="s">
+      <c r="T4" s="152" t="s">
         <v>5</v>
       </c>
-      <c r="U4" s="134"/>
-      <c r="V4" s="134"/>
-      <c r="W4" s="135"/>
-      <c r="X4" s="133" t="s">
+      <c r="U4" s="153"/>
+      <c r="V4" s="153"/>
+      <c r="W4" s="154"/>
+      <c r="X4" s="152" t="s">
         <v>6</v>
       </c>
-      <c r="Y4" s="134"/>
-      <c r="Z4" s="135"/>
-      <c r="AA4" s="133" t="s">
+      <c r="Y4" s="153"/>
+      <c r="Z4" s="154"/>
+      <c r="AA4" s="152" t="s">
         <v>7</v>
       </c>
-      <c r="AB4" s="134"/>
-      <c r="AC4" s="135"/>
-      <c r="AD4" s="133" t="s">
+      <c r="AB4" s="153"/>
+      <c r="AC4" s="154"/>
+      <c r="AD4" s="152" t="s">
         <v>8</v>
       </c>
-      <c r="AE4" s="134"/>
-      <c r="AF4" s="135"/>
+      <c r="AE4" s="153"/>
+      <c r="AF4" s="154"/>
       <c r="AI4" s="3"/>
       <c r="AJ4" s="3"/>
       <c r="AK4" s="3"/>
@@ -15251,21 +15255,21 @@
         <v>23</v>
       </c>
       <c r="S5" s="3"/>
-      <c r="T5" s="183" t="s">
+      <c r="T5" s="172" t="s">
         <v>64</v>
       </c>
-      <c r="U5" s="184"/>
-      <c r="V5" s="184"/>
-      <c r="W5" s="185"/>
+      <c r="U5" s="173"/>
+      <c r="V5" s="173"/>
+      <c r="W5" s="174"/>
       <c r="X5" s="11"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="12"/>
       <c r="AA5" s="11"/>
       <c r="AB5" s="3"/>
       <c r="AC5" s="12"/>
-      <c r="AD5" s="146"/>
-      <c r="AE5" s="147"/>
-      <c r="AF5" s="148"/>
+      <c r="AD5" s="144"/>
+      <c r="AE5" s="145"/>
+      <c r="AF5" s="146"/>
       <c r="AI5" s="3"/>
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3"/>
@@ -15497,19 +15501,19 @@
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
-      <c r="T6" s="183"/>
-      <c r="U6" s="184"/>
-      <c r="V6" s="184"/>
-      <c r="W6" s="185"/>
+      <c r="T6" s="172"/>
+      <c r="U6" s="173"/>
+      <c r="V6" s="173"/>
+      <c r="W6" s="174"/>
       <c r="X6" s="11"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="12"/>
       <c r="AA6" s="11"/>
       <c r="AB6" s="3"/>
       <c r="AC6" s="12"/>
-      <c r="AD6" s="146"/>
-      <c r="AE6" s="147"/>
-      <c r="AF6" s="148"/>
+      <c r="AD6" s="144"/>
+      <c r="AE6" s="145"/>
+      <c r="AF6" s="146"/>
       <c r="AI6" s="3"/>
       <c r="AJ6" s="3"/>
       <c r="AK6" s="3"/>
@@ -15741,19 +15745,19 @@
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
-      <c r="T7" s="186"/>
-      <c r="U7" s="187"/>
-      <c r="V7" s="187"/>
-      <c r="W7" s="188"/>
+      <c r="T7" s="175"/>
+      <c r="U7" s="176"/>
+      <c r="V7" s="176"/>
+      <c r="W7" s="177"/>
       <c r="X7" s="21"/>
       <c r="Y7" s="22"/>
       <c r="Z7" s="23"/>
       <c r="AA7" s="21"/>
       <c r="AB7" s="22"/>
       <c r="AC7" s="23"/>
-      <c r="AD7" s="149"/>
-      <c r="AE7" s="150"/>
-      <c r="AF7" s="151"/>
+      <c r="AD7" s="147"/>
+      <c r="AE7" s="148"/>
+      <c r="AF7" s="149"/>
       <c r="AG7" s="86"/>
       <c r="AI7" s="3"/>
       <c r="AJ7" s="3"/>
@@ -16270,22 +16274,22 @@
       <c r="R9" s="97" t="s">
         <v>76</v>
       </c>
-      <c r="S9" s="176" t="s">
+      <c r="S9" s="191" t="s">
         <v>78</v>
       </c>
-      <c r="T9" s="177"/>
-      <c r="U9" s="177"/>
-      <c r="V9" s="177"/>
-      <c r="W9" s="177"/>
-      <c r="X9" s="177"/>
-      <c r="Y9" s="177"/>
-      <c r="Z9" s="177"/>
-      <c r="AA9" s="177"/>
-      <c r="AB9" s="177"/>
-      <c r="AC9" s="177"/>
-      <c r="AD9" s="177"/>
-      <c r="AE9" s="177"/>
-      <c r="AF9" s="178"/>
+      <c r="T9" s="192"/>
+      <c r="U9" s="192"/>
+      <c r="V9" s="192"/>
+      <c r="W9" s="192"/>
+      <c r="X9" s="192"/>
+      <c r="Y9" s="192"/>
+      <c r="Z9" s="192"/>
+      <c r="AA9" s="192"/>
+      <c r="AB9" s="192"/>
+      <c r="AC9" s="192"/>
+      <c r="AD9" s="192"/>
+      <c r="AE9" s="192"/>
+      <c r="AF9" s="193"/>
       <c r="AI9" s="3"/>
       <c r="AJ9" s="3"/>
       <c r="AK9" s="3"/>
@@ -16504,8 +16508,8 @@
     </row>
     <row r="10" spans="1:254" s="2" customFormat="1" ht="23" hidden="1" customHeight="1">
       <c r="A10" s="29"/>
-      <c r="B10" s="152"/>
-      <c r="C10" s="153"/>
+      <c r="B10" s="150"/>
+      <c r="C10" s="151"/>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="31"/>
@@ -16831,10 +16835,10 @@
     </row>
     <row r="11" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A11" s="37"/>
-      <c r="B11" s="154" t="s">
+      <c r="B11" s="137" t="s">
         <v>105</v>
       </c>
-      <c r="C11" s="155"/>
+      <c r="C11" s="138"/>
       <c r="D11" s="92"/>
       <c r="E11" s="40"/>
       <c r="F11" s="93"/>
@@ -16850,20 +16854,20 @@
       <c r="P11" s="69"/>
       <c r="Q11" s="69"/>
       <c r="R11" s="69"/>
-      <c r="S11" s="191"/>
-      <c r="T11" s="192"/>
-      <c r="U11" s="192"/>
-      <c r="V11" s="192"/>
-      <c r="W11" s="192"/>
-      <c r="X11" s="192"/>
-      <c r="Y11" s="192"/>
-      <c r="Z11" s="192"/>
-      <c r="AA11" s="192"/>
-      <c r="AB11" s="192"/>
-      <c r="AC11" s="192"/>
-      <c r="AD11" s="192"/>
-      <c r="AE11" s="192"/>
-      <c r="AF11" s="193"/>
+      <c r="S11" s="180"/>
+      <c r="T11" s="181"/>
+      <c r="U11" s="181"/>
+      <c r="V11" s="181"/>
+      <c r="W11" s="181"/>
+      <c r="X11" s="181"/>
+      <c r="Y11" s="181"/>
+      <c r="Z11" s="181"/>
+      <c r="AA11" s="181"/>
+      <c r="AB11" s="181"/>
+      <c r="AC11" s="181"/>
+      <c r="AD11" s="181"/>
+      <c r="AE11" s="181"/>
+      <c r="AF11" s="182"/>
       <c r="AG11" s="69"/>
       <c r="AH11" s="69"/>
       <c r="AI11" s="69"/>
@@ -17089,10 +17093,10 @@
       <c r="A12" s="37">
         <v>1</v>
       </c>
-      <c r="B12" s="170" t="s">
+      <c r="B12" s="132" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="171"/>
+      <c r="C12" s="133"/>
       <c r="D12" s="92" t="s">
         <v>108</v>
       </c>
@@ -17110,20 +17114,20 @@
       <c r="P12" s="69"/>
       <c r="Q12" s="69"/>
       <c r="R12" s="69"/>
-      <c r="S12" s="172"/>
-      <c r="T12" s="173"/>
-      <c r="U12" s="173"/>
-      <c r="V12" s="173"/>
-      <c r="W12" s="173"/>
-      <c r="X12" s="173"/>
-      <c r="Y12" s="173"/>
-      <c r="Z12" s="173"/>
-      <c r="AA12" s="173"/>
-      <c r="AB12" s="173"/>
-      <c r="AC12" s="173"/>
-      <c r="AD12" s="173"/>
-      <c r="AE12" s="173"/>
-      <c r="AF12" s="174"/>
+      <c r="S12" s="183"/>
+      <c r="T12" s="184"/>
+      <c r="U12" s="184"/>
+      <c r="V12" s="184"/>
+      <c r="W12" s="184"/>
+      <c r="X12" s="184"/>
+      <c r="Y12" s="184"/>
+      <c r="Z12" s="184"/>
+      <c r="AA12" s="184"/>
+      <c r="AB12" s="184"/>
+      <c r="AC12" s="184"/>
+      <c r="AD12" s="184"/>
+      <c r="AE12" s="184"/>
+      <c r="AF12" s="185"/>
       <c r="AG12" s="69"/>
       <c r="AH12" s="69"/>
       <c r="AI12" s="69"/>
@@ -17349,10 +17353,10 @@
       <c r="A13" s="37">
         <v>2</v>
       </c>
-      <c r="B13" s="170" t="s">
+      <c r="B13" s="132" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="171"/>
+      <c r="C13" s="133"/>
       <c r="D13" s="92" t="s">
         <v>107</v>
       </c>
@@ -17370,20 +17374,20 @@
       <c r="P13" s="69"/>
       <c r="Q13" s="69"/>
       <c r="R13" s="69"/>
-      <c r="S13" s="172"/>
-      <c r="T13" s="173"/>
-      <c r="U13" s="173"/>
-      <c r="V13" s="173"/>
-      <c r="W13" s="173"/>
-      <c r="X13" s="173"/>
-      <c r="Y13" s="173"/>
-      <c r="Z13" s="173"/>
-      <c r="AA13" s="173"/>
-      <c r="AB13" s="173"/>
-      <c r="AC13" s="173"/>
-      <c r="AD13" s="173"/>
-      <c r="AE13" s="173"/>
-      <c r="AF13" s="174"/>
+      <c r="S13" s="183"/>
+      <c r="T13" s="184"/>
+      <c r="U13" s="184"/>
+      <c r="V13" s="184"/>
+      <c r="W13" s="184"/>
+      <c r="X13" s="184"/>
+      <c r="Y13" s="184"/>
+      <c r="Z13" s="184"/>
+      <c r="AA13" s="184"/>
+      <c r="AB13" s="184"/>
+      <c r="AC13" s="184"/>
+      <c r="AD13" s="184"/>
+      <c r="AE13" s="184"/>
+      <c r="AF13" s="185"/>
       <c r="AG13" s="69"/>
       <c r="AH13" s="69"/>
       <c r="AI13" s="69"/>
@@ -17609,10 +17613,10 @@
       <c r="A14" s="37">
         <v>3</v>
       </c>
-      <c r="B14" s="170" t="s">
+      <c r="B14" s="132" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="171"/>
+      <c r="C14" s="133"/>
       <c r="D14" s="92" t="s">
         <v>107</v>
       </c>
@@ -17630,20 +17634,20 @@
       <c r="P14" s="69"/>
       <c r="Q14" s="69"/>
       <c r="R14" s="69"/>
-      <c r="S14" s="172"/>
-      <c r="T14" s="173"/>
-      <c r="U14" s="173"/>
-      <c r="V14" s="173"/>
-      <c r="W14" s="173"/>
-      <c r="X14" s="173"/>
-      <c r="Y14" s="173"/>
-      <c r="Z14" s="173"/>
-      <c r="AA14" s="173"/>
-      <c r="AB14" s="173"/>
-      <c r="AC14" s="173"/>
-      <c r="AD14" s="173"/>
-      <c r="AE14" s="173"/>
-      <c r="AF14" s="174"/>
+      <c r="S14" s="183"/>
+      <c r="T14" s="184"/>
+      <c r="U14" s="184"/>
+      <c r="V14" s="184"/>
+      <c r="W14" s="184"/>
+      <c r="X14" s="184"/>
+      <c r="Y14" s="184"/>
+      <c r="Z14" s="184"/>
+      <c r="AA14" s="184"/>
+      <c r="AB14" s="184"/>
+      <c r="AC14" s="184"/>
+      <c r="AD14" s="184"/>
+      <c r="AE14" s="184"/>
+      <c r="AF14" s="185"/>
       <c r="AG14" s="69"/>
       <c r="AH14" s="69"/>
       <c r="AI14" s="69"/>
@@ -17869,10 +17873,10 @@
       <c r="A15" s="37">
         <v>4</v>
       </c>
-      <c r="B15" s="170" t="s">
+      <c r="B15" s="132" t="s">
         <v>82</v>
       </c>
-      <c r="C15" s="171"/>
+      <c r="C15" s="133"/>
       <c r="D15" s="92" t="s">
         <v>108</v>
       </c>
@@ -17890,20 +17894,20 @@
       <c r="P15" s="69"/>
       <c r="Q15" s="69"/>
       <c r="R15" s="69"/>
-      <c r="S15" s="172"/>
-      <c r="T15" s="173"/>
-      <c r="U15" s="173"/>
-      <c r="V15" s="173"/>
-      <c r="W15" s="173"/>
-      <c r="X15" s="173"/>
-      <c r="Y15" s="173"/>
-      <c r="Z15" s="173"/>
-      <c r="AA15" s="173"/>
-      <c r="AB15" s="173"/>
-      <c r="AC15" s="173"/>
-      <c r="AD15" s="173"/>
-      <c r="AE15" s="173"/>
-      <c r="AF15" s="174"/>
+      <c r="S15" s="183"/>
+      <c r="T15" s="184"/>
+      <c r="U15" s="184"/>
+      <c r="V15" s="184"/>
+      <c r="W15" s="184"/>
+      <c r="X15" s="184"/>
+      <c r="Y15" s="184"/>
+      <c r="Z15" s="184"/>
+      <c r="AA15" s="184"/>
+      <c r="AB15" s="184"/>
+      <c r="AC15" s="184"/>
+      <c r="AD15" s="184"/>
+      <c r="AE15" s="184"/>
+      <c r="AF15" s="185"/>
       <c r="AG15" s="69"/>
       <c r="AH15" s="69"/>
       <c r="AI15" s="69"/>
@@ -18129,10 +18133,10 @@
       <c r="A16" s="37">
         <v>5</v>
       </c>
-      <c r="B16" s="170" t="s">
+      <c r="B16" s="132" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="171"/>
+      <c r="C16" s="133"/>
       <c r="D16" s="92" t="s">
         <v>108</v>
       </c>
@@ -18150,20 +18154,20 @@
       <c r="P16" s="69"/>
       <c r="Q16" s="69"/>
       <c r="R16" s="69"/>
-      <c r="S16" s="172"/>
-      <c r="T16" s="173"/>
-      <c r="U16" s="173"/>
-      <c r="V16" s="173"/>
-      <c r="W16" s="173"/>
-      <c r="X16" s="173"/>
-      <c r="Y16" s="173"/>
-      <c r="Z16" s="173"/>
-      <c r="AA16" s="173"/>
-      <c r="AB16" s="173"/>
-      <c r="AC16" s="173"/>
-      <c r="AD16" s="173"/>
-      <c r="AE16" s="173"/>
-      <c r="AF16" s="174"/>
+      <c r="S16" s="183"/>
+      <c r="T16" s="184"/>
+      <c r="U16" s="184"/>
+      <c r="V16" s="184"/>
+      <c r="W16" s="184"/>
+      <c r="X16" s="184"/>
+      <c r="Y16" s="184"/>
+      <c r="Z16" s="184"/>
+      <c r="AA16" s="184"/>
+      <c r="AB16" s="184"/>
+      <c r="AC16" s="184"/>
+      <c r="AD16" s="184"/>
+      <c r="AE16" s="184"/>
+      <c r="AF16" s="185"/>
       <c r="AG16" s="69"/>
       <c r="AH16" s="69"/>
       <c r="AI16" s="69"/>
@@ -18389,10 +18393,10 @@
       <c r="A17" s="37">
         <v>6</v>
       </c>
-      <c r="B17" s="170" t="s">
+      <c r="B17" s="132" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="171"/>
+      <c r="C17" s="133"/>
       <c r="D17" s="92" t="s">
         <v>108</v>
       </c>
@@ -18410,20 +18414,20 @@
       <c r="P17" s="69"/>
       <c r="Q17" s="69"/>
       <c r="R17" s="69"/>
-      <c r="S17" s="172"/>
-      <c r="T17" s="173"/>
-      <c r="U17" s="173"/>
-      <c r="V17" s="173"/>
-      <c r="W17" s="173"/>
-      <c r="X17" s="173"/>
-      <c r="Y17" s="173"/>
-      <c r="Z17" s="173"/>
-      <c r="AA17" s="173"/>
-      <c r="AB17" s="173"/>
-      <c r="AC17" s="173"/>
-      <c r="AD17" s="173"/>
-      <c r="AE17" s="173"/>
-      <c r="AF17" s="174"/>
+      <c r="S17" s="183"/>
+      <c r="T17" s="184"/>
+      <c r="U17" s="184"/>
+      <c r="V17" s="184"/>
+      <c r="W17" s="184"/>
+      <c r="X17" s="184"/>
+      <c r="Y17" s="184"/>
+      <c r="Z17" s="184"/>
+      <c r="AA17" s="184"/>
+      <c r="AB17" s="184"/>
+      <c r="AC17" s="184"/>
+      <c r="AD17" s="184"/>
+      <c r="AE17" s="184"/>
+      <c r="AF17" s="185"/>
       <c r="AG17" s="69"/>
       <c r="AH17" s="69"/>
       <c r="AI17" s="69"/>
@@ -18649,10 +18653,10 @@
       <c r="A18" s="37">
         <v>7</v>
       </c>
-      <c r="B18" s="170" t="s">
+      <c r="B18" s="132" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="171"/>
+      <c r="C18" s="133"/>
       <c r="D18" s="92" t="s">
         <v>108</v>
       </c>
@@ -18670,20 +18674,20 @@
       <c r="P18" s="69"/>
       <c r="Q18" s="69"/>
       <c r="R18" s="69"/>
-      <c r="S18" s="172"/>
-      <c r="T18" s="173"/>
-      <c r="U18" s="173"/>
-      <c r="V18" s="173"/>
-      <c r="W18" s="173"/>
-      <c r="X18" s="173"/>
-      <c r="Y18" s="173"/>
-      <c r="Z18" s="173"/>
-      <c r="AA18" s="173"/>
-      <c r="AB18" s="173"/>
-      <c r="AC18" s="173"/>
-      <c r="AD18" s="173"/>
-      <c r="AE18" s="173"/>
-      <c r="AF18" s="174"/>
+      <c r="S18" s="183"/>
+      <c r="T18" s="184"/>
+      <c r="U18" s="184"/>
+      <c r="V18" s="184"/>
+      <c r="W18" s="184"/>
+      <c r="X18" s="184"/>
+      <c r="Y18" s="184"/>
+      <c r="Z18" s="184"/>
+      <c r="AA18" s="184"/>
+      <c r="AB18" s="184"/>
+      <c r="AC18" s="184"/>
+      <c r="AD18" s="184"/>
+      <c r="AE18" s="184"/>
+      <c r="AF18" s="185"/>
       <c r="AG18" s="69"/>
       <c r="AH18" s="69"/>
       <c r="AI18" s="69"/>
@@ -18909,10 +18913,10 @@
       <c r="A19" s="37">
         <v>8</v>
       </c>
-      <c r="B19" s="170" t="s">
+      <c r="B19" s="132" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="171"/>
+      <c r="C19" s="133"/>
       <c r="D19" s="92" t="s">
         <v>108</v>
       </c>
@@ -18930,20 +18934,20 @@
       <c r="P19" s="69"/>
       <c r="Q19" s="69"/>
       <c r="R19" s="69"/>
-      <c r="S19" s="172"/>
-      <c r="T19" s="173"/>
-      <c r="U19" s="173"/>
-      <c r="V19" s="173"/>
-      <c r="W19" s="173"/>
-      <c r="X19" s="173"/>
-      <c r="Y19" s="173"/>
-      <c r="Z19" s="173"/>
-      <c r="AA19" s="173"/>
-      <c r="AB19" s="173"/>
-      <c r="AC19" s="173"/>
-      <c r="AD19" s="173"/>
-      <c r="AE19" s="173"/>
-      <c r="AF19" s="174"/>
+      <c r="S19" s="183"/>
+      <c r="T19" s="184"/>
+      <c r="U19" s="184"/>
+      <c r="V19" s="184"/>
+      <c r="W19" s="184"/>
+      <c r="X19" s="184"/>
+      <c r="Y19" s="184"/>
+      <c r="Z19" s="184"/>
+      <c r="AA19" s="184"/>
+      <c r="AB19" s="184"/>
+      <c r="AC19" s="184"/>
+      <c r="AD19" s="184"/>
+      <c r="AE19" s="184"/>
+      <c r="AF19" s="185"/>
       <c r="AG19" s="69"/>
       <c r="AH19" s="69"/>
       <c r="AI19" s="69"/>
@@ -19167,10 +19171,10 @@
     </row>
     <row r="20" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A20" s="34"/>
-      <c r="B20" s="189" t="s">
+      <c r="B20" s="178" t="s">
         <v>120</v>
       </c>
-      <c r="C20" s="190"/>
+      <c r="C20" s="179"/>
       <c r="D20" s="35"/>
       <c r="E20" s="35"/>
       <c r="F20" s="36"/>
@@ -19186,20 +19190,20 @@
       <c r="P20" s="68"/>
       <c r="Q20" s="68"/>
       <c r="R20" s="68"/>
-      <c r="S20" s="172"/>
-      <c r="T20" s="173"/>
-      <c r="U20" s="173"/>
-      <c r="V20" s="173"/>
-      <c r="W20" s="173"/>
-      <c r="X20" s="173"/>
-      <c r="Y20" s="173"/>
-      <c r="Z20" s="173"/>
-      <c r="AA20" s="173"/>
-      <c r="AB20" s="173"/>
-      <c r="AC20" s="173"/>
-      <c r="AD20" s="173"/>
-      <c r="AE20" s="173"/>
-      <c r="AF20" s="174"/>
+      <c r="S20" s="183"/>
+      <c r="T20" s="184"/>
+      <c r="U20" s="184"/>
+      <c r="V20" s="184"/>
+      <c r="W20" s="184"/>
+      <c r="X20" s="184"/>
+      <c r="Y20" s="184"/>
+      <c r="Z20" s="184"/>
+      <c r="AA20" s="184"/>
+      <c r="AB20" s="184"/>
+      <c r="AC20" s="184"/>
+      <c r="AD20" s="184"/>
+      <c r="AE20" s="184"/>
+      <c r="AF20" s="185"/>
       <c r="AI20" s="3"/>
       <c r="AJ20" s="3"/>
       <c r="AK20" s="3"/>
@@ -19441,20 +19445,20 @@
       <c r="P21" s="69"/>
       <c r="Q21" s="69"/>
       <c r="R21" s="69"/>
-      <c r="S21" s="172"/>
-      <c r="T21" s="173"/>
-      <c r="U21" s="173"/>
-      <c r="V21" s="173"/>
-      <c r="W21" s="173"/>
-      <c r="X21" s="173"/>
-      <c r="Y21" s="173"/>
-      <c r="Z21" s="173"/>
-      <c r="AA21" s="173"/>
-      <c r="AB21" s="173"/>
-      <c r="AC21" s="173"/>
-      <c r="AD21" s="173"/>
-      <c r="AE21" s="173"/>
-      <c r="AF21" s="174"/>
+      <c r="S21" s="183"/>
+      <c r="T21" s="184"/>
+      <c r="U21" s="184"/>
+      <c r="V21" s="184"/>
+      <c r="W21" s="184"/>
+      <c r="X21" s="184"/>
+      <c r="Y21" s="184"/>
+      <c r="Z21" s="184"/>
+      <c r="AA21" s="184"/>
+      <c r="AB21" s="184"/>
+      <c r="AC21" s="184"/>
+      <c r="AD21" s="184"/>
+      <c r="AE21" s="184"/>
+      <c r="AF21" s="185"/>
       <c r="AI21" s="3"/>
       <c r="AJ21" s="3"/>
       <c r="AK21" s="3"/>
@@ -19696,20 +19700,20 @@
       <c r="P22" s="69"/>
       <c r="Q22" s="69"/>
       <c r="R22" s="69"/>
-      <c r="S22" s="172"/>
-      <c r="T22" s="173"/>
-      <c r="U22" s="173"/>
-      <c r="V22" s="173"/>
-      <c r="W22" s="173"/>
-      <c r="X22" s="173"/>
-      <c r="Y22" s="173"/>
-      <c r="Z22" s="173"/>
-      <c r="AA22" s="173"/>
-      <c r="AB22" s="173"/>
-      <c r="AC22" s="173"/>
-      <c r="AD22" s="173"/>
-      <c r="AE22" s="173"/>
-      <c r="AF22" s="174"/>
+      <c r="S22" s="183"/>
+      <c r="T22" s="184"/>
+      <c r="U22" s="184"/>
+      <c r="V22" s="184"/>
+      <c r="W22" s="184"/>
+      <c r="X22" s="184"/>
+      <c r="Y22" s="184"/>
+      <c r="Z22" s="184"/>
+      <c r="AA22" s="184"/>
+      <c r="AB22" s="184"/>
+      <c r="AC22" s="184"/>
+      <c r="AD22" s="184"/>
+      <c r="AE22" s="184"/>
+      <c r="AF22" s="185"/>
       <c r="AI22" s="3"/>
       <c r="AJ22" s="3"/>
       <c r="AK22" s="3"/>
@@ -19930,10 +19934,10 @@
       <c r="A23" s="101" t="s">
         <v>111</v>
       </c>
-      <c r="B23" s="181" t="s">
+      <c r="B23" s="186" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="182"/>
+      <c r="C23" s="187"/>
       <c r="D23" s="92" t="s">
         <v>110</v>
       </c>
@@ -19953,20 +19957,20 @@
       <c r="P23" s="69"/>
       <c r="Q23" s="69"/>
       <c r="R23" s="69"/>
-      <c r="S23" s="172"/>
-      <c r="T23" s="173"/>
-      <c r="U23" s="173"/>
-      <c r="V23" s="173"/>
-      <c r="W23" s="173"/>
-      <c r="X23" s="173"/>
-      <c r="Y23" s="173"/>
-      <c r="Z23" s="173"/>
-      <c r="AA23" s="173"/>
-      <c r="AB23" s="173"/>
-      <c r="AC23" s="173"/>
-      <c r="AD23" s="173"/>
-      <c r="AE23" s="173"/>
-      <c r="AF23" s="174"/>
+      <c r="S23" s="183"/>
+      <c r="T23" s="184"/>
+      <c r="U23" s="184"/>
+      <c r="V23" s="184"/>
+      <c r="W23" s="184"/>
+      <c r="X23" s="184"/>
+      <c r="Y23" s="184"/>
+      <c r="Z23" s="184"/>
+      <c r="AA23" s="184"/>
+      <c r="AB23" s="184"/>
+      <c r="AC23" s="184"/>
+      <c r="AD23" s="184"/>
+      <c r="AE23" s="184"/>
+      <c r="AF23" s="185"/>
       <c r="AI23" s="3"/>
       <c r="AJ23" s="3"/>
       <c r="AK23" s="3"/>
@@ -20210,20 +20214,20 @@
       <c r="P24" s="69"/>
       <c r="Q24" s="69"/>
       <c r="R24" s="69"/>
-      <c r="S24" s="172"/>
-      <c r="T24" s="173"/>
-      <c r="U24" s="173"/>
-      <c r="V24" s="173"/>
-      <c r="W24" s="173"/>
-      <c r="X24" s="173"/>
-      <c r="Y24" s="173"/>
-      <c r="Z24" s="173"/>
-      <c r="AA24" s="173"/>
-      <c r="AB24" s="173"/>
-      <c r="AC24" s="173"/>
-      <c r="AD24" s="173"/>
-      <c r="AE24" s="173"/>
-      <c r="AF24" s="174"/>
+      <c r="S24" s="183"/>
+      <c r="T24" s="184"/>
+      <c r="U24" s="184"/>
+      <c r="V24" s="184"/>
+      <c r="W24" s="184"/>
+      <c r="X24" s="184"/>
+      <c r="Y24" s="184"/>
+      <c r="Z24" s="184"/>
+      <c r="AA24" s="184"/>
+      <c r="AB24" s="184"/>
+      <c r="AC24" s="184"/>
+      <c r="AD24" s="184"/>
+      <c r="AE24" s="184"/>
+      <c r="AF24" s="185"/>
       <c r="AI24" s="3"/>
       <c r="AJ24" s="3"/>
       <c r="AK24" s="3"/>
@@ -20465,20 +20469,20 @@
       <c r="P25" s="69"/>
       <c r="Q25" s="69"/>
       <c r="R25" s="69"/>
-      <c r="S25" s="172"/>
-      <c r="T25" s="173"/>
-      <c r="U25" s="173"/>
-      <c r="V25" s="173"/>
-      <c r="W25" s="173"/>
-      <c r="X25" s="173"/>
-      <c r="Y25" s="173"/>
-      <c r="Z25" s="173"/>
-      <c r="AA25" s="173"/>
-      <c r="AB25" s="173"/>
-      <c r="AC25" s="173"/>
-      <c r="AD25" s="173"/>
-      <c r="AE25" s="173"/>
-      <c r="AF25" s="174"/>
+      <c r="S25" s="183"/>
+      <c r="T25" s="184"/>
+      <c r="U25" s="184"/>
+      <c r="V25" s="184"/>
+      <c r="W25" s="184"/>
+      <c r="X25" s="184"/>
+      <c r="Y25" s="184"/>
+      <c r="Z25" s="184"/>
+      <c r="AA25" s="184"/>
+      <c r="AB25" s="184"/>
+      <c r="AC25" s="184"/>
+      <c r="AD25" s="184"/>
+      <c r="AE25" s="184"/>
+      <c r="AF25" s="185"/>
       <c r="AI25" s="3"/>
       <c r="AJ25" s="3"/>
       <c r="AK25" s="3"/>
@@ -20720,20 +20724,20 @@
       <c r="P26" s="69"/>
       <c r="Q26" s="69"/>
       <c r="R26" s="69"/>
-      <c r="S26" s="172"/>
-      <c r="T26" s="173"/>
-      <c r="U26" s="173"/>
-      <c r="V26" s="173"/>
-      <c r="W26" s="173"/>
-      <c r="X26" s="173"/>
-      <c r="Y26" s="173"/>
-      <c r="Z26" s="173"/>
-      <c r="AA26" s="173"/>
-      <c r="AB26" s="173"/>
-      <c r="AC26" s="173"/>
-      <c r="AD26" s="173"/>
-      <c r="AE26" s="173"/>
-      <c r="AF26" s="174"/>
+      <c r="S26" s="183"/>
+      <c r="T26" s="184"/>
+      <c r="U26" s="184"/>
+      <c r="V26" s="184"/>
+      <c r="W26" s="184"/>
+      <c r="X26" s="184"/>
+      <c r="Y26" s="184"/>
+      <c r="Z26" s="184"/>
+      <c r="AA26" s="184"/>
+      <c r="AB26" s="184"/>
+      <c r="AC26" s="184"/>
+      <c r="AD26" s="184"/>
+      <c r="AE26" s="184"/>
+      <c r="AF26" s="185"/>
       <c r="AI26" s="3"/>
       <c r="AJ26" s="3"/>
       <c r="AK26" s="3"/>
@@ -20975,20 +20979,20 @@
       <c r="P27" s="69"/>
       <c r="Q27" s="69"/>
       <c r="R27" s="69"/>
-      <c r="S27" s="172"/>
-      <c r="T27" s="173"/>
-      <c r="U27" s="173"/>
-      <c r="V27" s="173"/>
-      <c r="W27" s="173"/>
-      <c r="X27" s="173"/>
-      <c r="Y27" s="173"/>
-      <c r="Z27" s="173"/>
-      <c r="AA27" s="173"/>
-      <c r="AB27" s="173"/>
-      <c r="AC27" s="173"/>
-      <c r="AD27" s="173"/>
-      <c r="AE27" s="173"/>
-      <c r="AF27" s="174"/>
+      <c r="S27" s="183"/>
+      <c r="T27" s="184"/>
+      <c r="U27" s="184"/>
+      <c r="V27" s="184"/>
+      <c r="W27" s="184"/>
+      <c r="X27" s="184"/>
+      <c r="Y27" s="184"/>
+      <c r="Z27" s="184"/>
+      <c r="AA27" s="184"/>
+      <c r="AB27" s="184"/>
+      <c r="AC27" s="184"/>
+      <c r="AD27" s="184"/>
+      <c r="AE27" s="184"/>
+      <c r="AF27" s="185"/>
       <c r="AI27" s="3"/>
       <c r="AJ27" s="3"/>
       <c r="AK27" s="3"/>
@@ -21230,20 +21234,20 @@
       <c r="P28" s="69"/>
       <c r="Q28" s="69"/>
       <c r="R28" s="69"/>
-      <c r="S28" s="172"/>
-      <c r="T28" s="173"/>
-      <c r="U28" s="173"/>
-      <c r="V28" s="173"/>
-      <c r="W28" s="173"/>
-      <c r="X28" s="173"/>
-      <c r="Y28" s="173"/>
-      <c r="Z28" s="173"/>
-      <c r="AA28" s="173"/>
-      <c r="AB28" s="173"/>
-      <c r="AC28" s="173"/>
-      <c r="AD28" s="173"/>
-      <c r="AE28" s="173"/>
-      <c r="AF28" s="174"/>
+      <c r="S28" s="183"/>
+      <c r="T28" s="184"/>
+      <c r="U28" s="184"/>
+      <c r="V28" s="184"/>
+      <c r="W28" s="184"/>
+      <c r="X28" s="184"/>
+      <c r="Y28" s="184"/>
+      <c r="Z28" s="184"/>
+      <c r="AA28" s="184"/>
+      <c r="AB28" s="184"/>
+      <c r="AC28" s="184"/>
+      <c r="AD28" s="184"/>
+      <c r="AE28" s="184"/>
+      <c r="AF28" s="185"/>
       <c r="AI28" s="3"/>
       <c r="AJ28" s="3"/>
       <c r="AK28" s="3"/>
@@ -21481,20 +21485,20 @@
       <c r="P29" s="69"/>
       <c r="Q29" s="69"/>
       <c r="R29" s="69"/>
-      <c r="S29" s="172"/>
-      <c r="T29" s="173"/>
-      <c r="U29" s="173"/>
-      <c r="V29" s="173"/>
-      <c r="W29" s="173"/>
-      <c r="X29" s="173"/>
-      <c r="Y29" s="173"/>
-      <c r="Z29" s="173"/>
-      <c r="AA29" s="173"/>
-      <c r="AB29" s="173"/>
-      <c r="AC29" s="173"/>
-      <c r="AD29" s="173"/>
-      <c r="AE29" s="173"/>
-      <c r="AF29" s="174"/>
+      <c r="S29" s="183"/>
+      <c r="T29" s="184"/>
+      <c r="U29" s="184"/>
+      <c r="V29" s="184"/>
+      <c r="W29" s="184"/>
+      <c r="X29" s="184"/>
+      <c r="Y29" s="184"/>
+      <c r="Z29" s="184"/>
+      <c r="AA29" s="184"/>
+      <c r="AB29" s="184"/>
+      <c r="AC29" s="184"/>
+      <c r="AD29" s="184"/>
+      <c r="AE29" s="184"/>
+      <c r="AF29" s="185"/>
       <c r="AI29" s="3"/>
       <c r="AJ29" s="3"/>
       <c r="AK29" s="3"/>
@@ -21713,10 +21717,10 @@
     </row>
     <row r="30" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A30" s="37"/>
-      <c r="B30" s="154" t="s">
+      <c r="B30" s="137" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="155"/>
+      <c r="C30" s="138"/>
       <c r="D30" s="92"/>
       <c r="E30" s="92"/>
       <c r="F30" s="36"/>
@@ -21732,20 +21736,20 @@
       <c r="P30" s="69"/>
       <c r="Q30" s="69"/>
       <c r="R30" s="69"/>
-      <c r="S30" s="172"/>
-      <c r="T30" s="173"/>
-      <c r="U30" s="173"/>
-      <c r="V30" s="173"/>
-      <c r="W30" s="173"/>
-      <c r="X30" s="173"/>
-      <c r="Y30" s="173"/>
-      <c r="Z30" s="173"/>
-      <c r="AA30" s="173"/>
-      <c r="AB30" s="173"/>
-      <c r="AC30" s="173"/>
-      <c r="AD30" s="173"/>
-      <c r="AE30" s="173"/>
-      <c r="AF30" s="174"/>
+      <c r="S30" s="183"/>
+      <c r="T30" s="184"/>
+      <c r="U30" s="184"/>
+      <c r="V30" s="184"/>
+      <c r="W30" s="184"/>
+      <c r="X30" s="184"/>
+      <c r="Y30" s="184"/>
+      <c r="Z30" s="184"/>
+      <c r="AA30" s="184"/>
+      <c r="AB30" s="184"/>
+      <c r="AC30" s="184"/>
+      <c r="AD30" s="184"/>
+      <c r="AE30" s="184"/>
+      <c r="AF30" s="185"/>
       <c r="AI30" s="3"/>
       <c r="AJ30" s="3"/>
       <c r="AK30" s="3"/>
@@ -21968,7 +21972,7 @@
         <v>92</v>
       </c>
       <c r="C31" s="118"/>
-      <c r="D31" s="158" t="s">
+      <c r="D31" s="134" t="s">
         <v>117</v>
       </c>
       <c r="E31" s="92"/>
@@ -21985,20 +21989,20 @@
       <c r="P31" s="69"/>
       <c r="Q31" s="69"/>
       <c r="R31" s="69"/>
-      <c r="S31" s="172"/>
-      <c r="T31" s="173"/>
-      <c r="U31" s="173"/>
-      <c r="V31" s="173"/>
-      <c r="W31" s="173"/>
-      <c r="X31" s="173"/>
-      <c r="Y31" s="173"/>
-      <c r="Z31" s="173"/>
-      <c r="AA31" s="173"/>
-      <c r="AB31" s="173"/>
-      <c r="AC31" s="173"/>
-      <c r="AD31" s="173"/>
-      <c r="AE31" s="173"/>
-      <c r="AF31" s="174"/>
+      <c r="S31" s="183"/>
+      <c r="T31" s="184"/>
+      <c r="U31" s="184"/>
+      <c r="V31" s="184"/>
+      <c r="W31" s="184"/>
+      <c r="X31" s="184"/>
+      <c r="Y31" s="184"/>
+      <c r="Z31" s="184"/>
+      <c r="AA31" s="184"/>
+      <c r="AB31" s="184"/>
+      <c r="AC31" s="184"/>
+      <c r="AD31" s="184"/>
+      <c r="AE31" s="184"/>
+      <c r="AF31" s="185"/>
       <c r="AI31" s="3"/>
       <c r="AJ31" s="3"/>
       <c r="AK31" s="3"/>
@@ -22221,7 +22225,7 @@
         <v>93</v>
       </c>
       <c r="C32" s="118"/>
-      <c r="D32" s="119"/>
+      <c r="D32" s="135"/>
       <c r="E32" s="92" t="s">
         <v>47</v>
       </c>
@@ -22238,20 +22242,20 @@
       <c r="P32" s="68"/>
       <c r="Q32" s="68"/>
       <c r="R32" s="68"/>
-      <c r="S32" s="172"/>
-      <c r="T32" s="173"/>
-      <c r="U32" s="173"/>
-      <c r="V32" s="173"/>
-      <c r="W32" s="173"/>
-      <c r="X32" s="173"/>
-      <c r="Y32" s="173"/>
-      <c r="Z32" s="173"/>
-      <c r="AA32" s="173"/>
-      <c r="AB32" s="173"/>
-      <c r="AC32" s="173"/>
-      <c r="AD32" s="173"/>
-      <c r="AE32" s="173"/>
-      <c r="AF32" s="174"/>
+      <c r="S32" s="183"/>
+      <c r="T32" s="184"/>
+      <c r="U32" s="184"/>
+      <c r="V32" s="184"/>
+      <c r="W32" s="184"/>
+      <c r="X32" s="184"/>
+      <c r="Y32" s="184"/>
+      <c r="Z32" s="184"/>
+      <c r="AA32" s="184"/>
+      <c r="AB32" s="184"/>
+      <c r="AC32" s="184"/>
+      <c r="AD32" s="184"/>
+      <c r="AE32" s="184"/>
+      <c r="AF32" s="185"/>
       <c r="AI32" s="3"/>
       <c r="AJ32" s="3"/>
       <c r="AK32" s="3"/>
@@ -22474,7 +22478,7 @@
         <v>94</v>
       </c>
       <c r="C33" s="118"/>
-      <c r="D33" s="120"/>
+      <c r="D33" s="136"/>
       <c r="E33" s="92"/>
       <c r="F33" s="36"/>
       <c r="G33" s="68"/>
@@ -22489,20 +22493,20 @@
       <c r="P33" s="68"/>
       <c r="Q33" s="68"/>
       <c r="R33" s="68"/>
-      <c r="S33" s="172"/>
-      <c r="T33" s="173"/>
-      <c r="U33" s="173"/>
-      <c r="V33" s="173"/>
-      <c r="W33" s="173"/>
-      <c r="X33" s="173"/>
-      <c r="Y33" s="173"/>
-      <c r="Z33" s="173"/>
-      <c r="AA33" s="173"/>
-      <c r="AB33" s="173"/>
-      <c r="AC33" s="173"/>
-      <c r="AD33" s="173"/>
-      <c r="AE33" s="173"/>
-      <c r="AF33" s="174"/>
+      <c r="S33" s="183"/>
+      <c r="T33" s="184"/>
+      <c r="U33" s="184"/>
+      <c r="V33" s="184"/>
+      <c r="W33" s="184"/>
+      <c r="X33" s="184"/>
+      <c r="Y33" s="184"/>
+      <c r="Z33" s="184"/>
+      <c r="AA33" s="184"/>
+      <c r="AB33" s="184"/>
+      <c r="AC33" s="184"/>
+      <c r="AD33" s="184"/>
+      <c r="AE33" s="184"/>
+      <c r="AF33" s="185"/>
       <c r="AI33" s="3"/>
       <c r="AJ33" s="3"/>
       <c r="AK33" s="3"/>
@@ -22721,10 +22725,10 @@
     </row>
     <row r="34" spans="1:249" s="2" customFormat="1" ht="28.25" customHeight="1">
       <c r="A34" s="38"/>
-      <c r="B34" s="154" t="s">
+      <c r="B34" s="137" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="155"/>
+      <c r="C34" s="138"/>
       <c r="D34" s="35"/>
       <c r="E34" s="35"/>
       <c r="F34" s="39"/>
@@ -22740,20 +22744,20 @@
       <c r="P34" s="68"/>
       <c r="Q34" s="68"/>
       <c r="R34" s="68"/>
-      <c r="S34" s="172"/>
-      <c r="T34" s="173"/>
-      <c r="U34" s="173"/>
-      <c r="V34" s="173"/>
-      <c r="W34" s="173"/>
-      <c r="X34" s="173"/>
-      <c r="Y34" s="173"/>
-      <c r="Z34" s="173"/>
-      <c r="AA34" s="173"/>
-      <c r="AB34" s="173"/>
-      <c r="AC34" s="173"/>
-      <c r="AD34" s="173"/>
-      <c r="AE34" s="173"/>
-      <c r="AF34" s="174"/>
+      <c r="S34" s="183"/>
+      <c r="T34" s="184"/>
+      <c r="U34" s="184"/>
+      <c r="V34" s="184"/>
+      <c r="W34" s="184"/>
+      <c r="X34" s="184"/>
+      <c r="Y34" s="184"/>
+      <c r="Z34" s="184"/>
+      <c r="AA34" s="184"/>
+      <c r="AB34" s="184"/>
+      <c r="AC34" s="184"/>
+      <c r="AD34" s="184"/>
+      <c r="AE34" s="184"/>
+      <c r="AF34" s="185"/>
       <c r="AI34" s="3"/>
       <c r="AJ34" s="3"/>
       <c r="AK34" s="3"/>
@@ -22974,15 +22978,15 @@
       <c r="A35" s="37">
         <v>1</v>
       </c>
-      <c r="B35" s="156" t="s">
+      <c r="B35" s="130" t="s">
         <v>104</v>
       </c>
-      <c r="C35" s="157"/>
+      <c r="C35" s="131"/>
       <c r="D35" s="96"/>
       <c r="E35" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="F35" s="158" t="s">
+      <c r="F35" s="134" t="s">
         <v>95</v>
       </c>
       <c r="G35" s="69"/>
@@ -22997,20 +23001,20 @@
       <c r="P35" s="69"/>
       <c r="Q35" s="69"/>
       <c r="R35" s="69"/>
-      <c r="S35" s="172"/>
-      <c r="T35" s="173"/>
-      <c r="U35" s="173"/>
-      <c r="V35" s="173"/>
-      <c r="W35" s="173"/>
-      <c r="X35" s="173"/>
-      <c r="Y35" s="173"/>
-      <c r="Z35" s="173"/>
-      <c r="AA35" s="173"/>
-      <c r="AB35" s="173"/>
-      <c r="AC35" s="173"/>
-      <c r="AD35" s="173"/>
-      <c r="AE35" s="173"/>
-      <c r="AF35" s="174"/>
+      <c r="S35" s="183"/>
+      <c r="T35" s="184"/>
+      <c r="U35" s="184"/>
+      <c r="V35" s="184"/>
+      <c r="W35" s="184"/>
+      <c r="X35" s="184"/>
+      <c r="Y35" s="184"/>
+      <c r="Z35" s="184"/>
+      <c r="AA35" s="184"/>
+      <c r="AB35" s="184"/>
+      <c r="AC35" s="184"/>
+      <c r="AD35" s="184"/>
+      <c r="AE35" s="184"/>
+      <c r="AF35" s="185"/>
       <c r="AI35" s="3"/>
       <c r="AJ35" s="3"/>
       <c r="AK35" s="3"/>
@@ -23237,7 +23241,7 @@
       <c r="E36" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="F36" s="119"/>
+      <c r="F36" s="135"/>
       <c r="G36" s="68"/>
       <c r="H36" s="68"/>
       <c r="I36" s="68"/>
@@ -23250,20 +23254,20 @@
       <c r="P36" s="68"/>
       <c r="Q36" s="68"/>
       <c r="R36" s="68"/>
-      <c r="S36" s="172"/>
-      <c r="T36" s="173"/>
-      <c r="U36" s="173"/>
-      <c r="V36" s="173"/>
-      <c r="W36" s="173"/>
-      <c r="X36" s="173"/>
-      <c r="Y36" s="173"/>
-      <c r="Z36" s="173"/>
-      <c r="AA36" s="173"/>
-      <c r="AB36" s="173"/>
-      <c r="AC36" s="173"/>
-      <c r="AD36" s="173"/>
-      <c r="AE36" s="173"/>
-      <c r="AF36" s="174"/>
+      <c r="S36" s="183"/>
+      <c r="T36" s="184"/>
+      <c r="U36" s="184"/>
+      <c r="V36" s="184"/>
+      <c r="W36" s="184"/>
+      <c r="X36" s="184"/>
+      <c r="Y36" s="184"/>
+      <c r="Z36" s="184"/>
+      <c r="AA36" s="184"/>
+      <c r="AB36" s="184"/>
+      <c r="AC36" s="184"/>
+      <c r="AD36" s="184"/>
+      <c r="AE36" s="184"/>
+      <c r="AF36" s="185"/>
       <c r="AI36" s="3"/>
       <c r="AJ36" s="3"/>
       <c r="AK36" s="3"/>
@@ -23484,11 +23488,11 @@
       <c r="A37" s="37">
         <v>3</v>
       </c>
-      <c r="B37" s="156"/>
-      <c r="C37" s="157"/>
+      <c r="B37" s="130"/>
+      <c r="C37" s="131"/>
       <c r="D37" s="92"/>
       <c r="E37" s="35"/>
-      <c r="F37" s="119"/>
+      <c r="F37" s="135"/>
       <c r="G37" s="68"/>
       <c r="H37" s="68"/>
       <c r="I37" s="68"/>
@@ -23501,20 +23505,20 @@
       <c r="P37" s="68"/>
       <c r="Q37" s="68"/>
       <c r="R37" s="68"/>
-      <c r="S37" s="172"/>
-      <c r="T37" s="173"/>
-      <c r="U37" s="173"/>
-      <c r="V37" s="173"/>
-      <c r="W37" s="173"/>
-      <c r="X37" s="173"/>
-      <c r="Y37" s="173"/>
-      <c r="Z37" s="173"/>
-      <c r="AA37" s="173"/>
-      <c r="AB37" s="173"/>
-      <c r="AC37" s="173"/>
-      <c r="AD37" s="173"/>
-      <c r="AE37" s="173"/>
-      <c r="AF37" s="174"/>
+      <c r="S37" s="183"/>
+      <c r="T37" s="184"/>
+      <c r="U37" s="184"/>
+      <c r="V37" s="184"/>
+      <c r="W37" s="184"/>
+      <c r="X37" s="184"/>
+      <c r="Y37" s="184"/>
+      <c r="Z37" s="184"/>
+      <c r="AA37" s="184"/>
+      <c r="AB37" s="184"/>
+      <c r="AC37" s="184"/>
+      <c r="AD37" s="184"/>
+      <c r="AE37" s="184"/>
+      <c r="AF37" s="185"/>
       <c r="AI37" s="3"/>
       <c r="AJ37" s="3"/>
       <c r="AK37" s="3"/>
@@ -23733,10 +23737,10 @@
     </row>
     <row r="38" spans="1:249" s="2" customFormat="1" ht="42" customHeight="1" thickBot="1">
       <c r="A38" s="41"/>
-      <c r="B38" s="168" t="s">
+      <c r="B38" s="128" t="s">
         <v>63</v>
       </c>
-      <c r="C38" s="169"/>
+      <c r="C38" s="129"/>
       <c r="D38" s="42" t="s">
         <v>16</v>
       </c>
@@ -23994,29 +23998,29 @@
       <c r="E39" s="44"/>
       <c r="F39" s="57"/>
       <c r="G39" s="75"/>
-      <c r="H39" s="180"/>
-      <c r="I39" s="180"/>
-      <c r="J39" s="180"/>
-      <c r="K39" s="180"/>
+      <c r="H39" s="188"/>
+      <c r="I39" s="188"/>
+      <c r="J39" s="188"/>
+      <c r="K39" s="188"/>
       <c r="L39" s="76"/>
       <c r="M39" s="75"/>
-      <c r="N39" s="180"/>
-      <c r="O39" s="180"/>
-      <c r="P39" s="180"/>
-      <c r="Q39" s="180"/>
+      <c r="N39" s="188"/>
+      <c r="O39" s="188"/>
+      <c r="P39" s="188"/>
+      <c r="Q39" s="188"/>
       <c r="R39" s="76"/>
       <c r="S39" s="75"/>
-      <c r="T39" s="180"/>
-      <c r="U39" s="180"/>
-      <c r="V39" s="180"/>
+      <c r="T39" s="188"/>
+      <c r="U39" s="188"/>
+      <c r="V39" s="188"/>
       <c r="W39" s="75"/>
-      <c r="X39" s="180"/>
-      <c r="Y39" s="180"/>
-      <c r="Z39" s="180"/>
+      <c r="X39" s="188"/>
+      <c r="Y39" s="188"/>
+      <c r="Z39" s="188"/>
       <c r="AA39" s="76"/>
       <c r="AB39" s="75"/>
-      <c r="AC39" s="180"/>
-      <c r="AD39" s="180"/>
+      <c r="AC39" s="188"/>
+      <c r="AD39" s="188"/>
       <c r="AE39" s="55"/>
       <c r="AF39" s="56"/>
       <c r="AI39" s="3"/>
@@ -24247,29 +24251,29 @@
       <c r="E40" s="90"/>
       <c r="F40" s="58"/>
       <c r="G40" s="77"/>
-      <c r="H40" s="179"/>
-      <c r="I40" s="179"/>
-      <c r="J40" s="179"/>
-      <c r="K40" s="179"/>
+      <c r="H40" s="189"/>
+      <c r="I40" s="189"/>
+      <c r="J40" s="189"/>
+      <c r="K40" s="189"/>
       <c r="L40" s="78"/>
       <c r="M40" s="77"/>
-      <c r="N40" s="179"/>
-      <c r="O40" s="179"/>
-      <c r="P40" s="179"/>
-      <c r="Q40" s="179"/>
+      <c r="N40" s="189"/>
+      <c r="O40" s="189"/>
+      <c r="P40" s="189"/>
+      <c r="Q40" s="189"/>
       <c r="R40" s="78"/>
       <c r="S40" s="77"/>
-      <c r="T40" s="179"/>
-      <c r="U40" s="179"/>
-      <c r="V40" s="179"/>
+      <c r="T40" s="189"/>
+      <c r="U40" s="189"/>
+      <c r="V40" s="189"/>
       <c r="W40" s="77"/>
-      <c r="X40" s="179"/>
-      <c r="Y40" s="179"/>
-      <c r="Z40" s="179"/>
+      <c r="X40" s="189"/>
+      <c r="Y40" s="189"/>
+      <c r="Z40" s="189"/>
       <c r="AA40" s="78"/>
       <c r="AB40" s="77"/>
-      <c r="AC40" s="179"/>
-      <c r="AD40" s="179"/>
+      <c r="AC40" s="189"/>
+      <c r="AD40" s="189"/>
       <c r="AE40" s="61"/>
       <c r="AF40" s="79"/>
       <c r="AI40" s="3"/>
@@ -24500,29 +24504,29 @@
       <c r="E41" s="91"/>
       <c r="F41" s="59"/>
       <c r="G41" s="77"/>
-      <c r="H41" s="179"/>
-      <c r="I41" s="179"/>
-      <c r="J41" s="179"/>
-      <c r="K41" s="179"/>
+      <c r="H41" s="189"/>
+      <c r="I41" s="189"/>
+      <c r="J41" s="189"/>
+      <c r="K41" s="189"/>
       <c r="L41" s="80"/>
       <c r="M41" s="77"/>
-      <c r="N41" s="179"/>
-      <c r="O41" s="179"/>
-      <c r="P41" s="179"/>
-      <c r="Q41" s="179"/>
+      <c r="N41" s="189"/>
+      <c r="O41" s="189"/>
+      <c r="P41" s="189"/>
+      <c r="Q41" s="189"/>
       <c r="R41" s="80"/>
       <c r="S41" s="77"/>
-      <c r="T41" s="179"/>
-      <c r="U41" s="179"/>
-      <c r="V41" s="179"/>
+      <c r="T41" s="189"/>
+      <c r="U41" s="189"/>
+      <c r="V41" s="189"/>
       <c r="W41" s="77"/>
-      <c r="X41" s="179"/>
-      <c r="Y41" s="179"/>
-      <c r="Z41" s="179"/>
+      <c r="X41" s="189"/>
+      <c r="Y41" s="189"/>
+      <c r="Z41" s="189"/>
       <c r="AA41" s="80"/>
       <c r="AB41" s="77"/>
-      <c r="AC41" s="179"/>
-      <c r="AD41" s="179"/>
+      <c r="AC41" s="189"/>
+      <c r="AD41" s="189"/>
       <c r="AE41" s="62"/>
       <c r="AF41" s="81"/>
       <c r="AI41" s="3"/>
@@ -24753,29 +24757,29 @@
       <c r="E42" s="91"/>
       <c r="F42" s="59"/>
       <c r="G42" s="77"/>
-      <c r="H42" s="179"/>
-      <c r="I42" s="179"/>
-      <c r="J42" s="179"/>
-      <c r="K42" s="179"/>
+      <c r="H42" s="189"/>
+      <c r="I42" s="189"/>
+      <c r="J42" s="189"/>
+      <c r="K42" s="189"/>
       <c r="L42" s="80"/>
       <c r="M42" s="77"/>
-      <c r="N42" s="179"/>
-      <c r="O42" s="179"/>
-      <c r="P42" s="179"/>
-      <c r="Q42" s="179"/>
+      <c r="N42" s="189"/>
+      <c r="O42" s="189"/>
+      <c r="P42" s="189"/>
+      <c r="Q42" s="189"/>
       <c r="R42" s="80"/>
       <c r="S42" s="77"/>
-      <c r="T42" s="179"/>
-      <c r="U42" s="179"/>
-      <c r="V42" s="179"/>
+      <c r="T42" s="189"/>
+      <c r="U42" s="189"/>
+      <c r="V42" s="189"/>
       <c r="W42" s="77"/>
-      <c r="X42" s="179"/>
-      <c r="Y42" s="179"/>
-      <c r="Z42" s="179"/>
+      <c r="X42" s="189"/>
+      <c r="Y42" s="189"/>
+      <c r="Z42" s="189"/>
       <c r="AA42" s="80"/>
       <c r="AB42" s="77"/>
-      <c r="AC42" s="179"/>
-      <c r="AD42" s="179"/>
+      <c r="AC42" s="189"/>
+      <c r="AD42" s="189"/>
       <c r="AE42" s="62"/>
       <c r="AF42" s="81"/>
       <c r="AI42" s="3"/>
@@ -25002,29 +25006,29 @@
       <c r="E43" s="50"/>
       <c r="F43" s="60"/>
       <c r="G43" s="82"/>
-      <c r="H43" s="175"/>
-      <c r="I43" s="175"/>
-      <c r="J43" s="175"/>
-      <c r="K43" s="175"/>
+      <c r="H43" s="190"/>
+      <c r="I43" s="190"/>
+      <c r="J43" s="190"/>
+      <c r="K43" s="190"/>
       <c r="L43" s="83"/>
       <c r="M43" s="82"/>
-      <c r="N43" s="175"/>
-      <c r="O43" s="175"/>
-      <c r="P43" s="175"/>
-      <c r="Q43" s="175"/>
+      <c r="N43" s="190"/>
+      <c r="O43" s="190"/>
+      <c r="P43" s="190"/>
+      <c r="Q43" s="190"/>
       <c r="R43" s="83"/>
       <c r="S43" s="82"/>
-      <c r="T43" s="175"/>
-      <c r="U43" s="175"/>
-      <c r="V43" s="175"/>
+      <c r="T43" s="190"/>
+      <c r="U43" s="190"/>
+      <c r="V43" s="190"/>
       <c r="W43" s="82"/>
-      <c r="X43" s="175"/>
-      <c r="Y43" s="175"/>
-      <c r="Z43" s="175"/>
+      <c r="X43" s="190"/>
+      <c r="Y43" s="190"/>
+      <c r="Z43" s="190"/>
       <c r="AA43" s="83"/>
       <c r="AB43" s="82"/>
-      <c r="AC43" s="175"/>
-      <c r="AD43" s="175"/>
+      <c r="AC43" s="190"/>
+      <c r="AD43" s="190"/>
       <c r="AE43" s="63"/>
       <c r="AF43" s="84"/>
       <c r="AI43" s="3"/>
@@ -25288,13 +25292,83 @@
     </row>
   </sheetData>
   <mergeCells count="100">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="F1:AF1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="T3:AF3"/>
+    <mergeCell ref="S32:AF32"/>
+    <mergeCell ref="S33:AF33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="S26:AF26"/>
+    <mergeCell ref="S28:AF28"/>
+    <mergeCell ref="S29:AF29"/>
+    <mergeCell ref="S30:AF30"/>
+    <mergeCell ref="S31:AF31"/>
+    <mergeCell ref="S27:AF27"/>
+    <mergeCell ref="AC43:AD43"/>
+    <mergeCell ref="S9:AF9"/>
+    <mergeCell ref="S20:AF20"/>
+    <mergeCell ref="S21:AF21"/>
+    <mergeCell ref="S22:AF22"/>
+    <mergeCell ref="S23:AF23"/>
+    <mergeCell ref="T41:V41"/>
+    <mergeCell ref="X41:Z41"/>
+    <mergeCell ref="AC41:AD41"/>
+    <mergeCell ref="T42:V42"/>
+    <mergeCell ref="X42:Z42"/>
+    <mergeCell ref="AC42:AD42"/>
+    <mergeCell ref="T39:V39"/>
+    <mergeCell ref="X39:Z39"/>
+    <mergeCell ref="S34:AF34"/>
+    <mergeCell ref="S35:AF35"/>
+    <mergeCell ref="H43:K43"/>
+    <mergeCell ref="N43:Q43"/>
+    <mergeCell ref="T43:V43"/>
+    <mergeCell ref="X43:Z43"/>
+    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="N41:Q41"/>
+    <mergeCell ref="H42:K42"/>
+    <mergeCell ref="N42:Q42"/>
+    <mergeCell ref="H40:K40"/>
+    <mergeCell ref="N40:Q40"/>
+    <mergeCell ref="T40:V40"/>
+    <mergeCell ref="X40:Z40"/>
+    <mergeCell ref="AC40:AD40"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="AC39:AD39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="H39:K39"/>
+    <mergeCell ref="N39:Q39"/>
+    <mergeCell ref="S36:AF36"/>
+    <mergeCell ref="S37:AF37"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="S14:AF14"/>
+    <mergeCell ref="S15:AF15"/>
+    <mergeCell ref="S16:AF16"/>
+    <mergeCell ref="S17:AF17"/>
+    <mergeCell ref="S18:AF18"/>
+    <mergeCell ref="S19:AF19"/>
+    <mergeCell ref="S25:AF25"/>
+    <mergeCell ref="S24:AF24"/>
     <mergeCell ref="T5:W7"/>
     <mergeCell ref="AD4:AF4"/>
     <mergeCell ref="AD5:AF7"/>
@@ -25311,87 +25385,17 @@
     <mergeCell ref="X4:Z4"/>
     <mergeCell ref="AA4:AC4"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="S14:AF14"/>
-    <mergeCell ref="S15:AF15"/>
-    <mergeCell ref="S16:AF16"/>
-    <mergeCell ref="S17:AF17"/>
-    <mergeCell ref="S18:AF18"/>
-    <mergeCell ref="S19:AF19"/>
-    <mergeCell ref="S25:AF25"/>
-    <mergeCell ref="S24:AF24"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="F35:F37"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="AC39:AD39"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="H39:K39"/>
-    <mergeCell ref="N39:Q39"/>
-    <mergeCell ref="S36:AF36"/>
-    <mergeCell ref="S37:AF37"/>
-    <mergeCell ref="H40:K40"/>
-    <mergeCell ref="N40:Q40"/>
-    <mergeCell ref="T40:V40"/>
-    <mergeCell ref="X40:Z40"/>
-    <mergeCell ref="AC40:AD40"/>
-    <mergeCell ref="H43:K43"/>
-    <mergeCell ref="N43:Q43"/>
-    <mergeCell ref="T43:V43"/>
-    <mergeCell ref="X43:Z43"/>
-    <mergeCell ref="H41:K41"/>
-    <mergeCell ref="N41:Q41"/>
-    <mergeCell ref="H42:K42"/>
-    <mergeCell ref="N42:Q42"/>
-    <mergeCell ref="AC43:AD43"/>
-    <mergeCell ref="S9:AF9"/>
-    <mergeCell ref="S20:AF20"/>
-    <mergeCell ref="S21:AF21"/>
-    <mergeCell ref="S22:AF22"/>
-    <mergeCell ref="S23:AF23"/>
-    <mergeCell ref="T41:V41"/>
-    <mergeCell ref="X41:Z41"/>
-    <mergeCell ref="AC41:AD41"/>
-    <mergeCell ref="T42:V42"/>
-    <mergeCell ref="X42:Z42"/>
-    <mergeCell ref="AC42:AD42"/>
-    <mergeCell ref="T39:V39"/>
-    <mergeCell ref="X39:Z39"/>
-    <mergeCell ref="S34:AF34"/>
-    <mergeCell ref="S35:AF35"/>
-    <mergeCell ref="S26:AF26"/>
-    <mergeCell ref="S28:AF28"/>
-    <mergeCell ref="S29:AF29"/>
-    <mergeCell ref="S30:AF30"/>
-    <mergeCell ref="S31:AF31"/>
-    <mergeCell ref="S27:AF27"/>
-    <mergeCell ref="S32:AF32"/>
-    <mergeCell ref="S33:AF33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:AF1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="T3:AF3"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="G11:R19 AG11:AK19">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>TEXT(G11,"aaa")="日"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/設備点検表.xlsx
+++ b/設備点検表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kosuk\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19409173-9DBE-4C7F-8154-6F4CE65B054C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B9EEF3-EBDD-4C2B-AC2F-1B3667F8E8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6C56CF13-AF7F-4C1F-982C-EF388A11F51A}"/>
   </bookViews>
@@ -2995,22 +2995,14 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準_設備点検表書式" xfId="1" xr:uid="{15F629F0-A893-4DD8-8A94-9D447F97F79C}"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <font>
         <strike val="0"/>
-        <color theme="1"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3035,7 +3027,6 @@
     <dxf>
       <font>
         <strike val="0"/>
-        <color theme="1"/>
       </font>
       <fill>
         <patternFill>
@@ -14194,13 +14185,16 @@
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="G9:AK10">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="5" priority="3">
       <formula>TEXT(G9,"aaa")="土"</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="4" priority="4">
+      <formula>TEXT(G9,"aaa")="日"</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G9:AK40">
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>TEXT(G9,"aaa")="日"</formula>
+  <conditionalFormatting sqref="G11:AK40">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>G$11="－"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.23622047244094491" right="3.937007874015748E-2" top="0.55118110236220474" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -25395,7 +25389,7 @@
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="G11:R19 AG11:AK19">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>TEXT(G11,"aaa")="日"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/設備点検表.xlsx
+++ b/設備点検表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kosuk\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B9EEF3-EBDD-4C2B-AC2F-1B3667F8E8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F27DE7C-47B1-4788-BC80-C71E91ECA4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6C56CF13-AF7F-4C1F-982C-EF388A11F51A}"/>
   </bookViews>
@@ -2765,65 +2765,71 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2864,65 +2870,92 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="71" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="72" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="73" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="67" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="74" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2957,45 +2990,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="71" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="72" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="73" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="67" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="74" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準_設備点検表書式" xfId="1" xr:uid="{15F629F0-A893-4DD8-8A94-9D447F97F79C}"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="6">
     <dxf>
       <font>
         <strike val="0"/>
@@ -3031,13 +3031,6 @@
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3383,45 +3376,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:254" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A1" s="155" t="s">
+      <c r="A1" s="121" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="155"/>
+      <c r="B1" s="121"/>
       <c r="C1" s="85"/>
-      <c r="F1" s="156" t="s">
+      <c r="F1" s="122" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
-      <c r="L1" s="156"/>
-      <c r="M1" s="156"/>
-      <c r="N1" s="156"/>
-      <c r="O1" s="156"/>
-      <c r="P1" s="156"/>
-      <c r="Q1" s="156"/>
-      <c r="R1" s="156"/>
-      <c r="S1" s="156"/>
-      <c r="T1" s="156"/>
-      <c r="U1" s="156"/>
-      <c r="V1" s="156"/>
-      <c r="W1" s="156"/>
-      <c r="X1" s="156"/>
-      <c r="Y1" s="156"/>
-      <c r="Z1" s="156"/>
-      <c r="AA1" s="156"/>
-      <c r="AB1" s="156"/>
-      <c r="AC1" s="156"/>
-      <c r="AD1" s="156"/>
-      <c r="AE1" s="156"/>
-      <c r="AF1" s="156"/>
-      <c r="AG1" s="156"/>
-      <c r="AH1" s="156"/>
-      <c r="AI1" s="156"/>
-      <c r="AJ1" s="156"/>
-      <c r="AK1" s="156"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
+      <c r="AC1" s="122"/>
+      <c r="AD1" s="122"/>
+      <c r="AE1" s="122"/>
+      <c r="AF1" s="122"/>
+      <c r="AG1" s="122"/>
+      <c r="AH1" s="122"/>
+      <c r="AI1" s="122"/>
+      <c r="AJ1" s="122"/>
+      <c r="AK1" s="122"/>
       <c r="AN1" s="3"/>
       <c r="AO1" s="3"/>
       <c r="AP1" s="3"/>
@@ -3892,52 +3885,52 @@
       <c r="IT2" s="3"/>
     </row>
     <row r="3" spans="1:254" s="2" customFormat="1" ht="20" customHeight="1" thickBot="1">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="123" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="125"/>
       <c r="E3" s="94"/>
       <c r="G3" s="51"/>
       <c r="H3" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="160" t="s">
+      <c r="K3" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="160"/>
-      <c r="M3" s="160" t="s">
+      <c r="L3" s="126"/>
+      <c r="M3" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="160"/>
-      <c r="O3" s="160"/>
-      <c r="P3" s="160" t="s">
+      <c r="N3" s="126"/>
+      <c r="O3" s="126"/>
+      <c r="P3" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="Q3" s="160"/>
-      <c r="R3" s="160"/>
+      <c r="Q3" s="126"/>
+      <c r="R3" s="126"/>
       <c r="S3" s="3"/>
-      <c r="T3" s="161" t="s">
+      <c r="T3" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="U3" s="162"/>
-      <c r="V3" s="162"/>
-      <c r="W3" s="162"/>
-      <c r="X3" s="162"/>
-      <c r="Y3" s="162"/>
-      <c r="Z3" s="162"/>
-      <c r="AA3" s="162"/>
-      <c r="AB3" s="162"/>
-      <c r="AC3" s="162"/>
-      <c r="AD3" s="162"/>
-      <c r="AE3" s="162"/>
-      <c r="AF3" s="162"/>
-      <c r="AG3" s="162"/>
-      <c r="AH3" s="162"/>
-      <c r="AI3" s="162"/>
-      <c r="AJ3" s="162"/>
-      <c r="AK3" s="163"/>
+      <c r="U3" s="128"/>
+      <c r="V3" s="128"/>
+      <c r="W3" s="128"/>
+      <c r="X3" s="128"/>
+      <c r="Y3" s="128"/>
+      <c r="Z3" s="128"/>
+      <c r="AA3" s="128"/>
+      <c r="AB3" s="128"/>
+      <c r="AC3" s="128"/>
+      <c r="AD3" s="128"/>
+      <c r="AE3" s="128"/>
+      <c r="AF3" s="128"/>
+      <c r="AG3" s="128"/>
+      <c r="AH3" s="128"/>
+      <c r="AI3" s="128"/>
+      <c r="AJ3" s="128"/>
+      <c r="AK3" s="129"/>
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
@@ -4166,47 +4159,47 @@
       <c r="H4" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="160" t="s">
+      <c r="K4" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="160"/>
-      <c r="M4" s="166">
+      <c r="L4" s="126"/>
+      <c r="M4" s="132">
         <v>46113</v>
       </c>
-      <c r="N4" s="166"/>
-      <c r="O4" s="166"/>
-      <c r="P4" s="160" t="s">
+      <c r="N4" s="132"/>
+      <c r="O4" s="132"/>
+      <c r="P4" s="126" t="s">
         <v>50</v>
       </c>
-      <c r="Q4" s="160"/>
-      <c r="R4" s="160"/>
+      <c r="Q4" s="126"/>
+      <c r="R4" s="126"/>
       <c r="S4" s="3"/>
-      <c r="T4" s="152" t="s">
+      <c r="T4" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="U4" s="153"/>
-      <c r="V4" s="153"/>
-      <c r="W4" s="153"/>
-      <c r="X4" s="153"/>
-      <c r="Y4" s="154"/>
-      <c r="Z4" s="152" t="s">
+      <c r="U4" s="134"/>
+      <c r="V4" s="134"/>
+      <c r="W4" s="134"/>
+      <c r="X4" s="134"/>
+      <c r="Y4" s="135"/>
+      <c r="Z4" s="133" t="s">
         <v>6</v>
       </c>
-      <c r="AA4" s="153"/>
-      <c r="AB4" s="153"/>
-      <c r="AC4" s="154"/>
-      <c r="AD4" s="152" t="s">
+      <c r="AA4" s="134"/>
+      <c r="AB4" s="134"/>
+      <c r="AC4" s="135"/>
+      <c r="AD4" s="133" t="s">
         <v>7</v>
       </c>
-      <c r="AE4" s="153"/>
-      <c r="AF4" s="153"/>
-      <c r="AG4" s="154"/>
-      <c r="AH4" s="152" t="s">
+      <c r="AE4" s="134"/>
+      <c r="AF4" s="134"/>
+      <c r="AG4" s="135"/>
+      <c r="AH4" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="AI4" s="153"/>
-      <c r="AJ4" s="153"/>
-      <c r="AK4" s="154"/>
+      <c r="AI4" s="134"/>
+      <c r="AJ4" s="134"/>
+      <c r="AK4" s="135"/>
       <c r="AN4" s="3"/>
       <c r="AO4" s="3"/>
       <c r="AP4" s="3"/>
@@ -4434,16 +4427,16 @@
         <v>23</v>
       </c>
       <c r="S5" s="3"/>
-      <c r="T5" s="167" t="s">
+      <c r="T5" s="136" t="s">
         <v>64</v>
       </c>
-      <c r="U5" s="168"/>
-      <c r="V5" s="168"/>
-      <c r="W5" s="139">
+      <c r="U5" s="137"/>
+      <c r="V5" s="137"/>
+      <c r="W5" s="141">
         <v>7</v>
       </c>
-      <c r="X5" s="140"/>
-      <c r="Y5" s="141"/>
+      <c r="X5" s="142"/>
+      <c r="Y5" s="143"/>
       <c r="Z5" s="11"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
@@ -4452,10 +4445,10 @@
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
       <c r="AG5" s="12"/>
-      <c r="AH5" s="144"/>
-      <c r="AI5" s="145"/>
-      <c r="AJ5" s="145"/>
-      <c r="AK5" s="146"/>
+      <c r="AH5" s="146"/>
+      <c r="AI5" s="147"/>
+      <c r="AJ5" s="147"/>
+      <c r="AK5" s="148"/>
       <c r="AN5" s="3"/>
       <c r="AO5" s="3"/>
       <c r="AP5" s="3"/>
@@ -4687,12 +4680,12 @@
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
-      <c r="T6" s="169"/>
-      <c r="U6" s="168"/>
-      <c r="V6" s="168"/>
-      <c r="W6" s="140"/>
-      <c r="X6" s="140"/>
-      <c r="Y6" s="141"/>
+      <c r="T6" s="138"/>
+      <c r="U6" s="137"/>
+      <c r="V6" s="137"/>
+      <c r="W6" s="142"/>
+      <c r="X6" s="142"/>
+      <c r="Y6" s="143"/>
       <c r="Z6" s="11"/>
       <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
@@ -4701,10 +4694,10 @@
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
       <c r="AG6" s="12"/>
-      <c r="AH6" s="144"/>
-      <c r="AI6" s="145"/>
-      <c r="AJ6" s="145"/>
-      <c r="AK6" s="146"/>
+      <c r="AH6" s="146"/>
+      <c r="AI6" s="147"/>
+      <c r="AJ6" s="147"/>
+      <c r="AK6" s="148"/>
       <c r="AN6" s="3"/>
       <c r="AO6" s="3"/>
       <c r="AP6" s="3"/>
@@ -4936,12 +4929,12 @@
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
-      <c r="T7" s="170"/>
-      <c r="U7" s="171"/>
-      <c r="V7" s="171"/>
-      <c r="W7" s="142"/>
-      <c r="X7" s="142"/>
-      <c r="Y7" s="143"/>
+      <c r="T7" s="139"/>
+      <c r="U7" s="140"/>
+      <c r="V7" s="140"/>
+      <c r="W7" s="144"/>
+      <c r="X7" s="144"/>
+      <c r="Y7" s="145"/>
       <c r="Z7" s="21"/>
       <c r="AA7" s="22"/>
       <c r="AB7" s="22"/>
@@ -4950,10 +4943,10 @@
       <c r="AE7" s="22"/>
       <c r="AF7" s="22"/>
       <c r="AG7" s="23"/>
-      <c r="AH7" s="147"/>
-      <c r="AI7" s="148"/>
-      <c r="AJ7" s="148"/>
-      <c r="AK7" s="149"/>
+      <c r="AH7" s="149"/>
+      <c r="AI7" s="150"/>
+      <c r="AJ7" s="150"/>
+      <c r="AK7" s="151"/>
       <c r="AL7" s="86"/>
       <c r="AN7" s="3"/>
       <c r="AO7" s="3"/>
@@ -5836,8 +5829,8 @@
     </row>
     <row r="10" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A10" s="29"/>
-      <c r="B10" s="150"/>
-      <c r="C10" s="151"/>
+      <c r="B10" s="152"/>
+      <c r="C10" s="153"/>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="31" t="s">
@@ -6185,10 +6178,10 @@
     </row>
     <row r="11" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A11" s="34"/>
-      <c r="B11" s="164" t="s">
+      <c r="B11" s="130" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="165"/>
+      <c r="C11" s="131"/>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
       <c r="F11" s="102" t="s">
@@ -6455,7 +6448,7 @@
       <c r="E12" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="134" t="s">
+      <c r="F12" s="158" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="106"/>
@@ -6717,7 +6710,7 @@
         <v>99</v>
       </c>
       <c r="E13" s="92"/>
-      <c r="F13" s="135"/>
+      <c r="F13" s="119"/>
       <c r="G13" s="106"/>
       <c r="H13" s="106"/>
       <c r="I13" s="106"/>
@@ -6979,7 +6972,7 @@
       <c r="E14" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="135"/>
+      <c r="F14" s="119"/>
       <c r="G14" s="106"/>
       <c r="H14" s="106"/>
       <c r="I14" s="106"/>
@@ -7241,7 +7234,7 @@
       <c r="E15" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="135"/>
+      <c r="F15" s="119"/>
       <c r="G15" s="106"/>
       <c r="H15" s="106"/>
       <c r="I15" s="106"/>
@@ -7503,7 +7496,7 @@
       <c r="E16" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="135"/>
+      <c r="F16" s="119"/>
       <c r="G16" s="106"/>
       <c r="H16" s="106"/>
       <c r="I16" s="106"/>
@@ -7765,7 +7758,7 @@
       <c r="E17" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="135"/>
+      <c r="F17" s="119"/>
       <c r="G17" s="106"/>
       <c r="H17" s="106"/>
       <c r="I17" s="106"/>
@@ -8027,7 +8020,7 @@
       <c r="E18" s="92" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="135"/>
+      <c r="F18" s="119"/>
       <c r="G18" s="106"/>
       <c r="H18" s="106"/>
       <c r="I18" s="106"/>
@@ -8289,7 +8282,7 @@
       <c r="E19" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="F19" s="135"/>
+      <c r="F19" s="119"/>
       <c r="G19" s="106"/>
       <c r="H19" s="106"/>
       <c r="I19" s="106"/>
@@ -8551,7 +8544,7 @@
       <c r="E20" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="F20" s="135"/>
+      <c r="F20" s="119"/>
       <c r="G20" s="106"/>
       <c r="H20" s="106"/>
       <c r="I20" s="106"/>
@@ -8811,7 +8804,7 @@
         <v>100</v>
       </c>
       <c r="E21" s="92"/>
-      <c r="F21" s="135"/>
+      <c r="F21" s="119"/>
       <c r="G21" s="106"/>
       <c r="H21" s="106"/>
       <c r="I21" s="106"/>
@@ -9071,7 +9064,7 @@
         <v>38</v>
       </c>
       <c r="E22" s="92"/>
-      <c r="F22" s="135" t="s">
+      <c r="F22" s="119" t="s">
         <v>135</v>
       </c>
       <c r="G22" s="106"/>
@@ -9335,7 +9328,7 @@
       <c r="E23" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="F23" s="136"/>
+      <c r="F23" s="120"/>
       <c r="G23" s="104"/>
       <c r="H23" s="104"/>
       <c r="I23" s="104"/>
@@ -10103,10 +10096,10 @@
     </row>
     <row r="26" spans="1:254" s="2" customFormat="1" ht="28.25" customHeight="1">
       <c r="A26" s="38"/>
-      <c r="B26" s="137" t="s">
+      <c r="B26" s="154" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="138"/>
+      <c r="C26" s="155"/>
       <c r="D26" s="35"/>
       <c r="E26" s="35"/>
       <c r="F26" s="39"/>
@@ -10361,17 +10354,17 @@
       <c r="A27" s="37">
         <v>1</v>
       </c>
-      <c r="B27" s="130" t="s">
+      <c r="B27" s="156" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="131"/>
+      <c r="C27" s="157"/>
       <c r="D27" s="92" t="s">
         <v>99</v>
       </c>
       <c r="E27" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="134" t="s">
+      <c r="F27" s="158" t="s">
         <v>15</v>
       </c>
       <c r="G27" s="106"/>
@@ -10625,15 +10618,15 @@
       <c r="A28" s="37">
         <v>2</v>
       </c>
-      <c r="B28" s="130" t="s">
+      <c r="B28" s="156" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="131"/>
+      <c r="C28" s="157"/>
       <c r="D28" s="35" t="s">
         <v>77</v>
       </c>
       <c r="E28" s="35"/>
-      <c r="F28" s="135"/>
+      <c r="F28" s="119"/>
       <c r="G28" s="106"/>
       <c r="H28" s="106"/>
       <c r="I28" s="106"/>
@@ -10893,7 +10886,7 @@
         <v>77</v>
       </c>
       <c r="E29" s="35"/>
-      <c r="F29" s="135"/>
+      <c r="F29" s="119"/>
       <c r="G29" s="106"/>
       <c r="H29" s="106"/>
       <c r="I29" s="106"/>
@@ -11155,7 +11148,7 @@
       <c r="E30" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="F30" s="135"/>
+      <c r="F30" s="119"/>
       <c r="G30" s="104"/>
       <c r="H30" s="104"/>
       <c r="I30" s="104"/>
@@ -11407,15 +11400,15 @@
       <c r="A31" s="37">
         <v>5</v>
       </c>
-      <c r="B31" s="130" t="s">
+      <c r="B31" s="156" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="131"/>
+      <c r="C31" s="157"/>
       <c r="D31" s="92" t="s">
         <v>80</v>
       </c>
       <c r="E31" s="35"/>
-      <c r="F31" s="135"/>
+      <c r="F31" s="119"/>
       <c r="G31" s="104"/>
       <c r="H31" s="104"/>
       <c r="I31" s="104"/>
@@ -11675,7 +11668,7 @@
         <v>118</v>
       </c>
       <c r="E32" s="35"/>
-      <c r="F32" s="135"/>
+      <c r="F32" s="119"/>
       <c r="G32" s="104"/>
       <c r="H32" s="104"/>
       <c r="I32" s="104"/>
@@ -11935,7 +11928,7 @@
         <v>118</v>
       </c>
       <c r="E33" s="35"/>
-      <c r="F33" s="135"/>
+      <c r="F33" s="119"/>
       <c r="G33" s="104"/>
       <c r="H33" s="104"/>
       <c r="I33" s="104"/>
@@ -12187,15 +12180,15 @@
       <c r="A34" s="37">
         <v>8</v>
       </c>
-      <c r="B34" s="130" t="s">
+      <c r="B34" s="156" t="s">
         <v>59</v>
       </c>
-      <c r="C34" s="131"/>
+      <c r="C34" s="157"/>
       <c r="D34" s="92" t="s">
         <v>99</v>
       </c>
       <c r="E34" s="40"/>
-      <c r="F34" s="135"/>
+      <c r="F34" s="119"/>
       <c r="G34" s="106"/>
       <c r="H34" s="106"/>
       <c r="I34" s="106"/>
@@ -12447,15 +12440,15 @@
       <c r="A35" s="37">
         <v>9</v>
       </c>
-      <c r="B35" s="130" t="s">
+      <c r="B35" s="156" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="131"/>
+      <c r="C35" s="157"/>
       <c r="D35" s="92" t="s">
         <v>49</v>
       </c>
       <c r="E35" s="40"/>
-      <c r="F35" s="136"/>
+      <c r="F35" s="120"/>
       <c r="G35" s="106"/>
       <c r="H35" s="106"/>
       <c r="I35" s="106"/>
@@ -12705,10 +12698,10 @@
     </row>
     <row r="36" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A36" s="37"/>
-      <c r="B36" s="137" t="s">
+      <c r="B36" s="154" t="s">
         <v>127</v>
       </c>
-      <c r="C36" s="138"/>
+      <c r="C36" s="155"/>
       <c r="D36" s="92"/>
       <c r="E36" s="40"/>
       <c r="F36" s="93"/>
@@ -12961,10 +12954,10 @@
     </row>
     <row r="37" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A37" s="37"/>
-      <c r="B37" s="130" t="s">
+      <c r="B37" s="156" t="s">
         <v>128</v>
       </c>
-      <c r="C37" s="131"/>
+      <c r="C37" s="157"/>
       <c r="D37" s="92"/>
       <c r="E37" s="40"/>
       <c r="F37" s="93"/>
@@ -13217,10 +13210,10 @@
     </row>
     <row r="38" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A38" s="37"/>
-      <c r="B38" s="132" t="s">
+      <c r="B38" s="170" t="s">
         <v>129</v>
       </c>
-      <c r="C38" s="133"/>
+      <c r="C38" s="171"/>
       <c r="D38" s="92"/>
       <c r="E38" s="40"/>
       <c r="F38" s="93"/>
@@ -13473,8 +13466,8 @@
     </row>
     <row r="39" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A39" s="37"/>
-      <c r="B39" s="132"/>
-      <c r="C39" s="133"/>
+      <c r="B39" s="170"/>
+      <c r="C39" s="171"/>
       <c r="D39" s="92"/>
       <c r="E39" s="40"/>
       <c r="F39" s="93"/>
@@ -13727,10 +13720,10 @@
     </row>
     <row r="40" spans="1:254" s="2" customFormat="1" ht="42" customHeight="1" thickBot="1">
       <c r="A40" s="41"/>
-      <c r="B40" s="128" t="s">
+      <c r="B40" s="168" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="129"/>
+      <c r="C40" s="169"/>
       <c r="D40" s="42" t="s">
         <v>16</v>
       </c>
@@ -13994,37 +13987,37 @@
         <v>96</v>
       </c>
       <c r="F41" s="75"/>
-      <c r="G41" s="122"/>
-      <c r="H41" s="122"/>
-      <c r="I41" s="122"/>
-      <c r="J41" s="122"/>
-      <c r="K41" s="122"/>
-      <c r="L41" s="122"/>
-      <c r="M41" s="122"/>
-      <c r="N41" s="122"/>
-      <c r="O41" s="122"/>
-      <c r="P41" s="122"/>
-      <c r="Q41" s="122"/>
-      <c r="R41" s="122"/>
-      <c r="S41" s="122"/>
-      <c r="T41" s="122"/>
-      <c r="U41" s="122"/>
-      <c r="V41" s="122"/>
-      <c r="W41" s="122"/>
-      <c r="X41" s="122"/>
-      <c r="Y41" s="122"/>
-      <c r="Z41" s="122"/>
-      <c r="AA41" s="123"/>
-      <c r="AB41" s="123"/>
-      <c r="AC41" s="123"/>
-      <c r="AD41" s="123"/>
-      <c r="AE41" s="123"/>
-      <c r="AF41" s="123"/>
-      <c r="AG41" s="123"/>
-      <c r="AH41" s="123"/>
-      <c r="AI41" s="123"/>
-      <c r="AJ41" s="123"/>
-      <c r="AK41" s="124"/>
+      <c r="G41" s="162"/>
+      <c r="H41" s="162"/>
+      <c r="I41" s="162"/>
+      <c r="J41" s="162"/>
+      <c r="K41" s="162"/>
+      <c r="L41" s="162"/>
+      <c r="M41" s="162"/>
+      <c r="N41" s="162"/>
+      <c r="O41" s="162"/>
+      <c r="P41" s="162"/>
+      <c r="Q41" s="162"/>
+      <c r="R41" s="162"/>
+      <c r="S41" s="162"/>
+      <c r="T41" s="162"/>
+      <c r="U41" s="162"/>
+      <c r="V41" s="162"/>
+      <c r="W41" s="162"/>
+      <c r="X41" s="162"/>
+      <c r="Y41" s="162"/>
+      <c r="Z41" s="162"/>
+      <c r="AA41" s="163"/>
+      <c r="AB41" s="163"/>
+      <c r="AC41" s="163"/>
+      <c r="AD41" s="163"/>
+      <c r="AE41" s="163"/>
+      <c r="AF41" s="163"/>
+      <c r="AG41" s="163"/>
+      <c r="AH41" s="163"/>
+      <c r="AI41" s="163"/>
+      <c r="AJ41" s="163"/>
+      <c r="AK41" s="164"/>
     </row>
     <row r="42" spans="1:254" ht="23" customHeight="1">
       <c r="A42" s="45"/>
@@ -14035,37 +14028,37 @@
         <v>97</v>
       </c>
       <c r="F42" s="77"/>
-      <c r="G42" s="125"/>
-      <c r="H42" s="125"/>
-      <c r="I42" s="125"/>
-      <c r="J42" s="125"/>
-      <c r="K42" s="125"/>
-      <c r="L42" s="125"/>
-      <c r="M42" s="125"/>
-      <c r="N42" s="125"/>
-      <c r="O42" s="125"/>
-      <c r="P42" s="125"/>
-      <c r="Q42" s="127"/>
-      <c r="R42" s="127"/>
-      <c r="S42" s="127"/>
-      <c r="T42" s="127"/>
-      <c r="U42" s="127"/>
-      <c r="V42" s="127"/>
-      <c r="W42" s="127"/>
-      <c r="X42" s="127"/>
-      <c r="Y42" s="127"/>
-      <c r="Z42" s="127"/>
-      <c r="AA42" s="125"/>
-      <c r="AB42" s="125"/>
-      <c r="AC42" s="125"/>
-      <c r="AD42" s="125"/>
-      <c r="AE42" s="125"/>
-      <c r="AF42" s="125"/>
-      <c r="AG42" s="125"/>
-      <c r="AH42" s="125"/>
-      <c r="AI42" s="125"/>
-      <c r="AJ42" s="125"/>
-      <c r="AK42" s="126"/>
+      <c r="G42" s="165"/>
+      <c r="H42" s="165"/>
+      <c r="I42" s="165"/>
+      <c r="J42" s="165"/>
+      <c r="K42" s="165"/>
+      <c r="L42" s="165"/>
+      <c r="M42" s="165"/>
+      <c r="N42" s="165"/>
+      <c r="O42" s="165"/>
+      <c r="P42" s="165"/>
+      <c r="Q42" s="167"/>
+      <c r="R42" s="167"/>
+      <c r="S42" s="167"/>
+      <c r="T42" s="167"/>
+      <c r="U42" s="167"/>
+      <c r="V42" s="167"/>
+      <c r="W42" s="167"/>
+      <c r="X42" s="167"/>
+      <c r="Y42" s="167"/>
+      <c r="Z42" s="167"/>
+      <c r="AA42" s="165"/>
+      <c r="AB42" s="165"/>
+      <c r="AC42" s="165"/>
+      <c r="AD42" s="165"/>
+      <c r="AE42" s="165"/>
+      <c r="AF42" s="165"/>
+      <c r="AG42" s="165"/>
+      <c r="AH42" s="165"/>
+      <c r="AI42" s="165"/>
+      <c r="AJ42" s="165"/>
+      <c r="AK42" s="166"/>
     </row>
     <row r="43" spans="1:254" ht="23" customHeight="1" thickBot="1">
       <c r="A43" s="49"/>
@@ -14076,37 +14069,37 @@
         <v>98</v>
       </c>
       <c r="F43" s="82"/>
-      <c r="G43" s="119"/>
-      <c r="H43" s="119"/>
-      <c r="I43" s="119"/>
-      <c r="J43" s="119"/>
-      <c r="K43" s="119"/>
-      <c r="L43" s="119"/>
-      <c r="M43" s="119"/>
-      <c r="N43" s="119"/>
-      <c r="O43" s="119"/>
-      <c r="P43" s="119"/>
-      <c r="Q43" s="121"/>
-      <c r="R43" s="121"/>
-      <c r="S43" s="121"/>
-      <c r="T43" s="121"/>
-      <c r="U43" s="121"/>
-      <c r="V43" s="121"/>
-      <c r="W43" s="121"/>
-      <c r="X43" s="121"/>
-      <c r="Y43" s="121"/>
-      <c r="Z43" s="121"/>
-      <c r="AA43" s="119"/>
-      <c r="AB43" s="119"/>
-      <c r="AC43" s="119"/>
-      <c r="AD43" s="119"/>
-      <c r="AE43" s="119"/>
-      <c r="AF43" s="119"/>
-      <c r="AG43" s="119"/>
-      <c r="AH43" s="119"/>
-      <c r="AI43" s="119"/>
-      <c r="AJ43" s="119"/>
-      <c r="AK43" s="120"/>
+      <c r="G43" s="159"/>
+      <c r="H43" s="159"/>
+      <c r="I43" s="159"/>
+      <c r="J43" s="159"/>
+      <c r="K43" s="159"/>
+      <c r="L43" s="159"/>
+      <c r="M43" s="159"/>
+      <c r="N43" s="159"/>
+      <c r="O43" s="159"/>
+      <c r="P43" s="159"/>
+      <c r="Q43" s="161"/>
+      <c r="R43" s="161"/>
+      <c r="S43" s="161"/>
+      <c r="T43" s="161"/>
+      <c r="U43" s="161"/>
+      <c r="V43" s="161"/>
+      <c r="W43" s="161"/>
+      <c r="X43" s="161"/>
+      <c r="Y43" s="161"/>
+      <c r="Z43" s="161"/>
+      <c r="AA43" s="159"/>
+      <c r="AB43" s="159"/>
+      <c r="AC43" s="159"/>
+      <c r="AD43" s="159"/>
+      <c r="AE43" s="159"/>
+      <c r="AF43" s="159"/>
+      <c r="AG43" s="159"/>
+      <c r="AH43" s="159"/>
+      <c r="AI43" s="159"/>
+      <c r="AJ43" s="159"/>
+      <c r="AK43" s="160"/>
     </row>
     <row r="44" spans="1:254">
       <c r="A44" s="52"/>
@@ -14122,6 +14115,50 @@
     </row>
   </sheetData>
   <mergeCells count="60">
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="AA43:AK43"/>
+    <mergeCell ref="Q43:Z43"/>
+    <mergeCell ref="G43:P43"/>
+    <mergeCell ref="Q41:Z41"/>
+    <mergeCell ref="AA41:AK41"/>
+    <mergeCell ref="AA42:AK42"/>
+    <mergeCell ref="Q42:Z42"/>
+    <mergeCell ref="G42:P42"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="G41:P41"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="F12:F21"/>
+    <mergeCell ref="F27:F35"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="W5:Y7"/>
+    <mergeCell ref="AH5:AK7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="Z4:AC4"/>
+    <mergeCell ref="AD4:AG4"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="F22:F23"/>
     <mergeCell ref="A1:B1"/>
@@ -14138,58 +14175,11 @@
     <mergeCell ref="T4:Y4"/>
     <mergeCell ref="AH4:AK4"/>
     <mergeCell ref="T5:V7"/>
-    <mergeCell ref="W5:Y7"/>
-    <mergeCell ref="AH5:AK7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="Z4:AC4"/>
-    <mergeCell ref="AD4:AG4"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="F12:F21"/>
-    <mergeCell ref="F27:F35"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="AA43:AK43"/>
-    <mergeCell ref="Q43:Z43"/>
-    <mergeCell ref="G43:P43"/>
-    <mergeCell ref="Q41:Z41"/>
-    <mergeCell ref="AA41:AK41"/>
-    <mergeCell ref="AA42:AK42"/>
-    <mergeCell ref="Q42:Z42"/>
-    <mergeCell ref="G42:P42"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="G41:P41"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="G9:AK10">
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>TEXT(G9,"aaa")="土"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="4">
-      <formula>TEXT(G9,"aaa")="日"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:AK40">
@@ -14218,40 +14208,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:254" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A1" s="155" t="s">
+      <c r="A1" s="121" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="155"/>
+      <c r="B1" s="121"/>
       <c r="C1" s="85"/>
-      <c r="F1" s="156" t="s">
+      <c r="F1" s="122" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
-      <c r="L1" s="156"/>
-      <c r="M1" s="156"/>
-      <c r="N1" s="156"/>
-      <c r="O1" s="156"/>
-      <c r="P1" s="156"/>
-      <c r="Q1" s="156"/>
-      <c r="R1" s="156"/>
-      <c r="S1" s="156"/>
-      <c r="T1" s="156"/>
-      <c r="U1" s="156"/>
-      <c r="V1" s="156"/>
-      <c r="W1" s="156"/>
-      <c r="X1" s="156"/>
-      <c r="Y1" s="156"/>
-      <c r="Z1" s="156"/>
-      <c r="AA1" s="156"/>
-      <c r="AB1" s="156"/>
-      <c r="AC1" s="156"/>
-      <c r="AD1" s="156"/>
-      <c r="AE1" s="156"/>
-      <c r="AF1" s="156"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
+      <c r="AC1" s="122"/>
+      <c r="AD1" s="122"/>
+      <c r="AE1" s="122"/>
+      <c r="AF1" s="122"/>
       <c r="AI1" s="3"/>
       <c r="AJ1" s="3"/>
       <c r="AK1" s="3"/>
@@ -14717,47 +14707,47 @@
       <c r="IO2" s="3"/>
     </row>
     <row r="3" spans="1:254" s="2" customFormat="1" ht="20" customHeight="1" thickBot="1">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="123" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="125"/>
       <c r="E3" s="94"/>
       <c r="G3" s="51"/>
       <c r="H3" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="160" t="s">
+      <c r="K3" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="160"/>
-      <c r="M3" s="160" t="s">
+      <c r="L3" s="126"/>
+      <c r="M3" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="160"/>
-      <c r="O3" s="160"/>
-      <c r="P3" s="160" t="s">
+      <c r="N3" s="126"/>
+      <c r="O3" s="126"/>
+      <c r="P3" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="Q3" s="160"/>
-      <c r="R3" s="160"/>
+      <c r="Q3" s="126"/>
+      <c r="R3" s="126"/>
       <c r="S3" s="3"/>
-      <c r="T3" s="161" t="s">
+      <c r="T3" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="U3" s="162"/>
-      <c r="V3" s="162"/>
-      <c r="W3" s="162"/>
-      <c r="X3" s="162"/>
-      <c r="Y3" s="162"/>
-      <c r="Z3" s="162"/>
-      <c r="AA3" s="162"/>
-      <c r="AB3" s="162"/>
-      <c r="AC3" s="162"/>
-      <c r="AD3" s="162"/>
-      <c r="AE3" s="162"/>
-      <c r="AF3" s="163"/>
+      <c r="U3" s="128"/>
+      <c r="V3" s="128"/>
+      <c r="W3" s="128"/>
+      <c r="X3" s="128"/>
+      <c r="Y3" s="128"/>
+      <c r="Z3" s="128"/>
+      <c r="AA3" s="128"/>
+      <c r="AB3" s="128"/>
+      <c r="AC3" s="128"/>
+      <c r="AD3" s="128"/>
+      <c r="AE3" s="128"/>
+      <c r="AF3" s="129"/>
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
       <c r="AK3" s="3"/>
@@ -14986,42 +14976,42 @@
       <c r="H4" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="160" t="s">
+      <c r="K4" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="160"/>
-      <c r="M4" s="166">
+      <c r="L4" s="126"/>
+      <c r="M4" s="132">
         <v>46113</v>
       </c>
-      <c r="N4" s="166"/>
-      <c r="O4" s="166"/>
-      <c r="P4" s="160" t="s">
+      <c r="N4" s="132"/>
+      <c r="O4" s="132"/>
+      <c r="P4" s="126" t="s">
         <v>50</v>
       </c>
-      <c r="Q4" s="160"/>
-      <c r="R4" s="160"/>
+      <c r="Q4" s="126"/>
+      <c r="R4" s="126"/>
       <c r="S4" s="3"/>
-      <c r="T4" s="152" t="s">
+      <c r="T4" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="U4" s="153"/>
-      <c r="V4" s="153"/>
-      <c r="W4" s="154"/>
-      <c r="X4" s="152" t="s">
+      <c r="U4" s="134"/>
+      <c r="V4" s="134"/>
+      <c r="W4" s="135"/>
+      <c r="X4" s="133" t="s">
         <v>6</v>
       </c>
-      <c r="Y4" s="153"/>
-      <c r="Z4" s="154"/>
-      <c r="AA4" s="152" t="s">
+      <c r="Y4" s="134"/>
+      <c r="Z4" s="135"/>
+      <c r="AA4" s="133" t="s">
         <v>7</v>
       </c>
-      <c r="AB4" s="153"/>
-      <c r="AC4" s="154"/>
-      <c r="AD4" s="152" t="s">
+      <c r="AB4" s="134"/>
+      <c r="AC4" s="135"/>
+      <c r="AD4" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="AE4" s="153"/>
-      <c r="AF4" s="154"/>
+      <c r="AE4" s="134"/>
+      <c r="AF4" s="135"/>
       <c r="AI4" s="3"/>
       <c r="AJ4" s="3"/>
       <c r="AK4" s="3"/>
@@ -15249,21 +15239,21 @@
         <v>23</v>
       </c>
       <c r="S5" s="3"/>
-      <c r="T5" s="172" t="s">
+      <c r="T5" s="183" t="s">
         <v>64</v>
       </c>
-      <c r="U5" s="173"/>
-      <c r="V5" s="173"/>
-      <c r="W5" s="174"/>
+      <c r="U5" s="184"/>
+      <c r="V5" s="184"/>
+      <c r="W5" s="185"/>
       <c r="X5" s="11"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="12"/>
       <c r="AA5" s="11"/>
       <c r="AB5" s="3"/>
       <c r="AC5" s="12"/>
-      <c r="AD5" s="144"/>
-      <c r="AE5" s="145"/>
-      <c r="AF5" s="146"/>
+      <c r="AD5" s="146"/>
+      <c r="AE5" s="147"/>
+      <c r="AF5" s="148"/>
       <c r="AI5" s="3"/>
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3"/>
@@ -15495,19 +15485,19 @@
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
-      <c r="T6" s="172"/>
-      <c r="U6" s="173"/>
-      <c r="V6" s="173"/>
-      <c r="W6" s="174"/>
+      <c r="T6" s="183"/>
+      <c r="U6" s="184"/>
+      <c r="V6" s="184"/>
+      <c r="W6" s="185"/>
       <c r="X6" s="11"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="12"/>
       <c r="AA6" s="11"/>
       <c r="AB6" s="3"/>
       <c r="AC6" s="12"/>
-      <c r="AD6" s="144"/>
-      <c r="AE6" s="145"/>
-      <c r="AF6" s="146"/>
+      <c r="AD6" s="146"/>
+      <c r="AE6" s="147"/>
+      <c r="AF6" s="148"/>
       <c r="AI6" s="3"/>
       <c r="AJ6" s="3"/>
       <c r="AK6" s="3"/>
@@ -15739,19 +15729,19 @@
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
-      <c r="T7" s="175"/>
-      <c r="U7" s="176"/>
-      <c r="V7" s="176"/>
-      <c r="W7" s="177"/>
+      <c r="T7" s="186"/>
+      <c r="U7" s="187"/>
+      <c r="V7" s="187"/>
+      <c r="W7" s="188"/>
       <c r="X7" s="21"/>
       <c r="Y7" s="22"/>
       <c r="Z7" s="23"/>
       <c r="AA7" s="21"/>
       <c r="AB7" s="22"/>
       <c r="AC7" s="23"/>
-      <c r="AD7" s="147"/>
-      <c r="AE7" s="148"/>
-      <c r="AF7" s="149"/>
+      <c r="AD7" s="149"/>
+      <c r="AE7" s="150"/>
+      <c r="AF7" s="151"/>
       <c r="AG7" s="86"/>
       <c r="AI7" s="3"/>
       <c r="AJ7" s="3"/>
@@ -16268,22 +16258,22 @@
       <c r="R9" s="97" t="s">
         <v>76</v>
       </c>
-      <c r="S9" s="191" t="s">
+      <c r="S9" s="176" t="s">
         <v>78</v>
       </c>
-      <c r="T9" s="192"/>
-      <c r="U9" s="192"/>
-      <c r="V9" s="192"/>
-      <c r="W9" s="192"/>
-      <c r="X9" s="192"/>
-      <c r="Y9" s="192"/>
-      <c r="Z9" s="192"/>
-      <c r="AA9" s="192"/>
-      <c r="AB9" s="192"/>
-      <c r="AC9" s="192"/>
-      <c r="AD9" s="192"/>
-      <c r="AE9" s="192"/>
-      <c r="AF9" s="193"/>
+      <c r="T9" s="177"/>
+      <c r="U9" s="177"/>
+      <c r="V9" s="177"/>
+      <c r="W9" s="177"/>
+      <c r="X9" s="177"/>
+      <c r="Y9" s="177"/>
+      <c r="Z9" s="177"/>
+      <c r="AA9" s="177"/>
+      <c r="AB9" s="177"/>
+      <c r="AC9" s="177"/>
+      <c r="AD9" s="177"/>
+      <c r="AE9" s="177"/>
+      <c r="AF9" s="178"/>
       <c r="AI9" s="3"/>
       <c r="AJ9" s="3"/>
       <c r="AK9" s="3"/>
@@ -16502,8 +16492,8 @@
     </row>
     <row r="10" spans="1:254" s="2" customFormat="1" ht="23" hidden="1" customHeight="1">
       <c r="A10" s="29"/>
-      <c r="B10" s="150"/>
-      <c r="C10" s="151"/>
+      <c r="B10" s="152"/>
+      <c r="C10" s="153"/>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="31"/>
@@ -16829,10 +16819,10 @@
     </row>
     <row r="11" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A11" s="37"/>
-      <c r="B11" s="137" t="s">
+      <c r="B11" s="154" t="s">
         <v>105</v>
       </c>
-      <c r="C11" s="138"/>
+      <c r="C11" s="155"/>
       <c r="D11" s="92"/>
       <c r="E11" s="40"/>
       <c r="F11" s="93"/>
@@ -16848,20 +16838,20 @@
       <c r="P11" s="69"/>
       <c r="Q11" s="69"/>
       <c r="R11" s="69"/>
-      <c r="S11" s="180"/>
-      <c r="T11" s="181"/>
-      <c r="U11" s="181"/>
-      <c r="V11" s="181"/>
-      <c r="W11" s="181"/>
-      <c r="X11" s="181"/>
-      <c r="Y11" s="181"/>
-      <c r="Z11" s="181"/>
-      <c r="AA11" s="181"/>
-      <c r="AB11" s="181"/>
-      <c r="AC11" s="181"/>
-      <c r="AD11" s="181"/>
-      <c r="AE11" s="181"/>
-      <c r="AF11" s="182"/>
+      <c r="S11" s="191"/>
+      <c r="T11" s="192"/>
+      <c r="U11" s="192"/>
+      <c r="V11" s="192"/>
+      <c r="W11" s="192"/>
+      <c r="X11" s="192"/>
+      <c r="Y11" s="192"/>
+      <c r="Z11" s="192"/>
+      <c r="AA11" s="192"/>
+      <c r="AB11" s="192"/>
+      <c r="AC11" s="192"/>
+      <c r="AD11" s="192"/>
+      <c r="AE11" s="192"/>
+      <c r="AF11" s="193"/>
       <c r="AG11" s="69"/>
       <c r="AH11" s="69"/>
       <c r="AI11" s="69"/>
@@ -17087,10 +17077,10 @@
       <c r="A12" s="37">
         <v>1</v>
       </c>
-      <c r="B12" s="132" t="s">
+      <c r="B12" s="170" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="133"/>
+      <c r="C12" s="171"/>
       <c r="D12" s="92" t="s">
         <v>108</v>
       </c>
@@ -17108,20 +17098,20 @@
       <c r="P12" s="69"/>
       <c r="Q12" s="69"/>
       <c r="R12" s="69"/>
-      <c r="S12" s="183"/>
-      <c r="T12" s="184"/>
-      <c r="U12" s="184"/>
-      <c r="V12" s="184"/>
-      <c r="W12" s="184"/>
-      <c r="X12" s="184"/>
-      <c r="Y12" s="184"/>
-      <c r="Z12" s="184"/>
-      <c r="AA12" s="184"/>
-      <c r="AB12" s="184"/>
-      <c r="AC12" s="184"/>
-      <c r="AD12" s="184"/>
-      <c r="AE12" s="184"/>
-      <c r="AF12" s="185"/>
+      <c r="S12" s="172"/>
+      <c r="T12" s="173"/>
+      <c r="U12" s="173"/>
+      <c r="V12" s="173"/>
+      <c r="W12" s="173"/>
+      <c r="X12" s="173"/>
+      <c r="Y12" s="173"/>
+      <c r="Z12" s="173"/>
+      <c r="AA12" s="173"/>
+      <c r="AB12" s="173"/>
+      <c r="AC12" s="173"/>
+      <c r="AD12" s="173"/>
+      <c r="AE12" s="173"/>
+      <c r="AF12" s="174"/>
       <c r="AG12" s="69"/>
       <c r="AH12" s="69"/>
       <c r="AI12" s="69"/>
@@ -17347,10 +17337,10 @@
       <c r="A13" s="37">
         <v>2</v>
       </c>
-      <c r="B13" s="132" t="s">
+      <c r="B13" s="170" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="133"/>
+      <c r="C13" s="171"/>
       <c r="D13" s="92" t="s">
         <v>107</v>
       </c>
@@ -17368,20 +17358,20 @@
       <c r="P13" s="69"/>
       <c r="Q13" s="69"/>
       <c r="R13" s="69"/>
-      <c r="S13" s="183"/>
-      <c r="T13" s="184"/>
-      <c r="U13" s="184"/>
-      <c r="V13" s="184"/>
-      <c r="W13" s="184"/>
-      <c r="X13" s="184"/>
-      <c r="Y13" s="184"/>
-      <c r="Z13" s="184"/>
-      <c r="AA13" s="184"/>
-      <c r="AB13" s="184"/>
-      <c r="AC13" s="184"/>
-      <c r="AD13" s="184"/>
-      <c r="AE13" s="184"/>
-      <c r="AF13" s="185"/>
+      <c r="S13" s="172"/>
+      <c r="T13" s="173"/>
+      <c r="U13" s="173"/>
+      <c r="V13" s="173"/>
+      <c r="W13" s="173"/>
+      <c r="X13" s="173"/>
+      <c r="Y13" s="173"/>
+      <c r="Z13" s="173"/>
+      <c r="AA13" s="173"/>
+      <c r="AB13" s="173"/>
+      <c r="AC13" s="173"/>
+      <c r="AD13" s="173"/>
+      <c r="AE13" s="173"/>
+      <c r="AF13" s="174"/>
       <c r="AG13" s="69"/>
       <c r="AH13" s="69"/>
       <c r="AI13" s="69"/>
@@ -17607,10 +17597,10 @@
       <c r="A14" s="37">
         <v>3</v>
       </c>
-      <c r="B14" s="132" t="s">
+      <c r="B14" s="170" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="133"/>
+      <c r="C14" s="171"/>
       <c r="D14" s="92" t="s">
         <v>107</v>
       </c>
@@ -17628,20 +17618,20 @@
       <c r="P14" s="69"/>
       <c r="Q14" s="69"/>
       <c r="R14" s="69"/>
-      <c r="S14" s="183"/>
-      <c r="T14" s="184"/>
-      <c r="U14" s="184"/>
-      <c r="V14" s="184"/>
-      <c r="W14" s="184"/>
-      <c r="X14" s="184"/>
-      <c r="Y14" s="184"/>
-      <c r="Z14" s="184"/>
-      <c r="AA14" s="184"/>
-      <c r="AB14" s="184"/>
-      <c r="AC14" s="184"/>
-      <c r="AD14" s="184"/>
-      <c r="AE14" s="184"/>
-      <c r="AF14" s="185"/>
+      <c r="S14" s="172"/>
+      <c r="T14" s="173"/>
+      <c r="U14" s="173"/>
+      <c r="V14" s="173"/>
+      <c r="W14" s="173"/>
+      <c r="X14" s="173"/>
+      <c r="Y14" s="173"/>
+      <c r="Z14" s="173"/>
+      <c r="AA14" s="173"/>
+      <c r="AB14" s="173"/>
+      <c r="AC14" s="173"/>
+      <c r="AD14" s="173"/>
+      <c r="AE14" s="173"/>
+      <c r="AF14" s="174"/>
       <c r="AG14" s="69"/>
       <c r="AH14" s="69"/>
       <c r="AI14" s="69"/>
@@ -17867,10 +17857,10 @@
       <c r="A15" s="37">
         <v>4</v>
       </c>
-      <c r="B15" s="132" t="s">
+      <c r="B15" s="170" t="s">
         <v>82</v>
       </c>
-      <c r="C15" s="133"/>
+      <c r="C15" s="171"/>
       <c r="D15" s="92" t="s">
         <v>108</v>
       </c>
@@ -17888,20 +17878,20 @@
       <c r="P15" s="69"/>
       <c r="Q15" s="69"/>
       <c r="R15" s="69"/>
-      <c r="S15" s="183"/>
-      <c r="T15" s="184"/>
-      <c r="U15" s="184"/>
-      <c r="V15" s="184"/>
-      <c r="W15" s="184"/>
-      <c r="X15" s="184"/>
-      <c r="Y15" s="184"/>
-      <c r="Z15" s="184"/>
-      <c r="AA15" s="184"/>
-      <c r="AB15" s="184"/>
-      <c r="AC15" s="184"/>
-      <c r="AD15" s="184"/>
-      <c r="AE15" s="184"/>
-      <c r="AF15" s="185"/>
+      <c r="S15" s="172"/>
+      <c r="T15" s="173"/>
+      <c r="U15" s="173"/>
+      <c r="V15" s="173"/>
+      <c r="W15" s="173"/>
+      <c r="X15" s="173"/>
+      <c r="Y15" s="173"/>
+      <c r="Z15" s="173"/>
+      <c r="AA15" s="173"/>
+      <c r="AB15" s="173"/>
+      <c r="AC15" s="173"/>
+      <c r="AD15" s="173"/>
+      <c r="AE15" s="173"/>
+      <c r="AF15" s="174"/>
       <c r="AG15" s="69"/>
       <c r="AH15" s="69"/>
       <c r="AI15" s="69"/>
@@ -18127,10 +18117,10 @@
       <c r="A16" s="37">
         <v>5</v>
       </c>
-      <c r="B16" s="132" t="s">
+      <c r="B16" s="170" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="133"/>
+      <c r="C16" s="171"/>
       <c r="D16" s="92" t="s">
         <v>108</v>
       </c>
@@ -18148,20 +18138,20 @@
       <c r="P16" s="69"/>
       <c r="Q16" s="69"/>
       <c r="R16" s="69"/>
-      <c r="S16" s="183"/>
-      <c r="T16" s="184"/>
-      <c r="U16" s="184"/>
-      <c r="V16" s="184"/>
-      <c r="W16" s="184"/>
-      <c r="X16" s="184"/>
-      <c r="Y16" s="184"/>
-      <c r="Z16" s="184"/>
-      <c r="AA16" s="184"/>
-      <c r="AB16" s="184"/>
-      <c r="AC16" s="184"/>
-      <c r="AD16" s="184"/>
-      <c r="AE16" s="184"/>
-      <c r="AF16" s="185"/>
+      <c r="S16" s="172"/>
+      <c r="T16" s="173"/>
+      <c r="U16" s="173"/>
+      <c r="V16" s="173"/>
+      <c r="W16" s="173"/>
+      <c r="X16" s="173"/>
+      <c r="Y16" s="173"/>
+      <c r="Z16" s="173"/>
+      <c r="AA16" s="173"/>
+      <c r="AB16" s="173"/>
+      <c r="AC16" s="173"/>
+      <c r="AD16" s="173"/>
+      <c r="AE16" s="173"/>
+      <c r="AF16" s="174"/>
       <c r="AG16" s="69"/>
       <c r="AH16" s="69"/>
       <c r="AI16" s="69"/>
@@ -18387,10 +18377,10 @@
       <c r="A17" s="37">
         <v>6</v>
       </c>
-      <c r="B17" s="132" t="s">
+      <c r="B17" s="170" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="133"/>
+      <c r="C17" s="171"/>
       <c r="D17" s="92" t="s">
         <v>108</v>
       </c>
@@ -18408,20 +18398,20 @@
       <c r="P17" s="69"/>
       <c r="Q17" s="69"/>
       <c r="R17" s="69"/>
-      <c r="S17" s="183"/>
-      <c r="T17" s="184"/>
-      <c r="U17" s="184"/>
-      <c r="V17" s="184"/>
-      <c r="W17" s="184"/>
-      <c r="X17" s="184"/>
-      <c r="Y17" s="184"/>
-      <c r="Z17" s="184"/>
-      <c r="AA17" s="184"/>
-      <c r="AB17" s="184"/>
-      <c r="AC17" s="184"/>
-      <c r="AD17" s="184"/>
-      <c r="AE17" s="184"/>
-      <c r="AF17" s="185"/>
+      <c r="S17" s="172"/>
+      <c r="T17" s="173"/>
+      <c r="U17" s="173"/>
+      <c r="V17" s="173"/>
+      <c r="W17" s="173"/>
+      <c r="X17" s="173"/>
+      <c r="Y17" s="173"/>
+      <c r="Z17" s="173"/>
+      <c r="AA17" s="173"/>
+      <c r="AB17" s="173"/>
+      <c r="AC17" s="173"/>
+      <c r="AD17" s="173"/>
+      <c r="AE17" s="173"/>
+      <c r="AF17" s="174"/>
       <c r="AG17" s="69"/>
       <c r="AH17" s="69"/>
       <c r="AI17" s="69"/>
@@ -18647,10 +18637,10 @@
       <c r="A18" s="37">
         <v>7</v>
       </c>
-      <c r="B18" s="132" t="s">
+      <c r="B18" s="170" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="133"/>
+      <c r="C18" s="171"/>
       <c r="D18" s="92" t="s">
         <v>108</v>
       </c>
@@ -18668,20 +18658,20 @@
       <c r="P18" s="69"/>
       <c r="Q18" s="69"/>
       <c r="R18" s="69"/>
-      <c r="S18" s="183"/>
-      <c r="T18" s="184"/>
-      <c r="U18" s="184"/>
-      <c r="V18" s="184"/>
-      <c r="W18" s="184"/>
-      <c r="X18" s="184"/>
-      <c r="Y18" s="184"/>
-      <c r="Z18" s="184"/>
-      <c r="AA18" s="184"/>
-      <c r="AB18" s="184"/>
-      <c r="AC18" s="184"/>
-      <c r="AD18" s="184"/>
-      <c r="AE18" s="184"/>
-      <c r="AF18" s="185"/>
+      <c r="S18" s="172"/>
+      <c r="T18" s="173"/>
+      <c r="U18" s="173"/>
+      <c r="V18" s="173"/>
+      <c r="W18" s="173"/>
+      <c r="X18" s="173"/>
+      <c r="Y18" s="173"/>
+      <c r="Z18" s="173"/>
+      <c r="AA18" s="173"/>
+      <c r="AB18" s="173"/>
+      <c r="AC18" s="173"/>
+      <c r="AD18" s="173"/>
+      <c r="AE18" s="173"/>
+      <c r="AF18" s="174"/>
       <c r="AG18" s="69"/>
       <c r="AH18" s="69"/>
       <c r="AI18" s="69"/>
@@ -18907,10 +18897,10 @@
       <c r="A19" s="37">
         <v>8</v>
       </c>
-      <c r="B19" s="132" t="s">
+      <c r="B19" s="170" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="133"/>
+      <c r="C19" s="171"/>
       <c r="D19" s="92" t="s">
         <v>108</v>
       </c>
@@ -18928,20 +18918,20 @@
       <c r="P19" s="69"/>
       <c r="Q19" s="69"/>
       <c r="R19" s="69"/>
-      <c r="S19" s="183"/>
-      <c r="T19" s="184"/>
-      <c r="U19" s="184"/>
-      <c r="V19" s="184"/>
-      <c r="W19" s="184"/>
-      <c r="X19" s="184"/>
-      <c r="Y19" s="184"/>
-      <c r="Z19" s="184"/>
-      <c r="AA19" s="184"/>
-      <c r="AB19" s="184"/>
-      <c r="AC19" s="184"/>
-      <c r="AD19" s="184"/>
-      <c r="AE19" s="184"/>
-      <c r="AF19" s="185"/>
+      <c r="S19" s="172"/>
+      <c r="T19" s="173"/>
+      <c r="U19" s="173"/>
+      <c r="V19" s="173"/>
+      <c r="W19" s="173"/>
+      <c r="X19" s="173"/>
+      <c r="Y19" s="173"/>
+      <c r="Z19" s="173"/>
+      <c r="AA19" s="173"/>
+      <c r="AB19" s="173"/>
+      <c r="AC19" s="173"/>
+      <c r="AD19" s="173"/>
+      <c r="AE19" s="173"/>
+      <c r="AF19" s="174"/>
       <c r="AG19" s="69"/>
       <c r="AH19" s="69"/>
       <c r="AI19" s="69"/>
@@ -19165,10 +19155,10 @@
     </row>
     <row r="20" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A20" s="34"/>
-      <c r="B20" s="178" t="s">
+      <c r="B20" s="189" t="s">
         <v>120</v>
       </c>
-      <c r="C20" s="179"/>
+      <c r="C20" s="190"/>
       <c r="D20" s="35"/>
       <c r="E20" s="35"/>
       <c r="F20" s="36"/>
@@ -19184,20 +19174,20 @@
       <c r="P20" s="68"/>
       <c r="Q20" s="68"/>
       <c r="R20" s="68"/>
-      <c r="S20" s="183"/>
-      <c r="T20" s="184"/>
-      <c r="U20" s="184"/>
-      <c r="V20" s="184"/>
-      <c r="W20" s="184"/>
-      <c r="X20" s="184"/>
-      <c r="Y20" s="184"/>
-      <c r="Z20" s="184"/>
-      <c r="AA20" s="184"/>
-      <c r="AB20" s="184"/>
-      <c r="AC20" s="184"/>
-      <c r="AD20" s="184"/>
-      <c r="AE20" s="184"/>
-      <c r="AF20" s="185"/>
+      <c r="S20" s="172"/>
+      <c r="T20" s="173"/>
+      <c r="U20" s="173"/>
+      <c r="V20" s="173"/>
+      <c r="W20" s="173"/>
+      <c r="X20" s="173"/>
+      <c r="Y20" s="173"/>
+      <c r="Z20" s="173"/>
+      <c r="AA20" s="173"/>
+      <c r="AB20" s="173"/>
+      <c r="AC20" s="173"/>
+      <c r="AD20" s="173"/>
+      <c r="AE20" s="173"/>
+      <c r="AF20" s="174"/>
       <c r="AI20" s="3"/>
       <c r="AJ20" s="3"/>
       <c r="AK20" s="3"/>
@@ -19439,20 +19429,20 @@
       <c r="P21" s="69"/>
       <c r="Q21" s="69"/>
       <c r="R21" s="69"/>
-      <c r="S21" s="183"/>
-      <c r="T21" s="184"/>
-      <c r="U21" s="184"/>
-      <c r="V21" s="184"/>
-      <c r="W21" s="184"/>
-      <c r="X21" s="184"/>
-      <c r="Y21" s="184"/>
-      <c r="Z21" s="184"/>
-      <c r="AA21" s="184"/>
-      <c r="AB21" s="184"/>
-      <c r="AC21" s="184"/>
-      <c r="AD21" s="184"/>
-      <c r="AE21" s="184"/>
-      <c r="AF21" s="185"/>
+      <c r="S21" s="172"/>
+      <c r="T21" s="173"/>
+      <c r="U21" s="173"/>
+      <c r="V21" s="173"/>
+      <c r="W21" s="173"/>
+      <c r="X21" s="173"/>
+      <c r="Y21" s="173"/>
+      <c r="Z21" s="173"/>
+      <c r="AA21" s="173"/>
+      <c r="AB21" s="173"/>
+      <c r="AC21" s="173"/>
+      <c r="AD21" s="173"/>
+      <c r="AE21" s="173"/>
+      <c r="AF21" s="174"/>
       <c r="AI21" s="3"/>
       <c r="AJ21" s="3"/>
       <c r="AK21" s="3"/>
@@ -19694,20 +19684,20 @@
       <c r="P22" s="69"/>
       <c r="Q22" s="69"/>
       <c r="R22" s="69"/>
-      <c r="S22" s="183"/>
-      <c r="T22" s="184"/>
-      <c r="U22" s="184"/>
-      <c r="V22" s="184"/>
-      <c r="W22" s="184"/>
-      <c r="X22" s="184"/>
-      <c r="Y22" s="184"/>
-      <c r="Z22" s="184"/>
-      <c r="AA22" s="184"/>
-      <c r="AB22" s="184"/>
-      <c r="AC22" s="184"/>
-      <c r="AD22" s="184"/>
-      <c r="AE22" s="184"/>
-      <c r="AF22" s="185"/>
+      <c r="S22" s="172"/>
+      <c r="T22" s="173"/>
+      <c r="U22" s="173"/>
+      <c r="V22" s="173"/>
+      <c r="W22" s="173"/>
+      <c r="X22" s="173"/>
+      <c r="Y22" s="173"/>
+      <c r="Z22" s="173"/>
+      <c r="AA22" s="173"/>
+      <c r="AB22" s="173"/>
+      <c r="AC22" s="173"/>
+      <c r="AD22" s="173"/>
+      <c r="AE22" s="173"/>
+      <c r="AF22" s="174"/>
       <c r="AI22" s="3"/>
       <c r="AJ22" s="3"/>
       <c r="AK22" s="3"/>
@@ -19928,10 +19918,10 @@
       <c r="A23" s="101" t="s">
         <v>111</v>
       </c>
-      <c r="B23" s="186" t="s">
+      <c r="B23" s="181" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="187"/>
+      <c r="C23" s="182"/>
       <c r="D23" s="92" t="s">
         <v>110</v>
       </c>
@@ -19951,20 +19941,20 @@
       <c r="P23" s="69"/>
       <c r="Q23" s="69"/>
       <c r="R23" s="69"/>
-      <c r="S23" s="183"/>
-      <c r="T23" s="184"/>
-      <c r="U23" s="184"/>
-      <c r="V23" s="184"/>
-      <c r="W23" s="184"/>
-      <c r="X23" s="184"/>
-      <c r="Y23" s="184"/>
-      <c r="Z23" s="184"/>
-      <c r="AA23" s="184"/>
-      <c r="AB23" s="184"/>
-      <c r="AC23" s="184"/>
-      <c r="AD23" s="184"/>
-      <c r="AE23" s="184"/>
-      <c r="AF23" s="185"/>
+      <c r="S23" s="172"/>
+      <c r="T23" s="173"/>
+      <c r="U23" s="173"/>
+      <c r="V23" s="173"/>
+      <c r="W23" s="173"/>
+      <c r="X23" s="173"/>
+      <c r="Y23" s="173"/>
+      <c r="Z23" s="173"/>
+      <c r="AA23" s="173"/>
+      <c r="AB23" s="173"/>
+      <c r="AC23" s="173"/>
+      <c r="AD23" s="173"/>
+      <c r="AE23" s="173"/>
+      <c r="AF23" s="174"/>
       <c r="AI23" s="3"/>
       <c r="AJ23" s="3"/>
       <c r="AK23" s="3"/>
@@ -20208,20 +20198,20 @@
       <c r="P24" s="69"/>
       <c r="Q24" s="69"/>
       <c r="R24" s="69"/>
-      <c r="S24" s="183"/>
-      <c r="T24" s="184"/>
-      <c r="U24" s="184"/>
-      <c r="V24" s="184"/>
-      <c r="W24" s="184"/>
-      <c r="X24" s="184"/>
-      <c r="Y24" s="184"/>
-      <c r="Z24" s="184"/>
-      <c r="AA24" s="184"/>
-      <c r="AB24" s="184"/>
-      <c r="AC24" s="184"/>
-      <c r="AD24" s="184"/>
-      <c r="AE24" s="184"/>
-      <c r="AF24" s="185"/>
+      <c r="S24" s="172"/>
+      <c r="T24" s="173"/>
+      <c r="U24" s="173"/>
+      <c r="V24" s="173"/>
+      <c r="W24" s="173"/>
+      <c r="X24" s="173"/>
+      <c r="Y24" s="173"/>
+      <c r="Z24" s="173"/>
+      <c r="AA24" s="173"/>
+      <c r="AB24" s="173"/>
+      <c r="AC24" s="173"/>
+      <c r="AD24" s="173"/>
+      <c r="AE24" s="173"/>
+      <c r="AF24" s="174"/>
       <c r="AI24" s="3"/>
       <c r="AJ24" s="3"/>
       <c r="AK24" s="3"/>
@@ -20463,20 +20453,20 @@
       <c r="P25" s="69"/>
       <c r="Q25" s="69"/>
       <c r="R25" s="69"/>
-      <c r="S25" s="183"/>
-      <c r="T25" s="184"/>
-      <c r="U25" s="184"/>
-      <c r="V25" s="184"/>
-      <c r="W25" s="184"/>
-      <c r="X25" s="184"/>
-      <c r="Y25" s="184"/>
-      <c r="Z25" s="184"/>
-      <c r="AA25" s="184"/>
-      <c r="AB25" s="184"/>
-      <c r="AC25" s="184"/>
-      <c r="AD25" s="184"/>
-      <c r="AE25" s="184"/>
-      <c r="AF25" s="185"/>
+      <c r="S25" s="172"/>
+      <c r="T25" s="173"/>
+      <c r="U25" s="173"/>
+      <c r="V25" s="173"/>
+      <c r="W25" s="173"/>
+      <c r="X25" s="173"/>
+      <c r="Y25" s="173"/>
+      <c r="Z25" s="173"/>
+      <c r="AA25" s="173"/>
+      <c r="AB25" s="173"/>
+      <c r="AC25" s="173"/>
+      <c r="AD25" s="173"/>
+      <c r="AE25" s="173"/>
+      <c r="AF25" s="174"/>
       <c r="AI25" s="3"/>
       <c r="AJ25" s="3"/>
       <c r="AK25" s="3"/>
@@ -20718,20 +20708,20 @@
       <c r="P26" s="69"/>
       <c r="Q26" s="69"/>
       <c r="R26" s="69"/>
-      <c r="S26" s="183"/>
-      <c r="T26" s="184"/>
-      <c r="U26" s="184"/>
-      <c r="V26" s="184"/>
-      <c r="W26" s="184"/>
-      <c r="X26" s="184"/>
-      <c r="Y26" s="184"/>
-      <c r="Z26" s="184"/>
-      <c r="AA26" s="184"/>
-      <c r="AB26" s="184"/>
-      <c r="AC26" s="184"/>
-      <c r="AD26" s="184"/>
-      <c r="AE26" s="184"/>
-      <c r="AF26" s="185"/>
+      <c r="S26" s="172"/>
+      <c r="T26" s="173"/>
+      <c r="U26" s="173"/>
+      <c r="V26" s="173"/>
+      <c r="W26" s="173"/>
+      <c r="X26" s="173"/>
+      <c r="Y26" s="173"/>
+      <c r="Z26" s="173"/>
+      <c r="AA26" s="173"/>
+      <c r="AB26" s="173"/>
+      <c r="AC26" s="173"/>
+      <c r="AD26" s="173"/>
+      <c r="AE26" s="173"/>
+      <c r="AF26" s="174"/>
       <c r="AI26" s="3"/>
       <c r="AJ26" s="3"/>
       <c r="AK26" s="3"/>
@@ -20973,20 +20963,20 @@
       <c r="P27" s="69"/>
       <c r="Q27" s="69"/>
       <c r="R27" s="69"/>
-      <c r="S27" s="183"/>
-      <c r="T27" s="184"/>
-      <c r="U27" s="184"/>
-      <c r="V27" s="184"/>
-      <c r="W27" s="184"/>
-      <c r="X27" s="184"/>
-      <c r="Y27" s="184"/>
-      <c r="Z27" s="184"/>
-      <c r="AA27" s="184"/>
-      <c r="AB27" s="184"/>
-      <c r="AC27" s="184"/>
-      <c r="AD27" s="184"/>
-      <c r="AE27" s="184"/>
-      <c r="AF27" s="185"/>
+      <c r="S27" s="172"/>
+      <c r="T27" s="173"/>
+      <c r="U27" s="173"/>
+      <c r="V27" s="173"/>
+      <c r="W27" s="173"/>
+      <c r="X27" s="173"/>
+      <c r="Y27" s="173"/>
+      <c r="Z27" s="173"/>
+      <c r="AA27" s="173"/>
+      <c r="AB27" s="173"/>
+      <c r="AC27" s="173"/>
+      <c r="AD27" s="173"/>
+      <c r="AE27" s="173"/>
+      <c r="AF27" s="174"/>
       <c r="AI27" s="3"/>
       <c r="AJ27" s="3"/>
       <c r="AK27" s="3"/>
@@ -21228,20 +21218,20 @@
       <c r="P28" s="69"/>
       <c r="Q28" s="69"/>
       <c r="R28" s="69"/>
-      <c r="S28" s="183"/>
-      <c r="T28" s="184"/>
-      <c r="U28" s="184"/>
-      <c r="V28" s="184"/>
-      <c r="W28" s="184"/>
-      <c r="X28" s="184"/>
-      <c r="Y28" s="184"/>
-      <c r="Z28" s="184"/>
-      <c r="AA28" s="184"/>
-      <c r="AB28" s="184"/>
-      <c r="AC28" s="184"/>
-      <c r="AD28" s="184"/>
-      <c r="AE28" s="184"/>
-      <c r="AF28" s="185"/>
+      <c r="S28" s="172"/>
+      <c r="T28" s="173"/>
+      <c r="U28" s="173"/>
+      <c r="V28" s="173"/>
+      <c r="W28" s="173"/>
+      <c r="X28" s="173"/>
+      <c r="Y28" s="173"/>
+      <c r="Z28" s="173"/>
+      <c r="AA28" s="173"/>
+      <c r="AB28" s="173"/>
+      <c r="AC28" s="173"/>
+      <c r="AD28" s="173"/>
+      <c r="AE28" s="173"/>
+      <c r="AF28" s="174"/>
       <c r="AI28" s="3"/>
       <c r="AJ28" s="3"/>
       <c r="AK28" s="3"/>
@@ -21479,20 +21469,20 @@
       <c r="P29" s="69"/>
       <c r="Q29" s="69"/>
       <c r="R29" s="69"/>
-      <c r="S29" s="183"/>
-      <c r="T29" s="184"/>
-      <c r="U29" s="184"/>
-      <c r="V29" s="184"/>
-      <c r="W29" s="184"/>
-      <c r="X29" s="184"/>
-      <c r="Y29" s="184"/>
-      <c r="Z29" s="184"/>
-      <c r="AA29" s="184"/>
-      <c r="AB29" s="184"/>
-      <c r="AC29" s="184"/>
-      <c r="AD29" s="184"/>
-      <c r="AE29" s="184"/>
-      <c r="AF29" s="185"/>
+      <c r="S29" s="172"/>
+      <c r="T29" s="173"/>
+      <c r="U29" s="173"/>
+      <c r="V29" s="173"/>
+      <c r="W29" s="173"/>
+      <c r="X29" s="173"/>
+      <c r="Y29" s="173"/>
+      <c r="Z29" s="173"/>
+      <c r="AA29" s="173"/>
+      <c r="AB29" s="173"/>
+      <c r="AC29" s="173"/>
+      <c r="AD29" s="173"/>
+      <c r="AE29" s="173"/>
+      <c r="AF29" s="174"/>
       <c r="AI29" s="3"/>
       <c r="AJ29" s="3"/>
       <c r="AK29" s="3"/>
@@ -21711,10 +21701,10 @@
     </row>
     <row r="30" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A30" s="37"/>
-      <c r="B30" s="137" t="s">
+      <c r="B30" s="154" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="138"/>
+      <c r="C30" s="155"/>
       <c r="D30" s="92"/>
       <c r="E30" s="92"/>
       <c r="F30" s="36"/>
@@ -21730,20 +21720,20 @@
       <c r="P30" s="69"/>
       <c r="Q30" s="69"/>
       <c r="R30" s="69"/>
-      <c r="S30" s="183"/>
-      <c r="T30" s="184"/>
-      <c r="U30" s="184"/>
-      <c r="V30" s="184"/>
-      <c r="W30" s="184"/>
-      <c r="X30" s="184"/>
-      <c r="Y30" s="184"/>
-      <c r="Z30" s="184"/>
-      <c r="AA30" s="184"/>
-      <c r="AB30" s="184"/>
-      <c r="AC30" s="184"/>
-      <c r="AD30" s="184"/>
-      <c r="AE30" s="184"/>
-      <c r="AF30" s="185"/>
+      <c r="S30" s="172"/>
+      <c r="T30" s="173"/>
+      <c r="U30" s="173"/>
+      <c r="V30" s="173"/>
+      <c r="W30" s="173"/>
+      <c r="X30" s="173"/>
+      <c r="Y30" s="173"/>
+      <c r="Z30" s="173"/>
+      <c r="AA30" s="173"/>
+      <c r="AB30" s="173"/>
+      <c r="AC30" s="173"/>
+      <c r="AD30" s="173"/>
+      <c r="AE30" s="173"/>
+      <c r="AF30" s="174"/>
       <c r="AI30" s="3"/>
       <c r="AJ30" s="3"/>
       <c r="AK30" s="3"/>
@@ -21966,7 +21956,7 @@
         <v>92</v>
       </c>
       <c r="C31" s="118"/>
-      <c r="D31" s="134" t="s">
+      <c r="D31" s="158" t="s">
         <v>117</v>
       </c>
       <c r="E31" s="92"/>
@@ -21983,20 +21973,20 @@
       <c r="P31" s="69"/>
       <c r="Q31" s="69"/>
       <c r="R31" s="69"/>
-      <c r="S31" s="183"/>
-      <c r="T31" s="184"/>
-      <c r="U31" s="184"/>
-      <c r="V31" s="184"/>
-      <c r="W31" s="184"/>
-      <c r="X31" s="184"/>
-      <c r="Y31" s="184"/>
-      <c r="Z31" s="184"/>
-      <c r="AA31" s="184"/>
-      <c r="AB31" s="184"/>
-      <c r="AC31" s="184"/>
-      <c r="AD31" s="184"/>
-      <c r="AE31" s="184"/>
-      <c r="AF31" s="185"/>
+      <c r="S31" s="172"/>
+      <c r="T31" s="173"/>
+      <c r="U31" s="173"/>
+      <c r="V31" s="173"/>
+      <c r="W31" s="173"/>
+      <c r="X31" s="173"/>
+      <c r="Y31" s="173"/>
+      <c r="Z31" s="173"/>
+      <c r="AA31" s="173"/>
+      <c r="AB31" s="173"/>
+      <c r="AC31" s="173"/>
+      <c r="AD31" s="173"/>
+      <c r="AE31" s="173"/>
+      <c r="AF31" s="174"/>
       <c r="AI31" s="3"/>
       <c r="AJ31" s="3"/>
       <c r="AK31" s="3"/>
@@ -22219,7 +22209,7 @@
         <v>93</v>
       </c>
       <c r="C32" s="118"/>
-      <c r="D32" s="135"/>
+      <c r="D32" s="119"/>
       <c r="E32" s="92" t="s">
         <v>47</v>
       </c>
@@ -22236,20 +22226,20 @@
       <c r="P32" s="68"/>
       <c r="Q32" s="68"/>
       <c r="R32" s="68"/>
-      <c r="S32" s="183"/>
-      <c r="T32" s="184"/>
-      <c r="U32" s="184"/>
-      <c r="V32" s="184"/>
-      <c r="W32" s="184"/>
-      <c r="X32" s="184"/>
-      <c r="Y32" s="184"/>
-      <c r="Z32" s="184"/>
-      <c r="AA32" s="184"/>
-      <c r="AB32" s="184"/>
-      <c r="AC32" s="184"/>
-      <c r="AD32" s="184"/>
-      <c r="AE32" s="184"/>
-      <c r="AF32" s="185"/>
+      <c r="S32" s="172"/>
+      <c r="T32" s="173"/>
+      <c r="U32" s="173"/>
+      <c r="V32" s="173"/>
+      <c r="W32" s="173"/>
+      <c r="X32" s="173"/>
+      <c r="Y32" s="173"/>
+      <c r="Z32" s="173"/>
+      <c r="AA32" s="173"/>
+      <c r="AB32" s="173"/>
+      <c r="AC32" s="173"/>
+      <c r="AD32" s="173"/>
+      <c r="AE32" s="173"/>
+      <c r="AF32" s="174"/>
       <c r="AI32" s="3"/>
       <c r="AJ32" s="3"/>
       <c r="AK32" s="3"/>
@@ -22472,7 +22462,7 @@
         <v>94</v>
       </c>
       <c r="C33" s="118"/>
-      <c r="D33" s="136"/>
+      <c r="D33" s="120"/>
       <c r="E33" s="92"/>
       <c r="F33" s="36"/>
       <c r="G33" s="68"/>
@@ -22487,20 +22477,20 @@
       <c r="P33" s="68"/>
       <c r="Q33" s="68"/>
       <c r="R33" s="68"/>
-      <c r="S33" s="183"/>
-      <c r="T33" s="184"/>
-      <c r="U33" s="184"/>
-      <c r="V33" s="184"/>
-      <c r="W33" s="184"/>
-      <c r="X33" s="184"/>
-      <c r="Y33" s="184"/>
-      <c r="Z33" s="184"/>
-      <c r="AA33" s="184"/>
-      <c r="AB33" s="184"/>
-      <c r="AC33" s="184"/>
-      <c r="AD33" s="184"/>
-      <c r="AE33" s="184"/>
-      <c r="AF33" s="185"/>
+      <c r="S33" s="172"/>
+      <c r="T33" s="173"/>
+      <c r="U33" s="173"/>
+      <c r="V33" s="173"/>
+      <c r="W33" s="173"/>
+      <c r="X33" s="173"/>
+      <c r="Y33" s="173"/>
+      <c r="Z33" s="173"/>
+      <c r="AA33" s="173"/>
+      <c r="AB33" s="173"/>
+      <c r="AC33" s="173"/>
+      <c r="AD33" s="173"/>
+      <c r="AE33" s="173"/>
+      <c r="AF33" s="174"/>
       <c r="AI33" s="3"/>
       <c r="AJ33" s="3"/>
       <c r="AK33" s="3"/>
@@ -22719,10 +22709,10 @@
     </row>
     <row r="34" spans="1:249" s="2" customFormat="1" ht="28.25" customHeight="1">
       <c r="A34" s="38"/>
-      <c r="B34" s="137" t="s">
+      <c r="B34" s="154" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="138"/>
+      <c r="C34" s="155"/>
       <c r="D34" s="35"/>
       <c r="E34" s="35"/>
       <c r="F34" s="39"/>
@@ -22738,20 +22728,20 @@
       <c r="P34" s="68"/>
       <c r="Q34" s="68"/>
       <c r="R34" s="68"/>
-      <c r="S34" s="183"/>
-      <c r="T34" s="184"/>
-      <c r="U34" s="184"/>
-      <c r="V34" s="184"/>
-      <c r="W34" s="184"/>
-      <c r="X34" s="184"/>
-      <c r="Y34" s="184"/>
-      <c r="Z34" s="184"/>
-      <c r="AA34" s="184"/>
-      <c r="AB34" s="184"/>
-      <c r="AC34" s="184"/>
-      <c r="AD34" s="184"/>
-      <c r="AE34" s="184"/>
-      <c r="AF34" s="185"/>
+      <c r="S34" s="172"/>
+      <c r="T34" s="173"/>
+      <c r="U34" s="173"/>
+      <c r="V34" s="173"/>
+      <c r="W34" s="173"/>
+      <c r="X34" s="173"/>
+      <c r="Y34" s="173"/>
+      <c r="Z34" s="173"/>
+      <c r="AA34" s="173"/>
+      <c r="AB34" s="173"/>
+      <c r="AC34" s="173"/>
+      <c r="AD34" s="173"/>
+      <c r="AE34" s="173"/>
+      <c r="AF34" s="174"/>
       <c r="AI34" s="3"/>
       <c r="AJ34" s="3"/>
       <c r="AK34" s="3"/>
@@ -22972,15 +22962,15 @@
       <c r="A35" s="37">
         <v>1</v>
       </c>
-      <c r="B35" s="130" t="s">
+      <c r="B35" s="156" t="s">
         <v>104</v>
       </c>
-      <c r="C35" s="131"/>
+      <c r="C35" s="157"/>
       <c r="D35" s="96"/>
       <c r="E35" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="F35" s="134" t="s">
+      <c r="F35" s="158" t="s">
         <v>95</v>
       </c>
       <c r="G35" s="69"/>
@@ -22995,20 +22985,20 @@
       <c r="P35" s="69"/>
       <c r="Q35" s="69"/>
       <c r="R35" s="69"/>
-      <c r="S35" s="183"/>
-      <c r="T35" s="184"/>
-      <c r="U35" s="184"/>
-      <c r="V35" s="184"/>
-      <c r="W35" s="184"/>
-      <c r="X35" s="184"/>
-      <c r="Y35" s="184"/>
-      <c r="Z35" s="184"/>
-      <c r="AA35" s="184"/>
-      <c r="AB35" s="184"/>
-      <c r="AC35" s="184"/>
-      <c r="AD35" s="184"/>
-      <c r="AE35" s="184"/>
-      <c r="AF35" s="185"/>
+      <c r="S35" s="172"/>
+      <c r="T35" s="173"/>
+      <c r="U35" s="173"/>
+      <c r="V35" s="173"/>
+      <c r="W35" s="173"/>
+      <c r="X35" s="173"/>
+      <c r="Y35" s="173"/>
+      <c r="Z35" s="173"/>
+      <c r="AA35" s="173"/>
+      <c r="AB35" s="173"/>
+      <c r="AC35" s="173"/>
+      <c r="AD35" s="173"/>
+      <c r="AE35" s="173"/>
+      <c r="AF35" s="174"/>
       <c r="AI35" s="3"/>
       <c r="AJ35" s="3"/>
       <c r="AK35" s="3"/>
@@ -23235,7 +23225,7 @@
       <c r="E36" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="F36" s="135"/>
+      <c r="F36" s="119"/>
       <c r="G36" s="68"/>
       <c r="H36" s="68"/>
       <c r="I36" s="68"/>
@@ -23248,20 +23238,20 @@
       <c r="P36" s="68"/>
       <c r="Q36" s="68"/>
       <c r="R36" s="68"/>
-      <c r="S36" s="183"/>
-      <c r="T36" s="184"/>
-      <c r="U36" s="184"/>
-      <c r="V36" s="184"/>
-      <c r="W36" s="184"/>
-      <c r="X36" s="184"/>
-      <c r="Y36" s="184"/>
-      <c r="Z36" s="184"/>
-      <c r="AA36" s="184"/>
-      <c r="AB36" s="184"/>
-      <c r="AC36" s="184"/>
-      <c r="AD36" s="184"/>
-      <c r="AE36" s="184"/>
-      <c r="AF36" s="185"/>
+      <c r="S36" s="172"/>
+      <c r="T36" s="173"/>
+      <c r="U36" s="173"/>
+      <c r="V36" s="173"/>
+      <c r="W36" s="173"/>
+      <c r="X36" s="173"/>
+      <c r="Y36" s="173"/>
+      <c r="Z36" s="173"/>
+      <c r="AA36" s="173"/>
+      <c r="AB36" s="173"/>
+      <c r="AC36" s="173"/>
+      <c r="AD36" s="173"/>
+      <c r="AE36" s="173"/>
+      <c r="AF36" s="174"/>
       <c r="AI36" s="3"/>
       <c r="AJ36" s="3"/>
       <c r="AK36" s="3"/>
@@ -23482,11 +23472,11 @@
       <c r="A37" s="37">
         <v>3</v>
       </c>
-      <c r="B37" s="130"/>
-      <c r="C37" s="131"/>
+      <c r="B37" s="156"/>
+      <c r="C37" s="157"/>
       <c r="D37" s="92"/>
       <c r="E37" s="35"/>
-      <c r="F37" s="135"/>
+      <c r="F37" s="119"/>
       <c r="G37" s="68"/>
       <c r="H37" s="68"/>
       <c r="I37" s="68"/>
@@ -23499,20 +23489,20 @@
       <c r="P37" s="68"/>
       <c r="Q37" s="68"/>
       <c r="R37" s="68"/>
-      <c r="S37" s="183"/>
-      <c r="T37" s="184"/>
-      <c r="U37" s="184"/>
-      <c r="V37" s="184"/>
-      <c r="W37" s="184"/>
-      <c r="X37" s="184"/>
-      <c r="Y37" s="184"/>
-      <c r="Z37" s="184"/>
-      <c r="AA37" s="184"/>
-      <c r="AB37" s="184"/>
-      <c r="AC37" s="184"/>
-      <c r="AD37" s="184"/>
-      <c r="AE37" s="184"/>
-      <c r="AF37" s="185"/>
+      <c r="S37" s="172"/>
+      <c r="T37" s="173"/>
+      <c r="U37" s="173"/>
+      <c r="V37" s="173"/>
+      <c r="W37" s="173"/>
+      <c r="X37" s="173"/>
+      <c r="Y37" s="173"/>
+      <c r="Z37" s="173"/>
+      <c r="AA37" s="173"/>
+      <c r="AB37" s="173"/>
+      <c r="AC37" s="173"/>
+      <c r="AD37" s="173"/>
+      <c r="AE37" s="173"/>
+      <c r="AF37" s="174"/>
       <c r="AI37" s="3"/>
       <c r="AJ37" s="3"/>
       <c r="AK37" s="3"/>
@@ -23731,10 +23721,10 @@
     </row>
     <row r="38" spans="1:249" s="2" customFormat="1" ht="42" customHeight="1" thickBot="1">
       <c r="A38" s="41"/>
-      <c r="B38" s="128" t="s">
+      <c r="B38" s="168" t="s">
         <v>63</v>
       </c>
-      <c r="C38" s="129"/>
+      <c r="C38" s="169"/>
       <c r="D38" s="42" t="s">
         <v>16</v>
       </c>
@@ -23992,29 +23982,29 @@
       <c r="E39" s="44"/>
       <c r="F39" s="57"/>
       <c r="G39" s="75"/>
-      <c r="H39" s="188"/>
-      <c r="I39" s="188"/>
-      <c r="J39" s="188"/>
-      <c r="K39" s="188"/>
+      <c r="H39" s="180"/>
+      <c r="I39" s="180"/>
+      <c r="J39" s="180"/>
+      <c r="K39" s="180"/>
       <c r="L39" s="76"/>
       <c r="M39" s="75"/>
-      <c r="N39" s="188"/>
-      <c r="O39" s="188"/>
-      <c r="P39" s="188"/>
-      <c r="Q39" s="188"/>
+      <c r="N39" s="180"/>
+      <c r="O39" s="180"/>
+      <c r="P39" s="180"/>
+      <c r="Q39" s="180"/>
       <c r="R39" s="76"/>
       <c r="S39" s="75"/>
-      <c r="T39" s="188"/>
-      <c r="U39" s="188"/>
-      <c r="V39" s="188"/>
+      <c r="T39" s="180"/>
+      <c r="U39" s="180"/>
+      <c r="V39" s="180"/>
       <c r="W39" s="75"/>
-      <c r="X39" s="188"/>
-      <c r="Y39" s="188"/>
-      <c r="Z39" s="188"/>
+      <c r="X39" s="180"/>
+      <c r="Y39" s="180"/>
+      <c r="Z39" s="180"/>
       <c r="AA39" s="76"/>
       <c r="AB39" s="75"/>
-      <c r="AC39" s="188"/>
-      <c r="AD39" s="188"/>
+      <c r="AC39" s="180"/>
+      <c r="AD39" s="180"/>
       <c r="AE39" s="55"/>
       <c r="AF39" s="56"/>
       <c r="AI39" s="3"/>
@@ -24245,29 +24235,29 @@
       <c r="E40" s="90"/>
       <c r="F40" s="58"/>
       <c r="G40" s="77"/>
-      <c r="H40" s="189"/>
-      <c r="I40" s="189"/>
-      <c r="J40" s="189"/>
-      <c r="K40" s="189"/>
+      <c r="H40" s="179"/>
+      <c r="I40" s="179"/>
+      <c r="J40" s="179"/>
+      <c r="K40" s="179"/>
       <c r="L40" s="78"/>
       <c r="M40" s="77"/>
-      <c r="N40" s="189"/>
-      <c r="O40" s="189"/>
-      <c r="P40" s="189"/>
-      <c r="Q40" s="189"/>
+      <c r="N40" s="179"/>
+      <c r="O40" s="179"/>
+      <c r="P40" s="179"/>
+      <c r="Q40" s="179"/>
       <c r="R40" s="78"/>
       <c r="S40" s="77"/>
-      <c r="T40" s="189"/>
-      <c r="U40" s="189"/>
-      <c r="V40" s="189"/>
+      <c r="T40" s="179"/>
+      <c r="U40" s="179"/>
+      <c r="V40" s="179"/>
       <c r="W40" s="77"/>
-      <c r="X40" s="189"/>
-      <c r="Y40" s="189"/>
-      <c r="Z40" s="189"/>
+      <c r="X40" s="179"/>
+      <c r="Y40" s="179"/>
+      <c r="Z40" s="179"/>
       <c r="AA40" s="78"/>
       <c r="AB40" s="77"/>
-      <c r="AC40" s="189"/>
-      <c r="AD40" s="189"/>
+      <c r="AC40" s="179"/>
+      <c r="AD40" s="179"/>
       <c r="AE40" s="61"/>
       <c r="AF40" s="79"/>
       <c r="AI40" s="3"/>
@@ -24498,29 +24488,29 @@
       <c r="E41" s="91"/>
       <c r="F41" s="59"/>
       <c r="G41" s="77"/>
-      <c r="H41" s="189"/>
-      <c r="I41" s="189"/>
-      <c r="J41" s="189"/>
-      <c r="K41" s="189"/>
+      <c r="H41" s="179"/>
+      <c r="I41" s="179"/>
+      <c r="J41" s="179"/>
+      <c r="K41" s="179"/>
       <c r="L41" s="80"/>
       <c r="M41" s="77"/>
-      <c r="N41" s="189"/>
-      <c r="O41" s="189"/>
-      <c r="P41" s="189"/>
-      <c r="Q41" s="189"/>
+      <c r="N41" s="179"/>
+      <c r="O41" s="179"/>
+      <c r="P41" s="179"/>
+      <c r="Q41" s="179"/>
       <c r="R41" s="80"/>
       <c r="S41" s="77"/>
-      <c r="T41" s="189"/>
-      <c r="U41" s="189"/>
-      <c r="V41" s="189"/>
+      <c r="T41" s="179"/>
+      <c r="U41" s="179"/>
+      <c r="V41" s="179"/>
       <c r="W41" s="77"/>
-      <c r="X41" s="189"/>
-      <c r="Y41" s="189"/>
-      <c r="Z41" s="189"/>
+      <c r="X41" s="179"/>
+      <c r="Y41" s="179"/>
+      <c r="Z41" s="179"/>
       <c r="AA41" s="80"/>
       <c r="AB41" s="77"/>
-      <c r="AC41" s="189"/>
-      <c r="AD41" s="189"/>
+      <c r="AC41" s="179"/>
+      <c r="AD41" s="179"/>
       <c r="AE41" s="62"/>
       <c r="AF41" s="81"/>
       <c r="AI41" s="3"/>
@@ -24751,29 +24741,29 @@
       <c r="E42" s="91"/>
       <c r="F42" s="59"/>
       <c r="G42" s="77"/>
-      <c r="H42" s="189"/>
-      <c r="I42" s="189"/>
-      <c r="J42" s="189"/>
-      <c r="K42" s="189"/>
+      <c r="H42" s="179"/>
+      <c r="I42" s="179"/>
+      <c r="J42" s="179"/>
+      <c r="K42" s="179"/>
       <c r="L42" s="80"/>
       <c r="M42" s="77"/>
-      <c r="N42" s="189"/>
-      <c r="O42" s="189"/>
-      <c r="P42" s="189"/>
-      <c r="Q42" s="189"/>
+      <c r="N42" s="179"/>
+      <c r="O42" s="179"/>
+      <c r="P42" s="179"/>
+      <c r="Q42" s="179"/>
       <c r="R42" s="80"/>
       <c r="S42" s="77"/>
-      <c r="T42" s="189"/>
-      <c r="U42" s="189"/>
-      <c r="V42" s="189"/>
+      <c r="T42" s="179"/>
+      <c r="U42" s="179"/>
+      <c r="V42" s="179"/>
       <c r="W42" s="77"/>
-      <c r="X42" s="189"/>
-      <c r="Y42" s="189"/>
-      <c r="Z42" s="189"/>
+      <c r="X42" s="179"/>
+      <c r="Y42" s="179"/>
+      <c r="Z42" s="179"/>
       <c r="AA42" s="80"/>
       <c r="AB42" s="77"/>
-      <c r="AC42" s="189"/>
-      <c r="AD42" s="189"/>
+      <c r="AC42" s="179"/>
+      <c r="AD42" s="179"/>
       <c r="AE42" s="62"/>
       <c r="AF42" s="81"/>
       <c r="AI42" s="3"/>
@@ -25000,29 +24990,29 @@
       <c r="E43" s="50"/>
       <c r="F43" s="60"/>
       <c r="G43" s="82"/>
-      <c r="H43" s="190"/>
-      <c r="I43" s="190"/>
-      <c r="J43" s="190"/>
-      <c r="K43" s="190"/>
+      <c r="H43" s="175"/>
+      <c r="I43" s="175"/>
+      <c r="J43" s="175"/>
+      <c r="K43" s="175"/>
       <c r="L43" s="83"/>
       <c r="M43" s="82"/>
-      <c r="N43" s="190"/>
-      <c r="O43" s="190"/>
-      <c r="P43" s="190"/>
-      <c r="Q43" s="190"/>
+      <c r="N43" s="175"/>
+      <c r="O43" s="175"/>
+      <c r="P43" s="175"/>
+      <c r="Q43" s="175"/>
       <c r="R43" s="83"/>
       <c r="S43" s="82"/>
-      <c r="T43" s="190"/>
-      <c r="U43" s="190"/>
-      <c r="V43" s="190"/>
+      <c r="T43" s="175"/>
+      <c r="U43" s="175"/>
+      <c r="V43" s="175"/>
       <c r="W43" s="82"/>
-      <c r="X43" s="190"/>
-      <c r="Y43" s="190"/>
-      <c r="Z43" s="190"/>
+      <c r="X43" s="175"/>
+      <c r="Y43" s="175"/>
+      <c r="Z43" s="175"/>
       <c r="AA43" s="83"/>
       <c r="AB43" s="82"/>
-      <c r="AC43" s="190"/>
-      <c r="AD43" s="190"/>
+      <c r="AC43" s="175"/>
+      <c r="AD43" s="175"/>
       <c r="AE43" s="63"/>
       <c r="AF43" s="84"/>
       <c r="AI43" s="3"/>
@@ -25286,18 +25276,78 @@
     </row>
   </sheetData>
   <mergeCells count="100">
-    <mergeCell ref="S32:AF32"/>
-    <mergeCell ref="S33:AF33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="S26:AF26"/>
-    <mergeCell ref="S28:AF28"/>
-    <mergeCell ref="S29:AF29"/>
-    <mergeCell ref="S30:AF30"/>
-    <mergeCell ref="S31:AF31"/>
-    <mergeCell ref="S27:AF27"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:AF1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="T3:AF3"/>
+    <mergeCell ref="T5:W7"/>
+    <mergeCell ref="AD4:AF4"/>
+    <mergeCell ref="AD5:AF7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="S11:AF11"/>
+    <mergeCell ref="S12:AF12"/>
+    <mergeCell ref="S13:AF13"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="T4:W4"/>
+    <mergeCell ref="X4:Z4"/>
+    <mergeCell ref="AA4:AC4"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="S14:AF14"/>
+    <mergeCell ref="S15:AF15"/>
+    <mergeCell ref="S16:AF16"/>
+    <mergeCell ref="S17:AF17"/>
+    <mergeCell ref="S18:AF18"/>
+    <mergeCell ref="S19:AF19"/>
+    <mergeCell ref="S25:AF25"/>
+    <mergeCell ref="S24:AF24"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="AC39:AD39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="H39:K39"/>
+    <mergeCell ref="N39:Q39"/>
+    <mergeCell ref="S36:AF36"/>
+    <mergeCell ref="S37:AF37"/>
+    <mergeCell ref="H40:K40"/>
+    <mergeCell ref="N40:Q40"/>
+    <mergeCell ref="T40:V40"/>
+    <mergeCell ref="X40:Z40"/>
+    <mergeCell ref="AC40:AD40"/>
+    <mergeCell ref="H43:K43"/>
+    <mergeCell ref="N43:Q43"/>
+    <mergeCell ref="T43:V43"/>
+    <mergeCell ref="X43:Z43"/>
+    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="N41:Q41"/>
+    <mergeCell ref="H42:K42"/>
+    <mergeCell ref="N42:Q42"/>
     <mergeCell ref="AC43:AD43"/>
     <mergeCell ref="S9:AF9"/>
     <mergeCell ref="S20:AF20"/>
@@ -25314,82 +25364,22 @@
     <mergeCell ref="X39:Z39"/>
     <mergeCell ref="S34:AF34"/>
     <mergeCell ref="S35:AF35"/>
-    <mergeCell ref="H43:K43"/>
-    <mergeCell ref="N43:Q43"/>
-    <mergeCell ref="T43:V43"/>
-    <mergeCell ref="X43:Z43"/>
-    <mergeCell ref="H41:K41"/>
-    <mergeCell ref="N41:Q41"/>
-    <mergeCell ref="H42:K42"/>
-    <mergeCell ref="N42:Q42"/>
-    <mergeCell ref="H40:K40"/>
-    <mergeCell ref="N40:Q40"/>
-    <mergeCell ref="T40:V40"/>
-    <mergeCell ref="X40:Z40"/>
-    <mergeCell ref="AC40:AD40"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="F35:F37"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="AC39:AD39"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="H39:K39"/>
-    <mergeCell ref="N39:Q39"/>
-    <mergeCell ref="S36:AF36"/>
-    <mergeCell ref="S37:AF37"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="S14:AF14"/>
-    <mergeCell ref="S15:AF15"/>
-    <mergeCell ref="S16:AF16"/>
-    <mergeCell ref="S17:AF17"/>
-    <mergeCell ref="S18:AF18"/>
-    <mergeCell ref="S19:AF19"/>
-    <mergeCell ref="S25:AF25"/>
-    <mergeCell ref="S24:AF24"/>
-    <mergeCell ref="T5:W7"/>
-    <mergeCell ref="AD4:AF4"/>
-    <mergeCell ref="AD5:AF7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="S11:AF11"/>
-    <mergeCell ref="S12:AF12"/>
-    <mergeCell ref="S13:AF13"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="T4:W4"/>
-    <mergeCell ref="X4:Z4"/>
-    <mergeCell ref="AA4:AC4"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="F1:AF1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="T3:AF3"/>
+    <mergeCell ref="S26:AF26"/>
+    <mergeCell ref="S28:AF28"/>
+    <mergeCell ref="S29:AF29"/>
+    <mergeCell ref="S30:AF30"/>
+    <mergeCell ref="S31:AF31"/>
+    <mergeCell ref="S27:AF27"/>
+    <mergeCell ref="S32:AF32"/>
+    <mergeCell ref="S33:AF33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="B31:C31"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="G11:R19 AG11:AK19">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>TEXT(G11,"aaa")="日"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/設備点検表.xlsx
+++ b/設備点検表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kosuk\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F27DE7C-47B1-4788-BC80-C71E91ECA4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B6DFB8F-DF51-4AAD-95B7-25507C49F775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6C56CF13-AF7F-4C1F-982C-EF388A11F51A}"/>
   </bookViews>
@@ -2765,71 +2765,65 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2870,92 +2864,65 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="71" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="72" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="73" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="67" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="74" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="178" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2990,40 +2957,45 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="71" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="72" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="73" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="67" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="74" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準_設備点検表書式" xfId="1" xr:uid="{15F629F0-A893-4DD8-8A94-9D447F97F79C}"/>
   </cellStyles>
   <dxfs count="6">
-    <dxf>
-      <font>
-        <strike val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -3042,6 +3014,38 @@
       <fill>
         <patternFill>
           <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3376,45 +3380,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:254" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="155" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="121"/>
+      <c r="B1" s="155"/>
       <c r="C1" s="85"/>
-      <c r="F1" s="122" t="s">
+      <c r="F1" s="156" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
-      <c r="AC1" s="122"/>
-      <c r="AD1" s="122"/>
-      <c r="AE1" s="122"/>
-      <c r="AF1" s="122"/>
-      <c r="AG1" s="122"/>
-      <c r="AH1" s="122"/>
-      <c r="AI1" s="122"/>
-      <c r="AJ1" s="122"/>
-      <c r="AK1" s="122"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+      <c r="L1" s="156"/>
+      <c r="M1" s="156"/>
+      <c r="N1" s="156"/>
+      <c r="O1" s="156"/>
+      <c r="P1" s="156"/>
+      <c r="Q1" s="156"/>
+      <c r="R1" s="156"/>
+      <c r="S1" s="156"/>
+      <c r="T1" s="156"/>
+      <c r="U1" s="156"/>
+      <c r="V1" s="156"/>
+      <c r="W1" s="156"/>
+      <c r="X1" s="156"/>
+      <c r="Y1" s="156"/>
+      <c r="Z1" s="156"/>
+      <c r="AA1" s="156"/>
+      <c r="AB1" s="156"/>
+      <c r="AC1" s="156"/>
+      <c r="AD1" s="156"/>
+      <c r="AE1" s="156"/>
+      <c r="AF1" s="156"/>
+      <c r="AG1" s="156"/>
+      <c r="AH1" s="156"/>
+      <c r="AI1" s="156"/>
+      <c r="AJ1" s="156"/>
+      <c r="AK1" s="156"/>
       <c r="AN1" s="3"/>
       <c r="AO1" s="3"/>
       <c r="AP1" s="3"/>
@@ -3885,52 +3889,52 @@
       <c r="IT2" s="3"/>
     </row>
     <row r="3" spans="1:254" s="2" customFormat="1" ht="20" customHeight="1" thickBot="1">
-      <c r="A3" s="123" t="s">
+      <c r="A3" s="157" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="125"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
       <c r="E3" s="94"/>
       <c r="G3" s="51"/>
       <c r="H3" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="126" t="s">
+      <c r="K3" s="160" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="126"/>
-      <c r="M3" s="126" t="s">
+      <c r="L3" s="160"/>
+      <c r="M3" s="160" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="126"/>
-      <c r="O3" s="126"/>
-      <c r="P3" s="126" t="s">
+      <c r="N3" s="160"/>
+      <c r="O3" s="160"/>
+      <c r="P3" s="160" t="s">
         <v>2</v>
       </c>
-      <c r="Q3" s="126"/>
-      <c r="R3" s="126"/>
+      <c r="Q3" s="160"/>
+      <c r="R3" s="160"/>
       <c r="S3" s="3"/>
-      <c r="T3" s="127" t="s">
+      <c r="T3" s="161" t="s">
         <v>3</v>
       </c>
-      <c r="U3" s="128"/>
-      <c r="V3" s="128"/>
-      <c r="W3" s="128"/>
-      <c r="X3" s="128"/>
-      <c r="Y3" s="128"/>
-      <c r="Z3" s="128"/>
-      <c r="AA3" s="128"/>
-      <c r="AB3" s="128"/>
-      <c r="AC3" s="128"/>
-      <c r="AD3" s="128"/>
-      <c r="AE3" s="128"/>
-      <c r="AF3" s="128"/>
-      <c r="AG3" s="128"/>
-      <c r="AH3" s="128"/>
-      <c r="AI3" s="128"/>
-      <c r="AJ3" s="128"/>
-      <c r="AK3" s="129"/>
+      <c r="U3" s="162"/>
+      <c r="V3" s="162"/>
+      <c r="W3" s="162"/>
+      <c r="X3" s="162"/>
+      <c r="Y3" s="162"/>
+      <c r="Z3" s="162"/>
+      <c r="AA3" s="162"/>
+      <c r="AB3" s="162"/>
+      <c r="AC3" s="162"/>
+      <c r="AD3" s="162"/>
+      <c r="AE3" s="162"/>
+      <c r="AF3" s="162"/>
+      <c r="AG3" s="162"/>
+      <c r="AH3" s="162"/>
+      <c r="AI3" s="162"/>
+      <c r="AJ3" s="162"/>
+      <c r="AK3" s="163"/>
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
@@ -4159,47 +4163,47 @@
       <c r="H4" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="126" t="s">
+      <c r="K4" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="126"/>
-      <c r="M4" s="132">
+      <c r="L4" s="160"/>
+      <c r="M4" s="166">
         <v>46113</v>
       </c>
-      <c r="N4" s="132"/>
-      <c r="O4" s="132"/>
-      <c r="P4" s="126" t="s">
+      <c r="N4" s="166"/>
+      <c r="O4" s="166"/>
+      <c r="P4" s="160" t="s">
         <v>50</v>
       </c>
-      <c r="Q4" s="126"/>
-      <c r="R4" s="126"/>
+      <c r="Q4" s="160"/>
+      <c r="R4" s="160"/>
       <c r="S4" s="3"/>
-      <c r="T4" s="133" t="s">
+      <c r="T4" s="152" t="s">
         <v>5</v>
       </c>
-      <c r="U4" s="134"/>
-      <c r="V4" s="134"/>
-      <c r="W4" s="134"/>
-      <c r="X4" s="134"/>
-      <c r="Y4" s="135"/>
-      <c r="Z4" s="133" t="s">
+      <c r="U4" s="153"/>
+      <c r="V4" s="153"/>
+      <c r="W4" s="153"/>
+      <c r="X4" s="153"/>
+      <c r="Y4" s="154"/>
+      <c r="Z4" s="152" t="s">
         <v>6</v>
       </c>
-      <c r="AA4" s="134"/>
-      <c r="AB4" s="134"/>
-      <c r="AC4" s="135"/>
-      <c r="AD4" s="133" t="s">
+      <c r="AA4" s="153"/>
+      <c r="AB4" s="153"/>
+      <c r="AC4" s="154"/>
+      <c r="AD4" s="152" t="s">
         <v>7</v>
       </c>
-      <c r="AE4" s="134"/>
-      <c r="AF4" s="134"/>
-      <c r="AG4" s="135"/>
-      <c r="AH4" s="133" t="s">
+      <c r="AE4" s="153"/>
+      <c r="AF4" s="153"/>
+      <c r="AG4" s="154"/>
+      <c r="AH4" s="152" t="s">
         <v>8</v>
       </c>
-      <c r="AI4" s="134"/>
-      <c r="AJ4" s="134"/>
-      <c r="AK4" s="135"/>
+      <c r="AI4" s="153"/>
+      <c r="AJ4" s="153"/>
+      <c r="AK4" s="154"/>
       <c r="AN4" s="3"/>
       <c r="AO4" s="3"/>
       <c r="AP4" s="3"/>
@@ -4427,16 +4431,16 @@
         <v>23</v>
       </c>
       <c r="S5" s="3"/>
-      <c r="T5" s="136" t="s">
+      <c r="T5" s="167" t="s">
         <v>64</v>
       </c>
-      <c r="U5" s="137"/>
-      <c r="V5" s="137"/>
-      <c r="W5" s="141">
+      <c r="U5" s="168"/>
+      <c r="V5" s="168"/>
+      <c r="W5" s="139">
         <v>7</v>
       </c>
-      <c r="X5" s="142"/>
-      <c r="Y5" s="143"/>
+      <c r="X5" s="140"/>
+      <c r="Y5" s="141"/>
       <c r="Z5" s="11"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
@@ -4445,10 +4449,10 @@
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
       <c r="AG5" s="12"/>
-      <c r="AH5" s="146"/>
-      <c r="AI5" s="147"/>
-      <c r="AJ5" s="147"/>
-      <c r="AK5" s="148"/>
+      <c r="AH5" s="144"/>
+      <c r="AI5" s="145"/>
+      <c r="AJ5" s="145"/>
+      <c r="AK5" s="146"/>
       <c r="AN5" s="3"/>
       <c r="AO5" s="3"/>
       <c r="AP5" s="3"/>
@@ -4680,12 +4684,12 @@
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
-      <c r="T6" s="138"/>
-      <c r="U6" s="137"/>
-      <c r="V6" s="137"/>
-      <c r="W6" s="142"/>
-      <c r="X6" s="142"/>
-      <c r="Y6" s="143"/>
+      <c r="T6" s="169"/>
+      <c r="U6" s="168"/>
+      <c r="V6" s="168"/>
+      <c r="W6" s="140"/>
+      <c r="X6" s="140"/>
+      <c r="Y6" s="141"/>
       <c r="Z6" s="11"/>
       <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
@@ -4694,10 +4698,10 @@
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
       <c r="AG6" s="12"/>
-      <c r="AH6" s="146"/>
-      <c r="AI6" s="147"/>
-      <c r="AJ6" s="147"/>
-      <c r="AK6" s="148"/>
+      <c r="AH6" s="144"/>
+      <c r="AI6" s="145"/>
+      <c r="AJ6" s="145"/>
+      <c r="AK6" s="146"/>
       <c r="AN6" s="3"/>
       <c r="AO6" s="3"/>
       <c r="AP6" s="3"/>
@@ -4929,12 +4933,12 @@
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
-      <c r="T7" s="139"/>
-      <c r="U7" s="140"/>
-      <c r="V7" s="140"/>
-      <c r="W7" s="144"/>
-      <c r="X7" s="144"/>
-      <c r="Y7" s="145"/>
+      <c r="T7" s="170"/>
+      <c r="U7" s="171"/>
+      <c r="V7" s="171"/>
+      <c r="W7" s="142"/>
+      <c r="X7" s="142"/>
+      <c r="Y7" s="143"/>
       <c r="Z7" s="21"/>
       <c r="AA7" s="22"/>
       <c r="AB7" s="22"/>
@@ -4943,10 +4947,10 @@
       <c r="AE7" s="22"/>
       <c r="AF7" s="22"/>
       <c r="AG7" s="23"/>
-      <c r="AH7" s="149"/>
-      <c r="AI7" s="150"/>
-      <c r="AJ7" s="150"/>
-      <c r="AK7" s="151"/>
+      <c r="AH7" s="147"/>
+      <c r="AI7" s="148"/>
+      <c r="AJ7" s="148"/>
+      <c r="AK7" s="149"/>
       <c r="AL7" s="86"/>
       <c r="AN7" s="3"/>
       <c r="AO7" s="3"/>
@@ -5829,8 +5833,8 @@
     </row>
     <row r="10" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A10" s="29"/>
-      <c r="B10" s="152"/>
-      <c r="C10" s="153"/>
+      <c r="B10" s="150"/>
+      <c r="C10" s="151"/>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="31" t="s">
@@ -6178,10 +6182,10 @@
     </row>
     <row r="11" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A11" s="34"/>
-      <c r="B11" s="130" t="s">
+      <c r="B11" s="164" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="131"/>
+      <c r="C11" s="165"/>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
       <c r="F11" s="102" t="s">
@@ -6448,7 +6452,7 @@
       <c r="E12" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="158" t="s">
+      <c r="F12" s="134" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="106"/>
@@ -6710,7 +6714,7 @@
         <v>99</v>
       </c>
       <c r="E13" s="92"/>
-      <c r="F13" s="119"/>
+      <c r="F13" s="135"/>
       <c r="G13" s="106"/>
       <c r="H13" s="106"/>
       <c r="I13" s="106"/>
@@ -6972,7 +6976,7 @@
       <c r="E14" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="119"/>
+      <c r="F14" s="135"/>
       <c r="G14" s="106"/>
       <c r="H14" s="106"/>
       <c r="I14" s="106"/>
@@ -7234,7 +7238,7 @@
       <c r="E15" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="119"/>
+      <c r="F15" s="135"/>
       <c r="G15" s="106"/>
       <c r="H15" s="106"/>
       <c r="I15" s="106"/>
@@ -7496,7 +7500,7 @@
       <c r="E16" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="119"/>
+      <c r="F16" s="135"/>
       <c r="G16" s="106"/>
       <c r="H16" s="106"/>
       <c r="I16" s="106"/>
@@ -7758,7 +7762,7 @@
       <c r="E17" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="119"/>
+      <c r="F17" s="135"/>
       <c r="G17" s="106"/>
       <c r="H17" s="106"/>
       <c r="I17" s="106"/>
@@ -8020,7 +8024,7 @@
       <c r="E18" s="92" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="119"/>
+      <c r="F18" s="135"/>
       <c r="G18" s="106"/>
       <c r="H18" s="106"/>
       <c r="I18" s="106"/>
@@ -8282,7 +8286,7 @@
       <c r="E19" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="F19" s="119"/>
+      <c r="F19" s="135"/>
       <c r="G19" s="106"/>
       <c r="H19" s="106"/>
       <c r="I19" s="106"/>
@@ -8544,7 +8548,7 @@
       <c r="E20" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="F20" s="119"/>
+      <c r="F20" s="135"/>
       <c r="G20" s="106"/>
       <c r="H20" s="106"/>
       <c r="I20" s="106"/>
@@ -8804,7 +8808,7 @@
         <v>100</v>
       </c>
       <c r="E21" s="92"/>
-      <c r="F21" s="119"/>
+      <c r="F21" s="135"/>
       <c r="G21" s="106"/>
       <c r="H21" s="106"/>
       <c r="I21" s="106"/>
@@ -9064,7 +9068,7 @@
         <v>38</v>
       </c>
       <c r="E22" s="92"/>
-      <c r="F22" s="119" t="s">
+      <c r="F22" s="135" t="s">
         <v>135</v>
       </c>
       <c r="G22" s="106"/>
@@ -9328,7 +9332,7 @@
       <c r="E23" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="F23" s="120"/>
+      <c r="F23" s="136"/>
       <c r="G23" s="104"/>
       <c r="H23" s="104"/>
       <c r="I23" s="104"/>
@@ -10096,10 +10100,10 @@
     </row>
     <row r="26" spans="1:254" s="2" customFormat="1" ht="28.25" customHeight="1">
       <c r="A26" s="38"/>
-      <c r="B26" s="154" t="s">
+      <c r="B26" s="137" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="155"/>
+      <c r="C26" s="138"/>
       <c r="D26" s="35"/>
       <c r="E26" s="35"/>
       <c r="F26" s="39"/>
@@ -10354,17 +10358,17 @@
       <c r="A27" s="37">
         <v>1</v>
       </c>
-      <c r="B27" s="156" t="s">
+      <c r="B27" s="130" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="157"/>
+      <c r="C27" s="131"/>
       <c r="D27" s="92" t="s">
         <v>99</v>
       </c>
       <c r="E27" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="158" t="s">
+      <c r="F27" s="134" t="s">
         <v>15</v>
       </c>
       <c r="G27" s="106"/>
@@ -10618,15 +10622,15 @@
       <c r="A28" s="37">
         <v>2</v>
       </c>
-      <c r="B28" s="156" t="s">
+      <c r="B28" s="130" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="157"/>
+      <c r="C28" s="131"/>
       <c r="D28" s="35" t="s">
         <v>77</v>
       </c>
       <c r="E28" s="35"/>
-      <c r="F28" s="119"/>
+      <c r="F28" s="135"/>
       <c r="G28" s="106"/>
       <c r="H28" s="106"/>
       <c r="I28" s="106"/>
@@ -10886,7 +10890,7 @@
         <v>77</v>
       </c>
       <c r="E29" s="35"/>
-      <c r="F29" s="119"/>
+      <c r="F29" s="135"/>
       <c r="G29" s="106"/>
       <c r="H29" s="106"/>
       <c r="I29" s="106"/>
@@ -11148,7 +11152,7 @@
       <c r="E30" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="F30" s="119"/>
+      <c r="F30" s="135"/>
       <c r="G30" s="104"/>
       <c r="H30" s="104"/>
       <c r="I30" s="104"/>
@@ -11400,15 +11404,15 @@
       <c r="A31" s="37">
         <v>5</v>
       </c>
-      <c r="B31" s="156" t="s">
+      <c r="B31" s="130" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="157"/>
+      <c r="C31" s="131"/>
       <c r="D31" s="92" t="s">
         <v>80</v>
       </c>
       <c r="E31" s="35"/>
-      <c r="F31" s="119"/>
+      <c r="F31" s="135"/>
       <c r="G31" s="104"/>
       <c r="H31" s="104"/>
       <c r="I31" s="104"/>
@@ -11668,7 +11672,7 @@
         <v>118</v>
       </c>
       <c r="E32" s="35"/>
-      <c r="F32" s="119"/>
+      <c r="F32" s="135"/>
       <c r="G32" s="104"/>
       <c r="H32" s="104"/>
       <c r="I32" s="104"/>
@@ -11928,7 +11932,7 @@
         <v>118</v>
       </c>
       <c r="E33" s="35"/>
-      <c r="F33" s="119"/>
+      <c r="F33" s="135"/>
       <c r="G33" s="104"/>
       <c r="H33" s="104"/>
       <c r="I33" s="104"/>
@@ -12180,15 +12184,15 @@
       <c r="A34" s="37">
         <v>8</v>
       </c>
-      <c r="B34" s="156" t="s">
+      <c r="B34" s="130" t="s">
         <v>59</v>
       </c>
-      <c r="C34" s="157"/>
+      <c r="C34" s="131"/>
       <c r="D34" s="92" t="s">
         <v>99</v>
       </c>
       <c r="E34" s="40"/>
-      <c r="F34" s="119"/>
+      <c r="F34" s="135"/>
       <c r="G34" s="106"/>
       <c r="H34" s="106"/>
       <c r="I34" s="106"/>
@@ -12440,15 +12444,15 @@
       <c r="A35" s="37">
         <v>9</v>
       </c>
-      <c r="B35" s="156" t="s">
+      <c r="B35" s="130" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="157"/>
+      <c r="C35" s="131"/>
       <c r="D35" s="92" t="s">
         <v>49</v>
       </c>
       <c r="E35" s="40"/>
-      <c r="F35" s="120"/>
+      <c r="F35" s="136"/>
       <c r="G35" s="106"/>
       <c r="H35" s="106"/>
       <c r="I35" s="106"/>
@@ -12698,10 +12702,10 @@
     </row>
     <row r="36" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A36" s="37"/>
-      <c r="B36" s="154" t="s">
+      <c r="B36" s="137" t="s">
         <v>127</v>
       </c>
-      <c r="C36" s="155"/>
+      <c r="C36" s="138"/>
       <c r="D36" s="92"/>
       <c r="E36" s="40"/>
       <c r="F36" s="93"/>
@@ -12954,10 +12958,10 @@
     </row>
     <row r="37" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A37" s="37"/>
-      <c r="B37" s="156" t="s">
+      <c r="B37" s="130" t="s">
         <v>128</v>
       </c>
-      <c r="C37" s="157"/>
+      <c r="C37" s="131"/>
       <c r="D37" s="92"/>
       <c r="E37" s="40"/>
       <c r="F37" s="93"/>
@@ -13210,10 +13214,10 @@
     </row>
     <row r="38" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A38" s="37"/>
-      <c r="B38" s="170" t="s">
+      <c r="B38" s="132" t="s">
         <v>129</v>
       </c>
-      <c r="C38" s="171"/>
+      <c r="C38" s="133"/>
       <c r="D38" s="92"/>
       <c r="E38" s="40"/>
       <c r="F38" s="93"/>
@@ -13466,8 +13470,8 @@
     </row>
     <row r="39" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A39" s="37"/>
-      <c r="B39" s="170"/>
-      <c r="C39" s="171"/>
+      <c r="B39" s="132"/>
+      <c r="C39" s="133"/>
       <c r="D39" s="92"/>
       <c r="E39" s="40"/>
       <c r="F39" s="93"/>
@@ -13720,10 +13724,10 @@
     </row>
     <row r="40" spans="1:254" s="2" customFormat="1" ht="42" customHeight="1" thickBot="1">
       <c r="A40" s="41"/>
-      <c r="B40" s="168" t="s">
+      <c r="B40" s="128" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="169"/>
+      <c r="C40" s="129"/>
       <c r="D40" s="42" t="s">
         <v>16</v>
       </c>
@@ -13987,37 +13991,37 @@
         <v>96</v>
       </c>
       <c r="F41" s="75"/>
-      <c r="G41" s="162"/>
-      <c r="H41" s="162"/>
-      <c r="I41" s="162"/>
-      <c r="J41" s="162"/>
-      <c r="K41" s="162"/>
-      <c r="L41" s="162"/>
-      <c r="M41" s="162"/>
-      <c r="N41" s="162"/>
-      <c r="O41" s="162"/>
-      <c r="P41" s="162"/>
-      <c r="Q41" s="162"/>
-      <c r="R41" s="162"/>
-      <c r="S41" s="162"/>
-      <c r="T41" s="162"/>
-      <c r="U41" s="162"/>
-      <c r="V41" s="162"/>
-      <c r="W41" s="162"/>
-      <c r="X41" s="162"/>
-      <c r="Y41" s="162"/>
-      <c r="Z41" s="162"/>
-      <c r="AA41" s="163"/>
-      <c r="AB41" s="163"/>
-      <c r="AC41" s="163"/>
-      <c r="AD41" s="163"/>
-      <c r="AE41" s="163"/>
-      <c r="AF41" s="163"/>
-      <c r="AG41" s="163"/>
-      <c r="AH41" s="163"/>
-      <c r="AI41" s="163"/>
-      <c r="AJ41" s="163"/>
-      <c r="AK41" s="164"/>
+      <c r="G41" s="122"/>
+      <c r="H41" s="122"/>
+      <c r="I41" s="122"/>
+      <c r="J41" s="122"/>
+      <c r="K41" s="122"/>
+      <c r="L41" s="122"/>
+      <c r="M41" s="122"/>
+      <c r="N41" s="122"/>
+      <c r="O41" s="122"/>
+      <c r="P41" s="122"/>
+      <c r="Q41" s="122"/>
+      <c r="R41" s="122"/>
+      <c r="S41" s="122"/>
+      <c r="T41" s="122"/>
+      <c r="U41" s="122"/>
+      <c r="V41" s="122"/>
+      <c r="W41" s="122"/>
+      <c r="X41" s="122"/>
+      <c r="Y41" s="122"/>
+      <c r="Z41" s="122"/>
+      <c r="AA41" s="123"/>
+      <c r="AB41" s="123"/>
+      <c r="AC41" s="123"/>
+      <c r="AD41" s="123"/>
+      <c r="AE41" s="123"/>
+      <c r="AF41" s="123"/>
+      <c r="AG41" s="123"/>
+      <c r="AH41" s="123"/>
+      <c r="AI41" s="123"/>
+      <c r="AJ41" s="123"/>
+      <c r="AK41" s="124"/>
     </row>
     <row r="42" spans="1:254" ht="23" customHeight="1">
       <c r="A42" s="45"/>
@@ -14028,37 +14032,37 @@
         <v>97</v>
       </c>
       <c r="F42" s="77"/>
-      <c r="G42" s="165"/>
-      <c r="H42" s="165"/>
-      <c r="I42" s="165"/>
-      <c r="J42" s="165"/>
-      <c r="K42" s="165"/>
-      <c r="L42" s="165"/>
-      <c r="M42" s="165"/>
-      <c r="N42" s="165"/>
-      <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
-      <c r="Q42" s="167"/>
-      <c r="R42" s="167"/>
-      <c r="S42" s="167"/>
-      <c r="T42" s="167"/>
-      <c r="U42" s="167"/>
-      <c r="V42" s="167"/>
-      <c r="W42" s="167"/>
-      <c r="X42" s="167"/>
-      <c r="Y42" s="167"/>
-      <c r="Z42" s="167"/>
-      <c r="AA42" s="165"/>
-      <c r="AB42" s="165"/>
-      <c r="AC42" s="165"/>
-      <c r="AD42" s="165"/>
-      <c r="AE42" s="165"/>
-      <c r="AF42" s="165"/>
-      <c r="AG42" s="165"/>
-      <c r="AH42" s="165"/>
-      <c r="AI42" s="165"/>
-      <c r="AJ42" s="165"/>
-      <c r="AK42" s="166"/>
+      <c r="G42" s="125"/>
+      <c r="H42" s="125"/>
+      <c r="I42" s="125"/>
+      <c r="J42" s="125"/>
+      <c r="K42" s="125"/>
+      <c r="L42" s="125"/>
+      <c r="M42" s="125"/>
+      <c r="N42" s="125"/>
+      <c r="O42" s="125"/>
+      <c r="P42" s="125"/>
+      <c r="Q42" s="127"/>
+      <c r="R42" s="127"/>
+      <c r="S42" s="127"/>
+      <c r="T42" s="127"/>
+      <c r="U42" s="127"/>
+      <c r="V42" s="127"/>
+      <c r="W42" s="127"/>
+      <c r="X42" s="127"/>
+      <c r="Y42" s="127"/>
+      <c r="Z42" s="127"/>
+      <c r="AA42" s="125"/>
+      <c r="AB42" s="125"/>
+      <c r="AC42" s="125"/>
+      <c r="AD42" s="125"/>
+      <c r="AE42" s="125"/>
+      <c r="AF42" s="125"/>
+      <c r="AG42" s="125"/>
+      <c r="AH42" s="125"/>
+      <c r="AI42" s="125"/>
+      <c r="AJ42" s="125"/>
+      <c r="AK42" s="126"/>
     </row>
     <row r="43" spans="1:254" ht="23" customHeight="1" thickBot="1">
       <c r="A43" s="49"/>
@@ -14069,37 +14073,37 @@
         <v>98</v>
       </c>
       <c r="F43" s="82"/>
-      <c r="G43" s="159"/>
-      <c r="H43" s="159"/>
-      <c r="I43" s="159"/>
-      <c r="J43" s="159"/>
-      <c r="K43" s="159"/>
-      <c r="L43" s="159"/>
-      <c r="M43" s="159"/>
-      <c r="N43" s="159"/>
-      <c r="O43" s="159"/>
-      <c r="P43" s="159"/>
-      <c r="Q43" s="161"/>
-      <c r="R43" s="161"/>
-      <c r="S43" s="161"/>
-      <c r="T43" s="161"/>
-      <c r="U43" s="161"/>
-      <c r="V43" s="161"/>
-      <c r="W43" s="161"/>
-      <c r="X43" s="161"/>
-      <c r="Y43" s="161"/>
-      <c r="Z43" s="161"/>
-      <c r="AA43" s="159"/>
-      <c r="AB43" s="159"/>
-      <c r="AC43" s="159"/>
-      <c r="AD43" s="159"/>
-      <c r="AE43" s="159"/>
-      <c r="AF43" s="159"/>
-      <c r="AG43" s="159"/>
-      <c r="AH43" s="159"/>
-      <c r="AI43" s="159"/>
-      <c r="AJ43" s="159"/>
-      <c r="AK43" s="160"/>
+      <c r="G43" s="119"/>
+      <c r="H43" s="119"/>
+      <c r="I43" s="119"/>
+      <c r="J43" s="119"/>
+      <c r="K43" s="119"/>
+      <c r="L43" s="119"/>
+      <c r="M43" s="119"/>
+      <c r="N43" s="119"/>
+      <c r="O43" s="119"/>
+      <c r="P43" s="119"/>
+      <c r="Q43" s="121"/>
+      <c r="R43" s="121"/>
+      <c r="S43" s="121"/>
+      <c r="T43" s="121"/>
+      <c r="U43" s="121"/>
+      <c r="V43" s="121"/>
+      <c r="W43" s="121"/>
+      <c r="X43" s="121"/>
+      <c r="Y43" s="121"/>
+      <c r="Z43" s="121"/>
+      <c r="AA43" s="119"/>
+      <c r="AB43" s="119"/>
+      <c r="AC43" s="119"/>
+      <c r="AD43" s="119"/>
+      <c r="AE43" s="119"/>
+      <c r="AF43" s="119"/>
+      <c r="AG43" s="119"/>
+      <c r="AH43" s="119"/>
+      <c r="AI43" s="119"/>
+      <c r="AJ43" s="119"/>
+      <c r="AK43" s="120"/>
     </row>
     <row r="44" spans="1:254">
       <c r="A44" s="52"/>
@@ -14115,6 +14119,50 @@
     </row>
   </sheetData>
   <mergeCells count="60">
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:AK1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="T3:AK3"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="T4:Y4"/>
+    <mergeCell ref="AH4:AK4"/>
+    <mergeCell ref="T5:V7"/>
+    <mergeCell ref="W5:Y7"/>
+    <mergeCell ref="AH5:AK7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="Z4:AC4"/>
+    <mergeCell ref="AD4:AG4"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="F12:F21"/>
+    <mergeCell ref="F27:F35"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B24:C24"/>
@@ -14131,59 +14179,18 @@
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="G41:P41"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="F12:F21"/>
-    <mergeCell ref="F27:F35"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="W5:Y7"/>
-    <mergeCell ref="AH5:AK7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="Z4:AC4"/>
-    <mergeCell ref="AD4:AG4"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="F1:AK1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="T3:AK3"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="T4:Y4"/>
-    <mergeCell ref="AH4:AK4"/>
-    <mergeCell ref="T5:V7"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="G9:AK10">
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>TEXT(G9,"aaa")="日"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>TEXT(G9,"aaa")="土"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:AK40">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>G$11="－"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14208,40 +14215,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:254" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="155" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="121"/>
+      <c r="B1" s="155"/>
       <c r="C1" s="85"/>
-      <c r="F1" s="122" t="s">
+      <c r="F1" s="156" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
-      <c r="AC1" s="122"/>
-      <c r="AD1" s="122"/>
-      <c r="AE1" s="122"/>
-      <c r="AF1" s="122"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+      <c r="L1" s="156"/>
+      <c r="M1" s="156"/>
+      <c r="N1" s="156"/>
+      <c r="O1" s="156"/>
+      <c r="P1" s="156"/>
+      <c r="Q1" s="156"/>
+      <c r="R1" s="156"/>
+      <c r="S1" s="156"/>
+      <c r="T1" s="156"/>
+      <c r="U1" s="156"/>
+      <c r="V1" s="156"/>
+      <c r="W1" s="156"/>
+      <c r="X1" s="156"/>
+      <c r="Y1" s="156"/>
+      <c r="Z1" s="156"/>
+      <c r="AA1" s="156"/>
+      <c r="AB1" s="156"/>
+      <c r="AC1" s="156"/>
+      <c r="AD1" s="156"/>
+      <c r="AE1" s="156"/>
+      <c r="AF1" s="156"/>
       <c r="AI1" s="3"/>
       <c r="AJ1" s="3"/>
       <c r="AK1" s="3"/>
@@ -14707,47 +14714,47 @@
       <c r="IO2" s="3"/>
     </row>
     <row r="3" spans="1:254" s="2" customFormat="1" ht="20" customHeight="1" thickBot="1">
-      <c r="A3" s="123" t="s">
+      <c r="A3" s="157" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="125"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="159"/>
       <c r="E3" s="94"/>
       <c r="G3" s="51"/>
       <c r="H3" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="126" t="s">
+      <c r="K3" s="160" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="126"/>
-      <c r="M3" s="126" t="s">
+      <c r="L3" s="160"/>
+      <c r="M3" s="160" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="126"/>
-      <c r="O3" s="126"/>
-      <c r="P3" s="126" t="s">
+      <c r="N3" s="160"/>
+      <c r="O3" s="160"/>
+      <c r="P3" s="160" t="s">
         <v>2</v>
       </c>
-      <c r="Q3" s="126"/>
-      <c r="R3" s="126"/>
+      <c r="Q3" s="160"/>
+      <c r="R3" s="160"/>
       <c r="S3" s="3"/>
-      <c r="T3" s="127" t="s">
+      <c r="T3" s="161" t="s">
         <v>3</v>
       </c>
-      <c r="U3" s="128"/>
-      <c r="V3" s="128"/>
-      <c r="W3" s="128"/>
-      <c r="X3" s="128"/>
-      <c r="Y3" s="128"/>
-      <c r="Z3" s="128"/>
-      <c r="AA3" s="128"/>
-      <c r="AB3" s="128"/>
-      <c r="AC3" s="128"/>
-      <c r="AD3" s="128"/>
-      <c r="AE3" s="128"/>
-      <c r="AF3" s="129"/>
+      <c r="U3" s="162"/>
+      <c r="V3" s="162"/>
+      <c r="W3" s="162"/>
+      <c r="X3" s="162"/>
+      <c r="Y3" s="162"/>
+      <c r="Z3" s="162"/>
+      <c r="AA3" s="162"/>
+      <c r="AB3" s="162"/>
+      <c r="AC3" s="162"/>
+      <c r="AD3" s="162"/>
+      <c r="AE3" s="162"/>
+      <c r="AF3" s="163"/>
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
       <c r="AK3" s="3"/>
@@ -14976,42 +14983,42 @@
       <c r="H4" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="126" t="s">
+      <c r="K4" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="126"/>
-      <c r="M4" s="132">
+      <c r="L4" s="160"/>
+      <c r="M4" s="166">
         <v>46113</v>
       </c>
-      <c r="N4" s="132"/>
-      <c r="O4" s="132"/>
-      <c r="P4" s="126" t="s">
+      <c r="N4" s="166"/>
+      <c r="O4" s="166"/>
+      <c r="P4" s="160" t="s">
         <v>50</v>
       </c>
-      <c r="Q4" s="126"/>
-      <c r="R4" s="126"/>
+      <c r="Q4" s="160"/>
+      <c r="R4" s="160"/>
       <c r="S4" s="3"/>
-      <c r="T4" s="133" t="s">
+      <c r="T4" s="152" t="s">
         <v>5</v>
       </c>
-      <c r="U4" s="134"/>
-      <c r="V4" s="134"/>
-      <c r="W4" s="135"/>
-      <c r="X4" s="133" t="s">
+      <c r="U4" s="153"/>
+      <c r="V4" s="153"/>
+      <c r="W4" s="154"/>
+      <c r="X4" s="152" t="s">
         <v>6</v>
       </c>
-      <c r="Y4" s="134"/>
-      <c r="Z4" s="135"/>
-      <c r="AA4" s="133" t="s">
+      <c r="Y4" s="153"/>
+      <c r="Z4" s="154"/>
+      <c r="AA4" s="152" t="s">
         <v>7</v>
       </c>
-      <c r="AB4" s="134"/>
-      <c r="AC4" s="135"/>
-      <c r="AD4" s="133" t="s">
+      <c r="AB4" s="153"/>
+      <c r="AC4" s="154"/>
+      <c r="AD4" s="152" t="s">
         <v>8</v>
       </c>
-      <c r="AE4" s="134"/>
-      <c r="AF4" s="135"/>
+      <c r="AE4" s="153"/>
+      <c r="AF4" s="154"/>
       <c r="AI4" s="3"/>
       <c r="AJ4" s="3"/>
       <c r="AK4" s="3"/>
@@ -15239,21 +15246,21 @@
         <v>23</v>
       </c>
       <c r="S5" s="3"/>
-      <c r="T5" s="183" t="s">
+      <c r="T5" s="172" t="s">
         <v>64</v>
       </c>
-      <c r="U5" s="184"/>
-      <c r="V5" s="184"/>
-      <c r="W5" s="185"/>
+      <c r="U5" s="173"/>
+      <c r="V5" s="173"/>
+      <c r="W5" s="174"/>
       <c r="X5" s="11"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="12"/>
       <c r="AA5" s="11"/>
       <c r="AB5" s="3"/>
       <c r="AC5" s="12"/>
-      <c r="AD5" s="146"/>
-      <c r="AE5" s="147"/>
-      <c r="AF5" s="148"/>
+      <c r="AD5" s="144"/>
+      <c r="AE5" s="145"/>
+      <c r="AF5" s="146"/>
       <c r="AI5" s="3"/>
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3"/>
@@ -15485,19 +15492,19 @@
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
-      <c r="T6" s="183"/>
-      <c r="U6" s="184"/>
-      <c r="V6" s="184"/>
-      <c r="W6" s="185"/>
+      <c r="T6" s="172"/>
+      <c r="U6" s="173"/>
+      <c r="V6" s="173"/>
+      <c r="W6" s="174"/>
       <c r="X6" s="11"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="12"/>
       <c r="AA6" s="11"/>
       <c r="AB6" s="3"/>
       <c r="AC6" s="12"/>
-      <c r="AD6" s="146"/>
-      <c r="AE6" s="147"/>
-      <c r="AF6" s="148"/>
+      <c r="AD6" s="144"/>
+      <c r="AE6" s="145"/>
+      <c r="AF6" s="146"/>
       <c r="AI6" s="3"/>
       <c r="AJ6" s="3"/>
       <c r="AK6" s="3"/>
@@ -15729,19 +15736,19 @@
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
-      <c r="T7" s="186"/>
-      <c r="U7" s="187"/>
-      <c r="V7" s="187"/>
-      <c r="W7" s="188"/>
+      <c r="T7" s="175"/>
+      <c r="U7" s="176"/>
+      <c r="V7" s="176"/>
+      <c r="W7" s="177"/>
       <c r="X7" s="21"/>
       <c r="Y7" s="22"/>
       <c r="Z7" s="23"/>
       <c r="AA7" s="21"/>
       <c r="AB7" s="22"/>
       <c r="AC7" s="23"/>
-      <c r="AD7" s="149"/>
-      <c r="AE7" s="150"/>
-      <c r="AF7" s="151"/>
+      <c r="AD7" s="147"/>
+      <c r="AE7" s="148"/>
+      <c r="AF7" s="149"/>
       <c r="AG7" s="86"/>
       <c r="AI7" s="3"/>
       <c r="AJ7" s="3"/>
@@ -16258,22 +16265,22 @@
       <c r="R9" s="97" t="s">
         <v>76</v>
       </c>
-      <c r="S9" s="176" t="s">
+      <c r="S9" s="191" t="s">
         <v>78</v>
       </c>
-      <c r="T9" s="177"/>
-      <c r="U9" s="177"/>
-      <c r="V9" s="177"/>
-      <c r="W9" s="177"/>
-      <c r="X9" s="177"/>
-      <c r="Y9" s="177"/>
-      <c r="Z9" s="177"/>
-      <c r="AA9" s="177"/>
-      <c r="AB9" s="177"/>
-      <c r="AC9" s="177"/>
-      <c r="AD9" s="177"/>
-      <c r="AE9" s="177"/>
-      <c r="AF9" s="178"/>
+      <c r="T9" s="192"/>
+      <c r="U9" s="192"/>
+      <c r="V9" s="192"/>
+      <c r="W9" s="192"/>
+      <c r="X9" s="192"/>
+      <c r="Y9" s="192"/>
+      <c r="Z9" s="192"/>
+      <c r="AA9" s="192"/>
+      <c r="AB9" s="192"/>
+      <c r="AC9" s="192"/>
+      <c r="AD9" s="192"/>
+      <c r="AE9" s="192"/>
+      <c r="AF9" s="193"/>
       <c r="AI9" s="3"/>
       <c r="AJ9" s="3"/>
       <c r="AK9" s="3"/>
@@ -16492,8 +16499,8 @@
     </row>
     <row r="10" spans="1:254" s="2" customFormat="1" ht="23" hidden="1" customHeight="1">
       <c r="A10" s="29"/>
-      <c r="B10" s="152"/>
-      <c r="C10" s="153"/>
+      <c r="B10" s="150"/>
+      <c r="C10" s="151"/>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="31"/>
@@ -16819,10 +16826,10 @@
     </row>
     <row r="11" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A11" s="37"/>
-      <c r="B11" s="154" t="s">
+      <c r="B11" s="137" t="s">
         <v>105</v>
       </c>
-      <c r="C11" s="155"/>
+      <c r="C11" s="138"/>
       <c r="D11" s="92"/>
       <c r="E11" s="40"/>
       <c r="F11" s="93"/>
@@ -16838,20 +16845,20 @@
       <c r="P11" s="69"/>
       <c r="Q11" s="69"/>
       <c r="R11" s="69"/>
-      <c r="S11" s="191"/>
-      <c r="T11" s="192"/>
-      <c r="U11" s="192"/>
-      <c r="V11" s="192"/>
-      <c r="W11" s="192"/>
-      <c r="X11" s="192"/>
-      <c r="Y11" s="192"/>
-      <c r="Z11" s="192"/>
-      <c r="AA11" s="192"/>
-      <c r="AB11" s="192"/>
-      <c r="AC11" s="192"/>
-      <c r="AD11" s="192"/>
-      <c r="AE11" s="192"/>
-      <c r="AF11" s="193"/>
+      <c r="S11" s="180"/>
+      <c r="T11" s="181"/>
+      <c r="U11" s="181"/>
+      <c r="V11" s="181"/>
+      <c r="W11" s="181"/>
+      <c r="X11" s="181"/>
+      <c r="Y11" s="181"/>
+      <c r="Z11" s="181"/>
+      <c r="AA11" s="181"/>
+      <c r="AB11" s="181"/>
+      <c r="AC11" s="181"/>
+      <c r="AD11" s="181"/>
+      <c r="AE11" s="181"/>
+      <c r="AF11" s="182"/>
       <c r="AG11" s="69"/>
       <c r="AH11" s="69"/>
       <c r="AI11" s="69"/>
@@ -17077,10 +17084,10 @@
       <c r="A12" s="37">
         <v>1</v>
       </c>
-      <c r="B12" s="170" t="s">
+      <c r="B12" s="132" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="171"/>
+      <c r="C12" s="133"/>
       <c r="D12" s="92" t="s">
         <v>108</v>
       </c>
@@ -17098,20 +17105,20 @@
       <c r="P12" s="69"/>
       <c r="Q12" s="69"/>
       <c r="R12" s="69"/>
-      <c r="S12" s="172"/>
-      <c r="T12" s="173"/>
-      <c r="U12" s="173"/>
-      <c r="V12" s="173"/>
-      <c r="W12" s="173"/>
-      <c r="X12" s="173"/>
-      <c r="Y12" s="173"/>
-      <c r="Z12" s="173"/>
-      <c r="AA12" s="173"/>
-      <c r="AB12" s="173"/>
-      <c r="AC12" s="173"/>
-      <c r="AD12" s="173"/>
-      <c r="AE12" s="173"/>
-      <c r="AF12" s="174"/>
+      <c r="S12" s="183"/>
+      <c r="T12" s="184"/>
+      <c r="U12" s="184"/>
+      <c r="V12" s="184"/>
+      <c r="W12" s="184"/>
+      <c r="X12" s="184"/>
+      <c r="Y12" s="184"/>
+      <c r="Z12" s="184"/>
+      <c r="AA12" s="184"/>
+      <c r="AB12" s="184"/>
+      <c r="AC12" s="184"/>
+      <c r="AD12" s="184"/>
+      <c r="AE12" s="184"/>
+      <c r="AF12" s="185"/>
       <c r="AG12" s="69"/>
       <c r="AH12" s="69"/>
       <c r="AI12" s="69"/>
@@ -17337,10 +17344,10 @@
       <c r="A13" s="37">
         <v>2</v>
       </c>
-      <c r="B13" s="170" t="s">
+      <c r="B13" s="132" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="171"/>
+      <c r="C13" s="133"/>
       <c r="D13" s="92" t="s">
         <v>107</v>
       </c>
@@ -17358,20 +17365,20 @@
       <c r="P13" s="69"/>
       <c r="Q13" s="69"/>
       <c r="R13" s="69"/>
-      <c r="S13" s="172"/>
-      <c r="T13" s="173"/>
-      <c r="U13" s="173"/>
-      <c r="V13" s="173"/>
-      <c r="W13" s="173"/>
-      <c r="X13" s="173"/>
-      <c r="Y13" s="173"/>
-      <c r="Z13" s="173"/>
-      <c r="AA13" s="173"/>
-      <c r="AB13" s="173"/>
-      <c r="AC13" s="173"/>
-      <c r="AD13" s="173"/>
-      <c r="AE13" s="173"/>
-      <c r="AF13" s="174"/>
+      <c r="S13" s="183"/>
+      <c r="T13" s="184"/>
+      <c r="U13" s="184"/>
+      <c r="V13" s="184"/>
+      <c r="W13" s="184"/>
+      <c r="X13" s="184"/>
+      <c r="Y13" s="184"/>
+      <c r="Z13" s="184"/>
+      <c r="AA13" s="184"/>
+      <c r="AB13" s="184"/>
+      <c r="AC13" s="184"/>
+      <c r="AD13" s="184"/>
+      <c r="AE13" s="184"/>
+      <c r="AF13" s="185"/>
       <c r="AG13" s="69"/>
       <c r="AH13" s="69"/>
       <c r="AI13" s="69"/>
@@ -17597,10 +17604,10 @@
       <c r="A14" s="37">
         <v>3</v>
       </c>
-      <c r="B14" s="170" t="s">
+      <c r="B14" s="132" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="171"/>
+      <c r="C14" s="133"/>
       <c r="D14" s="92" t="s">
         <v>107</v>
       </c>
@@ -17618,20 +17625,20 @@
       <c r="P14" s="69"/>
       <c r="Q14" s="69"/>
       <c r="R14" s="69"/>
-      <c r="S14" s="172"/>
-      <c r="T14" s="173"/>
-      <c r="U14" s="173"/>
-      <c r="V14" s="173"/>
-      <c r="W14" s="173"/>
-      <c r="X14" s="173"/>
-      <c r="Y14" s="173"/>
-      <c r="Z14" s="173"/>
-      <c r="AA14" s="173"/>
-      <c r="AB14" s="173"/>
-      <c r="AC14" s="173"/>
-      <c r="AD14" s="173"/>
-      <c r="AE14" s="173"/>
-      <c r="AF14" s="174"/>
+      <c r="S14" s="183"/>
+      <c r="T14" s="184"/>
+      <c r="U14" s="184"/>
+      <c r="V14" s="184"/>
+      <c r="W14" s="184"/>
+      <c r="X14" s="184"/>
+      <c r="Y14" s="184"/>
+      <c r="Z14" s="184"/>
+      <c r="AA14" s="184"/>
+      <c r="AB14" s="184"/>
+      <c r="AC14" s="184"/>
+      <c r="AD14" s="184"/>
+      <c r="AE14" s="184"/>
+      <c r="AF14" s="185"/>
       <c r="AG14" s="69"/>
       <c r="AH14" s="69"/>
       <c r="AI14" s="69"/>
@@ -17857,10 +17864,10 @@
       <c r="A15" s="37">
         <v>4</v>
       </c>
-      <c r="B15" s="170" t="s">
+      <c r="B15" s="132" t="s">
         <v>82</v>
       </c>
-      <c r="C15" s="171"/>
+      <c r="C15" s="133"/>
       <c r="D15" s="92" t="s">
         <v>108</v>
       </c>
@@ -17878,20 +17885,20 @@
       <c r="P15" s="69"/>
       <c r="Q15" s="69"/>
       <c r="R15" s="69"/>
-      <c r="S15" s="172"/>
-      <c r="T15" s="173"/>
-      <c r="U15" s="173"/>
-      <c r="V15" s="173"/>
-      <c r="W15" s="173"/>
-      <c r="X15" s="173"/>
-      <c r="Y15" s="173"/>
-      <c r="Z15" s="173"/>
-      <c r="AA15" s="173"/>
-      <c r="AB15" s="173"/>
-      <c r="AC15" s="173"/>
-      <c r="AD15" s="173"/>
-      <c r="AE15" s="173"/>
-      <c r="AF15" s="174"/>
+      <c r="S15" s="183"/>
+      <c r="T15" s="184"/>
+      <c r="U15" s="184"/>
+      <c r="V15" s="184"/>
+      <c r="W15" s="184"/>
+      <c r="X15" s="184"/>
+      <c r="Y15" s="184"/>
+      <c r="Z15" s="184"/>
+      <c r="AA15" s="184"/>
+      <c r="AB15" s="184"/>
+      <c r="AC15" s="184"/>
+      <c r="AD15" s="184"/>
+      <c r="AE15" s="184"/>
+      <c r="AF15" s="185"/>
       <c r="AG15" s="69"/>
       <c r="AH15" s="69"/>
       <c r="AI15" s="69"/>
@@ -18117,10 +18124,10 @@
       <c r="A16" s="37">
         <v>5</v>
       </c>
-      <c r="B16" s="170" t="s">
+      <c r="B16" s="132" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="171"/>
+      <c r="C16" s="133"/>
       <c r="D16" s="92" t="s">
         <v>108</v>
       </c>
@@ -18138,20 +18145,20 @@
       <c r="P16" s="69"/>
       <c r="Q16" s="69"/>
       <c r="R16" s="69"/>
-      <c r="S16" s="172"/>
-      <c r="T16" s="173"/>
-      <c r="U16" s="173"/>
-      <c r="V16" s="173"/>
-      <c r="W16" s="173"/>
-      <c r="X16" s="173"/>
-      <c r="Y16" s="173"/>
-      <c r="Z16" s="173"/>
-      <c r="AA16" s="173"/>
-      <c r="AB16" s="173"/>
-      <c r="AC16" s="173"/>
-      <c r="AD16" s="173"/>
-      <c r="AE16" s="173"/>
-      <c r="AF16" s="174"/>
+      <c r="S16" s="183"/>
+      <c r="T16" s="184"/>
+      <c r="U16" s="184"/>
+      <c r="V16" s="184"/>
+      <c r="W16" s="184"/>
+      <c r="X16" s="184"/>
+      <c r="Y16" s="184"/>
+      <c r="Z16" s="184"/>
+      <c r="AA16" s="184"/>
+      <c r="AB16" s="184"/>
+      <c r="AC16" s="184"/>
+      <c r="AD16" s="184"/>
+      <c r="AE16" s="184"/>
+      <c r="AF16" s="185"/>
       <c r="AG16" s="69"/>
       <c r="AH16" s="69"/>
       <c r="AI16" s="69"/>
@@ -18377,10 +18384,10 @@
       <c r="A17" s="37">
         <v>6</v>
       </c>
-      <c r="B17" s="170" t="s">
+      <c r="B17" s="132" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="171"/>
+      <c r="C17" s="133"/>
       <c r="D17" s="92" t="s">
         <v>108</v>
       </c>
@@ -18398,20 +18405,20 @@
       <c r="P17" s="69"/>
       <c r="Q17" s="69"/>
       <c r="R17" s="69"/>
-      <c r="S17" s="172"/>
-      <c r="T17" s="173"/>
-      <c r="U17" s="173"/>
-      <c r="V17" s="173"/>
-      <c r="W17" s="173"/>
-      <c r="X17" s="173"/>
-      <c r="Y17" s="173"/>
-      <c r="Z17" s="173"/>
-      <c r="AA17" s="173"/>
-      <c r="AB17" s="173"/>
-      <c r="AC17" s="173"/>
-      <c r="AD17" s="173"/>
-      <c r="AE17" s="173"/>
-      <c r="AF17" s="174"/>
+      <c r="S17" s="183"/>
+      <c r="T17" s="184"/>
+      <c r="U17" s="184"/>
+      <c r="V17" s="184"/>
+      <c r="W17" s="184"/>
+      <c r="X17" s="184"/>
+      <c r="Y17" s="184"/>
+      <c r="Z17" s="184"/>
+      <c r="AA17" s="184"/>
+      <c r="AB17" s="184"/>
+      <c r="AC17" s="184"/>
+      <c r="AD17" s="184"/>
+      <c r="AE17" s="184"/>
+      <c r="AF17" s="185"/>
       <c r="AG17" s="69"/>
       <c r="AH17" s="69"/>
       <c r="AI17" s="69"/>
@@ -18637,10 +18644,10 @@
       <c r="A18" s="37">
         <v>7</v>
       </c>
-      <c r="B18" s="170" t="s">
+      <c r="B18" s="132" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="171"/>
+      <c r="C18" s="133"/>
       <c r="D18" s="92" t="s">
         <v>108</v>
       </c>
@@ -18658,20 +18665,20 @@
       <c r="P18" s="69"/>
       <c r="Q18" s="69"/>
       <c r="R18" s="69"/>
-      <c r="S18" s="172"/>
-      <c r="T18" s="173"/>
-      <c r="U18" s="173"/>
-      <c r="V18" s="173"/>
-      <c r="W18" s="173"/>
-      <c r="X18" s="173"/>
-      <c r="Y18" s="173"/>
-      <c r="Z18" s="173"/>
-      <c r="AA18" s="173"/>
-      <c r="AB18" s="173"/>
-      <c r="AC18" s="173"/>
-      <c r="AD18" s="173"/>
-      <c r="AE18" s="173"/>
-      <c r="AF18" s="174"/>
+      <c r="S18" s="183"/>
+      <c r="T18" s="184"/>
+      <c r="U18" s="184"/>
+      <c r="V18" s="184"/>
+      <c r="W18" s="184"/>
+      <c r="X18" s="184"/>
+      <c r="Y18" s="184"/>
+      <c r="Z18" s="184"/>
+      <c r="AA18" s="184"/>
+      <c r="AB18" s="184"/>
+      <c r="AC18" s="184"/>
+      <c r="AD18" s="184"/>
+      <c r="AE18" s="184"/>
+      <c r="AF18" s="185"/>
       <c r="AG18" s="69"/>
       <c r="AH18" s="69"/>
       <c r="AI18" s="69"/>
@@ -18897,10 +18904,10 @@
       <c r="A19" s="37">
         <v>8</v>
       </c>
-      <c r="B19" s="170" t="s">
+      <c r="B19" s="132" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="171"/>
+      <c r="C19" s="133"/>
       <c r="D19" s="92" t="s">
         <v>108</v>
       </c>
@@ -18918,20 +18925,20 @@
       <c r="P19" s="69"/>
       <c r="Q19" s="69"/>
       <c r="R19" s="69"/>
-      <c r="S19" s="172"/>
-      <c r="T19" s="173"/>
-      <c r="U19" s="173"/>
-      <c r="V19" s="173"/>
-      <c r="W19" s="173"/>
-      <c r="X19" s="173"/>
-      <c r="Y19" s="173"/>
-      <c r="Z19" s="173"/>
-      <c r="AA19" s="173"/>
-      <c r="AB19" s="173"/>
-      <c r="AC19" s="173"/>
-      <c r="AD19" s="173"/>
-      <c r="AE19" s="173"/>
-      <c r="AF19" s="174"/>
+      <c r="S19" s="183"/>
+      <c r="T19" s="184"/>
+      <c r="U19" s="184"/>
+      <c r="V19" s="184"/>
+      <c r="W19" s="184"/>
+      <c r="X19" s="184"/>
+      <c r="Y19" s="184"/>
+      <c r="Z19" s="184"/>
+      <c r="AA19" s="184"/>
+      <c r="AB19" s="184"/>
+      <c r="AC19" s="184"/>
+      <c r="AD19" s="184"/>
+      <c r="AE19" s="184"/>
+      <c r="AF19" s="185"/>
       <c r="AG19" s="69"/>
       <c r="AH19" s="69"/>
       <c r="AI19" s="69"/>
@@ -19155,10 +19162,10 @@
     </row>
     <row r="20" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A20" s="34"/>
-      <c r="B20" s="189" t="s">
+      <c r="B20" s="178" t="s">
         <v>120</v>
       </c>
-      <c r="C20" s="190"/>
+      <c r="C20" s="179"/>
       <c r="D20" s="35"/>
       <c r="E20" s="35"/>
       <c r="F20" s="36"/>
@@ -19174,20 +19181,20 @@
       <c r="P20" s="68"/>
       <c r="Q20" s="68"/>
       <c r="R20" s="68"/>
-      <c r="S20" s="172"/>
-      <c r="T20" s="173"/>
-      <c r="U20" s="173"/>
-      <c r="V20" s="173"/>
-      <c r="W20" s="173"/>
-      <c r="X20" s="173"/>
-      <c r="Y20" s="173"/>
-      <c r="Z20" s="173"/>
-      <c r="AA20" s="173"/>
-      <c r="AB20" s="173"/>
-      <c r="AC20" s="173"/>
-      <c r="AD20" s="173"/>
-      <c r="AE20" s="173"/>
-      <c r="AF20" s="174"/>
+      <c r="S20" s="183"/>
+      <c r="T20" s="184"/>
+      <c r="U20" s="184"/>
+      <c r="V20" s="184"/>
+      <c r="W20" s="184"/>
+      <c r="X20" s="184"/>
+      <c r="Y20" s="184"/>
+      <c r="Z20" s="184"/>
+      <c r="AA20" s="184"/>
+      <c r="AB20" s="184"/>
+      <c r="AC20" s="184"/>
+      <c r="AD20" s="184"/>
+      <c r="AE20" s="184"/>
+      <c r="AF20" s="185"/>
       <c r="AI20" s="3"/>
       <c r="AJ20" s="3"/>
       <c r="AK20" s="3"/>
@@ -19429,20 +19436,20 @@
       <c r="P21" s="69"/>
       <c r="Q21" s="69"/>
       <c r="R21" s="69"/>
-      <c r="S21" s="172"/>
-      <c r="T21" s="173"/>
-      <c r="U21" s="173"/>
-      <c r="V21" s="173"/>
-      <c r="W21" s="173"/>
-      <c r="X21" s="173"/>
-      <c r="Y21" s="173"/>
-      <c r="Z21" s="173"/>
-      <c r="AA21" s="173"/>
-      <c r="AB21" s="173"/>
-      <c r="AC21" s="173"/>
-      <c r="AD21" s="173"/>
-      <c r="AE21" s="173"/>
-      <c r="AF21" s="174"/>
+      <c r="S21" s="183"/>
+      <c r="T21" s="184"/>
+      <c r="U21" s="184"/>
+      <c r="V21" s="184"/>
+      <c r="W21" s="184"/>
+      <c r="X21" s="184"/>
+      <c r="Y21" s="184"/>
+      <c r="Z21" s="184"/>
+      <c r="AA21" s="184"/>
+      <c r="AB21" s="184"/>
+      <c r="AC21" s="184"/>
+      <c r="AD21" s="184"/>
+      <c r="AE21" s="184"/>
+      <c r="AF21" s="185"/>
       <c r="AI21" s="3"/>
       <c r="AJ21" s="3"/>
       <c r="AK21" s="3"/>
@@ -19684,20 +19691,20 @@
       <c r="P22" s="69"/>
       <c r="Q22" s="69"/>
       <c r="R22" s="69"/>
-      <c r="S22" s="172"/>
-      <c r="T22" s="173"/>
-      <c r="U22" s="173"/>
-      <c r="V22" s="173"/>
-      <c r="W22" s="173"/>
-      <c r="X22" s="173"/>
-      <c r="Y22" s="173"/>
-      <c r="Z22" s="173"/>
-      <c r="AA22" s="173"/>
-      <c r="AB22" s="173"/>
-      <c r="AC22" s="173"/>
-      <c r="AD22" s="173"/>
-      <c r="AE22" s="173"/>
-      <c r="AF22" s="174"/>
+      <c r="S22" s="183"/>
+      <c r="T22" s="184"/>
+      <c r="U22" s="184"/>
+      <c r="V22" s="184"/>
+      <c r="W22" s="184"/>
+      <c r="X22" s="184"/>
+      <c r="Y22" s="184"/>
+      <c r="Z22" s="184"/>
+      <c r="AA22" s="184"/>
+      <c r="AB22" s="184"/>
+      <c r="AC22" s="184"/>
+      <c r="AD22" s="184"/>
+      <c r="AE22" s="184"/>
+      <c r="AF22" s="185"/>
       <c r="AI22" s="3"/>
       <c r="AJ22" s="3"/>
       <c r="AK22" s="3"/>
@@ -19918,10 +19925,10 @@
       <c r="A23" s="101" t="s">
         <v>111</v>
       </c>
-      <c r="B23" s="181" t="s">
+      <c r="B23" s="186" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="182"/>
+      <c r="C23" s="187"/>
       <c r="D23" s="92" t="s">
         <v>110</v>
       </c>
@@ -19941,20 +19948,20 @@
       <c r="P23" s="69"/>
       <c r="Q23" s="69"/>
       <c r="R23" s="69"/>
-      <c r="S23" s="172"/>
-      <c r="T23" s="173"/>
-      <c r="U23" s="173"/>
-      <c r="V23" s="173"/>
-      <c r="W23" s="173"/>
-      <c r="X23" s="173"/>
-      <c r="Y23" s="173"/>
-      <c r="Z23" s="173"/>
-      <c r="AA23" s="173"/>
-      <c r="AB23" s="173"/>
-      <c r="AC23" s="173"/>
-      <c r="AD23" s="173"/>
-      <c r="AE23" s="173"/>
-      <c r="AF23" s="174"/>
+      <c r="S23" s="183"/>
+      <c r="T23" s="184"/>
+      <c r="U23" s="184"/>
+      <c r="V23" s="184"/>
+      <c r="W23" s="184"/>
+      <c r="X23" s="184"/>
+      <c r="Y23" s="184"/>
+      <c r="Z23" s="184"/>
+      <c r="AA23" s="184"/>
+      <c r="AB23" s="184"/>
+      <c r="AC23" s="184"/>
+      <c r="AD23" s="184"/>
+      <c r="AE23" s="184"/>
+      <c r="AF23" s="185"/>
       <c r="AI23" s="3"/>
       <c r="AJ23" s="3"/>
       <c r="AK23" s="3"/>
@@ -20198,20 +20205,20 @@
       <c r="P24" s="69"/>
       <c r="Q24" s="69"/>
       <c r="R24" s="69"/>
-      <c r="S24" s="172"/>
-      <c r="T24" s="173"/>
-      <c r="U24" s="173"/>
-      <c r="V24" s="173"/>
-      <c r="W24" s="173"/>
-      <c r="X24" s="173"/>
-      <c r="Y24" s="173"/>
-      <c r="Z24" s="173"/>
-      <c r="AA24" s="173"/>
-      <c r="AB24" s="173"/>
-      <c r="AC24" s="173"/>
-      <c r="AD24" s="173"/>
-      <c r="AE24" s="173"/>
-      <c r="AF24" s="174"/>
+      <c r="S24" s="183"/>
+      <c r="T24" s="184"/>
+      <c r="U24" s="184"/>
+      <c r="V24" s="184"/>
+      <c r="W24" s="184"/>
+      <c r="X24" s="184"/>
+      <c r="Y24" s="184"/>
+      <c r="Z24" s="184"/>
+      <c r="AA24" s="184"/>
+      <c r="AB24" s="184"/>
+      <c r="AC24" s="184"/>
+      <c r="AD24" s="184"/>
+      <c r="AE24" s="184"/>
+      <c r="AF24" s="185"/>
       <c r="AI24" s="3"/>
       <c r="AJ24" s="3"/>
       <c r="AK24" s="3"/>
@@ -20453,20 +20460,20 @@
       <c r="P25" s="69"/>
       <c r="Q25" s="69"/>
       <c r="R25" s="69"/>
-      <c r="S25" s="172"/>
-      <c r="T25" s="173"/>
-      <c r="U25" s="173"/>
-      <c r="V25" s="173"/>
-      <c r="W25" s="173"/>
-      <c r="X25" s="173"/>
-      <c r="Y25" s="173"/>
-      <c r="Z25" s="173"/>
-      <c r="AA25" s="173"/>
-      <c r="AB25" s="173"/>
-      <c r="AC25" s="173"/>
-      <c r="AD25" s="173"/>
-      <c r="AE25" s="173"/>
-      <c r="AF25" s="174"/>
+      <c r="S25" s="183"/>
+      <c r="T25" s="184"/>
+      <c r="U25" s="184"/>
+      <c r="V25" s="184"/>
+      <c r="W25" s="184"/>
+      <c r="X25" s="184"/>
+      <c r="Y25" s="184"/>
+      <c r="Z25" s="184"/>
+      <c r="AA25" s="184"/>
+      <c r="AB25" s="184"/>
+      <c r="AC25" s="184"/>
+      <c r="AD25" s="184"/>
+      <c r="AE25" s="184"/>
+      <c r="AF25" s="185"/>
       <c r="AI25" s="3"/>
       <c r="AJ25" s="3"/>
       <c r="AK25" s="3"/>
@@ -20708,20 +20715,20 @@
       <c r="P26" s="69"/>
       <c r="Q26" s="69"/>
       <c r="R26" s="69"/>
-      <c r="S26" s="172"/>
-      <c r="T26" s="173"/>
-      <c r="U26" s="173"/>
-      <c r="V26" s="173"/>
-      <c r="W26" s="173"/>
-      <c r="X26" s="173"/>
-      <c r="Y26" s="173"/>
-      <c r="Z26" s="173"/>
-      <c r="AA26" s="173"/>
-      <c r="AB26" s="173"/>
-      <c r="AC26" s="173"/>
-      <c r="AD26" s="173"/>
-      <c r="AE26" s="173"/>
-      <c r="AF26" s="174"/>
+      <c r="S26" s="183"/>
+      <c r="T26" s="184"/>
+      <c r="U26" s="184"/>
+      <c r="V26" s="184"/>
+      <c r="W26" s="184"/>
+      <c r="X26" s="184"/>
+      <c r="Y26" s="184"/>
+      <c r="Z26" s="184"/>
+      <c r="AA26" s="184"/>
+      <c r="AB26" s="184"/>
+      <c r="AC26" s="184"/>
+      <c r="AD26" s="184"/>
+      <c r="AE26" s="184"/>
+      <c r="AF26" s="185"/>
       <c r="AI26" s="3"/>
       <c r="AJ26" s="3"/>
       <c r="AK26" s="3"/>
@@ -20963,20 +20970,20 @@
       <c r="P27" s="69"/>
       <c r="Q27" s="69"/>
       <c r="R27" s="69"/>
-      <c r="S27" s="172"/>
-      <c r="T27" s="173"/>
-      <c r="U27" s="173"/>
-      <c r="V27" s="173"/>
-      <c r="W27" s="173"/>
-      <c r="X27" s="173"/>
-      <c r="Y27" s="173"/>
-      <c r="Z27" s="173"/>
-      <c r="AA27" s="173"/>
-      <c r="AB27" s="173"/>
-      <c r="AC27" s="173"/>
-      <c r="AD27" s="173"/>
-      <c r="AE27" s="173"/>
-      <c r="AF27" s="174"/>
+      <c r="S27" s="183"/>
+      <c r="T27" s="184"/>
+      <c r="U27" s="184"/>
+      <c r="V27" s="184"/>
+      <c r="W27" s="184"/>
+      <c r="X27" s="184"/>
+      <c r="Y27" s="184"/>
+      <c r="Z27" s="184"/>
+      <c r="AA27" s="184"/>
+      <c r="AB27" s="184"/>
+      <c r="AC27" s="184"/>
+      <c r="AD27" s="184"/>
+      <c r="AE27" s="184"/>
+      <c r="AF27" s="185"/>
       <c r="AI27" s="3"/>
       <c r="AJ27" s="3"/>
       <c r="AK27" s="3"/>
@@ -21218,20 +21225,20 @@
       <c r="P28" s="69"/>
       <c r="Q28" s="69"/>
       <c r="R28" s="69"/>
-      <c r="S28" s="172"/>
-      <c r="T28" s="173"/>
-      <c r="U28" s="173"/>
-      <c r="V28" s="173"/>
-      <c r="W28" s="173"/>
-      <c r="X28" s="173"/>
-      <c r="Y28" s="173"/>
-      <c r="Z28" s="173"/>
-      <c r="AA28" s="173"/>
-      <c r="AB28" s="173"/>
-      <c r="AC28" s="173"/>
-      <c r="AD28" s="173"/>
-      <c r="AE28" s="173"/>
-      <c r="AF28" s="174"/>
+      <c r="S28" s="183"/>
+      <c r="T28" s="184"/>
+      <c r="U28" s="184"/>
+      <c r="V28" s="184"/>
+      <c r="W28" s="184"/>
+      <c r="X28" s="184"/>
+      <c r="Y28" s="184"/>
+      <c r="Z28" s="184"/>
+      <c r="AA28" s="184"/>
+      <c r="AB28" s="184"/>
+      <c r="AC28" s="184"/>
+      <c r="AD28" s="184"/>
+      <c r="AE28" s="184"/>
+      <c r="AF28" s="185"/>
       <c r="AI28" s="3"/>
       <c r="AJ28" s="3"/>
       <c r="AK28" s="3"/>
@@ -21469,20 +21476,20 @@
       <c r="P29" s="69"/>
       <c r="Q29" s="69"/>
       <c r="R29" s="69"/>
-      <c r="S29" s="172"/>
-      <c r="T29" s="173"/>
-      <c r="U29" s="173"/>
-      <c r="V29" s="173"/>
-      <c r="W29" s="173"/>
-      <c r="X29" s="173"/>
-      <c r="Y29" s="173"/>
-      <c r="Z29" s="173"/>
-      <c r="AA29" s="173"/>
-      <c r="AB29" s="173"/>
-      <c r="AC29" s="173"/>
-      <c r="AD29" s="173"/>
-      <c r="AE29" s="173"/>
-      <c r="AF29" s="174"/>
+      <c r="S29" s="183"/>
+      <c r="T29" s="184"/>
+      <c r="U29" s="184"/>
+      <c r="V29" s="184"/>
+      <c r="W29" s="184"/>
+      <c r="X29" s="184"/>
+      <c r="Y29" s="184"/>
+      <c r="Z29" s="184"/>
+      <c r="AA29" s="184"/>
+      <c r="AB29" s="184"/>
+      <c r="AC29" s="184"/>
+      <c r="AD29" s="184"/>
+      <c r="AE29" s="184"/>
+      <c r="AF29" s="185"/>
       <c r="AI29" s="3"/>
       <c r="AJ29" s="3"/>
       <c r="AK29" s="3"/>
@@ -21701,10 +21708,10 @@
     </row>
     <row r="30" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A30" s="37"/>
-      <c r="B30" s="154" t="s">
+      <c r="B30" s="137" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="155"/>
+      <c r="C30" s="138"/>
       <c r="D30" s="92"/>
       <c r="E30" s="92"/>
       <c r="F30" s="36"/>
@@ -21720,20 +21727,20 @@
       <c r="P30" s="69"/>
       <c r="Q30" s="69"/>
       <c r="R30" s="69"/>
-      <c r="S30" s="172"/>
-      <c r="T30" s="173"/>
-      <c r="U30" s="173"/>
-      <c r="V30" s="173"/>
-      <c r="W30" s="173"/>
-      <c r="X30" s="173"/>
-      <c r="Y30" s="173"/>
-      <c r="Z30" s="173"/>
-      <c r="AA30" s="173"/>
-      <c r="AB30" s="173"/>
-      <c r="AC30" s="173"/>
-      <c r="AD30" s="173"/>
-      <c r="AE30" s="173"/>
-      <c r="AF30" s="174"/>
+      <c r="S30" s="183"/>
+      <c r="T30" s="184"/>
+      <c r="U30" s="184"/>
+      <c r="V30" s="184"/>
+      <c r="W30" s="184"/>
+      <c r="X30" s="184"/>
+      <c r="Y30" s="184"/>
+      <c r="Z30" s="184"/>
+      <c r="AA30" s="184"/>
+      <c r="AB30" s="184"/>
+      <c r="AC30" s="184"/>
+      <c r="AD30" s="184"/>
+      <c r="AE30" s="184"/>
+      <c r="AF30" s="185"/>
       <c r="AI30" s="3"/>
       <c r="AJ30" s="3"/>
       <c r="AK30" s="3"/>
@@ -21956,7 +21963,7 @@
         <v>92</v>
       </c>
       <c r="C31" s="118"/>
-      <c r="D31" s="158" t="s">
+      <c r="D31" s="134" t="s">
         <v>117</v>
       </c>
       <c r="E31" s="92"/>
@@ -21973,20 +21980,20 @@
       <c r="P31" s="69"/>
       <c r="Q31" s="69"/>
       <c r="R31" s="69"/>
-      <c r="S31" s="172"/>
-      <c r="T31" s="173"/>
-      <c r="U31" s="173"/>
-      <c r="V31" s="173"/>
-      <c r="W31" s="173"/>
-      <c r="X31" s="173"/>
-      <c r="Y31" s="173"/>
-      <c r="Z31" s="173"/>
-      <c r="AA31" s="173"/>
-      <c r="AB31" s="173"/>
-      <c r="AC31" s="173"/>
-      <c r="AD31" s="173"/>
-      <c r="AE31" s="173"/>
-      <c r="AF31" s="174"/>
+      <c r="S31" s="183"/>
+      <c r="T31" s="184"/>
+      <c r="U31" s="184"/>
+      <c r="V31" s="184"/>
+      <c r="W31" s="184"/>
+      <c r="X31" s="184"/>
+      <c r="Y31" s="184"/>
+      <c r="Z31" s="184"/>
+      <c r="AA31" s="184"/>
+      <c r="AB31" s="184"/>
+      <c r="AC31" s="184"/>
+      <c r="AD31" s="184"/>
+      <c r="AE31" s="184"/>
+      <c r="AF31" s="185"/>
       <c r="AI31" s="3"/>
       <c r="AJ31" s="3"/>
       <c r="AK31" s="3"/>
@@ -22209,7 +22216,7 @@
         <v>93</v>
       </c>
       <c r="C32" s="118"/>
-      <c r="D32" s="119"/>
+      <c r="D32" s="135"/>
       <c r="E32" s="92" t="s">
         <v>47</v>
       </c>
@@ -22226,20 +22233,20 @@
       <c r="P32" s="68"/>
       <c r="Q32" s="68"/>
       <c r="R32" s="68"/>
-      <c r="S32" s="172"/>
-      <c r="T32" s="173"/>
-      <c r="U32" s="173"/>
-      <c r="V32" s="173"/>
-      <c r="W32" s="173"/>
-      <c r="X32" s="173"/>
-      <c r="Y32" s="173"/>
-      <c r="Z32" s="173"/>
-      <c r="AA32" s="173"/>
-      <c r="AB32" s="173"/>
-      <c r="AC32" s="173"/>
-      <c r="AD32" s="173"/>
-      <c r="AE32" s="173"/>
-      <c r="AF32" s="174"/>
+      <c r="S32" s="183"/>
+      <c r="T32" s="184"/>
+      <c r="U32" s="184"/>
+      <c r="V32" s="184"/>
+      <c r="W32" s="184"/>
+      <c r="X32" s="184"/>
+      <c r="Y32" s="184"/>
+      <c r="Z32" s="184"/>
+      <c r="AA32" s="184"/>
+      <c r="AB32" s="184"/>
+      <c r="AC32" s="184"/>
+      <c r="AD32" s="184"/>
+      <c r="AE32" s="184"/>
+      <c r="AF32" s="185"/>
       <c r="AI32" s="3"/>
       <c r="AJ32" s="3"/>
       <c r="AK32" s="3"/>
@@ -22462,7 +22469,7 @@
         <v>94</v>
       </c>
       <c r="C33" s="118"/>
-      <c r="D33" s="120"/>
+      <c r="D33" s="136"/>
       <c r="E33" s="92"/>
       <c r="F33" s="36"/>
       <c r="G33" s="68"/>
@@ -22477,20 +22484,20 @@
       <c r="P33" s="68"/>
       <c r="Q33" s="68"/>
       <c r="R33" s="68"/>
-      <c r="S33" s="172"/>
-      <c r="T33" s="173"/>
-      <c r="U33" s="173"/>
-      <c r="V33" s="173"/>
-      <c r="W33" s="173"/>
-      <c r="X33" s="173"/>
-      <c r="Y33" s="173"/>
-      <c r="Z33" s="173"/>
-      <c r="AA33" s="173"/>
-      <c r="AB33" s="173"/>
-      <c r="AC33" s="173"/>
-      <c r="AD33" s="173"/>
-      <c r="AE33" s="173"/>
-      <c r="AF33" s="174"/>
+      <c r="S33" s="183"/>
+      <c r="T33" s="184"/>
+      <c r="U33" s="184"/>
+      <c r="V33" s="184"/>
+      <c r="W33" s="184"/>
+      <c r="X33" s="184"/>
+      <c r="Y33" s="184"/>
+      <c r="Z33" s="184"/>
+      <c r="AA33" s="184"/>
+      <c r="AB33" s="184"/>
+      <c r="AC33" s="184"/>
+      <c r="AD33" s="184"/>
+      <c r="AE33" s="184"/>
+      <c r="AF33" s="185"/>
       <c r="AI33" s="3"/>
       <c r="AJ33" s="3"/>
       <c r="AK33" s="3"/>
@@ -22709,10 +22716,10 @@
     </row>
     <row r="34" spans="1:249" s="2" customFormat="1" ht="28.25" customHeight="1">
       <c r="A34" s="38"/>
-      <c r="B34" s="154" t="s">
+      <c r="B34" s="137" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="155"/>
+      <c r="C34" s="138"/>
       <c r="D34" s="35"/>
       <c r="E34" s="35"/>
       <c r="F34" s="39"/>
@@ -22728,20 +22735,20 @@
       <c r="P34" s="68"/>
       <c r="Q34" s="68"/>
       <c r="R34" s="68"/>
-      <c r="S34" s="172"/>
-      <c r="T34" s="173"/>
-      <c r="U34" s="173"/>
-      <c r="V34" s="173"/>
-      <c r="W34" s="173"/>
-      <c r="X34" s="173"/>
-      <c r="Y34" s="173"/>
-      <c r="Z34" s="173"/>
-      <c r="AA34" s="173"/>
-      <c r="AB34" s="173"/>
-      <c r="AC34" s="173"/>
-      <c r="AD34" s="173"/>
-      <c r="AE34" s="173"/>
-      <c r="AF34" s="174"/>
+      <c r="S34" s="183"/>
+      <c r="T34" s="184"/>
+      <c r="U34" s="184"/>
+      <c r="V34" s="184"/>
+      <c r="W34" s="184"/>
+      <c r="X34" s="184"/>
+      <c r="Y34" s="184"/>
+      <c r="Z34" s="184"/>
+      <c r="AA34" s="184"/>
+      <c r="AB34" s="184"/>
+      <c r="AC34" s="184"/>
+      <c r="AD34" s="184"/>
+      <c r="AE34" s="184"/>
+      <c r="AF34" s="185"/>
       <c r="AI34" s="3"/>
       <c r="AJ34" s="3"/>
       <c r="AK34" s="3"/>
@@ -22962,15 +22969,15 @@
       <c r="A35" s="37">
         <v>1</v>
       </c>
-      <c r="B35" s="156" t="s">
+      <c r="B35" s="130" t="s">
         <v>104</v>
       </c>
-      <c r="C35" s="157"/>
+      <c r="C35" s="131"/>
       <c r="D35" s="96"/>
       <c r="E35" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="F35" s="158" t="s">
+      <c r="F35" s="134" t="s">
         <v>95</v>
       </c>
       <c r="G35" s="69"/>
@@ -22985,20 +22992,20 @@
       <c r="P35" s="69"/>
       <c r="Q35" s="69"/>
       <c r="R35" s="69"/>
-      <c r="S35" s="172"/>
-      <c r="T35" s="173"/>
-      <c r="U35" s="173"/>
-      <c r="V35" s="173"/>
-      <c r="W35" s="173"/>
-      <c r="X35" s="173"/>
-      <c r="Y35" s="173"/>
-      <c r="Z35" s="173"/>
-      <c r="AA35" s="173"/>
-      <c r="AB35" s="173"/>
-      <c r="AC35" s="173"/>
-      <c r="AD35" s="173"/>
-      <c r="AE35" s="173"/>
-      <c r="AF35" s="174"/>
+      <c r="S35" s="183"/>
+      <c r="T35" s="184"/>
+      <c r="U35" s="184"/>
+      <c r="V35" s="184"/>
+      <c r="W35" s="184"/>
+      <c r="X35" s="184"/>
+      <c r="Y35" s="184"/>
+      <c r="Z35" s="184"/>
+      <c r="AA35" s="184"/>
+      <c r="AB35" s="184"/>
+      <c r="AC35" s="184"/>
+      <c r="AD35" s="184"/>
+      <c r="AE35" s="184"/>
+      <c r="AF35" s="185"/>
       <c r="AI35" s="3"/>
       <c r="AJ35" s="3"/>
       <c r="AK35" s="3"/>
@@ -23225,7 +23232,7 @@
       <c r="E36" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="F36" s="119"/>
+      <c r="F36" s="135"/>
       <c r="G36" s="68"/>
       <c r="H36" s="68"/>
       <c r="I36" s="68"/>
@@ -23238,20 +23245,20 @@
       <c r="P36" s="68"/>
       <c r="Q36" s="68"/>
       <c r="R36" s="68"/>
-      <c r="S36" s="172"/>
-      <c r="T36" s="173"/>
-      <c r="U36" s="173"/>
-      <c r="V36" s="173"/>
-      <c r="W36" s="173"/>
-      <c r="X36" s="173"/>
-      <c r="Y36" s="173"/>
-      <c r="Z36" s="173"/>
-      <c r="AA36" s="173"/>
-      <c r="AB36" s="173"/>
-      <c r="AC36" s="173"/>
-      <c r="AD36" s="173"/>
-      <c r="AE36" s="173"/>
-      <c r="AF36" s="174"/>
+      <c r="S36" s="183"/>
+      <c r="T36" s="184"/>
+      <c r="U36" s="184"/>
+      <c r="V36" s="184"/>
+      <c r="W36" s="184"/>
+      <c r="X36" s="184"/>
+      <c r="Y36" s="184"/>
+      <c r="Z36" s="184"/>
+      <c r="AA36" s="184"/>
+      <c r="AB36" s="184"/>
+      <c r="AC36" s="184"/>
+      <c r="AD36" s="184"/>
+      <c r="AE36" s="184"/>
+      <c r="AF36" s="185"/>
       <c r="AI36" s="3"/>
       <c r="AJ36" s="3"/>
       <c r="AK36" s="3"/>
@@ -23472,11 +23479,11 @@
       <c r="A37" s="37">
         <v>3</v>
       </c>
-      <c r="B37" s="156"/>
-      <c r="C37" s="157"/>
+      <c r="B37" s="130"/>
+      <c r="C37" s="131"/>
       <c r="D37" s="92"/>
       <c r="E37" s="35"/>
-      <c r="F37" s="119"/>
+      <c r="F37" s="135"/>
       <c r="G37" s="68"/>
       <c r="H37" s="68"/>
       <c r="I37" s="68"/>
@@ -23489,20 +23496,20 @@
       <c r="P37" s="68"/>
       <c r="Q37" s="68"/>
       <c r="R37" s="68"/>
-      <c r="S37" s="172"/>
-      <c r="T37" s="173"/>
-      <c r="U37" s="173"/>
-      <c r="V37" s="173"/>
-      <c r="W37" s="173"/>
-      <c r="X37" s="173"/>
-      <c r="Y37" s="173"/>
-      <c r="Z37" s="173"/>
-      <c r="AA37" s="173"/>
-      <c r="AB37" s="173"/>
-      <c r="AC37" s="173"/>
-      <c r="AD37" s="173"/>
-      <c r="AE37" s="173"/>
-      <c r="AF37" s="174"/>
+      <c r="S37" s="183"/>
+      <c r="T37" s="184"/>
+      <c r="U37" s="184"/>
+      <c r="V37" s="184"/>
+      <c r="W37" s="184"/>
+      <c r="X37" s="184"/>
+      <c r="Y37" s="184"/>
+      <c r="Z37" s="184"/>
+      <c r="AA37" s="184"/>
+      <c r="AB37" s="184"/>
+      <c r="AC37" s="184"/>
+      <c r="AD37" s="184"/>
+      <c r="AE37" s="184"/>
+      <c r="AF37" s="185"/>
       <c r="AI37" s="3"/>
       <c r="AJ37" s="3"/>
       <c r="AK37" s="3"/>
@@ -23721,10 +23728,10 @@
     </row>
     <row r="38" spans="1:249" s="2" customFormat="1" ht="42" customHeight="1" thickBot="1">
       <c r="A38" s="41"/>
-      <c r="B38" s="168" t="s">
+      <c r="B38" s="128" t="s">
         <v>63</v>
       </c>
-      <c r="C38" s="169"/>
+      <c r="C38" s="129"/>
       <c r="D38" s="42" t="s">
         <v>16</v>
       </c>
@@ -23982,29 +23989,29 @@
       <c r="E39" s="44"/>
       <c r="F39" s="57"/>
       <c r="G39" s="75"/>
-      <c r="H39" s="180"/>
-      <c r="I39" s="180"/>
-      <c r="J39" s="180"/>
-      <c r="K39" s="180"/>
+      <c r="H39" s="188"/>
+      <c r="I39" s="188"/>
+      <c r="J39" s="188"/>
+      <c r="K39" s="188"/>
       <c r="L39" s="76"/>
       <c r="M39" s="75"/>
-      <c r="N39" s="180"/>
-      <c r="O39" s="180"/>
-      <c r="P39" s="180"/>
-      <c r="Q39" s="180"/>
+      <c r="N39" s="188"/>
+      <c r="O39" s="188"/>
+      <c r="P39" s="188"/>
+      <c r="Q39" s="188"/>
       <c r="R39" s="76"/>
       <c r="S39" s="75"/>
-      <c r="T39" s="180"/>
-      <c r="U39" s="180"/>
-      <c r="V39" s="180"/>
+      <c r="T39" s="188"/>
+      <c r="U39" s="188"/>
+      <c r="V39" s="188"/>
       <c r="W39" s="75"/>
-      <c r="X39" s="180"/>
-      <c r="Y39" s="180"/>
-      <c r="Z39" s="180"/>
+      <c r="X39" s="188"/>
+      <c r="Y39" s="188"/>
+      <c r="Z39" s="188"/>
       <c r="AA39" s="76"/>
       <c r="AB39" s="75"/>
-      <c r="AC39" s="180"/>
-      <c r="AD39" s="180"/>
+      <c r="AC39" s="188"/>
+      <c r="AD39" s="188"/>
       <c r="AE39" s="55"/>
       <c r="AF39" s="56"/>
       <c r="AI39" s="3"/>
@@ -24235,29 +24242,29 @@
       <c r="E40" s="90"/>
       <c r="F40" s="58"/>
       <c r="G40" s="77"/>
-      <c r="H40" s="179"/>
-      <c r="I40" s="179"/>
-      <c r="J40" s="179"/>
-      <c r="K40" s="179"/>
+      <c r="H40" s="189"/>
+      <c r="I40" s="189"/>
+      <c r="J40" s="189"/>
+      <c r="K40" s="189"/>
       <c r="L40" s="78"/>
       <c r="M40" s="77"/>
-      <c r="N40" s="179"/>
-      <c r="O40" s="179"/>
-      <c r="P40" s="179"/>
-      <c r="Q40" s="179"/>
+      <c r="N40" s="189"/>
+      <c r="O40" s="189"/>
+      <c r="P40" s="189"/>
+      <c r="Q40" s="189"/>
       <c r="R40" s="78"/>
       <c r="S40" s="77"/>
-      <c r="T40" s="179"/>
-      <c r="U40" s="179"/>
-      <c r="V40" s="179"/>
+      <c r="T40" s="189"/>
+      <c r="U40" s="189"/>
+      <c r="V40" s="189"/>
       <c r="W40" s="77"/>
-      <c r="X40" s="179"/>
-      <c r="Y40" s="179"/>
-      <c r="Z40" s="179"/>
+      <c r="X40" s="189"/>
+      <c r="Y40" s="189"/>
+      <c r="Z40" s="189"/>
       <c r="AA40" s="78"/>
       <c r="AB40" s="77"/>
-      <c r="AC40" s="179"/>
-      <c r="AD40" s="179"/>
+      <c r="AC40" s="189"/>
+      <c r="AD40" s="189"/>
       <c r="AE40" s="61"/>
       <c r="AF40" s="79"/>
       <c r="AI40" s="3"/>
@@ -24488,29 +24495,29 @@
       <c r="E41" s="91"/>
       <c r="F41" s="59"/>
       <c r="G41" s="77"/>
-      <c r="H41" s="179"/>
-      <c r="I41" s="179"/>
-      <c r="J41" s="179"/>
-      <c r="K41" s="179"/>
+      <c r="H41" s="189"/>
+      <c r="I41" s="189"/>
+      <c r="J41" s="189"/>
+      <c r="K41" s="189"/>
       <c r="L41" s="80"/>
       <c r="M41" s="77"/>
-      <c r="N41" s="179"/>
-      <c r="O41" s="179"/>
-      <c r="P41" s="179"/>
-      <c r="Q41" s="179"/>
+      <c r="N41" s="189"/>
+      <c r="O41" s="189"/>
+      <c r="P41" s="189"/>
+      <c r="Q41" s="189"/>
       <c r="R41" s="80"/>
       <c r="S41" s="77"/>
-      <c r="T41" s="179"/>
-      <c r="U41" s="179"/>
-      <c r="V41" s="179"/>
+      <c r="T41" s="189"/>
+      <c r="U41" s="189"/>
+      <c r="V41" s="189"/>
       <c r="W41" s="77"/>
-      <c r="X41" s="179"/>
-      <c r="Y41" s="179"/>
-      <c r="Z41" s="179"/>
+      <c r="X41" s="189"/>
+      <c r="Y41" s="189"/>
+      <c r="Z41" s="189"/>
       <c r="AA41" s="80"/>
       <c r="AB41" s="77"/>
-      <c r="AC41" s="179"/>
-      <c r="AD41" s="179"/>
+      <c r="AC41" s="189"/>
+      <c r="AD41" s="189"/>
       <c r="AE41" s="62"/>
       <c r="AF41" s="81"/>
       <c r="AI41" s="3"/>
@@ -24741,29 +24748,29 @@
       <c r="E42" s="91"/>
       <c r="F42" s="59"/>
       <c r="G42" s="77"/>
-      <c r="H42" s="179"/>
-      <c r="I42" s="179"/>
-      <c r="J42" s="179"/>
-      <c r="K42" s="179"/>
+      <c r="H42" s="189"/>
+      <c r="I42" s="189"/>
+      <c r="J42" s="189"/>
+      <c r="K42" s="189"/>
       <c r="L42" s="80"/>
       <c r="M42" s="77"/>
-      <c r="N42" s="179"/>
-      <c r="O42" s="179"/>
-      <c r="P42" s="179"/>
-      <c r="Q42" s="179"/>
+      <c r="N42" s="189"/>
+      <c r="O42" s="189"/>
+      <c r="P42" s="189"/>
+      <c r="Q42" s="189"/>
       <c r="R42" s="80"/>
       <c r="S42" s="77"/>
-      <c r="T42" s="179"/>
-      <c r="U42" s="179"/>
-      <c r="V42" s="179"/>
+      <c r="T42" s="189"/>
+      <c r="U42" s="189"/>
+      <c r="V42" s="189"/>
       <c r="W42" s="77"/>
-      <c r="X42" s="179"/>
-      <c r="Y42" s="179"/>
-      <c r="Z42" s="179"/>
+      <c r="X42" s="189"/>
+      <c r="Y42" s="189"/>
+      <c r="Z42" s="189"/>
       <c r="AA42" s="80"/>
       <c r="AB42" s="77"/>
-      <c r="AC42" s="179"/>
-      <c r="AD42" s="179"/>
+      <c r="AC42" s="189"/>
+      <c r="AD42" s="189"/>
       <c r="AE42" s="62"/>
       <c r="AF42" s="81"/>
       <c r="AI42" s="3"/>
@@ -24990,29 +24997,29 @@
       <c r="E43" s="50"/>
       <c r="F43" s="60"/>
       <c r="G43" s="82"/>
-      <c r="H43" s="175"/>
-      <c r="I43" s="175"/>
-      <c r="J43" s="175"/>
-      <c r="K43" s="175"/>
+      <c r="H43" s="190"/>
+      <c r="I43" s="190"/>
+      <c r="J43" s="190"/>
+      <c r="K43" s="190"/>
       <c r="L43" s="83"/>
       <c r="M43" s="82"/>
-      <c r="N43" s="175"/>
-      <c r="O43" s="175"/>
-      <c r="P43" s="175"/>
-      <c r="Q43" s="175"/>
+      <c r="N43" s="190"/>
+      <c r="O43" s="190"/>
+      <c r="P43" s="190"/>
+      <c r="Q43" s="190"/>
       <c r="R43" s="83"/>
       <c r="S43" s="82"/>
-      <c r="T43" s="175"/>
-      <c r="U43" s="175"/>
-      <c r="V43" s="175"/>
+      <c r="T43" s="190"/>
+      <c r="U43" s="190"/>
+      <c r="V43" s="190"/>
       <c r="W43" s="82"/>
-      <c r="X43" s="175"/>
-      <c r="Y43" s="175"/>
-      <c r="Z43" s="175"/>
+      <c r="X43" s="190"/>
+      <c r="Y43" s="190"/>
+      <c r="Z43" s="190"/>
       <c r="AA43" s="83"/>
       <c r="AB43" s="82"/>
-      <c r="AC43" s="175"/>
-      <c r="AD43" s="175"/>
+      <c r="AC43" s="190"/>
+      <c r="AD43" s="190"/>
       <c r="AE43" s="63"/>
       <c r="AF43" s="84"/>
       <c r="AI43" s="3"/>
@@ -25276,13 +25283,83 @@
     </row>
   </sheetData>
   <mergeCells count="100">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="F1:AF1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="T3:AF3"/>
+    <mergeCell ref="S32:AF32"/>
+    <mergeCell ref="S33:AF33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="S26:AF26"/>
+    <mergeCell ref="S28:AF28"/>
+    <mergeCell ref="S29:AF29"/>
+    <mergeCell ref="S30:AF30"/>
+    <mergeCell ref="S31:AF31"/>
+    <mergeCell ref="S27:AF27"/>
+    <mergeCell ref="AC43:AD43"/>
+    <mergeCell ref="S9:AF9"/>
+    <mergeCell ref="S20:AF20"/>
+    <mergeCell ref="S21:AF21"/>
+    <mergeCell ref="S22:AF22"/>
+    <mergeCell ref="S23:AF23"/>
+    <mergeCell ref="T41:V41"/>
+    <mergeCell ref="X41:Z41"/>
+    <mergeCell ref="AC41:AD41"/>
+    <mergeCell ref="T42:V42"/>
+    <mergeCell ref="X42:Z42"/>
+    <mergeCell ref="AC42:AD42"/>
+    <mergeCell ref="T39:V39"/>
+    <mergeCell ref="X39:Z39"/>
+    <mergeCell ref="S34:AF34"/>
+    <mergeCell ref="S35:AF35"/>
+    <mergeCell ref="H43:K43"/>
+    <mergeCell ref="N43:Q43"/>
+    <mergeCell ref="T43:V43"/>
+    <mergeCell ref="X43:Z43"/>
+    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="N41:Q41"/>
+    <mergeCell ref="H42:K42"/>
+    <mergeCell ref="N42:Q42"/>
+    <mergeCell ref="H40:K40"/>
+    <mergeCell ref="N40:Q40"/>
+    <mergeCell ref="T40:V40"/>
+    <mergeCell ref="X40:Z40"/>
+    <mergeCell ref="AC40:AD40"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="AC39:AD39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="H39:K39"/>
+    <mergeCell ref="N39:Q39"/>
+    <mergeCell ref="S36:AF36"/>
+    <mergeCell ref="S37:AF37"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="S14:AF14"/>
+    <mergeCell ref="S15:AF15"/>
+    <mergeCell ref="S16:AF16"/>
+    <mergeCell ref="S17:AF17"/>
+    <mergeCell ref="S18:AF18"/>
+    <mergeCell ref="S19:AF19"/>
+    <mergeCell ref="S25:AF25"/>
+    <mergeCell ref="S24:AF24"/>
     <mergeCell ref="T5:W7"/>
     <mergeCell ref="AD4:AF4"/>
     <mergeCell ref="AD5:AF7"/>
@@ -25299,83 +25376,13 @@
     <mergeCell ref="X4:Z4"/>
     <mergeCell ref="AA4:AC4"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="S14:AF14"/>
-    <mergeCell ref="S15:AF15"/>
-    <mergeCell ref="S16:AF16"/>
-    <mergeCell ref="S17:AF17"/>
-    <mergeCell ref="S18:AF18"/>
-    <mergeCell ref="S19:AF19"/>
-    <mergeCell ref="S25:AF25"/>
-    <mergeCell ref="S24:AF24"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="F35:F37"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="AC39:AD39"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="H39:K39"/>
-    <mergeCell ref="N39:Q39"/>
-    <mergeCell ref="S36:AF36"/>
-    <mergeCell ref="S37:AF37"/>
-    <mergeCell ref="H40:K40"/>
-    <mergeCell ref="N40:Q40"/>
-    <mergeCell ref="T40:V40"/>
-    <mergeCell ref="X40:Z40"/>
-    <mergeCell ref="AC40:AD40"/>
-    <mergeCell ref="H43:K43"/>
-    <mergeCell ref="N43:Q43"/>
-    <mergeCell ref="T43:V43"/>
-    <mergeCell ref="X43:Z43"/>
-    <mergeCell ref="H41:K41"/>
-    <mergeCell ref="N41:Q41"/>
-    <mergeCell ref="H42:K42"/>
-    <mergeCell ref="N42:Q42"/>
-    <mergeCell ref="AC43:AD43"/>
-    <mergeCell ref="S9:AF9"/>
-    <mergeCell ref="S20:AF20"/>
-    <mergeCell ref="S21:AF21"/>
-    <mergeCell ref="S22:AF22"/>
-    <mergeCell ref="S23:AF23"/>
-    <mergeCell ref="T41:V41"/>
-    <mergeCell ref="X41:Z41"/>
-    <mergeCell ref="AC41:AD41"/>
-    <mergeCell ref="T42:V42"/>
-    <mergeCell ref="X42:Z42"/>
-    <mergeCell ref="AC42:AD42"/>
-    <mergeCell ref="T39:V39"/>
-    <mergeCell ref="X39:Z39"/>
-    <mergeCell ref="S34:AF34"/>
-    <mergeCell ref="S35:AF35"/>
-    <mergeCell ref="S26:AF26"/>
-    <mergeCell ref="S28:AF28"/>
-    <mergeCell ref="S29:AF29"/>
-    <mergeCell ref="S30:AF30"/>
-    <mergeCell ref="S31:AF31"/>
-    <mergeCell ref="S27:AF27"/>
-    <mergeCell ref="S32:AF32"/>
-    <mergeCell ref="S33:AF33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:AF1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="T3:AF3"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="G11:R19 AG11:AK19">

--- a/設備点検表.xlsx
+++ b/設備点検表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kosuk\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B6DFB8F-DF51-4AAD-95B7-25507C49F775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38418EB-2DF8-4034-A161-489A54E4460C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6C56CF13-AF7F-4C1F-982C-EF388A11F51A}"/>
   </bookViews>
@@ -2765,65 +2765,71 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2864,65 +2870,92 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="71" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="72" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="73" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="67" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="74" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2957,45 +2990,57 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="71" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="72" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="73" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="67" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="74" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準_設備点検表書式" xfId="1" xr:uid="{15F629F0-A893-4DD8-8A94-9D447F97F79C}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <strike val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -3013,7 +3058,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3025,27 +3070,6 @@
       <fill>
         <patternFill>
           <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3380,45 +3404,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:254" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A1" s="155" t="s">
+      <c r="A1" s="121" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="155"/>
+      <c r="B1" s="121"/>
       <c r="C1" s="85"/>
-      <c r="F1" s="156" t="s">
+      <c r="F1" s="122" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
-      <c r="L1" s="156"/>
-      <c r="M1" s="156"/>
-      <c r="N1" s="156"/>
-      <c r="O1" s="156"/>
-      <c r="P1" s="156"/>
-      <c r="Q1" s="156"/>
-      <c r="R1" s="156"/>
-      <c r="S1" s="156"/>
-      <c r="T1" s="156"/>
-      <c r="U1" s="156"/>
-      <c r="V1" s="156"/>
-      <c r="W1" s="156"/>
-      <c r="X1" s="156"/>
-      <c r="Y1" s="156"/>
-      <c r="Z1" s="156"/>
-      <c r="AA1" s="156"/>
-      <c r="AB1" s="156"/>
-      <c r="AC1" s="156"/>
-      <c r="AD1" s="156"/>
-      <c r="AE1" s="156"/>
-      <c r="AF1" s="156"/>
-      <c r="AG1" s="156"/>
-      <c r="AH1" s="156"/>
-      <c r="AI1" s="156"/>
-      <c r="AJ1" s="156"/>
-      <c r="AK1" s="156"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
+      <c r="AC1" s="122"/>
+      <c r="AD1" s="122"/>
+      <c r="AE1" s="122"/>
+      <c r="AF1" s="122"/>
+      <c r="AG1" s="122"/>
+      <c r="AH1" s="122"/>
+      <c r="AI1" s="122"/>
+      <c r="AJ1" s="122"/>
+      <c r="AK1" s="122"/>
       <c r="AN1" s="3"/>
       <c r="AO1" s="3"/>
       <c r="AP1" s="3"/>
@@ -3889,52 +3913,52 @@
       <c r="IT2" s="3"/>
     </row>
     <row r="3" spans="1:254" s="2" customFormat="1" ht="20" customHeight="1" thickBot="1">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="123" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="125"/>
       <c r="E3" s="94"/>
       <c r="G3" s="51"/>
       <c r="H3" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="160" t="s">
+      <c r="K3" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="160"/>
-      <c r="M3" s="160" t="s">
+      <c r="L3" s="126"/>
+      <c r="M3" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="160"/>
-      <c r="O3" s="160"/>
-      <c r="P3" s="160" t="s">
+      <c r="N3" s="126"/>
+      <c r="O3" s="126"/>
+      <c r="P3" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="Q3" s="160"/>
-      <c r="R3" s="160"/>
+      <c r="Q3" s="126"/>
+      <c r="R3" s="126"/>
       <c r="S3" s="3"/>
-      <c r="T3" s="161" t="s">
+      <c r="T3" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="U3" s="162"/>
-      <c r="V3" s="162"/>
-      <c r="W3" s="162"/>
-      <c r="X3" s="162"/>
-      <c r="Y3" s="162"/>
-      <c r="Z3" s="162"/>
-      <c r="AA3" s="162"/>
-      <c r="AB3" s="162"/>
-      <c r="AC3" s="162"/>
-      <c r="AD3" s="162"/>
-      <c r="AE3" s="162"/>
-      <c r="AF3" s="162"/>
-      <c r="AG3" s="162"/>
-      <c r="AH3" s="162"/>
-      <c r="AI3" s="162"/>
-      <c r="AJ3" s="162"/>
-      <c r="AK3" s="163"/>
+      <c r="U3" s="128"/>
+      <c r="V3" s="128"/>
+      <c r="W3" s="128"/>
+      <c r="X3" s="128"/>
+      <c r="Y3" s="128"/>
+      <c r="Z3" s="128"/>
+      <c r="AA3" s="128"/>
+      <c r="AB3" s="128"/>
+      <c r="AC3" s="128"/>
+      <c r="AD3" s="128"/>
+      <c r="AE3" s="128"/>
+      <c r="AF3" s="128"/>
+      <c r="AG3" s="128"/>
+      <c r="AH3" s="128"/>
+      <c r="AI3" s="128"/>
+      <c r="AJ3" s="128"/>
+      <c r="AK3" s="129"/>
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
@@ -4163,47 +4187,47 @@
       <c r="H4" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="160" t="s">
+      <c r="K4" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="160"/>
-      <c r="M4" s="166">
+      <c r="L4" s="126"/>
+      <c r="M4" s="132">
         <v>46113</v>
       </c>
-      <c r="N4" s="166"/>
-      <c r="O4" s="166"/>
-      <c r="P4" s="160" t="s">
+      <c r="N4" s="132"/>
+      <c r="O4" s="132"/>
+      <c r="P4" s="126" t="s">
         <v>50</v>
       </c>
-      <c r="Q4" s="160"/>
-      <c r="R4" s="160"/>
+      <c r="Q4" s="126"/>
+      <c r="R4" s="126"/>
       <c r="S4" s="3"/>
-      <c r="T4" s="152" t="s">
+      <c r="T4" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="U4" s="153"/>
-      <c r="V4" s="153"/>
-      <c r="W4" s="153"/>
-      <c r="X4" s="153"/>
-      <c r="Y4" s="154"/>
-      <c r="Z4" s="152" t="s">
+      <c r="U4" s="134"/>
+      <c r="V4" s="134"/>
+      <c r="W4" s="134"/>
+      <c r="X4" s="134"/>
+      <c r="Y4" s="135"/>
+      <c r="Z4" s="133" t="s">
         <v>6</v>
       </c>
-      <c r="AA4" s="153"/>
-      <c r="AB4" s="153"/>
-      <c r="AC4" s="154"/>
-      <c r="AD4" s="152" t="s">
+      <c r="AA4" s="134"/>
+      <c r="AB4" s="134"/>
+      <c r="AC4" s="135"/>
+      <c r="AD4" s="133" t="s">
         <v>7</v>
       </c>
-      <c r="AE4" s="153"/>
-      <c r="AF4" s="153"/>
-      <c r="AG4" s="154"/>
-      <c r="AH4" s="152" t="s">
+      <c r="AE4" s="134"/>
+      <c r="AF4" s="134"/>
+      <c r="AG4" s="135"/>
+      <c r="AH4" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="AI4" s="153"/>
-      <c r="AJ4" s="153"/>
-      <c r="AK4" s="154"/>
+      <c r="AI4" s="134"/>
+      <c r="AJ4" s="134"/>
+      <c r="AK4" s="135"/>
       <c r="AN4" s="3"/>
       <c r="AO4" s="3"/>
       <c r="AP4" s="3"/>
@@ -4431,16 +4455,16 @@
         <v>23</v>
       </c>
       <c r="S5" s="3"/>
-      <c r="T5" s="167" t="s">
+      <c r="T5" s="136" t="s">
         <v>64</v>
       </c>
-      <c r="U5" s="168"/>
-      <c r="V5" s="168"/>
-      <c r="W5" s="139">
+      <c r="U5" s="137"/>
+      <c r="V5" s="137"/>
+      <c r="W5" s="141">
         <v>7</v>
       </c>
-      <c r="X5" s="140"/>
-      <c r="Y5" s="141"/>
+      <c r="X5" s="142"/>
+      <c r="Y5" s="143"/>
       <c r="Z5" s="11"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
@@ -4449,10 +4473,10 @@
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
       <c r="AG5" s="12"/>
-      <c r="AH5" s="144"/>
-      <c r="AI5" s="145"/>
-      <c r="AJ5" s="145"/>
-      <c r="AK5" s="146"/>
+      <c r="AH5" s="146"/>
+      <c r="AI5" s="147"/>
+      <c r="AJ5" s="147"/>
+      <c r="AK5" s="148"/>
       <c r="AN5" s="3"/>
       <c r="AO5" s="3"/>
       <c r="AP5" s="3"/>
@@ -4684,12 +4708,12 @@
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
-      <c r="T6" s="169"/>
-      <c r="U6" s="168"/>
-      <c r="V6" s="168"/>
-      <c r="W6" s="140"/>
-      <c r="X6" s="140"/>
-      <c r="Y6" s="141"/>
+      <c r="T6" s="138"/>
+      <c r="U6" s="137"/>
+      <c r="V6" s="137"/>
+      <c r="W6" s="142"/>
+      <c r="X6" s="142"/>
+      <c r="Y6" s="143"/>
       <c r="Z6" s="11"/>
       <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
@@ -4698,10 +4722,10 @@
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
       <c r="AG6" s="12"/>
-      <c r="AH6" s="144"/>
-      <c r="AI6" s="145"/>
-      <c r="AJ6" s="145"/>
-      <c r="AK6" s="146"/>
+      <c r="AH6" s="146"/>
+      <c r="AI6" s="147"/>
+      <c r="AJ6" s="147"/>
+      <c r="AK6" s="148"/>
       <c r="AN6" s="3"/>
       <c r="AO6" s="3"/>
       <c r="AP6" s="3"/>
@@ -4933,12 +4957,12 @@
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
-      <c r="T7" s="170"/>
-      <c r="U7" s="171"/>
-      <c r="V7" s="171"/>
-      <c r="W7" s="142"/>
-      <c r="X7" s="142"/>
-      <c r="Y7" s="143"/>
+      <c r="T7" s="139"/>
+      <c r="U7" s="140"/>
+      <c r="V7" s="140"/>
+      <c r="W7" s="144"/>
+      <c r="X7" s="144"/>
+      <c r="Y7" s="145"/>
       <c r="Z7" s="21"/>
       <c r="AA7" s="22"/>
       <c r="AB7" s="22"/>
@@ -4947,10 +4971,10 @@
       <c r="AE7" s="22"/>
       <c r="AF7" s="22"/>
       <c r="AG7" s="23"/>
-      <c r="AH7" s="147"/>
-      <c r="AI7" s="148"/>
-      <c r="AJ7" s="148"/>
-      <c r="AK7" s="149"/>
+      <c r="AH7" s="149"/>
+      <c r="AI7" s="150"/>
+      <c r="AJ7" s="150"/>
+      <c r="AK7" s="151"/>
       <c r="AL7" s="86"/>
       <c r="AN7" s="3"/>
       <c r="AO7" s="3"/>
@@ -5833,8 +5857,8 @@
     </row>
     <row r="10" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A10" s="29"/>
-      <c r="B10" s="150"/>
-      <c r="C10" s="151"/>
+      <c r="B10" s="152"/>
+      <c r="C10" s="153"/>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="31" t="s">
@@ -6182,10 +6206,10 @@
     </row>
     <row r="11" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A11" s="34"/>
-      <c r="B11" s="164" t="s">
+      <c r="B11" s="130" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="165"/>
+      <c r="C11" s="131"/>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
       <c r="F11" s="102" t="s">
@@ -6452,7 +6476,7 @@
       <c r="E12" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="134" t="s">
+      <c r="F12" s="158" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="106"/>
@@ -6714,7 +6738,7 @@
         <v>99</v>
       </c>
       <c r="E13" s="92"/>
-      <c r="F13" s="135"/>
+      <c r="F13" s="119"/>
       <c r="G13" s="106"/>
       <c r="H13" s="106"/>
       <c r="I13" s="106"/>
@@ -6976,7 +7000,7 @@
       <c r="E14" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="135"/>
+      <c r="F14" s="119"/>
       <c r="G14" s="106"/>
       <c r="H14" s="106"/>
       <c r="I14" s="106"/>
@@ -7238,7 +7262,7 @@
       <c r="E15" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="135"/>
+      <c r="F15" s="119"/>
       <c r="G15" s="106"/>
       <c r="H15" s="106"/>
       <c r="I15" s="106"/>
@@ -7500,7 +7524,7 @@
       <c r="E16" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="135"/>
+      <c r="F16" s="119"/>
       <c r="G16" s="106"/>
       <c r="H16" s="106"/>
       <c r="I16" s="106"/>
@@ -7762,7 +7786,7 @@
       <c r="E17" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="135"/>
+      <c r="F17" s="119"/>
       <c r="G17" s="106"/>
       <c r="H17" s="106"/>
       <c r="I17" s="106"/>
@@ -8024,7 +8048,7 @@
       <c r="E18" s="92" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="135"/>
+      <c r="F18" s="119"/>
       <c r="G18" s="106"/>
       <c r="H18" s="106"/>
       <c r="I18" s="106"/>
@@ -8286,7 +8310,7 @@
       <c r="E19" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="F19" s="135"/>
+      <c r="F19" s="119"/>
       <c r="G19" s="106"/>
       <c r="H19" s="106"/>
       <c r="I19" s="106"/>
@@ -8548,7 +8572,7 @@
       <c r="E20" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="F20" s="135"/>
+      <c r="F20" s="119"/>
       <c r="G20" s="106"/>
       <c r="H20" s="106"/>
       <c r="I20" s="106"/>
@@ -8808,7 +8832,7 @@
         <v>100</v>
       </c>
       <c r="E21" s="92"/>
-      <c r="F21" s="135"/>
+      <c r="F21" s="119"/>
       <c r="G21" s="106"/>
       <c r="H21" s="106"/>
       <c r="I21" s="106"/>
@@ -9068,7 +9092,7 @@
         <v>38</v>
       </c>
       <c r="E22" s="92"/>
-      <c r="F22" s="135" t="s">
+      <c r="F22" s="119" t="s">
         <v>135</v>
       </c>
       <c r="G22" s="106"/>
@@ -9332,7 +9356,7 @@
       <c r="E23" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="F23" s="136"/>
+      <c r="F23" s="120"/>
       <c r="G23" s="104"/>
       <c r="H23" s="104"/>
       <c r="I23" s="104"/>
@@ -10100,10 +10124,10 @@
     </row>
     <row r="26" spans="1:254" s="2" customFormat="1" ht="28.25" customHeight="1">
       <c r="A26" s="38"/>
-      <c r="B26" s="137" t="s">
+      <c r="B26" s="154" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="138"/>
+      <c r="C26" s="155"/>
       <c r="D26" s="35"/>
       <c r="E26" s="35"/>
       <c r="F26" s="39"/>
@@ -10358,17 +10382,17 @@
       <c r="A27" s="37">
         <v>1</v>
       </c>
-      <c r="B27" s="130" t="s">
+      <c r="B27" s="156" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="131"/>
+      <c r="C27" s="157"/>
       <c r="D27" s="92" t="s">
         <v>99</v>
       </c>
       <c r="E27" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="134" t="s">
+      <c r="F27" s="158" t="s">
         <v>15</v>
       </c>
       <c r="G27" s="106"/>
@@ -10622,15 +10646,15 @@
       <c r="A28" s="37">
         <v>2</v>
       </c>
-      <c r="B28" s="130" t="s">
+      <c r="B28" s="156" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="131"/>
+      <c r="C28" s="157"/>
       <c r="D28" s="35" t="s">
         <v>77</v>
       </c>
       <c r="E28" s="35"/>
-      <c r="F28" s="135"/>
+      <c r="F28" s="119"/>
       <c r="G28" s="106"/>
       <c r="H28" s="106"/>
       <c r="I28" s="106"/>
@@ -10890,7 +10914,7 @@
         <v>77</v>
       </c>
       <c r="E29" s="35"/>
-      <c r="F29" s="135"/>
+      <c r="F29" s="119"/>
       <c r="G29" s="106"/>
       <c r="H29" s="106"/>
       <c r="I29" s="106"/>
@@ -11152,7 +11176,7 @@
       <c r="E30" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="F30" s="135"/>
+      <c r="F30" s="119"/>
       <c r="G30" s="104"/>
       <c r="H30" s="104"/>
       <c r="I30" s="104"/>
@@ -11404,15 +11428,15 @@
       <c r="A31" s="37">
         <v>5</v>
       </c>
-      <c r="B31" s="130" t="s">
+      <c r="B31" s="156" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="131"/>
+      <c r="C31" s="157"/>
       <c r="D31" s="92" t="s">
         <v>80</v>
       </c>
       <c r="E31" s="35"/>
-      <c r="F31" s="135"/>
+      <c r="F31" s="119"/>
       <c r="G31" s="104"/>
       <c r="H31" s="104"/>
       <c r="I31" s="104"/>
@@ -11672,7 +11696,7 @@
         <v>118</v>
       </c>
       <c r="E32" s="35"/>
-      <c r="F32" s="135"/>
+      <c r="F32" s="119"/>
       <c r="G32" s="104"/>
       <c r="H32" s="104"/>
       <c r="I32" s="104"/>
@@ -11932,7 +11956,7 @@
         <v>118</v>
       </c>
       <c r="E33" s="35"/>
-      <c r="F33" s="135"/>
+      <c r="F33" s="119"/>
       <c r="G33" s="104"/>
       <c r="H33" s="104"/>
       <c r="I33" s="104"/>
@@ -12184,15 +12208,15 @@
       <c r="A34" s="37">
         <v>8</v>
       </c>
-      <c r="B34" s="130" t="s">
+      <c r="B34" s="156" t="s">
         <v>59</v>
       </c>
-      <c r="C34" s="131"/>
+      <c r="C34" s="157"/>
       <c r="D34" s="92" t="s">
         <v>99</v>
       </c>
       <c r="E34" s="40"/>
-      <c r="F34" s="135"/>
+      <c r="F34" s="119"/>
       <c r="G34" s="106"/>
       <c r="H34" s="106"/>
       <c r="I34" s="106"/>
@@ -12444,15 +12468,15 @@
       <c r="A35" s="37">
         <v>9</v>
       </c>
-      <c r="B35" s="130" t="s">
+      <c r="B35" s="156" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="131"/>
+      <c r="C35" s="157"/>
       <c r="D35" s="92" t="s">
         <v>49</v>
       </c>
       <c r="E35" s="40"/>
-      <c r="F35" s="136"/>
+      <c r="F35" s="120"/>
       <c r="G35" s="106"/>
       <c r="H35" s="106"/>
       <c r="I35" s="106"/>
@@ -12702,10 +12726,10 @@
     </row>
     <row r="36" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A36" s="37"/>
-      <c r="B36" s="137" t="s">
+      <c r="B36" s="154" t="s">
         <v>127</v>
       </c>
-      <c r="C36" s="138"/>
+      <c r="C36" s="155"/>
       <c r="D36" s="92"/>
       <c r="E36" s="40"/>
       <c r="F36" s="93"/>
@@ -12958,10 +12982,10 @@
     </row>
     <row r="37" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A37" s="37"/>
-      <c r="B37" s="130" t="s">
+      <c r="B37" s="156" t="s">
         <v>128</v>
       </c>
-      <c r="C37" s="131"/>
+      <c r="C37" s="157"/>
       <c r="D37" s="92"/>
       <c r="E37" s="40"/>
       <c r="F37" s="93"/>
@@ -13214,10 +13238,10 @@
     </row>
     <row r="38" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A38" s="37"/>
-      <c r="B38" s="132" t="s">
+      <c r="B38" s="170" t="s">
         <v>129</v>
       </c>
-      <c r="C38" s="133"/>
+      <c r="C38" s="171"/>
       <c r="D38" s="92"/>
       <c r="E38" s="40"/>
       <c r="F38" s="93"/>
@@ -13470,8 +13494,8 @@
     </row>
     <row r="39" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A39" s="37"/>
-      <c r="B39" s="132"/>
-      <c r="C39" s="133"/>
+      <c r="B39" s="170"/>
+      <c r="C39" s="171"/>
       <c r="D39" s="92"/>
       <c r="E39" s="40"/>
       <c r="F39" s="93"/>
@@ -13724,10 +13748,10 @@
     </row>
     <row r="40" spans="1:254" s="2" customFormat="1" ht="42" customHeight="1" thickBot="1">
       <c r="A40" s="41"/>
-      <c r="B40" s="128" t="s">
+      <c r="B40" s="168" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="129"/>
+      <c r="C40" s="169"/>
       <c r="D40" s="42" t="s">
         <v>16</v>
       </c>
@@ -13991,37 +14015,37 @@
         <v>96</v>
       </c>
       <c r="F41" s="75"/>
-      <c r="G41" s="122"/>
-      <c r="H41" s="122"/>
-      <c r="I41" s="122"/>
-      <c r="J41" s="122"/>
-      <c r="K41" s="122"/>
-      <c r="L41" s="122"/>
-      <c r="M41" s="122"/>
-      <c r="N41" s="122"/>
-      <c r="O41" s="122"/>
-      <c r="P41" s="122"/>
-      <c r="Q41" s="122"/>
-      <c r="R41" s="122"/>
-      <c r="S41" s="122"/>
-      <c r="T41" s="122"/>
-      <c r="U41" s="122"/>
-      <c r="V41" s="122"/>
-      <c r="W41" s="122"/>
-      <c r="X41" s="122"/>
-      <c r="Y41" s="122"/>
-      <c r="Z41" s="122"/>
-      <c r="AA41" s="123"/>
-      <c r="AB41" s="123"/>
-      <c r="AC41" s="123"/>
-      <c r="AD41" s="123"/>
-      <c r="AE41" s="123"/>
-      <c r="AF41" s="123"/>
-      <c r="AG41" s="123"/>
-      <c r="AH41" s="123"/>
-      <c r="AI41" s="123"/>
-      <c r="AJ41" s="123"/>
-      <c r="AK41" s="124"/>
+      <c r="G41" s="162"/>
+      <c r="H41" s="162"/>
+      <c r="I41" s="162"/>
+      <c r="J41" s="162"/>
+      <c r="K41" s="162"/>
+      <c r="L41" s="162"/>
+      <c r="M41" s="162"/>
+      <c r="N41" s="162"/>
+      <c r="O41" s="162"/>
+      <c r="P41" s="162"/>
+      <c r="Q41" s="162"/>
+      <c r="R41" s="162"/>
+      <c r="S41" s="162"/>
+      <c r="T41" s="162"/>
+      <c r="U41" s="162"/>
+      <c r="V41" s="162"/>
+      <c r="W41" s="162"/>
+      <c r="X41" s="162"/>
+      <c r="Y41" s="162"/>
+      <c r="Z41" s="162"/>
+      <c r="AA41" s="163"/>
+      <c r="AB41" s="163"/>
+      <c r="AC41" s="163"/>
+      <c r="AD41" s="163"/>
+      <c r="AE41" s="163"/>
+      <c r="AF41" s="163"/>
+      <c r="AG41" s="163"/>
+      <c r="AH41" s="163"/>
+      <c r="AI41" s="163"/>
+      <c r="AJ41" s="163"/>
+      <c r="AK41" s="164"/>
     </row>
     <row r="42" spans="1:254" ht="23" customHeight="1">
       <c r="A42" s="45"/>
@@ -14032,37 +14056,37 @@
         <v>97</v>
       </c>
       <c r="F42" s="77"/>
-      <c r="G42" s="125"/>
-      <c r="H42" s="125"/>
-      <c r="I42" s="125"/>
-      <c r="J42" s="125"/>
-      <c r="K42" s="125"/>
-      <c r="L42" s="125"/>
-      <c r="M42" s="125"/>
-      <c r="N42" s="125"/>
-      <c r="O42" s="125"/>
-      <c r="P42" s="125"/>
-      <c r="Q42" s="127"/>
-      <c r="R42" s="127"/>
-      <c r="S42" s="127"/>
-      <c r="T42" s="127"/>
-      <c r="U42" s="127"/>
-      <c r="V42" s="127"/>
-      <c r="W42" s="127"/>
-      <c r="X42" s="127"/>
-      <c r="Y42" s="127"/>
-      <c r="Z42" s="127"/>
-      <c r="AA42" s="125"/>
-      <c r="AB42" s="125"/>
-      <c r="AC42" s="125"/>
-      <c r="AD42" s="125"/>
-      <c r="AE42" s="125"/>
-      <c r="AF42" s="125"/>
-      <c r="AG42" s="125"/>
-      <c r="AH42" s="125"/>
-      <c r="AI42" s="125"/>
-      <c r="AJ42" s="125"/>
-      <c r="AK42" s="126"/>
+      <c r="G42" s="165"/>
+      <c r="H42" s="165"/>
+      <c r="I42" s="165"/>
+      <c r="J42" s="165"/>
+      <c r="K42" s="165"/>
+      <c r="L42" s="165"/>
+      <c r="M42" s="165"/>
+      <c r="N42" s="165"/>
+      <c r="O42" s="165"/>
+      <c r="P42" s="165"/>
+      <c r="Q42" s="167"/>
+      <c r="R42" s="167"/>
+      <c r="S42" s="167"/>
+      <c r="T42" s="167"/>
+      <c r="U42" s="167"/>
+      <c r="V42" s="167"/>
+      <c r="W42" s="167"/>
+      <c r="X42" s="167"/>
+      <c r="Y42" s="167"/>
+      <c r="Z42" s="167"/>
+      <c r="AA42" s="165"/>
+      <c r="AB42" s="165"/>
+      <c r="AC42" s="165"/>
+      <c r="AD42" s="165"/>
+      <c r="AE42" s="165"/>
+      <c r="AF42" s="165"/>
+      <c r="AG42" s="165"/>
+      <c r="AH42" s="165"/>
+      <c r="AI42" s="165"/>
+      <c r="AJ42" s="165"/>
+      <c r="AK42" s="166"/>
     </row>
     <row r="43" spans="1:254" ht="23" customHeight="1" thickBot="1">
       <c r="A43" s="49"/>
@@ -14073,37 +14097,37 @@
         <v>98</v>
       </c>
       <c r="F43" s="82"/>
-      <c r="G43" s="119"/>
-      <c r="H43" s="119"/>
-      <c r="I43" s="119"/>
-      <c r="J43" s="119"/>
-      <c r="K43" s="119"/>
-      <c r="L43" s="119"/>
-      <c r="M43" s="119"/>
-      <c r="N43" s="119"/>
-      <c r="O43" s="119"/>
-      <c r="P43" s="119"/>
-      <c r="Q43" s="121"/>
-      <c r="R43" s="121"/>
-      <c r="S43" s="121"/>
-      <c r="T43" s="121"/>
-      <c r="U43" s="121"/>
-      <c r="V43" s="121"/>
-      <c r="W43" s="121"/>
-      <c r="X43" s="121"/>
-      <c r="Y43" s="121"/>
-      <c r="Z43" s="121"/>
-      <c r="AA43" s="119"/>
-      <c r="AB43" s="119"/>
-      <c r="AC43" s="119"/>
-      <c r="AD43" s="119"/>
-      <c r="AE43" s="119"/>
-      <c r="AF43" s="119"/>
-      <c r="AG43" s="119"/>
-      <c r="AH43" s="119"/>
-      <c r="AI43" s="119"/>
-      <c r="AJ43" s="119"/>
-      <c r="AK43" s="120"/>
+      <c r="G43" s="159"/>
+      <c r="H43" s="159"/>
+      <c r="I43" s="159"/>
+      <c r="J43" s="159"/>
+      <c r="K43" s="159"/>
+      <c r="L43" s="159"/>
+      <c r="M43" s="159"/>
+      <c r="N43" s="159"/>
+      <c r="O43" s="159"/>
+      <c r="P43" s="159"/>
+      <c r="Q43" s="161"/>
+      <c r="R43" s="161"/>
+      <c r="S43" s="161"/>
+      <c r="T43" s="161"/>
+      <c r="U43" s="161"/>
+      <c r="V43" s="161"/>
+      <c r="W43" s="161"/>
+      <c r="X43" s="161"/>
+      <c r="Y43" s="161"/>
+      <c r="Z43" s="161"/>
+      <c r="AA43" s="159"/>
+      <c r="AB43" s="159"/>
+      <c r="AC43" s="159"/>
+      <c r="AD43" s="159"/>
+      <c r="AE43" s="159"/>
+      <c r="AF43" s="159"/>
+      <c r="AG43" s="159"/>
+      <c r="AH43" s="159"/>
+      <c r="AI43" s="159"/>
+      <c r="AJ43" s="159"/>
+      <c r="AK43" s="160"/>
     </row>
     <row r="44" spans="1:254">
       <c r="A44" s="52"/>
@@ -14119,6 +14143,50 @@
     </row>
   </sheetData>
   <mergeCells count="60">
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="AA43:AK43"/>
+    <mergeCell ref="Q43:Z43"/>
+    <mergeCell ref="G43:P43"/>
+    <mergeCell ref="Q41:Z41"/>
+    <mergeCell ref="AA41:AK41"/>
+    <mergeCell ref="AA42:AK42"/>
+    <mergeCell ref="Q42:Z42"/>
+    <mergeCell ref="G42:P42"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="G41:P41"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="F12:F21"/>
+    <mergeCell ref="F27:F35"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="W5:Y7"/>
+    <mergeCell ref="AH5:AK7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="Z4:AC4"/>
+    <mergeCell ref="AD4:AG4"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="F22:F23"/>
     <mergeCell ref="A1:B1"/>
@@ -14135,62 +14203,18 @@
     <mergeCell ref="T4:Y4"/>
     <mergeCell ref="AH4:AK4"/>
     <mergeCell ref="T5:V7"/>
-    <mergeCell ref="W5:Y7"/>
-    <mergeCell ref="AH5:AK7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="Z4:AC4"/>
-    <mergeCell ref="AD4:AG4"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="F12:F21"/>
-    <mergeCell ref="F27:F35"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="AA43:AK43"/>
-    <mergeCell ref="Q43:Z43"/>
-    <mergeCell ref="G43:P43"/>
-    <mergeCell ref="Q41:Z41"/>
-    <mergeCell ref="AA41:AK41"/>
-    <mergeCell ref="AA42:AK42"/>
-    <mergeCell ref="Q42:Z42"/>
-    <mergeCell ref="G42:P42"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="G41:P41"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="G9:AK10">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>TEXT(G9,"aaa")="土"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>TEXT(G9,"aaa")="日"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="1">
-      <formula>TEXT(G9,"aaa")="土"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:AK40">
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>G$11="－"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14215,40 +14239,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:254" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A1" s="155" t="s">
+      <c r="A1" s="121" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="155"/>
+      <c r="B1" s="121"/>
       <c r="C1" s="85"/>
-      <c r="F1" s="156" t="s">
+      <c r="F1" s="122" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
-      <c r="L1" s="156"/>
-      <c r="M1" s="156"/>
-      <c r="N1" s="156"/>
-      <c r="O1" s="156"/>
-      <c r="P1" s="156"/>
-      <c r="Q1" s="156"/>
-      <c r="R1" s="156"/>
-      <c r="S1" s="156"/>
-      <c r="T1" s="156"/>
-      <c r="U1" s="156"/>
-      <c r="V1" s="156"/>
-      <c r="W1" s="156"/>
-      <c r="X1" s="156"/>
-      <c r="Y1" s="156"/>
-      <c r="Z1" s="156"/>
-      <c r="AA1" s="156"/>
-      <c r="AB1" s="156"/>
-      <c r="AC1" s="156"/>
-      <c r="AD1" s="156"/>
-      <c r="AE1" s="156"/>
-      <c r="AF1" s="156"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
+      <c r="AC1" s="122"/>
+      <c r="AD1" s="122"/>
+      <c r="AE1" s="122"/>
+      <c r="AF1" s="122"/>
       <c r="AI1" s="3"/>
       <c r="AJ1" s="3"/>
       <c r="AK1" s="3"/>
@@ -14714,47 +14738,47 @@
       <c r="IO2" s="3"/>
     </row>
     <row r="3" spans="1:254" s="2" customFormat="1" ht="20" customHeight="1" thickBot="1">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="123" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="125"/>
       <c r="E3" s="94"/>
       <c r="G3" s="51"/>
       <c r="H3" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="160" t="s">
+      <c r="K3" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="160"/>
-      <c r="M3" s="160" t="s">
+      <c r="L3" s="126"/>
+      <c r="M3" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="160"/>
-      <c r="O3" s="160"/>
-      <c r="P3" s="160" t="s">
+      <c r="N3" s="126"/>
+      <c r="O3" s="126"/>
+      <c r="P3" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="Q3" s="160"/>
-      <c r="R3" s="160"/>
+      <c r="Q3" s="126"/>
+      <c r="R3" s="126"/>
       <c r="S3" s="3"/>
-      <c r="T3" s="161" t="s">
+      <c r="T3" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="U3" s="162"/>
-      <c r="V3" s="162"/>
-      <c r="W3" s="162"/>
-      <c r="X3" s="162"/>
-      <c r="Y3" s="162"/>
-      <c r="Z3" s="162"/>
-      <c r="AA3" s="162"/>
-      <c r="AB3" s="162"/>
-      <c r="AC3" s="162"/>
-      <c r="AD3" s="162"/>
-      <c r="AE3" s="162"/>
-      <c r="AF3" s="163"/>
+      <c r="U3" s="128"/>
+      <c r="V3" s="128"/>
+      <c r="W3" s="128"/>
+      <c r="X3" s="128"/>
+      <c r="Y3" s="128"/>
+      <c r="Z3" s="128"/>
+      <c r="AA3" s="128"/>
+      <c r="AB3" s="128"/>
+      <c r="AC3" s="128"/>
+      <c r="AD3" s="128"/>
+      <c r="AE3" s="128"/>
+      <c r="AF3" s="129"/>
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
       <c r="AK3" s="3"/>
@@ -14983,42 +15007,42 @@
       <c r="H4" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="160" t="s">
+      <c r="K4" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="160"/>
-      <c r="M4" s="166">
+      <c r="L4" s="126"/>
+      <c r="M4" s="132">
         <v>46113</v>
       </c>
-      <c r="N4" s="166"/>
-      <c r="O4" s="166"/>
-      <c r="P4" s="160" t="s">
+      <c r="N4" s="132"/>
+      <c r="O4" s="132"/>
+      <c r="P4" s="126" t="s">
         <v>50</v>
       </c>
-      <c r="Q4" s="160"/>
-      <c r="R4" s="160"/>
+      <c r="Q4" s="126"/>
+      <c r="R4" s="126"/>
       <c r="S4" s="3"/>
-      <c r="T4" s="152" t="s">
+      <c r="T4" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="U4" s="153"/>
-      <c r="V4" s="153"/>
-      <c r="W4" s="154"/>
-      <c r="X4" s="152" t="s">
+      <c r="U4" s="134"/>
+      <c r="V4" s="134"/>
+      <c r="W4" s="135"/>
+      <c r="X4" s="133" t="s">
         <v>6</v>
       </c>
-      <c r="Y4" s="153"/>
-      <c r="Z4" s="154"/>
-      <c r="AA4" s="152" t="s">
+      <c r="Y4" s="134"/>
+      <c r="Z4" s="135"/>
+      <c r="AA4" s="133" t="s">
         <v>7</v>
       </c>
-      <c r="AB4" s="153"/>
-      <c r="AC4" s="154"/>
-      <c r="AD4" s="152" t="s">
+      <c r="AB4" s="134"/>
+      <c r="AC4" s="135"/>
+      <c r="AD4" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="AE4" s="153"/>
-      <c r="AF4" s="154"/>
+      <c r="AE4" s="134"/>
+      <c r="AF4" s="135"/>
       <c r="AI4" s="3"/>
       <c r="AJ4" s="3"/>
       <c r="AK4" s="3"/>
@@ -15246,21 +15270,21 @@
         <v>23</v>
       </c>
       <c r="S5" s="3"/>
-      <c r="T5" s="172" t="s">
+      <c r="T5" s="183" t="s">
         <v>64</v>
       </c>
-      <c r="U5" s="173"/>
-      <c r="V5" s="173"/>
-      <c r="W5" s="174"/>
+      <c r="U5" s="184"/>
+      <c r="V5" s="184"/>
+      <c r="W5" s="185"/>
       <c r="X5" s="11"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="12"/>
       <c r="AA5" s="11"/>
       <c r="AB5" s="3"/>
       <c r="AC5" s="12"/>
-      <c r="AD5" s="144"/>
-      <c r="AE5" s="145"/>
-      <c r="AF5" s="146"/>
+      <c r="AD5" s="146"/>
+      <c r="AE5" s="147"/>
+      <c r="AF5" s="148"/>
       <c r="AI5" s="3"/>
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3"/>
@@ -15492,19 +15516,19 @@
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
-      <c r="T6" s="172"/>
-      <c r="U6" s="173"/>
-      <c r="V6" s="173"/>
-      <c r="W6" s="174"/>
+      <c r="T6" s="183"/>
+      <c r="U6" s="184"/>
+      <c r="V6" s="184"/>
+      <c r="W6" s="185"/>
       <c r="X6" s="11"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="12"/>
       <c r="AA6" s="11"/>
       <c r="AB6" s="3"/>
       <c r="AC6" s="12"/>
-      <c r="AD6" s="144"/>
-      <c r="AE6" s="145"/>
-      <c r="AF6" s="146"/>
+      <c r="AD6" s="146"/>
+      <c r="AE6" s="147"/>
+      <c r="AF6" s="148"/>
       <c r="AI6" s="3"/>
       <c r="AJ6" s="3"/>
       <c r="AK6" s="3"/>
@@ -15736,19 +15760,19 @@
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
-      <c r="T7" s="175"/>
-      <c r="U7" s="176"/>
-      <c r="V7" s="176"/>
-      <c r="W7" s="177"/>
+      <c r="T7" s="186"/>
+      <c r="U7" s="187"/>
+      <c r="V7" s="187"/>
+      <c r="W7" s="188"/>
       <c r="X7" s="21"/>
       <c r="Y7" s="22"/>
       <c r="Z7" s="23"/>
       <c r="AA7" s="21"/>
       <c r="AB7" s="22"/>
       <c r="AC7" s="23"/>
-      <c r="AD7" s="147"/>
-      <c r="AE7" s="148"/>
-      <c r="AF7" s="149"/>
+      <c r="AD7" s="149"/>
+      <c r="AE7" s="150"/>
+      <c r="AF7" s="151"/>
       <c r="AG7" s="86"/>
       <c r="AI7" s="3"/>
       <c r="AJ7" s="3"/>
@@ -16265,22 +16289,22 @@
       <c r="R9" s="97" t="s">
         <v>76</v>
       </c>
-      <c r="S9" s="191" t="s">
+      <c r="S9" s="176" t="s">
         <v>78</v>
       </c>
-      <c r="T9" s="192"/>
-      <c r="U9" s="192"/>
-      <c r="V9" s="192"/>
-      <c r="W9" s="192"/>
-      <c r="X9" s="192"/>
-      <c r="Y9" s="192"/>
-      <c r="Z9" s="192"/>
-      <c r="AA9" s="192"/>
-      <c r="AB9" s="192"/>
-      <c r="AC9" s="192"/>
-      <c r="AD9" s="192"/>
-      <c r="AE9" s="192"/>
-      <c r="AF9" s="193"/>
+      <c r="T9" s="177"/>
+      <c r="U9" s="177"/>
+      <c r="V9" s="177"/>
+      <c r="W9" s="177"/>
+      <c r="X9" s="177"/>
+      <c r="Y9" s="177"/>
+      <c r="Z9" s="177"/>
+      <c r="AA9" s="177"/>
+      <c r="AB9" s="177"/>
+      <c r="AC9" s="177"/>
+      <c r="AD9" s="177"/>
+      <c r="AE9" s="177"/>
+      <c r="AF9" s="178"/>
       <c r="AI9" s="3"/>
       <c r="AJ9" s="3"/>
       <c r="AK9" s="3"/>
@@ -16499,8 +16523,8 @@
     </row>
     <row r="10" spans="1:254" s="2" customFormat="1" ht="23" hidden="1" customHeight="1">
       <c r="A10" s="29"/>
-      <c r="B10" s="150"/>
-      <c r="C10" s="151"/>
+      <c r="B10" s="152"/>
+      <c r="C10" s="153"/>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="31"/>
@@ -16826,10 +16850,10 @@
     </row>
     <row r="11" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A11" s="37"/>
-      <c r="B11" s="137" t="s">
+      <c r="B11" s="154" t="s">
         <v>105</v>
       </c>
-      <c r="C11" s="138"/>
+      <c r="C11" s="155"/>
       <c r="D11" s="92"/>
       <c r="E11" s="40"/>
       <c r="F11" s="93"/>
@@ -16845,20 +16869,20 @@
       <c r="P11" s="69"/>
       <c r="Q11" s="69"/>
       <c r="R11" s="69"/>
-      <c r="S11" s="180"/>
-      <c r="T11" s="181"/>
-      <c r="U11" s="181"/>
-      <c r="V11" s="181"/>
-      <c r="W11" s="181"/>
-      <c r="X11" s="181"/>
-      <c r="Y11" s="181"/>
-      <c r="Z11" s="181"/>
-      <c r="AA11" s="181"/>
-      <c r="AB11" s="181"/>
-      <c r="AC11" s="181"/>
-      <c r="AD11" s="181"/>
-      <c r="AE11" s="181"/>
-      <c r="AF11" s="182"/>
+      <c r="S11" s="191"/>
+      <c r="T11" s="192"/>
+      <c r="U11" s="192"/>
+      <c r="V11" s="192"/>
+      <c r="W11" s="192"/>
+      <c r="X11" s="192"/>
+      <c r="Y11" s="192"/>
+      <c r="Z11" s="192"/>
+      <c r="AA11" s="192"/>
+      <c r="AB11" s="192"/>
+      <c r="AC11" s="192"/>
+      <c r="AD11" s="192"/>
+      <c r="AE11" s="192"/>
+      <c r="AF11" s="193"/>
       <c r="AG11" s="69"/>
       <c r="AH11" s="69"/>
       <c r="AI11" s="69"/>
@@ -17084,10 +17108,10 @@
       <c r="A12" s="37">
         <v>1</v>
       </c>
-      <c r="B12" s="132" t="s">
+      <c r="B12" s="170" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="133"/>
+      <c r="C12" s="171"/>
       <c r="D12" s="92" t="s">
         <v>108</v>
       </c>
@@ -17105,20 +17129,20 @@
       <c r="P12" s="69"/>
       <c r="Q12" s="69"/>
       <c r="R12" s="69"/>
-      <c r="S12" s="183"/>
-      <c r="T12" s="184"/>
-      <c r="U12" s="184"/>
-      <c r="V12" s="184"/>
-      <c r="W12" s="184"/>
-      <c r="X12" s="184"/>
-      <c r="Y12" s="184"/>
-      <c r="Z12" s="184"/>
-      <c r="AA12" s="184"/>
-      <c r="AB12" s="184"/>
-      <c r="AC12" s="184"/>
-      <c r="AD12" s="184"/>
-      <c r="AE12" s="184"/>
-      <c r="AF12" s="185"/>
+      <c r="S12" s="172"/>
+      <c r="T12" s="173"/>
+      <c r="U12" s="173"/>
+      <c r="V12" s="173"/>
+      <c r="W12" s="173"/>
+      <c r="X12" s="173"/>
+      <c r="Y12" s="173"/>
+      <c r="Z12" s="173"/>
+      <c r="AA12" s="173"/>
+      <c r="AB12" s="173"/>
+      <c r="AC12" s="173"/>
+      <c r="AD12" s="173"/>
+      <c r="AE12" s="173"/>
+      <c r="AF12" s="174"/>
       <c r="AG12" s="69"/>
       <c r="AH12" s="69"/>
       <c r="AI12" s="69"/>
@@ -17344,10 +17368,10 @@
       <c r="A13" s="37">
         <v>2</v>
       </c>
-      <c r="B13" s="132" t="s">
+      <c r="B13" s="170" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="133"/>
+      <c r="C13" s="171"/>
       <c r="D13" s="92" t="s">
         <v>107</v>
       </c>
@@ -17365,20 +17389,20 @@
       <c r="P13" s="69"/>
       <c r="Q13" s="69"/>
       <c r="R13" s="69"/>
-      <c r="S13" s="183"/>
-      <c r="T13" s="184"/>
-      <c r="U13" s="184"/>
-      <c r="V13" s="184"/>
-      <c r="W13" s="184"/>
-      <c r="X13" s="184"/>
-      <c r="Y13" s="184"/>
-      <c r="Z13" s="184"/>
-      <c r="AA13" s="184"/>
-      <c r="AB13" s="184"/>
-      <c r="AC13" s="184"/>
-      <c r="AD13" s="184"/>
-      <c r="AE13" s="184"/>
-      <c r="AF13" s="185"/>
+      <c r="S13" s="172"/>
+      <c r="T13" s="173"/>
+      <c r="U13" s="173"/>
+      <c r="V13" s="173"/>
+      <c r="W13" s="173"/>
+      <c r="X13" s="173"/>
+      <c r="Y13" s="173"/>
+      <c r="Z13" s="173"/>
+      <c r="AA13" s="173"/>
+      <c r="AB13" s="173"/>
+      <c r="AC13" s="173"/>
+      <c r="AD13" s="173"/>
+      <c r="AE13" s="173"/>
+      <c r="AF13" s="174"/>
       <c r="AG13" s="69"/>
       <c r="AH13" s="69"/>
       <c r="AI13" s="69"/>
@@ -17604,10 +17628,10 @@
       <c r="A14" s="37">
         <v>3</v>
       </c>
-      <c r="B14" s="132" t="s">
+      <c r="B14" s="170" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="133"/>
+      <c r="C14" s="171"/>
       <c r="D14" s="92" t="s">
         <v>107</v>
       </c>
@@ -17625,20 +17649,20 @@
       <c r="P14" s="69"/>
       <c r="Q14" s="69"/>
       <c r="R14" s="69"/>
-      <c r="S14" s="183"/>
-      <c r="T14" s="184"/>
-      <c r="U14" s="184"/>
-      <c r="V14" s="184"/>
-      <c r="W14" s="184"/>
-      <c r="X14" s="184"/>
-      <c r="Y14" s="184"/>
-      <c r="Z14" s="184"/>
-      <c r="AA14" s="184"/>
-      <c r="AB14" s="184"/>
-      <c r="AC14" s="184"/>
-      <c r="AD14" s="184"/>
-      <c r="AE14" s="184"/>
-      <c r="AF14" s="185"/>
+      <c r="S14" s="172"/>
+      <c r="T14" s="173"/>
+      <c r="U14" s="173"/>
+      <c r="V14" s="173"/>
+      <c r="W14" s="173"/>
+      <c r="X14" s="173"/>
+      <c r="Y14" s="173"/>
+      <c r="Z14" s="173"/>
+      <c r="AA14" s="173"/>
+      <c r="AB14" s="173"/>
+      <c r="AC14" s="173"/>
+      <c r="AD14" s="173"/>
+      <c r="AE14" s="173"/>
+      <c r="AF14" s="174"/>
       <c r="AG14" s="69"/>
       <c r="AH14" s="69"/>
       <c r="AI14" s="69"/>
@@ -17864,10 +17888,10 @@
       <c r="A15" s="37">
         <v>4</v>
       </c>
-      <c r="B15" s="132" t="s">
+      <c r="B15" s="170" t="s">
         <v>82</v>
       </c>
-      <c r="C15" s="133"/>
+      <c r="C15" s="171"/>
       <c r="D15" s="92" t="s">
         <v>108</v>
       </c>
@@ -17885,20 +17909,20 @@
       <c r="P15" s="69"/>
       <c r="Q15" s="69"/>
       <c r="R15" s="69"/>
-      <c r="S15" s="183"/>
-      <c r="T15" s="184"/>
-      <c r="U15" s="184"/>
-      <c r="V15" s="184"/>
-      <c r="W15" s="184"/>
-      <c r="X15" s="184"/>
-      <c r="Y15" s="184"/>
-      <c r="Z15" s="184"/>
-      <c r="AA15" s="184"/>
-      <c r="AB15" s="184"/>
-      <c r="AC15" s="184"/>
-      <c r="AD15" s="184"/>
-      <c r="AE15" s="184"/>
-      <c r="AF15" s="185"/>
+      <c r="S15" s="172"/>
+      <c r="T15" s="173"/>
+      <c r="U15" s="173"/>
+      <c r="V15" s="173"/>
+      <c r="W15" s="173"/>
+      <c r="X15" s="173"/>
+      <c r="Y15" s="173"/>
+      <c r="Z15" s="173"/>
+      <c r="AA15" s="173"/>
+      <c r="AB15" s="173"/>
+      <c r="AC15" s="173"/>
+      <c r="AD15" s="173"/>
+      <c r="AE15" s="173"/>
+      <c r="AF15" s="174"/>
       <c r="AG15" s="69"/>
       <c r="AH15" s="69"/>
       <c r="AI15" s="69"/>
@@ -18124,10 +18148,10 @@
       <c r="A16" s="37">
         <v>5</v>
       </c>
-      <c r="B16" s="132" t="s">
+      <c r="B16" s="170" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="133"/>
+      <c r="C16" s="171"/>
       <c r="D16" s="92" t="s">
         <v>108</v>
       </c>
@@ -18145,20 +18169,20 @@
       <c r="P16" s="69"/>
       <c r="Q16" s="69"/>
       <c r="R16" s="69"/>
-      <c r="S16" s="183"/>
-      <c r="T16" s="184"/>
-      <c r="U16" s="184"/>
-      <c r="V16" s="184"/>
-      <c r="W16" s="184"/>
-      <c r="X16" s="184"/>
-      <c r="Y16" s="184"/>
-      <c r="Z16" s="184"/>
-      <c r="AA16" s="184"/>
-      <c r="AB16" s="184"/>
-      <c r="AC16" s="184"/>
-      <c r="AD16" s="184"/>
-      <c r="AE16" s="184"/>
-      <c r="AF16" s="185"/>
+      <c r="S16" s="172"/>
+      <c r="T16" s="173"/>
+      <c r="U16" s="173"/>
+      <c r="V16" s="173"/>
+      <c r="W16" s="173"/>
+      <c r="X16" s="173"/>
+      <c r="Y16" s="173"/>
+      <c r="Z16" s="173"/>
+      <c r="AA16" s="173"/>
+      <c r="AB16" s="173"/>
+      <c r="AC16" s="173"/>
+      <c r="AD16" s="173"/>
+      <c r="AE16" s="173"/>
+      <c r="AF16" s="174"/>
       <c r="AG16" s="69"/>
       <c r="AH16" s="69"/>
       <c r="AI16" s="69"/>
@@ -18384,10 +18408,10 @@
       <c r="A17" s="37">
         <v>6</v>
       </c>
-      <c r="B17" s="132" t="s">
+      <c r="B17" s="170" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="133"/>
+      <c r="C17" s="171"/>
       <c r="D17" s="92" t="s">
         <v>108</v>
       </c>
@@ -18405,20 +18429,20 @@
       <c r="P17" s="69"/>
       <c r="Q17" s="69"/>
       <c r="R17" s="69"/>
-      <c r="S17" s="183"/>
-      <c r="T17" s="184"/>
-      <c r="U17" s="184"/>
-      <c r="V17" s="184"/>
-      <c r="W17" s="184"/>
-      <c r="X17" s="184"/>
-      <c r="Y17" s="184"/>
-      <c r="Z17" s="184"/>
-      <c r="AA17" s="184"/>
-      <c r="AB17" s="184"/>
-      <c r="AC17" s="184"/>
-      <c r="AD17" s="184"/>
-      <c r="AE17" s="184"/>
-      <c r="AF17" s="185"/>
+      <c r="S17" s="172"/>
+      <c r="T17" s="173"/>
+      <c r="U17" s="173"/>
+      <c r="V17" s="173"/>
+      <c r="W17" s="173"/>
+      <c r="X17" s="173"/>
+      <c r="Y17" s="173"/>
+      <c r="Z17" s="173"/>
+      <c r="AA17" s="173"/>
+      <c r="AB17" s="173"/>
+      <c r="AC17" s="173"/>
+      <c r="AD17" s="173"/>
+      <c r="AE17" s="173"/>
+      <c r="AF17" s="174"/>
       <c r="AG17" s="69"/>
       <c r="AH17" s="69"/>
       <c r="AI17" s="69"/>
@@ -18644,10 +18668,10 @@
       <c r="A18" s="37">
         <v>7</v>
       </c>
-      <c r="B18" s="132" t="s">
+      <c r="B18" s="170" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="133"/>
+      <c r="C18" s="171"/>
       <c r="D18" s="92" t="s">
         <v>108</v>
       </c>
@@ -18665,20 +18689,20 @@
       <c r="P18" s="69"/>
       <c r="Q18" s="69"/>
       <c r="R18" s="69"/>
-      <c r="S18" s="183"/>
-      <c r="T18" s="184"/>
-      <c r="U18" s="184"/>
-      <c r="V18" s="184"/>
-      <c r="W18" s="184"/>
-      <c r="X18" s="184"/>
-      <c r="Y18" s="184"/>
-      <c r="Z18" s="184"/>
-      <c r="AA18" s="184"/>
-      <c r="AB18" s="184"/>
-      <c r="AC18" s="184"/>
-      <c r="AD18" s="184"/>
-      <c r="AE18" s="184"/>
-      <c r="AF18" s="185"/>
+      <c r="S18" s="172"/>
+      <c r="T18" s="173"/>
+      <c r="U18" s="173"/>
+      <c r="V18" s="173"/>
+      <c r="W18" s="173"/>
+      <c r="X18" s="173"/>
+      <c r="Y18" s="173"/>
+      <c r="Z18" s="173"/>
+      <c r="AA18" s="173"/>
+      <c r="AB18" s="173"/>
+      <c r="AC18" s="173"/>
+      <c r="AD18" s="173"/>
+      <c r="AE18" s="173"/>
+      <c r="AF18" s="174"/>
       <c r="AG18" s="69"/>
       <c r="AH18" s="69"/>
       <c r="AI18" s="69"/>
@@ -18904,10 +18928,10 @@
       <c r="A19" s="37">
         <v>8</v>
       </c>
-      <c r="B19" s="132" t="s">
+      <c r="B19" s="170" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="133"/>
+      <c r="C19" s="171"/>
       <c r="D19" s="92" t="s">
         <v>108</v>
       </c>
@@ -18925,20 +18949,20 @@
       <c r="P19" s="69"/>
       <c r="Q19" s="69"/>
       <c r="R19" s="69"/>
-      <c r="S19" s="183"/>
-      <c r="T19" s="184"/>
-      <c r="U19" s="184"/>
-      <c r="V19" s="184"/>
-      <c r="W19" s="184"/>
-      <c r="X19" s="184"/>
-      <c r="Y19" s="184"/>
-      <c r="Z19" s="184"/>
-      <c r="AA19" s="184"/>
-      <c r="AB19" s="184"/>
-      <c r="AC19" s="184"/>
-      <c r="AD19" s="184"/>
-      <c r="AE19" s="184"/>
-      <c r="AF19" s="185"/>
+      <c r="S19" s="172"/>
+      <c r="T19" s="173"/>
+      <c r="U19" s="173"/>
+      <c r="V19" s="173"/>
+      <c r="W19" s="173"/>
+      <c r="X19" s="173"/>
+      <c r="Y19" s="173"/>
+      <c r="Z19" s="173"/>
+      <c r="AA19" s="173"/>
+      <c r="AB19" s="173"/>
+      <c r="AC19" s="173"/>
+      <c r="AD19" s="173"/>
+      <c r="AE19" s="173"/>
+      <c r="AF19" s="174"/>
       <c r="AG19" s="69"/>
       <c r="AH19" s="69"/>
       <c r="AI19" s="69"/>
@@ -19162,10 +19186,10 @@
     </row>
     <row r="20" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A20" s="34"/>
-      <c r="B20" s="178" t="s">
+      <c r="B20" s="189" t="s">
         <v>120</v>
       </c>
-      <c r="C20" s="179"/>
+      <c r="C20" s="190"/>
       <c r="D20" s="35"/>
       <c r="E20" s="35"/>
       <c r="F20" s="36"/>
@@ -19181,20 +19205,20 @@
       <c r="P20" s="68"/>
       <c r="Q20" s="68"/>
       <c r="R20" s="68"/>
-      <c r="S20" s="183"/>
-      <c r="T20" s="184"/>
-      <c r="U20" s="184"/>
-      <c r="V20" s="184"/>
-      <c r="W20" s="184"/>
-      <c r="X20" s="184"/>
-      <c r="Y20" s="184"/>
-      <c r="Z20" s="184"/>
-      <c r="AA20" s="184"/>
-      <c r="AB20" s="184"/>
-      <c r="AC20" s="184"/>
-      <c r="AD20" s="184"/>
-      <c r="AE20" s="184"/>
-      <c r="AF20" s="185"/>
+      <c r="S20" s="172"/>
+      <c r="T20" s="173"/>
+      <c r="U20" s="173"/>
+      <c r="V20" s="173"/>
+      <c r="W20" s="173"/>
+      <c r="X20" s="173"/>
+      <c r="Y20" s="173"/>
+      <c r="Z20" s="173"/>
+      <c r="AA20" s="173"/>
+      <c r="AB20" s="173"/>
+      <c r="AC20" s="173"/>
+      <c r="AD20" s="173"/>
+      <c r="AE20" s="173"/>
+      <c r="AF20" s="174"/>
       <c r="AI20" s="3"/>
       <c r="AJ20" s="3"/>
       <c r="AK20" s="3"/>
@@ -19436,20 +19460,20 @@
       <c r="P21" s="69"/>
       <c r="Q21" s="69"/>
       <c r="R21" s="69"/>
-      <c r="S21" s="183"/>
-      <c r="T21" s="184"/>
-      <c r="U21" s="184"/>
-      <c r="V21" s="184"/>
-      <c r="W21" s="184"/>
-      <c r="X21" s="184"/>
-      <c r="Y21" s="184"/>
-      <c r="Z21" s="184"/>
-      <c r="AA21" s="184"/>
-      <c r="AB21" s="184"/>
-      <c r="AC21" s="184"/>
-      <c r="AD21" s="184"/>
-      <c r="AE21" s="184"/>
-      <c r="AF21" s="185"/>
+      <c r="S21" s="172"/>
+      <c r="T21" s="173"/>
+      <c r="U21" s="173"/>
+      <c r="V21" s="173"/>
+      <c r="W21" s="173"/>
+      <c r="X21" s="173"/>
+      <c r="Y21" s="173"/>
+      <c r="Z21" s="173"/>
+      <c r="AA21" s="173"/>
+      <c r="AB21" s="173"/>
+      <c r="AC21" s="173"/>
+      <c r="AD21" s="173"/>
+      <c r="AE21" s="173"/>
+      <c r="AF21" s="174"/>
       <c r="AI21" s="3"/>
       <c r="AJ21" s="3"/>
       <c r="AK21" s="3"/>
@@ -19691,20 +19715,20 @@
       <c r="P22" s="69"/>
       <c r="Q22" s="69"/>
       <c r="R22" s="69"/>
-      <c r="S22" s="183"/>
-      <c r="T22" s="184"/>
-      <c r="U22" s="184"/>
-      <c r="V22" s="184"/>
-      <c r="W22" s="184"/>
-      <c r="X22" s="184"/>
-      <c r="Y22" s="184"/>
-      <c r="Z22" s="184"/>
-      <c r="AA22" s="184"/>
-      <c r="AB22" s="184"/>
-      <c r="AC22" s="184"/>
-      <c r="AD22" s="184"/>
-      <c r="AE22" s="184"/>
-      <c r="AF22" s="185"/>
+      <c r="S22" s="172"/>
+      <c r="T22" s="173"/>
+      <c r="U22" s="173"/>
+      <c r="V22" s="173"/>
+      <c r="W22" s="173"/>
+      <c r="X22" s="173"/>
+      <c r="Y22" s="173"/>
+      <c r="Z22" s="173"/>
+      <c r="AA22" s="173"/>
+      <c r="AB22" s="173"/>
+      <c r="AC22" s="173"/>
+      <c r="AD22" s="173"/>
+      <c r="AE22" s="173"/>
+      <c r="AF22" s="174"/>
       <c r="AI22" s="3"/>
       <c r="AJ22" s="3"/>
       <c r="AK22" s="3"/>
@@ -19925,10 +19949,10 @@
       <c r="A23" s="101" t="s">
         <v>111</v>
       </c>
-      <c r="B23" s="186" t="s">
+      <c r="B23" s="181" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="187"/>
+      <c r="C23" s="182"/>
       <c r="D23" s="92" t="s">
         <v>110</v>
       </c>
@@ -19948,20 +19972,20 @@
       <c r="P23" s="69"/>
       <c r="Q23" s="69"/>
       <c r="R23" s="69"/>
-      <c r="S23" s="183"/>
-      <c r="T23" s="184"/>
-      <c r="U23" s="184"/>
-      <c r="V23" s="184"/>
-      <c r="W23" s="184"/>
-      <c r="X23" s="184"/>
-      <c r="Y23" s="184"/>
-      <c r="Z23" s="184"/>
-      <c r="AA23" s="184"/>
-      <c r="AB23" s="184"/>
-      <c r="AC23" s="184"/>
-      <c r="AD23" s="184"/>
-      <c r="AE23" s="184"/>
-      <c r="AF23" s="185"/>
+      <c r="S23" s="172"/>
+      <c r="T23" s="173"/>
+      <c r="U23" s="173"/>
+      <c r="V23" s="173"/>
+      <c r="W23" s="173"/>
+      <c r="X23" s="173"/>
+      <c r="Y23" s="173"/>
+      <c r="Z23" s="173"/>
+      <c r="AA23" s="173"/>
+      <c r="AB23" s="173"/>
+      <c r="AC23" s="173"/>
+      <c r="AD23" s="173"/>
+      <c r="AE23" s="173"/>
+      <c r="AF23" s="174"/>
       <c r="AI23" s="3"/>
       <c r="AJ23" s="3"/>
       <c r="AK23" s="3"/>
@@ -20205,20 +20229,20 @@
       <c r="P24" s="69"/>
       <c r="Q24" s="69"/>
       <c r="R24" s="69"/>
-      <c r="S24" s="183"/>
-      <c r="T24" s="184"/>
-      <c r="U24" s="184"/>
-      <c r="V24" s="184"/>
-      <c r="W24" s="184"/>
-      <c r="X24" s="184"/>
-      <c r="Y24" s="184"/>
-      <c r="Z24" s="184"/>
-      <c r="AA24" s="184"/>
-      <c r="AB24" s="184"/>
-      <c r="AC24" s="184"/>
-      <c r="AD24" s="184"/>
-      <c r="AE24" s="184"/>
-      <c r="AF24" s="185"/>
+      <c r="S24" s="172"/>
+      <c r="T24" s="173"/>
+      <c r="U24" s="173"/>
+      <c r="V24" s="173"/>
+      <c r="W24" s="173"/>
+      <c r="X24" s="173"/>
+      <c r="Y24" s="173"/>
+      <c r="Z24" s="173"/>
+      <c r="AA24" s="173"/>
+      <c r="AB24" s="173"/>
+      <c r="AC24" s="173"/>
+      <c r="AD24" s="173"/>
+      <c r="AE24" s="173"/>
+      <c r="AF24" s="174"/>
       <c r="AI24" s="3"/>
       <c r="AJ24" s="3"/>
       <c r="AK24" s="3"/>
@@ -20460,20 +20484,20 @@
       <c r="P25" s="69"/>
       <c r="Q25" s="69"/>
       <c r="R25" s="69"/>
-      <c r="S25" s="183"/>
-      <c r="T25" s="184"/>
-      <c r="U25" s="184"/>
-      <c r="V25" s="184"/>
-      <c r="W25" s="184"/>
-      <c r="X25" s="184"/>
-      <c r="Y25" s="184"/>
-      <c r="Z25" s="184"/>
-      <c r="AA25" s="184"/>
-      <c r="AB25" s="184"/>
-      <c r="AC25" s="184"/>
-      <c r="AD25" s="184"/>
-      <c r="AE25" s="184"/>
-      <c r="AF25" s="185"/>
+      <c r="S25" s="172"/>
+      <c r="T25" s="173"/>
+      <c r="U25" s="173"/>
+      <c r="V25" s="173"/>
+      <c r="W25" s="173"/>
+      <c r="X25" s="173"/>
+      <c r="Y25" s="173"/>
+      <c r="Z25" s="173"/>
+      <c r="AA25" s="173"/>
+      <c r="AB25" s="173"/>
+      <c r="AC25" s="173"/>
+      <c r="AD25" s="173"/>
+      <c r="AE25" s="173"/>
+      <c r="AF25" s="174"/>
       <c r="AI25" s="3"/>
       <c r="AJ25" s="3"/>
       <c r="AK25" s="3"/>
@@ -20715,20 +20739,20 @@
       <c r="P26" s="69"/>
       <c r="Q26" s="69"/>
       <c r="R26" s="69"/>
-      <c r="S26" s="183"/>
-      <c r="T26" s="184"/>
-      <c r="U26" s="184"/>
-      <c r="V26" s="184"/>
-      <c r="W26" s="184"/>
-      <c r="X26" s="184"/>
-      <c r="Y26" s="184"/>
-      <c r="Z26" s="184"/>
-      <c r="AA26" s="184"/>
-      <c r="AB26" s="184"/>
-      <c r="AC26" s="184"/>
-      <c r="AD26" s="184"/>
-      <c r="AE26" s="184"/>
-      <c r="AF26" s="185"/>
+      <c r="S26" s="172"/>
+      <c r="T26" s="173"/>
+      <c r="U26" s="173"/>
+      <c r="V26" s="173"/>
+      <c r="W26" s="173"/>
+      <c r="X26" s="173"/>
+      <c r="Y26" s="173"/>
+      <c r="Z26" s="173"/>
+      <c r="AA26" s="173"/>
+      <c r="AB26" s="173"/>
+      <c r="AC26" s="173"/>
+      <c r="AD26" s="173"/>
+      <c r="AE26" s="173"/>
+      <c r="AF26" s="174"/>
       <c r="AI26" s="3"/>
       <c r="AJ26" s="3"/>
       <c r="AK26" s="3"/>
@@ -20970,20 +20994,20 @@
       <c r="P27" s="69"/>
       <c r="Q27" s="69"/>
       <c r="R27" s="69"/>
-      <c r="S27" s="183"/>
-      <c r="T27" s="184"/>
-      <c r="U27" s="184"/>
-      <c r="V27" s="184"/>
-      <c r="W27" s="184"/>
-      <c r="X27" s="184"/>
-      <c r="Y27" s="184"/>
-      <c r="Z27" s="184"/>
-      <c r="AA27" s="184"/>
-      <c r="AB27" s="184"/>
-      <c r="AC27" s="184"/>
-      <c r="AD27" s="184"/>
-      <c r="AE27" s="184"/>
-      <c r="AF27" s="185"/>
+      <c r="S27" s="172"/>
+      <c r="T27" s="173"/>
+      <c r="U27" s="173"/>
+      <c r="V27" s="173"/>
+      <c r="W27" s="173"/>
+      <c r="X27" s="173"/>
+      <c r="Y27" s="173"/>
+      <c r="Z27" s="173"/>
+      <c r="AA27" s="173"/>
+      <c r="AB27" s="173"/>
+      <c r="AC27" s="173"/>
+      <c r="AD27" s="173"/>
+      <c r="AE27" s="173"/>
+      <c r="AF27" s="174"/>
       <c r="AI27" s="3"/>
       <c r="AJ27" s="3"/>
       <c r="AK27" s="3"/>
@@ -21225,20 +21249,20 @@
       <c r="P28" s="69"/>
       <c r="Q28" s="69"/>
       <c r="R28" s="69"/>
-      <c r="S28" s="183"/>
-      <c r="T28" s="184"/>
-      <c r="U28" s="184"/>
-      <c r="V28" s="184"/>
-      <c r="W28" s="184"/>
-      <c r="X28" s="184"/>
-      <c r="Y28" s="184"/>
-      <c r="Z28" s="184"/>
-      <c r="AA28" s="184"/>
-      <c r="AB28" s="184"/>
-      <c r="AC28" s="184"/>
-      <c r="AD28" s="184"/>
-      <c r="AE28" s="184"/>
-      <c r="AF28" s="185"/>
+      <c r="S28" s="172"/>
+      <c r="T28" s="173"/>
+      <c r="U28" s="173"/>
+      <c r="V28" s="173"/>
+      <c r="W28" s="173"/>
+      <c r="X28" s="173"/>
+      <c r="Y28" s="173"/>
+      <c r="Z28" s="173"/>
+      <c r="AA28" s="173"/>
+      <c r="AB28" s="173"/>
+      <c r="AC28" s="173"/>
+      <c r="AD28" s="173"/>
+      <c r="AE28" s="173"/>
+      <c r="AF28" s="174"/>
       <c r="AI28" s="3"/>
       <c r="AJ28" s="3"/>
       <c r="AK28" s="3"/>
@@ -21476,20 +21500,20 @@
       <c r="P29" s="69"/>
       <c r="Q29" s="69"/>
       <c r="R29" s="69"/>
-      <c r="S29" s="183"/>
-      <c r="T29" s="184"/>
-      <c r="U29" s="184"/>
-      <c r="V29" s="184"/>
-      <c r="W29" s="184"/>
-      <c r="X29" s="184"/>
-      <c r="Y29" s="184"/>
-      <c r="Z29" s="184"/>
-      <c r="AA29" s="184"/>
-      <c r="AB29" s="184"/>
-      <c r="AC29" s="184"/>
-      <c r="AD29" s="184"/>
-      <c r="AE29" s="184"/>
-      <c r="AF29" s="185"/>
+      <c r="S29" s="172"/>
+      <c r="T29" s="173"/>
+      <c r="U29" s="173"/>
+      <c r="V29" s="173"/>
+      <c r="W29" s="173"/>
+      <c r="X29" s="173"/>
+      <c r="Y29" s="173"/>
+      <c r="Z29" s="173"/>
+      <c r="AA29" s="173"/>
+      <c r="AB29" s="173"/>
+      <c r="AC29" s="173"/>
+      <c r="AD29" s="173"/>
+      <c r="AE29" s="173"/>
+      <c r="AF29" s="174"/>
       <c r="AI29" s="3"/>
       <c r="AJ29" s="3"/>
       <c r="AK29" s="3"/>
@@ -21708,10 +21732,10 @@
     </row>
     <row r="30" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A30" s="37"/>
-      <c r="B30" s="137" t="s">
+      <c r="B30" s="154" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="138"/>
+      <c r="C30" s="155"/>
       <c r="D30" s="92"/>
       <c r="E30" s="92"/>
       <c r="F30" s="36"/>
@@ -21727,20 +21751,20 @@
       <c r="P30" s="69"/>
       <c r="Q30" s="69"/>
       <c r="R30" s="69"/>
-      <c r="S30" s="183"/>
-      <c r="T30" s="184"/>
-      <c r="U30" s="184"/>
-      <c r="V30" s="184"/>
-      <c r="W30" s="184"/>
-      <c r="X30" s="184"/>
-      <c r="Y30" s="184"/>
-      <c r="Z30" s="184"/>
-      <c r="AA30" s="184"/>
-      <c r="AB30" s="184"/>
-      <c r="AC30" s="184"/>
-      <c r="AD30" s="184"/>
-      <c r="AE30" s="184"/>
-      <c r="AF30" s="185"/>
+      <c r="S30" s="172"/>
+      <c r="T30" s="173"/>
+      <c r="U30" s="173"/>
+      <c r="V30" s="173"/>
+      <c r="W30" s="173"/>
+      <c r="X30" s="173"/>
+      <c r="Y30" s="173"/>
+      <c r="Z30" s="173"/>
+      <c r="AA30" s="173"/>
+      <c r="AB30" s="173"/>
+      <c r="AC30" s="173"/>
+      <c r="AD30" s="173"/>
+      <c r="AE30" s="173"/>
+      <c r="AF30" s="174"/>
       <c r="AI30" s="3"/>
       <c r="AJ30" s="3"/>
       <c r="AK30" s="3"/>
@@ -21963,7 +21987,7 @@
         <v>92</v>
       </c>
       <c r="C31" s="118"/>
-      <c r="D31" s="134" t="s">
+      <c r="D31" s="158" t="s">
         <v>117</v>
       </c>
       <c r="E31" s="92"/>
@@ -21980,20 +22004,20 @@
       <c r="P31" s="69"/>
       <c r="Q31" s="69"/>
       <c r="R31" s="69"/>
-      <c r="S31" s="183"/>
-      <c r="T31" s="184"/>
-      <c r="U31" s="184"/>
-      <c r="V31" s="184"/>
-      <c r="W31" s="184"/>
-      <c r="X31" s="184"/>
-      <c r="Y31" s="184"/>
-      <c r="Z31" s="184"/>
-      <c r="AA31" s="184"/>
-      <c r="AB31" s="184"/>
-      <c r="AC31" s="184"/>
-      <c r="AD31" s="184"/>
-      <c r="AE31" s="184"/>
-      <c r="AF31" s="185"/>
+      <c r="S31" s="172"/>
+      <c r="T31" s="173"/>
+      <c r="U31" s="173"/>
+      <c r="V31" s="173"/>
+      <c r="W31" s="173"/>
+      <c r="X31" s="173"/>
+      <c r="Y31" s="173"/>
+      <c r="Z31" s="173"/>
+      <c r="AA31" s="173"/>
+      <c r="AB31" s="173"/>
+      <c r="AC31" s="173"/>
+      <c r="AD31" s="173"/>
+      <c r="AE31" s="173"/>
+      <c r="AF31" s="174"/>
       <c r="AI31" s="3"/>
       <c r="AJ31" s="3"/>
       <c r="AK31" s="3"/>
@@ -22216,7 +22240,7 @@
         <v>93</v>
       </c>
       <c r="C32" s="118"/>
-      <c r="D32" s="135"/>
+      <c r="D32" s="119"/>
       <c r="E32" s="92" t="s">
         <v>47</v>
       </c>
@@ -22233,20 +22257,20 @@
       <c r="P32" s="68"/>
       <c r="Q32" s="68"/>
       <c r="R32" s="68"/>
-      <c r="S32" s="183"/>
-      <c r="T32" s="184"/>
-      <c r="U32" s="184"/>
-      <c r="V32" s="184"/>
-      <c r="W32" s="184"/>
-      <c r="X32" s="184"/>
-      <c r="Y32" s="184"/>
-      <c r="Z32" s="184"/>
-      <c r="AA32" s="184"/>
-      <c r="AB32" s="184"/>
-      <c r="AC32" s="184"/>
-      <c r="AD32" s="184"/>
-      <c r="AE32" s="184"/>
-      <c r="AF32" s="185"/>
+      <c r="S32" s="172"/>
+      <c r="T32" s="173"/>
+      <c r="U32" s="173"/>
+      <c r="V32" s="173"/>
+      <c r="W32" s="173"/>
+      <c r="X32" s="173"/>
+      <c r="Y32" s="173"/>
+      <c r="Z32" s="173"/>
+      <c r="AA32" s="173"/>
+      <c r="AB32" s="173"/>
+      <c r="AC32" s="173"/>
+      <c r="AD32" s="173"/>
+      <c r="AE32" s="173"/>
+      <c r="AF32" s="174"/>
       <c r="AI32" s="3"/>
       <c r="AJ32" s="3"/>
       <c r="AK32" s="3"/>
@@ -22469,7 +22493,7 @@
         <v>94</v>
       </c>
       <c r="C33" s="118"/>
-      <c r="D33" s="136"/>
+      <c r="D33" s="120"/>
       <c r="E33" s="92"/>
       <c r="F33" s="36"/>
       <c r="G33" s="68"/>
@@ -22484,20 +22508,20 @@
       <c r="P33" s="68"/>
       <c r="Q33" s="68"/>
       <c r="R33" s="68"/>
-      <c r="S33" s="183"/>
-      <c r="T33" s="184"/>
-      <c r="U33" s="184"/>
-      <c r="V33" s="184"/>
-      <c r="W33" s="184"/>
-      <c r="X33" s="184"/>
-      <c r="Y33" s="184"/>
-      <c r="Z33" s="184"/>
-      <c r="AA33" s="184"/>
-      <c r="AB33" s="184"/>
-      <c r="AC33" s="184"/>
-      <c r="AD33" s="184"/>
-      <c r="AE33" s="184"/>
-      <c r="AF33" s="185"/>
+      <c r="S33" s="172"/>
+      <c r="T33" s="173"/>
+      <c r="U33" s="173"/>
+      <c r="V33" s="173"/>
+      <c r="W33" s="173"/>
+      <c r="X33" s="173"/>
+      <c r="Y33" s="173"/>
+      <c r="Z33" s="173"/>
+      <c r="AA33" s="173"/>
+      <c r="AB33" s="173"/>
+      <c r="AC33" s="173"/>
+      <c r="AD33" s="173"/>
+      <c r="AE33" s="173"/>
+      <c r="AF33" s="174"/>
       <c r="AI33" s="3"/>
       <c r="AJ33" s="3"/>
       <c r="AK33" s="3"/>
@@ -22716,10 +22740,10 @@
     </row>
     <row r="34" spans="1:249" s="2" customFormat="1" ht="28.25" customHeight="1">
       <c r="A34" s="38"/>
-      <c r="B34" s="137" t="s">
+      <c r="B34" s="154" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="138"/>
+      <c r="C34" s="155"/>
       <c r="D34" s="35"/>
       <c r="E34" s="35"/>
       <c r="F34" s="39"/>
@@ -22735,20 +22759,20 @@
       <c r="P34" s="68"/>
       <c r="Q34" s="68"/>
       <c r="R34" s="68"/>
-      <c r="S34" s="183"/>
-      <c r="T34" s="184"/>
-      <c r="U34" s="184"/>
-      <c r="V34" s="184"/>
-      <c r="W34" s="184"/>
-      <c r="X34" s="184"/>
-      <c r="Y34" s="184"/>
-      <c r="Z34" s="184"/>
-      <c r="AA34" s="184"/>
-      <c r="AB34" s="184"/>
-      <c r="AC34" s="184"/>
-      <c r="AD34" s="184"/>
-      <c r="AE34" s="184"/>
-      <c r="AF34" s="185"/>
+      <c r="S34" s="172"/>
+      <c r="T34" s="173"/>
+      <c r="U34" s="173"/>
+      <c r="V34" s="173"/>
+      <c r="W34" s="173"/>
+      <c r="X34" s="173"/>
+      <c r="Y34" s="173"/>
+      <c r="Z34" s="173"/>
+      <c r="AA34" s="173"/>
+      <c r="AB34" s="173"/>
+      <c r="AC34" s="173"/>
+      <c r="AD34" s="173"/>
+      <c r="AE34" s="173"/>
+      <c r="AF34" s="174"/>
       <c r="AI34" s="3"/>
       <c r="AJ34" s="3"/>
       <c r="AK34" s="3"/>
@@ -22969,15 +22993,15 @@
       <c r="A35" s="37">
         <v>1</v>
       </c>
-      <c r="B35" s="130" t="s">
+      <c r="B35" s="156" t="s">
         <v>104</v>
       </c>
-      <c r="C35" s="131"/>
+      <c r="C35" s="157"/>
       <c r="D35" s="96"/>
       <c r="E35" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="F35" s="134" t="s">
+      <c r="F35" s="158" t="s">
         <v>95</v>
       </c>
       <c r="G35" s="69"/>
@@ -22992,20 +23016,20 @@
       <c r="P35" s="69"/>
       <c r="Q35" s="69"/>
       <c r="R35" s="69"/>
-      <c r="S35" s="183"/>
-      <c r="T35" s="184"/>
-      <c r="U35" s="184"/>
-      <c r="V35" s="184"/>
-      <c r="W35" s="184"/>
-      <c r="X35" s="184"/>
-      <c r="Y35" s="184"/>
-      <c r="Z35" s="184"/>
-      <c r="AA35" s="184"/>
-      <c r="AB35" s="184"/>
-      <c r="AC35" s="184"/>
-      <c r="AD35" s="184"/>
-      <c r="AE35" s="184"/>
-      <c r="AF35" s="185"/>
+      <c r="S35" s="172"/>
+      <c r="T35" s="173"/>
+      <c r="U35" s="173"/>
+      <c r="V35" s="173"/>
+      <c r="W35" s="173"/>
+      <c r="X35" s="173"/>
+      <c r="Y35" s="173"/>
+      <c r="Z35" s="173"/>
+      <c r="AA35" s="173"/>
+      <c r="AB35" s="173"/>
+      <c r="AC35" s="173"/>
+      <c r="AD35" s="173"/>
+      <c r="AE35" s="173"/>
+      <c r="AF35" s="174"/>
       <c r="AI35" s="3"/>
       <c r="AJ35" s="3"/>
       <c r="AK35" s="3"/>
@@ -23232,7 +23256,7 @@
       <c r="E36" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="F36" s="135"/>
+      <c r="F36" s="119"/>
       <c r="G36" s="68"/>
       <c r="H36" s="68"/>
       <c r="I36" s="68"/>
@@ -23245,20 +23269,20 @@
       <c r="P36" s="68"/>
       <c r="Q36" s="68"/>
       <c r="R36" s="68"/>
-      <c r="S36" s="183"/>
-      <c r="T36" s="184"/>
-      <c r="U36" s="184"/>
-      <c r="V36" s="184"/>
-      <c r="W36" s="184"/>
-      <c r="X36" s="184"/>
-      <c r="Y36" s="184"/>
-      <c r="Z36" s="184"/>
-      <c r="AA36" s="184"/>
-      <c r="AB36" s="184"/>
-      <c r="AC36" s="184"/>
-      <c r="AD36" s="184"/>
-      <c r="AE36" s="184"/>
-      <c r="AF36" s="185"/>
+      <c r="S36" s="172"/>
+      <c r="T36" s="173"/>
+      <c r="U36" s="173"/>
+      <c r="V36" s="173"/>
+      <c r="W36" s="173"/>
+      <c r="X36" s="173"/>
+      <c r="Y36" s="173"/>
+      <c r="Z36" s="173"/>
+      <c r="AA36" s="173"/>
+      <c r="AB36" s="173"/>
+      <c r="AC36" s="173"/>
+      <c r="AD36" s="173"/>
+      <c r="AE36" s="173"/>
+      <c r="AF36" s="174"/>
       <c r="AI36" s="3"/>
       <c r="AJ36" s="3"/>
       <c r="AK36" s="3"/>
@@ -23479,11 +23503,11 @@
       <c r="A37" s="37">
         <v>3</v>
       </c>
-      <c r="B37" s="130"/>
-      <c r="C37" s="131"/>
+      <c r="B37" s="156"/>
+      <c r="C37" s="157"/>
       <c r="D37" s="92"/>
       <c r="E37" s="35"/>
-      <c r="F37" s="135"/>
+      <c r="F37" s="119"/>
       <c r="G37" s="68"/>
       <c r="H37" s="68"/>
       <c r="I37" s="68"/>
@@ -23496,20 +23520,20 @@
       <c r="P37" s="68"/>
       <c r="Q37" s="68"/>
       <c r="R37" s="68"/>
-      <c r="S37" s="183"/>
-      <c r="T37" s="184"/>
-      <c r="U37" s="184"/>
-      <c r="V37" s="184"/>
-      <c r="W37" s="184"/>
-      <c r="X37" s="184"/>
-      <c r="Y37" s="184"/>
-      <c r="Z37" s="184"/>
-      <c r="AA37" s="184"/>
-      <c r="AB37" s="184"/>
-      <c r="AC37" s="184"/>
-      <c r="AD37" s="184"/>
-      <c r="AE37" s="184"/>
-      <c r="AF37" s="185"/>
+      <c r="S37" s="172"/>
+      <c r="T37" s="173"/>
+      <c r="U37" s="173"/>
+      <c r="V37" s="173"/>
+      <c r="W37" s="173"/>
+      <c r="X37" s="173"/>
+      <c r="Y37" s="173"/>
+      <c r="Z37" s="173"/>
+      <c r="AA37" s="173"/>
+      <c r="AB37" s="173"/>
+      <c r="AC37" s="173"/>
+      <c r="AD37" s="173"/>
+      <c r="AE37" s="173"/>
+      <c r="AF37" s="174"/>
       <c r="AI37" s="3"/>
       <c r="AJ37" s="3"/>
       <c r="AK37" s="3"/>
@@ -23728,10 +23752,10 @@
     </row>
     <row r="38" spans="1:249" s="2" customFormat="1" ht="42" customHeight="1" thickBot="1">
       <c r="A38" s="41"/>
-      <c r="B38" s="128" t="s">
+      <c r="B38" s="168" t="s">
         <v>63</v>
       </c>
-      <c r="C38" s="129"/>
+      <c r="C38" s="169"/>
       <c r="D38" s="42" t="s">
         <v>16</v>
       </c>
@@ -23989,29 +24013,29 @@
       <c r="E39" s="44"/>
       <c r="F39" s="57"/>
       <c r="G39" s="75"/>
-      <c r="H39" s="188"/>
-      <c r="I39" s="188"/>
-      <c r="J39" s="188"/>
-      <c r="K39" s="188"/>
+      <c r="H39" s="180"/>
+      <c r="I39" s="180"/>
+      <c r="J39" s="180"/>
+      <c r="K39" s="180"/>
       <c r="L39" s="76"/>
       <c r="M39" s="75"/>
-      <c r="N39" s="188"/>
-      <c r="O39" s="188"/>
-      <c r="P39" s="188"/>
-      <c r="Q39" s="188"/>
+      <c r="N39" s="180"/>
+      <c r="O39" s="180"/>
+      <c r="P39" s="180"/>
+      <c r="Q39" s="180"/>
       <c r="R39" s="76"/>
       <c r="S39" s="75"/>
-      <c r="T39" s="188"/>
-      <c r="U39" s="188"/>
-      <c r="V39" s="188"/>
+      <c r="T39" s="180"/>
+      <c r="U39" s="180"/>
+      <c r="V39" s="180"/>
       <c r="W39" s="75"/>
-      <c r="X39" s="188"/>
-      <c r="Y39" s="188"/>
-      <c r="Z39" s="188"/>
+      <c r="X39" s="180"/>
+      <c r="Y39" s="180"/>
+      <c r="Z39" s="180"/>
       <c r="AA39" s="76"/>
       <c r="AB39" s="75"/>
-      <c r="AC39" s="188"/>
-      <c r="AD39" s="188"/>
+      <c r="AC39" s="180"/>
+      <c r="AD39" s="180"/>
       <c r="AE39" s="55"/>
       <c r="AF39" s="56"/>
       <c r="AI39" s="3"/>
@@ -24242,29 +24266,29 @@
       <c r="E40" s="90"/>
       <c r="F40" s="58"/>
       <c r="G40" s="77"/>
-      <c r="H40" s="189"/>
-      <c r="I40" s="189"/>
-      <c r="J40" s="189"/>
-      <c r="K40" s="189"/>
+      <c r="H40" s="179"/>
+      <c r="I40" s="179"/>
+      <c r="J40" s="179"/>
+      <c r="K40" s="179"/>
       <c r="L40" s="78"/>
       <c r="M40" s="77"/>
-      <c r="N40" s="189"/>
-      <c r="O40" s="189"/>
-      <c r="P40" s="189"/>
-      <c r="Q40" s="189"/>
+      <c r="N40" s="179"/>
+      <c r="O40" s="179"/>
+      <c r="P40" s="179"/>
+      <c r="Q40" s="179"/>
       <c r="R40" s="78"/>
       <c r="S40" s="77"/>
-      <c r="T40" s="189"/>
-      <c r="U40" s="189"/>
-      <c r="V40" s="189"/>
+      <c r="T40" s="179"/>
+      <c r="U40" s="179"/>
+      <c r="V40" s="179"/>
       <c r="W40" s="77"/>
-      <c r="X40" s="189"/>
-      <c r="Y40" s="189"/>
-      <c r="Z40" s="189"/>
+      <c r="X40" s="179"/>
+      <c r="Y40" s="179"/>
+      <c r="Z40" s="179"/>
       <c r="AA40" s="78"/>
       <c r="AB40" s="77"/>
-      <c r="AC40" s="189"/>
-      <c r="AD40" s="189"/>
+      <c r="AC40" s="179"/>
+      <c r="AD40" s="179"/>
       <c r="AE40" s="61"/>
       <c r="AF40" s="79"/>
       <c r="AI40" s="3"/>
@@ -24495,29 +24519,29 @@
       <c r="E41" s="91"/>
       <c r="F41" s="59"/>
       <c r="G41" s="77"/>
-      <c r="H41" s="189"/>
-      <c r="I41" s="189"/>
-      <c r="J41" s="189"/>
-      <c r="K41" s="189"/>
+      <c r="H41" s="179"/>
+      <c r="I41" s="179"/>
+      <c r="J41" s="179"/>
+      <c r="K41" s="179"/>
       <c r="L41" s="80"/>
       <c r="M41" s="77"/>
-      <c r="N41" s="189"/>
-      <c r="O41" s="189"/>
-      <c r="P41" s="189"/>
-      <c r="Q41" s="189"/>
+      <c r="N41" s="179"/>
+      <c r="O41" s="179"/>
+      <c r="P41" s="179"/>
+      <c r="Q41" s="179"/>
       <c r="R41" s="80"/>
       <c r="S41" s="77"/>
-      <c r="T41" s="189"/>
-      <c r="U41" s="189"/>
-      <c r="V41" s="189"/>
+      <c r="T41" s="179"/>
+      <c r="U41" s="179"/>
+      <c r="V41" s="179"/>
       <c r="W41" s="77"/>
-      <c r="X41" s="189"/>
-      <c r="Y41" s="189"/>
-      <c r="Z41" s="189"/>
+      <c r="X41" s="179"/>
+      <c r="Y41" s="179"/>
+      <c r="Z41" s="179"/>
       <c r="AA41" s="80"/>
       <c r="AB41" s="77"/>
-      <c r="AC41" s="189"/>
-      <c r="AD41" s="189"/>
+      <c r="AC41" s="179"/>
+      <c r="AD41" s="179"/>
       <c r="AE41" s="62"/>
       <c r="AF41" s="81"/>
       <c r="AI41" s="3"/>
@@ -24748,29 +24772,29 @@
       <c r="E42" s="91"/>
       <c r="F42" s="59"/>
       <c r="G42" s="77"/>
-      <c r="H42" s="189"/>
-      <c r="I42" s="189"/>
-      <c r="J42" s="189"/>
-      <c r="K42" s="189"/>
+      <c r="H42" s="179"/>
+      <c r="I42" s="179"/>
+      <c r="J42" s="179"/>
+      <c r="K42" s="179"/>
       <c r="L42" s="80"/>
       <c r="M42" s="77"/>
-      <c r="N42" s="189"/>
-      <c r="O42" s="189"/>
-      <c r="P42" s="189"/>
-      <c r="Q42" s="189"/>
+      <c r="N42" s="179"/>
+      <c r="O42" s="179"/>
+      <c r="P42" s="179"/>
+      <c r="Q42" s="179"/>
       <c r="R42" s="80"/>
       <c r="S42" s="77"/>
-      <c r="T42" s="189"/>
-      <c r="U42" s="189"/>
-      <c r="V42" s="189"/>
+      <c r="T42" s="179"/>
+      <c r="U42" s="179"/>
+      <c r="V42" s="179"/>
       <c r="W42" s="77"/>
-      <c r="X42" s="189"/>
-      <c r="Y42" s="189"/>
-      <c r="Z42" s="189"/>
+      <c r="X42" s="179"/>
+      <c r="Y42" s="179"/>
+      <c r="Z42" s="179"/>
       <c r="AA42" s="80"/>
       <c r="AB42" s="77"/>
-      <c r="AC42" s="189"/>
-      <c r="AD42" s="189"/>
+      <c r="AC42" s="179"/>
+      <c r="AD42" s="179"/>
       <c r="AE42" s="62"/>
       <c r="AF42" s="81"/>
       <c r="AI42" s="3"/>
@@ -24997,29 +25021,29 @@
       <c r="E43" s="50"/>
       <c r="F43" s="60"/>
       <c r="G43" s="82"/>
-      <c r="H43" s="190"/>
-      <c r="I43" s="190"/>
-      <c r="J43" s="190"/>
-      <c r="K43" s="190"/>
+      <c r="H43" s="175"/>
+      <c r="I43" s="175"/>
+      <c r="J43" s="175"/>
+      <c r="K43" s="175"/>
       <c r="L43" s="83"/>
       <c r="M43" s="82"/>
-      <c r="N43" s="190"/>
-      <c r="O43" s="190"/>
-      <c r="P43" s="190"/>
-      <c r="Q43" s="190"/>
+      <c r="N43" s="175"/>
+      <c r="O43" s="175"/>
+      <c r="P43" s="175"/>
+      <c r="Q43" s="175"/>
       <c r="R43" s="83"/>
       <c r="S43" s="82"/>
-      <c r="T43" s="190"/>
-      <c r="U43" s="190"/>
-      <c r="V43" s="190"/>
+      <c r="T43" s="175"/>
+      <c r="U43" s="175"/>
+      <c r="V43" s="175"/>
       <c r="W43" s="82"/>
-      <c r="X43" s="190"/>
-      <c r="Y43" s="190"/>
-      <c r="Z43" s="190"/>
+      <c r="X43" s="175"/>
+      <c r="Y43" s="175"/>
+      <c r="Z43" s="175"/>
       <c r="AA43" s="83"/>
       <c r="AB43" s="82"/>
-      <c r="AC43" s="190"/>
-      <c r="AD43" s="190"/>
+      <c r="AC43" s="175"/>
+      <c r="AD43" s="175"/>
       <c r="AE43" s="63"/>
       <c r="AF43" s="84"/>
       <c r="AI43" s="3"/>
@@ -25283,18 +25307,78 @@
     </row>
   </sheetData>
   <mergeCells count="100">
-    <mergeCell ref="S32:AF32"/>
-    <mergeCell ref="S33:AF33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="S26:AF26"/>
-    <mergeCell ref="S28:AF28"/>
-    <mergeCell ref="S29:AF29"/>
-    <mergeCell ref="S30:AF30"/>
-    <mergeCell ref="S31:AF31"/>
-    <mergeCell ref="S27:AF27"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:AF1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="T3:AF3"/>
+    <mergeCell ref="T5:W7"/>
+    <mergeCell ref="AD4:AF4"/>
+    <mergeCell ref="AD5:AF7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="S11:AF11"/>
+    <mergeCell ref="S12:AF12"/>
+    <mergeCell ref="S13:AF13"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="T4:W4"/>
+    <mergeCell ref="X4:Z4"/>
+    <mergeCell ref="AA4:AC4"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="S14:AF14"/>
+    <mergeCell ref="S15:AF15"/>
+    <mergeCell ref="S16:AF16"/>
+    <mergeCell ref="S17:AF17"/>
+    <mergeCell ref="S18:AF18"/>
+    <mergeCell ref="S19:AF19"/>
+    <mergeCell ref="S25:AF25"/>
+    <mergeCell ref="S24:AF24"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="AC39:AD39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="H39:K39"/>
+    <mergeCell ref="N39:Q39"/>
+    <mergeCell ref="S36:AF36"/>
+    <mergeCell ref="S37:AF37"/>
+    <mergeCell ref="H40:K40"/>
+    <mergeCell ref="N40:Q40"/>
+    <mergeCell ref="T40:V40"/>
+    <mergeCell ref="X40:Z40"/>
+    <mergeCell ref="AC40:AD40"/>
+    <mergeCell ref="H43:K43"/>
+    <mergeCell ref="N43:Q43"/>
+    <mergeCell ref="T43:V43"/>
+    <mergeCell ref="X43:Z43"/>
+    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="N41:Q41"/>
+    <mergeCell ref="H42:K42"/>
+    <mergeCell ref="N42:Q42"/>
     <mergeCell ref="AC43:AD43"/>
     <mergeCell ref="S9:AF9"/>
     <mergeCell ref="S20:AF20"/>
@@ -25311,82 +25395,22 @@
     <mergeCell ref="X39:Z39"/>
     <mergeCell ref="S34:AF34"/>
     <mergeCell ref="S35:AF35"/>
-    <mergeCell ref="H43:K43"/>
-    <mergeCell ref="N43:Q43"/>
-    <mergeCell ref="T43:V43"/>
-    <mergeCell ref="X43:Z43"/>
-    <mergeCell ref="H41:K41"/>
-    <mergeCell ref="N41:Q41"/>
-    <mergeCell ref="H42:K42"/>
-    <mergeCell ref="N42:Q42"/>
-    <mergeCell ref="H40:K40"/>
-    <mergeCell ref="N40:Q40"/>
-    <mergeCell ref="T40:V40"/>
-    <mergeCell ref="X40:Z40"/>
-    <mergeCell ref="AC40:AD40"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="F35:F37"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="AC39:AD39"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="H39:K39"/>
-    <mergeCell ref="N39:Q39"/>
-    <mergeCell ref="S36:AF36"/>
-    <mergeCell ref="S37:AF37"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="S14:AF14"/>
-    <mergeCell ref="S15:AF15"/>
-    <mergeCell ref="S16:AF16"/>
-    <mergeCell ref="S17:AF17"/>
-    <mergeCell ref="S18:AF18"/>
-    <mergeCell ref="S19:AF19"/>
-    <mergeCell ref="S25:AF25"/>
-    <mergeCell ref="S24:AF24"/>
-    <mergeCell ref="T5:W7"/>
-    <mergeCell ref="AD4:AF4"/>
-    <mergeCell ref="AD5:AF7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="S11:AF11"/>
-    <mergeCell ref="S12:AF12"/>
-    <mergeCell ref="S13:AF13"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="T4:W4"/>
-    <mergeCell ref="X4:Z4"/>
-    <mergeCell ref="AA4:AC4"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="F1:AF1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="T3:AF3"/>
+    <mergeCell ref="S26:AF26"/>
+    <mergeCell ref="S28:AF28"/>
+    <mergeCell ref="S29:AF29"/>
+    <mergeCell ref="S30:AF30"/>
+    <mergeCell ref="S31:AF31"/>
+    <mergeCell ref="S27:AF27"/>
+    <mergeCell ref="S32:AF32"/>
+    <mergeCell ref="S33:AF33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="B31:C31"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="G11:R19 AG11:AK19">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>TEXT(G11,"aaa")="日"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/設備点検表.xlsx
+++ b/設備点検表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kosuk\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38418EB-2DF8-4034-A161-489A54E4460C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7141F1C4-F1B5-41E2-9F91-D2F312B71617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6C56CF13-AF7F-4C1F-982C-EF388A11F51A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{6C56CF13-AF7F-4C1F-982C-EF388A11F51A}"/>
   </bookViews>
   <sheets>
     <sheet name="日常～週" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="139">
   <si>
     <t>改版</t>
     <rPh sb="0" eb="2">
@@ -1301,6 +1301,29 @@
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
+  <si>
+    <t>1回/月</t>
+    <rPh sb="3" eb="4">
+      <t>ツキ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>1回/
+3ヶ月</t>
+    <rPh sb="6" eb="7">
+      <t>ゲツ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>1回/
+6ヶ月</t>
+    <rPh sb="6" eb="7">
+      <t>ゲツ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
 </sst>
 </file>
 
@@ -1509,7 +1532,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="78">
+  <borders count="81">
     <border>
       <left/>
       <right/>
@@ -2442,6 +2465,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2618,19 +2678,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2759,17 +2807,44 @@
     <xf numFmtId="179" fontId="13" fillId="0" borderId="77" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="78" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="79" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="80" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="72" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="73" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="71" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -2798,13 +2873,22 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="180" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="180" fontId="25" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="25" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="25" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="25" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="25" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2815,36 +2899,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2870,11 +2924,38 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="75" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2882,7 +2963,28 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="67" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="74" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2912,111 +3014,52 @@
     <xf numFmtId="177" fontId="5" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="71" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="72" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="73" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="67" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="74" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="25" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="25" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="25" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="25" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="25" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="75" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="178" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準_設備点検表書式" xfId="1" xr:uid="{15F629F0-A893-4DD8-8A94-9D447F97F79C}"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <font>
-        <strike val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3038,45 +3081,6 @@
       <fill>
         <patternFill>
           <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3404,45 +3408,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:254" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="126" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="85"/>
-      <c r="F1" s="122" t="s">
+      <c r="B1" s="126"/>
+      <c r="C1" s="81"/>
+      <c r="F1" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
-      <c r="AC1" s="122"/>
-      <c r="AD1" s="122"/>
-      <c r="AE1" s="122"/>
-      <c r="AF1" s="122"/>
-      <c r="AG1" s="122"/>
-      <c r="AH1" s="122"/>
-      <c r="AI1" s="122"/>
-      <c r="AJ1" s="122"/>
-      <c r="AK1" s="122"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="127"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="127"/>
+      <c r="R1" s="127"/>
+      <c r="S1" s="127"/>
+      <c r="T1" s="127"/>
+      <c r="U1" s="127"/>
+      <c r="V1" s="127"/>
+      <c r="W1" s="127"/>
+      <c r="X1" s="127"/>
+      <c r="Y1" s="127"/>
+      <c r="Z1" s="127"/>
+      <c r="AA1" s="127"/>
+      <c r="AB1" s="127"/>
+      <c r="AC1" s="127"/>
+      <c r="AD1" s="127"/>
+      <c r="AE1" s="127"/>
+      <c r="AF1" s="127"/>
+      <c r="AG1" s="127"/>
+      <c r="AH1" s="127"/>
+      <c r="AI1" s="127"/>
+      <c r="AJ1" s="127"/>
+      <c r="AK1" s="127"/>
       <c r="AN1" s="3"/>
       <c r="AO1" s="3"/>
       <c r="AP1" s="3"/>
@@ -3913,52 +3917,52 @@
       <c r="IT2" s="3"/>
     </row>
     <row r="3" spans="1:254" s="2" customFormat="1" ht="20" customHeight="1" thickBot="1">
-      <c r="A3" s="123" t="s">
+      <c r="A3" s="128" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="125"/>
-      <c r="E3" s="94"/>
+      <c r="B3" s="129"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="130"/>
+      <c r="E3" s="90"/>
       <c r="G3" s="51"/>
       <c r="H3" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="126" t="s">
+      <c r="K3" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="126"/>
-      <c r="M3" s="126" t="s">
+      <c r="L3" s="131"/>
+      <c r="M3" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="126"/>
-      <c r="O3" s="126"/>
-      <c r="P3" s="126" t="s">
+      <c r="N3" s="131"/>
+      <c r="O3" s="131"/>
+      <c r="P3" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="Q3" s="126"/>
-      <c r="R3" s="126"/>
+      <c r="Q3" s="131"/>
+      <c r="R3" s="131"/>
       <c r="S3" s="3"/>
-      <c r="T3" s="127" t="s">
+      <c r="T3" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="U3" s="128"/>
-      <c r="V3" s="128"/>
-      <c r="W3" s="128"/>
-      <c r="X3" s="128"/>
-      <c r="Y3" s="128"/>
-      <c r="Z3" s="128"/>
-      <c r="AA3" s="128"/>
-      <c r="AB3" s="128"/>
-      <c r="AC3" s="128"/>
-      <c r="AD3" s="128"/>
-      <c r="AE3" s="128"/>
-      <c r="AF3" s="128"/>
-      <c r="AG3" s="128"/>
-      <c r="AH3" s="128"/>
-      <c r="AI3" s="128"/>
-      <c r="AJ3" s="128"/>
-      <c r="AK3" s="129"/>
+      <c r="U3" s="133"/>
+      <c r="V3" s="133"/>
+      <c r="W3" s="133"/>
+      <c r="X3" s="133"/>
+      <c r="Y3" s="133"/>
+      <c r="Z3" s="133"/>
+      <c r="AA3" s="133"/>
+      <c r="AB3" s="133"/>
+      <c r="AC3" s="133"/>
+      <c r="AD3" s="133"/>
+      <c r="AE3" s="133"/>
+      <c r="AF3" s="133"/>
+      <c r="AG3" s="133"/>
+      <c r="AH3" s="133"/>
+      <c r="AI3" s="133"/>
+      <c r="AJ3" s="133"/>
+      <c r="AK3" s="134"/>
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
@@ -4187,47 +4191,47 @@
       <c r="H4" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="126" t="s">
+      <c r="K4" s="131" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="126"/>
-      <c r="M4" s="132">
+      <c r="L4" s="131"/>
+      <c r="M4" s="156">
         <v>46113</v>
       </c>
-      <c r="N4" s="132"/>
-      <c r="O4" s="132"/>
-      <c r="P4" s="126" t="s">
+      <c r="N4" s="156"/>
+      <c r="O4" s="156"/>
+      <c r="P4" s="131" t="s">
         <v>50</v>
       </c>
-      <c r="Q4" s="126"/>
-      <c r="R4" s="126"/>
+      <c r="Q4" s="131"/>
+      <c r="R4" s="131"/>
       <c r="S4" s="3"/>
-      <c r="T4" s="133" t="s">
+      <c r="T4" s="141" t="s">
         <v>5</v>
       </c>
-      <c r="U4" s="134"/>
-      <c r="V4" s="134"/>
-      <c r="W4" s="134"/>
-      <c r="X4" s="134"/>
-      <c r="Y4" s="135"/>
-      <c r="Z4" s="133" t="s">
+      <c r="U4" s="142"/>
+      <c r="V4" s="142"/>
+      <c r="W4" s="142"/>
+      <c r="X4" s="142"/>
+      <c r="Y4" s="143"/>
+      <c r="Z4" s="141" t="s">
         <v>6</v>
       </c>
-      <c r="AA4" s="134"/>
-      <c r="AB4" s="134"/>
-      <c r="AC4" s="135"/>
-      <c r="AD4" s="133" t="s">
+      <c r="AA4" s="142"/>
+      <c r="AB4" s="142"/>
+      <c r="AC4" s="143"/>
+      <c r="AD4" s="141" t="s">
         <v>7</v>
       </c>
-      <c r="AE4" s="134"/>
-      <c r="AF4" s="134"/>
-      <c r="AG4" s="135"/>
-      <c r="AH4" s="133" t="s">
+      <c r="AE4" s="142"/>
+      <c r="AF4" s="142"/>
+      <c r="AG4" s="143"/>
+      <c r="AH4" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="AI4" s="134"/>
-      <c r="AJ4" s="134"/>
-      <c r="AK4" s="135"/>
+      <c r="AI4" s="142"/>
+      <c r="AJ4" s="142"/>
+      <c r="AK4" s="143"/>
       <c r="AN4" s="3"/>
       <c r="AO4" s="3"/>
       <c r="AP4" s="3"/>
@@ -4455,16 +4459,16 @@
         <v>23</v>
       </c>
       <c r="S5" s="3"/>
-      <c r="T5" s="136" t="s">
+      <c r="T5" s="189" t="s">
         <v>64</v>
       </c>
-      <c r="U5" s="137"/>
-      <c r="V5" s="137"/>
-      <c r="W5" s="141">
+      <c r="U5" s="190"/>
+      <c r="V5" s="190"/>
+      <c r="W5" s="182">
         <v>7</v>
       </c>
-      <c r="X5" s="142"/>
-      <c r="Y5" s="143"/>
+      <c r="X5" s="183"/>
+      <c r="Y5" s="184"/>
       <c r="Z5" s="11"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
@@ -4473,10 +4477,10 @@
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
       <c r="AG5" s="12"/>
-      <c r="AH5" s="146"/>
-      <c r="AI5" s="147"/>
-      <c r="AJ5" s="147"/>
-      <c r="AK5" s="148"/>
+      <c r="AH5" s="144"/>
+      <c r="AI5" s="145"/>
+      <c r="AJ5" s="145"/>
+      <c r="AK5" s="146"/>
       <c r="AN5" s="3"/>
       <c r="AO5" s="3"/>
       <c r="AP5" s="3"/>
@@ -4708,12 +4712,12 @@
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
-      <c r="T6" s="138"/>
-      <c r="U6" s="137"/>
-      <c r="V6" s="137"/>
-      <c r="W6" s="142"/>
-      <c r="X6" s="142"/>
-      <c r="Y6" s="143"/>
+      <c r="T6" s="191"/>
+      <c r="U6" s="190"/>
+      <c r="V6" s="190"/>
+      <c r="W6" s="183"/>
+      <c r="X6" s="183"/>
+      <c r="Y6" s="184"/>
       <c r="Z6" s="11"/>
       <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
@@ -4722,10 +4726,10 @@
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
       <c r="AG6" s="12"/>
-      <c r="AH6" s="146"/>
-      <c r="AI6" s="147"/>
-      <c r="AJ6" s="147"/>
-      <c r="AK6" s="148"/>
+      <c r="AH6" s="144"/>
+      <c r="AI6" s="145"/>
+      <c r="AJ6" s="145"/>
+      <c r="AK6" s="146"/>
       <c r="AN6" s="3"/>
       <c r="AO6" s="3"/>
       <c r="AP6" s="3"/>
@@ -4957,12 +4961,12 @@
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
-      <c r="T7" s="139"/>
-      <c r="U7" s="140"/>
-      <c r="V7" s="140"/>
-      <c r="W7" s="144"/>
-      <c r="X7" s="144"/>
-      <c r="Y7" s="145"/>
+      <c r="T7" s="192"/>
+      <c r="U7" s="193"/>
+      <c r="V7" s="193"/>
+      <c r="W7" s="185"/>
+      <c r="X7" s="185"/>
+      <c r="Y7" s="186"/>
       <c r="Z7" s="21"/>
       <c r="AA7" s="22"/>
       <c r="AB7" s="22"/>
@@ -4971,11 +4975,11 @@
       <c r="AE7" s="22"/>
       <c r="AF7" s="22"/>
       <c r="AG7" s="23"/>
-      <c r="AH7" s="149"/>
-      <c r="AI7" s="150"/>
-      <c r="AJ7" s="150"/>
-      <c r="AK7" s="151"/>
-      <c r="AL7" s="86"/>
+      <c r="AH7" s="147"/>
+      <c r="AI7" s="148"/>
+      <c r="AJ7" s="148"/>
+      <c r="AK7" s="149"/>
+      <c r="AL7" s="82"/>
       <c r="AN7" s="3"/>
       <c r="AO7" s="3"/>
       <c r="AP7" s="3"/>
@@ -5199,7 +5203,7 @@
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
-      <c r="G8" s="103" t="s">
+      <c r="G8" s="99" t="s">
         <v>124</v>
       </c>
       <c r="H8" s="24"/>
@@ -5267,23 +5271,23 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AH8" s="98" t="str">
+      <c r="AH8" s="94" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AI8" s="98" t="str">
+      <c r="AI8" s="94" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AJ8" s="98" t="str">
+      <c r="AJ8" s="94" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AK8" s="98" t="str">
+      <c r="AK8" s="94" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AL8" s="87"/>
+      <c r="AL8" s="83"/>
       <c r="AN8" s="3"/>
       <c r="AO8" s="3"/>
       <c r="AP8" s="3"/>
@@ -5515,127 +5519,127 @@
       <c r="F9" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="G9" s="97">
+      <c r="G9" s="93">
         <f>DATE($T$5,$W$5,1)</f>
         <v>46204</v>
       </c>
-      <c r="H9" s="97">
+      <c r="H9" s="93">
         <f>DATE($T$5,$W$5,2)</f>
         <v>46205</v>
       </c>
-      <c r="I9" s="97">
+      <c r="I9" s="93">
         <f>DATE($T$5,$W$5,3)</f>
         <v>46206</v>
       </c>
-      <c r="J9" s="97">
+      <c r="J9" s="93">
         <f t="shared" ref="J9:AK9" si="1">I9+1</f>
         <v>46207</v>
       </c>
-      <c r="K9" s="97">
+      <c r="K9" s="93">
         <f t="shared" si="1"/>
         <v>46208</v>
       </c>
-      <c r="L9" s="97">
+      <c r="L9" s="93">
         <f t="shared" si="1"/>
         <v>46209</v>
       </c>
-      <c r="M9" s="97">
+      <c r="M9" s="93">
         <f t="shared" si="1"/>
         <v>46210</v>
       </c>
-      <c r="N9" s="97">
+      <c r="N9" s="93">
         <f t="shared" si="1"/>
         <v>46211</v>
       </c>
-      <c r="O9" s="97">
+      <c r="O9" s="93">
         <f t="shared" si="1"/>
         <v>46212</v>
       </c>
-      <c r="P9" s="97">
+      <c r="P9" s="93">
         <f t="shared" si="1"/>
         <v>46213</v>
       </c>
-      <c r="Q9" s="97">
+      <c r="Q9" s="93">
         <f t="shared" si="1"/>
         <v>46214</v>
       </c>
-      <c r="R9" s="97">
+      <c r="R9" s="93">
         <f t="shared" si="1"/>
         <v>46215</v>
       </c>
-      <c r="S9" s="97">
+      <c r="S9" s="93">
         <f t="shared" si="1"/>
         <v>46216</v>
       </c>
-      <c r="T9" s="97">
+      <c r="T9" s="93">
         <f t="shared" si="1"/>
         <v>46217</v>
       </c>
-      <c r="U9" s="97">
+      <c r="U9" s="93">
         <f t="shared" si="1"/>
         <v>46218</v>
       </c>
-      <c r="V9" s="97">
+      <c r="V9" s="93">
         <f t="shared" si="1"/>
         <v>46219</v>
       </c>
-      <c r="W9" s="97">
+      <c r="W9" s="93">
         <f t="shared" si="1"/>
         <v>46220</v>
       </c>
-      <c r="X9" s="97">
+      <c r="X9" s="93">
         <f t="shared" si="1"/>
         <v>46221</v>
       </c>
-      <c r="Y9" s="97">
+      <c r="Y9" s="93">
         <f t="shared" si="1"/>
         <v>46222</v>
       </c>
-      <c r="Z9" s="97">
+      <c r="Z9" s="93">
         <f t="shared" si="1"/>
         <v>46223</v>
       </c>
-      <c r="AA9" s="97">
+      <c r="AA9" s="93">
         <f t="shared" si="1"/>
         <v>46224</v>
       </c>
-      <c r="AB9" s="97">
+      <c r="AB9" s="93">
         <f t="shared" si="1"/>
         <v>46225</v>
       </c>
-      <c r="AC9" s="97">
+      <c r="AC9" s="93">
         <f t="shared" si="1"/>
         <v>46226</v>
       </c>
-      <c r="AD9" s="97">
+      <c r="AD9" s="93">
         <f t="shared" si="1"/>
         <v>46227</v>
       </c>
-      <c r="AE9" s="97">
+      <c r="AE9" s="93">
         <f t="shared" si="1"/>
         <v>46228</v>
       </c>
-      <c r="AF9" s="97">
+      <c r="AF9" s="93">
         <f t="shared" si="1"/>
         <v>46229</v>
       </c>
-      <c r="AG9" s="97">
+      <c r="AG9" s="93">
         <f t="shared" si="1"/>
         <v>46230</v>
       </c>
-      <c r="AH9" s="97">
+      <c r="AH9" s="93">
         <f t="shared" si="1"/>
         <v>46231</v>
       </c>
-      <c r="AI9" s="97">
+      <c r="AI9" s="93">
         <f t="shared" si="1"/>
         <v>46232</v>
       </c>
-      <c r="AJ9" s="97">
+      <c r="AJ9" s="93">
         <f t="shared" si="1"/>
         <v>46233</v>
       </c>
-      <c r="AK9" s="116">
+      <c r="AK9" s="112">
         <f t="shared" si="1"/>
         <v>46234</v>
       </c>
@@ -5857,8 +5861,8 @@
     </row>
     <row r="10" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A10" s="29"/>
-      <c r="B10" s="152"/>
-      <c r="C10" s="153"/>
+      <c r="B10" s="150"/>
+      <c r="C10" s="151"/>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="31" t="s">
@@ -6206,46 +6210,46 @@
     </row>
     <row r="11" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A11" s="34"/>
-      <c r="B11" s="130" t="s">
+      <c r="B11" s="187" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="131"/>
+      <c r="C11" s="188"/>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
-      <c r="F11" s="102" t="s">
+      <c r="F11" s="98" t="s">
         <v>122</v>
       </c>
-      <c r="G11" s="104"/>
-      <c r="H11" s="104"/>
-      <c r="I11" s="104"/>
-      <c r="J11" s="104"/>
-      <c r="K11" s="104"/>
-      <c r="L11" s="104"/>
-      <c r="M11" s="104"/>
-      <c r="N11" s="104"/>
-      <c r="O11" s="104"/>
-      <c r="P11" s="104"/>
-      <c r="Q11" s="104"/>
-      <c r="R11" s="104"/>
-      <c r="S11" s="104"/>
-      <c r="T11" s="104"/>
-      <c r="U11" s="104"/>
-      <c r="V11" s="104"/>
-      <c r="W11" s="104"/>
-      <c r="X11" s="104"/>
-      <c r="Y11" s="104"/>
-      <c r="Z11" s="104"/>
-      <c r="AA11" s="104"/>
-      <c r="AB11" s="104"/>
-      <c r="AC11" s="104"/>
-      <c r="AD11" s="104"/>
-      <c r="AE11" s="104"/>
-      <c r="AF11" s="104"/>
-      <c r="AG11" s="104"/>
-      <c r="AH11" s="104"/>
-      <c r="AI11" s="104"/>
-      <c r="AJ11" s="104"/>
-      <c r="AK11" s="105"/>
+      <c r="G11" s="100"/>
+      <c r="H11" s="100"/>
+      <c r="I11" s="100"/>
+      <c r="J11" s="100"/>
+      <c r="K11" s="100"/>
+      <c r="L11" s="100"/>
+      <c r="M11" s="100"/>
+      <c r="N11" s="100"/>
+      <c r="O11" s="100"/>
+      <c r="P11" s="100"/>
+      <c r="Q11" s="100"/>
+      <c r="R11" s="100"/>
+      <c r="S11" s="100"/>
+      <c r="T11" s="100"/>
+      <c r="U11" s="100"/>
+      <c r="V11" s="100"/>
+      <c r="W11" s="100"/>
+      <c r="X11" s="100"/>
+      <c r="Y11" s="100"/>
+      <c r="Z11" s="100"/>
+      <c r="AA11" s="100"/>
+      <c r="AB11" s="100"/>
+      <c r="AC11" s="100"/>
+      <c r="AD11" s="100"/>
+      <c r="AE11" s="100"/>
+      <c r="AF11" s="100"/>
+      <c r="AG11" s="100"/>
+      <c r="AH11" s="100"/>
+      <c r="AI11" s="100"/>
+      <c r="AJ11" s="100"/>
+      <c r="AK11" s="101"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
@@ -6463,53 +6467,53 @@
       <c r="IT11" s="3"/>
     </row>
     <row r="12" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A12" s="99">
+      <c r="A12" s="95">
         <v>1</v>
       </c>
-      <c r="B12" s="117" t="s">
+      <c r="B12" s="161" t="s">
         <v>119</v>
       </c>
-      <c r="C12" s="118"/>
-      <c r="D12" s="92" t="s">
+      <c r="C12" s="162"/>
+      <c r="D12" s="88" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="92" t="s">
+      <c r="E12" s="88" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="158" t="s">
+      <c r="F12" s="116" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="106"/>
-      <c r="H12" s="106"/>
-      <c r="I12" s="106"/>
-      <c r="J12" s="106"/>
-      <c r="K12" s="106"/>
-      <c r="L12" s="106"/>
-      <c r="M12" s="106"/>
-      <c r="N12" s="106"/>
-      <c r="O12" s="106"/>
-      <c r="P12" s="106"/>
-      <c r="Q12" s="106"/>
-      <c r="R12" s="106"/>
-      <c r="S12" s="106"/>
-      <c r="T12" s="106"/>
-      <c r="U12" s="106"/>
-      <c r="V12" s="106"/>
-      <c r="W12" s="106"/>
-      <c r="X12" s="106"/>
-      <c r="Y12" s="106"/>
-      <c r="Z12" s="106"/>
-      <c r="AA12" s="106"/>
-      <c r="AB12" s="106"/>
-      <c r="AC12" s="106"/>
-      <c r="AD12" s="106"/>
-      <c r="AE12" s="106"/>
-      <c r="AF12" s="106"/>
-      <c r="AG12" s="106"/>
-      <c r="AH12" s="106"/>
-      <c r="AI12" s="106"/>
-      <c r="AJ12" s="106"/>
-      <c r="AK12" s="107"/>
+      <c r="G12" s="102"/>
+      <c r="H12" s="102"/>
+      <c r="I12" s="102"/>
+      <c r="J12" s="102"/>
+      <c r="K12" s="102"/>
+      <c r="L12" s="102"/>
+      <c r="M12" s="102"/>
+      <c r="N12" s="102"/>
+      <c r="O12" s="102"/>
+      <c r="P12" s="102"/>
+      <c r="Q12" s="102"/>
+      <c r="R12" s="102"/>
+      <c r="S12" s="102"/>
+      <c r="T12" s="102"/>
+      <c r="U12" s="102"/>
+      <c r="V12" s="102"/>
+      <c r="W12" s="102"/>
+      <c r="X12" s="102"/>
+      <c r="Y12" s="102"/>
+      <c r="Z12" s="102"/>
+      <c r="AA12" s="102"/>
+      <c r="AB12" s="102"/>
+      <c r="AC12" s="102"/>
+      <c r="AD12" s="102"/>
+      <c r="AE12" s="102"/>
+      <c r="AF12" s="102"/>
+      <c r="AG12" s="102"/>
+      <c r="AH12" s="102"/>
+      <c r="AI12" s="102"/>
+      <c r="AJ12" s="102"/>
+      <c r="AK12" s="103"/>
       <c r="AN12" s="3"/>
       <c r="AO12" s="3"/>
       <c r="AP12" s="3"/>
@@ -6727,49 +6731,49 @@
       <c r="IT12" s="3"/>
     </row>
     <row r="13" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A13" s="99">
+      <c r="A13" s="95">
         <v>2</v>
       </c>
-      <c r="B13" s="117" t="s">
+      <c r="B13" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="118"/>
-      <c r="D13" s="92" t="s">
+      <c r="C13" s="162"/>
+      <c r="D13" s="88" t="s">
         <v>99</v>
       </c>
-      <c r="E13" s="92"/>
-      <c r="F13" s="119"/>
-      <c r="G13" s="106"/>
-      <c r="H13" s="106"/>
-      <c r="I13" s="106"/>
-      <c r="J13" s="106"/>
-      <c r="K13" s="106"/>
-      <c r="L13" s="106"/>
-      <c r="M13" s="106"/>
-      <c r="N13" s="106"/>
-      <c r="O13" s="106"/>
-      <c r="P13" s="106"/>
-      <c r="Q13" s="106"/>
-      <c r="R13" s="106"/>
-      <c r="S13" s="106"/>
-      <c r="T13" s="106"/>
-      <c r="U13" s="106"/>
-      <c r="V13" s="106"/>
-      <c r="W13" s="106"/>
-      <c r="X13" s="106"/>
-      <c r="Y13" s="106"/>
-      <c r="Z13" s="106"/>
-      <c r="AA13" s="106"/>
-      <c r="AB13" s="106"/>
-      <c r="AC13" s="106"/>
-      <c r="AD13" s="106"/>
-      <c r="AE13" s="106"/>
-      <c r="AF13" s="106"/>
-      <c r="AG13" s="106"/>
-      <c r="AH13" s="106"/>
-      <c r="AI13" s="106"/>
-      <c r="AJ13" s="106"/>
-      <c r="AK13" s="107"/>
+      <c r="E13" s="88"/>
+      <c r="F13" s="117"/>
+      <c r="G13" s="102"/>
+      <c r="H13" s="102"/>
+      <c r="I13" s="102"/>
+      <c r="J13" s="102"/>
+      <c r="K13" s="102"/>
+      <c r="L13" s="102"/>
+      <c r="M13" s="102"/>
+      <c r="N13" s="102"/>
+      <c r="O13" s="102"/>
+      <c r="P13" s="102"/>
+      <c r="Q13" s="102"/>
+      <c r="R13" s="102"/>
+      <c r="S13" s="102"/>
+      <c r="T13" s="102"/>
+      <c r="U13" s="102"/>
+      <c r="V13" s="102"/>
+      <c r="W13" s="102"/>
+      <c r="X13" s="102"/>
+      <c r="Y13" s="102"/>
+      <c r="Z13" s="102"/>
+      <c r="AA13" s="102"/>
+      <c r="AB13" s="102"/>
+      <c r="AC13" s="102"/>
+      <c r="AD13" s="102"/>
+      <c r="AE13" s="102"/>
+      <c r="AF13" s="102"/>
+      <c r="AG13" s="102"/>
+      <c r="AH13" s="102"/>
+      <c r="AI13" s="102"/>
+      <c r="AJ13" s="102"/>
+      <c r="AK13" s="103"/>
       <c r="AN13" s="3"/>
       <c r="AO13" s="3"/>
       <c r="AP13" s="3"/>
@@ -6987,51 +6991,51 @@
       <c r="IT13" s="3"/>
     </row>
     <row r="14" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A14" s="99">
+      <c r="A14" s="95">
         <v>3</v>
       </c>
-      <c r="B14" s="117" t="s">
+      <c r="B14" s="161" t="s">
         <v>130</v>
       </c>
-      <c r="C14" s="118"/>
-      <c r="D14" s="92" t="s">
+      <c r="C14" s="162"/>
+      <c r="D14" s="88" t="s">
         <v>99</v>
       </c>
-      <c r="E14" s="92" t="s">
+      <c r="E14" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="119"/>
-      <c r="G14" s="106"/>
-      <c r="H14" s="106"/>
-      <c r="I14" s="106"/>
-      <c r="J14" s="106"/>
-      <c r="K14" s="106"/>
-      <c r="L14" s="106"/>
-      <c r="M14" s="106"/>
-      <c r="N14" s="106"/>
-      <c r="O14" s="106"/>
-      <c r="P14" s="106"/>
-      <c r="Q14" s="106"/>
-      <c r="R14" s="106"/>
-      <c r="S14" s="106"/>
-      <c r="T14" s="106"/>
-      <c r="U14" s="106"/>
-      <c r="V14" s="106"/>
-      <c r="W14" s="106"/>
-      <c r="X14" s="106"/>
-      <c r="Y14" s="106"/>
-      <c r="Z14" s="106"/>
-      <c r="AA14" s="106"/>
-      <c r="AB14" s="106"/>
-      <c r="AC14" s="106"/>
-      <c r="AD14" s="106"/>
-      <c r="AE14" s="106"/>
-      <c r="AF14" s="106"/>
-      <c r="AG14" s="106"/>
-      <c r="AH14" s="106"/>
-      <c r="AI14" s="106"/>
-      <c r="AJ14" s="106"/>
-      <c r="AK14" s="107"/>
+      <c r="F14" s="117"/>
+      <c r="G14" s="102"/>
+      <c r="H14" s="102"/>
+      <c r="I14" s="102"/>
+      <c r="J14" s="102"/>
+      <c r="K14" s="102"/>
+      <c r="L14" s="102"/>
+      <c r="M14" s="102"/>
+      <c r="N14" s="102"/>
+      <c r="O14" s="102"/>
+      <c r="P14" s="102"/>
+      <c r="Q14" s="102"/>
+      <c r="R14" s="102"/>
+      <c r="S14" s="102"/>
+      <c r="T14" s="102"/>
+      <c r="U14" s="102"/>
+      <c r="V14" s="102"/>
+      <c r="W14" s="102"/>
+      <c r="X14" s="102"/>
+      <c r="Y14" s="102"/>
+      <c r="Z14" s="102"/>
+      <c r="AA14" s="102"/>
+      <c r="AB14" s="102"/>
+      <c r="AC14" s="102"/>
+      <c r="AD14" s="102"/>
+      <c r="AE14" s="102"/>
+      <c r="AF14" s="102"/>
+      <c r="AG14" s="102"/>
+      <c r="AH14" s="102"/>
+      <c r="AI14" s="102"/>
+      <c r="AJ14" s="102"/>
+      <c r="AK14" s="103"/>
       <c r="AN14" s="3"/>
       <c r="AO14" s="3"/>
       <c r="AP14" s="3"/>
@@ -7249,51 +7253,51 @@
       <c r="IT14" s="3"/>
     </row>
     <row r="15" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A15" s="99">
+      <c r="A15" s="95">
         <v>4</v>
       </c>
-      <c r="B15" s="117" t="s">
+      <c r="B15" s="161" t="s">
         <v>131</v>
       </c>
-      <c r="C15" s="118"/>
-      <c r="D15" s="92" t="s">
+      <c r="C15" s="162"/>
+      <c r="D15" s="88" t="s">
         <v>99</v>
       </c>
-      <c r="E15" s="92" t="s">
+      <c r="E15" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="119"/>
-      <c r="G15" s="106"/>
-      <c r="H15" s="106"/>
-      <c r="I15" s="106"/>
-      <c r="J15" s="106"/>
-      <c r="K15" s="106"/>
-      <c r="L15" s="106"/>
-      <c r="M15" s="106"/>
-      <c r="N15" s="106"/>
-      <c r="O15" s="106"/>
-      <c r="P15" s="106"/>
-      <c r="Q15" s="106"/>
-      <c r="R15" s="106"/>
-      <c r="S15" s="106"/>
-      <c r="T15" s="106"/>
-      <c r="U15" s="106"/>
-      <c r="V15" s="106"/>
-      <c r="W15" s="106"/>
-      <c r="X15" s="106"/>
-      <c r="Y15" s="106"/>
-      <c r="Z15" s="106"/>
-      <c r="AA15" s="106"/>
-      <c r="AB15" s="106"/>
-      <c r="AC15" s="106"/>
-      <c r="AD15" s="106"/>
-      <c r="AE15" s="106"/>
-      <c r="AF15" s="106"/>
-      <c r="AG15" s="106"/>
-      <c r="AH15" s="106"/>
-      <c r="AI15" s="106"/>
-      <c r="AJ15" s="106"/>
-      <c r="AK15" s="107"/>
+      <c r="F15" s="117"/>
+      <c r="G15" s="102"/>
+      <c r="H15" s="102"/>
+      <c r="I15" s="102"/>
+      <c r="J15" s="102"/>
+      <c r="K15" s="102"/>
+      <c r="L15" s="102"/>
+      <c r="M15" s="102"/>
+      <c r="N15" s="102"/>
+      <c r="O15" s="102"/>
+      <c r="P15" s="102"/>
+      <c r="Q15" s="102"/>
+      <c r="R15" s="102"/>
+      <c r="S15" s="102"/>
+      <c r="T15" s="102"/>
+      <c r="U15" s="102"/>
+      <c r="V15" s="102"/>
+      <c r="W15" s="102"/>
+      <c r="X15" s="102"/>
+      <c r="Y15" s="102"/>
+      <c r="Z15" s="102"/>
+      <c r="AA15" s="102"/>
+      <c r="AB15" s="102"/>
+      <c r="AC15" s="102"/>
+      <c r="AD15" s="102"/>
+      <c r="AE15" s="102"/>
+      <c r="AF15" s="102"/>
+      <c r="AG15" s="102"/>
+      <c r="AH15" s="102"/>
+      <c r="AI15" s="102"/>
+      <c r="AJ15" s="102"/>
+      <c r="AK15" s="103"/>
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
       <c r="AP15" s="3"/>
@@ -7511,51 +7515,51 @@
       <c r="IT15" s="3"/>
     </row>
     <row r="16" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A16" s="99">
+      <c r="A16" s="95">
         <v>5</v>
       </c>
-      <c r="B16" s="117" t="s">
+      <c r="B16" s="161" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="118"/>
-      <c r="D16" s="92" t="s">
+      <c r="C16" s="162"/>
+      <c r="D16" s="88" t="s">
         <v>133</v>
       </c>
-      <c r="E16" s="92" t="s">
+      <c r="E16" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="119"/>
-      <c r="G16" s="106"/>
-      <c r="H16" s="106"/>
-      <c r="I16" s="106"/>
-      <c r="J16" s="106"/>
-      <c r="K16" s="106"/>
-      <c r="L16" s="106"/>
-      <c r="M16" s="106"/>
-      <c r="N16" s="106"/>
-      <c r="O16" s="106"/>
-      <c r="P16" s="106"/>
-      <c r="Q16" s="106"/>
-      <c r="R16" s="106"/>
-      <c r="S16" s="106"/>
-      <c r="T16" s="106"/>
-      <c r="U16" s="106"/>
-      <c r="V16" s="106"/>
-      <c r="W16" s="106"/>
-      <c r="X16" s="106"/>
-      <c r="Y16" s="106"/>
-      <c r="Z16" s="106"/>
-      <c r="AA16" s="106"/>
-      <c r="AB16" s="106"/>
-      <c r="AC16" s="106"/>
-      <c r="AD16" s="106"/>
-      <c r="AE16" s="106"/>
-      <c r="AF16" s="106"/>
-      <c r="AG16" s="106"/>
-      <c r="AH16" s="106"/>
-      <c r="AI16" s="106"/>
-      <c r="AJ16" s="106"/>
-      <c r="AK16" s="107"/>
+      <c r="F16" s="117"/>
+      <c r="G16" s="102"/>
+      <c r="H16" s="102"/>
+      <c r="I16" s="102"/>
+      <c r="J16" s="102"/>
+      <c r="K16" s="102"/>
+      <c r="L16" s="102"/>
+      <c r="M16" s="102"/>
+      <c r="N16" s="102"/>
+      <c r="O16" s="102"/>
+      <c r="P16" s="102"/>
+      <c r="Q16" s="102"/>
+      <c r="R16" s="102"/>
+      <c r="S16" s="102"/>
+      <c r="T16" s="102"/>
+      <c r="U16" s="102"/>
+      <c r="V16" s="102"/>
+      <c r="W16" s="102"/>
+      <c r="X16" s="102"/>
+      <c r="Y16" s="102"/>
+      <c r="Z16" s="102"/>
+      <c r="AA16" s="102"/>
+      <c r="AB16" s="102"/>
+      <c r="AC16" s="102"/>
+      <c r="AD16" s="102"/>
+      <c r="AE16" s="102"/>
+      <c r="AF16" s="102"/>
+      <c r="AG16" s="102"/>
+      <c r="AH16" s="102"/>
+      <c r="AI16" s="102"/>
+      <c r="AJ16" s="102"/>
+      <c r="AK16" s="103"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
@@ -7773,51 +7777,51 @@
       <c r="IT16" s="3"/>
     </row>
     <row r="17" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A17" s="99">
+      <c r="A17" s="95">
         <v>6</v>
       </c>
-      <c r="B17" s="117" t="s">
+      <c r="B17" s="161" t="s">
         <v>134</v>
       </c>
-      <c r="C17" s="118"/>
-      <c r="D17" s="92" t="s">
+      <c r="C17" s="162"/>
+      <c r="D17" s="88" t="s">
         <v>99</v>
       </c>
-      <c r="E17" s="92" t="s">
+      <c r="E17" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="119"/>
-      <c r="G17" s="106"/>
-      <c r="H17" s="106"/>
-      <c r="I17" s="106"/>
-      <c r="J17" s="106"/>
-      <c r="K17" s="106"/>
-      <c r="L17" s="106"/>
-      <c r="M17" s="106"/>
-      <c r="N17" s="106"/>
-      <c r="O17" s="106"/>
-      <c r="P17" s="106"/>
-      <c r="Q17" s="106"/>
-      <c r="R17" s="106"/>
-      <c r="S17" s="106"/>
-      <c r="T17" s="106"/>
-      <c r="U17" s="106"/>
-      <c r="V17" s="106"/>
-      <c r="W17" s="106"/>
-      <c r="X17" s="106"/>
-      <c r="Y17" s="106"/>
-      <c r="Z17" s="106"/>
-      <c r="AA17" s="106"/>
-      <c r="AB17" s="106"/>
-      <c r="AC17" s="106"/>
-      <c r="AD17" s="106"/>
-      <c r="AE17" s="106"/>
-      <c r="AF17" s="106"/>
-      <c r="AG17" s="106"/>
-      <c r="AH17" s="106"/>
-      <c r="AI17" s="106"/>
-      <c r="AJ17" s="106"/>
-      <c r="AK17" s="107"/>
+      <c r="F17" s="117"/>
+      <c r="G17" s="102"/>
+      <c r="H17" s="102"/>
+      <c r="I17" s="102"/>
+      <c r="J17" s="102"/>
+      <c r="K17" s="102"/>
+      <c r="L17" s="102"/>
+      <c r="M17" s="102"/>
+      <c r="N17" s="102"/>
+      <c r="O17" s="102"/>
+      <c r="P17" s="102"/>
+      <c r="Q17" s="102"/>
+      <c r="R17" s="102"/>
+      <c r="S17" s="102"/>
+      <c r="T17" s="102"/>
+      <c r="U17" s="102"/>
+      <c r="V17" s="102"/>
+      <c r="W17" s="102"/>
+      <c r="X17" s="102"/>
+      <c r="Y17" s="102"/>
+      <c r="Z17" s="102"/>
+      <c r="AA17" s="102"/>
+      <c r="AB17" s="102"/>
+      <c r="AC17" s="102"/>
+      <c r="AD17" s="102"/>
+      <c r="AE17" s="102"/>
+      <c r="AF17" s="102"/>
+      <c r="AG17" s="102"/>
+      <c r="AH17" s="102"/>
+      <c r="AI17" s="102"/>
+      <c r="AJ17" s="102"/>
+      <c r="AK17" s="103"/>
       <c r="AN17" s="3"/>
       <c r="AO17" s="3"/>
       <c r="AP17" s="3"/>
@@ -8035,51 +8039,51 @@
       <c r="IT17" s="3"/>
     </row>
     <row r="18" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A18" s="99">
+      <c r="A18" s="95">
         <v>7</v>
       </c>
-      <c r="B18" s="117" t="s">
+      <c r="B18" s="161" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="118"/>
-      <c r="D18" s="92" t="s">
+      <c r="C18" s="162"/>
+      <c r="D18" s="88" t="s">
         <v>99</v>
       </c>
-      <c r="E18" s="92" t="s">
+      <c r="E18" s="88" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="119"/>
-      <c r="G18" s="106"/>
-      <c r="H18" s="106"/>
-      <c r="I18" s="106"/>
-      <c r="J18" s="106"/>
-      <c r="K18" s="106"/>
-      <c r="L18" s="106"/>
-      <c r="M18" s="106"/>
-      <c r="N18" s="106"/>
-      <c r="O18" s="106"/>
-      <c r="P18" s="106"/>
-      <c r="Q18" s="106"/>
-      <c r="R18" s="106"/>
-      <c r="S18" s="106"/>
-      <c r="T18" s="106"/>
-      <c r="U18" s="106"/>
-      <c r="V18" s="106"/>
-      <c r="W18" s="106"/>
-      <c r="X18" s="106"/>
-      <c r="Y18" s="106"/>
-      <c r="Z18" s="106"/>
-      <c r="AA18" s="106"/>
-      <c r="AB18" s="106"/>
-      <c r="AC18" s="106"/>
-      <c r="AD18" s="106"/>
-      <c r="AE18" s="106"/>
-      <c r="AF18" s="106"/>
-      <c r="AG18" s="106"/>
-      <c r="AH18" s="106"/>
-      <c r="AI18" s="106"/>
-      <c r="AJ18" s="106"/>
-      <c r="AK18" s="107"/>
+      <c r="F18" s="117"/>
+      <c r="G18" s="102"/>
+      <c r="H18" s="102"/>
+      <c r="I18" s="102"/>
+      <c r="J18" s="102"/>
+      <c r="K18" s="102"/>
+      <c r="L18" s="102"/>
+      <c r="M18" s="102"/>
+      <c r="N18" s="102"/>
+      <c r="O18" s="102"/>
+      <c r="P18" s="102"/>
+      <c r="Q18" s="102"/>
+      <c r="R18" s="102"/>
+      <c r="S18" s="102"/>
+      <c r="T18" s="102"/>
+      <c r="U18" s="102"/>
+      <c r="V18" s="102"/>
+      <c r="W18" s="102"/>
+      <c r="X18" s="102"/>
+      <c r="Y18" s="102"/>
+      <c r="Z18" s="102"/>
+      <c r="AA18" s="102"/>
+      <c r="AB18" s="102"/>
+      <c r="AC18" s="102"/>
+      <c r="AD18" s="102"/>
+      <c r="AE18" s="102"/>
+      <c r="AF18" s="102"/>
+      <c r="AG18" s="102"/>
+      <c r="AH18" s="102"/>
+      <c r="AI18" s="102"/>
+      <c r="AJ18" s="102"/>
+      <c r="AK18" s="103"/>
       <c r="AN18" s="3"/>
       <c r="AO18" s="3"/>
       <c r="AP18" s="3"/>
@@ -8297,51 +8301,51 @@
       <c r="IT18" s="3"/>
     </row>
     <row r="19" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A19" s="99">
+      <c r="A19" s="95">
         <v>8</v>
       </c>
-      <c r="B19" s="117" t="s">
+      <c r="B19" s="161" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="118"/>
-      <c r="D19" s="92" t="s">
+      <c r="C19" s="162"/>
+      <c r="D19" s="88" t="s">
         <v>99</v>
       </c>
-      <c r="E19" s="92" t="s">
+      <c r="E19" s="88" t="s">
         <v>40</v>
       </c>
-      <c r="F19" s="119"/>
-      <c r="G19" s="106"/>
-      <c r="H19" s="106"/>
-      <c r="I19" s="106"/>
-      <c r="J19" s="106"/>
-      <c r="K19" s="106"/>
-      <c r="L19" s="106"/>
-      <c r="M19" s="106"/>
-      <c r="N19" s="106"/>
-      <c r="O19" s="106"/>
-      <c r="P19" s="106"/>
-      <c r="Q19" s="106"/>
-      <c r="R19" s="106"/>
-      <c r="S19" s="106"/>
-      <c r="T19" s="106"/>
-      <c r="U19" s="106"/>
-      <c r="V19" s="106"/>
-      <c r="W19" s="106"/>
-      <c r="X19" s="106"/>
-      <c r="Y19" s="106"/>
-      <c r="Z19" s="106"/>
-      <c r="AA19" s="106"/>
-      <c r="AB19" s="106"/>
-      <c r="AC19" s="106"/>
-      <c r="AD19" s="106"/>
-      <c r="AE19" s="106"/>
-      <c r="AF19" s="106"/>
-      <c r="AG19" s="106"/>
-      <c r="AH19" s="106"/>
-      <c r="AI19" s="106"/>
-      <c r="AJ19" s="106"/>
-      <c r="AK19" s="107"/>
+      <c r="F19" s="117"/>
+      <c r="G19" s="102"/>
+      <c r="H19" s="102"/>
+      <c r="I19" s="102"/>
+      <c r="J19" s="102"/>
+      <c r="K19" s="102"/>
+      <c r="L19" s="102"/>
+      <c r="M19" s="102"/>
+      <c r="N19" s="102"/>
+      <c r="O19" s="102"/>
+      <c r="P19" s="102"/>
+      <c r="Q19" s="102"/>
+      <c r="R19" s="102"/>
+      <c r="S19" s="102"/>
+      <c r="T19" s="102"/>
+      <c r="U19" s="102"/>
+      <c r="V19" s="102"/>
+      <c r="W19" s="102"/>
+      <c r="X19" s="102"/>
+      <c r="Y19" s="102"/>
+      <c r="Z19" s="102"/>
+      <c r="AA19" s="102"/>
+      <c r="AB19" s="102"/>
+      <c r="AC19" s="102"/>
+      <c r="AD19" s="102"/>
+      <c r="AE19" s="102"/>
+      <c r="AF19" s="102"/>
+      <c r="AG19" s="102"/>
+      <c r="AH19" s="102"/>
+      <c r="AI19" s="102"/>
+      <c r="AJ19" s="102"/>
+      <c r="AK19" s="103"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
@@ -8559,51 +8563,51 @@
       <c r="IT19" s="3"/>
     </row>
     <row r="20" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A20" s="99">
+      <c r="A20" s="95">
         <v>9</v>
       </c>
-      <c r="B20" s="117" t="s">
+      <c r="B20" s="161" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="118"/>
-      <c r="D20" s="92" t="s">
+      <c r="C20" s="162"/>
+      <c r="D20" s="88" t="s">
         <v>99</v>
       </c>
-      <c r="E20" s="92" t="s">
+      <c r="E20" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="F20" s="119"/>
-      <c r="G20" s="106"/>
-      <c r="H20" s="106"/>
-      <c r="I20" s="106"/>
-      <c r="J20" s="106"/>
-      <c r="K20" s="106"/>
-      <c r="L20" s="106"/>
-      <c r="M20" s="106"/>
-      <c r="N20" s="106"/>
-      <c r="O20" s="106"/>
-      <c r="P20" s="106"/>
-      <c r="Q20" s="106"/>
-      <c r="R20" s="106"/>
-      <c r="S20" s="106"/>
-      <c r="T20" s="106"/>
-      <c r="U20" s="106"/>
-      <c r="V20" s="106"/>
-      <c r="W20" s="106"/>
-      <c r="X20" s="106"/>
-      <c r="Y20" s="106"/>
-      <c r="Z20" s="106"/>
-      <c r="AA20" s="106"/>
-      <c r="AB20" s="106"/>
-      <c r="AC20" s="106"/>
-      <c r="AD20" s="106"/>
-      <c r="AE20" s="106"/>
-      <c r="AF20" s="106"/>
-      <c r="AG20" s="106"/>
-      <c r="AH20" s="106"/>
-      <c r="AI20" s="106"/>
-      <c r="AJ20" s="106"/>
-      <c r="AK20" s="107"/>
+      <c r="F20" s="117"/>
+      <c r="G20" s="102"/>
+      <c r="H20" s="102"/>
+      <c r="I20" s="102"/>
+      <c r="J20" s="102"/>
+      <c r="K20" s="102"/>
+      <c r="L20" s="102"/>
+      <c r="M20" s="102"/>
+      <c r="N20" s="102"/>
+      <c r="O20" s="102"/>
+      <c r="P20" s="102"/>
+      <c r="Q20" s="102"/>
+      <c r="R20" s="102"/>
+      <c r="S20" s="102"/>
+      <c r="T20" s="102"/>
+      <c r="U20" s="102"/>
+      <c r="V20" s="102"/>
+      <c r="W20" s="102"/>
+      <c r="X20" s="102"/>
+      <c r="Y20" s="102"/>
+      <c r="Z20" s="102"/>
+      <c r="AA20" s="102"/>
+      <c r="AB20" s="102"/>
+      <c r="AC20" s="102"/>
+      <c r="AD20" s="102"/>
+      <c r="AE20" s="102"/>
+      <c r="AF20" s="102"/>
+      <c r="AG20" s="102"/>
+      <c r="AH20" s="102"/>
+      <c r="AI20" s="102"/>
+      <c r="AJ20" s="102"/>
+      <c r="AK20" s="103"/>
       <c r="AN20" s="3"/>
       <c r="AO20" s="3"/>
       <c r="AP20" s="3"/>
@@ -8821,49 +8825,49 @@
       <c r="IT20" s="3"/>
     </row>
     <row r="21" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A21" s="99">
+      <c r="A21" s="95">
         <v>10</v>
       </c>
-      <c r="B21" s="117" t="s">
+      <c r="B21" s="161" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="118"/>
-      <c r="D21" s="92" t="s">
+      <c r="C21" s="162"/>
+      <c r="D21" s="88" t="s">
         <v>100</v>
       </c>
-      <c r="E21" s="92"/>
-      <c r="F21" s="119"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="106"/>
-      <c r="I21" s="106"/>
-      <c r="J21" s="106"/>
-      <c r="K21" s="106"/>
-      <c r="L21" s="106"/>
-      <c r="M21" s="106"/>
-      <c r="N21" s="106"/>
-      <c r="O21" s="106"/>
-      <c r="P21" s="106"/>
-      <c r="Q21" s="106"/>
-      <c r="R21" s="106"/>
-      <c r="S21" s="106"/>
-      <c r="T21" s="106"/>
-      <c r="U21" s="106"/>
-      <c r="V21" s="106"/>
-      <c r="W21" s="106"/>
-      <c r="X21" s="106"/>
-      <c r="Y21" s="106"/>
-      <c r="Z21" s="106"/>
-      <c r="AA21" s="106"/>
-      <c r="AB21" s="106"/>
-      <c r="AC21" s="106"/>
-      <c r="AD21" s="106"/>
-      <c r="AE21" s="106"/>
-      <c r="AF21" s="106"/>
-      <c r="AG21" s="106"/>
-      <c r="AH21" s="106"/>
-      <c r="AI21" s="106"/>
-      <c r="AJ21" s="106"/>
-      <c r="AK21" s="107"/>
+      <c r="E21" s="88"/>
+      <c r="F21" s="117"/>
+      <c r="G21" s="102"/>
+      <c r="H21" s="102"/>
+      <c r="I21" s="102"/>
+      <c r="J21" s="102"/>
+      <c r="K21" s="102"/>
+      <c r="L21" s="102"/>
+      <c r="M21" s="102"/>
+      <c r="N21" s="102"/>
+      <c r="O21" s="102"/>
+      <c r="P21" s="102"/>
+      <c r="Q21" s="102"/>
+      <c r="R21" s="102"/>
+      <c r="S21" s="102"/>
+      <c r="T21" s="102"/>
+      <c r="U21" s="102"/>
+      <c r="V21" s="102"/>
+      <c r="W21" s="102"/>
+      <c r="X21" s="102"/>
+      <c r="Y21" s="102"/>
+      <c r="Z21" s="102"/>
+      <c r="AA21" s="102"/>
+      <c r="AB21" s="102"/>
+      <c r="AC21" s="102"/>
+      <c r="AD21" s="102"/>
+      <c r="AE21" s="102"/>
+      <c r="AF21" s="102"/>
+      <c r="AG21" s="102"/>
+      <c r="AH21" s="102"/>
+      <c r="AI21" s="102"/>
+      <c r="AJ21" s="102"/>
+      <c r="AK21" s="103"/>
       <c r="AN21" s="3"/>
       <c r="AO21" s="3"/>
       <c r="AP21" s="3"/>
@@ -9081,51 +9085,51 @@
       <c r="IT21" s="3"/>
     </row>
     <row r="22" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A22" s="99">
+      <c r="A22" s="95">
         <v>11</v>
       </c>
-      <c r="B22" s="117" t="s">
+      <c r="B22" s="161" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="118"/>
-      <c r="D22" s="92" t="s">
+      <c r="C22" s="162"/>
+      <c r="D22" s="88" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="92"/>
-      <c r="F22" s="119" t="s">
+      <c r="E22" s="88"/>
+      <c r="F22" s="117" t="s">
         <v>135</v>
       </c>
-      <c r="G22" s="106"/>
-      <c r="H22" s="106"/>
-      <c r="I22" s="106"/>
-      <c r="J22" s="106"/>
-      <c r="K22" s="106"/>
-      <c r="L22" s="106"/>
-      <c r="M22" s="106"/>
-      <c r="N22" s="106"/>
-      <c r="O22" s="106"/>
-      <c r="P22" s="106"/>
-      <c r="Q22" s="106"/>
-      <c r="R22" s="106"/>
-      <c r="S22" s="106"/>
-      <c r="T22" s="106"/>
-      <c r="U22" s="106"/>
-      <c r="V22" s="106"/>
-      <c r="W22" s="106"/>
-      <c r="X22" s="106"/>
-      <c r="Y22" s="106"/>
-      <c r="Z22" s="106"/>
-      <c r="AA22" s="106"/>
-      <c r="AB22" s="106"/>
-      <c r="AC22" s="106"/>
-      <c r="AD22" s="106"/>
-      <c r="AE22" s="106"/>
-      <c r="AF22" s="106"/>
-      <c r="AG22" s="106"/>
-      <c r="AH22" s="106"/>
-      <c r="AI22" s="106"/>
-      <c r="AJ22" s="106"/>
-      <c r="AK22" s="107"/>
+      <c r="G22" s="102"/>
+      <c r="H22" s="102"/>
+      <c r="I22" s="102"/>
+      <c r="J22" s="102"/>
+      <c r="K22" s="102"/>
+      <c r="L22" s="102"/>
+      <c r="M22" s="102"/>
+      <c r="N22" s="102"/>
+      <c r="O22" s="102"/>
+      <c r="P22" s="102"/>
+      <c r="Q22" s="102"/>
+      <c r="R22" s="102"/>
+      <c r="S22" s="102"/>
+      <c r="T22" s="102"/>
+      <c r="U22" s="102"/>
+      <c r="V22" s="102"/>
+      <c r="W22" s="102"/>
+      <c r="X22" s="102"/>
+      <c r="Y22" s="102"/>
+      <c r="Z22" s="102"/>
+      <c r="AA22" s="102"/>
+      <c r="AB22" s="102"/>
+      <c r="AC22" s="102"/>
+      <c r="AD22" s="102"/>
+      <c r="AE22" s="102"/>
+      <c r="AF22" s="102"/>
+      <c r="AG22" s="102"/>
+      <c r="AH22" s="102"/>
+      <c r="AI22" s="102"/>
+      <c r="AJ22" s="102"/>
+      <c r="AK22" s="103"/>
       <c r="AN22" s="3"/>
       <c r="AO22" s="3"/>
       <c r="AP22" s="3"/>
@@ -9343,51 +9347,51 @@
       <c r="IT22" s="3"/>
     </row>
     <row r="23" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A23" s="99">
+      <c r="A23" s="95">
         <v>13</v>
       </c>
-      <c r="B23" s="117" t="s">
+      <c r="B23" s="161" t="s">
         <v>132</v>
       </c>
-      <c r="C23" s="118"/>
-      <c r="D23" s="92" t="s">
+      <c r="C23" s="162"/>
+      <c r="D23" s="88" t="s">
         <v>99</v>
       </c>
-      <c r="E23" s="92" t="s">
+      <c r="E23" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="F23" s="120"/>
-      <c r="G23" s="104"/>
-      <c r="H23" s="104"/>
-      <c r="I23" s="104"/>
-      <c r="J23" s="104"/>
-      <c r="K23" s="104"/>
-      <c r="L23" s="104"/>
-      <c r="M23" s="104"/>
-      <c r="N23" s="104"/>
-      <c r="O23" s="104"/>
-      <c r="P23" s="104"/>
-      <c r="Q23" s="104"/>
-      <c r="R23" s="104"/>
-      <c r="S23" s="104"/>
-      <c r="T23" s="104"/>
-      <c r="U23" s="104"/>
-      <c r="V23" s="104"/>
-      <c r="W23" s="104"/>
-      <c r="X23" s="104"/>
-      <c r="Y23" s="104"/>
-      <c r="Z23" s="104"/>
-      <c r="AA23" s="104"/>
-      <c r="AB23" s="104"/>
-      <c r="AC23" s="104"/>
-      <c r="AD23" s="104"/>
-      <c r="AE23" s="104"/>
-      <c r="AF23" s="104"/>
-      <c r="AG23" s="104"/>
-      <c r="AH23" s="104"/>
-      <c r="AI23" s="104"/>
-      <c r="AJ23" s="104"/>
-      <c r="AK23" s="105"/>
+      <c r="F23" s="118"/>
+      <c r="G23" s="100"/>
+      <c r="H23" s="100"/>
+      <c r="I23" s="100"/>
+      <c r="J23" s="100"/>
+      <c r="K23" s="100"/>
+      <c r="L23" s="100"/>
+      <c r="M23" s="100"/>
+      <c r="N23" s="100"/>
+      <c r="O23" s="100"/>
+      <c r="P23" s="100"/>
+      <c r="Q23" s="100"/>
+      <c r="R23" s="100"/>
+      <c r="S23" s="100"/>
+      <c r="T23" s="100"/>
+      <c r="U23" s="100"/>
+      <c r="V23" s="100"/>
+      <c r="W23" s="100"/>
+      <c r="X23" s="100"/>
+      <c r="Y23" s="100"/>
+      <c r="Z23" s="100"/>
+      <c r="AA23" s="100"/>
+      <c r="AB23" s="100"/>
+      <c r="AC23" s="100"/>
+      <c r="AD23" s="100"/>
+      <c r="AE23" s="100"/>
+      <c r="AF23" s="100"/>
+      <c r="AG23" s="100"/>
+      <c r="AH23" s="100"/>
+      <c r="AI23" s="100"/>
+      <c r="AJ23" s="100"/>
+      <c r="AK23" s="101"/>
       <c r="AN23" s="3"/>
       <c r="AO23" s="3"/>
       <c r="AP23" s="3"/>
@@ -9605,53 +9609,53 @@
       <c r="IT23" s="3"/>
     </row>
     <row r="24" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A24" s="99">
+      <c r="A24" s="95">
         <v>12</v>
       </c>
-      <c r="B24" s="117" t="s">
+      <c r="B24" s="161" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="118"/>
-      <c r="D24" s="92" t="s">
+      <c r="C24" s="162"/>
+      <c r="D24" s="88" t="s">
         <v>49</v>
       </c>
-      <c r="E24" s="92" t="s">
+      <c r="E24" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="F24" s="93" t="s">
+      <c r="F24" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="G24" s="104"/>
-      <c r="H24" s="104"/>
-      <c r="I24" s="104"/>
-      <c r="J24" s="104"/>
-      <c r="K24" s="104"/>
-      <c r="L24" s="104"/>
-      <c r="M24" s="104"/>
-      <c r="N24" s="104"/>
-      <c r="O24" s="104"/>
-      <c r="P24" s="104"/>
-      <c r="Q24" s="104"/>
-      <c r="R24" s="104"/>
-      <c r="S24" s="104"/>
-      <c r="T24" s="104"/>
-      <c r="U24" s="104"/>
-      <c r="V24" s="104"/>
-      <c r="W24" s="104"/>
-      <c r="X24" s="104"/>
-      <c r="Y24" s="104"/>
-      <c r="Z24" s="104"/>
-      <c r="AA24" s="104"/>
-      <c r="AB24" s="104"/>
-      <c r="AC24" s="104"/>
-      <c r="AD24" s="104"/>
-      <c r="AE24" s="104"/>
-      <c r="AF24" s="104"/>
-      <c r="AG24" s="104"/>
-      <c r="AH24" s="104"/>
-      <c r="AI24" s="104"/>
-      <c r="AJ24" s="104"/>
-      <c r="AK24" s="105"/>
+      <c r="G24" s="100"/>
+      <c r="H24" s="100"/>
+      <c r="I24" s="100"/>
+      <c r="J24" s="100"/>
+      <c r="K24" s="100"/>
+      <c r="L24" s="100"/>
+      <c r="M24" s="100"/>
+      <c r="N24" s="100"/>
+      <c r="O24" s="100"/>
+      <c r="P24" s="100"/>
+      <c r="Q24" s="100"/>
+      <c r="R24" s="100"/>
+      <c r="S24" s="100"/>
+      <c r="T24" s="100"/>
+      <c r="U24" s="100"/>
+      <c r="V24" s="100"/>
+      <c r="W24" s="100"/>
+      <c r="X24" s="100"/>
+      <c r="Y24" s="100"/>
+      <c r="Z24" s="100"/>
+      <c r="AA24" s="100"/>
+      <c r="AB24" s="100"/>
+      <c r="AC24" s="100"/>
+      <c r="AD24" s="100"/>
+      <c r="AE24" s="100"/>
+      <c r="AF24" s="100"/>
+      <c r="AG24" s="100"/>
+      <c r="AH24" s="100"/>
+      <c r="AI24" s="100"/>
+      <c r="AJ24" s="100"/>
+      <c r="AK24" s="101"/>
       <c r="AN24" s="3"/>
       <c r="AO24" s="3"/>
       <c r="AP24" s="3"/>
@@ -9870,42 +9874,42 @@
     </row>
     <row r="25" spans="1:254" s="2" customFormat="1" ht="10" customHeight="1">
       <c r="A25" s="37"/>
-      <c r="B25" s="117"/>
-      <c r="C25" s="118"/>
-      <c r="D25" s="92"/>
-      <c r="E25" s="92"/>
+      <c r="B25" s="161"/>
+      <c r="C25" s="162"/>
+      <c r="D25" s="88"/>
+      <c r="E25" s="88"/>
       <c r="F25" s="36"/>
-      <c r="G25" s="104"/>
-      <c r="H25" s="104"/>
-      <c r="I25" s="104"/>
-      <c r="J25" s="104"/>
-      <c r="K25" s="104"/>
-      <c r="L25" s="104"/>
-      <c r="M25" s="104"/>
-      <c r="N25" s="104"/>
-      <c r="O25" s="104"/>
-      <c r="P25" s="104"/>
-      <c r="Q25" s="104"/>
-      <c r="R25" s="104"/>
-      <c r="S25" s="104"/>
-      <c r="T25" s="104"/>
-      <c r="U25" s="104"/>
-      <c r="V25" s="104"/>
-      <c r="W25" s="104"/>
-      <c r="X25" s="104"/>
-      <c r="Y25" s="104"/>
-      <c r="Z25" s="104"/>
-      <c r="AA25" s="104"/>
-      <c r="AB25" s="104"/>
-      <c r="AC25" s="104"/>
-      <c r="AD25" s="104"/>
-      <c r="AE25" s="104"/>
-      <c r="AF25" s="104"/>
-      <c r="AG25" s="104"/>
-      <c r="AH25" s="104"/>
-      <c r="AI25" s="104"/>
-      <c r="AJ25" s="104"/>
-      <c r="AK25" s="105"/>
+      <c r="G25" s="100"/>
+      <c r="H25" s="100"/>
+      <c r="I25" s="100"/>
+      <c r="J25" s="100"/>
+      <c r="K25" s="100"/>
+      <c r="L25" s="100"/>
+      <c r="M25" s="100"/>
+      <c r="N25" s="100"/>
+      <c r="O25" s="100"/>
+      <c r="P25" s="100"/>
+      <c r="Q25" s="100"/>
+      <c r="R25" s="100"/>
+      <c r="S25" s="100"/>
+      <c r="T25" s="100"/>
+      <c r="U25" s="100"/>
+      <c r="V25" s="100"/>
+      <c r="W25" s="100"/>
+      <c r="X25" s="100"/>
+      <c r="Y25" s="100"/>
+      <c r="Z25" s="100"/>
+      <c r="AA25" s="100"/>
+      <c r="AB25" s="100"/>
+      <c r="AC25" s="100"/>
+      <c r="AD25" s="100"/>
+      <c r="AE25" s="100"/>
+      <c r="AF25" s="100"/>
+      <c r="AG25" s="100"/>
+      <c r="AH25" s="100"/>
+      <c r="AI25" s="100"/>
+      <c r="AJ25" s="100"/>
+      <c r="AK25" s="101"/>
       <c r="AN25" s="3"/>
       <c r="AO25" s="3"/>
       <c r="AP25" s="3"/>
@@ -10124,44 +10128,44 @@
     </row>
     <row r="26" spans="1:254" s="2" customFormat="1" ht="28.25" customHeight="1">
       <c r="A26" s="38"/>
-      <c r="B26" s="154" t="s">
+      <c r="B26" s="157" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="155"/>
+      <c r="C26" s="158"/>
       <c r="D26" s="35"/>
       <c r="E26" s="35"/>
       <c r="F26" s="39"/>
-      <c r="G26" s="104"/>
-      <c r="H26" s="104"/>
-      <c r="I26" s="104"/>
-      <c r="J26" s="104"/>
-      <c r="K26" s="104"/>
-      <c r="L26" s="104"/>
-      <c r="M26" s="104"/>
-      <c r="N26" s="104"/>
-      <c r="O26" s="104"/>
-      <c r="P26" s="104"/>
-      <c r="Q26" s="104"/>
-      <c r="R26" s="104"/>
-      <c r="S26" s="104"/>
-      <c r="T26" s="104"/>
-      <c r="U26" s="104"/>
-      <c r="V26" s="104"/>
-      <c r="W26" s="104"/>
-      <c r="X26" s="104"/>
-      <c r="Y26" s="104"/>
-      <c r="Z26" s="104"/>
-      <c r="AA26" s="104"/>
-      <c r="AB26" s="104"/>
-      <c r="AC26" s="104"/>
-      <c r="AD26" s="104"/>
-      <c r="AE26" s="104"/>
-      <c r="AF26" s="104"/>
-      <c r="AG26" s="104"/>
-      <c r="AH26" s="104"/>
-      <c r="AI26" s="104"/>
-      <c r="AJ26" s="104"/>
-      <c r="AK26" s="105"/>
+      <c r="G26" s="100"/>
+      <c r="H26" s="100"/>
+      <c r="I26" s="100"/>
+      <c r="J26" s="100"/>
+      <c r="K26" s="100"/>
+      <c r="L26" s="100"/>
+      <c r="M26" s="100"/>
+      <c r="N26" s="100"/>
+      <c r="O26" s="100"/>
+      <c r="P26" s="100"/>
+      <c r="Q26" s="100"/>
+      <c r="R26" s="100"/>
+      <c r="S26" s="100"/>
+      <c r="T26" s="100"/>
+      <c r="U26" s="100"/>
+      <c r="V26" s="100"/>
+      <c r="W26" s="100"/>
+      <c r="X26" s="100"/>
+      <c r="Y26" s="100"/>
+      <c r="Z26" s="100"/>
+      <c r="AA26" s="100"/>
+      <c r="AB26" s="100"/>
+      <c r="AC26" s="100"/>
+      <c r="AD26" s="100"/>
+      <c r="AE26" s="100"/>
+      <c r="AF26" s="100"/>
+      <c r="AG26" s="100"/>
+      <c r="AH26" s="100"/>
+      <c r="AI26" s="100"/>
+      <c r="AJ26" s="100"/>
+      <c r="AK26" s="101"/>
       <c r="AN26" s="3"/>
       <c r="AO26" s="3"/>
       <c r="AP26" s="3"/>
@@ -10382,50 +10386,50 @@
       <c r="A27" s="37">
         <v>1</v>
       </c>
-      <c r="B27" s="156" t="s">
+      <c r="B27" s="163" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="157"/>
-      <c r="D27" s="92" t="s">
+      <c r="C27" s="164"/>
+      <c r="D27" s="88" t="s">
         <v>99</v>
       </c>
-      <c r="E27" s="92" t="s">
+      <c r="E27" s="88" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="158" t="s">
+      <c r="F27" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="G27" s="106"/>
-      <c r="H27" s="106"/>
-      <c r="I27" s="106"/>
-      <c r="J27" s="106"/>
-      <c r="K27" s="106"/>
-      <c r="L27" s="106"/>
-      <c r="M27" s="106"/>
-      <c r="N27" s="106"/>
-      <c r="O27" s="106"/>
-      <c r="P27" s="106"/>
-      <c r="Q27" s="106"/>
-      <c r="R27" s="106"/>
-      <c r="S27" s="106"/>
-      <c r="T27" s="106"/>
-      <c r="U27" s="106"/>
-      <c r="V27" s="106"/>
-      <c r="W27" s="106"/>
-      <c r="X27" s="106"/>
-      <c r="Y27" s="106"/>
-      <c r="Z27" s="106"/>
-      <c r="AA27" s="106"/>
-      <c r="AB27" s="106"/>
-      <c r="AC27" s="106"/>
-      <c r="AD27" s="106"/>
-      <c r="AE27" s="106"/>
-      <c r="AF27" s="106"/>
-      <c r="AG27" s="106"/>
-      <c r="AH27" s="106"/>
-      <c r="AI27" s="106"/>
-      <c r="AJ27" s="106"/>
-      <c r="AK27" s="107"/>
+      <c r="G27" s="102"/>
+      <c r="H27" s="102"/>
+      <c r="I27" s="102"/>
+      <c r="J27" s="102"/>
+      <c r="K27" s="102"/>
+      <c r="L27" s="102"/>
+      <c r="M27" s="102"/>
+      <c r="N27" s="102"/>
+      <c r="O27" s="102"/>
+      <c r="P27" s="102"/>
+      <c r="Q27" s="102"/>
+      <c r="R27" s="102"/>
+      <c r="S27" s="102"/>
+      <c r="T27" s="102"/>
+      <c r="U27" s="102"/>
+      <c r="V27" s="102"/>
+      <c r="W27" s="102"/>
+      <c r="X27" s="102"/>
+      <c r="Y27" s="102"/>
+      <c r="Z27" s="102"/>
+      <c r="AA27" s="102"/>
+      <c r="AB27" s="102"/>
+      <c r="AC27" s="102"/>
+      <c r="AD27" s="102"/>
+      <c r="AE27" s="102"/>
+      <c r="AF27" s="102"/>
+      <c r="AG27" s="102"/>
+      <c r="AH27" s="102"/>
+      <c r="AI27" s="102"/>
+      <c r="AJ27" s="102"/>
+      <c r="AK27" s="103"/>
       <c r="AN27" s="3"/>
       <c r="AO27" s="3"/>
       <c r="AP27" s="3"/>
@@ -10646,46 +10650,46 @@
       <c r="A28" s="37">
         <v>2</v>
       </c>
-      <c r="B28" s="156" t="s">
+      <c r="B28" s="163" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="157"/>
+      <c r="C28" s="164"/>
       <c r="D28" s="35" t="s">
         <v>77</v>
       </c>
       <c r="E28" s="35"/>
-      <c r="F28" s="119"/>
-      <c r="G28" s="106"/>
-      <c r="H28" s="106"/>
-      <c r="I28" s="106"/>
-      <c r="J28" s="106"/>
-      <c r="K28" s="106"/>
-      <c r="L28" s="106"/>
-      <c r="M28" s="106"/>
-      <c r="N28" s="106"/>
-      <c r="O28" s="106"/>
-      <c r="P28" s="106"/>
-      <c r="Q28" s="106"/>
-      <c r="R28" s="106"/>
-      <c r="S28" s="106"/>
-      <c r="T28" s="106"/>
-      <c r="U28" s="106"/>
-      <c r="V28" s="106"/>
-      <c r="W28" s="106"/>
-      <c r="X28" s="106"/>
-      <c r="Y28" s="106"/>
-      <c r="Z28" s="106"/>
-      <c r="AA28" s="106"/>
-      <c r="AB28" s="106"/>
-      <c r="AC28" s="106"/>
-      <c r="AD28" s="106"/>
-      <c r="AE28" s="106"/>
-      <c r="AF28" s="106"/>
-      <c r="AG28" s="106"/>
-      <c r="AH28" s="106"/>
-      <c r="AI28" s="106"/>
-      <c r="AJ28" s="106"/>
-      <c r="AK28" s="107"/>
+      <c r="F28" s="117"/>
+      <c r="G28" s="102"/>
+      <c r="H28" s="102"/>
+      <c r="I28" s="102"/>
+      <c r="J28" s="102"/>
+      <c r="K28" s="102"/>
+      <c r="L28" s="102"/>
+      <c r="M28" s="102"/>
+      <c r="N28" s="102"/>
+      <c r="O28" s="102"/>
+      <c r="P28" s="102"/>
+      <c r="Q28" s="102"/>
+      <c r="R28" s="102"/>
+      <c r="S28" s="102"/>
+      <c r="T28" s="102"/>
+      <c r="U28" s="102"/>
+      <c r="V28" s="102"/>
+      <c r="W28" s="102"/>
+      <c r="X28" s="102"/>
+      <c r="Y28" s="102"/>
+      <c r="Z28" s="102"/>
+      <c r="AA28" s="102"/>
+      <c r="AB28" s="102"/>
+      <c r="AC28" s="102"/>
+      <c r="AD28" s="102"/>
+      <c r="AE28" s="102"/>
+      <c r="AF28" s="102"/>
+      <c r="AG28" s="102"/>
+      <c r="AH28" s="102"/>
+      <c r="AI28" s="102"/>
+      <c r="AJ28" s="102"/>
+      <c r="AK28" s="103"/>
       <c r="AN28" s="3"/>
       <c r="AO28" s="3"/>
       <c r="AP28" s="3"/>
@@ -10906,46 +10910,46 @@
       <c r="A29" s="37">
         <v>3</v>
       </c>
-      <c r="B29" s="117" t="s">
+      <c r="B29" s="161" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="118"/>
+      <c r="C29" s="162"/>
       <c r="D29" s="35" t="s">
         <v>77</v>
       </c>
       <c r="E29" s="35"/>
-      <c r="F29" s="119"/>
-      <c r="G29" s="106"/>
-      <c r="H29" s="106"/>
-      <c r="I29" s="106"/>
-      <c r="J29" s="106"/>
-      <c r="K29" s="106"/>
-      <c r="L29" s="106"/>
-      <c r="M29" s="106"/>
-      <c r="N29" s="106"/>
-      <c r="O29" s="106"/>
-      <c r="P29" s="106"/>
-      <c r="Q29" s="106"/>
-      <c r="R29" s="106"/>
-      <c r="S29" s="106"/>
-      <c r="T29" s="106"/>
-      <c r="U29" s="106"/>
-      <c r="V29" s="106"/>
-      <c r="W29" s="106"/>
-      <c r="X29" s="106"/>
-      <c r="Y29" s="106"/>
-      <c r="Z29" s="106"/>
-      <c r="AA29" s="106"/>
-      <c r="AB29" s="106"/>
-      <c r="AC29" s="106"/>
-      <c r="AD29" s="106"/>
-      <c r="AE29" s="106"/>
-      <c r="AF29" s="106"/>
-      <c r="AG29" s="106"/>
-      <c r="AH29" s="106"/>
-      <c r="AI29" s="106"/>
-      <c r="AJ29" s="106"/>
-      <c r="AK29" s="108"/>
+      <c r="F29" s="117"/>
+      <c r="G29" s="102"/>
+      <c r="H29" s="102"/>
+      <c r="I29" s="102"/>
+      <c r="J29" s="102"/>
+      <c r="K29" s="102"/>
+      <c r="L29" s="102"/>
+      <c r="M29" s="102"/>
+      <c r="N29" s="102"/>
+      <c r="O29" s="102"/>
+      <c r="P29" s="102"/>
+      <c r="Q29" s="102"/>
+      <c r="R29" s="102"/>
+      <c r="S29" s="102"/>
+      <c r="T29" s="102"/>
+      <c r="U29" s="102"/>
+      <c r="V29" s="102"/>
+      <c r="W29" s="102"/>
+      <c r="X29" s="102"/>
+      <c r="Y29" s="102"/>
+      <c r="Z29" s="102"/>
+      <c r="AA29" s="102"/>
+      <c r="AB29" s="102"/>
+      <c r="AC29" s="102"/>
+      <c r="AD29" s="102"/>
+      <c r="AE29" s="102"/>
+      <c r="AF29" s="102"/>
+      <c r="AG29" s="102"/>
+      <c r="AH29" s="102"/>
+      <c r="AI29" s="102"/>
+      <c r="AJ29" s="102"/>
+      <c r="AK29" s="104"/>
       <c r="AN29" s="3"/>
       <c r="AO29" s="3"/>
       <c r="AP29" s="3"/>
@@ -11166,48 +11170,48 @@
       <c r="A30" s="37">
         <v>4</v>
       </c>
-      <c r="B30" s="117" t="s">
+      <c r="B30" s="161" t="s">
         <v>54</v>
       </c>
-      <c r="C30" s="118"/>
-      <c r="D30" s="96" t="s">
+      <c r="C30" s="162"/>
+      <c r="D30" s="92" t="s">
         <v>103</v>
       </c>
-      <c r="E30" s="92" t="s">
+      <c r="E30" s="88" t="s">
         <v>62</v>
       </c>
-      <c r="F30" s="119"/>
-      <c r="G30" s="104"/>
-      <c r="H30" s="104"/>
-      <c r="I30" s="104"/>
-      <c r="J30" s="104"/>
-      <c r="K30" s="104"/>
-      <c r="L30" s="104"/>
-      <c r="M30" s="104"/>
-      <c r="N30" s="104"/>
-      <c r="O30" s="104"/>
-      <c r="P30" s="104"/>
-      <c r="Q30" s="104"/>
-      <c r="R30" s="104"/>
-      <c r="S30" s="104"/>
-      <c r="T30" s="104"/>
-      <c r="U30" s="104"/>
-      <c r="V30" s="104"/>
-      <c r="W30" s="104"/>
-      <c r="X30" s="104"/>
-      <c r="Y30" s="104"/>
-      <c r="Z30" s="104"/>
-      <c r="AA30" s="104"/>
-      <c r="AB30" s="104"/>
-      <c r="AC30" s="104"/>
-      <c r="AD30" s="104"/>
-      <c r="AE30" s="104"/>
-      <c r="AF30" s="104"/>
-      <c r="AG30" s="104"/>
-      <c r="AH30" s="104"/>
-      <c r="AI30" s="104"/>
-      <c r="AJ30" s="104"/>
-      <c r="AK30" s="105"/>
+      <c r="F30" s="117"/>
+      <c r="G30" s="100"/>
+      <c r="H30" s="100"/>
+      <c r="I30" s="100"/>
+      <c r="J30" s="100"/>
+      <c r="K30" s="100"/>
+      <c r="L30" s="100"/>
+      <c r="M30" s="100"/>
+      <c r="N30" s="100"/>
+      <c r="O30" s="100"/>
+      <c r="P30" s="100"/>
+      <c r="Q30" s="100"/>
+      <c r="R30" s="100"/>
+      <c r="S30" s="100"/>
+      <c r="T30" s="100"/>
+      <c r="U30" s="100"/>
+      <c r="V30" s="100"/>
+      <c r="W30" s="100"/>
+      <c r="X30" s="100"/>
+      <c r="Y30" s="100"/>
+      <c r="Z30" s="100"/>
+      <c r="AA30" s="100"/>
+      <c r="AB30" s="100"/>
+      <c r="AC30" s="100"/>
+      <c r="AD30" s="100"/>
+      <c r="AE30" s="100"/>
+      <c r="AF30" s="100"/>
+      <c r="AG30" s="100"/>
+      <c r="AH30" s="100"/>
+      <c r="AI30" s="100"/>
+      <c r="AJ30" s="100"/>
+      <c r="AK30" s="101"/>
       <c r="AN30" s="3"/>
       <c r="AO30" s="3"/>
       <c r="AP30" s="3"/>
@@ -11428,46 +11432,46 @@
       <c r="A31" s="37">
         <v>5</v>
       </c>
-      <c r="B31" s="156" t="s">
+      <c r="B31" s="163" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="157"/>
-      <c r="D31" s="92" t="s">
+      <c r="C31" s="164"/>
+      <c r="D31" s="88" t="s">
         <v>80</v>
       </c>
       <c r="E31" s="35"/>
-      <c r="F31" s="119"/>
-      <c r="G31" s="104"/>
-      <c r="H31" s="104"/>
-      <c r="I31" s="104"/>
-      <c r="J31" s="104"/>
-      <c r="K31" s="104"/>
-      <c r="L31" s="104"/>
-      <c r="M31" s="104"/>
-      <c r="N31" s="104"/>
-      <c r="O31" s="104"/>
-      <c r="P31" s="104"/>
-      <c r="Q31" s="104"/>
-      <c r="R31" s="104"/>
-      <c r="S31" s="104"/>
-      <c r="T31" s="104"/>
-      <c r="U31" s="104"/>
-      <c r="V31" s="104"/>
-      <c r="W31" s="104"/>
-      <c r="X31" s="104"/>
-      <c r="Y31" s="104"/>
-      <c r="Z31" s="104"/>
-      <c r="AA31" s="104"/>
-      <c r="AB31" s="104"/>
-      <c r="AC31" s="104"/>
-      <c r="AD31" s="104"/>
-      <c r="AE31" s="104"/>
-      <c r="AF31" s="104"/>
-      <c r="AG31" s="104"/>
-      <c r="AH31" s="104"/>
-      <c r="AI31" s="104"/>
-      <c r="AJ31" s="104"/>
-      <c r="AK31" s="105"/>
+      <c r="F31" s="117"/>
+      <c r="G31" s="100"/>
+      <c r="H31" s="100"/>
+      <c r="I31" s="100"/>
+      <c r="J31" s="100"/>
+      <c r="K31" s="100"/>
+      <c r="L31" s="100"/>
+      <c r="M31" s="100"/>
+      <c r="N31" s="100"/>
+      <c r="O31" s="100"/>
+      <c r="P31" s="100"/>
+      <c r="Q31" s="100"/>
+      <c r="R31" s="100"/>
+      <c r="S31" s="100"/>
+      <c r="T31" s="100"/>
+      <c r="U31" s="100"/>
+      <c r="V31" s="100"/>
+      <c r="W31" s="100"/>
+      <c r="X31" s="100"/>
+      <c r="Y31" s="100"/>
+      <c r="Z31" s="100"/>
+      <c r="AA31" s="100"/>
+      <c r="AB31" s="100"/>
+      <c r="AC31" s="100"/>
+      <c r="AD31" s="100"/>
+      <c r="AE31" s="100"/>
+      <c r="AF31" s="100"/>
+      <c r="AG31" s="100"/>
+      <c r="AH31" s="100"/>
+      <c r="AI31" s="100"/>
+      <c r="AJ31" s="100"/>
+      <c r="AK31" s="101"/>
       <c r="AN31" s="3"/>
       <c r="AO31" s="3"/>
       <c r="AP31" s="3"/>
@@ -11688,46 +11692,46 @@
       <c r="A32" s="37">
         <v>6</v>
       </c>
-      <c r="B32" s="117" t="s">
+      <c r="B32" s="161" t="s">
         <v>57</v>
       </c>
-      <c r="C32" s="118"/>
-      <c r="D32" s="92" t="s">
+      <c r="C32" s="162"/>
+      <c r="D32" s="88" t="s">
         <v>118</v>
       </c>
       <c r="E32" s="35"/>
-      <c r="F32" s="119"/>
-      <c r="G32" s="104"/>
-      <c r="H32" s="104"/>
-      <c r="I32" s="104"/>
-      <c r="J32" s="104"/>
-      <c r="K32" s="104"/>
-      <c r="L32" s="104"/>
-      <c r="M32" s="104"/>
-      <c r="N32" s="104"/>
-      <c r="O32" s="104"/>
-      <c r="P32" s="104"/>
-      <c r="Q32" s="104"/>
-      <c r="R32" s="104"/>
-      <c r="S32" s="104"/>
-      <c r="T32" s="104"/>
-      <c r="U32" s="104"/>
-      <c r="V32" s="104"/>
-      <c r="W32" s="104"/>
-      <c r="X32" s="104"/>
-      <c r="Y32" s="104"/>
-      <c r="Z32" s="104"/>
-      <c r="AA32" s="104"/>
-      <c r="AB32" s="104"/>
-      <c r="AC32" s="104"/>
-      <c r="AD32" s="104"/>
-      <c r="AE32" s="104"/>
-      <c r="AF32" s="104"/>
-      <c r="AG32" s="104"/>
-      <c r="AH32" s="104"/>
-      <c r="AI32" s="104"/>
-      <c r="AJ32" s="109"/>
-      <c r="AK32" s="110"/>
+      <c r="F32" s="117"/>
+      <c r="G32" s="100"/>
+      <c r="H32" s="100"/>
+      <c r="I32" s="100"/>
+      <c r="J32" s="100"/>
+      <c r="K32" s="100"/>
+      <c r="L32" s="100"/>
+      <c r="M32" s="100"/>
+      <c r="N32" s="100"/>
+      <c r="O32" s="100"/>
+      <c r="P32" s="100"/>
+      <c r="Q32" s="100"/>
+      <c r="R32" s="100"/>
+      <c r="S32" s="100"/>
+      <c r="T32" s="100"/>
+      <c r="U32" s="100"/>
+      <c r="V32" s="100"/>
+      <c r="W32" s="100"/>
+      <c r="X32" s="100"/>
+      <c r="Y32" s="100"/>
+      <c r="Z32" s="100"/>
+      <c r="AA32" s="100"/>
+      <c r="AB32" s="100"/>
+      <c r="AC32" s="100"/>
+      <c r="AD32" s="100"/>
+      <c r="AE32" s="100"/>
+      <c r="AF32" s="100"/>
+      <c r="AG32" s="100"/>
+      <c r="AH32" s="100"/>
+      <c r="AI32" s="100"/>
+      <c r="AJ32" s="105"/>
+      <c r="AK32" s="106"/>
       <c r="AN32" s="3"/>
       <c r="AO32" s="3"/>
       <c r="AP32" s="3"/>
@@ -11948,46 +11952,46 @@
       <c r="A33" s="37">
         <v>7</v>
       </c>
-      <c r="B33" s="117" t="s">
+      <c r="B33" s="161" t="s">
         <v>58</v>
       </c>
-      <c r="C33" s="118"/>
-      <c r="D33" s="92" t="s">
+      <c r="C33" s="162"/>
+      <c r="D33" s="88" t="s">
         <v>118</v>
       </c>
       <c r="E33" s="35"/>
-      <c r="F33" s="119"/>
-      <c r="G33" s="104"/>
-      <c r="H33" s="104"/>
-      <c r="I33" s="104"/>
-      <c r="J33" s="104"/>
-      <c r="K33" s="104"/>
-      <c r="L33" s="104"/>
-      <c r="M33" s="104"/>
-      <c r="N33" s="104"/>
-      <c r="O33" s="104"/>
-      <c r="P33" s="104"/>
-      <c r="Q33" s="104"/>
-      <c r="R33" s="104"/>
-      <c r="S33" s="104"/>
-      <c r="T33" s="104"/>
-      <c r="U33" s="104"/>
-      <c r="V33" s="104"/>
-      <c r="W33" s="104"/>
-      <c r="X33" s="104"/>
-      <c r="Y33" s="104"/>
-      <c r="Z33" s="104"/>
-      <c r="AA33" s="104"/>
-      <c r="AB33" s="104"/>
-      <c r="AC33" s="104"/>
-      <c r="AD33" s="104"/>
-      <c r="AE33" s="104"/>
-      <c r="AF33" s="104"/>
-      <c r="AG33" s="104"/>
-      <c r="AH33" s="104"/>
-      <c r="AI33" s="104"/>
-      <c r="AJ33" s="109"/>
-      <c r="AK33" s="110"/>
+      <c r="F33" s="117"/>
+      <c r="G33" s="100"/>
+      <c r="H33" s="100"/>
+      <c r="I33" s="100"/>
+      <c r="J33" s="100"/>
+      <c r="K33" s="100"/>
+      <c r="L33" s="100"/>
+      <c r="M33" s="100"/>
+      <c r="N33" s="100"/>
+      <c r="O33" s="100"/>
+      <c r="P33" s="100"/>
+      <c r="Q33" s="100"/>
+      <c r="R33" s="100"/>
+      <c r="S33" s="100"/>
+      <c r="T33" s="100"/>
+      <c r="U33" s="100"/>
+      <c r="V33" s="100"/>
+      <c r="W33" s="100"/>
+      <c r="X33" s="100"/>
+      <c r="Y33" s="100"/>
+      <c r="Z33" s="100"/>
+      <c r="AA33" s="100"/>
+      <c r="AB33" s="100"/>
+      <c r="AC33" s="100"/>
+      <c r="AD33" s="100"/>
+      <c r="AE33" s="100"/>
+      <c r="AF33" s="100"/>
+      <c r="AG33" s="100"/>
+      <c r="AH33" s="100"/>
+      <c r="AI33" s="100"/>
+      <c r="AJ33" s="105"/>
+      <c r="AK33" s="106"/>
       <c r="AN33" s="3"/>
       <c r="AO33" s="3"/>
       <c r="AP33" s="3"/>
@@ -12208,46 +12212,46 @@
       <c r="A34" s="37">
         <v>8</v>
       </c>
-      <c r="B34" s="156" t="s">
+      <c r="B34" s="163" t="s">
         <v>59</v>
       </c>
-      <c r="C34" s="157"/>
-      <c r="D34" s="92" t="s">
+      <c r="C34" s="164"/>
+      <c r="D34" s="88" t="s">
         <v>99</v>
       </c>
       <c r="E34" s="40"/>
-      <c r="F34" s="119"/>
-      <c r="G34" s="106"/>
-      <c r="H34" s="106"/>
-      <c r="I34" s="106"/>
-      <c r="J34" s="106"/>
-      <c r="K34" s="106"/>
-      <c r="L34" s="106"/>
-      <c r="M34" s="106"/>
-      <c r="N34" s="106"/>
-      <c r="O34" s="106"/>
-      <c r="P34" s="106"/>
-      <c r="Q34" s="106"/>
-      <c r="R34" s="106"/>
-      <c r="S34" s="106"/>
-      <c r="T34" s="106"/>
-      <c r="U34" s="106"/>
-      <c r="V34" s="106"/>
-      <c r="W34" s="106"/>
-      <c r="X34" s="106"/>
-      <c r="Y34" s="106"/>
-      <c r="Z34" s="106"/>
-      <c r="AA34" s="106"/>
-      <c r="AB34" s="106"/>
-      <c r="AC34" s="106"/>
-      <c r="AD34" s="106"/>
-      <c r="AE34" s="106"/>
-      <c r="AF34" s="106"/>
-      <c r="AG34" s="106"/>
-      <c r="AH34" s="106"/>
-      <c r="AI34" s="106"/>
-      <c r="AJ34" s="111"/>
-      <c r="AK34" s="112"/>
+      <c r="F34" s="117"/>
+      <c r="G34" s="102"/>
+      <c r="H34" s="102"/>
+      <c r="I34" s="102"/>
+      <c r="J34" s="102"/>
+      <c r="K34" s="102"/>
+      <c r="L34" s="102"/>
+      <c r="M34" s="102"/>
+      <c r="N34" s="102"/>
+      <c r="O34" s="102"/>
+      <c r="P34" s="102"/>
+      <c r="Q34" s="102"/>
+      <c r="R34" s="102"/>
+      <c r="S34" s="102"/>
+      <c r="T34" s="102"/>
+      <c r="U34" s="102"/>
+      <c r="V34" s="102"/>
+      <c r="W34" s="102"/>
+      <c r="X34" s="102"/>
+      <c r="Y34" s="102"/>
+      <c r="Z34" s="102"/>
+      <c r="AA34" s="102"/>
+      <c r="AB34" s="102"/>
+      <c r="AC34" s="102"/>
+      <c r="AD34" s="102"/>
+      <c r="AE34" s="102"/>
+      <c r="AF34" s="102"/>
+      <c r="AG34" s="102"/>
+      <c r="AH34" s="102"/>
+      <c r="AI34" s="102"/>
+      <c r="AJ34" s="107"/>
+      <c r="AK34" s="108"/>
       <c r="AN34" s="3"/>
       <c r="AO34" s="3"/>
       <c r="AP34" s="3"/>
@@ -12468,46 +12472,46 @@
       <c r="A35" s="37">
         <v>9</v>
       </c>
-      <c r="B35" s="156" t="s">
+      <c r="B35" s="163" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="157"/>
-      <c r="D35" s="92" t="s">
+      <c r="C35" s="164"/>
+      <c r="D35" s="88" t="s">
         <v>49</v>
       </c>
       <c r="E35" s="40"/>
-      <c r="F35" s="120"/>
-      <c r="G35" s="106"/>
-      <c r="H35" s="106"/>
-      <c r="I35" s="106"/>
-      <c r="J35" s="106"/>
-      <c r="K35" s="106"/>
-      <c r="L35" s="106"/>
-      <c r="M35" s="106"/>
-      <c r="N35" s="106"/>
-      <c r="O35" s="106"/>
-      <c r="P35" s="106"/>
-      <c r="Q35" s="106"/>
-      <c r="R35" s="106"/>
-      <c r="S35" s="106"/>
-      <c r="T35" s="106"/>
-      <c r="U35" s="106"/>
-      <c r="V35" s="106"/>
-      <c r="W35" s="106"/>
-      <c r="X35" s="106"/>
-      <c r="Y35" s="106"/>
-      <c r="Z35" s="106"/>
-      <c r="AA35" s="106"/>
-      <c r="AB35" s="106"/>
-      <c r="AC35" s="106"/>
-      <c r="AD35" s="106"/>
-      <c r="AE35" s="106"/>
-      <c r="AF35" s="106"/>
-      <c r="AG35" s="106"/>
-      <c r="AH35" s="106"/>
-      <c r="AI35" s="106"/>
-      <c r="AJ35" s="111"/>
-      <c r="AK35" s="112"/>
+      <c r="F35" s="118"/>
+      <c r="G35" s="102"/>
+      <c r="H35" s="102"/>
+      <c r="I35" s="102"/>
+      <c r="J35" s="102"/>
+      <c r="K35" s="102"/>
+      <c r="L35" s="102"/>
+      <c r="M35" s="102"/>
+      <c r="N35" s="102"/>
+      <c r="O35" s="102"/>
+      <c r="P35" s="102"/>
+      <c r="Q35" s="102"/>
+      <c r="R35" s="102"/>
+      <c r="S35" s="102"/>
+      <c r="T35" s="102"/>
+      <c r="U35" s="102"/>
+      <c r="V35" s="102"/>
+      <c r="W35" s="102"/>
+      <c r="X35" s="102"/>
+      <c r="Y35" s="102"/>
+      <c r="Z35" s="102"/>
+      <c r="AA35" s="102"/>
+      <c r="AB35" s="102"/>
+      <c r="AC35" s="102"/>
+      <c r="AD35" s="102"/>
+      <c r="AE35" s="102"/>
+      <c r="AF35" s="102"/>
+      <c r="AG35" s="102"/>
+      <c r="AH35" s="102"/>
+      <c r="AI35" s="102"/>
+      <c r="AJ35" s="107"/>
+      <c r="AK35" s="108"/>
       <c r="AN35" s="3"/>
       <c r="AO35" s="3"/>
       <c r="AP35" s="3"/>
@@ -12726,44 +12730,44 @@
     </row>
     <row r="36" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A36" s="37"/>
-      <c r="B36" s="154" t="s">
+      <c r="B36" s="157" t="s">
         <v>127</v>
       </c>
-      <c r="C36" s="155"/>
-      <c r="D36" s="92"/>
+      <c r="C36" s="158"/>
+      <c r="D36" s="88"/>
       <c r="E36" s="40"/>
-      <c r="F36" s="93"/>
-      <c r="G36" s="106"/>
-      <c r="H36" s="106"/>
-      <c r="I36" s="106"/>
-      <c r="J36" s="106"/>
-      <c r="K36" s="106"/>
-      <c r="L36" s="106"/>
-      <c r="M36" s="106"/>
-      <c r="N36" s="106"/>
-      <c r="O36" s="106"/>
-      <c r="P36" s="106"/>
-      <c r="Q36" s="106"/>
-      <c r="R36" s="106"/>
-      <c r="S36" s="106"/>
-      <c r="T36" s="106"/>
-      <c r="U36" s="106"/>
-      <c r="V36" s="106"/>
-      <c r="W36" s="106"/>
-      <c r="X36" s="106"/>
-      <c r="Y36" s="106"/>
-      <c r="Z36" s="106"/>
-      <c r="AA36" s="106"/>
-      <c r="AB36" s="106"/>
-      <c r="AC36" s="106"/>
-      <c r="AD36" s="106"/>
-      <c r="AE36" s="106"/>
-      <c r="AF36" s="106"/>
-      <c r="AG36" s="106"/>
-      <c r="AH36" s="106"/>
-      <c r="AI36" s="106"/>
-      <c r="AJ36" s="111"/>
-      <c r="AK36" s="112"/>
+      <c r="F36" s="89"/>
+      <c r="G36" s="102"/>
+      <c r="H36" s="102"/>
+      <c r="I36" s="102"/>
+      <c r="J36" s="102"/>
+      <c r="K36" s="102"/>
+      <c r="L36" s="102"/>
+      <c r="M36" s="102"/>
+      <c r="N36" s="102"/>
+      <c r="O36" s="102"/>
+      <c r="P36" s="102"/>
+      <c r="Q36" s="102"/>
+      <c r="R36" s="102"/>
+      <c r="S36" s="102"/>
+      <c r="T36" s="102"/>
+      <c r="U36" s="102"/>
+      <c r="V36" s="102"/>
+      <c r="W36" s="102"/>
+      <c r="X36" s="102"/>
+      <c r="Y36" s="102"/>
+      <c r="Z36" s="102"/>
+      <c r="AA36" s="102"/>
+      <c r="AB36" s="102"/>
+      <c r="AC36" s="102"/>
+      <c r="AD36" s="102"/>
+      <c r="AE36" s="102"/>
+      <c r="AF36" s="102"/>
+      <c r="AG36" s="102"/>
+      <c r="AH36" s="102"/>
+      <c r="AI36" s="102"/>
+      <c r="AJ36" s="107"/>
+      <c r="AK36" s="108"/>
       <c r="AN36" s="3"/>
       <c r="AO36" s="3"/>
       <c r="AP36" s="3"/>
@@ -12982,44 +12986,44 @@
     </row>
     <row r="37" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A37" s="37"/>
-      <c r="B37" s="156" t="s">
+      <c r="B37" s="163" t="s">
         <v>128</v>
       </c>
-      <c r="C37" s="157"/>
-      <c r="D37" s="92"/>
+      <c r="C37" s="164"/>
+      <c r="D37" s="88"/>
       <c r="E37" s="40"/>
-      <c r="F37" s="93"/>
-      <c r="G37" s="106"/>
-      <c r="H37" s="106"/>
-      <c r="I37" s="106"/>
-      <c r="J37" s="106"/>
-      <c r="K37" s="106"/>
-      <c r="L37" s="106"/>
-      <c r="M37" s="106"/>
-      <c r="N37" s="106"/>
-      <c r="O37" s="106"/>
-      <c r="P37" s="106"/>
-      <c r="Q37" s="106"/>
-      <c r="R37" s="106"/>
-      <c r="S37" s="106"/>
-      <c r="T37" s="106"/>
-      <c r="U37" s="106"/>
-      <c r="V37" s="106"/>
-      <c r="W37" s="106"/>
-      <c r="X37" s="106"/>
-      <c r="Y37" s="106"/>
-      <c r="Z37" s="106"/>
-      <c r="AA37" s="106"/>
-      <c r="AB37" s="106"/>
-      <c r="AC37" s="106"/>
-      <c r="AD37" s="106"/>
-      <c r="AE37" s="106"/>
-      <c r="AF37" s="106"/>
-      <c r="AG37" s="106"/>
-      <c r="AH37" s="106"/>
-      <c r="AI37" s="106"/>
-      <c r="AJ37" s="111"/>
-      <c r="AK37" s="112"/>
+      <c r="F37" s="89"/>
+      <c r="G37" s="102"/>
+      <c r="H37" s="102"/>
+      <c r="I37" s="102"/>
+      <c r="J37" s="102"/>
+      <c r="K37" s="102"/>
+      <c r="L37" s="102"/>
+      <c r="M37" s="102"/>
+      <c r="N37" s="102"/>
+      <c r="O37" s="102"/>
+      <c r="P37" s="102"/>
+      <c r="Q37" s="102"/>
+      <c r="R37" s="102"/>
+      <c r="S37" s="102"/>
+      <c r="T37" s="102"/>
+      <c r="U37" s="102"/>
+      <c r="V37" s="102"/>
+      <c r="W37" s="102"/>
+      <c r="X37" s="102"/>
+      <c r="Y37" s="102"/>
+      <c r="Z37" s="102"/>
+      <c r="AA37" s="102"/>
+      <c r="AB37" s="102"/>
+      <c r="AC37" s="102"/>
+      <c r="AD37" s="102"/>
+      <c r="AE37" s="102"/>
+      <c r="AF37" s="102"/>
+      <c r="AG37" s="102"/>
+      <c r="AH37" s="102"/>
+      <c r="AI37" s="102"/>
+      <c r="AJ37" s="107"/>
+      <c r="AK37" s="108"/>
       <c r="AN37" s="3"/>
       <c r="AO37" s="3"/>
       <c r="AP37" s="3"/>
@@ -13238,44 +13242,44 @@
     </row>
     <row r="38" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A38" s="37"/>
-      <c r="B38" s="170" t="s">
+      <c r="B38" s="154" t="s">
         <v>129</v>
       </c>
-      <c r="C38" s="171"/>
-      <c r="D38" s="92"/>
+      <c r="C38" s="155"/>
+      <c r="D38" s="88"/>
       <c r="E38" s="40"/>
-      <c r="F38" s="93"/>
-      <c r="G38" s="106"/>
-      <c r="H38" s="106"/>
-      <c r="I38" s="106"/>
-      <c r="J38" s="106"/>
-      <c r="K38" s="106"/>
-      <c r="L38" s="106"/>
-      <c r="M38" s="106"/>
-      <c r="N38" s="106"/>
-      <c r="O38" s="106"/>
-      <c r="P38" s="106"/>
-      <c r="Q38" s="106"/>
-      <c r="R38" s="106"/>
-      <c r="S38" s="106"/>
-      <c r="T38" s="106"/>
-      <c r="U38" s="106"/>
-      <c r="V38" s="106"/>
-      <c r="W38" s="106"/>
-      <c r="X38" s="106"/>
-      <c r="Y38" s="106"/>
-      <c r="Z38" s="106"/>
-      <c r="AA38" s="106"/>
-      <c r="AB38" s="106"/>
-      <c r="AC38" s="106"/>
-      <c r="AD38" s="106"/>
-      <c r="AE38" s="106"/>
-      <c r="AF38" s="106"/>
-      <c r="AG38" s="106"/>
-      <c r="AH38" s="106"/>
-      <c r="AI38" s="106"/>
-      <c r="AJ38" s="111"/>
-      <c r="AK38" s="112"/>
+      <c r="F38" s="89"/>
+      <c r="G38" s="102"/>
+      <c r="H38" s="102"/>
+      <c r="I38" s="102"/>
+      <c r="J38" s="102"/>
+      <c r="K38" s="102"/>
+      <c r="L38" s="102"/>
+      <c r="M38" s="102"/>
+      <c r="N38" s="102"/>
+      <c r="O38" s="102"/>
+      <c r="P38" s="102"/>
+      <c r="Q38" s="102"/>
+      <c r="R38" s="102"/>
+      <c r="S38" s="102"/>
+      <c r="T38" s="102"/>
+      <c r="U38" s="102"/>
+      <c r="V38" s="102"/>
+      <c r="W38" s="102"/>
+      <c r="X38" s="102"/>
+      <c r="Y38" s="102"/>
+      <c r="Z38" s="102"/>
+      <c r="AA38" s="102"/>
+      <c r="AB38" s="102"/>
+      <c r="AC38" s="102"/>
+      <c r="AD38" s="102"/>
+      <c r="AE38" s="102"/>
+      <c r="AF38" s="102"/>
+      <c r="AG38" s="102"/>
+      <c r="AH38" s="102"/>
+      <c r="AI38" s="102"/>
+      <c r="AJ38" s="107"/>
+      <c r="AK38" s="108"/>
       <c r="AN38" s="3"/>
       <c r="AO38" s="3"/>
       <c r="AP38" s="3"/>
@@ -13494,42 +13498,42 @@
     </row>
     <row r="39" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A39" s="37"/>
-      <c r="B39" s="170"/>
-      <c r="C39" s="171"/>
-      <c r="D39" s="92"/>
+      <c r="B39" s="154"/>
+      <c r="C39" s="155"/>
+      <c r="D39" s="88"/>
       <c r="E39" s="40"/>
-      <c r="F39" s="93"/>
-      <c r="G39" s="106"/>
-      <c r="H39" s="106"/>
-      <c r="I39" s="106"/>
-      <c r="J39" s="106"/>
-      <c r="K39" s="106"/>
-      <c r="L39" s="106"/>
-      <c r="M39" s="106"/>
-      <c r="N39" s="106"/>
-      <c r="O39" s="106"/>
-      <c r="P39" s="106"/>
-      <c r="Q39" s="106"/>
-      <c r="R39" s="106"/>
-      <c r="S39" s="106"/>
-      <c r="T39" s="106"/>
-      <c r="U39" s="106"/>
-      <c r="V39" s="106"/>
-      <c r="W39" s="106"/>
-      <c r="X39" s="106"/>
-      <c r="Y39" s="106"/>
-      <c r="Z39" s="106"/>
-      <c r="AA39" s="106"/>
-      <c r="AB39" s="106"/>
-      <c r="AC39" s="106"/>
-      <c r="AD39" s="106"/>
-      <c r="AE39" s="106"/>
-      <c r="AF39" s="106"/>
-      <c r="AG39" s="106"/>
-      <c r="AH39" s="106"/>
-      <c r="AI39" s="106"/>
-      <c r="AJ39" s="111"/>
-      <c r="AK39" s="112"/>
+      <c r="F39" s="89"/>
+      <c r="G39" s="102"/>
+      <c r="H39" s="102"/>
+      <c r="I39" s="102"/>
+      <c r="J39" s="102"/>
+      <c r="K39" s="102"/>
+      <c r="L39" s="102"/>
+      <c r="M39" s="102"/>
+      <c r="N39" s="102"/>
+      <c r="O39" s="102"/>
+      <c r="P39" s="102"/>
+      <c r="Q39" s="102"/>
+      <c r="R39" s="102"/>
+      <c r="S39" s="102"/>
+      <c r="T39" s="102"/>
+      <c r="U39" s="102"/>
+      <c r="V39" s="102"/>
+      <c r="W39" s="102"/>
+      <c r="X39" s="102"/>
+      <c r="Y39" s="102"/>
+      <c r="Z39" s="102"/>
+      <c r="AA39" s="102"/>
+      <c r="AB39" s="102"/>
+      <c r="AC39" s="102"/>
+      <c r="AD39" s="102"/>
+      <c r="AE39" s="102"/>
+      <c r="AF39" s="102"/>
+      <c r="AG39" s="102"/>
+      <c r="AH39" s="102"/>
+      <c r="AI39" s="102"/>
+      <c r="AJ39" s="107"/>
+      <c r="AK39" s="108"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
@@ -13748,46 +13752,46 @@
     </row>
     <row r="40" spans="1:254" s="2" customFormat="1" ht="42" customHeight="1" thickBot="1">
       <c r="A40" s="41"/>
-      <c r="B40" s="168" t="s">
+      <c r="B40" s="166" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="169"/>
+      <c r="C40" s="167"/>
       <c r="D40" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="E40" s="95"/>
+      <c r="E40" s="91"/>
       <c r="F40" s="43"/>
-      <c r="G40" s="113"/>
-      <c r="H40" s="113"/>
-      <c r="I40" s="113"/>
-      <c r="J40" s="113"/>
-      <c r="K40" s="113"/>
-      <c r="L40" s="113"/>
-      <c r="M40" s="113"/>
-      <c r="N40" s="113"/>
-      <c r="O40" s="113"/>
-      <c r="P40" s="113"/>
-      <c r="Q40" s="113"/>
-      <c r="R40" s="113"/>
-      <c r="S40" s="113"/>
-      <c r="T40" s="113"/>
-      <c r="U40" s="113"/>
-      <c r="V40" s="113"/>
-      <c r="W40" s="113"/>
-      <c r="X40" s="113"/>
-      <c r="Y40" s="113"/>
-      <c r="Z40" s="113"/>
-      <c r="AA40" s="113"/>
-      <c r="AB40" s="113"/>
-      <c r="AC40" s="113"/>
-      <c r="AD40" s="113"/>
-      <c r="AE40" s="113"/>
-      <c r="AF40" s="113"/>
-      <c r="AG40" s="113"/>
-      <c r="AH40" s="113"/>
-      <c r="AI40" s="113"/>
-      <c r="AJ40" s="114"/>
-      <c r="AK40" s="115"/>
+      <c r="G40" s="109"/>
+      <c r="H40" s="109"/>
+      <c r="I40" s="109"/>
+      <c r="J40" s="109"/>
+      <c r="K40" s="109"/>
+      <c r="L40" s="109"/>
+      <c r="M40" s="109"/>
+      <c r="N40" s="109"/>
+      <c r="O40" s="109"/>
+      <c r="P40" s="109"/>
+      <c r="Q40" s="109"/>
+      <c r="R40" s="109"/>
+      <c r="S40" s="109"/>
+      <c r="T40" s="109"/>
+      <c r="U40" s="109"/>
+      <c r="V40" s="109"/>
+      <c r="W40" s="109"/>
+      <c r="X40" s="109"/>
+      <c r="Y40" s="109"/>
+      <c r="Z40" s="109"/>
+      <c r="AA40" s="109"/>
+      <c r="AB40" s="109"/>
+      <c r="AC40" s="109"/>
+      <c r="AD40" s="109"/>
+      <c r="AE40" s="109"/>
+      <c r="AF40" s="109"/>
+      <c r="AG40" s="109"/>
+      <c r="AH40" s="109"/>
+      <c r="AI40" s="109"/>
+      <c r="AJ40" s="110"/>
+      <c r="AK40" s="111"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
@@ -14014,79 +14018,79 @@
       <c r="E41" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="F41" s="75"/>
-      <c r="G41" s="162"/>
-      <c r="H41" s="162"/>
-      <c r="I41" s="162"/>
-      <c r="J41" s="162"/>
-      <c r="K41" s="162"/>
-      <c r="L41" s="162"/>
-      <c r="M41" s="162"/>
-      <c r="N41" s="162"/>
-      <c r="O41" s="162"/>
-      <c r="P41" s="162"/>
-      <c r="Q41" s="162"/>
-      <c r="R41" s="162"/>
-      <c r="S41" s="162"/>
-      <c r="T41" s="162"/>
-      <c r="U41" s="162"/>
-      <c r="V41" s="162"/>
-      <c r="W41" s="162"/>
-      <c r="X41" s="162"/>
-      <c r="Y41" s="162"/>
-      <c r="Z41" s="162"/>
-      <c r="AA41" s="163"/>
-      <c r="AB41" s="163"/>
-      <c r="AC41" s="163"/>
-      <c r="AD41" s="163"/>
-      <c r="AE41" s="163"/>
-      <c r="AF41" s="163"/>
-      <c r="AG41" s="163"/>
-      <c r="AH41" s="163"/>
-      <c r="AI41" s="163"/>
-      <c r="AJ41" s="163"/>
-      <c r="AK41" s="164"/>
+      <c r="F41" s="71"/>
+      <c r="G41" s="176"/>
+      <c r="H41" s="176"/>
+      <c r="I41" s="176"/>
+      <c r="J41" s="176"/>
+      <c r="K41" s="176"/>
+      <c r="L41" s="176"/>
+      <c r="M41" s="176"/>
+      <c r="N41" s="176"/>
+      <c r="O41" s="176"/>
+      <c r="P41" s="176"/>
+      <c r="Q41" s="176"/>
+      <c r="R41" s="176"/>
+      <c r="S41" s="176"/>
+      <c r="T41" s="176"/>
+      <c r="U41" s="176"/>
+      <c r="V41" s="176"/>
+      <c r="W41" s="176"/>
+      <c r="X41" s="176"/>
+      <c r="Y41" s="176"/>
+      <c r="Z41" s="176"/>
+      <c r="AA41" s="177"/>
+      <c r="AB41" s="177"/>
+      <c r="AC41" s="177"/>
+      <c r="AD41" s="177"/>
+      <c r="AE41" s="177"/>
+      <c r="AF41" s="177"/>
+      <c r="AG41" s="177"/>
+      <c r="AH41" s="177"/>
+      <c r="AI41" s="177"/>
+      <c r="AJ41" s="177"/>
+      <c r="AK41" s="178"/>
     </row>
     <row r="42" spans="1:254" ht="23" customHeight="1">
       <c r="A42" s="45"/>
       <c r="B42" s="46"/>
-      <c r="C42" s="88"/>
-      <c r="D42" s="90"/>
+      <c r="C42" s="84"/>
+      <c r="D42" s="86"/>
       <c r="E42" s="58" t="s">
         <v>97</v>
       </c>
-      <c r="F42" s="77"/>
-      <c r="G42" s="165"/>
-      <c r="H42" s="165"/>
-      <c r="I42" s="165"/>
-      <c r="J42" s="165"/>
-      <c r="K42" s="165"/>
-      <c r="L42" s="165"/>
-      <c r="M42" s="165"/>
-      <c r="N42" s="165"/>
-      <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
-      <c r="Q42" s="167"/>
-      <c r="R42" s="167"/>
-      <c r="S42" s="167"/>
-      <c r="T42" s="167"/>
-      <c r="U42" s="167"/>
-      <c r="V42" s="167"/>
-      <c r="W42" s="167"/>
-      <c r="X42" s="167"/>
-      <c r="Y42" s="167"/>
-      <c r="Z42" s="167"/>
-      <c r="AA42" s="165"/>
-      <c r="AB42" s="165"/>
-      <c r="AC42" s="165"/>
-      <c r="AD42" s="165"/>
-      <c r="AE42" s="165"/>
-      <c r="AF42" s="165"/>
-      <c r="AG42" s="165"/>
-      <c r="AH42" s="165"/>
-      <c r="AI42" s="165"/>
-      <c r="AJ42" s="165"/>
-      <c r="AK42" s="166"/>
+      <c r="F42" s="73"/>
+      <c r="G42" s="179"/>
+      <c r="H42" s="179"/>
+      <c r="I42" s="179"/>
+      <c r="J42" s="179"/>
+      <c r="K42" s="179"/>
+      <c r="L42" s="179"/>
+      <c r="M42" s="179"/>
+      <c r="N42" s="179"/>
+      <c r="O42" s="179"/>
+      <c r="P42" s="179"/>
+      <c r="Q42" s="181"/>
+      <c r="R42" s="181"/>
+      <c r="S42" s="181"/>
+      <c r="T42" s="181"/>
+      <c r="U42" s="181"/>
+      <c r="V42" s="181"/>
+      <c r="W42" s="181"/>
+      <c r="X42" s="181"/>
+      <c r="Y42" s="181"/>
+      <c r="Z42" s="181"/>
+      <c r="AA42" s="179"/>
+      <c r="AB42" s="179"/>
+      <c r="AC42" s="179"/>
+      <c r="AD42" s="179"/>
+      <c r="AE42" s="179"/>
+      <c r="AF42" s="179"/>
+      <c r="AG42" s="179"/>
+      <c r="AH42" s="179"/>
+      <c r="AI42" s="179"/>
+      <c r="AJ42" s="179"/>
+      <c r="AK42" s="180"/>
     </row>
     <row r="43" spans="1:254" ht="23" customHeight="1" thickBot="1">
       <c r="A43" s="49"/>
@@ -14096,38 +14100,38 @@
       <c r="E43" s="60" t="s">
         <v>98</v>
       </c>
-      <c r="F43" s="82"/>
-      <c r="G43" s="159"/>
-      <c r="H43" s="159"/>
-      <c r="I43" s="159"/>
-      <c r="J43" s="159"/>
-      <c r="K43" s="159"/>
-      <c r="L43" s="159"/>
-      <c r="M43" s="159"/>
-      <c r="N43" s="159"/>
-      <c r="O43" s="159"/>
-      <c r="P43" s="159"/>
-      <c r="Q43" s="161"/>
-      <c r="R43" s="161"/>
-      <c r="S43" s="161"/>
-      <c r="T43" s="161"/>
-      <c r="U43" s="161"/>
-      <c r="V43" s="161"/>
-      <c r="W43" s="161"/>
-      <c r="X43" s="161"/>
-      <c r="Y43" s="161"/>
-      <c r="Z43" s="161"/>
-      <c r="AA43" s="159"/>
-      <c r="AB43" s="159"/>
-      <c r="AC43" s="159"/>
-      <c r="AD43" s="159"/>
-      <c r="AE43" s="159"/>
-      <c r="AF43" s="159"/>
-      <c r="AG43" s="159"/>
-      <c r="AH43" s="159"/>
-      <c r="AI43" s="159"/>
-      <c r="AJ43" s="159"/>
-      <c r="AK43" s="160"/>
+      <c r="F43" s="78"/>
+      <c r="G43" s="173"/>
+      <c r="H43" s="173"/>
+      <c r="I43" s="173"/>
+      <c r="J43" s="173"/>
+      <c r="K43" s="173"/>
+      <c r="L43" s="173"/>
+      <c r="M43" s="173"/>
+      <c r="N43" s="173"/>
+      <c r="O43" s="173"/>
+      <c r="P43" s="173"/>
+      <c r="Q43" s="175"/>
+      <c r="R43" s="175"/>
+      <c r="S43" s="175"/>
+      <c r="T43" s="175"/>
+      <c r="U43" s="175"/>
+      <c r="V43" s="175"/>
+      <c r="W43" s="175"/>
+      <c r="X43" s="175"/>
+      <c r="Y43" s="175"/>
+      <c r="Z43" s="175"/>
+      <c r="AA43" s="173"/>
+      <c r="AB43" s="173"/>
+      <c r="AC43" s="173"/>
+      <c r="AD43" s="173"/>
+      <c r="AE43" s="173"/>
+      <c r="AF43" s="173"/>
+      <c r="AG43" s="173"/>
+      <c r="AH43" s="173"/>
+      <c r="AI43" s="173"/>
+      <c r="AJ43" s="173"/>
+      <c r="AK43" s="174"/>
     </row>
     <row r="44" spans="1:254">
       <c r="A44" s="52"/>
@@ -14143,6 +14147,50 @@
     </row>
   </sheetData>
   <mergeCells count="60">
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:AK1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="T3:AK3"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="T4:Y4"/>
+    <mergeCell ref="AH4:AK4"/>
+    <mergeCell ref="T5:V7"/>
+    <mergeCell ref="W5:Y7"/>
+    <mergeCell ref="AH5:AK7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="Z4:AC4"/>
+    <mergeCell ref="AD4:AG4"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="F12:F21"/>
+    <mergeCell ref="F27:F35"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B24:C24"/>
@@ -14159,66 +14207,22 @@
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="G41:P41"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="F12:F21"/>
-    <mergeCell ref="F27:F35"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="W5:Y7"/>
-    <mergeCell ref="AH5:AK7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="Z4:AC4"/>
-    <mergeCell ref="AD4:AG4"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="F1:AK1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="T3:AK3"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="T4:Y4"/>
-    <mergeCell ref="AH4:AK4"/>
-    <mergeCell ref="T5:V7"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="G9:AK10">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>TEXT(G9,"aaa")="土"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>TEXT(G9,"aaa")="日"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:AK40">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>G$11="－"</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.23622047244094491" right="3.937007874015748E-2" top="0.55118110236220474" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageMargins left="0.43307086614173229" right="3.937007874015748E-2" top="0.15748031496062992" bottom="0" header="0.11811023622047244" footer="0.11811023622047244"/>
   <pageSetup paperSize="9" scale="54" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
@@ -14228,7 +14232,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:IT50"/>
+  <dimension ref="A1:IO50"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="27.83203125" customWidth="1"/>
@@ -14238,41 +14242,41 @@
     <col min="7" max="32" width="6.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:254" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A1" s="121" t="s">
+    <row r="1" spans="1:249" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A1" s="126" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="85"/>
-      <c r="F1" s="122" t="s">
+      <c r="B1" s="126"/>
+      <c r="C1" s="81"/>
+      <c r="F1" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
-      <c r="AC1" s="122"/>
-      <c r="AD1" s="122"/>
-      <c r="AE1" s="122"/>
-      <c r="AF1" s="122"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="127"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="127"/>
+      <c r="R1" s="127"/>
+      <c r="S1" s="127"/>
+      <c r="T1" s="127"/>
+      <c r="U1" s="127"/>
+      <c r="V1" s="127"/>
+      <c r="W1" s="127"/>
+      <c r="X1" s="127"/>
+      <c r="Y1" s="127"/>
+      <c r="Z1" s="127"/>
+      <c r="AA1" s="127"/>
+      <c r="AB1" s="127"/>
+      <c r="AC1" s="127"/>
+      <c r="AD1" s="127"/>
+      <c r="AE1" s="127"/>
+      <c r="AF1" s="127"/>
       <c r="AI1" s="3"/>
       <c r="AJ1" s="3"/>
       <c r="AK1" s="3"/>
@@ -14489,7 +14493,7 @@
       <c r="IN1" s="3"/>
       <c r="IO1" s="3"/>
     </row>
-    <row r="2" spans="1:254" s="2" customFormat="1" ht="15.65" customHeight="1" thickTop="1" thickBot="1">
+    <row r="2" spans="1:249" s="2" customFormat="1" ht="15.65" customHeight="1" thickTop="1" thickBot="1">
       <c r="A2" s="4"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -14737,48 +14741,48 @@
       <c r="IN2" s="3"/>
       <c r="IO2" s="3"/>
     </row>
-    <row r="3" spans="1:254" s="2" customFormat="1" ht="20" customHeight="1" thickBot="1">
-      <c r="A3" s="123" t="s">
+    <row r="3" spans="1:249" s="2" customFormat="1" ht="20" customHeight="1" thickBot="1">
+      <c r="A3" s="128" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="125"/>
-      <c r="E3" s="94"/>
+      <c r="B3" s="129"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="130"/>
+      <c r="E3" s="90"/>
       <c r="G3" s="51"/>
       <c r="H3" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="126" t="s">
+      <c r="K3" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="126"/>
-      <c r="M3" s="126" t="s">
+      <c r="L3" s="131"/>
+      <c r="M3" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="126"/>
-      <c r="O3" s="126"/>
-      <c r="P3" s="126" t="s">
+      <c r="N3" s="131"/>
+      <c r="O3" s="131"/>
+      <c r="P3" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="Q3" s="126"/>
-      <c r="R3" s="126"/>
+      <c r="Q3" s="131"/>
+      <c r="R3" s="131"/>
       <c r="S3" s="3"/>
-      <c r="T3" s="127" t="s">
+      <c r="T3" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="U3" s="128"/>
-      <c r="V3" s="128"/>
-      <c r="W3" s="128"/>
-      <c r="X3" s="128"/>
-      <c r="Y3" s="128"/>
-      <c r="Z3" s="128"/>
-      <c r="AA3" s="128"/>
-      <c r="AB3" s="128"/>
-      <c r="AC3" s="128"/>
-      <c r="AD3" s="128"/>
-      <c r="AE3" s="128"/>
-      <c r="AF3" s="129"/>
+      <c r="U3" s="133"/>
+      <c r="V3" s="133"/>
+      <c r="W3" s="133"/>
+      <c r="X3" s="133"/>
+      <c r="Y3" s="133"/>
+      <c r="Z3" s="133"/>
+      <c r="AA3" s="133"/>
+      <c r="AB3" s="133"/>
+      <c r="AC3" s="133"/>
+      <c r="AD3" s="133"/>
+      <c r="AE3" s="133"/>
+      <c r="AF3" s="134"/>
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
       <c r="AK3" s="3"/>
@@ -14995,7 +14999,7 @@
       <c r="IN3" s="3"/>
       <c r="IO3" s="3"/>
     </row>
-    <row r="4" spans="1:254" s="2" customFormat="1" ht="20" customHeight="1">
+    <row r="4" spans="1:249" s="2" customFormat="1" ht="20" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>52</v>
       </c>
@@ -15007,42 +15011,42 @@
       <c r="H4" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="126" t="s">
+      <c r="K4" s="131" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="126"/>
-      <c r="M4" s="132">
+      <c r="L4" s="131"/>
+      <c r="M4" s="156">
         <v>46113</v>
       </c>
-      <c r="N4" s="132"/>
-      <c r="O4" s="132"/>
-      <c r="P4" s="126" t="s">
+      <c r="N4" s="156"/>
+      <c r="O4" s="156"/>
+      <c r="P4" s="131" t="s">
         <v>50</v>
       </c>
-      <c r="Q4" s="126"/>
-      <c r="R4" s="126"/>
+      <c r="Q4" s="131"/>
+      <c r="R4" s="131"/>
       <c r="S4" s="3"/>
-      <c r="T4" s="133" t="s">
+      <c r="T4" s="141" t="s">
         <v>5</v>
       </c>
-      <c r="U4" s="134"/>
-      <c r="V4" s="134"/>
-      <c r="W4" s="135"/>
-      <c r="X4" s="133" t="s">
+      <c r="U4" s="142"/>
+      <c r="V4" s="142"/>
+      <c r="W4" s="143"/>
+      <c r="X4" s="141" t="s">
         <v>6</v>
       </c>
-      <c r="Y4" s="134"/>
-      <c r="Z4" s="135"/>
-      <c r="AA4" s="133" t="s">
+      <c r="Y4" s="142"/>
+      <c r="Z4" s="143"/>
+      <c r="AA4" s="141" t="s">
         <v>7</v>
       </c>
-      <c r="AB4" s="134"/>
-      <c r="AC4" s="135"/>
-      <c r="AD4" s="133" t="s">
+      <c r="AB4" s="142"/>
+      <c r="AC4" s="143"/>
+      <c r="AD4" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="AE4" s="134"/>
-      <c r="AF4" s="135"/>
+      <c r="AE4" s="142"/>
+      <c r="AF4" s="143"/>
       <c r="AI4" s="3"/>
       <c r="AJ4" s="3"/>
       <c r="AK4" s="3"/>
@@ -15259,7 +15263,7 @@
       <c r="IN4" s="3"/>
       <c r="IO4" s="3"/>
     </row>
-    <row r="5" spans="1:254" s="2" customFormat="1" ht="12" customHeight="1" thickBot="1">
+    <row r="5" spans="1:249" s="2" customFormat="1" ht="12" customHeight="1" thickBot="1">
       <c r="A5" s="10"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -15270,21 +15274,21 @@
         <v>23</v>
       </c>
       <c r="S5" s="3"/>
-      <c r="T5" s="183" t="s">
+      <c r="T5" s="135" t="s">
         <v>64</v>
       </c>
-      <c r="U5" s="184"/>
-      <c r="V5" s="184"/>
-      <c r="W5" s="185"/>
+      <c r="U5" s="136"/>
+      <c r="V5" s="136"/>
+      <c r="W5" s="137"/>
       <c r="X5" s="11"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="12"/>
       <c r="AA5" s="11"/>
       <c r="AB5" s="3"/>
       <c r="AC5" s="12"/>
-      <c r="AD5" s="146"/>
-      <c r="AE5" s="147"/>
-      <c r="AF5" s="148"/>
+      <c r="AD5" s="144"/>
+      <c r="AE5" s="145"/>
+      <c r="AF5" s="146"/>
       <c r="AI5" s="3"/>
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3"/>
@@ -15501,8 +15505,8 @@
       <c r="IN5" s="3"/>
       <c r="IO5" s="3"/>
     </row>
-    <row r="6" spans="1:254" s="2" customFormat="1" ht="18.75" customHeight="1" thickTop="1">
-      <c r="A6" s="100" t="s">
+    <row r="6" spans="1:249" s="2" customFormat="1" ht="18.75" customHeight="1" thickTop="1">
+      <c r="A6" s="96" t="s">
         <v>121</v>
       </c>
       <c r="B6" s="14"/>
@@ -15516,19 +15520,19 @@
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
-      <c r="T6" s="183"/>
-      <c r="U6" s="184"/>
-      <c r="V6" s="184"/>
-      <c r="W6" s="185"/>
+      <c r="T6" s="135"/>
+      <c r="U6" s="136"/>
+      <c r="V6" s="136"/>
+      <c r="W6" s="137"/>
       <c r="X6" s="11"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="12"/>
       <c r="AA6" s="11"/>
       <c r="AB6" s="3"/>
       <c r="AC6" s="12"/>
-      <c r="AD6" s="146"/>
-      <c r="AE6" s="147"/>
-      <c r="AF6" s="148"/>
+      <c r="AD6" s="144"/>
+      <c r="AE6" s="145"/>
+      <c r="AF6" s="146"/>
       <c r="AI6" s="3"/>
       <c r="AJ6" s="3"/>
       <c r="AK6" s="3"/>
@@ -15745,7 +15749,7 @@
       <c r="IN6" s="3"/>
       <c r="IO6" s="3"/>
     </row>
-    <row r="7" spans="1:254" s="2" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
+    <row r="7" spans="1:249" s="2" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="A7" s="17" t="s">
         <v>9</v>
       </c>
@@ -15760,20 +15764,20 @@
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
-      <c r="T7" s="186"/>
-      <c r="U7" s="187"/>
-      <c r="V7" s="187"/>
-      <c r="W7" s="188"/>
+      <c r="T7" s="138"/>
+      <c r="U7" s="139"/>
+      <c r="V7" s="139"/>
+      <c r="W7" s="140"/>
       <c r="X7" s="21"/>
       <c r="Y7" s="22"/>
       <c r="Z7" s="23"/>
       <c r="AA7" s="21"/>
       <c r="AB7" s="22"/>
       <c r="AC7" s="23"/>
-      <c r="AD7" s="149"/>
-      <c r="AE7" s="150"/>
-      <c r="AF7" s="151"/>
-      <c r="AG7" s="86"/>
+      <c r="AD7" s="147"/>
+      <c r="AE7" s="148"/>
+      <c r="AF7" s="149"/>
+      <c r="AG7" s="82"/>
       <c r="AI7" s="3"/>
       <c r="AJ7" s="3"/>
       <c r="AK7" s="3"/>
@@ -15990,7 +15994,7 @@
       <c r="IN7" s="3"/>
       <c r="IO7" s="3"/>
     </row>
-    <row r="8" spans="1:254" s="2" customFormat="1" ht="20" customHeight="1" thickTop="1" thickBot="1">
+    <row r="8" spans="1:249" s="2" customFormat="1" ht="20" customHeight="1" thickTop="1" thickBot="1">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -16020,10 +16024,10 @@
       <c r="AA8" s="24"/>
       <c r="AB8" s="24"/>
       <c r="AC8" s="24"/>
-      <c r="AD8" s="98"/>
-      <c r="AE8" s="98"/>
-      <c r="AF8" s="98"/>
-      <c r="AG8" s="87"/>
+      <c r="AD8" s="94"/>
+      <c r="AE8" s="94"/>
+      <c r="AF8" s="94"/>
+      <c r="AG8" s="83"/>
       <c r="AI8" s="3"/>
       <c r="AJ8" s="3"/>
       <c r="AK8" s="3"/>
@@ -16240,7 +16244,7 @@
       <c r="IN8" s="3"/>
       <c r="IO8" s="3"/>
     </row>
-    <row r="9" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
+    <row r="9" spans="1:249" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A9" s="25"/>
       <c r="B9" s="26" t="s">
         <v>10</v>
@@ -16253,58 +16257,58 @@
         <v>48</v>
       </c>
       <c r="F9" s="28"/>
-      <c r="G9" s="97" t="s">
+      <c r="G9" s="93" t="s">
         <v>65</v>
       </c>
-      <c r="H9" s="97" t="s">
+      <c r="H9" s="93" t="s">
         <v>66</v>
       </c>
-      <c r="I9" s="97" t="s">
+      <c r="I9" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="J9" s="97" t="s">
+      <c r="J9" s="93" t="s">
         <v>68</v>
       </c>
-      <c r="K9" s="97" t="s">
+      <c r="K9" s="93" t="s">
         <v>69</v>
       </c>
-      <c r="L9" s="97" t="s">
+      <c r="L9" s="93" t="s">
         <v>70</v>
       </c>
-      <c r="M9" s="97" t="s">
+      <c r="M9" s="93" t="s">
         <v>71</v>
       </c>
-      <c r="N9" s="97" t="s">
+      <c r="N9" s="93" t="s">
         <v>72</v>
       </c>
-      <c r="O9" s="97" t="s">
+      <c r="O9" s="93" t="s">
         <v>73</v>
       </c>
-      <c r="P9" s="97" t="s">
+      <c r="P9" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="Q9" s="97" t="s">
+      <c r="Q9" s="93" t="s">
         <v>75</v>
       </c>
-      <c r="R9" s="97" t="s">
+      <c r="R9" s="93" t="s">
         <v>76</v>
       </c>
-      <c r="S9" s="176" t="s">
+      <c r="S9" s="170" t="s">
         <v>78</v>
       </c>
-      <c r="T9" s="177"/>
-      <c r="U9" s="177"/>
-      <c r="V9" s="177"/>
-      <c r="W9" s="177"/>
-      <c r="X9" s="177"/>
-      <c r="Y9" s="177"/>
-      <c r="Z9" s="177"/>
-      <c r="AA9" s="177"/>
-      <c r="AB9" s="177"/>
-      <c r="AC9" s="177"/>
-      <c r="AD9" s="177"/>
-      <c r="AE9" s="177"/>
-      <c r="AF9" s="178"/>
+      <c r="T9" s="171"/>
+      <c r="U9" s="171"/>
+      <c r="V9" s="171"/>
+      <c r="W9" s="171"/>
+      <c r="X9" s="171"/>
+      <c r="Y9" s="171"/>
+      <c r="Z9" s="171"/>
+      <c r="AA9" s="171"/>
+      <c r="AB9" s="171"/>
+      <c r="AC9" s="171"/>
+      <c r="AD9" s="171"/>
+      <c r="AE9" s="171"/>
+      <c r="AF9" s="172"/>
       <c r="AI9" s="3"/>
       <c r="AJ9" s="3"/>
       <c r="AK9" s="3"/>
@@ -16521,10 +16525,10 @@
       <c r="IN9" s="3"/>
       <c r="IO9" s="3"/>
     </row>
-    <row r="10" spans="1:254" s="2" customFormat="1" ht="23" hidden="1" customHeight="1">
+    <row r="10" spans="1:249" s="2" customFormat="1" ht="23" hidden="1" customHeight="1">
       <c r="A10" s="29"/>
-      <c r="B10" s="152"/>
-      <c r="C10" s="153"/>
+      <c r="B10" s="150"/>
+      <c r="C10" s="151"/>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="31"/>
@@ -16848,15 +16852,15 @@
       <c r="IN10" s="3"/>
       <c r="IO10" s="3"/>
     </row>
-    <row r="11" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
+    <row r="11" spans="1:249" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A11" s="37"/>
-      <c r="B11" s="154" t="s">
+      <c r="B11" s="157" t="s">
         <v>105</v>
       </c>
-      <c r="C11" s="155"/>
-      <c r="D11" s="92"/>
+      <c r="C11" s="158"/>
+      <c r="D11" s="88"/>
       <c r="E11" s="40"/>
-      <c r="F11" s="93"/>
+      <c r="F11" s="89"/>
       <c r="G11" s="69"/>
       <c r="H11" s="69"/>
       <c r="I11" s="69"/>
@@ -16869,25 +16873,25 @@
       <c r="P11" s="69"/>
       <c r="Q11" s="69"/>
       <c r="R11" s="69"/>
-      <c r="S11" s="191"/>
-      <c r="T11" s="192"/>
-      <c r="U11" s="192"/>
-      <c r="V11" s="192"/>
-      <c r="W11" s="192"/>
-      <c r="X11" s="192"/>
-      <c r="Y11" s="192"/>
-      <c r="Z11" s="192"/>
-      <c r="AA11" s="192"/>
-      <c r="AB11" s="192"/>
-      <c r="AC11" s="192"/>
-      <c r="AD11" s="192"/>
-      <c r="AE11" s="192"/>
-      <c r="AF11" s="193"/>
-      <c r="AG11" s="69"/>
-      <c r="AH11" s="69"/>
-      <c r="AI11" s="69"/>
-      <c r="AJ11" s="70"/>
-      <c r="AK11" s="71"/>
+      <c r="S11" s="125"/>
+      <c r="T11" s="123"/>
+      <c r="U11" s="123"/>
+      <c r="V11" s="123"/>
+      <c r="W11" s="123"/>
+      <c r="X11" s="123"/>
+      <c r="Y11" s="123"/>
+      <c r="Z11" s="123"/>
+      <c r="AA11" s="123"/>
+      <c r="AB11" s="123"/>
+      <c r="AC11" s="123"/>
+      <c r="AD11" s="123"/>
+      <c r="AE11" s="123"/>
+      <c r="AF11" s="124"/>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
@@ -17098,25 +17102,22 @@
       <c r="IM11" s="3"/>
       <c r="IN11" s="3"/>
       <c r="IO11" s="3"/>
-      <c r="IP11" s="3"/>
-      <c r="IQ11" s="3"/>
-      <c r="IR11" s="3"/>
-      <c r="IS11" s="3"/>
-      <c r="IT11" s="3"/>
     </row>
-    <row r="12" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
+    <row r="12" spans="1:249" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A12" s="37">
         <v>1</v>
       </c>
-      <c r="B12" s="170" t="s">
+      <c r="B12" s="154" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="171"/>
-      <c r="D12" s="92" t="s">
+      <c r="C12" s="155"/>
+      <c r="D12" s="88" t="s">
         <v>108</v>
       </c>
       <c r="E12" s="40"/>
-      <c r="F12" s="36"/>
+      <c r="F12" s="116" t="s">
+        <v>136</v>
+      </c>
       <c r="G12" s="69"/>
       <c r="H12" s="69"/>
       <c r="I12" s="69"/>
@@ -17129,25 +17130,25 @@
       <c r="P12" s="69"/>
       <c r="Q12" s="69"/>
       <c r="R12" s="69"/>
-      <c r="S12" s="172"/>
-      <c r="T12" s="173"/>
-      <c r="U12" s="173"/>
-      <c r="V12" s="173"/>
-      <c r="W12" s="173"/>
-      <c r="X12" s="173"/>
-      <c r="Y12" s="173"/>
-      <c r="Z12" s="173"/>
-      <c r="AA12" s="173"/>
-      <c r="AB12" s="173"/>
-      <c r="AC12" s="173"/>
-      <c r="AD12" s="173"/>
-      <c r="AE12" s="173"/>
-      <c r="AF12" s="174"/>
-      <c r="AG12" s="69"/>
-      <c r="AH12" s="69"/>
-      <c r="AI12" s="69"/>
-      <c r="AJ12" s="70"/>
-      <c r="AK12" s="71"/>
+      <c r="S12" s="122"/>
+      <c r="T12" s="120"/>
+      <c r="U12" s="120"/>
+      <c r="V12" s="120"/>
+      <c r="W12" s="120"/>
+      <c r="X12" s="120"/>
+      <c r="Y12" s="120"/>
+      <c r="Z12" s="120"/>
+      <c r="AA12" s="120"/>
+      <c r="AB12" s="120"/>
+      <c r="AC12" s="120"/>
+      <c r="AD12" s="120"/>
+      <c r="AE12" s="120"/>
+      <c r="AF12" s="121"/>
+      <c r="AI12" s="3"/>
+      <c r="AJ12" s="3"/>
+      <c r="AK12" s="3"/>
+      <c r="AL12" s="3"/>
+      <c r="AM12" s="3"/>
       <c r="AN12" s="3"/>
       <c r="AO12" s="3"/>
       <c r="AP12" s="3"/>
@@ -17358,25 +17359,20 @@
       <c r="IM12" s="3"/>
       <c r="IN12" s="3"/>
       <c r="IO12" s="3"/>
-      <c r="IP12" s="3"/>
-      <c r="IQ12" s="3"/>
-      <c r="IR12" s="3"/>
-      <c r="IS12" s="3"/>
-      <c r="IT12" s="3"/>
     </row>
-    <row r="13" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
+    <row r="13" spans="1:249" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A13" s="37">
         <v>2</v>
       </c>
-      <c r="B13" s="170" t="s">
+      <c r="B13" s="154" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="171"/>
-      <c r="D13" s="92" t="s">
+      <c r="C13" s="155"/>
+      <c r="D13" s="88" t="s">
         <v>107</v>
       </c>
       <c r="E13" s="40"/>
-      <c r="F13" s="36"/>
+      <c r="F13" s="117"/>
       <c r="G13" s="69"/>
       <c r="H13" s="69"/>
       <c r="I13" s="69"/>
@@ -17389,25 +17385,25 @@
       <c r="P13" s="69"/>
       <c r="Q13" s="69"/>
       <c r="R13" s="69"/>
-      <c r="S13" s="172"/>
-      <c r="T13" s="173"/>
-      <c r="U13" s="173"/>
-      <c r="V13" s="173"/>
-      <c r="W13" s="173"/>
-      <c r="X13" s="173"/>
-      <c r="Y13" s="173"/>
-      <c r="Z13" s="173"/>
-      <c r="AA13" s="173"/>
-      <c r="AB13" s="173"/>
-      <c r="AC13" s="173"/>
-      <c r="AD13" s="173"/>
-      <c r="AE13" s="173"/>
-      <c r="AF13" s="174"/>
-      <c r="AG13" s="69"/>
-      <c r="AH13" s="69"/>
-      <c r="AI13" s="69"/>
-      <c r="AJ13" s="70"/>
-      <c r="AK13" s="71"/>
+      <c r="S13" s="122"/>
+      <c r="T13" s="120"/>
+      <c r="U13" s="120"/>
+      <c r="V13" s="120"/>
+      <c r="W13" s="120"/>
+      <c r="X13" s="120"/>
+      <c r="Y13" s="120"/>
+      <c r="Z13" s="120"/>
+      <c r="AA13" s="120"/>
+      <c r="AB13" s="120"/>
+      <c r="AC13" s="120"/>
+      <c r="AD13" s="120"/>
+      <c r="AE13" s="120"/>
+      <c r="AF13" s="121"/>
+      <c r="AI13" s="3"/>
+      <c r="AJ13" s="3"/>
+      <c r="AK13" s="3"/>
+      <c r="AL13" s="3"/>
+      <c r="AM13" s="3"/>
       <c r="AN13" s="3"/>
       <c r="AO13" s="3"/>
       <c r="AP13" s="3"/>
@@ -17618,25 +17614,20 @@
       <c r="IM13" s="3"/>
       <c r="IN13" s="3"/>
       <c r="IO13" s="3"/>
-      <c r="IP13" s="3"/>
-      <c r="IQ13" s="3"/>
-      <c r="IR13" s="3"/>
-      <c r="IS13" s="3"/>
-      <c r="IT13" s="3"/>
     </row>
-    <row r="14" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
+    <row r="14" spans="1:249" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A14" s="37">
         <v>3</v>
       </c>
-      <c r="B14" s="170" t="s">
+      <c r="B14" s="154" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="171"/>
-      <c r="D14" s="92" t="s">
+      <c r="C14" s="155"/>
+      <c r="D14" s="88" t="s">
         <v>107</v>
       </c>
       <c r="E14" s="40"/>
-      <c r="F14" s="36"/>
+      <c r="F14" s="117"/>
       <c r="G14" s="69"/>
       <c r="H14" s="69"/>
       <c r="I14" s="69"/>
@@ -17649,25 +17640,25 @@
       <c r="P14" s="69"/>
       <c r="Q14" s="69"/>
       <c r="R14" s="69"/>
-      <c r="S14" s="172"/>
-      <c r="T14" s="173"/>
-      <c r="U14" s="173"/>
-      <c r="V14" s="173"/>
-      <c r="W14" s="173"/>
-      <c r="X14" s="173"/>
-      <c r="Y14" s="173"/>
-      <c r="Z14" s="173"/>
-      <c r="AA14" s="173"/>
-      <c r="AB14" s="173"/>
-      <c r="AC14" s="173"/>
-      <c r="AD14" s="173"/>
-      <c r="AE14" s="173"/>
-      <c r="AF14" s="174"/>
-      <c r="AG14" s="69"/>
-      <c r="AH14" s="69"/>
-      <c r="AI14" s="69"/>
-      <c r="AJ14" s="70"/>
-      <c r="AK14" s="71"/>
+      <c r="S14" s="122"/>
+      <c r="T14" s="120"/>
+      <c r="U14" s="120"/>
+      <c r="V14" s="120"/>
+      <c r="W14" s="120"/>
+      <c r="X14" s="120"/>
+      <c r="Y14" s="120"/>
+      <c r="Z14" s="120"/>
+      <c r="AA14" s="120"/>
+      <c r="AB14" s="120"/>
+      <c r="AC14" s="120"/>
+      <c r="AD14" s="120"/>
+      <c r="AE14" s="120"/>
+      <c r="AF14" s="121"/>
+      <c r="AI14" s="3"/>
+      <c r="AJ14" s="3"/>
+      <c r="AK14" s="3"/>
+      <c r="AL14" s="3"/>
+      <c r="AM14" s="3"/>
       <c r="AN14" s="3"/>
       <c r="AO14" s="3"/>
       <c r="AP14" s="3"/>
@@ -17878,25 +17869,20 @@
       <c r="IM14" s="3"/>
       <c r="IN14" s="3"/>
       <c r="IO14" s="3"/>
-      <c r="IP14" s="3"/>
-      <c r="IQ14" s="3"/>
-      <c r="IR14" s="3"/>
-      <c r="IS14" s="3"/>
-      <c r="IT14" s="3"/>
     </row>
-    <row r="15" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
+    <row r="15" spans="1:249" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A15" s="37">
         <v>4</v>
       </c>
-      <c r="B15" s="170" t="s">
+      <c r="B15" s="154" t="s">
         <v>82</v>
       </c>
-      <c r="C15" s="171"/>
-      <c r="D15" s="92" t="s">
+      <c r="C15" s="155"/>
+      <c r="D15" s="88" t="s">
         <v>108</v>
       </c>
       <c r="E15" s="40"/>
-      <c r="F15" s="36"/>
+      <c r="F15" s="117"/>
       <c r="G15" s="69"/>
       <c r="H15" s="69"/>
       <c r="I15" s="69"/>
@@ -17909,25 +17895,25 @@
       <c r="P15" s="69"/>
       <c r="Q15" s="69"/>
       <c r="R15" s="69"/>
-      <c r="S15" s="172"/>
-      <c r="T15" s="173"/>
-      <c r="U15" s="173"/>
-      <c r="V15" s="173"/>
-      <c r="W15" s="173"/>
-      <c r="X15" s="173"/>
-      <c r="Y15" s="173"/>
-      <c r="Z15" s="173"/>
-      <c r="AA15" s="173"/>
-      <c r="AB15" s="173"/>
-      <c r="AC15" s="173"/>
-      <c r="AD15" s="173"/>
-      <c r="AE15" s="173"/>
-      <c r="AF15" s="174"/>
-      <c r="AG15" s="69"/>
-      <c r="AH15" s="69"/>
-      <c r="AI15" s="69"/>
-      <c r="AJ15" s="70"/>
-      <c r="AK15" s="71"/>
+      <c r="S15" s="122"/>
+      <c r="T15" s="120"/>
+      <c r="U15" s="120"/>
+      <c r="V15" s="120"/>
+      <c r="W15" s="120"/>
+      <c r="X15" s="120"/>
+      <c r="Y15" s="120"/>
+      <c r="Z15" s="120"/>
+      <c r="AA15" s="120"/>
+      <c r="AB15" s="120"/>
+      <c r="AC15" s="120"/>
+      <c r="AD15" s="120"/>
+      <c r="AE15" s="120"/>
+      <c r="AF15" s="121"/>
+      <c r="AI15" s="3"/>
+      <c r="AJ15" s="3"/>
+      <c r="AK15" s="3"/>
+      <c r="AL15" s="3"/>
+      <c r="AM15" s="3"/>
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
       <c r="AP15" s="3"/>
@@ -18138,25 +18124,20 @@
       <c r="IM15" s="3"/>
       <c r="IN15" s="3"/>
       <c r="IO15" s="3"/>
-      <c r="IP15" s="3"/>
-      <c r="IQ15" s="3"/>
-      <c r="IR15" s="3"/>
-      <c r="IS15" s="3"/>
-      <c r="IT15" s="3"/>
     </row>
-    <row r="16" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
+    <row r="16" spans="1:249" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A16" s="37">
         <v>5</v>
       </c>
-      <c r="B16" s="170" t="s">
+      <c r="B16" s="154" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="171"/>
-      <c r="D16" s="92" t="s">
+      <c r="C16" s="155"/>
+      <c r="D16" s="88" t="s">
         <v>108</v>
       </c>
       <c r="E16" s="40"/>
-      <c r="F16" s="36"/>
+      <c r="F16" s="117"/>
       <c r="G16" s="69"/>
       <c r="H16" s="69"/>
       <c r="I16" s="69"/>
@@ -18169,25 +18150,25 @@
       <c r="P16" s="69"/>
       <c r="Q16" s="69"/>
       <c r="R16" s="69"/>
-      <c r="S16" s="172"/>
-      <c r="T16" s="173"/>
-      <c r="U16" s="173"/>
-      <c r="V16" s="173"/>
-      <c r="W16" s="173"/>
-      <c r="X16" s="173"/>
-      <c r="Y16" s="173"/>
-      <c r="Z16" s="173"/>
-      <c r="AA16" s="173"/>
-      <c r="AB16" s="173"/>
-      <c r="AC16" s="173"/>
-      <c r="AD16" s="173"/>
-      <c r="AE16" s="173"/>
-      <c r="AF16" s="174"/>
-      <c r="AG16" s="69"/>
-      <c r="AH16" s="69"/>
-      <c r="AI16" s="69"/>
-      <c r="AJ16" s="70"/>
-      <c r="AK16" s="71"/>
+      <c r="S16" s="122"/>
+      <c r="T16" s="120"/>
+      <c r="U16" s="120"/>
+      <c r="V16" s="120"/>
+      <c r="W16" s="120"/>
+      <c r="X16" s="120"/>
+      <c r="Y16" s="120"/>
+      <c r="Z16" s="120"/>
+      <c r="AA16" s="120"/>
+      <c r="AB16" s="120"/>
+      <c r="AC16" s="120"/>
+      <c r="AD16" s="120"/>
+      <c r="AE16" s="120"/>
+      <c r="AF16" s="121"/>
+      <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
@@ -18398,25 +18379,20 @@
       <c r="IM16" s="3"/>
       <c r="IN16" s="3"/>
       <c r="IO16" s="3"/>
-      <c r="IP16" s="3"/>
-      <c r="IQ16" s="3"/>
-      <c r="IR16" s="3"/>
-      <c r="IS16" s="3"/>
-      <c r="IT16" s="3"/>
     </row>
-    <row r="17" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
+    <row r="17" spans="1:249" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A17" s="37">
         <v>6</v>
       </c>
-      <c r="B17" s="170" t="s">
+      <c r="B17" s="154" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="171"/>
-      <c r="D17" s="92" t="s">
+      <c r="C17" s="155"/>
+      <c r="D17" s="88" t="s">
         <v>108</v>
       </c>
       <c r="E17" s="40"/>
-      <c r="F17" s="36"/>
+      <c r="F17" s="117"/>
       <c r="G17" s="69"/>
       <c r="H17" s="69"/>
       <c r="I17" s="69"/>
@@ -18429,25 +18405,25 @@
       <c r="P17" s="69"/>
       <c r="Q17" s="69"/>
       <c r="R17" s="69"/>
-      <c r="S17" s="172"/>
-      <c r="T17" s="173"/>
-      <c r="U17" s="173"/>
-      <c r="V17" s="173"/>
-      <c r="W17" s="173"/>
-      <c r="X17" s="173"/>
-      <c r="Y17" s="173"/>
-      <c r="Z17" s="173"/>
-      <c r="AA17" s="173"/>
-      <c r="AB17" s="173"/>
-      <c r="AC17" s="173"/>
-      <c r="AD17" s="173"/>
-      <c r="AE17" s="173"/>
-      <c r="AF17" s="174"/>
-      <c r="AG17" s="69"/>
-      <c r="AH17" s="69"/>
-      <c r="AI17" s="69"/>
-      <c r="AJ17" s="70"/>
-      <c r="AK17" s="71"/>
+      <c r="S17" s="122"/>
+      <c r="T17" s="120"/>
+      <c r="U17" s="120"/>
+      <c r="V17" s="120"/>
+      <c r="W17" s="120"/>
+      <c r="X17" s="120"/>
+      <c r="Y17" s="120"/>
+      <c r="Z17" s="120"/>
+      <c r="AA17" s="120"/>
+      <c r="AB17" s="120"/>
+      <c r="AC17" s="120"/>
+      <c r="AD17" s="120"/>
+      <c r="AE17" s="120"/>
+      <c r="AF17" s="121"/>
+      <c r="AI17" s="3"/>
+      <c r="AJ17" s="3"/>
+      <c r="AK17" s="3"/>
+      <c r="AL17" s="3"/>
+      <c r="AM17" s="3"/>
       <c r="AN17" s="3"/>
       <c r="AO17" s="3"/>
       <c r="AP17" s="3"/>
@@ -18658,25 +18634,20 @@
       <c r="IM17" s="3"/>
       <c r="IN17" s="3"/>
       <c r="IO17" s="3"/>
-      <c r="IP17" s="3"/>
-      <c r="IQ17" s="3"/>
-      <c r="IR17" s="3"/>
-      <c r="IS17" s="3"/>
-      <c r="IT17" s="3"/>
     </row>
-    <row r="18" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
+    <row r="18" spans="1:249" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A18" s="37">
         <v>7</v>
       </c>
-      <c r="B18" s="170" t="s">
+      <c r="B18" s="154" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="171"/>
-      <c r="D18" s="92" t="s">
+      <c r="C18" s="155"/>
+      <c r="D18" s="88" t="s">
         <v>108</v>
       </c>
       <c r="E18" s="40"/>
-      <c r="F18" s="36"/>
+      <c r="F18" s="117"/>
       <c r="G18" s="69"/>
       <c r="H18" s="69"/>
       <c r="I18" s="69"/>
@@ -18689,25 +18660,25 @@
       <c r="P18" s="69"/>
       <c r="Q18" s="69"/>
       <c r="R18" s="69"/>
-      <c r="S18" s="172"/>
-      <c r="T18" s="173"/>
-      <c r="U18" s="173"/>
-      <c r="V18" s="173"/>
-      <c r="W18" s="173"/>
-      <c r="X18" s="173"/>
-      <c r="Y18" s="173"/>
-      <c r="Z18" s="173"/>
-      <c r="AA18" s="173"/>
-      <c r="AB18" s="173"/>
-      <c r="AC18" s="173"/>
-      <c r="AD18" s="173"/>
-      <c r="AE18" s="173"/>
-      <c r="AF18" s="174"/>
-      <c r="AG18" s="69"/>
-      <c r="AH18" s="69"/>
-      <c r="AI18" s="69"/>
-      <c r="AJ18" s="70"/>
-      <c r="AK18" s="71"/>
+      <c r="S18" s="122"/>
+      <c r="T18" s="120"/>
+      <c r="U18" s="120"/>
+      <c r="V18" s="120"/>
+      <c r="W18" s="120"/>
+      <c r="X18" s="120"/>
+      <c r="Y18" s="120"/>
+      <c r="Z18" s="120"/>
+      <c r="AA18" s="120"/>
+      <c r="AB18" s="120"/>
+      <c r="AC18" s="120"/>
+      <c r="AD18" s="120"/>
+      <c r="AE18" s="120"/>
+      <c r="AF18" s="121"/>
+      <c r="AI18" s="3"/>
+      <c r="AJ18" s="3"/>
+      <c r="AK18" s="3"/>
+      <c r="AL18" s="3"/>
+      <c r="AM18" s="3"/>
       <c r="AN18" s="3"/>
       <c r="AO18" s="3"/>
       <c r="AP18" s="3"/>
@@ -18918,25 +18889,20 @@
       <c r="IM18" s="3"/>
       <c r="IN18" s="3"/>
       <c r="IO18" s="3"/>
-      <c r="IP18" s="3"/>
-      <c r="IQ18" s="3"/>
-      <c r="IR18" s="3"/>
-      <c r="IS18" s="3"/>
-      <c r="IT18" s="3"/>
     </row>
-    <row r="19" spans="1:254" s="2" customFormat="1" ht="21.65" customHeight="1">
+    <row r="19" spans="1:249" s="2" customFormat="1" ht="21.65" customHeight="1">
       <c r="A19" s="37">
         <v>8</v>
       </c>
-      <c r="B19" s="170" t="s">
+      <c r="B19" s="154" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="171"/>
-      <c r="D19" s="92" t="s">
+      <c r="C19" s="155"/>
+      <c r="D19" s="88" t="s">
         <v>108</v>
       </c>
       <c r="E19" s="40"/>
-      <c r="F19" s="36"/>
+      <c r="F19" s="118"/>
       <c r="G19" s="69"/>
       <c r="H19" s="69"/>
       <c r="I19" s="69"/>
@@ -18949,25 +18915,25 @@
       <c r="P19" s="69"/>
       <c r="Q19" s="69"/>
       <c r="R19" s="69"/>
-      <c r="S19" s="172"/>
-      <c r="T19" s="173"/>
-      <c r="U19" s="173"/>
-      <c r="V19" s="173"/>
-      <c r="W19" s="173"/>
-      <c r="X19" s="173"/>
-      <c r="Y19" s="173"/>
-      <c r="Z19" s="173"/>
-      <c r="AA19" s="173"/>
-      <c r="AB19" s="173"/>
-      <c r="AC19" s="173"/>
-      <c r="AD19" s="173"/>
-      <c r="AE19" s="173"/>
-      <c r="AF19" s="174"/>
-      <c r="AG19" s="69"/>
-      <c r="AH19" s="69"/>
-      <c r="AI19" s="69"/>
-      <c r="AJ19" s="70"/>
-      <c r="AK19" s="71"/>
+      <c r="S19" s="122"/>
+      <c r="T19" s="120"/>
+      <c r="U19" s="120"/>
+      <c r="V19" s="120"/>
+      <c r="W19" s="120"/>
+      <c r="X19" s="120"/>
+      <c r="Y19" s="120"/>
+      <c r="Z19" s="120"/>
+      <c r="AA19" s="120"/>
+      <c r="AB19" s="120"/>
+      <c r="AC19" s="120"/>
+      <c r="AD19" s="120"/>
+      <c r="AE19" s="120"/>
+      <c r="AF19" s="121"/>
+      <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
@@ -19178,21 +19144,16 @@
       <c r="IM19" s="3"/>
       <c r="IN19" s="3"/>
       <c r="IO19" s="3"/>
-      <c r="IP19" s="3"/>
-      <c r="IQ19" s="3"/>
-      <c r="IR19" s="3"/>
-      <c r="IS19" s="3"/>
-      <c r="IT19" s="3"/>
     </row>
-    <row r="20" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
+    <row r="20" spans="1:249" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A20" s="34"/>
-      <c r="B20" s="189" t="s">
+      <c r="B20" s="152" t="s">
         <v>120</v>
       </c>
-      <c r="C20" s="190"/>
+      <c r="C20" s="153"/>
       <c r="D20" s="35"/>
       <c r="E20" s="35"/>
-      <c r="F20" s="36"/>
+      <c r="F20" s="89"/>
       <c r="G20" s="68"/>
       <c r="H20" s="68"/>
       <c r="I20" s="68"/>
@@ -19205,20 +19166,22 @@
       <c r="P20" s="68"/>
       <c r="Q20" s="68"/>
       <c r="R20" s="68"/>
-      <c r="S20" s="172"/>
-      <c r="T20" s="173"/>
-      <c r="U20" s="173"/>
-      <c r="V20" s="173"/>
-      <c r="W20" s="173"/>
-      <c r="X20" s="173"/>
-      <c r="Y20" s="173"/>
-      <c r="Z20" s="173"/>
-      <c r="AA20" s="173"/>
-      <c r="AB20" s="173"/>
-      <c r="AC20" s="173"/>
-      <c r="AD20" s="173"/>
-      <c r="AE20" s="173"/>
-      <c r="AF20" s="174"/>
+      <c r="S20" s="122"/>
+      <c r="T20" s="120"/>
+      <c r="U20" s="120"/>
+      <c r="V20" s="120"/>
+      <c r="W20" s="120"/>
+      <c r="X20" s="120"/>
+      <c r="Y20" s="120"/>
+      <c r="Z20" s="120"/>
+      <c r="AA20" s="120"/>
+      <c r="AB20" s="120"/>
+      <c r="AC20" s="120"/>
+      <c r="AD20" s="120"/>
+      <c r="AE20" s="120"/>
+      <c r="AF20" s="121"/>
+      <c r="AG20" s="3"/>
+      <c r="AH20" s="3"/>
       <c r="AI20" s="3"/>
       <c r="AJ20" s="3"/>
       <c r="AK20" s="3"/>
@@ -19429,25 +19392,22 @@
       <c r="IH20" s="3"/>
       <c r="II20" s="3"/>
       <c r="IJ20" s="3"/>
-      <c r="IK20" s="3"/>
-      <c r="IL20" s="3"/>
-      <c r="IM20" s="3"/>
-      <c r="IN20" s="3"/>
-      <c r="IO20" s="3"/>
     </row>
-    <row r="21" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
+    <row r="21" spans="1:249" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A21" s="37">
         <v>1</v>
       </c>
-      <c r="B21" s="117" t="s">
+      <c r="B21" s="161" t="s">
         <v>87</v>
       </c>
-      <c r="C21" s="118"/>
-      <c r="D21" s="92"/>
-      <c r="E21" s="92" t="s">
+      <c r="C21" s="162"/>
+      <c r="D21" s="88"/>
+      <c r="E21" s="88" t="s">
         <v>42</v>
       </c>
-      <c r="F21" s="36"/>
+      <c r="F21" s="119" t="s">
+        <v>137</v>
+      </c>
       <c r="G21" s="69"/>
       <c r="H21" s="69"/>
       <c r="I21" s="69"/>
@@ -19460,20 +19420,20 @@
       <c r="P21" s="69"/>
       <c r="Q21" s="69"/>
       <c r="R21" s="69"/>
-      <c r="S21" s="172"/>
-      <c r="T21" s="173"/>
-      <c r="U21" s="173"/>
-      <c r="V21" s="173"/>
-      <c r="W21" s="173"/>
-      <c r="X21" s="173"/>
-      <c r="Y21" s="173"/>
-      <c r="Z21" s="173"/>
-      <c r="AA21" s="173"/>
-      <c r="AB21" s="173"/>
-      <c r="AC21" s="173"/>
-      <c r="AD21" s="173"/>
-      <c r="AE21" s="173"/>
-      <c r="AF21" s="174"/>
+      <c r="S21" s="122"/>
+      <c r="T21" s="120"/>
+      <c r="U21" s="120"/>
+      <c r="V21" s="120"/>
+      <c r="W21" s="120"/>
+      <c r="X21" s="120"/>
+      <c r="Y21" s="120"/>
+      <c r="Z21" s="120"/>
+      <c r="AA21" s="120"/>
+      <c r="AB21" s="120"/>
+      <c r="AC21" s="120"/>
+      <c r="AD21" s="120"/>
+      <c r="AE21" s="120"/>
+      <c r="AF21" s="121"/>
       <c r="AI21" s="3"/>
       <c r="AJ21" s="3"/>
       <c r="AK21" s="3"/>
@@ -19690,19 +19650,19 @@
       <c r="IN21" s="3"/>
       <c r="IO21" s="3"/>
     </row>
-    <row r="22" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
+    <row r="22" spans="1:249" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A22" s="37">
         <v>2</v>
       </c>
-      <c r="B22" s="117" t="s">
+      <c r="B22" s="161" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="118"/>
-      <c r="D22" s="92"/>
-      <c r="E22" s="92" t="s">
+      <c r="C22" s="162"/>
+      <c r="D22" s="88"/>
+      <c r="E22" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="F22" s="36"/>
+      <c r="F22" s="117"/>
       <c r="G22" s="69"/>
       <c r="H22" s="69"/>
       <c r="I22" s="69"/>
@@ -19715,20 +19675,20 @@
       <c r="P22" s="69"/>
       <c r="Q22" s="69"/>
       <c r="R22" s="69"/>
-      <c r="S22" s="172"/>
-      <c r="T22" s="173"/>
-      <c r="U22" s="173"/>
-      <c r="V22" s="173"/>
-      <c r="W22" s="173"/>
-      <c r="X22" s="173"/>
-      <c r="Y22" s="173"/>
-      <c r="Z22" s="173"/>
-      <c r="AA22" s="173"/>
-      <c r="AB22" s="173"/>
-      <c r="AC22" s="173"/>
-      <c r="AD22" s="173"/>
-      <c r="AE22" s="173"/>
-      <c r="AF22" s="174"/>
+      <c r="S22" s="122"/>
+      <c r="T22" s="120"/>
+      <c r="U22" s="120"/>
+      <c r="V22" s="120"/>
+      <c r="W22" s="120"/>
+      <c r="X22" s="120"/>
+      <c r="Y22" s="120"/>
+      <c r="Z22" s="120"/>
+      <c r="AA22" s="120"/>
+      <c r="AB22" s="120"/>
+      <c r="AC22" s="120"/>
+      <c r="AD22" s="120"/>
+      <c r="AE22" s="120"/>
+      <c r="AF22" s="121"/>
       <c r="AI22" s="3"/>
       <c r="AJ22" s="3"/>
       <c r="AK22" s="3"/>
@@ -19945,21 +19905,21 @@
       <c r="IN22" s="3"/>
       <c r="IO22" s="3"/>
     </row>
-    <row r="23" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A23" s="101" t="s">
+    <row r="23" spans="1:249" s="2" customFormat="1" ht="23" customHeight="1">
+      <c r="A23" s="97" t="s">
         <v>111</v>
       </c>
-      <c r="B23" s="181" t="s">
+      <c r="B23" s="159" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="182"/>
-      <c r="D23" s="92" t="s">
+      <c r="C23" s="160"/>
+      <c r="D23" s="88" t="s">
         <v>110</v>
       </c>
-      <c r="E23" s="92" t="s">
+      <c r="E23" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="F23" s="36"/>
+      <c r="F23" s="117"/>
       <c r="G23" s="69"/>
       <c r="H23" s="69"/>
       <c r="I23" s="69"/>
@@ -19972,20 +19932,20 @@
       <c r="P23" s="69"/>
       <c r="Q23" s="69"/>
       <c r="R23" s="69"/>
-      <c r="S23" s="172"/>
-      <c r="T23" s="173"/>
-      <c r="U23" s="173"/>
-      <c r="V23" s="173"/>
-      <c r="W23" s="173"/>
-      <c r="X23" s="173"/>
-      <c r="Y23" s="173"/>
-      <c r="Z23" s="173"/>
-      <c r="AA23" s="173"/>
-      <c r="AB23" s="173"/>
-      <c r="AC23" s="173"/>
-      <c r="AD23" s="173"/>
-      <c r="AE23" s="173"/>
-      <c r="AF23" s="174"/>
+      <c r="S23" s="122"/>
+      <c r="T23" s="120"/>
+      <c r="U23" s="120"/>
+      <c r="V23" s="120"/>
+      <c r="W23" s="120"/>
+      <c r="X23" s="120"/>
+      <c r="Y23" s="120"/>
+      <c r="Z23" s="120"/>
+      <c r="AA23" s="120"/>
+      <c r="AB23" s="120"/>
+      <c r="AC23" s="120"/>
+      <c r="AD23" s="120"/>
+      <c r="AE23" s="120"/>
+      <c r="AF23" s="121"/>
       <c r="AI23" s="3"/>
       <c r="AJ23" s="3"/>
       <c r="AK23" s="3"/>
@@ -20202,21 +20162,21 @@
       <c r="IN23" s="3"/>
       <c r="IO23" s="3"/>
     </row>
-    <row r="24" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
-      <c r="A24" s="101" t="s">
+    <row r="24" spans="1:249" s="2" customFormat="1" ht="23" customHeight="1">
+      <c r="A24" s="97" t="s">
         <v>112</v>
       </c>
-      <c r="B24" s="117" t="s">
+      <c r="B24" s="161" t="s">
         <v>113</v>
       </c>
-      <c r="C24" s="118"/>
-      <c r="D24" s="92" t="s">
+      <c r="C24" s="162"/>
+      <c r="D24" s="88" t="s">
         <v>110</v>
       </c>
-      <c r="E24" s="92" t="s">
+      <c r="E24" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="F24" s="36"/>
+      <c r="F24" s="117"/>
       <c r="G24" s="69"/>
       <c r="H24" s="69"/>
       <c r="I24" s="69"/>
@@ -20229,20 +20189,20 @@
       <c r="P24" s="69"/>
       <c r="Q24" s="69"/>
       <c r="R24" s="69"/>
-      <c r="S24" s="172"/>
-      <c r="T24" s="173"/>
-      <c r="U24" s="173"/>
-      <c r="V24" s="173"/>
-      <c r="W24" s="173"/>
-      <c r="X24" s="173"/>
-      <c r="Y24" s="173"/>
-      <c r="Z24" s="173"/>
-      <c r="AA24" s="173"/>
-      <c r="AB24" s="173"/>
-      <c r="AC24" s="173"/>
-      <c r="AD24" s="173"/>
-      <c r="AE24" s="173"/>
-      <c r="AF24" s="174"/>
+      <c r="S24" s="122"/>
+      <c r="T24" s="120"/>
+      <c r="U24" s="120"/>
+      <c r="V24" s="120"/>
+      <c r="W24" s="120"/>
+      <c r="X24" s="120"/>
+      <c r="Y24" s="120"/>
+      <c r="Z24" s="120"/>
+      <c r="AA24" s="120"/>
+      <c r="AB24" s="120"/>
+      <c r="AC24" s="120"/>
+      <c r="AD24" s="120"/>
+      <c r="AE24" s="120"/>
+      <c r="AF24" s="121"/>
       <c r="AI24" s="3"/>
       <c r="AJ24" s="3"/>
       <c r="AK24" s="3"/>
@@ -20459,19 +20419,19 @@
       <c r="IN24" s="3"/>
       <c r="IO24" s="3"/>
     </row>
-    <row r="25" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
+    <row r="25" spans="1:249" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A25" s="37">
         <v>4</v>
       </c>
-      <c r="B25" s="117" t="s">
+      <c r="B25" s="161" t="s">
         <v>89</v>
       </c>
-      <c r="C25" s="118"/>
-      <c r="D25" s="92"/>
-      <c r="E25" s="92" t="s">
+      <c r="C25" s="162"/>
+      <c r="D25" s="88"/>
+      <c r="E25" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="F25" s="36"/>
+      <c r="F25" s="117"/>
       <c r="G25" s="69"/>
       <c r="H25" s="69"/>
       <c r="I25" s="69"/>
@@ -20484,20 +20444,20 @@
       <c r="P25" s="69"/>
       <c r="Q25" s="69"/>
       <c r="R25" s="69"/>
-      <c r="S25" s="172"/>
-      <c r="T25" s="173"/>
-      <c r="U25" s="173"/>
-      <c r="V25" s="173"/>
-      <c r="W25" s="173"/>
-      <c r="X25" s="173"/>
-      <c r="Y25" s="173"/>
-      <c r="Z25" s="173"/>
-      <c r="AA25" s="173"/>
-      <c r="AB25" s="173"/>
-      <c r="AC25" s="173"/>
-      <c r="AD25" s="173"/>
-      <c r="AE25" s="173"/>
-      <c r="AF25" s="174"/>
+      <c r="S25" s="122"/>
+      <c r="T25" s="120"/>
+      <c r="U25" s="120"/>
+      <c r="V25" s="120"/>
+      <c r="W25" s="120"/>
+      <c r="X25" s="120"/>
+      <c r="Y25" s="120"/>
+      <c r="Z25" s="120"/>
+      <c r="AA25" s="120"/>
+      <c r="AB25" s="120"/>
+      <c r="AC25" s="120"/>
+      <c r="AD25" s="120"/>
+      <c r="AE25" s="120"/>
+      <c r="AF25" s="121"/>
       <c r="AI25" s="3"/>
       <c r="AJ25" s="3"/>
       <c r="AK25" s="3"/>
@@ -20714,19 +20674,19 @@
       <c r="IN25" s="3"/>
       <c r="IO25" s="3"/>
     </row>
-    <row r="26" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
+    <row r="26" spans="1:249" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A26" s="37">
         <v>5</v>
       </c>
-      <c r="B26" s="117" t="s">
+      <c r="B26" s="161" t="s">
         <v>114</v>
       </c>
-      <c r="C26" s="118"/>
-      <c r="D26" s="92"/>
-      <c r="E26" s="92" t="s">
+      <c r="C26" s="162"/>
+      <c r="D26" s="88"/>
+      <c r="E26" s="88" t="s">
         <v>41</v>
       </c>
-      <c r="F26" s="36"/>
+      <c r="F26" s="117"/>
       <c r="G26" s="69"/>
       <c r="H26" s="69"/>
       <c r="I26" s="69"/>
@@ -20739,20 +20699,20 @@
       <c r="P26" s="69"/>
       <c r="Q26" s="69"/>
       <c r="R26" s="69"/>
-      <c r="S26" s="172"/>
-      <c r="T26" s="173"/>
-      <c r="U26" s="173"/>
-      <c r="V26" s="173"/>
-      <c r="W26" s="173"/>
-      <c r="X26" s="173"/>
-      <c r="Y26" s="173"/>
-      <c r="Z26" s="173"/>
-      <c r="AA26" s="173"/>
-      <c r="AB26" s="173"/>
-      <c r="AC26" s="173"/>
-      <c r="AD26" s="173"/>
-      <c r="AE26" s="173"/>
-      <c r="AF26" s="174"/>
+      <c r="S26" s="122"/>
+      <c r="T26" s="120"/>
+      <c r="U26" s="120"/>
+      <c r="V26" s="120"/>
+      <c r="W26" s="120"/>
+      <c r="X26" s="120"/>
+      <c r="Y26" s="120"/>
+      <c r="Z26" s="120"/>
+      <c r="AA26" s="120"/>
+      <c r="AB26" s="120"/>
+      <c r="AC26" s="120"/>
+      <c r="AD26" s="120"/>
+      <c r="AE26" s="120"/>
+      <c r="AF26" s="121"/>
       <c r="AI26" s="3"/>
       <c r="AJ26" s="3"/>
       <c r="AK26" s="3"/>
@@ -20969,19 +20929,19 @@
       <c r="IN26" s="3"/>
       <c r="IO26" s="3"/>
     </row>
-    <row r="27" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
+    <row r="27" spans="1:249" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A27" s="37">
         <v>6</v>
       </c>
-      <c r="B27" s="117" t="s">
+      <c r="B27" s="161" t="s">
         <v>116</v>
       </c>
-      <c r="C27" s="118"/>
-      <c r="D27" s="92"/>
-      <c r="E27" s="92" t="s">
+      <c r="C27" s="162"/>
+      <c r="D27" s="88"/>
+      <c r="E27" s="88" t="s">
         <v>41</v>
       </c>
-      <c r="F27" s="36"/>
+      <c r="F27" s="117"/>
       <c r="G27" s="69"/>
       <c r="H27" s="69"/>
       <c r="I27" s="69"/>
@@ -20994,20 +20954,20 @@
       <c r="P27" s="69"/>
       <c r="Q27" s="69"/>
       <c r="R27" s="69"/>
-      <c r="S27" s="172"/>
-      <c r="T27" s="173"/>
-      <c r="U27" s="173"/>
-      <c r="V27" s="173"/>
-      <c r="W27" s="173"/>
-      <c r="X27" s="173"/>
-      <c r="Y27" s="173"/>
-      <c r="Z27" s="173"/>
-      <c r="AA27" s="173"/>
-      <c r="AB27" s="173"/>
-      <c r="AC27" s="173"/>
-      <c r="AD27" s="173"/>
-      <c r="AE27" s="173"/>
-      <c r="AF27" s="174"/>
+      <c r="S27" s="122"/>
+      <c r="T27" s="120"/>
+      <c r="U27" s="120"/>
+      <c r="V27" s="120"/>
+      <c r="W27" s="120"/>
+      <c r="X27" s="120"/>
+      <c r="Y27" s="120"/>
+      <c r="Z27" s="120"/>
+      <c r="AA27" s="120"/>
+      <c r="AB27" s="120"/>
+      <c r="AC27" s="120"/>
+      <c r="AD27" s="120"/>
+      <c r="AE27" s="120"/>
+      <c r="AF27" s="121"/>
       <c r="AI27" s="3"/>
       <c r="AJ27" s="3"/>
       <c r="AK27" s="3"/>
@@ -21224,19 +21184,19 @@
       <c r="IN27" s="3"/>
       <c r="IO27" s="3"/>
     </row>
-    <row r="28" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
+    <row r="28" spans="1:249" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A28" s="37">
         <v>7</v>
       </c>
-      <c r="B28" s="117" t="s">
+      <c r="B28" s="161" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="118"/>
-      <c r="D28" s="92"/>
-      <c r="E28" s="92" t="s">
+      <c r="C28" s="162"/>
+      <c r="D28" s="88"/>
+      <c r="E28" s="88" t="s">
         <v>40</v>
       </c>
-      <c r="F28" s="36"/>
+      <c r="F28" s="118"/>
       <c r="G28" s="69"/>
       <c r="H28" s="69"/>
       <c r="I28" s="69"/>
@@ -21249,20 +21209,20 @@
       <c r="P28" s="69"/>
       <c r="Q28" s="69"/>
       <c r="R28" s="69"/>
-      <c r="S28" s="172"/>
-      <c r="T28" s="173"/>
-      <c r="U28" s="173"/>
-      <c r="V28" s="173"/>
-      <c r="W28" s="173"/>
-      <c r="X28" s="173"/>
-      <c r="Y28" s="173"/>
-      <c r="Z28" s="173"/>
-      <c r="AA28" s="173"/>
-      <c r="AB28" s="173"/>
-      <c r="AC28" s="173"/>
-      <c r="AD28" s="173"/>
-      <c r="AE28" s="173"/>
-      <c r="AF28" s="174"/>
+      <c r="S28" s="122"/>
+      <c r="T28" s="120"/>
+      <c r="U28" s="120"/>
+      <c r="V28" s="120"/>
+      <c r="W28" s="120"/>
+      <c r="X28" s="120"/>
+      <c r="Y28" s="120"/>
+      <c r="Z28" s="120"/>
+      <c r="AA28" s="120"/>
+      <c r="AB28" s="120"/>
+      <c r="AC28" s="120"/>
+      <c r="AD28" s="120"/>
+      <c r="AE28" s="120"/>
+      <c r="AF28" s="121"/>
       <c r="AI28" s="3"/>
       <c r="AJ28" s="3"/>
       <c r="AK28" s="3"/>
@@ -21479,15 +21439,15 @@
       <c r="IN28" s="3"/>
       <c r="IO28" s="3"/>
     </row>
-    <row r="29" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
+    <row r="29" spans="1:249" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A29" s="37"/>
-      <c r="B29" s="117"/>
-      <c r="C29" s="118"/>
-      <c r="D29" s="92"/>
-      <c r="E29" s="92" t="s">
+      <c r="B29" s="161"/>
+      <c r="C29" s="162"/>
+      <c r="D29" s="88"/>
+      <c r="E29" s="88" t="s">
         <v>40</v>
       </c>
-      <c r="F29" s="36"/>
+      <c r="F29" s="89"/>
       <c r="G29" s="69"/>
       <c r="H29" s="69"/>
       <c r="I29" s="69"/>
@@ -21500,20 +21460,20 @@
       <c r="P29" s="69"/>
       <c r="Q29" s="69"/>
       <c r="R29" s="69"/>
-      <c r="S29" s="172"/>
-      <c r="T29" s="173"/>
-      <c r="U29" s="173"/>
-      <c r="V29" s="173"/>
-      <c r="W29" s="173"/>
-      <c r="X29" s="173"/>
-      <c r="Y29" s="173"/>
-      <c r="Z29" s="173"/>
-      <c r="AA29" s="173"/>
-      <c r="AB29" s="173"/>
-      <c r="AC29" s="173"/>
-      <c r="AD29" s="173"/>
-      <c r="AE29" s="173"/>
-      <c r="AF29" s="174"/>
+      <c r="S29" s="122"/>
+      <c r="T29" s="120"/>
+      <c r="U29" s="120"/>
+      <c r="V29" s="120"/>
+      <c r="W29" s="120"/>
+      <c r="X29" s="120"/>
+      <c r="Y29" s="120"/>
+      <c r="Z29" s="120"/>
+      <c r="AA29" s="120"/>
+      <c r="AB29" s="120"/>
+      <c r="AC29" s="120"/>
+      <c r="AD29" s="120"/>
+      <c r="AE29" s="120"/>
+      <c r="AF29" s="121"/>
       <c r="AI29" s="3"/>
       <c r="AJ29" s="3"/>
       <c r="AK29" s="3"/>
@@ -21730,15 +21690,15 @@
       <c r="IN29" s="3"/>
       <c r="IO29" s="3"/>
     </row>
-    <row r="30" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
+    <row r="30" spans="1:249" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A30" s="37"/>
-      <c r="B30" s="154" t="s">
+      <c r="B30" s="157" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="155"/>
-      <c r="D30" s="92"/>
-      <c r="E30" s="92"/>
-      <c r="F30" s="36"/>
+      <c r="C30" s="158"/>
+      <c r="D30" s="88"/>
+      <c r="E30" s="88"/>
+      <c r="F30" s="89"/>
       <c r="G30" s="69"/>
       <c r="H30" s="69"/>
       <c r="I30" s="69"/>
@@ -21751,20 +21711,20 @@
       <c r="P30" s="69"/>
       <c r="Q30" s="69"/>
       <c r="R30" s="69"/>
-      <c r="S30" s="172"/>
-      <c r="T30" s="173"/>
-      <c r="U30" s="173"/>
-      <c r="V30" s="173"/>
-      <c r="W30" s="173"/>
-      <c r="X30" s="173"/>
-      <c r="Y30" s="173"/>
-      <c r="Z30" s="173"/>
-      <c r="AA30" s="173"/>
-      <c r="AB30" s="173"/>
-      <c r="AC30" s="173"/>
-      <c r="AD30" s="173"/>
-      <c r="AE30" s="173"/>
-      <c r="AF30" s="174"/>
+      <c r="S30" s="122"/>
+      <c r="T30" s="120"/>
+      <c r="U30" s="120"/>
+      <c r="V30" s="120"/>
+      <c r="W30" s="120"/>
+      <c r="X30" s="120"/>
+      <c r="Y30" s="120"/>
+      <c r="Z30" s="120"/>
+      <c r="AA30" s="120"/>
+      <c r="AB30" s="120"/>
+      <c r="AC30" s="120"/>
+      <c r="AD30" s="120"/>
+      <c r="AE30" s="120"/>
+      <c r="AF30" s="121"/>
       <c r="AI30" s="3"/>
       <c r="AJ30" s="3"/>
       <c r="AK30" s="3"/>
@@ -21981,17 +21941,19 @@
       <c r="IN30" s="3"/>
       <c r="IO30" s="3"/>
     </row>
-    <row r="31" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
+    <row r="31" spans="1:249" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A31" s="37"/>
-      <c r="B31" s="117" t="s">
+      <c r="B31" s="161" t="s">
         <v>92</v>
       </c>
-      <c r="C31" s="118"/>
-      <c r="D31" s="158" t="s">
+      <c r="C31" s="162"/>
+      <c r="D31" s="116" t="s">
         <v>117</v>
       </c>
-      <c r="E31" s="92"/>
-      <c r="F31" s="36"/>
+      <c r="E31" s="88"/>
+      <c r="F31" s="119" t="s">
+        <v>138</v>
+      </c>
       <c r="G31" s="69"/>
       <c r="H31" s="69"/>
       <c r="I31" s="69"/>
@@ -22004,20 +21966,20 @@
       <c r="P31" s="69"/>
       <c r="Q31" s="69"/>
       <c r="R31" s="69"/>
-      <c r="S31" s="172"/>
-      <c r="T31" s="173"/>
-      <c r="U31" s="173"/>
-      <c r="V31" s="173"/>
-      <c r="W31" s="173"/>
-      <c r="X31" s="173"/>
-      <c r="Y31" s="173"/>
-      <c r="Z31" s="173"/>
-      <c r="AA31" s="173"/>
-      <c r="AB31" s="173"/>
-      <c r="AC31" s="173"/>
-      <c r="AD31" s="173"/>
-      <c r="AE31" s="173"/>
-      <c r="AF31" s="174"/>
+      <c r="S31" s="122"/>
+      <c r="T31" s="120"/>
+      <c r="U31" s="120"/>
+      <c r="V31" s="120"/>
+      <c r="W31" s="120"/>
+      <c r="X31" s="120"/>
+      <c r="Y31" s="120"/>
+      <c r="Z31" s="120"/>
+      <c r="AA31" s="120"/>
+      <c r="AB31" s="120"/>
+      <c r="AC31" s="120"/>
+      <c r="AD31" s="120"/>
+      <c r="AE31" s="120"/>
+      <c r="AF31" s="121"/>
       <c r="AI31" s="3"/>
       <c r="AJ31" s="3"/>
       <c r="AK31" s="3"/>
@@ -22234,17 +22196,17 @@
       <c r="IN31" s="3"/>
       <c r="IO31" s="3"/>
     </row>
-    <row r="32" spans="1:254" s="2" customFormat="1" ht="23" customHeight="1">
+    <row r="32" spans="1:249" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A32" s="37"/>
-      <c r="B32" s="117" t="s">
+      <c r="B32" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C32" s="118"/>
-      <c r="D32" s="119"/>
-      <c r="E32" s="92" t="s">
+      <c r="C32" s="162"/>
+      <c r="D32" s="117"/>
+      <c r="E32" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="F32" s="36"/>
+      <c r="F32" s="117"/>
       <c r="G32" s="68"/>
       <c r="H32" s="68"/>
       <c r="I32" s="68"/>
@@ -22257,20 +22219,20 @@
       <c r="P32" s="68"/>
       <c r="Q32" s="68"/>
       <c r="R32" s="68"/>
-      <c r="S32" s="172"/>
-      <c r="T32" s="173"/>
-      <c r="U32" s="173"/>
-      <c r="V32" s="173"/>
-      <c r="W32" s="173"/>
-      <c r="X32" s="173"/>
-      <c r="Y32" s="173"/>
-      <c r="Z32" s="173"/>
-      <c r="AA32" s="173"/>
-      <c r="AB32" s="173"/>
-      <c r="AC32" s="173"/>
-      <c r="AD32" s="173"/>
-      <c r="AE32" s="173"/>
-      <c r="AF32" s="174"/>
+      <c r="S32" s="122"/>
+      <c r="T32" s="120"/>
+      <c r="U32" s="120"/>
+      <c r="V32" s="120"/>
+      <c r="W32" s="120"/>
+      <c r="X32" s="120"/>
+      <c r="Y32" s="120"/>
+      <c r="Z32" s="120"/>
+      <c r="AA32" s="120"/>
+      <c r="AB32" s="120"/>
+      <c r="AC32" s="120"/>
+      <c r="AD32" s="120"/>
+      <c r="AE32" s="120"/>
+      <c r="AF32" s="121"/>
       <c r="AI32" s="3"/>
       <c r="AJ32" s="3"/>
       <c r="AK32" s="3"/>
@@ -22489,13 +22451,13 @@
     </row>
     <row r="33" spans="1:249" s="2" customFormat="1" ht="23" customHeight="1">
       <c r="A33" s="37"/>
-      <c r="B33" s="117" t="s">
+      <c r="B33" s="161" t="s">
         <v>94</v>
       </c>
-      <c r="C33" s="118"/>
-      <c r="D33" s="120"/>
-      <c r="E33" s="92"/>
-      <c r="F33" s="36"/>
+      <c r="C33" s="162"/>
+      <c r="D33" s="118"/>
+      <c r="E33" s="88"/>
+      <c r="F33" s="118"/>
       <c r="G33" s="68"/>
       <c r="H33" s="68"/>
       <c r="I33" s="68"/>
@@ -22508,20 +22470,20 @@
       <c r="P33" s="68"/>
       <c r="Q33" s="68"/>
       <c r="R33" s="68"/>
-      <c r="S33" s="172"/>
-      <c r="T33" s="173"/>
-      <c r="U33" s="173"/>
-      <c r="V33" s="173"/>
-      <c r="W33" s="173"/>
-      <c r="X33" s="173"/>
-      <c r="Y33" s="173"/>
-      <c r="Z33" s="173"/>
-      <c r="AA33" s="173"/>
-      <c r="AB33" s="173"/>
-      <c r="AC33" s="173"/>
-      <c r="AD33" s="173"/>
-      <c r="AE33" s="173"/>
-      <c r="AF33" s="174"/>
+      <c r="S33" s="122"/>
+      <c r="T33" s="120"/>
+      <c r="U33" s="120"/>
+      <c r="V33" s="120"/>
+      <c r="W33" s="120"/>
+      <c r="X33" s="120"/>
+      <c r="Y33" s="120"/>
+      <c r="Z33" s="120"/>
+      <c r="AA33" s="120"/>
+      <c r="AB33" s="120"/>
+      <c r="AC33" s="120"/>
+      <c r="AD33" s="120"/>
+      <c r="AE33" s="120"/>
+      <c r="AF33" s="121"/>
       <c r="AI33" s="3"/>
       <c r="AJ33" s="3"/>
       <c r="AK33" s="3"/>
@@ -22740,10 +22702,10 @@
     </row>
     <row r="34" spans="1:249" s="2" customFormat="1" ht="28.25" customHeight="1">
       <c r="A34" s="38"/>
-      <c r="B34" s="154" t="s">
+      <c r="B34" s="157" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="155"/>
+      <c r="C34" s="158"/>
       <c r="D34" s="35"/>
       <c r="E34" s="35"/>
       <c r="F34" s="39"/>
@@ -22759,20 +22721,20 @@
       <c r="P34" s="68"/>
       <c r="Q34" s="68"/>
       <c r="R34" s="68"/>
-      <c r="S34" s="172"/>
-      <c r="T34" s="173"/>
-      <c r="U34" s="173"/>
-      <c r="V34" s="173"/>
-      <c r="W34" s="173"/>
-      <c r="X34" s="173"/>
-      <c r="Y34" s="173"/>
-      <c r="Z34" s="173"/>
-      <c r="AA34" s="173"/>
-      <c r="AB34" s="173"/>
-      <c r="AC34" s="173"/>
-      <c r="AD34" s="173"/>
-      <c r="AE34" s="173"/>
-      <c r="AF34" s="174"/>
+      <c r="S34" s="122"/>
+      <c r="T34" s="120"/>
+      <c r="U34" s="120"/>
+      <c r="V34" s="120"/>
+      <c r="W34" s="120"/>
+      <c r="X34" s="120"/>
+      <c r="Y34" s="120"/>
+      <c r="Z34" s="120"/>
+      <c r="AA34" s="120"/>
+      <c r="AB34" s="120"/>
+      <c r="AC34" s="120"/>
+      <c r="AD34" s="120"/>
+      <c r="AE34" s="120"/>
+      <c r="AF34" s="121"/>
       <c r="AI34" s="3"/>
       <c r="AJ34" s="3"/>
       <c r="AK34" s="3"/>
@@ -22993,15 +22955,15 @@
       <c r="A35" s="37">
         <v>1</v>
       </c>
-      <c r="B35" s="156" t="s">
+      <c r="B35" s="163" t="s">
         <v>104</v>
       </c>
-      <c r="C35" s="157"/>
-      <c r="D35" s="96"/>
-      <c r="E35" s="92" t="s">
+      <c r="C35" s="164"/>
+      <c r="D35" s="92"/>
+      <c r="E35" s="88" t="s">
         <v>61</v>
       </c>
-      <c r="F35" s="158" t="s">
+      <c r="F35" s="116" t="s">
         <v>95</v>
       </c>
       <c r="G35" s="69"/>
@@ -23016,20 +22978,20 @@
       <c r="P35" s="69"/>
       <c r="Q35" s="69"/>
       <c r="R35" s="69"/>
-      <c r="S35" s="172"/>
-      <c r="T35" s="173"/>
-      <c r="U35" s="173"/>
-      <c r="V35" s="173"/>
-      <c r="W35" s="173"/>
-      <c r="X35" s="173"/>
-      <c r="Y35" s="173"/>
-      <c r="Z35" s="173"/>
-      <c r="AA35" s="173"/>
-      <c r="AB35" s="173"/>
-      <c r="AC35" s="173"/>
-      <c r="AD35" s="173"/>
-      <c r="AE35" s="173"/>
-      <c r="AF35" s="174"/>
+      <c r="S35" s="122"/>
+      <c r="T35" s="120"/>
+      <c r="U35" s="120"/>
+      <c r="V35" s="120"/>
+      <c r="W35" s="120"/>
+      <c r="X35" s="120"/>
+      <c r="Y35" s="120"/>
+      <c r="Z35" s="120"/>
+      <c r="AA35" s="120"/>
+      <c r="AB35" s="120"/>
+      <c r="AC35" s="120"/>
+      <c r="AD35" s="120"/>
+      <c r="AE35" s="120"/>
+      <c r="AF35" s="121"/>
       <c r="AI35" s="3"/>
       <c r="AJ35" s="3"/>
       <c r="AK35" s="3"/>
@@ -23250,13 +23212,13 @@
       <c r="A36" s="37">
         <v>2</v>
       </c>
-      <c r="B36" s="117"/>
-      <c r="C36" s="118"/>
-      <c r="D36" s="96"/>
-      <c r="E36" s="92" t="s">
+      <c r="B36" s="161"/>
+      <c r="C36" s="162"/>
+      <c r="D36" s="92"/>
+      <c r="E36" s="88" t="s">
         <v>62</v>
       </c>
-      <c r="F36" s="119"/>
+      <c r="F36" s="117"/>
       <c r="G36" s="68"/>
       <c r="H36" s="68"/>
       <c r="I36" s="68"/>
@@ -23269,20 +23231,20 @@
       <c r="P36" s="68"/>
       <c r="Q36" s="68"/>
       <c r="R36" s="68"/>
-      <c r="S36" s="172"/>
-      <c r="T36" s="173"/>
-      <c r="U36" s="173"/>
-      <c r="V36" s="173"/>
-      <c r="W36" s="173"/>
-      <c r="X36" s="173"/>
-      <c r="Y36" s="173"/>
-      <c r="Z36" s="173"/>
-      <c r="AA36" s="173"/>
-      <c r="AB36" s="173"/>
-      <c r="AC36" s="173"/>
-      <c r="AD36" s="173"/>
-      <c r="AE36" s="173"/>
-      <c r="AF36" s="174"/>
+      <c r="S36" s="122"/>
+      <c r="T36" s="120"/>
+      <c r="U36" s="120"/>
+      <c r="V36" s="120"/>
+      <c r="W36" s="120"/>
+      <c r="X36" s="120"/>
+      <c r="Y36" s="120"/>
+      <c r="Z36" s="120"/>
+      <c r="AA36" s="120"/>
+      <c r="AB36" s="120"/>
+      <c r="AC36" s="120"/>
+      <c r="AD36" s="120"/>
+      <c r="AE36" s="120"/>
+      <c r="AF36" s="121"/>
       <c r="AI36" s="3"/>
       <c r="AJ36" s="3"/>
       <c r="AK36" s="3"/>
@@ -23503,11 +23465,11 @@
       <c r="A37" s="37">
         <v>3</v>
       </c>
-      <c r="B37" s="156"/>
-      <c r="C37" s="157"/>
-      <c r="D37" s="92"/>
+      <c r="B37" s="163"/>
+      <c r="C37" s="164"/>
+      <c r="D37" s="88"/>
       <c r="E37" s="35"/>
-      <c r="F37" s="119"/>
+      <c r="F37" s="117"/>
       <c r="G37" s="68"/>
       <c r="H37" s="68"/>
       <c r="I37" s="68"/>
@@ -23520,20 +23482,20 @@
       <c r="P37" s="68"/>
       <c r="Q37" s="68"/>
       <c r="R37" s="68"/>
-      <c r="S37" s="172"/>
-      <c r="T37" s="173"/>
-      <c r="U37" s="173"/>
-      <c r="V37" s="173"/>
-      <c r="W37" s="173"/>
-      <c r="X37" s="173"/>
-      <c r="Y37" s="173"/>
-      <c r="Z37" s="173"/>
-      <c r="AA37" s="173"/>
-      <c r="AB37" s="173"/>
-      <c r="AC37" s="173"/>
-      <c r="AD37" s="173"/>
-      <c r="AE37" s="173"/>
-      <c r="AF37" s="174"/>
+      <c r="S37" s="122"/>
+      <c r="T37" s="120"/>
+      <c r="U37" s="120"/>
+      <c r="V37" s="120"/>
+      <c r="W37" s="120"/>
+      <c r="X37" s="120"/>
+      <c r="Y37" s="120"/>
+      <c r="Z37" s="120"/>
+      <c r="AA37" s="120"/>
+      <c r="AB37" s="120"/>
+      <c r="AC37" s="120"/>
+      <c r="AD37" s="120"/>
+      <c r="AE37" s="120"/>
+      <c r="AF37" s="121"/>
       <c r="AI37" s="3"/>
       <c r="AJ37" s="3"/>
       <c r="AK37" s="3"/>
@@ -23752,41 +23714,41 @@
     </row>
     <row r="38" spans="1:249" s="2" customFormat="1" ht="42" customHeight="1" thickBot="1">
       <c r="A38" s="41"/>
-      <c r="B38" s="168" t="s">
+      <c r="B38" s="166" t="s">
         <v>63</v>
       </c>
-      <c r="C38" s="169"/>
+      <c r="C38" s="167"/>
       <c r="D38" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="E38" s="95"/>
+      <c r="E38" s="91"/>
       <c r="F38" s="43"/>
-      <c r="G38" s="72"/>
-      <c r="H38" s="72"/>
-      <c r="I38" s="72"/>
-      <c r="J38" s="72"/>
-      <c r="K38" s="72"/>
-      <c r="L38" s="72"/>
-      <c r="M38" s="72"/>
-      <c r="N38" s="72"/>
-      <c r="O38" s="72"/>
-      <c r="P38" s="72"/>
-      <c r="Q38" s="72"/>
-      <c r="R38" s="72"/>
-      <c r="S38" s="72"/>
-      <c r="T38" s="72"/>
-      <c r="U38" s="72"/>
-      <c r="V38" s="72"/>
-      <c r="W38" s="72"/>
-      <c r="X38" s="72"/>
-      <c r="Y38" s="72"/>
-      <c r="Z38" s="72"/>
-      <c r="AA38" s="72"/>
-      <c r="AB38" s="72"/>
-      <c r="AC38" s="72"/>
-      <c r="AD38" s="72"/>
-      <c r="AE38" s="73"/>
-      <c r="AF38" s="74"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="70"/>
+      <c r="L38" s="70"/>
+      <c r="M38" s="70"/>
+      <c r="N38" s="70"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="70"/>
+      <c r="Q38" s="70"/>
+      <c r="R38" s="70"/>
+      <c r="S38" s="113"/>
+      <c r="T38" s="114"/>
+      <c r="U38" s="114"/>
+      <c r="V38" s="114"/>
+      <c r="W38" s="114"/>
+      <c r="X38" s="114"/>
+      <c r="Y38" s="114"/>
+      <c r="Z38" s="114"/>
+      <c r="AA38" s="114"/>
+      <c r="AB38" s="114"/>
+      <c r="AC38" s="114"/>
+      <c r="AD38" s="114"/>
+      <c r="AE38" s="114"/>
+      <c r="AF38" s="115"/>
       <c r="AI38" s="3"/>
       <c r="AJ38" s="3"/>
       <c r="AK38" s="3"/>
@@ -24012,30 +23974,30 @@
       <c r="D39" s="44"/>
       <c r="E39" s="44"/>
       <c r="F39" s="57"/>
-      <c r="G39" s="75"/>
-      <c r="H39" s="180"/>
-      <c r="I39" s="180"/>
-      <c r="J39" s="180"/>
-      <c r="K39" s="180"/>
-      <c r="L39" s="76"/>
-      <c r="M39" s="75"/>
-      <c r="N39" s="180"/>
-      <c r="O39" s="180"/>
-      <c r="P39" s="180"/>
-      <c r="Q39" s="180"/>
-      <c r="R39" s="76"/>
-      <c r="S39" s="75"/>
-      <c r="T39" s="180"/>
-      <c r="U39" s="180"/>
-      <c r="V39" s="180"/>
-      <c r="W39" s="75"/>
-      <c r="X39" s="180"/>
-      <c r="Y39" s="180"/>
-      <c r="Z39" s="180"/>
-      <c r="AA39" s="76"/>
-      <c r="AB39" s="75"/>
-      <c r="AC39" s="180"/>
-      <c r="AD39" s="180"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="165"/>
+      <c r="I39" s="165"/>
+      <c r="J39" s="165"/>
+      <c r="K39" s="165"/>
+      <c r="L39" s="72"/>
+      <c r="M39" s="71"/>
+      <c r="N39" s="165"/>
+      <c r="O39" s="165"/>
+      <c r="P39" s="165"/>
+      <c r="Q39" s="165"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="71"/>
+      <c r="T39" s="165"/>
+      <c r="U39" s="165"/>
+      <c r="V39" s="165"/>
+      <c r="W39" s="71"/>
+      <c r="X39" s="165"/>
+      <c r="Y39" s="165"/>
+      <c r="Z39" s="165"/>
+      <c r="AA39" s="72"/>
+      <c r="AB39" s="71"/>
+      <c r="AC39" s="165"/>
+      <c r="AD39" s="165"/>
       <c r="AE39" s="55"/>
       <c r="AF39" s="56"/>
       <c r="AI39" s="3"/>
@@ -24257,40 +24219,40 @@
     <row r="40" spans="1:249" s="2" customFormat="1" ht="23" hidden="1" customHeight="1">
       <c r="A40" s="45"/>
       <c r="B40" s="46"/>
-      <c r="C40" s="88" t="s">
+      <c r="C40" s="84" t="s">
         <v>27</v>
       </c>
-      <c r="D40" s="90" t="s">
+      <c r="D40" s="86" t="s">
         <v>22</v>
       </c>
-      <c r="E40" s="90"/>
+      <c r="E40" s="86"/>
       <c r="F40" s="58"/>
-      <c r="G40" s="77"/>
-      <c r="H40" s="179"/>
-      <c r="I40" s="179"/>
-      <c r="J40" s="179"/>
-      <c r="K40" s="179"/>
-      <c r="L40" s="78"/>
-      <c r="M40" s="77"/>
-      <c r="N40" s="179"/>
-      <c r="O40" s="179"/>
-      <c r="P40" s="179"/>
-      <c r="Q40" s="179"/>
-      <c r="R40" s="78"/>
-      <c r="S40" s="77"/>
-      <c r="T40" s="179"/>
-      <c r="U40" s="179"/>
-      <c r="V40" s="179"/>
-      <c r="W40" s="77"/>
-      <c r="X40" s="179"/>
-      <c r="Y40" s="179"/>
-      <c r="Z40" s="179"/>
-      <c r="AA40" s="78"/>
-      <c r="AB40" s="77"/>
-      <c r="AC40" s="179"/>
-      <c r="AD40" s="179"/>
+      <c r="G40" s="73"/>
+      <c r="H40" s="168"/>
+      <c r="I40" s="168"/>
+      <c r="J40" s="168"/>
+      <c r="K40" s="168"/>
+      <c r="L40" s="74"/>
+      <c r="M40" s="73"/>
+      <c r="N40" s="168"/>
+      <c r="O40" s="168"/>
+      <c r="P40" s="168"/>
+      <c r="Q40" s="168"/>
+      <c r="R40" s="74"/>
+      <c r="S40" s="73"/>
+      <c r="T40" s="168"/>
+      <c r="U40" s="168"/>
+      <c r="V40" s="168"/>
+      <c r="W40" s="73"/>
+      <c r="X40" s="168"/>
+      <c r="Y40" s="168"/>
+      <c r="Z40" s="168"/>
+      <c r="AA40" s="74"/>
+      <c r="AB40" s="73"/>
+      <c r="AC40" s="168"/>
+      <c r="AD40" s="168"/>
       <c r="AE40" s="61"/>
-      <c r="AF40" s="79"/>
+      <c r="AF40" s="75"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
@@ -24510,40 +24472,40 @@
     <row r="41" spans="1:249" s="2" customFormat="1" ht="23" hidden="1" customHeight="1">
       <c r="A41" s="47"/>
       <c r="B41" s="46"/>
-      <c r="C41" s="89" t="s">
+      <c r="C41" s="85" t="s">
         <v>28</v>
       </c>
-      <c r="D41" s="91" t="s">
+      <c r="D41" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="E41" s="91"/>
+      <c r="E41" s="87"/>
       <c r="F41" s="59"/>
-      <c r="G41" s="77"/>
-      <c r="H41" s="179"/>
-      <c r="I41" s="179"/>
-      <c r="J41" s="179"/>
-      <c r="K41" s="179"/>
-      <c r="L41" s="80"/>
-      <c r="M41" s="77"/>
-      <c r="N41" s="179"/>
-      <c r="O41" s="179"/>
-      <c r="P41" s="179"/>
-      <c r="Q41" s="179"/>
-      <c r="R41" s="80"/>
-      <c r="S41" s="77"/>
-      <c r="T41" s="179"/>
-      <c r="U41" s="179"/>
-      <c r="V41" s="179"/>
-      <c r="W41" s="77"/>
-      <c r="X41" s="179"/>
-      <c r="Y41" s="179"/>
-      <c r="Z41" s="179"/>
-      <c r="AA41" s="80"/>
-      <c r="AB41" s="77"/>
-      <c r="AC41" s="179"/>
-      <c r="AD41" s="179"/>
+      <c r="G41" s="73"/>
+      <c r="H41" s="168"/>
+      <c r="I41" s="168"/>
+      <c r="J41" s="168"/>
+      <c r="K41" s="168"/>
+      <c r="L41" s="76"/>
+      <c r="M41" s="73"/>
+      <c r="N41" s="168"/>
+      <c r="O41" s="168"/>
+      <c r="P41" s="168"/>
+      <c r="Q41" s="168"/>
+      <c r="R41" s="76"/>
+      <c r="S41" s="73"/>
+      <c r="T41" s="168"/>
+      <c r="U41" s="168"/>
+      <c r="V41" s="168"/>
+      <c r="W41" s="73"/>
+      <c r="X41" s="168"/>
+      <c r="Y41" s="168"/>
+      <c r="Z41" s="168"/>
+      <c r="AA41" s="76"/>
+      <c r="AB41" s="73"/>
+      <c r="AC41" s="168"/>
+      <c r="AD41" s="168"/>
       <c r="AE41" s="62"/>
-      <c r="AF41" s="81"/>
+      <c r="AF41" s="77"/>
       <c r="AI41" s="3"/>
       <c r="AJ41" s="3"/>
       <c r="AK41" s="3"/>
@@ -24763,40 +24725,40 @@
     <row r="42" spans="1:249" s="2" customFormat="1" ht="23" hidden="1" customHeight="1">
       <c r="A42" s="48"/>
       <c r="B42" s="46"/>
-      <c r="C42" s="89" t="s">
+      <c r="C42" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="D42" s="91" t="s">
+      <c r="D42" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="91"/>
+      <c r="E42" s="87"/>
       <c r="F42" s="59"/>
-      <c r="G42" s="77"/>
-      <c r="H42" s="179"/>
-      <c r="I42" s="179"/>
-      <c r="J42" s="179"/>
-      <c r="K42" s="179"/>
-      <c r="L42" s="80"/>
-      <c r="M42" s="77"/>
-      <c r="N42" s="179"/>
-      <c r="O42" s="179"/>
-      <c r="P42" s="179"/>
-      <c r="Q42" s="179"/>
-      <c r="R42" s="80"/>
-      <c r="S42" s="77"/>
-      <c r="T42" s="179"/>
-      <c r="U42" s="179"/>
-      <c r="V42" s="179"/>
-      <c r="W42" s="77"/>
-      <c r="X42" s="179"/>
-      <c r="Y42" s="179"/>
-      <c r="Z42" s="179"/>
-      <c r="AA42" s="80"/>
-      <c r="AB42" s="77"/>
-      <c r="AC42" s="179"/>
-      <c r="AD42" s="179"/>
+      <c r="G42" s="73"/>
+      <c r="H42" s="168"/>
+      <c r="I42" s="168"/>
+      <c r="J42" s="168"/>
+      <c r="K42" s="168"/>
+      <c r="L42" s="76"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="168"/>
+      <c r="O42" s="168"/>
+      <c r="P42" s="168"/>
+      <c r="Q42" s="168"/>
+      <c r="R42" s="76"/>
+      <c r="S42" s="73"/>
+      <c r="T42" s="168"/>
+      <c r="U42" s="168"/>
+      <c r="V42" s="168"/>
+      <c r="W42" s="73"/>
+      <c r="X42" s="168"/>
+      <c r="Y42" s="168"/>
+      <c r="Z42" s="168"/>
+      <c r="AA42" s="76"/>
+      <c r="AB42" s="73"/>
+      <c r="AC42" s="168"/>
+      <c r="AD42" s="168"/>
       <c r="AE42" s="62"/>
-      <c r="AF42" s="81"/>
+      <c r="AF42" s="77"/>
       <c r="AI42" s="3"/>
       <c r="AJ42" s="3"/>
       <c r="AK42" s="3"/>
@@ -25020,32 +24982,32 @@
       <c r="D43" s="50"/>
       <c r="E43" s="50"/>
       <c r="F43" s="60"/>
-      <c r="G43" s="82"/>
-      <c r="H43" s="175"/>
-      <c r="I43" s="175"/>
-      <c r="J43" s="175"/>
-      <c r="K43" s="175"/>
-      <c r="L43" s="83"/>
-      <c r="M43" s="82"/>
-      <c r="N43" s="175"/>
-      <c r="O43" s="175"/>
-      <c r="P43" s="175"/>
-      <c r="Q43" s="175"/>
-      <c r="R43" s="83"/>
-      <c r="S43" s="82"/>
-      <c r="T43" s="175"/>
-      <c r="U43" s="175"/>
-      <c r="V43" s="175"/>
-      <c r="W43" s="82"/>
-      <c r="X43" s="175"/>
-      <c r="Y43" s="175"/>
-      <c r="Z43" s="175"/>
-      <c r="AA43" s="83"/>
-      <c r="AB43" s="82"/>
-      <c r="AC43" s="175"/>
-      <c r="AD43" s="175"/>
+      <c r="G43" s="78"/>
+      <c r="H43" s="169"/>
+      <c r="I43" s="169"/>
+      <c r="J43" s="169"/>
+      <c r="K43" s="169"/>
+      <c r="L43" s="79"/>
+      <c r="M43" s="78"/>
+      <c r="N43" s="169"/>
+      <c r="O43" s="169"/>
+      <c r="P43" s="169"/>
+      <c r="Q43" s="169"/>
+      <c r="R43" s="79"/>
+      <c r="S43" s="78"/>
+      <c r="T43" s="169"/>
+      <c r="U43" s="169"/>
+      <c r="V43" s="169"/>
+      <c r="W43" s="78"/>
+      <c r="X43" s="169"/>
+      <c r="Y43" s="169"/>
+      <c r="Z43" s="169"/>
+      <c r="AA43" s="79"/>
+      <c r="AB43" s="78"/>
+      <c r="AC43" s="169"/>
+      <c r="AD43" s="169"/>
       <c r="AE43" s="63"/>
-      <c r="AF43" s="84"/>
+      <c r="AF43" s="80"/>
       <c r="AI43" s="3"/>
       <c r="AJ43" s="3"/>
       <c r="AK43" s="3"/>
@@ -25306,40 +25268,48 @@
       <c r="C50" s="52"/>
     </row>
   </sheetData>
-  <mergeCells count="100">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="F1:AF1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="T3:AF3"/>
-    <mergeCell ref="T5:W7"/>
-    <mergeCell ref="AD4:AF4"/>
-    <mergeCell ref="AD5:AF7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="S11:AF11"/>
-    <mergeCell ref="S12:AF12"/>
-    <mergeCell ref="S13:AF13"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="T4:W4"/>
-    <mergeCell ref="X4:Z4"/>
-    <mergeCell ref="AA4:AC4"/>
-    <mergeCell ref="B11:C11"/>
+  <mergeCells count="157">
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="S32:W32"/>
+    <mergeCell ref="X32:AB32"/>
+    <mergeCell ref="AC32:AF32"/>
+    <mergeCell ref="S33:W33"/>
+    <mergeCell ref="H40:K40"/>
+    <mergeCell ref="N40:Q40"/>
+    <mergeCell ref="T40:V40"/>
+    <mergeCell ref="X40:Z40"/>
+    <mergeCell ref="AC40:AD40"/>
+    <mergeCell ref="H43:K43"/>
+    <mergeCell ref="N43:Q43"/>
+    <mergeCell ref="T43:V43"/>
+    <mergeCell ref="X43:Z43"/>
+    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="N41:Q41"/>
+    <mergeCell ref="H42:K42"/>
+    <mergeCell ref="N42:Q42"/>
+    <mergeCell ref="AC43:AD43"/>
+    <mergeCell ref="T41:V41"/>
+    <mergeCell ref="X41:Z41"/>
+    <mergeCell ref="AC41:AD41"/>
+    <mergeCell ref="T42:V42"/>
+    <mergeCell ref="X42:Z42"/>
+    <mergeCell ref="AC42:AD42"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="AC39:AD39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="H39:K39"/>
+    <mergeCell ref="N39:Q39"/>
+    <mergeCell ref="S37:W37"/>
+    <mergeCell ref="X37:AB37"/>
+    <mergeCell ref="AC37:AF37"/>
+    <mergeCell ref="T39:V39"/>
+    <mergeCell ref="X39:Z39"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B25:C25"/>
-    <mergeCell ref="S14:AF14"/>
-    <mergeCell ref="S15:AF15"/>
-    <mergeCell ref="S16:AF16"/>
-    <mergeCell ref="S17:AF17"/>
-    <mergeCell ref="S18:AF18"/>
-    <mergeCell ref="S19:AF19"/>
-    <mergeCell ref="S25:AF25"/>
-    <mergeCell ref="S24:AF24"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
@@ -25356,61 +25326,110 @@
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="F35:F37"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="AC39:AD39"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="H39:K39"/>
-    <mergeCell ref="N39:Q39"/>
-    <mergeCell ref="S36:AF36"/>
-    <mergeCell ref="S37:AF37"/>
-    <mergeCell ref="H40:K40"/>
-    <mergeCell ref="N40:Q40"/>
-    <mergeCell ref="T40:V40"/>
-    <mergeCell ref="X40:Z40"/>
-    <mergeCell ref="AC40:AD40"/>
-    <mergeCell ref="H43:K43"/>
-    <mergeCell ref="N43:Q43"/>
-    <mergeCell ref="T43:V43"/>
-    <mergeCell ref="X43:Z43"/>
-    <mergeCell ref="H41:K41"/>
-    <mergeCell ref="N41:Q41"/>
-    <mergeCell ref="H42:K42"/>
-    <mergeCell ref="N42:Q42"/>
-    <mergeCell ref="AC43:AD43"/>
-    <mergeCell ref="S9:AF9"/>
-    <mergeCell ref="S20:AF20"/>
-    <mergeCell ref="S21:AF21"/>
-    <mergeCell ref="S22:AF22"/>
-    <mergeCell ref="S23:AF23"/>
-    <mergeCell ref="T41:V41"/>
-    <mergeCell ref="X41:Z41"/>
-    <mergeCell ref="AC41:AD41"/>
-    <mergeCell ref="T42:V42"/>
-    <mergeCell ref="X42:Z42"/>
-    <mergeCell ref="AC42:AD42"/>
-    <mergeCell ref="T39:V39"/>
-    <mergeCell ref="X39:Z39"/>
-    <mergeCell ref="S34:AF34"/>
-    <mergeCell ref="S35:AF35"/>
-    <mergeCell ref="S26:AF26"/>
-    <mergeCell ref="S28:AF28"/>
-    <mergeCell ref="S29:AF29"/>
-    <mergeCell ref="S30:AF30"/>
-    <mergeCell ref="S31:AF31"/>
-    <mergeCell ref="S27:AF27"/>
-    <mergeCell ref="S32:AF32"/>
-    <mergeCell ref="S33:AF33"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="T4:W4"/>
+    <mergeCell ref="X4:Z4"/>
+    <mergeCell ref="AA4:AC4"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="S9:AF9"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:AF1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="T3:AF3"/>
+    <mergeCell ref="T5:W7"/>
+    <mergeCell ref="AD4:AF4"/>
+    <mergeCell ref="AD5:AF7"/>
+    <mergeCell ref="AC11:AF11"/>
+    <mergeCell ref="S11:W11"/>
+    <mergeCell ref="X11:AB11"/>
+    <mergeCell ref="AC12:AF12"/>
+    <mergeCell ref="X12:AB12"/>
+    <mergeCell ref="S12:W12"/>
+    <mergeCell ref="S13:W13"/>
+    <mergeCell ref="X13:AB13"/>
+    <mergeCell ref="AC13:AF13"/>
+    <mergeCell ref="S14:W14"/>
+    <mergeCell ref="X14:AB14"/>
+    <mergeCell ref="AC14:AF14"/>
+    <mergeCell ref="S15:W15"/>
+    <mergeCell ref="X15:AB15"/>
+    <mergeCell ref="AC15:AF15"/>
+    <mergeCell ref="S16:W16"/>
+    <mergeCell ref="X16:AB16"/>
+    <mergeCell ref="AC16:AF16"/>
+    <mergeCell ref="S17:W17"/>
+    <mergeCell ref="X17:AB17"/>
+    <mergeCell ref="AC17:AF17"/>
+    <mergeCell ref="S18:W18"/>
+    <mergeCell ref="X18:AB18"/>
+    <mergeCell ref="AC18:AF18"/>
+    <mergeCell ref="S19:W19"/>
+    <mergeCell ref="X19:AB19"/>
+    <mergeCell ref="AC19:AF19"/>
+    <mergeCell ref="S20:W20"/>
+    <mergeCell ref="X20:AB20"/>
+    <mergeCell ref="AC20:AF20"/>
+    <mergeCell ref="S21:W21"/>
+    <mergeCell ref="X21:AB21"/>
+    <mergeCell ref="AC21:AF21"/>
+    <mergeCell ref="S22:W22"/>
+    <mergeCell ref="X22:AB22"/>
+    <mergeCell ref="AC22:AF22"/>
+    <mergeCell ref="X27:AB27"/>
+    <mergeCell ref="AC27:AF27"/>
+    <mergeCell ref="S35:W35"/>
+    <mergeCell ref="X35:AB35"/>
+    <mergeCell ref="AC35:AF35"/>
+    <mergeCell ref="S36:W36"/>
+    <mergeCell ref="X36:AB36"/>
+    <mergeCell ref="AC36:AF36"/>
+    <mergeCell ref="S23:W23"/>
+    <mergeCell ref="X23:AB23"/>
+    <mergeCell ref="AC23:AF23"/>
+    <mergeCell ref="S24:W24"/>
+    <mergeCell ref="X24:AB24"/>
+    <mergeCell ref="AC24:AF24"/>
+    <mergeCell ref="S25:W25"/>
+    <mergeCell ref="X25:AB25"/>
+    <mergeCell ref="AC25:AF25"/>
+    <mergeCell ref="F12:F19"/>
+    <mergeCell ref="F21:F28"/>
+    <mergeCell ref="F31:F33"/>
+    <mergeCell ref="X33:AB33"/>
+    <mergeCell ref="AC33:AF33"/>
+    <mergeCell ref="S34:W34"/>
+    <mergeCell ref="X34:AB34"/>
+    <mergeCell ref="AC34:AF34"/>
+    <mergeCell ref="S30:W30"/>
+    <mergeCell ref="X30:AB30"/>
+    <mergeCell ref="AC30:AF30"/>
+    <mergeCell ref="S31:W31"/>
+    <mergeCell ref="X31:AB31"/>
+    <mergeCell ref="AC31:AF31"/>
+    <mergeCell ref="S28:W28"/>
+    <mergeCell ref="X28:AB28"/>
+    <mergeCell ref="AC28:AF28"/>
+    <mergeCell ref="S29:W29"/>
+    <mergeCell ref="X29:AB29"/>
+    <mergeCell ref="AC29:AF29"/>
+    <mergeCell ref="S26:W26"/>
+    <mergeCell ref="X26:AB26"/>
+    <mergeCell ref="AC26:AF26"/>
+    <mergeCell ref="S27:W27"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
-  <conditionalFormatting sqref="G11:R19 AG11:AK19">
-    <cfRule type="expression" dxfId="9" priority="1">
+  <conditionalFormatting sqref="G11:R19">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>TEXT(G11,"aaa")="日"</formula>
     </cfRule>
   </conditionalFormatting>
